--- a/RSC 08.0000.25 - Relatório de Serviço de Campo - Padrão - Rev.38.xlsx
+++ b/RSC 08.0000.25 - Relatório de Serviço de Campo - Padrão - Rev.38.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPasta_de_trabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ktsabr.sharepoint.com/sites/ISO9001/Shared Documents/General/SGQ_KTSA_ISO 9001_2015/1 DOCUMENTOS SGQ/9_FR FORMULÁRIOS E REGISTROS/Engenharia/RSC - Relatório de Serviço de Campo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ktsabr-my.sharepoint.com/personal/gustavo_arruda_ktsa_com_br/Documents/PROJETOS/Engenharia/RSC - Relatório de Serviço de Campo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{F948FEA9-3545-4234-B576-12B0A63E47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DA45396-0DE3-462E-9496-A15C9FF405C3}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{F948FEA9-3545-4234-B576-12B0A63E47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{354B54C3-8341-42D5-BFC4-9813F2A749B8}"/>
   <bookViews>
-    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" tabRatio="688" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Frente - Relatório de SC - 1" sheetId="4" r:id="rId1"/>
@@ -2688,7 +2688,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="48">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -3269,6 +3269,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3280,7 +3325,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="287">
+  <cellXfs count="290">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3498,67 +3543,468 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3586,409 +4032,38 @@
     <xf numFmtId="164" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4004,39 +4079,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4103,6 +4145,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5163,14 +5217,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="168"/>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="170"/>
+      <c r="A1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="139"/>
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
       <c r="K1" s="21"/>
@@ -5207,87 +5261,87 @@
       <c r="AP1" s="22"/>
       <c r="AQ1" s="22"/>
       <c r="AR1" s="22"/>
-      <c r="AS1" s="177" t="s">
+      <c r="AS1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="AT1" s="178"/>
-      <c r="AU1" s="178"/>
-      <c r="AV1" s="178"/>
-      <c r="AW1" s="178"/>
-      <c r="AX1" s="178"/>
-      <c r="AY1" s="178"/>
-      <c r="AZ1" s="179"/>
+      <c r="AT1" s="147"/>
+      <c r="AU1" s="147"/>
+      <c r="AV1" s="147"/>
+      <c r="AW1" s="147"/>
+      <c r="AX1" s="147"/>
+      <c r="AY1" s="147"/>
+      <c r="AZ1" s="148"/>
       <c r="BD1" s="23"/>
       <c r="BF1" s="27"/>
       <c r="BG1" s="27"/>
     </row>
     <row r="2" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="171"/>
-      <c r="B2" s="172"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="173"/>
-      <c r="K2" s="187" t="s">
+      <c r="A2" s="140"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="142"/>
+      <c r="K2" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="188"/>
-      <c r="M2" s="188"/>
-      <c r="N2" s="188"/>
-      <c r="O2" s="188"/>
-      <c r="P2" s="188"/>
-      <c r="Q2" s="188"/>
-      <c r="R2" s="188"/>
-      <c r="S2" s="188"/>
-      <c r="T2" s="188"/>
-      <c r="U2" s="188"/>
-      <c r="V2" s="188"/>
-      <c r="W2" s="188"/>
-      <c r="X2" s="188"/>
-      <c r="Y2" s="188"/>
-      <c r="Z2" s="188"/>
-      <c r="AA2" s="188"/>
-      <c r="AB2" s="188"/>
-      <c r="AC2" s="188"/>
-      <c r="AD2" s="188"/>
-      <c r="AE2" s="188"/>
-      <c r="AF2" s="188"/>
-      <c r="AG2" s="188"/>
-      <c r="AH2" s="188"/>
-      <c r="AI2" s="188"/>
-      <c r="AJ2" s="188"/>
-      <c r="AK2" s="188"/>
-      <c r="AL2" s="188"/>
-      <c r="AM2" s="188"/>
-      <c r="AN2" s="188"/>
-      <c r="AO2" s="188"/>
-      <c r="AP2" s="188"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="157"/>
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="157"/>
+      <c r="U2" s="157"/>
+      <c r="V2" s="157"/>
+      <c r="W2" s="157"/>
+      <c r="X2" s="157"/>
+      <c r="Y2" s="157"/>
+      <c r="Z2" s="157"/>
+      <c r="AA2" s="157"/>
+      <c r="AB2" s="157"/>
+      <c r="AC2" s="157"/>
+      <c r="AD2" s="157"/>
+      <c r="AE2" s="157"/>
+      <c r="AF2" s="157"/>
+      <c r="AG2" s="157"/>
+      <c r="AH2" s="157"/>
+      <c r="AI2" s="157"/>
+      <c r="AJ2" s="157"/>
+      <c r="AK2" s="157"/>
+      <c r="AL2" s="157"/>
+      <c r="AM2" s="157"/>
+      <c r="AN2" s="157"/>
+      <c r="AO2" s="157"/>
+      <c r="AP2" s="157"/>
       <c r="AQ2" s="17"/>
       <c r="AR2" s="17"/>
-      <c r="AS2" s="180"/>
-      <c r="AT2" s="181"/>
-      <c r="AU2" s="181"/>
-      <c r="AV2" s="181"/>
-      <c r="AW2" s="181"/>
-      <c r="AX2" s="181"/>
-      <c r="AY2" s="181"/>
-      <c r="AZ2" s="182"/>
+      <c r="AS2" s="149"/>
+      <c r="AT2" s="150"/>
+      <c r="AU2" s="150"/>
+      <c r="AV2" s="150"/>
+      <c r="AW2" s="150"/>
+      <c r="AX2" s="150"/>
+      <c r="AY2" s="150"/>
+      <c r="AZ2" s="151"/>
       <c r="BA2" s="7"/>
       <c r="BF2" s="25"/>
       <c r="BG2" s="25"/>
       <c r="BH2" s="25"/>
     </row>
     <row r="3" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="174"/>
-      <c r="B3" s="175"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="176"/>
+      <c r="A3" s="143"/>
+      <c r="B3" s="144"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="145"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -5324,392 +5378,392 @@
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
       <c r="AR3" s="4"/>
-      <c r="AS3" s="183"/>
-      <c r="AT3" s="184"/>
-      <c r="AU3" s="184"/>
-      <c r="AV3" s="184"/>
-      <c r="AW3" s="184"/>
-      <c r="AX3" s="184"/>
-      <c r="AY3" s="184"/>
-      <c r="AZ3" s="185"/>
+      <c r="AS3" s="152"/>
+      <c r="AT3" s="153"/>
+      <c r="AU3" s="153"/>
+      <c r="AV3" s="153"/>
+      <c r="AW3" s="153"/>
+      <c r="AX3" s="153"/>
+      <c r="AY3" s="153"/>
+      <c r="AZ3" s="154"/>
     </row>
     <row r="4" spans="1:60" s="3" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="189" t="s">
+      <c r="A4" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="190"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="190"/>
-      <c r="K4" s="190"/>
-      <c r="L4" s="190"/>
-      <c r="M4" s="190"/>
-      <c r="N4" s="190"/>
-      <c r="O4" s="190"/>
-      <c r="P4" s="190"/>
-      <c r="Q4" s="190"/>
-      <c r="R4" s="190"/>
-      <c r="S4" s="190"/>
-      <c r="T4" s="190"/>
-      <c r="U4" s="190"/>
-      <c r="V4" s="190"/>
-      <c r="W4" s="190"/>
-      <c r="X4" s="190"/>
-      <c r="Y4" s="190"/>
-      <c r="Z4" s="190"/>
-      <c r="AA4" s="190"/>
-      <c r="AB4" s="190"/>
-      <c r="AC4" s="190"/>
-      <c r="AD4" s="190"/>
-      <c r="AE4" s="190"/>
-      <c r="AF4" s="190"/>
-      <c r="AG4" s="190"/>
-      <c r="AH4" s="190"/>
-      <c r="AI4" s="190"/>
-      <c r="AJ4" s="190"/>
-      <c r="AK4" s="190"/>
-      <c r="AL4" s="190"/>
-      <c r="AM4" s="190"/>
-      <c r="AN4" s="190"/>
-      <c r="AO4" s="190"/>
-      <c r="AP4" s="190"/>
-      <c r="AQ4" s="190"/>
-      <c r="AR4" s="190"/>
-      <c r="AS4" s="190"/>
-      <c r="AT4" s="190"/>
-      <c r="AU4" s="190"/>
-      <c r="AV4" s="190"/>
-      <c r="AW4" s="190"/>
-      <c r="AX4" s="190"/>
-      <c r="AY4" s="190"/>
-      <c r="AZ4" s="191"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="101"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="101"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="101"/>
+      <c r="S4" s="101"/>
+      <c r="T4" s="101"/>
+      <c r="U4" s="101"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="101"/>
+      <c r="X4" s="101"/>
+      <c r="Y4" s="101"/>
+      <c r="Z4" s="101"/>
+      <c r="AA4" s="101"/>
+      <c r="AB4" s="101"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="101"/>
+      <c r="AE4" s="101"/>
+      <c r="AF4" s="101"/>
+      <c r="AG4" s="101"/>
+      <c r="AH4" s="101"/>
+      <c r="AI4" s="101"/>
+      <c r="AJ4" s="101"/>
+      <c r="AK4" s="101"/>
+      <c r="AL4" s="101"/>
+      <c r="AM4" s="101"/>
+      <c r="AN4" s="101"/>
+      <c r="AO4" s="101"/>
+      <c r="AP4" s="101"/>
+      <c r="AQ4" s="101"/>
+      <c r="AR4" s="101"/>
+      <c r="AS4" s="101"/>
+      <c r="AT4" s="101"/>
+      <c r="AU4" s="101"/>
+      <c r="AV4" s="101"/>
+      <c r="AW4" s="101"/>
+      <c r="AX4" s="101"/>
+      <c r="AY4" s="101"/>
+      <c r="AZ4" s="102"/>
       <c r="BA4" s="9"/>
       <c r="BB4" s="9"/>
       <c r="BC4" s="9"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="195" t="s">
+      <c r="A5" s="161" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="196"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="196"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="201"/>
-      <c r="H5" s="201"/>
-      <c r="I5" s="201"/>
-      <c r="J5" s="201"/>
-      <c r="K5" s="201"/>
-      <c r="L5" s="201"/>
-      <c r="M5" s="201"/>
-      <c r="N5" s="201"/>
-      <c r="O5" s="201"/>
-      <c r="P5" s="201"/>
-      <c r="Q5" s="201"/>
-      <c r="R5" s="201"/>
-      <c r="S5" s="201"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="201"/>
-      <c r="V5" s="201"/>
-      <c r="W5" s="201"/>
-      <c r="X5" s="201"/>
-      <c r="Y5" s="201"/>
-      <c r="Z5" s="201"/>
-      <c r="AA5" s="201"/>
-      <c r="AB5" s="201"/>
+      <c r="B5" s="162"/>
+      <c r="C5" s="162"/>
+      <c r="D5" s="162"/>
+      <c r="E5" s="162"/>
+      <c r="F5" s="162"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="171"/>
+      <c r="J5" s="171"/>
+      <c r="K5" s="171"/>
+      <c r="L5" s="171"/>
+      <c r="M5" s="171"/>
+      <c r="N5" s="171"/>
+      <c r="O5" s="171"/>
+      <c r="P5" s="171"/>
+      <c r="Q5" s="171"/>
+      <c r="R5" s="171"/>
+      <c r="S5" s="171"/>
+      <c r="T5" s="171"/>
+      <c r="U5" s="171"/>
+      <c r="V5" s="171"/>
+      <c r="W5" s="171"/>
+      <c r="X5" s="171"/>
+      <c r="Y5" s="171"/>
+      <c r="Z5" s="171"/>
+      <c r="AA5" s="171"/>
+      <c r="AB5" s="171"/>
       <c r="AC5" s="55"/>
       <c r="AD5" s="58"/>
-      <c r="AE5" s="106" t="s">
+      <c r="AE5" s="170" t="s">
         <v>5</v>
       </c>
-      <c r="AF5" s="106"/>
-      <c r="AG5" s="106"/>
-      <c r="AH5" s="106"/>
-      <c r="AI5" s="106"/>
-      <c r="AJ5" s="106"/>
-      <c r="AK5" s="106"/>
-      <c r="AL5" s="208"/>
-      <c r="AM5" s="208"/>
-      <c r="AN5" s="208"/>
-      <c r="AO5" s="208"/>
-      <c r="AP5" s="208"/>
-      <c r="AQ5" s="208"/>
-      <c r="AR5" s="208"/>
-      <c r="AS5" s="208"/>
-      <c r="AT5" s="208"/>
-      <c r="AU5" s="208"/>
-      <c r="AV5" s="208"/>
-      <c r="AW5" s="208"/>
-      <c r="AX5" s="208"/>
-      <c r="AY5" s="208"/>
-      <c r="AZ5" s="209"/>
+      <c r="AF5" s="170"/>
+      <c r="AG5" s="170"/>
+      <c r="AH5" s="170"/>
+      <c r="AI5" s="170"/>
+      <c r="AJ5" s="170"/>
+      <c r="AK5" s="170"/>
+      <c r="AL5" s="181"/>
+      <c r="AM5" s="181"/>
+      <c r="AN5" s="181"/>
+      <c r="AO5" s="181"/>
+      <c r="AP5" s="181"/>
+      <c r="AQ5" s="181"/>
+      <c r="AR5" s="181"/>
+      <c r="AS5" s="181"/>
+      <c r="AT5" s="181"/>
+      <c r="AU5" s="181"/>
+      <c r="AV5" s="181"/>
+      <c r="AW5" s="181"/>
+      <c r="AX5" s="181"/>
+      <c r="AY5" s="181"/>
+      <c r="AZ5" s="182"/>
       <c r="BA5"/>
       <c r="BB5" s="9"/>
       <c r="BC5" s="9"/>
       <c r="BD5" s="9"/>
     </row>
     <row r="6" spans="1:60" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="195" t="s">
+      <c r="A6" s="161" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="196"/>
-      <c r="C6" s="196"/>
-      <c r="D6" s="196"/>
-      <c r="E6" s="196"/>
-      <c r="F6" s="196"/>
-      <c r="G6" s="91" t="str">
+      <c r="B6" s="162"/>
+      <c r="C6" s="162"/>
+      <c r="D6" s="162"/>
+      <c r="E6" s="162"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="136" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,4,0))</f>
         <v/>
       </c>
-      <c r="H6" s="91"/>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
-      <c r="K6" s="91"/>
-      <c r="L6" s="91"/>
-      <c r="M6" s="91"/>
-      <c r="N6" s="91"/>
-      <c r="O6" s="91"/>
-      <c r="P6" s="91"/>
-      <c r="Q6" s="91"/>
-      <c r="R6" s="91"/>
-      <c r="S6" s="91"/>
-      <c r="T6" s="91"/>
-      <c r="U6" s="91"/>
-      <c r="V6" s="91"/>
-      <c r="W6" s="91"/>
-      <c r="X6" s="91"/>
-      <c r="Y6" s="91"/>
-      <c r="Z6" s="91"/>
-      <c r="AA6" s="91"/>
-      <c r="AB6" s="91"/>
-      <c r="AC6" s="91"/>
-      <c r="AD6" s="91"/>
-      <c r="AE6" s="91"/>
-      <c r="AF6" s="91"/>
-      <c r="AG6" s="91"/>
-      <c r="AH6" s="91"/>
-      <c r="AI6" s="91"/>
-      <c r="AJ6" s="91"/>
-      <c r="AK6" s="91"/>
-      <c r="AL6" s="91"/>
-      <c r="AM6" s="91"/>
-      <c r="AN6" s="91"/>
-      <c r="AO6" s="91"/>
-      <c r="AP6" s="91"/>
-      <c r="AQ6" s="91"/>
-      <c r="AR6" s="91"/>
-      <c r="AS6" s="91"/>
-      <c r="AT6" s="91"/>
-      <c r="AU6" s="91"/>
-      <c r="AV6" s="91"/>
-      <c r="AW6" s="91"/>
-      <c r="AX6" s="91"/>
-      <c r="AY6" s="91"/>
-      <c r="AZ6" s="186"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
+      <c r="N6" s="136"/>
+      <c r="O6" s="136"/>
+      <c r="P6" s="136"/>
+      <c r="Q6" s="136"/>
+      <c r="R6" s="136"/>
+      <c r="S6" s="136"/>
+      <c r="T6" s="136"/>
+      <c r="U6" s="136"/>
+      <c r="V6" s="136"/>
+      <c r="W6" s="136"/>
+      <c r="X6" s="136"/>
+      <c r="Y6" s="136"/>
+      <c r="Z6" s="136"/>
+      <c r="AA6" s="136"/>
+      <c r="AB6" s="136"/>
+      <c r="AC6" s="136"/>
+      <c r="AD6" s="136"/>
+      <c r="AE6" s="136"/>
+      <c r="AF6" s="136"/>
+      <c r="AG6" s="136"/>
+      <c r="AH6" s="136"/>
+      <c r="AI6" s="136"/>
+      <c r="AJ6" s="136"/>
+      <c r="AK6" s="136"/>
+      <c r="AL6" s="136"/>
+      <c r="AM6" s="136"/>
+      <c r="AN6" s="136"/>
+      <c r="AO6" s="136"/>
+      <c r="AP6" s="136"/>
+      <c r="AQ6" s="136"/>
+      <c r="AR6" s="136"/>
+      <c r="AS6" s="136"/>
+      <c r="AT6" s="136"/>
+      <c r="AU6" s="136"/>
+      <c r="AV6" s="136"/>
+      <c r="AW6" s="136"/>
+      <c r="AX6" s="136"/>
+      <c r="AY6" s="136"/>
+      <c r="AZ6" s="155"/>
     </row>
     <row r="7" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="195" t="s">
+      <c r="A7" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="196"/>
-      <c r="C7" s="196"/>
-      <c r="D7" s="196"/>
-      <c r="E7" s="196"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="91" t="str">
+      <c r="B7" s="162"/>
+      <c r="C7" s="162"/>
+      <c r="D7" s="162"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="136" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,5,0))</f>
         <v/>
       </c>
-      <c r="H7" s="91"/>
-      <c r="I7" s="91"/>
-      <c r="J7" s="91"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="91"/>
-      <c r="N7" s="91"/>
-      <c r="O7" s="91"/>
-      <c r="P7" s="91"/>
-      <c r="Q7" s="91"/>
-      <c r="R7" s="91"/>
-      <c r="S7" s="91"/>
-      <c r="T7" s="91"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="136"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="136"/>
+      <c r="P7" s="136"/>
+      <c r="Q7" s="136"/>
+      <c r="R7" s="136"/>
+      <c r="S7" s="136"/>
+      <c r="T7" s="136"/>
       <c r="U7" s="57"/>
-      <c r="V7" s="161" t="s">
+      <c r="V7" s="176" t="s">
         <v>8</v>
       </c>
-      <c r="W7" s="161"/>
-      <c r="X7" s="161"/>
-      <c r="Y7" s="161"/>
-      <c r="Z7" s="91" t="str">
+      <c r="W7" s="176"/>
+      <c r="X7" s="176"/>
+      <c r="Y7" s="176"/>
+      <c r="Z7" s="136" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,2,0))</f>
         <v/>
       </c>
-      <c r="AA7" s="91"/>
-      <c r="AB7" s="91"/>
-      <c r="AC7" s="91"/>
-      <c r="AD7" s="91"/>
-      <c r="AE7" s="91"/>
-      <c r="AF7" s="91"/>
-      <c r="AG7" s="91"/>
-      <c r="AH7" s="91"/>
-      <c r="AI7" s="91"/>
-      <c r="AJ7" s="91"/>
-      <c r="AK7" s="91"/>
-      <c r="AL7" s="91"/>
-      <c r="AM7" s="91"/>
-      <c r="AN7" s="91"/>
-      <c r="AO7" s="91"/>
-      <c r="AP7" s="91"/>
+      <c r="AA7" s="136"/>
+      <c r="AB7" s="136"/>
+      <c r="AC7" s="136"/>
+      <c r="AD7" s="136"/>
+      <c r="AE7" s="136"/>
+      <c r="AF7" s="136"/>
+      <c r="AG7" s="136"/>
+      <c r="AH7" s="136"/>
+      <c r="AI7" s="136"/>
+      <c r="AJ7" s="136"/>
+      <c r="AK7" s="136"/>
+      <c r="AL7" s="136"/>
+      <c r="AM7" s="136"/>
+      <c r="AN7" s="136"/>
+      <c r="AO7" s="136"/>
+      <c r="AP7" s="136"/>
       <c r="AQ7" s="57"/>
-      <c r="AR7" s="161" t="s">
+      <c r="AR7" s="176" t="s">
         <v>9</v>
       </c>
-      <c r="AS7" s="161"/>
-      <c r="AT7" s="161"/>
-      <c r="AU7" s="161"/>
-      <c r="AV7" s="104" t="str">
+      <c r="AS7" s="176"/>
+      <c r="AT7" s="176"/>
+      <c r="AU7" s="176"/>
+      <c r="AV7" s="187" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,3,0))</f>
         <v/>
       </c>
-      <c r="AW7" s="104"/>
-      <c r="AX7" s="104"/>
-      <c r="AY7" s="104"/>
-      <c r="AZ7" s="105"/>
+      <c r="AW7" s="187"/>
+      <c r="AX7" s="187"/>
+      <c r="AY7" s="187"/>
+      <c r="AZ7" s="188"/>
       <c r="BA7"/>
     </row>
     <row r="8" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="202" t="s">
+      <c r="A8" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="203"/>
-      <c r="C8" s="203"/>
-      <c r="D8" s="203"/>
-      <c r="E8" s="203"/>
-      <c r="F8" s="203"/>
-      <c r="G8" s="204" t="str">
+      <c r="B8" s="173"/>
+      <c r="C8" s="173"/>
+      <c r="D8" s="173"/>
+      <c r="E8" s="173"/>
+      <c r="F8" s="173"/>
+      <c r="G8" s="174" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,6,0))</f>
         <v/>
       </c>
-      <c r="H8" s="205"/>
-      <c r="I8" s="205"/>
-      <c r="J8" s="205"/>
-      <c r="K8" s="205"/>
-      <c r="L8" s="205"/>
-      <c r="M8" s="205"/>
-      <c r="N8" s="205"/>
-      <c r="O8" s="205"/>
-      <c r="P8" s="205"/>
-      <c r="Q8" s="205"/>
-      <c r="R8" s="205"/>
-      <c r="S8" s="205"/>
-      <c r="T8" s="205"/>
-      <c r="U8" s="205"/>
-      <c r="V8" s="205"/>
-      <c r="W8" s="205"/>
-      <c r="X8" s="205"/>
-      <c r="Y8" s="205"/>
-      <c r="Z8" s="205"/>
-      <c r="AA8" s="205"/>
-      <c r="AB8" s="205"/>
-      <c r="AC8" s="205"/>
+      <c r="H8" s="175"/>
+      <c r="I8" s="175"/>
+      <c r="J8" s="175"/>
+      <c r="K8" s="175"/>
+      <c r="L8" s="175"/>
+      <c r="M8" s="175"/>
+      <c r="N8" s="175"/>
+      <c r="O8" s="175"/>
+      <c r="P8" s="175"/>
+      <c r="Q8" s="175"/>
+      <c r="R8" s="175"/>
+      <c r="S8" s="175"/>
+      <c r="T8" s="175"/>
+      <c r="U8" s="175"/>
+      <c r="V8" s="175"/>
+      <c r="W8" s="175"/>
+      <c r="X8" s="175"/>
+      <c r="Y8" s="175"/>
+      <c r="Z8" s="175"/>
+      <c r="AA8" s="175"/>
+      <c r="AB8" s="175"/>
+      <c r="AC8" s="175"/>
       <c r="AD8" s="59"/>
-      <c r="AE8" s="162" t="s">
+      <c r="AE8" s="186" t="s">
         <v>13</v>
       </c>
-      <c r="AF8" s="162"/>
-      <c r="AG8" s="162"/>
-      <c r="AH8" s="162"/>
-      <c r="AI8" s="162"/>
-      <c r="AJ8" s="162"/>
-      <c r="AK8" s="162"/>
-      <c r="AL8" s="93" t="str">
+      <c r="AF8" s="186"/>
+      <c r="AG8" s="186"/>
+      <c r="AH8" s="186"/>
+      <c r="AI8" s="186"/>
+      <c r="AJ8" s="186"/>
+      <c r="AK8" s="186"/>
+      <c r="AL8" s="179" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,7,0))</f>
         <v/>
       </c>
-      <c r="AM8" s="93"/>
-      <c r="AN8" s="93"/>
-      <c r="AO8" s="93"/>
-      <c r="AP8" s="93"/>
-      <c r="AQ8" s="93"/>
-      <c r="AR8" s="93"/>
-      <c r="AS8" s="93"/>
-      <c r="AT8" s="93"/>
-      <c r="AU8" s="93"/>
-      <c r="AV8" s="93"/>
-      <c r="AW8" s="93"/>
-      <c r="AX8" s="93"/>
-      <c r="AY8" s="93"/>
-      <c r="AZ8" s="94"/>
+      <c r="AM8" s="179"/>
+      <c r="AN8" s="179"/>
+      <c r="AO8" s="179"/>
+      <c r="AP8" s="179"/>
+      <c r="AQ8" s="179"/>
+      <c r="AR8" s="179"/>
+      <c r="AS8" s="179"/>
+      <c r="AT8" s="179"/>
+      <c r="AU8" s="179"/>
+      <c r="AV8" s="179"/>
+      <c r="AW8" s="179"/>
+      <c r="AX8" s="179"/>
+      <c r="AY8" s="179"/>
+      <c r="AZ8" s="180"/>
     </row>
     <row r="9" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="202" t="s">
+      <c r="A9" s="172" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="203"/>
-      <c r="C9" s="203"/>
-      <c r="D9" s="203"/>
-      <c r="E9" s="203"/>
-      <c r="F9" s="203"/>
-      <c r="G9" s="206" t="str">
+      <c r="B9" s="173"/>
+      <c r="C9" s="173"/>
+      <c r="D9" s="173"/>
+      <c r="E9" s="173"/>
+      <c r="F9" s="173"/>
+      <c r="G9" s="177" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,8,0))</f>
         <v/>
       </c>
-      <c r="H9" s="207"/>
-      <c r="I9" s="207"/>
-      <c r="J9" s="207"/>
-      <c r="K9" s="207"/>
-      <c r="L9" s="207"/>
-      <c r="M9" s="207"/>
-      <c r="N9" s="207"/>
-      <c r="O9" s="207"/>
-      <c r="P9" s="207"/>
-      <c r="Q9" s="207"/>
-      <c r="R9" s="207"/>
-      <c r="S9" s="207"/>
-      <c r="T9" s="207"/>
-      <c r="U9" s="207"/>
-      <c r="V9" s="207"/>
-      <c r="W9" s="207"/>
-      <c r="X9" s="207"/>
-      <c r="Y9" s="207"/>
-      <c r="Z9" s="207"/>
-      <c r="AA9" s="207"/>
-      <c r="AB9" s="207"/>
-      <c r="AC9" s="207"/>
+      <c r="H9" s="178"/>
+      <c r="I9" s="178"/>
+      <c r="J9" s="178"/>
+      <c r="K9" s="178"/>
+      <c r="L9" s="178"/>
+      <c r="M9" s="178"/>
+      <c r="N9" s="178"/>
+      <c r="O9" s="178"/>
+      <c r="P9" s="178"/>
+      <c r="Q9" s="178"/>
+      <c r="R9" s="178"/>
+      <c r="S9" s="178"/>
+      <c r="T9" s="178"/>
+      <c r="U9" s="178"/>
+      <c r="V9" s="178"/>
+      <c r="W9" s="178"/>
+      <c r="X9" s="178"/>
+      <c r="Y9" s="178"/>
+      <c r="Z9" s="178"/>
+      <c r="AA9" s="178"/>
+      <c r="AB9" s="178"/>
+      <c r="AC9" s="178"/>
       <c r="AD9" s="59"/>
-      <c r="AE9" s="106" t="s">
+      <c r="AE9" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="AF9" s="106"/>
-      <c r="AG9" s="106"/>
-      <c r="AH9" s="106"/>
-      <c r="AI9" s="106"/>
-      <c r="AJ9" s="106"/>
-      <c r="AK9" s="106"/>
-      <c r="AL9" s="192" t="str">
+      <c r="AF9" s="170"/>
+      <c r="AG9" s="170"/>
+      <c r="AH9" s="170"/>
+      <c r="AI9" s="170"/>
+      <c r="AJ9" s="170"/>
+      <c r="AK9" s="170"/>
+      <c r="AL9" s="158" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,9,0))</f>
         <v/>
       </c>
-      <c r="AM9" s="193"/>
-      <c r="AN9" s="193"/>
-      <c r="AO9" s="193"/>
-      <c r="AP9" s="193"/>
-      <c r="AQ9" s="193"/>
-      <c r="AR9" s="193"/>
-      <c r="AS9" s="193"/>
-      <c r="AT9" s="193"/>
-      <c r="AU9" s="193"/>
-      <c r="AV9" s="193"/>
-      <c r="AW9" s="193"/>
-      <c r="AX9" s="193"/>
-      <c r="AY9" s="193"/>
-      <c r="AZ9" s="194"/>
+      <c r="AM9" s="159"/>
+      <c r="AN9" s="159"/>
+      <c r="AO9" s="159"/>
+      <c r="AP9" s="159"/>
+      <c r="AQ9" s="159"/>
+      <c r="AR9" s="159"/>
+      <c r="AS9" s="159"/>
+      <c r="AT9" s="159"/>
+      <c r="AU9" s="159"/>
+      <c r="AV9" s="159"/>
+      <c r="AW9" s="159"/>
+      <c r="AX9" s="159"/>
+      <c r="AY9" s="159"/>
+      <c r="AZ9" s="160"/>
     </row>
     <row r="10" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
@@ -5771,48 +5825,48 @@
       <c r="H12" s="59"/>
       <c r="I12" s="59"/>
       <c r="J12" s="59"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="93"/>
-      <c r="N12" s="93"/>
-      <c r="O12" s="93"/>
-      <c r="P12" s="93"/>
-      <c r="Q12" s="93"/>
-      <c r="R12" s="93"/>
-      <c r="S12" s="93"/>
-      <c r="T12" s="93"/>
-      <c r="U12" s="93"/>
-      <c r="V12" s="93"/>
-      <c r="W12" s="93"/>
-      <c r="X12" s="93"/>
-      <c r="Y12" s="93"/>
-      <c r="Z12" s="93"/>
-      <c r="AA12" s="93"/>
-      <c r="AB12" s="93"/>
-      <c r="AC12" s="93"/>
-      <c r="AD12" s="93"/>
-      <c r="AE12" s="93"/>
-      <c r="AF12" s="93"/>
-      <c r="AG12" s="93"/>
-      <c r="AH12" s="93"/>
-      <c r="AI12" s="93"/>
-      <c r="AJ12" s="93"/>
-      <c r="AK12" s="93"/>
-      <c r="AL12" s="93"/>
-      <c r="AM12" s="93"/>
-      <c r="AN12" s="93"/>
-      <c r="AO12" s="93"/>
-      <c r="AP12" s="93"/>
-      <c r="AQ12" s="93"/>
-      <c r="AR12" s="93"/>
-      <c r="AS12" s="93"/>
-      <c r="AT12" s="93"/>
-      <c r="AU12" s="93"/>
-      <c r="AV12" s="93"/>
-      <c r="AW12" s="93"/>
-      <c r="AX12" s="93"/>
-      <c r="AY12" s="93"/>
-      <c r="AZ12" s="94"/>
+      <c r="K12" s="230"/>
+      <c r="L12" s="179"/>
+      <c r="M12" s="179"/>
+      <c r="N12" s="179"/>
+      <c r="O12" s="179"/>
+      <c r="P12" s="179"/>
+      <c r="Q12" s="179"/>
+      <c r="R12" s="179"/>
+      <c r="S12" s="179"/>
+      <c r="T12" s="179"/>
+      <c r="U12" s="179"/>
+      <c r="V12" s="179"/>
+      <c r="W12" s="179"/>
+      <c r="X12" s="179"/>
+      <c r="Y12" s="179"/>
+      <c r="Z12" s="179"/>
+      <c r="AA12" s="179"/>
+      <c r="AB12" s="179"/>
+      <c r="AC12" s="179"/>
+      <c r="AD12" s="179"/>
+      <c r="AE12" s="179"/>
+      <c r="AF12" s="179"/>
+      <c r="AG12" s="179"/>
+      <c r="AH12" s="179"/>
+      <c r="AI12" s="179"/>
+      <c r="AJ12" s="179"/>
+      <c r="AK12" s="179"/>
+      <c r="AL12" s="179"/>
+      <c r="AM12" s="179"/>
+      <c r="AN12" s="179"/>
+      <c r="AO12" s="179"/>
+      <c r="AP12" s="179"/>
+      <c r="AQ12" s="179"/>
+      <c r="AR12" s="179"/>
+      <c r="AS12" s="179"/>
+      <c r="AT12" s="179"/>
+      <c r="AU12" s="179"/>
+      <c r="AV12" s="179"/>
+      <c r="AW12" s="179"/>
+      <c r="AX12" s="179"/>
+      <c r="AY12" s="179"/>
+      <c r="AZ12" s="180"/>
     </row>
     <row r="13" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56" t="s">
@@ -5827,398 +5881,398 @@
       <c r="H13" s="59"/>
       <c r="I13" s="59"/>
       <c r="J13" s="59"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="104"/>
-      <c r="O13" s="104"/>
-      <c r="P13" s="104"/>
-      <c r="Q13" s="104"/>
-      <c r="R13" s="104"/>
-      <c r="S13" s="104"/>
-      <c r="T13" s="104"/>
-      <c r="U13" s="104"/>
-      <c r="V13" s="104"/>
-      <c r="W13" s="104"/>
-      <c r="X13" s="104"/>
-      <c r="Y13" s="104"/>
-      <c r="Z13" s="104"/>
-      <c r="AA13" s="104"/>
-      <c r="AB13" s="104"/>
-      <c r="AC13" s="104"/>
-      <c r="AD13" s="104"/>
-      <c r="AE13" s="104"/>
-      <c r="AF13" s="104"/>
-      <c r="AG13" s="104"/>
-      <c r="AH13" s="104"/>
-      <c r="AI13" s="104"/>
-      <c r="AJ13" s="104"/>
-      <c r="AK13" s="104"/>
-      <c r="AL13" s="104"/>
-      <c r="AM13" s="104"/>
-      <c r="AN13" s="104"/>
-      <c r="AO13" s="104"/>
-      <c r="AP13" s="104"/>
-      <c r="AQ13" s="104"/>
-      <c r="AR13" s="104"/>
-      <c r="AS13" s="104"/>
-      <c r="AT13" s="104"/>
-      <c r="AU13" s="104"/>
-      <c r="AV13" s="104"/>
-      <c r="AW13" s="104"/>
-      <c r="AX13" s="104"/>
-      <c r="AY13" s="104"/>
-      <c r="AZ13" s="105"/>
+      <c r="K13" s="187"/>
+      <c r="L13" s="187"/>
+      <c r="M13" s="187"/>
+      <c r="N13" s="187"/>
+      <c r="O13" s="187"/>
+      <c r="P13" s="187"/>
+      <c r="Q13" s="187"/>
+      <c r="R13" s="187"/>
+      <c r="S13" s="187"/>
+      <c r="T13" s="187"/>
+      <c r="U13" s="187"/>
+      <c r="V13" s="187"/>
+      <c r="W13" s="187"/>
+      <c r="X13" s="187"/>
+      <c r="Y13" s="187"/>
+      <c r="Z13" s="187"/>
+      <c r="AA13" s="187"/>
+      <c r="AB13" s="187"/>
+      <c r="AC13" s="187"/>
+      <c r="AD13" s="187"/>
+      <c r="AE13" s="187"/>
+      <c r="AF13" s="187"/>
+      <c r="AG13" s="187"/>
+      <c r="AH13" s="187"/>
+      <c r="AI13" s="187"/>
+      <c r="AJ13" s="187"/>
+      <c r="AK13" s="187"/>
+      <c r="AL13" s="187"/>
+      <c r="AM13" s="187"/>
+      <c r="AN13" s="187"/>
+      <c r="AO13" s="187"/>
+      <c r="AP13" s="187"/>
+      <c r="AQ13" s="187"/>
+      <c r="AR13" s="187"/>
+      <c r="AS13" s="187"/>
+      <c r="AT13" s="187"/>
+      <c r="AU13" s="187"/>
+      <c r="AV13" s="187"/>
+      <c r="AW13" s="187"/>
+      <c r="AX13" s="187"/>
+      <c r="AY13" s="187"/>
+      <c r="AZ13" s="188"/>
     </row>
     <row r="14" spans="1:60" s="10" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="107"/>
-      <c r="B14" s="108"/>
-      <c r="C14" s="108"/>
-      <c r="D14" s="108"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="108"/>
-      <c r="I14" s="108"/>
-      <c r="J14" s="108"/>
-      <c r="K14" s="108"/>
-      <c r="L14" s="108"/>
-      <c r="M14" s="108"/>
-      <c r="N14" s="108"/>
-      <c r="O14" s="108"/>
-      <c r="P14" s="108"/>
-      <c r="Q14" s="108"/>
-      <c r="R14" s="108"/>
-      <c r="S14" s="108"/>
-      <c r="T14" s="108"/>
-      <c r="U14" s="108"/>
-      <c r="V14" s="108"/>
-      <c r="W14" s="108"/>
-      <c r="X14" s="108"/>
-      <c r="Y14" s="108"/>
-      <c r="Z14" s="108"/>
-      <c r="AA14" s="108"/>
-      <c r="AB14" s="108"/>
-      <c r="AC14" s="108"/>
-      <c r="AD14" s="108"/>
-      <c r="AE14" s="108"/>
-      <c r="AF14" s="108"/>
-      <c r="AG14" s="108"/>
-      <c r="AH14" s="108"/>
-      <c r="AI14" s="108"/>
-      <c r="AJ14" s="108"/>
-      <c r="AK14" s="108"/>
-      <c r="AL14" s="108"/>
-      <c r="AM14" s="108"/>
-      <c r="AN14" s="108"/>
-      <c r="AO14" s="108"/>
-      <c r="AP14" s="108"/>
-      <c r="AQ14" s="108"/>
-      <c r="AR14" s="108"/>
-      <c r="AS14" s="108"/>
-      <c r="AT14" s="108"/>
-      <c r="AU14" s="108"/>
-      <c r="AV14" s="108"/>
-      <c r="AW14" s="108"/>
-      <c r="AX14" s="108"/>
-      <c r="AY14" s="108"/>
-      <c r="AZ14" s="109"/>
+      <c r="A14" s="233"/>
+      <c r="B14" s="234"/>
+      <c r="C14" s="234"/>
+      <c r="D14" s="234"/>
+      <c r="E14" s="234"/>
+      <c r="F14" s="234"/>
+      <c r="G14" s="234"/>
+      <c r="H14" s="234"/>
+      <c r="I14" s="234"/>
+      <c r="J14" s="234"/>
+      <c r="K14" s="234"/>
+      <c r="L14" s="234"/>
+      <c r="M14" s="234"/>
+      <c r="N14" s="234"/>
+      <c r="O14" s="234"/>
+      <c r="P14" s="234"/>
+      <c r="Q14" s="234"/>
+      <c r="R14" s="234"/>
+      <c r="S14" s="234"/>
+      <c r="T14" s="234"/>
+      <c r="U14" s="234"/>
+      <c r="V14" s="234"/>
+      <c r="W14" s="234"/>
+      <c r="X14" s="234"/>
+      <c r="Y14" s="234"/>
+      <c r="Z14" s="234"/>
+      <c r="AA14" s="234"/>
+      <c r="AB14" s="234"/>
+      <c r="AC14" s="234"/>
+      <c r="AD14" s="234"/>
+      <c r="AE14" s="234"/>
+      <c r="AF14" s="234"/>
+      <c r="AG14" s="234"/>
+      <c r="AH14" s="234"/>
+      <c r="AI14" s="234"/>
+      <c r="AJ14" s="234"/>
+      <c r="AK14" s="234"/>
+      <c r="AL14" s="234"/>
+      <c r="AM14" s="234"/>
+      <c r="AN14" s="234"/>
+      <c r="AO14" s="234"/>
+      <c r="AP14" s="234"/>
+      <c r="AQ14" s="234"/>
+      <c r="AR14" s="234"/>
+      <c r="AS14" s="234"/>
+      <c r="AT14" s="234"/>
+      <c r="AU14" s="234"/>
+      <c r="AV14" s="234"/>
+      <c r="AW14" s="234"/>
+      <c r="AX14" s="234"/>
+      <c r="AY14" s="234"/>
+      <c r="AZ14" s="235"/>
       <c r="BC14" s="24"/>
     </row>
     <row r="15" spans="1:60" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="146"/>
-      <c r="B15" s="146"/>
-      <c r="C15" s="146"/>
-      <c r="D15" s="146"/>
-      <c r="E15" s="146"/>
-      <c r="F15" s="146"/>
-      <c r="G15" s="146"/>
-      <c r="H15" s="146"/>
-      <c r="I15" s="146"/>
-      <c r="J15" s="146"/>
-      <c r="K15" s="146"/>
-      <c r="L15" s="146"/>
-      <c r="M15" s="146"/>
-      <c r="N15" s="146"/>
-      <c r="O15" s="146"/>
-      <c r="P15" s="146"/>
-      <c r="Q15" s="146"/>
-      <c r="R15" s="146"/>
-      <c r="S15" s="146"/>
-      <c r="T15" s="146"/>
-      <c r="U15" s="146"/>
-      <c r="V15" s="146"/>
-      <c r="W15" s="146"/>
-      <c r="X15" s="146"/>
-      <c r="Y15" s="146"/>
-      <c r="Z15" s="146"/>
-      <c r="AA15" s="146"/>
-      <c r="AB15" s="146"/>
-      <c r="AC15" s="146"/>
-      <c r="AD15" s="146"/>
-      <c r="AE15" s="146"/>
-      <c r="AF15" s="146"/>
-      <c r="AG15" s="146"/>
-      <c r="AH15" s="146"/>
-      <c r="AI15" s="146"/>
-      <c r="AJ15" s="146"/>
-      <c r="AK15" s="146"/>
-      <c r="AL15" s="146"/>
-      <c r="AM15" s="146"/>
-      <c r="AN15" s="146"/>
-      <c r="AO15" s="146"/>
-      <c r="AP15" s="146"/>
-      <c r="AQ15" s="146"/>
-      <c r="AR15" s="146"/>
-      <c r="AS15" s="146"/>
-      <c r="AT15" s="146"/>
-      <c r="AU15" s="146"/>
-      <c r="AV15" s="146"/>
-      <c r="AW15" s="146"/>
-      <c r="AX15" s="146"/>
-      <c r="AY15" s="146"/>
-      <c r="AZ15" s="146"/>
+      <c r="A15" s="99"/>
+      <c r="B15" s="99"/>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="99"/>
+      <c r="L15" s="99"/>
+      <c r="M15" s="99"/>
+      <c r="N15" s="99"/>
+      <c r="O15" s="99"/>
+      <c r="P15" s="99"/>
+      <c r="Q15" s="99"/>
+      <c r="R15" s="99"/>
+      <c r="S15" s="99"/>
+      <c r="T15" s="99"/>
+      <c r="U15" s="99"/>
+      <c r="V15" s="99"/>
+      <c r="W15" s="99"/>
+      <c r="X15" s="99"/>
+      <c r="Y15" s="99"/>
+      <c r="Z15" s="99"/>
+      <c r="AA15" s="99"/>
+      <c r="AB15" s="99"/>
+      <c r="AC15" s="99"/>
+      <c r="AD15" s="99"/>
+      <c r="AE15" s="99"/>
+      <c r="AF15" s="99"/>
+      <c r="AG15" s="99"/>
+      <c r="AH15" s="99"/>
+      <c r="AI15" s="99"/>
+      <c r="AJ15" s="99"/>
+      <c r="AK15" s="99"/>
+      <c r="AL15" s="99"/>
+      <c r="AM15" s="99"/>
+      <c r="AN15" s="99"/>
+      <c r="AO15" s="99"/>
+      <c r="AP15" s="99"/>
+      <c r="AQ15" s="99"/>
+      <c r="AR15" s="99"/>
+      <c r="AS15" s="99"/>
+      <c r="AT15" s="99"/>
+      <c r="AU15" s="99"/>
+      <c r="AV15" s="99"/>
+      <c r="AW15" s="99"/>
+      <c r="AX15" s="99"/>
+      <c r="AY15" s="99"/>
+      <c r="AZ15" s="99"/>
     </row>
     <row r="16" spans="1:60" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="110" t="s">
+      <c r="A16" s="236" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="111"/>
-      <c r="P16" s="111"/>
-      <c r="Q16" s="111"/>
-      <c r="R16" s="111"/>
-      <c r="S16" s="111"/>
-      <c r="T16" s="111"/>
-      <c r="U16" s="111"/>
-      <c r="V16" s="111"/>
-      <c r="W16" s="111"/>
-      <c r="X16" s="111"/>
-      <c r="Y16" s="111"/>
-      <c r="Z16" s="111"/>
-      <c r="AA16" s="111"/>
-      <c r="AB16" s="111"/>
-      <c r="AC16" s="111"/>
-      <c r="AD16" s="111"/>
-      <c r="AE16" s="111"/>
-      <c r="AF16" s="111"/>
-      <c r="AG16" s="111"/>
-      <c r="AH16" s="111"/>
-      <c r="AI16" s="111"/>
-      <c r="AJ16" s="111"/>
-      <c r="AK16" s="111"/>
-      <c r="AL16" s="111"/>
-      <c r="AM16" s="111"/>
-      <c r="AN16" s="111"/>
-      <c r="AO16" s="111"/>
-      <c r="AP16" s="111"/>
-      <c r="AQ16" s="111"/>
-      <c r="AR16" s="111"/>
-      <c r="AS16" s="111"/>
-      <c r="AT16" s="111"/>
-      <c r="AU16" s="111"/>
-      <c r="AV16" s="111"/>
-      <c r="AW16" s="111"/>
-      <c r="AX16" s="111"/>
-      <c r="AY16" s="111"/>
-      <c r="AZ16" s="112"/>
-    </row>
-    <row r="17" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="199" t="s">
+      <c r="B16" s="237"/>
+      <c r="C16" s="237"/>
+      <c r="D16" s="237"/>
+      <c r="E16" s="237"/>
+      <c r="F16" s="237"/>
+      <c r="G16" s="237"/>
+      <c r="H16" s="237"/>
+      <c r="I16" s="237"/>
+      <c r="J16" s="237"/>
+      <c r="K16" s="237"/>
+      <c r="L16" s="237"/>
+      <c r="M16" s="237"/>
+      <c r="N16" s="237"/>
+      <c r="O16" s="237"/>
+      <c r="P16" s="237"/>
+      <c r="Q16" s="237"/>
+      <c r="R16" s="237"/>
+      <c r="S16" s="237"/>
+      <c r="T16" s="237"/>
+      <c r="U16" s="237"/>
+      <c r="V16" s="237"/>
+      <c r="W16" s="237"/>
+      <c r="X16" s="237"/>
+      <c r="Y16" s="237"/>
+      <c r="Z16" s="237"/>
+      <c r="AA16" s="237"/>
+      <c r="AB16" s="237"/>
+      <c r="AC16" s="237"/>
+      <c r="AD16" s="237"/>
+      <c r="AE16" s="237"/>
+      <c r="AF16" s="237"/>
+      <c r="AG16" s="237"/>
+      <c r="AH16" s="237"/>
+      <c r="AI16" s="237"/>
+      <c r="AJ16" s="237"/>
+      <c r="AK16" s="237"/>
+      <c r="AL16" s="237"/>
+      <c r="AM16" s="237"/>
+      <c r="AN16" s="237"/>
+      <c r="AO16" s="237"/>
+      <c r="AP16" s="237"/>
+      <c r="AQ16" s="237"/>
+      <c r="AR16" s="237"/>
+      <c r="AS16" s="237"/>
+      <c r="AT16" s="237"/>
+      <c r="AU16" s="237"/>
+      <c r="AV16" s="237"/>
+      <c r="AW16" s="237"/>
+      <c r="AX16" s="237"/>
+      <c r="AY16" s="237"/>
+      <c r="AZ16" s="238"/>
+    </row>
+    <row r="17" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="200"/>
-      <c r="C17" s="200"/>
-      <c r="D17" s="200"/>
-      <c r="E17" s="200"/>
-      <c r="F17" s="200"/>
-      <c r="G17" s="200"/>
-      <c r="H17" s="200"/>
-      <c r="I17" s="200"/>
-      <c r="J17" s="200"/>
-      <c r="K17" s="200"/>
-      <c r="L17" s="200"/>
-      <c r="M17" s="197" t="s">
+      <c r="B17" s="169"/>
+      <c r="C17" s="169"/>
+      <c r="D17" s="169"/>
+      <c r="E17" s="169"/>
+      <c r="F17" s="169"/>
+      <c r="G17" s="169"/>
+      <c r="H17" s="169"/>
+      <c r="I17" s="169"/>
+      <c r="J17" s="169"/>
+      <c r="K17" s="169"/>
+      <c r="L17" s="169"/>
+      <c r="M17" s="166" t="s">
         <v>32</v>
       </c>
-      <c r="N17" s="198"/>
-      <c r="O17" s="198"/>
-      <c r="P17" s="198"/>
-      <c r="Q17" s="198"/>
-      <c r="R17" s="116" t="s">
+      <c r="N17" s="167"/>
+      <c r="O17" s="167"/>
+      <c r="P17" s="167"/>
+      <c r="Q17" s="167"/>
+      <c r="R17" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="118"/>
-      <c r="W17" s="116" t="s">
+      <c r="S17" s="164"/>
+      <c r="T17" s="164"/>
+      <c r="U17" s="164"/>
+      <c r="V17" s="165"/>
+      <c r="W17" s="163" t="s">
         <v>34</v>
       </c>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="118"/>
-      <c r="AB17" s="116" t="s">
+      <c r="X17" s="164"/>
+      <c r="Y17" s="164"/>
+      <c r="Z17" s="164"/>
+      <c r="AA17" s="165"/>
+      <c r="AB17" s="163" t="s">
         <v>35</v>
       </c>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="118"/>
-      <c r="AG17" s="116" t="s">
+      <c r="AC17" s="164"/>
+      <c r="AD17" s="164"/>
+      <c r="AE17" s="164"/>
+      <c r="AF17" s="165"/>
+      <c r="AG17" s="163" t="s">
         <v>36</v>
       </c>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="117"/>
-      <c r="AJ17" s="117"/>
-      <c r="AK17" s="118"/>
-      <c r="AL17" s="116" t="s">
+      <c r="AH17" s="164"/>
+      <c r="AI17" s="164"/>
+      <c r="AJ17" s="164"/>
+      <c r="AK17" s="165"/>
+      <c r="AL17" s="163" t="s">
         <v>37</v>
       </c>
-      <c r="AM17" s="117"/>
-      <c r="AN17" s="117"/>
-      <c r="AO17" s="117"/>
-      <c r="AP17" s="118"/>
-      <c r="AQ17" s="116" t="s">
+      <c r="AM17" s="164"/>
+      <c r="AN17" s="164"/>
+      <c r="AO17" s="164"/>
+      <c r="AP17" s="165"/>
+      <c r="AQ17" s="163" t="s">
         <v>38</v>
       </c>
-      <c r="AR17" s="117"/>
-      <c r="AS17" s="117"/>
-      <c r="AT17" s="117"/>
-      <c r="AU17" s="118"/>
-      <c r="AV17" s="113" t="s">
+      <c r="AR17" s="164"/>
+      <c r="AS17" s="164"/>
+      <c r="AT17" s="164"/>
+      <c r="AU17" s="165"/>
+      <c r="AV17" s="239" t="s">
         <v>32</v>
       </c>
-      <c r="AW17" s="114"/>
-      <c r="AX17" s="114"/>
-      <c r="AY17" s="114"/>
-      <c r="AZ17" s="115"/>
+      <c r="AW17" s="240"/>
+      <c r="AX17" s="240"/>
+      <c r="AY17" s="240"/>
+      <c r="AZ17" s="241"/>
     </row>
     <row r="18" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="228" t="s">
+      <c r="A18" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="229"/>
-      <c r="C18" s="229"/>
-      <c r="D18" s="229"/>
-      <c r="E18" s="229"/>
-      <c r="F18" s="229"/>
-      <c r="G18" s="229"/>
-      <c r="H18" s="229"/>
-      <c r="I18" s="229"/>
-      <c r="J18" s="229"/>
-      <c r="K18" s="229"/>
-      <c r="L18" s="230"/>
-      <c r="M18" s="227"/>
-      <c r="N18" s="120"/>
-      <c r="O18" s="120"/>
-      <c r="P18" s="120"/>
-      <c r="Q18" s="120"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="120"/>
-      <c r="T18" s="120"/>
-      <c r="U18" s="120"/>
-      <c r="V18" s="120"/>
-      <c r="W18" s="119"/>
-      <c r="X18" s="120"/>
-      <c r="Y18" s="120"/>
-      <c r="Z18" s="120"/>
-      <c r="AA18" s="120"/>
-      <c r="AB18" s="119"/>
-      <c r="AC18" s="120"/>
-      <c r="AD18" s="120"/>
-      <c r="AE18" s="120"/>
-      <c r="AF18" s="120"/>
-      <c r="AG18" s="119"/>
-      <c r="AH18" s="120"/>
-      <c r="AI18" s="120"/>
-      <c r="AJ18" s="120"/>
-      <c r="AK18" s="120"/>
-      <c r="AL18" s="119"/>
-      <c r="AM18" s="120"/>
-      <c r="AN18" s="120"/>
-      <c r="AO18" s="120"/>
-      <c r="AP18" s="120"/>
-      <c r="AQ18" s="119"/>
-      <c r="AR18" s="120"/>
-      <c r="AS18" s="120"/>
-      <c r="AT18" s="120"/>
-      <c r="AU18" s="120"/>
-      <c r="AV18" s="119"/>
-      <c r="AW18" s="120"/>
-      <c r="AX18" s="120"/>
-      <c r="AY18" s="120"/>
-      <c r="AZ18" s="121"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="93"/>
+      <c r="K18" s="93"/>
+      <c r="L18" s="94"/>
+      <c r="M18" s="91"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="89"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="89"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="89"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="89"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="90"/>
+      <c r="AK18" s="90"/>
+      <c r="AL18" s="89"/>
+      <c r="AM18" s="90"/>
+      <c r="AN18" s="90"/>
+      <c r="AO18" s="90"/>
+      <c r="AP18" s="90"/>
+      <c r="AQ18" s="89"/>
+      <c r="AR18" s="90"/>
+      <c r="AS18" s="90"/>
+      <c r="AT18" s="90"/>
+      <c r="AU18" s="286"/>
+      <c r="AV18" s="287"/>
+      <c r="AW18" s="288"/>
+      <c r="AX18" s="288"/>
+      <c r="AY18" s="288"/>
+      <c r="AZ18" s="289"/>
       <c r="BD18" s="26"/>
     </row>
     <row r="19" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="218" t="s">
+      <c r="A19" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="219"/>
-      <c r="C19" s="219"/>
-      <c r="D19" s="219"/>
-      <c r="E19" s="219"/>
-      <c r="F19" s="219"/>
-      <c r="G19" s="219"/>
-      <c r="H19" s="219"/>
-      <c r="I19" s="219"/>
-      <c r="J19" s="219"/>
-      <c r="K19" s="219"/>
-      <c r="L19" s="220"/>
-      <c r="M19" s="213"/>
-      <c r="N19" s="163"/>
-      <c r="O19" s="163"/>
-      <c r="P19" s="163"/>
-      <c r="Q19" s="163"/>
-      <c r="R19" s="163"/>
-      <c r="S19" s="163"/>
-      <c r="T19" s="163"/>
-      <c r="U19" s="163"/>
-      <c r="V19" s="163"/>
-      <c r="W19" s="163"/>
-      <c r="X19" s="163"/>
-      <c r="Y19" s="163"/>
-      <c r="Z19" s="163"/>
-      <c r="AA19" s="163"/>
-      <c r="AB19" s="210"/>
-      <c r="AC19" s="163"/>
-      <c r="AD19" s="163"/>
-      <c r="AE19" s="163"/>
-      <c r="AF19" s="163"/>
-      <c r="AG19" s="210"/>
-      <c r="AH19" s="163"/>
-      <c r="AI19" s="163"/>
-      <c r="AJ19" s="163"/>
-      <c r="AK19" s="163"/>
-      <c r="AL19" s="210"/>
-      <c r="AM19" s="163"/>
-      <c r="AN19" s="163"/>
-      <c r="AO19" s="163"/>
-      <c r="AP19" s="163"/>
-      <c r="AQ19" s="210"/>
-      <c r="AR19" s="163"/>
-      <c r="AS19" s="163"/>
-      <c r="AT19" s="163"/>
-      <c r="AU19" s="163"/>
-      <c r="AV19" s="210"/>
-      <c r="AW19" s="163"/>
-      <c r="AX19" s="163"/>
-      <c r="AY19" s="163"/>
-      <c r="AZ19" s="231"/>
+      <c r="B19" s="130"/>
+      <c r="C19" s="130"/>
+      <c r="D19" s="130"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="130"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="130"/>
+      <c r="J19" s="130"/>
+      <c r="K19" s="130"/>
+      <c r="L19" s="131"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="96"/>
+      <c r="O19" s="96"/>
+      <c r="P19" s="96"/>
+      <c r="Q19" s="96"/>
+      <c r="R19" s="96"/>
+      <c r="S19" s="96"/>
+      <c r="T19" s="96"/>
+      <c r="U19" s="96"/>
+      <c r="V19" s="96"/>
+      <c r="W19" s="96"/>
+      <c r="X19" s="96"/>
+      <c r="Y19" s="96"/>
+      <c r="Z19" s="96"/>
+      <c r="AA19" s="96"/>
+      <c r="AB19" s="95"/>
+      <c r="AC19" s="96"/>
+      <c r="AD19" s="96"/>
+      <c r="AE19" s="96"/>
+      <c r="AF19" s="96"/>
+      <c r="AG19" s="95"/>
+      <c r="AH19" s="96"/>
+      <c r="AI19" s="96"/>
+      <c r="AJ19" s="96"/>
+      <c r="AK19" s="96"/>
+      <c r="AL19" s="95"/>
+      <c r="AM19" s="96"/>
+      <c r="AN19" s="96"/>
+      <c r="AO19" s="96"/>
+      <c r="AP19" s="96"/>
+      <c r="AQ19" s="95"/>
+      <c r="AR19" s="96"/>
+      <c r="AS19" s="96"/>
+      <c r="AT19" s="96"/>
+      <c r="AU19" s="96"/>
+      <c r="AV19" s="95"/>
+      <c r="AW19" s="96"/>
+      <c r="AX19" s="96"/>
+      <c r="AY19" s="96"/>
+      <c r="AZ19" s="97"/>
       <c r="BC19" s="29"/>
       <c r="BD19" s="49"/>
       <c r="BE19" s="30"/>
@@ -6229,60 +6283,60 @@
       <c r="BJ19" s="49"/>
     </row>
     <row r="20" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="221" t="s">
+      <c r="A20" s="132" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="222"/>
-      <c r="C20" s="222"/>
-      <c r="D20" s="222"/>
-      <c r="E20" s="222"/>
-      <c r="F20" s="222"/>
-      <c r="G20" s="222"/>
-      <c r="H20" s="222"/>
-      <c r="I20" s="222"/>
-      <c r="J20" s="222"/>
-      <c r="K20" s="222"/>
-      <c r="L20" s="223"/>
-      <c r="M20" s="214"/>
-      <c r="N20" s="164"/>
-      <c r="O20" s="164"/>
-      <c r="P20" s="164"/>
-      <c r="Q20" s="164"/>
-      <c r="R20" s="164"/>
-      <c r="S20" s="164"/>
-      <c r="T20" s="164"/>
-      <c r="U20" s="164"/>
-      <c r="V20" s="164"/>
-      <c r="W20" s="164"/>
-      <c r="X20" s="164"/>
-      <c r="Y20" s="164"/>
-      <c r="Z20" s="164"/>
-      <c r="AA20" s="164"/>
-      <c r="AB20" s="164"/>
-      <c r="AC20" s="164"/>
-      <c r="AD20" s="164"/>
-      <c r="AE20" s="164"/>
-      <c r="AF20" s="164"/>
-      <c r="AG20" s="164"/>
-      <c r="AH20" s="164"/>
-      <c r="AI20" s="164"/>
-      <c r="AJ20" s="164"/>
-      <c r="AK20" s="164"/>
-      <c r="AL20" s="164"/>
-      <c r="AM20" s="164"/>
-      <c r="AN20" s="164"/>
-      <c r="AO20" s="164"/>
-      <c r="AP20" s="164"/>
-      <c r="AQ20" s="164"/>
-      <c r="AR20" s="164"/>
-      <c r="AS20" s="164"/>
-      <c r="AT20" s="164"/>
-      <c r="AU20" s="164"/>
-      <c r="AV20" s="164"/>
-      <c r="AW20" s="164"/>
-      <c r="AX20" s="164"/>
-      <c r="AY20" s="164"/>
-      <c r="AZ20" s="166"/>
+      <c r="B20" s="133"/>
+      <c r="C20" s="133"/>
+      <c r="D20" s="133"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="133"/>
+      <c r="G20" s="133"/>
+      <c r="H20" s="133"/>
+      <c r="I20" s="133"/>
+      <c r="J20" s="133"/>
+      <c r="K20" s="133"/>
+      <c r="L20" s="134"/>
+      <c r="M20" s="122"/>
+      <c r="N20" s="123"/>
+      <c r="O20" s="123"/>
+      <c r="P20" s="123"/>
+      <c r="Q20" s="123"/>
+      <c r="R20" s="123"/>
+      <c r="S20" s="123"/>
+      <c r="T20" s="123"/>
+      <c r="U20" s="123"/>
+      <c r="V20" s="123"/>
+      <c r="W20" s="123"/>
+      <c r="X20" s="123"/>
+      <c r="Y20" s="123"/>
+      <c r="Z20" s="123"/>
+      <c r="AA20" s="123"/>
+      <c r="AB20" s="123"/>
+      <c r="AC20" s="123"/>
+      <c r="AD20" s="123"/>
+      <c r="AE20" s="123"/>
+      <c r="AF20" s="123"/>
+      <c r="AG20" s="123"/>
+      <c r="AH20" s="123"/>
+      <c r="AI20" s="123"/>
+      <c r="AJ20" s="123"/>
+      <c r="AK20" s="123"/>
+      <c r="AL20" s="123"/>
+      <c r="AM20" s="123"/>
+      <c r="AN20" s="123"/>
+      <c r="AO20" s="123"/>
+      <c r="AP20" s="123"/>
+      <c r="AQ20" s="123"/>
+      <c r="AR20" s="123"/>
+      <c r="AS20" s="123"/>
+      <c r="AT20" s="123"/>
+      <c r="AU20" s="123"/>
+      <c r="AV20" s="123"/>
+      <c r="AW20" s="123"/>
+      <c r="AX20" s="123"/>
+      <c r="AY20" s="123"/>
+      <c r="AZ20" s="192"/>
       <c r="BC20" s="29"/>
       <c r="BD20" s="31"/>
       <c r="BE20" s="31"/>
@@ -6293,63 +6347,63 @@
       <c r="BJ20" s="31"/>
     </row>
     <row r="21" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="221" t="s">
+      <c r="A21" s="132" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="222"/>
-      <c r="C21" s="222"/>
-      <c r="D21" s="222"/>
-      <c r="E21" s="222"/>
-      <c r="F21" s="222"/>
-      <c r="G21" s="222"/>
-      <c r="H21" s="222"/>
-      <c r="I21" s="222"/>
-      <c r="J21" s="222"/>
-      <c r="K21" s="222"/>
-      <c r="L21" s="223"/>
-      <c r="M21" s="215"/>
-      <c r="N21" s="165"/>
-      <c r="O21" s="165"/>
-      <c r="P21" s="165"/>
-      <c r="Q21" s="165"/>
-      <c r="R21" s="165"/>
-      <c r="S21" s="165"/>
-      <c r="T21" s="165"/>
-      <c r="U21" s="165"/>
-      <c r="V21" s="165"/>
-      <c r="W21" s="165"/>
-      <c r="X21" s="165"/>
-      <c r="Y21" s="165"/>
-      <c r="Z21" s="165"/>
-      <c r="AA21" s="165"/>
-      <c r="AB21" s="165"/>
-      <c r="AC21" s="165"/>
-      <c r="AD21" s="165"/>
-      <c r="AE21" s="165"/>
-      <c r="AF21" s="165"/>
-      <c r="AG21" s="165"/>
-      <c r="AH21" s="165"/>
-      <c r="AI21" s="165"/>
-      <c r="AJ21" s="165"/>
-      <c r="AK21" s="165"/>
-      <c r="AL21" s="165"/>
-      <c r="AM21" s="165"/>
-      <c r="AN21" s="165"/>
-      <c r="AO21" s="165"/>
-      <c r="AP21" s="165"/>
-      <c r="AQ21" s="165"/>
-      <c r="AR21" s="165"/>
-      <c r="AS21" s="165"/>
-      <c r="AT21" s="165"/>
-      <c r="AU21" s="165"/>
-      <c r="AV21" s="165"/>
-      <c r="AW21" s="165"/>
-      <c r="AX21" s="165"/>
-      <c r="AY21" s="165"/>
-      <c r="AZ21" s="167"/>
+      <c r="B21" s="133"/>
+      <c r="C21" s="133"/>
+      <c r="D21" s="133"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="133"/>
+      <c r="I21" s="133"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="134"/>
+      <c r="M21" s="124"/>
+      <c r="N21" s="115"/>
+      <c r="O21" s="115"/>
+      <c r="P21" s="115"/>
+      <c r="Q21" s="115"/>
+      <c r="R21" s="115"/>
+      <c r="S21" s="115"/>
+      <c r="T21" s="115"/>
+      <c r="U21" s="115"/>
+      <c r="V21" s="115"/>
+      <c r="W21" s="115"/>
+      <c r="X21" s="115"/>
+      <c r="Y21" s="115"/>
+      <c r="Z21" s="115"/>
+      <c r="AA21" s="115"/>
+      <c r="AB21" s="115"/>
+      <c r="AC21" s="115"/>
+      <c r="AD21" s="115"/>
+      <c r="AE21" s="115"/>
+      <c r="AF21" s="115"/>
+      <c r="AG21" s="115"/>
+      <c r="AH21" s="115"/>
+      <c r="AI21" s="115"/>
+      <c r="AJ21" s="115"/>
+      <c r="AK21" s="115"/>
+      <c r="AL21" s="115"/>
+      <c r="AM21" s="115"/>
+      <c r="AN21" s="115"/>
+      <c r="AO21" s="115"/>
+      <c r="AP21" s="115"/>
+      <c r="AQ21" s="115"/>
+      <c r="AR21" s="115"/>
+      <c r="AS21" s="115"/>
+      <c r="AT21" s="115"/>
+      <c r="AU21" s="115"/>
+      <c r="AV21" s="115"/>
+      <c r="AW21" s="115"/>
+      <c r="AX21" s="115"/>
+      <c r="AY21" s="115"/>
+      <c r="AZ21" s="116"/>
       <c r="BC21" s="29"/>
-      <c r="BD21" s="90"/>
-      <c r="BE21" s="90"/>
+      <c r="BD21" s="229"/>
+      <c r="BE21" s="229"/>
       <c r="BF21" s="29"/>
       <c r="BG21" s="29"/>
       <c r="BH21" s="29"/>
@@ -6357,84 +6411,84 @@
       <c r="BJ21" s="29"/>
     </row>
     <row r="22" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="221" t="s">
+      <c r="A22" s="132" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="222"/>
-      <c r="C22" s="222"/>
-      <c r="D22" s="222"/>
-      <c r="E22" s="222"/>
-      <c r="F22" s="222"/>
-      <c r="G22" s="222"/>
-      <c r="H22" s="222"/>
-      <c r="I22" s="222"/>
-      <c r="J22" s="222"/>
-      <c r="K22" s="222"/>
-      <c r="L22" s="223"/>
-      <c r="M22" s="215" t="str">
+      <c r="B22" s="133"/>
+      <c r="C22" s="133"/>
+      <c r="D22" s="133"/>
+      <c r="E22" s="133"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="133"/>
+      <c r="I22" s="133"/>
+      <c r="J22" s="133"/>
+      <c r="K22" s="133"/>
+      <c r="L22" s="134"/>
+      <c r="M22" s="124" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="N22" s="165"/>
-      <c r="O22" s="165"/>
-      <c r="P22" s="165"/>
-      <c r="Q22" s="165"/>
-      <c r="R22" s="165" t="str">
+      <c r="N22" s="115"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="115"/>
+      <c r="Q22" s="115"/>
+      <c r="R22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="S22" s="165"/>
-      <c r="T22" s="165"/>
-      <c r="U22" s="165"/>
-      <c r="V22" s="165"/>
-      <c r="W22" s="165" t="str">
+      <c r="S22" s="115"/>
+      <c r="T22" s="115"/>
+      <c r="U22" s="115"/>
+      <c r="V22" s="115"/>
+      <c r="W22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="X22" s="165"/>
-      <c r="Y22" s="165"/>
-      <c r="Z22" s="165"/>
-      <c r="AA22" s="165"/>
-      <c r="AB22" s="165" t="str">
+      <c r="X22" s="115"/>
+      <c r="Y22" s="115"/>
+      <c r="Z22" s="115"/>
+      <c r="AA22" s="115"/>
+      <c r="AB22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AC22" s="165"/>
-      <c r="AD22" s="165"/>
-      <c r="AE22" s="165"/>
-      <c r="AF22" s="165"/>
-      <c r="AG22" s="165" t="str">
+      <c r="AC22" s="115"/>
+      <c r="AD22" s="115"/>
+      <c r="AE22" s="115"/>
+      <c r="AF22" s="115"/>
+      <c r="AG22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AH22" s="165"/>
-      <c r="AI22" s="165"/>
-      <c r="AJ22" s="165"/>
-      <c r="AK22" s="165"/>
-      <c r="AL22" s="165" t="str">
+      <c r="AH22" s="115"/>
+      <c r="AI22" s="115"/>
+      <c r="AJ22" s="115"/>
+      <c r="AK22" s="115"/>
+      <c r="AL22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AM22" s="165"/>
-      <c r="AN22" s="165"/>
-      <c r="AO22" s="165"/>
-      <c r="AP22" s="165"/>
-      <c r="AQ22" s="165" t="str">
+      <c r="AM22" s="115"/>
+      <c r="AN22" s="115"/>
+      <c r="AO22" s="115"/>
+      <c r="AP22" s="115"/>
+      <c r="AQ22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AR22" s="165"/>
-      <c r="AS22" s="165"/>
-      <c r="AT22" s="165"/>
-      <c r="AU22" s="165"/>
-      <c r="AV22" s="165" t="str">
+      <c r="AR22" s="115"/>
+      <c r="AS22" s="115"/>
+      <c r="AT22" s="115"/>
+      <c r="AU22" s="115"/>
+      <c r="AV22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AW22" s="165"/>
-      <c r="AX22" s="165"/>
-      <c r="AY22" s="165"/>
-      <c r="AZ22" s="167"/>
+      <c r="AW22" s="115"/>
+      <c r="AX22" s="115"/>
+      <c r="AY22" s="115"/>
+      <c r="AZ22" s="116"/>
       <c r="BC22" s="29"/>
       <c r="BD22" s="31"/>
       <c r="BE22" s="31"/>
@@ -6445,87 +6499,87 @@
       <c r="BJ22" s="29"/>
     </row>
     <row r="23" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="221" t="s">
+      <c r="A23" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="222"/>
-      <c r="C23" s="222"/>
-      <c r="D23" s="222"/>
-      <c r="E23" s="222"/>
-      <c r="F23" s="222"/>
-      <c r="G23" s="222"/>
-      <c r="H23" s="222"/>
-      <c r="I23" s="222"/>
-      <c r="J23" s="222"/>
-      <c r="K23" s="222"/>
-      <c r="L23" s="223"/>
-      <c r="M23" s="215" t="str">
+      <c r="B23" s="133"/>
+      <c r="C23" s="133"/>
+      <c r="D23" s="133"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="133"/>
+      <c r="I23" s="133"/>
+      <c r="J23" s="133"/>
+      <c r="K23" s="133"/>
+      <c r="L23" s="134"/>
+      <c r="M23" s="124" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="N23" s="165"/>
-      <c r="O23" s="165"/>
-      <c r="P23" s="165"/>
-      <c r="Q23" s="165"/>
-      <c r="R23" s="165" t="str">
+      <c r="N23" s="115"/>
+      <c r="O23" s="115"/>
+      <c r="P23" s="115"/>
+      <c r="Q23" s="115"/>
+      <c r="R23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="S23" s="165"/>
-      <c r="T23" s="165"/>
-      <c r="U23" s="165"/>
-      <c r="V23" s="165"/>
-      <c r="W23" s="165" t="str">
+      <c r="S23" s="115"/>
+      <c r="T23" s="115"/>
+      <c r="U23" s="115"/>
+      <c r="V23" s="115"/>
+      <c r="W23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="X23" s="165"/>
-      <c r="Y23" s="165"/>
-      <c r="Z23" s="165"/>
-      <c r="AA23" s="165"/>
-      <c r="AB23" s="165" t="str">
+      <c r="X23" s="115"/>
+      <c r="Y23" s="115"/>
+      <c r="Z23" s="115"/>
+      <c r="AA23" s="115"/>
+      <c r="AB23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AC23" s="165"/>
-      <c r="AD23" s="165"/>
-      <c r="AE23" s="165"/>
-      <c r="AF23" s="165"/>
-      <c r="AG23" s="165" t="str">
+      <c r="AC23" s="115"/>
+      <c r="AD23" s="115"/>
+      <c r="AE23" s="115"/>
+      <c r="AF23" s="115"/>
+      <c r="AG23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AH23" s="165"/>
-      <c r="AI23" s="165"/>
-      <c r="AJ23" s="165"/>
-      <c r="AK23" s="165"/>
-      <c r="AL23" s="165" t="str">
+      <c r="AH23" s="115"/>
+      <c r="AI23" s="115"/>
+      <c r="AJ23" s="115"/>
+      <c r="AK23" s="115"/>
+      <c r="AL23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AM23" s="165"/>
-      <c r="AN23" s="165"/>
-      <c r="AO23" s="165"/>
-      <c r="AP23" s="165"/>
-      <c r="AQ23" s="165" t="str">
+      <c r="AM23" s="115"/>
+      <c r="AN23" s="115"/>
+      <c r="AO23" s="115"/>
+      <c r="AP23" s="115"/>
+      <c r="AQ23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AR23" s="165"/>
-      <c r="AS23" s="165"/>
-      <c r="AT23" s="165"/>
-      <c r="AU23" s="165"/>
-      <c r="AV23" s="165" t="str">
+      <c r="AR23" s="115"/>
+      <c r="AS23" s="115"/>
+      <c r="AT23" s="115"/>
+      <c r="AU23" s="115"/>
+      <c r="AV23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AW23" s="165"/>
-      <c r="AX23" s="165"/>
-      <c r="AY23" s="165"/>
-      <c r="AZ23" s="167"/>
+      <c r="AW23" s="115"/>
+      <c r="AX23" s="115"/>
+      <c r="AY23" s="115"/>
+      <c r="AZ23" s="116"/>
       <c r="BC23" s="32"/>
-      <c r="BD23" s="90"/>
-      <c r="BE23" s="90"/>
+      <c r="BD23" s="229"/>
+      <c r="BE23" s="229"/>
       <c r="BF23" s="32"/>
       <c r="BG23" s="32"/>
       <c r="BH23" s="32"/>
@@ -6533,84 +6587,84 @@
       <c r="BJ23" s="32"/>
     </row>
     <row r="24" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="221" t="s">
+      <c r="A24" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="222"/>
-      <c r="C24" s="222"/>
-      <c r="D24" s="222"/>
-      <c r="E24" s="222"/>
-      <c r="F24" s="222"/>
-      <c r="G24" s="222"/>
-      <c r="H24" s="222"/>
-      <c r="I24" s="222"/>
-      <c r="J24" s="222"/>
-      <c r="K24" s="222"/>
-      <c r="L24" s="223"/>
-      <c r="M24" s="216" t="str">
+      <c r="B24" s="133"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="133"/>
+      <c r="I24" s="133"/>
+      <c r="J24" s="133"/>
+      <c r="K24" s="133"/>
+      <c r="L24" s="134"/>
+      <c r="M24" s="125" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="N24" s="158"/>
-      <c r="O24" s="158"/>
-      <c r="P24" s="158"/>
-      <c r="Q24" s="158"/>
-      <c r="R24" s="158" t="str">
+      <c r="N24" s="126"/>
+      <c r="O24" s="126"/>
+      <c r="P24" s="126"/>
+      <c r="Q24" s="126"/>
+      <c r="R24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="S24" s="158"/>
-      <c r="T24" s="158"/>
-      <c r="U24" s="158"/>
-      <c r="V24" s="158"/>
-      <c r="W24" s="158" t="str">
+      <c r="S24" s="126"/>
+      <c r="T24" s="126"/>
+      <c r="U24" s="126"/>
+      <c r="V24" s="126"/>
+      <c r="W24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="X24" s="158"/>
-      <c r="Y24" s="158"/>
-      <c r="Z24" s="158"/>
-      <c r="AA24" s="158"/>
-      <c r="AB24" s="158" t="str">
+      <c r="X24" s="126"/>
+      <c r="Y24" s="126"/>
+      <c r="Z24" s="126"/>
+      <c r="AA24" s="126"/>
+      <c r="AB24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AC24" s="158"/>
-      <c r="AD24" s="158"/>
-      <c r="AE24" s="158"/>
-      <c r="AF24" s="158"/>
-      <c r="AG24" s="158" t="str">
+      <c r="AC24" s="126"/>
+      <c r="AD24" s="126"/>
+      <c r="AE24" s="126"/>
+      <c r="AF24" s="126"/>
+      <c r="AG24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AH24" s="158"/>
-      <c r="AI24" s="158"/>
-      <c r="AJ24" s="158"/>
-      <c r="AK24" s="158"/>
-      <c r="AL24" s="158" t="str">
+      <c r="AH24" s="126"/>
+      <c r="AI24" s="126"/>
+      <c r="AJ24" s="126"/>
+      <c r="AK24" s="126"/>
+      <c r="AL24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AM24" s="158"/>
-      <c r="AN24" s="158"/>
-      <c r="AO24" s="158"/>
-      <c r="AP24" s="158"/>
-      <c r="AQ24" s="158" t="str">
+      <c r="AM24" s="126"/>
+      <c r="AN24" s="126"/>
+      <c r="AO24" s="126"/>
+      <c r="AP24" s="126"/>
+      <c r="AQ24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AR24" s="158"/>
-      <c r="AS24" s="158"/>
-      <c r="AT24" s="158"/>
-      <c r="AU24" s="158"/>
-      <c r="AV24" s="158" t="str">
+      <c r="AR24" s="126"/>
+      <c r="AS24" s="126"/>
+      <c r="AT24" s="126"/>
+      <c r="AU24" s="126"/>
+      <c r="AV24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AW24" s="158"/>
-      <c r="AX24" s="158"/>
-      <c r="AY24" s="158"/>
-      <c r="AZ24" s="159"/>
+      <c r="AW24" s="126"/>
+      <c r="AX24" s="126"/>
+      <c r="AY24" s="126"/>
+      <c r="AZ24" s="193"/>
       <c r="BC24" s="29"/>
       <c r="BD24" s="31"/>
       <c r="BE24" s="31"/>
@@ -6621,87 +6675,87 @@
       <c r="BJ24" s="29"/>
     </row>
     <row r="25" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="224" t="s">
+      <c r="A25" s="111" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="225"/>
-      <c r="C25" s="225"/>
-      <c r="D25" s="225"/>
-      <c r="E25" s="225"/>
-      <c r="F25" s="225"/>
-      <c r="G25" s="225"/>
-      <c r="H25" s="225"/>
-      <c r="I25" s="225"/>
-      <c r="J25" s="225"/>
-      <c r="K25" s="225"/>
-      <c r="L25" s="226"/>
-      <c r="M25" s="217" t="str">
+      <c r="B25" s="112"/>
+      <c r="C25" s="112"/>
+      <c r="D25" s="112"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="112"/>
+      <c r="H25" s="112"/>
+      <c r="I25" s="112"/>
+      <c r="J25" s="112"/>
+      <c r="K25" s="112"/>
+      <c r="L25" s="135"/>
+      <c r="M25" s="127" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="N25" s="157"/>
-      <c r="O25" s="157"/>
-      <c r="P25" s="157"/>
-      <c r="Q25" s="157"/>
-      <c r="R25" s="157" t="str">
+      <c r="N25" s="128"/>
+      <c r="O25" s="128"/>
+      <c r="P25" s="128"/>
+      <c r="Q25" s="128"/>
+      <c r="R25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="S25" s="157"/>
-      <c r="T25" s="157"/>
-      <c r="U25" s="157"/>
-      <c r="V25" s="157"/>
-      <c r="W25" s="157" t="str">
+      <c r="S25" s="128"/>
+      <c r="T25" s="128"/>
+      <c r="U25" s="128"/>
+      <c r="V25" s="128"/>
+      <c r="W25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="X25" s="157"/>
-      <c r="Y25" s="157"/>
-      <c r="Z25" s="157"/>
-      <c r="AA25" s="157"/>
-      <c r="AB25" s="157" t="str">
+      <c r="X25" s="128"/>
+      <c r="Y25" s="128"/>
+      <c r="Z25" s="128"/>
+      <c r="AA25" s="128"/>
+      <c r="AB25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AC25" s="157"/>
-      <c r="AD25" s="157"/>
-      <c r="AE25" s="157"/>
-      <c r="AF25" s="157"/>
-      <c r="AG25" s="157" t="str">
+      <c r="AC25" s="128"/>
+      <c r="AD25" s="128"/>
+      <c r="AE25" s="128"/>
+      <c r="AF25" s="128"/>
+      <c r="AG25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AH25" s="157"/>
-      <c r="AI25" s="157"/>
-      <c r="AJ25" s="157"/>
-      <c r="AK25" s="157"/>
-      <c r="AL25" s="157" t="str">
+      <c r="AH25" s="128"/>
+      <c r="AI25" s="128"/>
+      <c r="AJ25" s="128"/>
+      <c r="AK25" s="128"/>
+      <c r="AL25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AM25" s="157"/>
-      <c r="AN25" s="157"/>
-      <c r="AO25" s="157"/>
-      <c r="AP25" s="157"/>
-      <c r="AQ25" s="157" t="str">
+      <c r="AM25" s="128"/>
+      <c r="AN25" s="128"/>
+      <c r="AO25" s="128"/>
+      <c r="AP25" s="128"/>
+      <c r="AQ25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AR25" s="157"/>
-      <c r="AS25" s="157"/>
-      <c r="AT25" s="157"/>
-      <c r="AU25" s="157"/>
-      <c r="AV25" s="157" t="str">
+      <c r="AR25" s="128"/>
+      <c r="AS25" s="128"/>
+      <c r="AT25" s="128"/>
+      <c r="AU25" s="128"/>
+      <c r="AV25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AW25" s="157"/>
-      <c r="AX25" s="157"/>
-      <c r="AY25" s="157"/>
-      <c r="AZ25" s="160"/>
+      <c r="AW25" s="128"/>
+      <c r="AX25" s="128"/>
+      <c r="AY25" s="128"/>
+      <c r="AZ25" s="194"/>
       <c r="BC25" s="29"/>
-      <c r="BD25" s="90"/>
-      <c r="BE25" s="90"/>
+      <c r="BD25" s="229"/>
+      <c r="BE25" s="229"/>
       <c r="BF25" s="29"/>
       <c r="BG25" s="29"/>
       <c r="BH25" s="29"/>
@@ -6709,1150 +6763,1150 @@
       <c r="BJ25" s="29"/>
     </row>
     <row r="26" spans="1:62" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="146"/>
-      <c r="B26" s="146"/>
-      <c r="C26" s="146"/>
-      <c r="D26" s="146"/>
-      <c r="E26" s="146"/>
-      <c r="F26" s="146"/>
-      <c r="G26" s="146"/>
-      <c r="H26" s="146"/>
-      <c r="I26" s="146"/>
-      <c r="J26" s="146"/>
-      <c r="K26" s="146"/>
-      <c r="L26" s="146"/>
-      <c r="M26" s="146"/>
-      <c r="N26" s="146"/>
-      <c r="O26" s="146"/>
-      <c r="P26" s="146"/>
-      <c r="Q26" s="146"/>
-      <c r="R26" s="146"/>
-      <c r="S26" s="146"/>
-      <c r="T26" s="146"/>
-      <c r="U26" s="146"/>
-      <c r="V26" s="146"/>
-      <c r="W26" s="146"/>
-      <c r="X26" s="146"/>
-      <c r="Y26" s="146"/>
-      <c r="Z26" s="146"/>
-      <c r="AA26" s="146"/>
-      <c r="AB26" s="146"/>
-      <c r="AC26" s="146"/>
-      <c r="AD26" s="146"/>
-      <c r="AE26" s="146"/>
-      <c r="AF26" s="146"/>
-      <c r="AG26" s="146"/>
-      <c r="AH26" s="146"/>
-      <c r="AI26" s="146"/>
-      <c r="AJ26" s="146"/>
-      <c r="AK26" s="146"/>
-      <c r="AL26" s="146"/>
-      <c r="AM26" s="146"/>
-      <c r="AN26" s="146"/>
-      <c r="AO26" s="146"/>
-      <c r="AP26" s="146"/>
-      <c r="AQ26" s="146"/>
-      <c r="AR26" s="146"/>
-      <c r="AS26" s="146"/>
-      <c r="AT26" s="146"/>
-      <c r="AU26" s="146"/>
-      <c r="AV26" s="146"/>
-      <c r="AW26" s="146"/>
-      <c r="AX26" s="146"/>
-      <c r="AY26" s="146"/>
-      <c r="AZ26" s="146"/>
+      <c r="A26" s="99"/>
+      <c r="B26" s="99"/>
+      <c r="C26" s="99"/>
+      <c r="D26" s="99"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="99"/>
+      <c r="H26" s="99"/>
+      <c r="I26" s="99"/>
+      <c r="J26" s="99"/>
+      <c r="K26" s="99"/>
+      <c r="L26" s="99"/>
+      <c r="M26" s="99"/>
+      <c r="N26" s="99"/>
+      <c r="O26" s="99"/>
+      <c r="P26" s="99"/>
+      <c r="Q26" s="99"/>
+      <c r="R26" s="99"/>
+      <c r="S26" s="99"/>
+      <c r="T26" s="99"/>
+      <c r="U26" s="99"/>
+      <c r="V26" s="99"/>
+      <c r="W26" s="99"/>
+      <c r="X26" s="99"/>
+      <c r="Y26" s="99"/>
+      <c r="Z26" s="99"/>
+      <c r="AA26" s="99"/>
+      <c r="AB26" s="99"/>
+      <c r="AC26" s="99"/>
+      <c r="AD26" s="99"/>
+      <c r="AE26" s="99"/>
+      <c r="AF26" s="99"/>
+      <c r="AG26" s="99"/>
+      <c r="AH26" s="99"/>
+      <c r="AI26" s="99"/>
+      <c r="AJ26" s="99"/>
+      <c r="AK26" s="99"/>
+      <c r="AL26" s="99"/>
+      <c r="AM26" s="99"/>
+      <c r="AN26" s="99"/>
+      <c r="AO26" s="99"/>
+      <c r="AP26" s="99"/>
+      <c r="AQ26" s="99"/>
+      <c r="AR26" s="99"/>
+      <c r="AS26" s="99"/>
+      <c r="AT26" s="99"/>
+      <c r="AU26" s="99"/>
+      <c r="AV26" s="99"/>
+      <c r="AW26" s="99"/>
+      <c r="AX26" s="99"/>
+      <c r="AY26" s="99"/>
+      <c r="AZ26" s="99"/>
     </row>
     <row r="27" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="189" t="s">
+      <c r="A27" s="100" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="190"/>
-      <c r="C27" s="190"/>
-      <c r="D27" s="190"/>
-      <c r="E27" s="190"/>
-      <c r="F27" s="190"/>
-      <c r="G27" s="190"/>
-      <c r="H27" s="190"/>
-      <c r="I27" s="190"/>
-      <c r="J27" s="190"/>
-      <c r="K27" s="190"/>
-      <c r="L27" s="190"/>
-      <c r="M27" s="190"/>
-      <c r="N27" s="190"/>
-      <c r="O27" s="190"/>
-      <c r="P27" s="190"/>
-      <c r="Q27" s="190"/>
-      <c r="R27" s="190"/>
-      <c r="S27" s="190"/>
-      <c r="T27" s="190"/>
-      <c r="U27" s="190"/>
-      <c r="V27" s="190"/>
-      <c r="W27" s="190"/>
-      <c r="X27" s="190"/>
-      <c r="Y27" s="190"/>
-      <c r="Z27" s="190"/>
-      <c r="AA27" s="190"/>
-      <c r="AB27" s="190"/>
-      <c r="AC27" s="190"/>
-      <c r="AD27" s="190"/>
-      <c r="AE27" s="190"/>
-      <c r="AF27" s="190"/>
-      <c r="AG27" s="190"/>
-      <c r="AH27" s="190"/>
-      <c r="AI27" s="190"/>
-      <c r="AJ27" s="190"/>
-      <c r="AK27" s="190"/>
-      <c r="AL27" s="190"/>
-      <c r="AM27" s="190"/>
-      <c r="AN27" s="190"/>
-      <c r="AO27" s="190"/>
-      <c r="AP27" s="190"/>
-      <c r="AQ27" s="190"/>
-      <c r="AR27" s="190"/>
-      <c r="AS27" s="190"/>
-      <c r="AT27" s="190"/>
-      <c r="AU27" s="190"/>
-      <c r="AV27" s="190"/>
-      <c r="AW27" s="190"/>
-      <c r="AX27" s="190"/>
-      <c r="AY27" s="190"/>
-      <c r="AZ27" s="191"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="101"/>
+      <c r="F27" s="101"/>
+      <c r="G27" s="101"/>
+      <c r="H27" s="101"/>
+      <c r="I27" s="101"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="101"/>
+      <c r="L27" s="101"/>
+      <c r="M27" s="101"/>
+      <c r="N27" s="101"/>
+      <c r="O27" s="101"/>
+      <c r="P27" s="101"/>
+      <c r="Q27" s="101"/>
+      <c r="R27" s="101"/>
+      <c r="S27" s="101"/>
+      <c r="T27" s="101"/>
+      <c r="U27" s="101"/>
+      <c r="V27" s="101"/>
+      <c r="W27" s="101"/>
+      <c r="X27" s="101"/>
+      <c r="Y27" s="101"/>
+      <c r="Z27" s="101"/>
+      <c r="AA27" s="101"/>
+      <c r="AB27" s="101"/>
+      <c r="AC27" s="101"/>
+      <c r="AD27" s="101"/>
+      <c r="AE27" s="101"/>
+      <c r="AF27" s="101"/>
+      <c r="AG27" s="101"/>
+      <c r="AH27" s="101"/>
+      <c r="AI27" s="101"/>
+      <c r="AJ27" s="101"/>
+      <c r="AK27" s="101"/>
+      <c r="AL27" s="101"/>
+      <c r="AM27" s="101"/>
+      <c r="AN27" s="101"/>
+      <c r="AO27" s="101"/>
+      <c r="AP27" s="101"/>
+      <c r="AQ27" s="101"/>
+      <c r="AR27" s="101"/>
+      <c r="AS27" s="101"/>
+      <c r="AT27" s="101"/>
+      <c r="AU27" s="101"/>
+      <c r="AV27" s="101"/>
+      <c r="AW27" s="101"/>
+      <c r="AX27" s="101"/>
+      <c r="AY27" s="101"/>
+      <c r="AZ27" s="102"/>
     </row>
     <row r="28" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="233" t="s">
+      <c r="A28" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="234"/>
-      <c r="C28" s="234"/>
-      <c r="D28" s="234"/>
-      <c r="E28" s="234"/>
-      <c r="F28" s="234"/>
-      <c r="G28" s="234"/>
-      <c r="H28" s="234"/>
-      <c r="I28" s="234"/>
-      <c r="J28" s="234"/>
-      <c r="K28" s="234"/>
-      <c r="L28" s="234"/>
-      <c r="M28" s="234"/>
-      <c r="N28" s="234"/>
-      <c r="O28" s="234"/>
-      <c r="P28" s="234"/>
-      <c r="Q28" s="234"/>
-      <c r="R28" s="234"/>
-      <c r="S28" s="234"/>
-      <c r="T28" s="235" t="s">
+      <c r="B28" s="104"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="104"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="104"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="104"/>
+      <c r="N28" s="104"/>
+      <c r="O28" s="104"/>
+      <c r="P28" s="104"/>
+      <c r="Q28" s="104"/>
+      <c r="R28" s="104"/>
+      <c r="S28" s="104"/>
+      <c r="T28" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="U28" s="235"/>
-      <c r="V28" s="235"/>
-      <c r="W28" s="235"/>
-      <c r="X28" s="235"/>
-      <c r="Y28" s="235"/>
-      <c r="Z28" s="235"/>
-      <c r="AA28" s="234" t="s">
+      <c r="U28" s="105"/>
+      <c r="V28" s="105"/>
+      <c r="W28" s="105"/>
+      <c r="X28" s="105"/>
+      <c r="Y28" s="105"/>
+      <c r="Z28" s="105"/>
+      <c r="AA28" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="AB28" s="234"/>
-      <c r="AC28" s="234"/>
-      <c r="AD28" s="234"/>
-      <c r="AE28" s="234"/>
-      <c r="AF28" s="234"/>
-      <c r="AG28" s="234"/>
-      <c r="AH28" s="234"/>
-      <c r="AI28" s="234"/>
-      <c r="AJ28" s="234"/>
-      <c r="AK28" s="234"/>
-      <c r="AL28" s="234"/>
-      <c r="AM28" s="234"/>
-      <c r="AN28" s="234"/>
-      <c r="AO28" s="234"/>
-      <c r="AP28" s="234"/>
-      <c r="AQ28" s="234"/>
-      <c r="AR28" s="234"/>
-      <c r="AS28" s="234"/>
-      <c r="AT28" s="235" t="s">
+      <c r="AB28" s="104"/>
+      <c r="AC28" s="104"/>
+      <c r="AD28" s="104"/>
+      <c r="AE28" s="104"/>
+      <c r="AF28" s="104"/>
+      <c r="AG28" s="104"/>
+      <c r="AH28" s="104"/>
+      <c r="AI28" s="104"/>
+      <c r="AJ28" s="104"/>
+      <c r="AK28" s="104"/>
+      <c r="AL28" s="104"/>
+      <c r="AM28" s="104"/>
+      <c r="AN28" s="104"/>
+      <c r="AO28" s="104"/>
+      <c r="AP28" s="104"/>
+      <c r="AQ28" s="104"/>
+      <c r="AR28" s="104"/>
+      <c r="AS28" s="104"/>
+      <c r="AT28" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="AU28" s="235"/>
-      <c r="AV28" s="235"/>
-      <c r="AW28" s="235"/>
-      <c r="AX28" s="235"/>
-      <c r="AY28" s="235"/>
-      <c r="AZ28" s="236"/>
+      <c r="AU28" s="105"/>
+      <c r="AV28" s="105"/>
+      <c r="AW28" s="105"/>
+      <c r="AX28" s="105"/>
+      <c r="AY28" s="105"/>
+      <c r="AZ28" s="106"/>
     </row>
     <row r="29" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="237" t="s">
+      <c r="A29" s="107" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="238"/>
-      <c r="C29" s="238"/>
-      <c r="D29" s="238"/>
-      <c r="E29" s="238"/>
-      <c r="F29" s="238"/>
-      <c r="G29" s="238"/>
-      <c r="H29" s="238"/>
-      <c r="I29" s="238"/>
-      <c r="J29" s="238"/>
-      <c r="K29" s="238"/>
-      <c r="L29" s="238"/>
-      <c r="M29" s="238"/>
-      <c r="N29" s="238"/>
-      <c r="O29" s="238"/>
-      <c r="P29" s="238"/>
-      <c r="Q29" s="238"/>
-      <c r="R29" s="238"/>
-      <c r="S29" s="238"/>
-      <c r="T29" s="239"/>
-      <c r="U29" s="239"/>
-      <c r="V29" s="239"/>
-      <c r="W29" s="239"/>
-      <c r="X29" s="239"/>
-      <c r="Y29" s="239"/>
-      <c r="Z29" s="239"/>
-      <c r="AA29" s="238" t="s">
+      <c r="B29" s="108"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="108"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="108"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="108"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="108"/>
+      <c r="K29" s="108"/>
+      <c r="L29" s="108"/>
+      <c r="M29" s="108"/>
+      <c r="N29" s="108"/>
+      <c r="O29" s="108"/>
+      <c r="P29" s="108"/>
+      <c r="Q29" s="108"/>
+      <c r="R29" s="108"/>
+      <c r="S29" s="108"/>
+      <c r="T29" s="109"/>
+      <c r="U29" s="109"/>
+      <c r="V29" s="109"/>
+      <c r="W29" s="109"/>
+      <c r="X29" s="109"/>
+      <c r="Y29" s="109"/>
+      <c r="Z29" s="109"/>
+      <c r="AA29" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="AB29" s="238"/>
-      <c r="AC29" s="238"/>
-      <c r="AD29" s="238"/>
-      <c r="AE29" s="238"/>
-      <c r="AF29" s="238"/>
-      <c r="AG29" s="238"/>
-      <c r="AH29" s="238"/>
-      <c r="AI29" s="238"/>
-      <c r="AJ29" s="238"/>
-      <c r="AK29" s="238"/>
-      <c r="AL29" s="238"/>
-      <c r="AM29" s="238"/>
-      <c r="AN29" s="238"/>
-      <c r="AO29" s="238"/>
-      <c r="AP29" s="238"/>
-      <c r="AQ29" s="238"/>
-      <c r="AR29" s="238"/>
-      <c r="AS29" s="238"/>
-      <c r="AT29" s="239"/>
-      <c r="AU29" s="239"/>
-      <c r="AV29" s="239"/>
-      <c r="AW29" s="239"/>
-      <c r="AX29" s="239"/>
-      <c r="AY29" s="239"/>
-      <c r="AZ29" s="240"/>
+      <c r="AB29" s="108"/>
+      <c r="AC29" s="108"/>
+      <c r="AD29" s="108"/>
+      <c r="AE29" s="108"/>
+      <c r="AF29" s="108"/>
+      <c r="AG29" s="108"/>
+      <c r="AH29" s="108"/>
+      <c r="AI29" s="108"/>
+      <c r="AJ29" s="108"/>
+      <c r="AK29" s="108"/>
+      <c r="AL29" s="108"/>
+      <c r="AM29" s="108"/>
+      <c r="AN29" s="108"/>
+      <c r="AO29" s="108"/>
+      <c r="AP29" s="108"/>
+      <c r="AQ29" s="108"/>
+      <c r="AR29" s="108"/>
+      <c r="AS29" s="108"/>
+      <c r="AT29" s="109"/>
+      <c r="AU29" s="109"/>
+      <c r="AV29" s="109"/>
+      <c r="AW29" s="109"/>
+      <c r="AX29" s="109"/>
+      <c r="AY29" s="109"/>
+      <c r="AZ29" s="110"/>
     </row>
     <row r="30" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="237" t="s">
+      <c r="A30" s="107" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="238"/>
-      <c r="C30" s="238"/>
-      <c r="D30" s="238"/>
-      <c r="E30" s="238"/>
-      <c r="F30" s="238"/>
-      <c r="G30" s="238"/>
-      <c r="H30" s="238"/>
-      <c r="I30" s="238"/>
-      <c r="J30" s="238"/>
-      <c r="K30" s="238"/>
-      <c r="L30" s="238"/>
-      <c r="M30" s="238"/>
-      <c r="N30" s="238"/>
-      <c r="O30" s="238"/>
-      <c r="P30" s="238"/>
-      <c r="Q30" s="238"/>
-      <c r="R30" s="238"/>
-      <c r="S30" s="238"/>
-      <c r="T30" s="239"/>
-      <c r="U30" s="239"/>
-      <c r="V30" s="239"/>
-      <c r="W30" s="239"/>
-      <c r="X30" s="239"/>
-      <c r="Y30" s="239"/>
-      <c r="Z30" s="239"/>
-      <c r="AA30" s="238" t="s">
+      <c r="B30" s="108"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="108"/>
+      <c r="I30" s="108"/>
+      <c r="J30" s="108"/>
+      <c r="K30" s="108"/>
+      <c r="L30" s="108"/>
+      <c r="M30" s="108"/>
+      <c r="N30" s="108"/>
+      <c r="O30" s="108"/>
+      <c r="P30" s="108"/>
+      <c r="Q30" s="108"/>
+      <c r="R30" s="108"/>
+      <c r="S30" s="108"/>
+      <c r="T30" s="109"/>
+      <c r="U30" s="109"/>
+      <c r="V30" s="109"/>
+      <c r="W30" s="109"/>
+      <c r="X30" s="109"/>
+      <c r="Y30" s="109"/>
+      <c r="Z30" s="109"/>
+      <c r="AA30" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="AB30" s="238"/>
-      <c r="AC30" s="238"/>
-      <c r="AD30" s="238"/>
-      <c r="AE30" s="238"/>
-      <c r="AF30" s="238"/>
-      <c r="AG30" s="238"/>
-      <c r="AH30" s="238"/>
-      <c r="AI30" s="238"/>
-      <c r="AJ30" s="238"/>
-      <c r="AK30" s="238"/>
-      <c r="AL30" s="238"/>
-      <c r="AM30" s="238"/>
-      <c r="AN30" s="238"/>
-      <c r="AO30" s="238"/>
-      <c r="AP30" s="238"/>
-      <c r="AQ30" s="238"/>
-      <c r="AR30" s="238"/>
-      <c r="AS30" s="238"/>
-      <c r="AT30" s="239"/>
-      <c r="AU30" s="239"/>
-      <c r="AV30" s="239"/>
-      <c r="AW30" s="239"/>
-      <c r="AX30" s="239"/>
-      <c r="AY30" s="239"/>
-      <c r="AZ30" s="240"/>
+      <c r="AB30" s="108"/>
+      <c r="AC30" s="108"/>
+      <c r="AD30" s="108"/>
+      <c r="AE30" s="108"/>
+      <c r="AF30" s="108"/>
+      <c r="AG30" s="108"/>
+      <c r="AH30" s="108"/>
+      <c r="AI30" s="108"/>
+      <c r="AJ30" s="108"/>
+      <c r="AK30" s="108"/>
+      <c r="AL30" s="108"/>
+      <c r="AM30" s="108"/>
+      <c r="AN30" s="108"/>
+      <c r="AO30" s="108"/>
+      <c r="AP30" s="108"/>
+      <c r="AQ30" s="108"/>
+      <c r="AR30" s="108"/>
+      <c r="AS30" s="108"/>
+      <c r="AT30" s="109"/>
+      <c r="AU30" s="109"/>
+      <c r="AV30" s="109"/>
+      <c r="AW30" s="109"/>
+      <c r="AX30" s="109"/>
+      <c r="AY30" s="109"/>
+      <c r="AZ30" s="110"/>
     </row>
     <row r="31" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="224" t="s">
+      <c r="A31" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="225"/>
-      <c r="C31" s="225"/>
-      <c r="D31" s="225"/>
-      <c r="E31" s="225"/>
-      <c r="F31" s="225"/>
-      <c r="G31" s="225"/>
-      <c r="H31" s="225"/>
-      <c r="I31" s="225"/>
-      <c r="J31" s="225"/>
-      <c r="K31" s="225"/>
-      <c r="L31" s="225"/>
-      <c r="M31" s="225"/>
-      <c r="N31" s="225"/>
-      <c r="O31" s="225"/>
-      <c r="P31" s="225"/>
-      <c r="Q31" s="225"/>
-      <c r="R31" s="225"/>
-      <c r="S31" s="225"/>
-      <c r="T31" s="241"/>
-      <c r="U31" s="241"/>
-      <c r="V31" s="241"/>
-      <c r="W31" s="241"/>
-      <c r="X31" s="241"/>
-      <c r="Y31" s="241"/>
-      <c r="Z31" s="241"/>
-      <c r="AA31" s="225" t="s">
+      <c r="B31" s="112"/>
+      <c r="C31" s="112"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="112"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="112"/>
+      <c r="J31" s="112"/>
+      <c r="K31" s="112"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="112"/>
+      <c r="R31" s="112"/>
+      <c r="S31" s="112"/>
+      <c r="T31" s="113"/>
+      <c r="U31" s="113"/>
+      <c r="V31" s="113"/>
+      <c r="W31" s="113"/>
+      <c r="X31" s="113"/>
+      <c r="Y31" s="113"/>
+      <c r="Z31" s="113"/>
+      <c r="AA31" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="AB31" s="225"/>
-      <c r="AC31" s="225"/>
-      <c r="AD31" s="225"/>
-      <c r="AE31" s="225"/>
-      <c r="AF31" s="225"/>
-      <c r="AG31" s="225"/>
-      <c r="AH31" s="225"/>
-      <c r="AI31" s="225"/>
-      <c r="AJ31" s="225"/>
-      <c r="AK31" s="225"/>
-      <c r="AL31" s="225"/>
-      <c r="AM31" s="225"/>
-      <c r="AN31" s="225"/>
-      <c r="AO31" s="225"/>
-      <c r="AP31" s="225"/>
-      <c r="AQ31" s="225"/>
-      <c r="AR31" s="225"/>
-      <c r="AS31" s="225"/>
-      <c r="AT31" s="241"/>
-      <c r="AU31" s="241"/>
-      <c r="AV31" s="241"/>
-      <c r="AW31" s="241"/>
-      <c r="AX31" s="241"/>
-      <c r="AY31" s="241"/>
-      <c r="AZ31" s="242"/>
+      <c r="AB31" s="112"/>
+      <c r="AC31" s="112"/>
+      <c r="AD31" s="112"/>
+      <c r="AE31" s="112"/>
+      <c r="AF31" s="112"/>
+      <c r="AG31" s="112"/>
+      <c r="AH31" s="112"/>
+      <c r="AI31" s="112"/>
+      <c r="AJ31" s="112"/>
+      <c r="AK31" s="112"/>
+      <c r="AL31" s="112"/>
+      <c r="AM31" s="112"/>
+      <c r="AN31" s="112"/>
+      <c r="AO31" s="112"/>
+      <c r="AP31" s="112"/>
+      <c r="AQ31" s="112"/>
+      <c r="AR31" s="112"/>
+      <c r="AS31" s="112"/>
+      <c r="AT31" s="113"/>
+      <c r="AU31" s="113"/>
+      <c r="AV31" s="113"/>
+      <c r="AW31" s="113"/>
+      <c r="AX31" s="113"/>
+      <c r="AY31" s="113"/>
+      <c r="AZ31" s="114"/>
     </row>
     <row r="32" spans="1:62" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="232"/>
-      <c r="B32" s="232"/>
-      <c r="C32" s="232"/>
-      <c r="D32" s="232"/>
-      <c r="E32" s="232"/>
-      <c r="F32" s="232"/>
-      <c r="G32" s="232"/>
-      <c r="H32" s="232"/>
-      <c r="I32" s="232"/>
-      <c r="J32" s="232"/>
-      <c r="K32" s="232"/>
-      <c r="L32" s="232"/>
-      <c r="M32" s="232"/>
-      <c r="N32" s="232"/>
-      <c r="O32" s="232"/>
-      <c r="P32" s="232"/>
-      <c r="Q32" s="232"/>
-      <c r="R32" s="232"/>
-      <c r="S32" s="232"/>
-      <c r="T32" s="232"/>
-      <c r="U32" s="232"/>
-      <c r="V32" s="232"/>
-      <c r="W32" s="232"/>
-      <c r="X32" s="232"/>
-      <c r="Y32" s="232"/>
-      <c r="Z32" s="232"/>
-      <c r="AA32" s="232"/>
-      <c r="AB32" s="232"/>
-      <c r="AC32" s="232"/>
-      <c r="AD32" s="232"/>
-      <c r="AE32" s="232"/>
-      <c r="AF32" s="232"/>
-      <c r="AG32" s="232"/>
-      <c r="AH32" s="232"/>
-      <c r="AI32" s="232"/>
-      <c r="AJ32" s="232"/>
-      <c r="AK32" s="232"/>
-      <c r="AL32" s="232"/>
-      <c r="AM32" s="232"/>
-      <c r="AN32" s="232"/>
-      <c r="AO32" s="232"/>
-      <c r="AP32" s="232"/>
-      <c r="AQ32" s="232"/>
-      <c r="AR32" s="232"/>
-      <c r="AS32" s="232"/>
-      <c r="AT32" s="232"/>
-      <c r="AU32" s="232"/>
-      <c r="AV32" s="232"/>
-      <c r="AW32" s="232"/>
-      <c r="AX32" s="232"/>
-      <c r="AY32" s="232"/>
-      <c r="AZ32" s="232"/>
+      <c r="A32" s="98"/>
+      <c r="B32" s="98"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="98"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="98"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="98"/>
+      <c r="N32" s="98"/>
+      <c r="O32" s="98"/>
+      <c r="P32" s="98"/>
+      <c r="Q32" s="98"/>
+      <c r="R32" s="98"/>
+      <c r="S32" s="98"/>
+      <c r="T32" s="98"/>
+      <c r="U32" s="98"/>
+      <c r="V32" s="98"/>
+      <c r="W32" s="98"/>
+      <c r="X32" s="98"/>
+      <c r="Y32" s="98"/>
+      <c r="Z32" s="98"/>
+      <c r="AA32" s="98"/>
+      <c r="AB32" s="98"/>
+      <c r="AC32" s="98"/>
+      <c r="AD32" s="98"/>
+      <c r="AE32" s="98"/>
+      <c r="AF32" s="98"/>
+      <c r="AG32" s="98"/>
+      <c r="AH32" s="98"/>
+      <c r="AI32" s="98"/>
+      <c r="AJ32" s="98"/>
+      <c r="AK32" s="98"/>
+      <c r="AL32" s="98"/>
+      <c r="AM32" s="98"/>
+      <c r="AN32" s="98"/>
+      <c r="AO32" s="98"/>
+      <c r="AP32" s="98"/>
+      <c r="AQ32" s="98"/>
+      <c r="AR32" s="98"/>
+      <c r="AS32" s="98"/>
+      <c r="AT32" s="98"/>
+      <c r="AU32" s="98"/>
+      <c r="AV32" s="98"/>
+      <c r="AW32" s="98"/>
+      <c r="AX32" s="98"/>
+      <c r="AY32" s="98"/>
+      <c r="AZ32" s="98"/>
     </row>
     <row r="33" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="131" t="s">
+      <c r="A33" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="132"/>
-      <c r="C33" s="132"/>
-      <c r="D33" s="132"/>
-      <c r="E33" s="132"/>
-      <c r="F33" s="132"/>
-      <c r="G33" s="132"/>
-      <c r="H33" s="132"/>
-      <c r="I33" s="132"/>
-      <c r="J33" s="132"/>
-      <c r="K33" s="132"/>
-      <c r="L33" s="132"/>
-      <c r="M33" s="132"/>
-      <c r="N33" s="132"/>
-      <c r="O33" s="132"/>
-      <c r="P33" s="132"/>
-      <c r="Q33" s="132"/>
-      <c r="R33" s="133"/>
-      <c r="S33" s="98" t="s">
+      <c r="B33" s="206"/>
+      <c r="C33" s="206"/>
+      <c r="D33" s="206"/>
+      <c r="E33" s="206"/>
+      <c r="F33" s="206"/>
+      <c r="G33" s="206"/>
+      <c r="H33" s="206"/>
+      <c r="I33" s="206"/>
+      <c r="J33" s="206"/>
+      <c r="K33" s="206"/>
+      <c r="L33" s="206"/>
+      <c r="M33" s="206"/>
+      <c r="N33" s="206"/>
+      <c r="O33" s="206"/>
+      <c r="P33" s="206"/>
+      <c r="Q33" s="206"/>
+      <c r="R33" s="207"/>
+      <c r="S33" s="196" t="s">
         <v>56</v>
       </c>
-      <c r="T33" s="99"/>
-      <c r="U33" s="99"/>
-      <c r="V33" s="99"/>
-      <c r="W33" s="99"/>
-      <c r="X33" s="99"/>
-      <c r="Y33" s="99"/>
-      <c r="Z33" s="99"/>
-      <c r="AA33" s="99"/>
-      <c r="AB33" s="99"/>
-      <c r="AC33" s="99"/>
-      <c r="AD33" s="99"/>
-      <c r="AE33" s="99"/>
-      <c r="AF33" s="99"/>
-      <c r="AG33" s="123"/>
-      <c r="AH33" s="98" t="s">
+      <c r="T33" s="197"/>
+      <c r="U33" s="197"/>
+      <c r="V33" s="197"/>
+      <c r="W33" s="197"/>
+      <c r="X33" s="197"/>
+      <c r="Y33" s="197"/>
+      <c r="Z33" s="197"/>
+      <c r="AA33" s="197"/>
+      <c r="AB33" s="197"/>
+      <c r="AC33" s="197"/>
+      <c r="AD33" s="197"/>
+      <c r="AE33" s="197"/>
+      <c r="AF33" s="197"/>
+      <c r="AG33" s="198"/>
+      <c r="AH33" s="196" t="s">
         <v>57</v>
       </c>
-      <c r="AI33" s="99"/>
-      <c r="AJ33" s="99"/>
-      <c r="AK33" s="99"/>
-      <c r="AL33" s="99"/>
-      <c r="AM33" s="99"/>
-      <c r="AN33" s="99"/>
-      <c r="AO33" s="99"/>
-      <c r="AP33" s="99"/>
-      <c r="AQ33" s="99"/>
-      <c r="AR33" s="99"/>
-      <c r="AS33" s="99"/>
-      <c r="AT33" s="99"/>
-      <c r="AU33" s="99"/>
-      <c r="AV33" s="99"/>
-      <c r="AW33" s="99"/>
-      <c r="AX33" s="99"/>
-      <c r="AY33" s="99"/>
-      <c r="AZ33" s="100"/>
+      <c r="AI33" s="197"/>
+      <c r="AJ33" s="197"/>
+      <c r="AK33" s="197"/>
+      <c r="AL33" s="197"/>
+      <c r="AM33" s="197"/>
+      <c r="AN33" s="197"/>
+      <c r="AO33" s="197"/>
+      <c r="AP33" s="197"/>
+      <c r="AQ33" s="197"/>
+      <c r="AR33" s="197"/>
+      <c r="AS33" s="197"/>
+      <c r="AT33" s="197"/>
+      <c r="AU33" s="197"/>
+      <c r="AV33" s="197"/>
+      <c r="AW33" s="197"/>
+      <c r="AX33" s="197"/>
+      <c r="AY33" s="197"/>
+      <c r="AZ33" s="231"/>
     </row>
     <row r="34" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="134"/>
-      <c r="B34" s="135"/>
-      <c r="C34" s="135"/>
-      <c r="D34" s="135"/>
-      <c r="E34" s="135"/>
-      <c r="F34" s="135"/>
-      <c r="G34" s="135"/>
-      <c r="H34" s="135"/>
-      <c r="I34" s="135"/>
-      <c r="J34" s="135"/>
-      <c r="K34" s="135"/>
-      <c r="L34" s="135"/>
-      <c r="M34" s="135"/>
-      <c r="N34" s="135"/>
-      <c r="O34" s="135"/>
-      <c r="P34" s="135"/>
-      <c r="Q34" s="135"/>
-      <c r="R34" s="136"/>
-      <c r="S34" s="101"/>
-      <c r="T34" s="102"/>
-      <c r="U34" s="102"/>
-      <c r="V34" s="102"/>
-      <c r="W34" s="102"/>
-      <c r="X34" s="102"/>
-      <c r="Y34" s="102"/>
-      <c r="Z34" s="102"/>
-      <c r="AA34" s="102"/>
-      <c r="AB34" s="102"/>
-      <c r="AC34" s="102"/>
-      <c r="AD34" s="102"/>
-      <c r="AE34" s="102"/>
-      <c r="AF34" s="102"/>
-      <c r="AG34" s="124"/>
-      <c r="AH34" s="101"/>
-      <c r="AI34" s="102"/>
-      <c r="AJ34" s="102"/>
-      <c r="AK34" s="102"/>
-      <c r="AL34" s="102"/>
-      <c r="AM34" s="102"/>
-      <c r="AN34" s="102"/>
-      <c r="AO34" s="102"/>
-      <c r="AP34" s="102"/>
-      <c r="AQ34" s="102"/>
-      <c r="AR34" s="102"/>
-      <c r="AS34" s="102"/>
-      <c r="AT34" s="102"/>
-      <c r="AU34" s="102"/>
-      <c r="AV34" s="102"/>
-      <c r="AW34" s="102"/>
-      <c r="AX34" s="102"/>
-      <c r="AY34" s="102"/>
-      <c r="AZ34" s="103"/>
+      <c r="A34" s="208"/>
+      <c r="B34" s="209"/>
+      <c r="C34" s="209"/>
+      <c r="D34" s="209"/>
+      <c r="E34" s="209"/>
+      <c r="F34" s="209"/>
+      <c r="G34" s="209"/>
+      <c r="H34" s="209"/>
+      <c r="I34" s="209"/>
+      <c r="J34" s="209"/>
+      <c r="K34" s="209"/>
+      <c r="L34" s="209"/>
+      <c r="M34" s="209"/>
+      <c r="N34" s="209"/>
+      <c r="O34" s="209"/>
+      <c r="P34" s="209"/>
+      <c r="Q34" s="209"/>
+      <c r="R34" s="210"/>
+      <c r="S34" s="199"/>
+      <c r="T34" s="200"/>
+      <c r="U34" s="200"/>
+      <c r="V34" s="200"/>
+      <c r="W34" s="200"/>
+      <c r="X34" s="200"/>
+      <c r="Y34" s="200"/>
+      <c r="Z34" s="200"/>
+      <c r="AA34" s="200"/>
+      <c r="AB34" s="200"/>
+      <c r="AC34" s="200"/>
+      <c r="AD34" s="200"/>
+      <c r="AE34" s="200"/>
+      <c r="AF34" s="200"/>
+      <c r="AG34" s="201"/>
+      <c r="AH34" s="199"/>
+      <c r="AI34" s="200"/>
+      <c r="AJ34" s="200"/>
+      <c r="AK34" s="200"/>
+      <c r="AL34" s="200"/>
+      <c r="AM34" s="200"/>
+      <c r="AN34" s="200"/>
+      <c r="AO34" s="200"/>
+      <c r="AP34" s="200"/>
+      <c r="AQ34" s="200"/>
+      <c r="AR34" s="200"/>
+      <c r="AS34" s="200"/>
+      <c r="AT34" s="200"/>
+      <c r="AU34" s="200"/>
+      <c r="AV34" s="200"/>
+      <c r="AW34" s="200"/>
+      <c r="AX34" s="200"/>
+      <c r="AY34" s="200"/>
+      <c r="AZ34" s="232"/>
     </row>
     <row r="35" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="125" t="s">
+      <c r="A35" s="183" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="126"/>
-      <c r="C35" s="126"/>
-      <c r="D35" s="126"/>
-      <c r="E35" s="126"/>
-      <c r="F35" s="126"/>
-      <c r="G35" s="126"/>
-      <c r="H35" s="126"/>
-      <c r="I35" s="126"/>
-      <c r="J35" s="126"/>
-      <c r="K35" s="126"/>
-      <c r="L35" s="126"/>
-      <c r="M35" s="126"/>
-      <c r="N35" s="126"/>
-      <c r="O35" s="126"/>
-      <c r="P35" s="126"/>
-      <c r="Q35" s="126"/>
-      <c r="R35" s="127"/>
-      <c r="S35" s="128" t="s">
+      <c r="B35" s="184"/>
+      <c r="C35" s="184"/>
+      <c r="D35" s="184"/>
+      <c r="E35" s="184"/>
+      <c r="F35" s="184"/>
+      <c r="G35" s="184"/>
+      <c r="H35" s="184"/>
+      <c r="I35" s="184"/>
+      <c r="J35" s="184"/>
+      <c r="K35" s="184"/>
+      <c r="L35" s="184"/>
+      <c r="M35" s="184"/>
+      <c r="N35" s="184"/>
+      <c r="O35" s="184"/>
+      <c r="P35" s="184"/>
+      <c r="Q35" s="184"/>
+      <c r="R35" s="185"/>
+      <c r="S35" s="189" t="s">
         <v>59</v>
       </c>
-      <c r="T35" s="129"/>
-      <c r="U35" s="129"/>
-      <c r="V35" s="129"/>
-      <c r="W35" s="129"/>
-      <c r="X35" s="129"/>
-      <c r="Y35" s="129"/>
-      <c r="Z35" s="129"/>
-      <c r="AA35" s="129"/>
-      <c r="AB35" s="129"/>
-      <c r="AC35" s="129"/>
-      <c r="AD35" s="129"/>
-      <c r="AE35" s="129"/>
-      <c r="AF35" s="129"/>
-      <c r="AG35" s="130"/>
-      <c r="AH35" s="95" t="s">
+      <c r="T35" s="190"/>
+      <c r="U35" s="190"/>
+      <c r="V35" s="190"/>
+      <c r="W35" s="190"/>
+      <c r="X35" s="190"/>
+      <c r="Y35" s="190"/>
+      <c r="Z35" s="190"/>
+      <c r="AA35" s="190"/>
+      <c r="AB35" s="190"/>
+      <c r="AC35" s="190"/>
+      <c r="AD35" s="190"/>
+      <c r="AE35" s="190"/>
+      <c r="AF35" s="190"/>
+      <c r="AG35" s="191"/>
+      <c r="AH35" s="202" t="s">
         <v>60</v>
       </c>
-      <c r="AI35" s="96"/>
-      <c r="AJ35" s="96"/>
-      <c r="AK35" s="96"/>
-      <c r="AL35" s="96"/>
-      <c r="AM35" s="96"/>
-      <c r="AN35" s="96"/>
-      <c r="AO35" s="96"/>
-      <c r="AP35" s="96"/>
-      <c r="AQ35" s="96"/>
-      <c r="AR35" s="96"/>
-      <c r="AS35" s="96"/>
-      <c r="AT35" s="96"/>
-      <c r="AU35" s="96"/>
-      <c r="AV35" s="96"/>
-      <c r="AW35" s="96"/>
-      <c r="AX35" s="96"/>
-      <c r="AY35" s="96"/>
-      <c r="AZ35" s="97"/>
+      <c r="AI35" s="203"/>
+      <c r="AJ35" s="203"/>
+      <c r="AK35" s="203"/>
+      <c r="AL35" s="203"/>
+      <c r="AM35" s="203"/>
+      <c r="AN35" s="203"/>
+      <c r="AO35" s="203"/>
+      <c r="AP35" s="203"/>
+      <c r="AQ35" s="203"/>
+      <c r="AR35" s="203"/>
+      <c r="AS35" s="203"/>
+      <c r="AT35" s="203"/>
+      <c r="AU35" s="203"/>
+      <c r="AV35" s="203"/>
+      <c r="AW35" s="203"/>
+      <c r="AX35" s="203"/>
+      <c r="AY35" s="203"/>
+      <c r="AZ35" s="204"/>
     </row>
     <row r="36" spans="1:52" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="125" t="s">
+      <c r="A36" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="126"/>
-      <c r="C36" s="126"/>
-      <c r="D36" s="126"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="126"/>
-      <c r="G36" s="126"/>
-      <c r="H36" s="126"/>
-      <c r="I36" s="126"/>
-      <c r="J36" s="126"/>
-      <c r="K36" s="126"/>
-      <c r="L36" s="126"/>
-      <c r="M36" s="126"/>
-      <c r="N36" s="126"/>
-      <c r="O36" s="126"/>
-      <c r="P36" s="126"/>
-      <c r="Q36" s="126"/>
-      <c r="R36" s="127"/>
-      <c r="S36" s="128" t="s">
+      <c r="B36" s="184"/>
+      <c r="C36" s="184"/>
+      <c r="D36" s="184"/>
+      <c r="E36" s="184"/>
+      <c r="F36" s="184"/>
+      <c r="G36" s="184"/>
+      <c r="H36" s="184"/>
+      <c r="I36" s="184"/>
+      <c r="J36" s="184"/>
+      <c r="K36" s="184"/>
+      <c r="L36" s="184"/>
+      <c r="M36" s="184"/>
+      <c r="N36" s="184"/>
+      <c r="O36" s="184"/>
+      <c r="P36" s="184"/>
+      <c r="Q36" s="184"/>
+      <c r="R36" s="185"/>
+      <c r="S36" s="189" t="s">
         <v>62</v>
       </c>
-      <c r="T36" s="129"/>
-      <c r="U36" s="129"/>
-      <c r="V36" s="129"/>
-      <c r="W36" s="129"/>
-      <c r="X36" s="129"/>
-      <c r="Y36" s="129"/>
-      <c r="Z36" s="129"/>
-      <c r="AA36" s="129"/>
-      <c r="AB36" s="129"/>
-      <c r="AC36" s="129"/>
-      <c r="AD36" s="129"/>
-      <c r="AE36" s="129"/>
-      <c r="AF36" s="129"/>
-      <c r="AG36" s="130"/>
-      <c r="AH36" s="95" t="s">
+      <c r="T36" s="190"/>
+      <c r="U36" s="190"/>
+      <c r="V36" s="190"/>
+      <c r="W36" s="190"/>
+      <c r="X36" s="190"/>
+      <c r="Y36" s="190"/>
+      <c r="Z36" s="190"/>
+      <c r="AA36" s="190"/>
+      <c r="AB36" s="190"/>
+      <c r="AC36" s="190"/>
+      <c r="AD36" s="190"/>
+      <c r="AE36" s="190"/>
+      <c r="AF36" s="190"/>
+      <c r="AG36" s="191"/>
+      <c r="AH36" s="202" t="s">
         <v>63</v>
       </c>
-      <c r="AI36" s="96"/>
-      <c r="AJ36" s="96"/>
-      <c r="AK36" s="96"/>
-      <c r="AL36" s="96"/>
-      <c r="AM36" s="96"/>
-      <c r="AN36" s="96"/>
-      <c r="AO36" s="96"/>
-      <c r="AP36" s="96"/>
-      <c r="AQ36" s="96"/>
-      <c r="AR36" s="96"/>
-      <c r="AS36" s="96"/>
-      <c r="AT36" s="96"/>
-      <c r="AU36" s="96"/>
-      <c r="AV36" s="96"/>
-      <c r="AW36" s="96"/>
-      <c r="AX36" s="96"/>
-      <c r="AY36" s="96"/>
-      <c r="AZ36" s="97"/>
+      <c r="AI36" s="203"/>
+      <c r="AJ36" s="203"/>
+      <c r="AK36" s="203"/>
+      <c r="AL36" s="203"/>
+      <c r="AM36" s="203"/>
+      <c r="AN36" s="203"/>
+      <c r="AO36" s="203"/>
+      <c r="AP36" s="203"/>
+      <c r="AQ36" s="203"/>
+      <c r="AR36" s="203"/>
+      <c r="AS36" s="203"/>
+      <c r="AT36" s="203"/>
+      <c r="AU36" s="203"/>
+      <c r="AV36" s="203"/>
+      <c r="AW36" s="203"/>
+      <c r="AX36" s="203"/>
+      <c r="AY36" s="203"/>
+      <c r="AZ36" s="204"/>
     </row>
     <row r="37" spans="1:52" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="125" t="s">
+      <c r="A37" s="183" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="126"/>
-      <c r="C37" s="126"/>
-      <c r="D37" s="126"/>
-      <c r="E37" s="126"/>
-      <c r="F37" s="126"/>
-      <c r="G37" s="126"/>
-      <c r="H37" s="126"/>
-      <c r="I37" s="126"/>
-      <c r="J37" s="126"/>
-      <c r="K37" s="126"/>
-      <c r="L37" s="126"/>
-      <c r="M37" s="126"/>
-      <c r="N37" s="126"/>
-      <c r="O37" s="126"/>
-      <c r="P37" s="126"/>
-      <c r="Q37" s="126"/>
-      <c r="R37" s="127"/>
-      <c r="S37" s="128" t="s">
+      <c r="B37" s="184"/>
+      <c r="C37" s="184"/>
+      <c r="D37" s="184"/>
+      <c r="E37" s="184"/>
+      <c r="F37" s="184"/>
+      <c r="G37" s="184"/>
+      <c r="H37" s="184"/>
+      <c r="I37" s="184"/>
+      <c r="J37" s="184"/>
+      <c r="K37" s="184"/>
+      <c r="L37" s="184"/>
+      <c r="M37" s="184"/>
+      <c r="N37" s="184"/>
+      <c r="O37" s="184"/>
+      <c r="P37" s="184"/>
+      <c r="Q37" s="184"/>
+      <c r="R37" s="185"/>
+      <c r="S37" s="189" t="s">
         <v>65</v>
       </c>
-      <c r="T37" s="129"/>
-      <c r="U37" s="129"/>
-      <c r="V37" s="129"/>
-      <c r="W37" s="129"/>
-      <c r="X37" s="129"/>
-      <c r="Y37" s="129"/>
-      <c r="Z37" s="129"/>
-      <c r="AA37" s="129"/>
-      <c r="AB37" s="129"/>
-      <c r="AC37" s="129"/>
-      <c r="AD37" s="129"/>
-      <c r="AE37" s="129"/>
-      <c r="AF37" s="129"/>
-      <c r="AG37" s="130"/>
-      <c r="AH37" s="95" t="s">
+      <c r="T37" s="190"/>
+      <c r="U37" s="190"/>
+      <c r="V37" s="190"/>
+      <c r="W37" s="190"/>
+      <c r="X37" s="190"/>
+      <c r="Y37" s="190"/>
+      <c r="Z37" s="190"/>
+      <c r="AA37" s="190"/>
+      <c r="AB37" s="190"/>
+      <c r="AC37" s="190"/>
+      <c r="AD37" s="190"/>
+      <c r="AE37" s="190"/>
+      <c r="AF37" s="190"/>
+      <c r="AG37" s="191"/>
+      <c r="AH37" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="AI37" s="96"/>
-      <c r="AJ37" s="96"/>
-      <c r="AK37" s="96"/>
-      <c r="AL37" s="96"/>
-      <c r="AM37" s="96"/>
-      <c r="AN37" s="96"/>
-      <c r="AO37" s="96"/>
-      <c r="AP37" s="96"/>
-      <c r="AQ37" s="96"/>
-      <c r="AR37" s="96"/>
-      <c r="AS37" s="96"/>
-      <c r="AT37" s="96"/>
-      <c r="AU37" s="96"/>
-      <c r="AV37" s="96"/>
-      <c r="AW37" s="96"/>
-      <c r="AX37" s="96"/>
-      <c r="AY37" s="96"/>
-      <c r="AZ37" s="97"/>
+      <c r="AI37" s="203"/>
+      <c r="AJ37" s="203"/>
+      <c r="AK37" s="203"/>
+      <c r="AL37" s="203"/>
+      <c r="AM37" s="203"/>
+      <c r="AN37" s="203"/>
+      <c r="AO37" s="203"/>
+      <c r="AP37" s="203"/>
+      <c r="AQ37" s="203"/>
+      <c r="AR37" s="203"/>
+      <c r="AS37" s="203"/>
+      <c r="AT37" s="203"/>
+      <c r="AU37" s="203"/>
+      <c r="AV37" s="203"/>
+      <c r="AW37" s="203"/>
+      <c r="AX37" s="203"/>
+      <c r="AY37" s="203"/>
+      <c r="AZ37" s="204"/>
     </row>
     <row r="38" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="125" t="s">
+      <c r="A38" s="183" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="126"/>
-      <c r="C38" s="126"/>
-      <c r="D38" s="126"/>
-      <c r="E38" s="126"/>
-      <c r="F38" s="126"/>
-      <c r="G38" s="126"/>
-      <c r="H38" s="126"/>
-      <c r="I38" s="126"/>
-      <c r="J38" s="126"/>
-      <c r="K38" s="126"/>
-      <c r="L38" s="126"/>
-      <c r="M38" s="126"/>
-      <c r="N38" s="126"/>
-      <c r="O38" s="126"/>
-      <c r="P38" s="126"/>
-      <c r="Q38" s="126"/>
-      <c r="R38" s="127"/>
-      <c r="S38" s="128" t="s">
+      <c r="B38" s="184"/>
+      <c r="C38" s="184"/>
+      <c r="D38" s="184"/>
+      <c r="E38" s="184"/>
+      <c r="F38" s="184"/>
+      <c r="G38" s="184"/>
+      <c r="H38" s="184"/>
+      <c r="I38" s="184"/>
+      <c r="J38" s="184"/>
+      <c r="K38" s="184"/>
+      <c r="L38" s="184"/>
+      <c r="M38" s="184"/>
+      <c r="N38" s="184"/>
+      <c r="O38" s="184"/>
+      <c r="P38" s="184"/>
+      <c r="Q38" s="184"/>
+      <c r="R38" s="185"/>
+      <c r="S38" s="189" t="s">
         <v>68</v>
       </c>
-      <c r="T38" s="129"/>
-      <c r="U38" s="129"/>
-      <c r="V38" s="129"/>
-      <c r="W38" s="129"/>
-      <c r="X38" s="129"/>
-      <c r="Y38" s="129"/>
-      <c r="Z38" s="129"/>
-      <c r="AA38" s="129"/>
-      <c r="AB38" s="129"/>
-      <c r="AC38" s="129"/>
-      <c r="AD38" s="129"/>
-      <c r="AE38" s="129"/>
-      <c r="AF38" s="129"/>
-      <c r="AG38" s="130"/>
-      <c r="AH38" s="95" t="s">
+      <c r="T38" s="190"/>
+      <c r="U38" s="190"/>
+      <c r="V38" s="190"/>
+      <c r="W38" s="190"/>
+      <c r="X38" s="190"/>
+      <c r="Y38" s="190"/>
+      <c r="Z38" s="190"/>
+      <c r="AA38" s="190"/>
+      <c r="AB38" s="190"/>
+      <c r="AC38" s="190"/>
+      <c r="AD38" s="190"/>
+      <c r="AE38" s="190"/>
+      <c r="AF38" s="190"/>
+      <c r="AG38" s="191"/>
+      <c r="AH38" s="202" t="s">
         <v>69</v>
       </c>
-      <c r="AI38" s="96"/>
-      <c r="AJ38" s="96"/>
-      <c r="AK38" s="96"/>
-      <c r="AL38" s="96"/>
-      <c r="AM38" s="96"/>
-      <c r="AN38" s="96"/>
-      <c r="AO38" s="96"/>
-      <c r="AP38" s="96"/>
-      <c r="AQ38" s="96"/>
-      <c r="AR38" s="96"/>
-      <c r="AS38" s="96"/>
-      <c r="AT38" s="96"/>
-      <c r="AU38" s="96"/>
-      <c r="AV38" s="96"/>
-      <c r="AW38" s="96"/>
-      <c r="AX38" s="96"/>
-      <c r="AY38" s="96"/>
-      <c r="AZ38" s="97"/>
+      <c r="AI38" s="203"/>
+      <c r="AJ38" s="203"/>
+      <c r="AK38" s="203"/>
+      <c r="AL38" s="203"/>
+      <c r="AM38" s="203"/>
+      <c r="AN38" s="203"/>
+      <c r="AO38" s="203"/>
+      <c r="AP38" s="203"/>
+      <c r="AQ38" s="203"/>
+      <c r="AR38" s="203"/>
+      <c r="AS38" s="203"/>
+      <c r="AT38" s="203"/>
+      <c r="AU38" s="203"/>
+      <c r="AV38" s="203"/>
+      <c r="AW38" s="203"/>
+      <c r="AX38" s="203"/>
+      <c r="AY38" s="203"/>
+      <c r="AZ38" s="204"/>
     </row>
     <row r="39" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="125" t="s">
+      <c r="A39" s="183" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="126"/>
-      <c r="C39" s="126"/>
-      <c r="D39" s="126"/>
-      <c r="E39" s="126"/>
-      <c r="F39" s="126"/>
-      <c r="G39" s="126"/>
-      <c r="H39" s="126"/>
-      <c r="I39" s="126"/>
-      <c r="J39" s="126"/>
-      <c r="K39" s="126"/>
-      <c r="L39" s="126"/>
-      <c r="M39" s="126"/>
-      <c r="N39" s="126"/>
-      <c r="O39" s="126"/>
-      <c r="P39" s="126"/>
-      <c r="Q39" s="126"/>
-      <c r="R39" s="127"/>
-      <c r="S39" s="128" t="s">
+      <c r="B39" s="184"/>
+      <c r="C39" s="184"/>
+      <c r="D39" s="184"/>
+      <c r="E39" s="184"/>
+      <c r="F39" s="184"/>
+      <c r="G39" s="184"/>
+      <c r="H39" s="184"/>
+      <c r="I39" s="184"/>
+      <c r="J39" s="184"/>
+      <c r="K39" s="184"/>
+      <c r="L39" s="184"/>
+      <c r="M39" s="184"/>
+      <c r="N39" s="184"/>
+      <c r="O39" s="184"/>
+      <c r="P39" s="184"/>
+      <c r="Q39" s="184"/>
+      <c r="R39" s="185"/>
+      <c r="S39" s="189" t="s">
         <v>71</v>
       </c>
-      <c r="T39" s="129"/>
-      <c r="U39" s="129"/>
-      <c r="V39" s="129"/>
-      <c r="W39" s="129"/>
-      <c r="X39" s="129"/>
-      <c r="Y39" s="129"/>
-      <c r="Z39" s="129"/>
-      <c r="AA39" s="129"/>
-      <c r="AB39" s="129"/>
-      <c r="AC39" s="129"/>
-      <c r="AD39" s="129"/>
-      <c r="AE39" s="129"/>
-      <c r="AF39" s="129"/>
-      <c r="AG39" s="130"/>
-      <c r="AH39" s="148"/>
-      <c r="AI39" s="149"/>
-      <c r="AJ39" s="149"/>
-      <c r="AK39" s="149"/>
-      <c r="AL39" s="149"/>
-      <c r="AM39" s="149"/>
-      <c r="AN39" s="149"/>
-      <c r="AO39" s="149"/>
-      <c r="AP39" s="149"/>
-      <c r="AQ39" s="149"/>
-      <c r="AR39" s="149"/>
-      <c r="AS39" s="149"/>
-      <c r="AT39" s="149"/>
-      <c r="AU39" s="149"/>
-      <c r="AV39" s="149"/>
-      <c r="AW39" s="149"/>
-      <c r="AX39" s="149"/>
-      <c r="AY39" s="149"/>
-      <c r="AZ39" s="150"/>
+      <c r="T39" s="190"/>
+      <c r="U39" s="190"/>
+      <c r="V39" s="190"/>
+      <c r="W39" s="190"/>
+      <c r="X39" s="190"/>
+      <c r="Y39" s="190"/>
+      <c r="Z39" s="190"/>
+      <c r="AA39" s="190"/>
+      <c r="AB39" s="190"/>
+      <c r="AC39" s="190"/>
+      <c r="AD39" s="190"/>
+      <c r="AE39" s="190"/>
+      <c r="AF39" s="190"/>
+      <c r="AG39" s="191"/>
+      <c r="AH39" s="220"/>
+      <c r="AI39" s="221"/>
+      <c r="AJ39" s="221"/>
+      <c r="AK39" s="221"/>
+      <c r="AL39" s="221"/>
+      <c r="AM39" s="221"/>
+      <c r="AN39" s="221"/>
+      <c r="AO39" s="221"/>
+      <c r="AP39" s="221"/>
+      <c r="AQ39" s="221"/>
+      <c r="AR39" s="221"/>
+      <c r="AS39" s="221"/>
+      <c r="AT39" s="221"/>
+      <c r="AU39" s="221"/>
+      <c r="AV39" s="221"/>
+      <c r="AW39" s="221"/>
+      <c r="AX39" s="221"/>
+      <c r="AY39" s="221"/>
+      <c r="AZ39" s="222"/>
     </row>
     <row r="40" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="125" t="s">
+      <c r="A40" s="183" t="s">
         <v>72</v>
       </c>
-      <c r="B40" s="126"/>
-      <c r="C40" s="126"/>
-      <c r="D40" s="126"/>
-      <c r="E40" s="126"/>
-      <c r="F40" s="126"/>
-      <c r="G40" s="126"/>
-      <c r="H40" s="126"/>
-      <c r="I40" s="126"/>
-      <c r="J40" s="126"/>
-      <c r="K40" s="126"/>
-      <c r="L40" s="126"/>
-      <c r="M40" s="126"/>
-      <c r="N40" s="126"/>
-      <c r="O40" s="126"/>
-      <c r="P40" s="126"/>
-      <c r="Q40" s="126"/>
-      <c r="R40" s="127"/>
-      <c r="S40" s="128" t="s">
+      <c r="B40" s="184"/>
+      <c r="C40" s="184"/>
+      <c r="D40" s="184"/>
+      <c r="E40" s="184"/>
+      <c r="F40" s="184"/>
+      <c r="G40" s="184"/>
+      <c r="H40" s="184"/>
+      <c r="I40" s="184"/>
+      <c r="J40" s="184"/>
+      <c r="K40" s="184"/>
+      <c r="L40" s="184"/>
+      <c r="M40" s="184"/>
+      <c r="N40" s="184"/>
+      <c r="O40" s="184"/>
+      <c r="P40" s="184"/>
+      <c r="Q40" s="184"/>
+      <c r="R40" s="185"/>
+      <c r="S40" s="189" t="s">
         <v>73</v>
       </c>
-      <c r="T40" s="129"/>
-      <c r="U40" s="129"/>
-      <c r="V40" s="129"/>
-      <c r="W40" s="129"/>
-      <c r="X40" s="129"/>
-      <c r="Y40" s="129"/>
-      <c r="Z40" s="129"/>
-      <c r="AA40" s="129"/>
-      <c r="AB40" s="129"/>
-      <c r="AC40" s="129"/>
-      <c r="AD40" s="129"/>
-      <c r="AE40" s="129"/>
-      <c r="AF40" s="129"/>
-      <c r="AG40" s="130"/>
-      <c r="AH40" s="148"/>
-      <c r="AI40" s="149"/>
-      <c r="AJ40" s="149"/>
-      <c r="AK40" s="149"/>
-      <c r="AL40" s="149"/>
-      <c r="AM40" s="149"/>
-      <c r="AN40" s="149"/>
-      <c r="AO40" s="149"/>
-      <c r="AP40" s="149"/>
-      <c r="AQ40" s="149"/>
-      <c r="AR40" s="149"/>
-      <c r="AS40" s="149"/>
-      <c r="AT40" s="149"/>
-      <c r="AU40" s="149"/>
-      <c r="AV40" s="149"/>
-      <c r="AW40" s="149"/>
-      <c r="AX40" s="149"/>
-      <c r="AY40" s="149"/>
-      <c r="AZ40" s="150"/>
+      <c r="T40" s="190"/>
+      <c r="U40" s="190"/>
+      <c r="V40" s="190"/>
+      <c r="W40" s="190"/>
+      <c r="X40" s="190"/>
+      <c r="Y40" s="190"/>
+      <c r="Z40" s="190"/>
+      <c r="AA40" s="190"/>
+      <c r="AB40" s="190"/>
+      <c r="AC40" s="190"/>
+      <c r="AD40" s="190"/>
+      <c r="AE40" s="190"/>
+      <c r="AF40" s="190"/>
+      <c r="AG40" s="191"/>
+      <c r="AH40" s="220"/>
+      <c r="AI40" s="221"/>
+      <c r="AJ40" s="221"/>
+      <c r="AK40" s="221"/>
+      <c r="AL40" s="221"/>
+      <c r="AM40" s="221"/>
+      <c r="AN40" s="221"/>
+      <c r="AO40" s="221"/>
+      <c r="AP40" s="221"/>
+      <c r="AQ40" s="221"/>
+      <c r="AR40" s="221"/>
+      <c r="AS40" s="221"/>
+      <c r="AT40" s="221"/>
+      <c r="AU40" s="221"/>
+      <c r="AV40" s="221"/>
+      <c r="AW40" s="221"/>
+      <c r="AX40" s="221"/>
+      <c r="AY40" s="221"/>
+      <c r="AZ40" s="222"/>
     </row>
     <row r="41" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="125"/>
-      <c r="B41" s="126"/>
-      <c r="C41" s="126"/>
-      <c r="D41" s="126"/>
-      <c r="E41" s="126"/>
-      <c r="F41" s="126"/>
-      <c r="G41" s="126"/>
-      <c r="H41" s="126"/>
-      <c r="I41" s="126"/>
-      <c r="J41" s="126"/>
-      <c r="K41" s="126"/>
-      <c r="L41" s="126"/>
-      <c r="M41" s="126"/>
-      <c r="N41" s="126"/>
-      <c r="O41" s="126"/>
-      <c r="P41" s="126"/>
-      <c r="Q41" s="126"/>
-      <c r="R41" s="127"/>
-      <c r="S41" s="128" t="s">
+      <c r="A41" s="183"/>
+      <c r="B41" s="184"/>
+      <c r="C41" s="184"/>
+      <c r="D41" s="184"/>
+      <c r="E41" s="184"/>
+      <c r="F41" s="184"/>
+      <c r="G41" s="184"/>
+      <c r="H41" s="184"/>
+      <c r="I41" s="184"/>
+      <c r="J41" s="184"/>
+      <c r="K41" s="184"/>
+      <c r="L41" s="184"/>
+      <c r="M41" s="184"/>
+      <c r="N41" s="184"/>
+      <c r="O41" s="184"/>
+      <c r="P41" s="184"/>
+      <c r="Q41" s="184"/>
+      <c r="R41" s="185"/>
+      <c r="S41" s="189" t="s">
         <v>74</v>
       </c>
-      <c r="T41" s="129"/>
-      <c r="U41" s="129"/>
-      <c r="V41" s="129"/>
-      <c r="W41" s="129"/>
-      <c r="X41" s="129"/>
-      <c r="Y41" s="129"/>
-      <c r="Z41" s="129"/>
-      <c r="AA41" s="129"/>
-      <c r="AB41" s="129"/>
-      <c r="AC41" s="129"/>
-      <c r="AD41" s="129"/>
-      <c r="AE41" s="129"/>
-      <c r="AF41" s="129"/>
-      <c r="AG41" s="130"/>
-      <c r="AH41" s="148"/>
-      <c r="AI41" s="149"/>
-      <c r="AJ41" s="149"/>
-      <c r="AK41" s="149"/>
-      <c r="AL41" s="149"/>
-      <c r="AM41" s="149"/>
-      <c r="AN41" s="149"/>
-      <c r="AO41" s="149"/>
-      <c r="AP41" s="149"/>
-      <c r="AQ41" s="149"/>
-      <c r="AR41" s="149"/>
-      <c r="AS41" s="149"/>
-      <c r="AT41" s="149"/>
-      <c r="AU41" s="149"/>
-      <c r="AV41" s="149"/>
-      <c r="AW41" s="149"/>
-      <c r="AX41" s="149"/>
-      <c r="AY41" s="149"/>
-      <c r="AZ41" s="150"/>
+      <c r="T41" s="190"/>
+      <c r="U41" s="190"/>
+      <c r="V41" s="190"/>
+      <c r="W41" s="190"/>
+      <c r="X41" s="190"/>
+      <c r="Y41" s="190"/>
+      <c r="Z41" s="190"/>
+      <c r="AA41" s="190"/>
+      <c r="AB41" s="190"/>
+      <c r="AC41" s="190"/>
+      <c r="AD41" s="190"/>
+      <c r="AE41" s="190"/>
+      <c r="AF41" s="190"/>
+      <c r="AG41" s="191"/>
+      <c r="AH41" s="220"/>
+      <c r="AI41" s="221"/>
+      <c r="AJ41" s="221"/>
+      <c r="AK41" s="221"/>
+      <c r="AL41" s="221"/>
+      <c r="AM41" s="221"/>
+      <c r="AN41" s="221"/>
+      <c r="AO41" s="221"/>
+      <c r="AP41" s="221"/>
+      <c r="AQ41" s="221"/>
+      <c r="AR41" s="221"/>
+      <c r="AS41" s="221"/>
+      <c r="AT41" s="221"/>
+      <c r="AU41" s="221"/>
+      <c r="AV41" s="221"/>
+      <c r="AW41" s="221"/>
+      <c r="AX41" s="221"/>
+      <c r="AY41" s="221"/>
+      <c r="AZ41" s="222"/>
     </row>
     <row r="42" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="151"/>
-      <c r="B42" s="152"/>
-      <c r="C42" s="152"/>
-      <c r="D42" s="152"/>
-      <c r="E42" s="152"/>
-      <c r="F42" s="152"/>
-      <c r="G42" s="152"/>
-      <c r="H42" s="152"/>
-      <c r="I42" s="152"/>
-      <c r="J42" s="152"/>
-      <c r="K42" s="152"/>
-      <c r="L42" s="152"/>
-      <c r="M42" s="152"/>
-      <c r="N42" s="152"/>
-      <c r="O42" s="152"/>
-      <c r="P42" s="152"/>
-      <c r="Q42" s="152"/>
-      <c r="R42" s="153"/>
-      <c r="S42" s="137" t="s">
+      <c r="A42" s="223"/>
+      <c r="B42" s="224"/>
+      <c r="C42" s="224"/>
+      <c r="D42" s="224"/>
+      <c r="E42" s="224"/>
+      <c r="F42" s="224"/>
+      <c r="G42" s="224"/>
+      <c r="H42" s="224"/>
+      <c r="I42" s="224"/>
+      <c r="J42" s="224"/>
+      <c r="K42" s="224"/>
+      <c r="L42" s="224"/>
+      <c r="M42" s="224"/>
+      <c r="N42" s="224"/>
+      <c r="O42" s="224"/>
+      <c r="P42" s="224"/>
+      <c r="Q42" s="224"/>
+      <c r="R42" s="225"/>
+      <c r="S42" s="211" t="s">
         <v>75</v>
       </c>
-      <c r="T42" s="138"/>
-      <c r="U42" s="138"/>
-      <c r="V42" s="138"/>
-      <c r="W42" s="138"/>
-      <c r="X42" s="138"/>
-      <c r="Y42" s="138"/>
-      <c r="Z42" s="138"/>
-      <c r="AA42" s="138"/>
-      <c r="AB42" s="138"/>
-      <c r="AC42" s="138"/>
-      <c r="AD42" s="138"/>
-      <c r="AE42" s="138"/>
-      <c r="AF42" s="138"/>
-      <c r="AG42" s="139"/>
-      <c r="AH42" s="154"/>
-      <c r="AI42" s="155"/>
-      <c r="AJ42" s="155"/>
-      <c r="AK42" s="155"/>
-      <c r="AL42" s="155"/>
-      <c r="AM42" s="155"/>
-      <c r="AN42" s="155"/>
-      <c r="AO42" s="155"/>
-      <c r="AP42" s="155"/>
-      <c r="AQ42" s="155"/>
-      <c r="AR42" s="155"/>
-      <c r="AS42" s="155"/>
-      <c r="AT42" s="155"/>
-      <c r="AU42" s="155"/>
-      <c r="AV42" s="155"/>
-      <c r="AW42" s="155"/>
-      <c r="AX42" s="155"/>
-      <c r="AY42" s="155"/>
-      <c r="AZ42" s="156"/>
+      <c r="T42" s="212"/>
+      <c r="U42" s="212"/>
+      <c r="V42" s="212"/>
+      <c r="W42" s="212"/>
+      <c r="X42" s="212"/>
+      <c r="Y42" s="212"/>
+      <c r="Z42" s="212"/>
+      <c r="AA42" s="212"/>
+      <c r="AB42" s="212"/>
+      <c r="AC42" s="212"/>
+      <c r="AD42" s="212"/>
+      <c r="AE42" s="212"/>
+      <c r="AF42" s="212"/>
+      <c r="AG42" s="213"/>
+      <c r="AH42" s="226"/>
+      <c r="AI42" s="227"/>
+      <c r="AJ42" s="227"/>
+      <c r="AK42" s="227"/>
+      <c r="AL42" s="227"/>
+      <c r="AM42" s="227"/>
+      <c r="AN42" s="227"/>
+      <c r="AO42" s="227"/>
+      <c r="AP42" s="227"/>
+      <c r="AQ42" s="227"/>
+      <c r="AR42" s="227"/>
+      <c r="AS42" s="227"/>
+      <c r="AT42" s="227"/>
+      <c r="AU42" s="227"/>
+      <c r="AV42" s="227"/>
+      <c r="AW42" s="227"/>
+      <c r="AX42" s="227"/>
+      <c r="AY42" s="227"/>
+      <c r="AZ42" s="228"/>
     </row>
     <row r="43" spans="1:52" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="146"/>
-      <c r="B43" s="146"/>
-      <c r="C43" s="146"/>
-      <c r="D43" s="146"/>
-      <c r="E43" s="146"/>
-      <c r="F43" s="146"/>
-      <c r="G43" s="146"/>
-      <c r="H43" s="146"/>
-      <c r="I43" s="146"/>
-      <c r="J43" s="146"/>
-      <c r="K43" s="146"/>
-      <c r="L43" s="146"/>
-      <c r="M43" s="146"/>
-      <c r="N43" s="146"/>
-      <c r="O43" s="146"/>
-      <c r="P43" s="146"/>
-      <c r="Q43" s="146"/>
-      <c r="R43" s="146"/>
-      <c r="S43" s="146"/>
-      <c r="T43" s="146"/>
-      <c r="U43" s="146"/>
-      <c r="V43" s="146"/>
-      <c r="W43" s="146"/>
-      <c r="X43" s="146"/>
-      <c r="Y43" s="146"/>
-      <c r="Z43" s="146"/>
-      <c r="AA43" s="146"/>
-      <c r="AB43" s="146"/>
-      <c r="AC43" s="146"/>
-      <c r="AD43" s="146"/>
-      <c r="AE43" s="146"/>
-      <c r="AF43" s="146"/>
-      <c r="AG43" s="146"/>
-      <c r="AH43" s="146"/>
-      <c r="AI43" s="146"/>
-      <c r="AJ43" s="146"/>
-      <c r="AK43" s="146"/>
-      <c r="AL43" s="146"/>
-      <c r="AM43" s="146"/>
-      <c r="AN43" s="146"/>
-      <c r="AO43" s="146"/>
-      <c r="AP43" s="146"/>
-      <c r="AQ43" s="146"/>
-      <c r="AR43" s="146"/>
-      <c r="AS43" s="146"/>
-      <c r="AT43" s="146"/>
-      <c r="AU43" s="146"/>
-      <c r="AV43" s="146"/>
-      <c r="AW43" s="146"/>
-      <c r="AX43" s="146"/>
-      <c r="AY43" s="146"/>
-      <c r="AZ43" s="146"/>
+      <c r="A43" s="99"/>
+      <c r="B43" s="99"/>
+      <c r="C43" s="99"/>
+      <c r="D43" s="99"/>
+      <c r="E43" s="99"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="99"/>
+      <c r="J43" s="99"/>
+      <c r="K43" s="99"/>
+      <c r="L43" s="99"/>
+      <c r="M43" s="99"/>
+      <c r="N43" s="99"/>
+      <c r="O43" s="99"/>
+      <c r="P43" s="99"/>
+      <c r="Q43" s="99"/>
+      <c r="R43" s="99"/>
+      <c r="S43" s="99"/>
+      <c r="T43" s="99"/>
+      <c r="U43" s="99"/>
+      <c r="V43" s="99"/>
+      <c r="W43" s="99"/>
+      <c r="X43" s="99"/>
+      <c r="Y43" s="99"/>
+      <c r="Z43" s="99"/>
+      <c r="AA43" s="99"/>
+      <c r="AB43" s="99"/>
+      <c r="AC43" s="99"/>
+      <c r="AD43" s="99"/>
+      <c r="AE43" s="99"/>
+      <c r="AF43" s="99"/>
+      <c r="AG43" s="99"/>
+      <c r="AH43" s="99"/>
+      <c r="AI43" s="99"/>
+      <c r="AJ43" s="99"/>
+      <c r="AK43" s="99"/>
+      <c r="AL43" s="99"/>
+      <c r="AM43" s="99"/>
+      <c r="AN43" s="99"/>
+      <c r="AO43" s="99"/>
+      <c r="AP43" s="99"/>
+      <c r="AQ43" s="99"/>
+      <c r="AR43" s="99"/>
+      <c r="AS43" s="99"/>
+      <c r="AT43" s="99"/>
+      <c r="AU43" s="99"/>
+      <c r="AV43" s="99"/>
+      <c r="AW43" s="99"/>
+      <c r="AX43" s="99"/>
+      <c r="AY43" s="99"/>
+      <c r="AZ43" s="99"/>
     </row>
     <row r="44" spans="1:52" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="140" t="s">
+      <c r="A44" s="214" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="141"/>
-      <c r="C44" s="141"/>
-      <c r="D44" s="141"/>
-      <c r="E44" s="141"/>
-      <c r="F44" s="141"/>
-      <c r="G44" s="141"/>
-      <c r="H44" s="141"/>
-      <c r="I44" s="141"/>
-      <c r="J44" s="141"/>
-      <c r="K44" s="141"/>
-      <c r="L44" s="141"/>
-      <c r="M44" s="141"/>
-      <c r="N44" s="141"/>
-      <c r="O44" s="141"/>
-      <c r="P44" s="141"/>
-      <c r="Q44" s="141"/>
-      <c r="R44" s="141"/>
-      <c r="S44" s="141"/>
-      <c r="T44" s="141"/>
-      <c r="U44" s="141"/>
-      <c r="V44" s="141"/>
-      <c r="W44" s="141"/>
-      <c r="X44" s="141"/>
-      <c r="Y44" s="141"/>
-      <c r="Z44" s="141"/>
-      <c r="AA44" s="141"/>
-      <c r="AB44" s="141"/>
-      <c r="AC44" s="141"/>
-      <c r="AD44" s="141"/>
-      <c r="AE44" s="141"/>
-      <c r="AF44" s="141"/>
-      <c r="AG44" s="141"/>
-      <c r="AH44" s="141"/>
-      <c r="AI44" s="141"/>
-      <c r="AJ44" s="141"/>
-      <c r="AK44" s="141"/>
-      <c r="AL44" s="141"/>
-      <c r="AM44" s="141"/>
-      <c r="AN44" s="141"/>
-      <c r="AO44" s="141"/>
-      <c r="AP44" s="141"/>
-      <c r="AQ44" s="141"/>
-      <c r="AR44" s="141"/>
-      <c r="AS44" s="141"/>
-      <c r="AT44" s="141"/>
-      <c r="AU44" s="141"/>
-      <c r="AV44" s="141"/>
-      <c r="AW44" s="141"/>
-      <c r="AX44" s="141"/>
-      <c r="AY44" s="141"/>
-      <c r="AZ44" s="142"/>
+      <c r="B44" s="215"/>
+      <c r="C44" s="215"/>
+      <c r="D44" s="215"/>
+      <c r="E44" s="215"/>
+      <c r="F44" s="215"/>
+      <c r="G44" s="215"/>
+      <c r="H44" s="215"/>
+      <c r="I44" s="215"/>
+      <c r="J44" s="215"/>
+      <c r="K44" s="215"/>
+      <c r="L44" s="215"/>
+      <c r="M44" s="215"/>
+      <c r="N44" s="215"/>
+      <c r="O44" s="215"/>
+      <c r="P44" s="215"/>
+      <c r="Q44" s="215"/>
+      <c r="R44" s="215"/>
+      <c r="S44" s="215"/>
+      <c r="T44" s="215"/>
+      <c r="U44" s="215"/>
+      <c r="V44" s="215"/>
+      <c r="W44" s="215"/>
+      <c r="X44" s="215"/>
+      <c r="Y44" s="215"/>
+      <c r="Z44" s="215"/>
+      <c r="AA44" s="215"/>
+      <c r="AB44" s="215"/>
+      <c r="AC44" s="215"/>
+      <c r="AD44" s="215"/>
+      <c r="AE44" s="215"/>
+      <c r="AF44" s="215"/>
+      <c r="AG44" s="215"/>
+      <c r="AH44" s="215"/>
+      <c r="AI44" s="215"/>
+      <c r="AJ44" s="215"/>
+      <c r="AK44" s="215"/>
+      <c r="AL44" s="215"/>
+      <c r="AM44" s="215"/>
+      <c r="AN44" s="215"/>
+      <c r="AO44" s="215"/>
+      <c r="AP44" s="215"/>
+      <c r="AQ44" s="215"/>
+      <c r="AR44" s="215"/>
+      <c r="AS44" s="215"/>
+      <c r="AT44" s="215"/>
+      <c r="AU44" s="215"/>
+      <c r="AV44" s="215"/>
+      <c r="AW44" s="215"/>
+      <c r="AX44" s="215"/>
+      <c r="AY44" s="215"/>
+      <c r="AZ44" s="216"/>
     </row>
     <row r="45" spans="1:52" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="143"/>
-      <c r="B45" s="144"/>
-      <c r="C45" s="144"/>
-      <c r="D45" s="144"/>
-      <c r="E45" s="144"/>
-      <c r="F45" s="144"/>
-      <c r="G45" s="144"/>
-      <c r="H45" s="144"/>
-      <c r="I45" s="144"/>
-      <c r="J45" s="144"/>
-      <c r="K45" s="144"/>
-      <c r="L45" s="144"/>
-      <c r="M45" s="144"/>
-      <c r="N45" s="144"/>
-      <c r="O45" s="144"/>
-      <c r="P45" s="144"/>
-      <c r="Q45" s="144"/>
-      <c r="R45" s="144"/>
-      <c r="S45" s="144"/>
-      <c r="T45" s="144"/>
-      <c r="U45" s="144"/>
-      <c r="V45" s="144"/>
-      <c r="W45" s="144"/>
-      <c r="X45" s="144"/>
-      <c r="Y45" s="144"/>
-      <c r="Z45" s="144"/>
-      <c r="AA45" s="144"/>
-      <c r="AB45" s="144"/>
-      <c r="AC45" s="144"/>
-      <c r="AD45" s="144"/>
-      <c r="AE45" s="144"/>
-      <c r="AF45" s="144"/>
-      <c r="AG45" s="144"/>
-      <c r="AH45" s="144"/>
-      <c r="AI45" s="144"/>
-      <c r="AJ45" s="144"/>
-      <c r="AK45" s="144"/>
-      <c r="AL45" s="144"/>
-      <c r="AM45" s="144"/>
-      <c r="AN45" s="144"/>
-      <c r="AO45" s="144"/>
-      <c r="AP45" s="144"/>
-      <c r="AQ45" s="144"/>
-      <c r="AR45" s="144"/>
-      <c r="AS45" s="144"/>
-      <c r="AT45" s="144"/>
-      <c r="AU45" s="144"/>
-      <c r="AV45" s="144"/>
-      <c r="AW45" s="144"/>
-      <c r="AX45" s="144"/>
-      <c r="AY45" s="144"/>
-      <c r="AZ45" s="145"/>
+      <c r="A45" s="217"/>
+      <c r="B45" s="218"/>
+      <c r="C45" s="218"/>
+      <c r="D45" s="218"/>
+      <c r="E45" s="218"/>
+      <c r="F45" s="218"/>
+      <c r="G45" s="218"/>
+      <c r="H45" s="218"/>
+      <c r="I45" s="218"/>
+      <c r="J45" s="218"/>
+      <c r="K45" s="218"/>
+      <c r="L45" s="218"/>
+      <c r="M45" s="218"/>
+      <c r="N45" s="218"/>
+      <c r="O45" s="218"/>
+      <c r="P45" s="218"/>
+      <c r="Q45" s="218"/>
+      <c r="R45" s="218"/>
+      <c r="S45" s="218"/>
+      <c r="T45" s="218"/>
+      <c r="U45" s="218"/>
+      <c r="V45" s="218"/>
+      <c r="W45" s="218"/>
+      <c r="X45" s="218"/>
+      <c r="Y45" s="218"/>
+      <c r="Z45" s="218"/>
+      <c r="AA45" s="218"/>
+      <c r="AB45" s="218"/>
+      <c r="AC45" s="218"/>
+      <c r="AD45" s="218"/>
+      <c r="AE45" s="218"/>
+      <c r="AF45" s="218"/>
+      <c r="AG45" s="218"/>
+      <c r="AH45" s="218"/>
+      <c r="AI45" s="218"/>
+      <c r="AJ45" s="218"/>
+      <c r="AK45" s="218"/>
+      <c r="AL45" s="218"/>
+      <c r="AM45" s="218"/>
+      <c r="AN45" s="218"/>
+      <c r="AO45" s="218"/>
+      <c r="AP45" s="218"/>
+      <c r="AQ45" s="218"/>
+      <c r="AR45" s="218"/>
+      <c r="AS45" s="218"/>
+      <c r="AT45" s="218"/>
+      <c r="AU45" s="218"/>
+      <c r="AV45" s="218"/>
+      <c r="AW45" s="218"/>
+      <c r="AX45" s="218"/>
+      <c r="AY45" s="218"/>
+      <c r="AZ45" s="219"/>
     </row>
     <row r="46" spans="1:52" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
@@ -7909,174 +7963,174 @@
       <c r="AZ46"/>
     </row>
     <row r="47" spans="1:52" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="147"/>
-      <c r="B47" s="147"/>
-      <c r="C47" s="147"/>
-      <c r="D47" s="147"/>
-      <c r="E47" s="147"/>
-      <c r="F47" s="147"/>
-      <c r="G47" s="147"/>
-      <c r="H47" s="147"/>
-      <c r="I47" s="147"/>
-      <c r="J47" s="147"/>
-      <c r="K47" s="147"/>
-      <c r="L47" s="147"/>
-      <c r="M47" s="147"/>
-      <c r="N47" s="147"/>
-      <c r="O47" s="147"/>
-      <c r="P47" s="147"/>
+      <c r="A47" s="117"/>
+      <c r="B47" s="117"/>
+      <c r="C47" s="117"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="117"/>
+      <c r="H47" s="117"/>
+      <c r="I47" s="117"/>
+      <c r="J47" s="117"/>
+      <c r="K47" s="117"/>
+      <c r="L47" s="117"/>
+      <c r="M47" s="117"/>
+      <c r="N47" s="117"/>
+      <c r="O47" s="117"/>
+      <c r="P47" s="117"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
-      <c r="S47" s="147"/>
-      <c r="T47" s="147"/>
-      <c r="U47" s="147"/>
-      <c r="V47" s="147"/>
-      <c r="W47" s="147"/>
-      <c r="X47" s="147"/>
-      <c r="Y47" s="147"/>
-      <c r="Z47" s="147"/>
-      <c r="AA47" s="147"/>
-      <c r="AB47" s="147"/>
-      <c r="AC47" s="147"/>
-      <c r="AD47" s="147"/>
-      <c r="AE47" s="147"/>
-      <c r="AF47" s="147"/>
-      <c r="AG47" s="147"/>
-      <c r="AH47" s="147"/>
+      <c r="S47" s="117"/>
+      <c r="T47" s="117"/>
+      <c r="U47" s="117"/>
+      <c r="V47" s="117"/>
+      <c r="W47" s="117"/>
+      <c r="X47" s="117"/>
+      <c r="Y47" s="117"/>
+      <c r="Z47" s="117"/>
+      <c r="AA47" s="117"/>
+      <c r="AB47" s="117"/>
+      <c r="AC47" s="117"/>
+      <c r="AD47" s="117"/>
+      <c r="AE47" s="117"/>
+      <c r="AF47" s="117"/>
+      <c r="AG47" s="117"/>
+      <c r="AH47" s="117"/>
       <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
-      <c r="AK47" s="147"/>
-      <c r="AL47" s="147"/>
-      <c r="AM47" s="147"/>
-      <c r="AN47" s="147"/>
-      <c r="AO47" s="147"/>
-      <c r="AP47" s="147"/>
-      <c r="AQ47" s="147"/>
-      <c r="AR47" s="147"/>
-      <c r="AS47" s="147"/>
-      <c r="AT47" s="147"/>
-      <c r="AU47" s="147"/>
-      <c r="AV47" s="147"/>
-      <c r="AW47" s="147"/>
-      <c r="AX47" s="147"/>
-      <c r="AY47" s="147"/>
-      <c r="AZ47" s="147"/>
+      <c r="AK47" s="117"/>
+      <c r="AL47" s="117"/>
+      <c r="AM47" s="117"/>
+      <c r="AN47" s="117"/>
+      <c r="AO47" s="117"/>
+      <c r="AP47" s="117"/>
+      <c r="AQ47" s="117"/>
+      <c r="AR47" s="117"/>
+      <c r="AS47" s="117"/>
+      <c r="AT47" s="117"/>
+      <c r="AU47" s="117"/>
+      <c r="AV47" s="117"/>
+      <c r="AW47" s="117"/>
+      <c r="AX47" s="117"/>
+      <c r="AY47" s="117"/>
+      <c r="AZ47" s="117"/>
     </row>
     <row r="48" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="211" t="s">
+      <c r="A48" s="118" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="211"/>
-      <c r="C48" s="211"/>
-      <c r="D48" s="211"/>
-      <c r="E48" s="211"/>
-      <c r="F48" s="211"/>
-      <c r="G48" s="211"/>
-      <c r="H48" s="211"/>
-      <c r="I48" s="211"/>
-      <c r="J48" s="211"/>
-      <c r="K48" s="211"/>
-      <c r="L48" s="211"/>
-      <c r="M48" s="211"/>
-      <c r="N48" s="211"/>
-      <c r="O48" s="211"/>
-      <c r="P48" s="211"/>
+      <c r="B48" s="118"/>
+      <c r="C48" s="118"/>
+      <c r="D48" s="118"/>
+      <c r="E48" s="118"/>
+      <c r="F48" s="118"/>
+      <c r="G48" s="118"/>
+      <c r="H48" s="118"/>
+      <c r="I48" s="118"/>
+      <c r="J48" s="118"/>
+      <c r="K48" s="118"/>
+      <c r="L48" s="118"/>
+      <c r="M48" s="118"/>
+      <c r="N48" s="118"/>
+      <c r="O48" s="118"/>
+      <c r="P48" s="118"/>
       <c r="Q48" s="54"/>
       <c r="R48" s="54"/>
-      <c r="S48" s="122" t="s">
+      <c r="S48" s="195" t="s">
         <v>78</v>
       </c>
-      <c r="T48" s="122"/>
-      <c r="U48" s="122"/>
-      <c r="V48" s="122"/>
-      <c r="W48" s="122"/>
-      <c r="X48" s="122"/>
-      <c r="Y48" s="122"/>
-      <c r="Z48" s="122"/>
-      <c r="AA48" s="122"/>
-      <c r="AB48" s="122"/>
-      <c r="AC48" s="122"/>
-      <c r="AD48" s="122"/>
-      <c r="AE48" s="122"/>
-      <c r="AF48" s="122"/>
-      <c r="AG48" s="122"/>
-      <c r="AH48" s="122"/>
+      <c r="T48" s="195"/>
+      <c r="U48" s="195"/>
+      <c r="V48" s="195"/>
+      <c r="W48" s="195"/>
+      <c r="X48" s="195"/>
+      <c r="Y48" s="195"/>
+      <c r="Z48" s="195"/>
+      <c r="AA48" s="195"/>
+      <c r="AB48" s="195"/>
+      <c r="AC48" s="195"/>
+      <c r="AD48" s="195"/>
+      <c r="AE48" s="195"/>
+      <c r="AF48" s="195"/>
+      <c r="AG48" s="195"/>
+      <c r="AH48" s="195"/>
       <c r="AI48" s="54"/>
       <c r="AJ48" s="54"/>
-      <c r="AK48" s="211" t="s">
+      <c r="AK48" s="118" t="s">
         <v>79</v>
       </c>
-      <c r="AL48" s="211"/>
-      <c r="AM48" s="211"/>
-      <c r="AN48" s="211"/>
-      <c r="AO48" s="211"/>
-      <c r="AP48" s="211"/>
-      <c r="AQ48" s="211"/>
-      <c r="AR48" s="211"/>
-      <c r="AS48" s="211"/>
-      <c r="AT48" s="211"/>
-      <c r="AU48" s="211"/>
-      <c r="AV48" s="211"/>
-      <c r="AW48" s="211"/>
-      <c r="AX48" s="211"/>
-      <c r="AY48" s="211"/>
-      <c r="AZ48" s="211"/>
+      <c r="AL48" s="118"/>
+      <c r="AM48" s="118"/>
+      <c r="AN48" s="118"/>
+      <c r="AO48" s="118"/>
+      <c r="AP48" s="118"/>
+      <c r="AQ48" s="118"/>
+      <c r="AR48" s="118"/>
+      <c r="AS48" s="118"/>
+      <c r="AT48" s="118"/>
+      <c r="AU48" s="118"/>
+      <c r="AV48" s="118"/>
+      <c r="AW48" s="118"/>
+      <c r="AX48" s="118"/>
+      <c r="AY48" s="118"/>
+      <c r="AZ48" s="118"/>
     </row>
     <row r="49" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="89" t="s">
+      <c r="A49" s="120" t="s">
         <v>80</v>
       </c>
-      <c r="B49" s="89"/>
-      <c r="C49" s="89"/>
-      <c r="D49" s="89"/>
-      <c r="E49" s="89"/>
-      <c r="F49" s="89"/>
-      <c r="G49" s="89"/>
-      <c r="H49" s="89"/>
-      <c r="I49" s="89"/>
-      <c r="J49" s="89"/>
-      <c r="K49" s="89"/>
-      <c r="L49" s="89"/>
-      <c r="M49" s="89"/>
-      <c r="N49" s="89"/>
-      <c r="O49" s="89"/>
-      <c r="P49" s="89"/>
-      <c r="S49" s="89" t="s">
+      <c r="B49" s="120"/>
+      <c r="C49" s="120"/>
+      <c r="D49" s="120"/>
+      <c r="E49" s="120"/>
+      <c r="F49" s="120"/>
+      <c r="G49" s="120"/>
+      <c r="H49" s="120"/>
+      <c r="I49" s="120"/>
+      <c r="J49" s="120"/>
+      <c r="K49" s="120"/>
+      <c r="L49" s="120"/>
+      <c r="M49" s="120"/>
+      <c r="N49" s="120"/>
+      <c r="O49" s="120"/>
+      <c r="P49" s="120"/>
+      <c r="S49" s="120" t="s">
         <v>81</v>
       </c>
-      <c r="T49" s="89"/>
-      <c r="U49" s="89"/>
-      <c r="V49" s="89"/>
-      <c r="W49" s="89"/>
-      <c r="X49" s="89"/>
-      <c r="Y49" s="89"/>
-      <c r="Z49" s="89"/>
-      <c r="AA49" s="89"/>
-      <c r="AB49" s="89"/>
-      <c r="AC49" s="89"/>
-      <c r="AD49" s="89"/>
-      <c r="AE49" s="89"/>
-      <c r="AF49" s="89"/>
-      <c r="AG49" s="89"/>
-      <c r="AH49" s="89"/>
-      <c r="AK49" s="212" t="s">
+      <c r="T49" s="120"/>
+      <c r="U49" s="120"/>
+      <c r="V49" s="120"/>
+      <c r="W49" s="120"/>
+      <c r="X49" s="120"/>
+      <c r="Y49" s="120"/>
+      <c r="Z49" s="120"/>
+      <c r="AA49" s="120"/>
+      <c r="AB49" s="120"/>
+      <c r="AC49" s="120"/>
+      <c r="AD49" s="120"/>
+      <c r="AE49" s="120"/>
+      <c r="AF49" s="120"/>
+      <c r="AG49" s="120"/>
+      <c r="AH49" s="120"/>
+      <c r="AK49" s="119" t="s">
         <v>792</v>
       </c>
-      <c r="AL49" s="212"/>
-      <c r="AM49" s="212"/>
-      <c r="AN49" s="212"/>
-      <c r="AO49" s="212"/>
-      <c r="AP49" s="212"/>
-      <c r="AQ49" s="212"/>
-      <c r="AR49" s="212"/>
-      <c r="AS49" s="212"/>
-      <c r="AT49" s="212"/>
-      <c r="AU49" s="212"/>
-      <c r="AV49" s="212"/>
-      <c r="AW49" s="212"/>
-      <c r="AX49" s="212"/>
-      <c r="AY49" s="212"/>
-      <c r="AZ49" s="212"/>
+      <c r="AL49" s="119"/>
+      <c r="AM49" s="119"/>
+      <c r="AN49" s="119"/>
+      <c r="AO49" s="119"/>
+      <c r="AP49" s="119"/>
+      <c r="AQ49" s="119"/>
+      <c r="AR49" s="119"/>
+      <c r="AS49" s="119"/>
+      <c r="AT49" s="119"/>
+      <c r="AU49" s="119"/>
+      <c r="AV49" s="119"/>
+      <c r="AW49" s="119"/>
+      <c r="AX49" s="119"/>
+      <c r="AY49" s="119"/>
+      <c r="AZ49" s="119"/>
     </row>
     <row r="50" spans="1:52" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
@@ -9546,6 +9600,153 @@
   </sortState>
   <dataConsolidate function="count"/>
   <mergeCells count="171">
+    <mergeCell ref="S49:U49"/>
+    <mergeCell ref="V49:AH49"/>
+    <mergeCell ref="BD21:BE21"/>
+    <mergeCell ref="BD23:BE23"/>
+    <mergeCell ref="BD25:BE25"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="K12:AZ12"/>
+    <mergeCell ref="AH37:AZ37"/>
+    <mergeCell ref="AH38:AZ38"/>
+    <mergeCell ref="AH33:AZ34"/>
+    <mergeCell ref="AH35:AZ35"/>
+    <mergeCell ref="K13:AZ13"/>
+    <mergeCell ref="AE9:AK9"/>
+    <mergeCell ref="A14:AZ14"/>
+    <mergeCell ref="A16:AZ16"/>
+    <mergeCell ref="AV17:AZ17"/>
+    <mergeCell ref="AQ17:AU17"/>
+    <mergeCell ref="AL17:AP17"/>
+    <mergeCell ref="AG17:AK17"/>
+    <mergeCell ref="AB17:AF17"/>
+    <mergeCell ref="W17:AA17"/>
+    <mergeCell ref="AV18:AZ18"/>
+    <mergeCell ref="AQ18:AU18"/>
+    <mergeCell ref="AL18:AP18"/>
+    <mergeCell ref="S48:AH48"/>
+    <mergeCell ref="S33:AG34"/>
+    <mergeCell ref="AH36:AZ36"/>
+    <mergeCell ref="A36:R36"/>
+    <mergeCell ref="A37:R37"/>
+    <mergeCell ref="A35:R35"/>
+    <mergeCell ref="S35:AG35"/>
+    <mergeCell ref="A33:R34"/>
+    <mergeCell ref="S42:AG42"/>
+    <mergeCell ref="S41:AG41"/>
+    <mergeCell ref="A44:AZ45"/>
+    <mergeCell ref="A43:AZ43"/>
+    <mergeCell ref="S47:AH47"/>
+    <mergeCell ref="AH39:AZ39"/>
+    <mergeCell ref="S36:AG36"/>
+    <mergeCell ref="A40:R40"/>
+    <mergeCell ref="A42:R42"/>
+    <mergeCell ref="S39:AG39"/>
+    <mergeCell ref="S38:AG38"/>
+    <mergeCell ref="S37:AG37"/>
+    <mergeCell ref="AH42:AZ42"/>
+    <mergeCell ref="AH41:AZ41"/>
+    <mergeCell ref="AH40:AZ40"/>
+    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="R25:V25"/>
+    <mergeCell ref="AV24:AZ24"/>
+    <mergeCell ref="AV25:AZ25"/>
+    <mergeCell ref="AQ24:AU24"/>
+    <mergeCell ref="AQ25:AU25"/>
+    <mergeCell ref="W24:AA24"/>
+    <mergeCell ref="W25:AA25"/>
+    <mergeCell ref="AL24:AP24"/>
+    <mergeCell ref="AL25:AP25"/>
+    <mergeCell ref="AB25:AF25"/>
+    <mergeCell ref="AG25:AK25"/>
+    <mergeCell ref="A38:R38"/>
+    <mergeCell ref="AR7:AU7"/>
+    <mergeCell ref="AE8:AK8"/>
+    <mergeCell ref="AV7:AZ7"/>
+    <mergeCell ref="S40:AG40"/>
+    <mergeCell ref="A39:R39"/>
+    <mergeCell ref="R19:V19"/>
+    <mergeCell ref="R20:V20"/>
+    <mergeCell ref="R21:V21"/>
+    <mergeCell ref="R22:V22"/>
+    <mergeCell ref="R23:V23"/>
+    <mergeCell ref="R24:V24"/>
+    <mergeCell ref="AG20:AK20"/>
+    <mergeCell ref="AG21:AK21"/>
+    <mergeCell ref="AG22:AK22"/>
+    <mergeCell ref="AG23:AK23"/>
+    <mergeCell ref="AG18:AK18"/>
+    <mergeCell ref="AB18:AF18"/>
+    <mergeCell ref="AB21:AF21"/>
+    <mergeCell ref="W18:AA18"/>
+    <mergeCell ref="A15:AZ15"/>
+    <mergeCell ref="AG24:AK24"/>
+    <mergeCell ref="AV20:AZ20"/>
+    <mergeCell ref="AV21:AZ21"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="AS1:AZ3"/>
+    <mergeCell ref="G6:AZ6"/>
+    <mergeCell ref="K2:AP2"/>
+    <mergeCell ref="A4:AZ4"/>
+    <mergeCell ref="AL9:AZ9"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="R17:V17"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="AE5:AK5"/>
+    <mergeCell ref="G5:AB5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="G8:AC8"/>
+    <mergeCell ref="V7:Y7"/>
+    <mergeCell ref="G9:AC9"/>
+    <mergeCell ref="AL8:AZ8"/>
+    <mergeCell ref="AL5:AZ5"/>
+    <mergeCell ref="AB23:AF23"/>
+    <mergeCell ref="AB24:AF24"/>
+    <mergeCell ref="Z7:AP7"/>
+    <mergeCell ref="AV23:AZ23"/>
+    <mergeCell ref="AQ19:AU19"/>
+    <mergeCell ref="AQ20:AU20"/>
+    <mergeCell ref="AQ21:AU21"/>
+    <mergeCell ref="AQ22:AU22"/>
+    <mergeCell ref="AQ23:AU23"/>
+    <mergeCell ref="W20:AA20"/>
+    <mergeCell ref="W21:AA21"/>
+    <mergeCell ref="W22:AA22"/>
+    <mergeCell ref="W23:AA23"/>
+    <mergeCell ref="AL19:AP19"/>
+    <mergeCell ref="AL20:AP20"/>
+    <mergeCell ref="AL21:AP21"/>
+    <mergeCell ref="AL22:AP22"/>
+    <mergeCell ref="AL23:AP23"/>
+    <mergeCell ref="AG19:AK19"/>
+    <mergeCell ref="A47:P47"/>
+    <mergeCell ref="AK47:AZ47"/>
+    <mergeCell ref="AK48:AZ48"/>
+    <mergeCell ref="A48:P48"/>
+    <mergeCell ref="AK49:AZ49"/>
+    <mergeCell ref="A49:P49"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="M23:Q23"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="AB19:AF19"/>
+    <mergeCell ref="AB20:AF20"/>
+    <mergeCell ref="W19:AA19"/>
+    <mergeCell ref="AB22:AF22"/>
     <mergeCell ref="R18:V18"/>
     <mergeCell ref="M18:Q18"/>
     <mergeCell ref="A18:L18"/>
@@ -9570,153 +9771,6 @@
     <mergeCell ref="AA31:AS31"/>
     <mergeCell ref="AT31:AZ31"/>
     <mergeCell ref="AV22:AZ22"/>
-    <mergeCell ref="A47:P47"/>
-    <mergeCell ref="AK47:AZ47"/>
-    <mergeCell ref="AK48:AZ48"/>
-    <mergeCell ref="A48:P48"/>
-    <mergeCell ref="AK49:AZ49"/>
-    <mergeCell ref="A49:P49"/>
-    <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="M21:Q21"/>
-    <mergeCell ref="M22:Q22"/>
-    <mergeCell ref="M23:Q23"/>
-    <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="M25:Q25"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A21:L21"/>
-    <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="AB19:AF19"/>
-    <mergeCell ref="AB20:AF20"/>
-    <mergeCell ref="W19:AA19"/>
-    <mergeCell ref="AB22:AF22"/>
-    <mergeCell ref="AB23:AF23"/>
-    <mergeCell ref="AB24:AF24"/>
-    <mergeCell ref="Z7:AP7"/>
-    <mergeCell ref="AV23:AZ23"/>
-    <mergeCell ref="AQ19:AU19"/>
-    <mergeCell ref="AQ20:AU20"/>
-    <mergeCell ref="AQ21:AU21"/>
-    <mergeCell ref="AQ22:AU22"/>
-    <mergeCell ref="AQ23:AU23"/>
-    <mergeCell ref="W20:AA20"/>
-    <mergeCell ref="W21:AA21"/>
-    <mergeCell ref="W22:AA22"/>
-    <mergeCell ref="W23:AA23"/>
-    <mergeCell ref="AL19:AP19"/>
-    <mergeCell ref="AL20:AP20"/>
-    <mergeCell ref="AL21:AP21"/>
-    <mergeCell ref="AL22:AP22"/>
-    <mergeCell ref="AL23:AP23"/>
-    <mergeCell ref="AG19:AK19"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="AS1:AZ3"/>
-    <mergeCell ref="G6:AZ6"/>
-    <mergeCell ref="K2:AP2"/>
-    <mergeCell ref="A4:AZ4"/>
-    <mergeCell ref="AL9:AZ9"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="R17:V17"/>
-    <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="AE5:AK5"/>
-    <mergeCell ref="G5:AB5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="G8:AC8"/>
-    <mergeCell ref="V7:Y7"/>
-    <mergeCell ref="G9:AC9"/>
-    <mergeCell ref="AL8:AZ8"/>
-    <mergeCell ref="AL5:AZ5"/>
-    <mergeCell ref="A38:R38"/>
-    <mergeCell ref="AR7:AU7"/>
-    <mergeCell ref="AE8:AK8"/>
-    <mergeCell ref="AV7:AZ7"/>
-    <mergeCell ref="S40:AG40"/>
-    <mergeCell ref="A39:R39"/>
-    <mergeCell ref="R19:V19"/>
-    <mergeCell ref="R20:V20"/>
-    <mergeCell ref="R21:V21"/>
-    <mergeCell ref="R22:V22"/>
-    <mergeCell ref="R23:V23"/>
-    <mergeCell ref="R24:V24"/>
-    <mergeCell ref="AG20:AK20"/>
-    <mergeCell ref="AG21:AK21"/>
-    <mergeCell ref="AG22:AK22"/>
-    <mergeCell ref="AG23:AK23"/>
-    <mergeCell ref="AG18:AK18"/>
-    <mergeCell ref="AB18:AF18"/>
-    <mergeCell ref="AB21:AF21"/>
-    <mergeCell ref="W18:AA18"/>
-    <mergeCell ref="A15:AZ15"/>
-    <mergeCell ref="AG24:AK24"/>
-    <mergeCell ref="AV20:AZ20"/>
-    <mergeCell ref="AV21:AZ21"/>
-    <mergeCell ref="R25:V25"/>
-    <mergeCell ref="AV24:AZ24"/>
-    <mergeCell ref="AV25:AZ25"/>
-    <mergeCell ref="AQ24:AU24"/>
-    <mergeCell ref="AQ25:AU25"/>
-    <mergeCell ref="W24:AA24"/>
-    <mergeCell ref="W25:AA25"/>
-    <mergeCell ref="AL24:AP24"/>
-    <mergeCell ref="AL25:AP25"/>
-    <mergeCell ref="AB25:AF25"/>
-    <mergeCell ref="AG25:AK25"/>
-    <mergeCell ref="S48:AH48"/>
-    <mergeCell ref="S33:AG34"/>
-    <mergeCell ref="AH36:AZ36"/>
-    <mergeCell ref="A36:R36"/>
-    <mergeCell ref="A37:R37"/>
-    <mergeCell ref="A35:R35"/>
-    <mergeCell ref="S35:AG35"/>
-    <mergeCell ref="A33:R34"/>
-    <mergeCell ref="S42:AG42"/>
-    <mergeCell ref="S41:AG41"/>
-    <mergeCell ref="A44:AZ45"/>
-    <mergeCell ref="A43:AZ43"/>
-    <mergeCell ref="S47:AH47"/>
-    <mergeCell ref="AH39:AZ39"/>
-    <mergeCell ref="S36:AG36"/>
-    <mergeCell ref="A40:R40"/>
-    <mergeCell ref="A42:R42"/>
-    <mergeCell ref="S39:AG39"/>
-    <mergeCell ref="S38:AG38"/>
-    <mergeCell ref="S37:AG37"/>
-    <mergeCell ref="AH42:AZ42"/>
-    <mergeCell ref="AH41:AZ41"/>
-    <mergeCell ref="AH40:AZ40"/>
-    <mergeCell ref="A41:R41"/>
-    <mergeCell ref="S49:U49"/>
-    <mergeCell ref="V49:AH49"/>
-    <mergeCell ref="BD21:BE21"/>
-    <mergeCell ref="BD23:BE23"/>
-    <mergeCell ref="BD25:BE25"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="K12:AZ12"/>
-    <mergeCell ref="AH37:AZ37"/>
-    <mergeCell ref="AH38:AZ38"/>
-    <mergeCell ref="AH33:AZ34"/>
-    <mergeCell ref="AH35:AZ35"/>
-    <mergeCell ref="K13:AZ13"/>
-    <mergeCell ref="AE9:AK9"/>
-    <mergeCell ref="A14:AZ14"/>
-    <mergeCell ref="A16:AZ16"/>
-    <mergeCell ref="AV17:AZ17"/>
-    <mergeCell ref="AQ17:AU17"/>
-    <mergeCell ref="AL17:AP17"/>
-    <mergeCell ref="AG17:AK17"/>
-    <mergeCell ref="AB17:AF17"/>
-    <mergeCell ref="W17:AA17"/>
-    <mergeCell ref="AV18:AZ18"/>
-    <mergeCell ref="AQ18:AU18"/>
-    <mergeCell ref="AL18:AP18"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations count="1">
@@ -9756,14 +9810,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="168"/>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="170"/>
+      <c r="A1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="139"/>
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
       <c r="K1" s="21"/>
@@ -9800,87 +9854,87 @@
       <c r="AP1" s="22"/>
       <c r="AQ1" s="22"/>
       <c r="AR1" s="22"/>
-      <c r="AS1" s="177" t="s">
+      <c r="AS1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="AT1" s="178"/>
-      <c r="AU1" s="178"/>
-      <c r="AV1" s="178"/>
-      <c r="AW1" s="178"/>
-      <c r="AX1" s="178"/>
-      <c r="AY1" s="178"/>
-      <c r="AZ1" s="179"/>
+      <c r="AT1" s="147"/>
+      <c r="AU1" s="147"/>
+      <c r="AV1" s="147"/>
+      <c r="AW1" s="147"/>
+      <c r="AX1" s="147"/>
+      <c r="AY1" s="147"/>
+      <c r="AZ1" s="148"/>
       <c r="BD1" s="23"/>
       <c r="BF1" s="27"/>
       <c r="BG1" s="27"/>
     </row>
     <row r="2" spans="1:60" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="171"/>
-      <c r="B2" s="172"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="173"/>
-      <c r="K2" s="187" t="s">
+      <c r="A2" s="140"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="142"/>
+      <c r="K2" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="252"/>
-      <c r="M2" s="252"/>
-      <c r="N2" s="252"/>
-      <c r="O2" s="252"/>
-      <c r="P2" s="252"/>
-      <c r="Q2" s="252"/>
-      <c r="R2" s="252"/>
-      <c r="S2" s="252"/>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252"/>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
-      <c r="AA2" s="252"/>
-      <c r="AB2" s="252"/>
-      <c r="AC2" s="252"/>
-      <c r="AD2" s="252"/>
-      <c r="AE2" s="252"/>
-      <c r="AF2" s="252"/>
-      <c r="AG2" s="252"/>
-      <c r="AH2" s="252"/>
-      <c r="AI2" s="252"/>
-      <c r="AJ2" s="252"/>
-      <c r="AK2" s="252"/>
-      <c r="AL2" s="252"/>
-      <c r="AM2" s="252"/>
-      <c r="AN2" s="252"/>
-      <c r="AO2" s="252"/>
-      <c r="AP2" s="252"/>
+      <c r="L2" s="246"/>
+      <c r="M2" s="246"/>
+      <c r="N2" s="246"/>
+      <c r="O2" s="246"/>
+      <c r="P2" s="246"/>
+      <c r="Q2" s="246"/>
+      <c r="R2" s="246"/>
+      <c r="S2" s="246"/>
+      <c r="T2" s="246"/>
+      <c r="U2" s="246"/>
+      <c r="V2" s="246"/>
+      <c r="W2" s="246"/>
+      <c r="X2" s="246"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
+      <c r="AA2" s="246"/>
+      <c r="AB2" s="246"/>
+      <c r="AC2" s="246"/>
+      <c r="AD2" s="246"/>
+      <c r="AE2" s="246"/>
+      <c r="AF2" s="246"/>
+      <c r="AG2" s="246"/>
+      <c r="AH2" s="246"/>
+      <c r="AI2" s="246"/>
+      <c r="AJ2" s="246"/>
+      <c r="AK2" s="246"/>
+      <c r="AL2" s="246"/>
+      <c r="AM2" s="246"/>
+      <c r="AN2" s="246"/>
+      <c r="AO2" s="246"/>
+      <c r="AP2" s="246"/>
       <c r="AQ2" s="17"/>
       <c r="AR2" s="17"/>
-      <c r="AS2" s="180"/>
-      <c r="AT2" s="181"/>
-      <c r="AU2" s="181"/>
-      <c r="AV2" s="181"/>
-      <c r="AW2" s="181"/>
-      <c r="AX2" s="181"/>
-      <c r="AY2" s="181"/>
-      <c r="AZ2" s="182"/>
+      <c r="AS2" s="149"/>
+      <c r="AT2" s="150"/>
+      <c r="AU2" s="150"/>
+      <c r="AV2" s="150"/>
+      <c r="AW2" s="150"/>
+      <c r="AX2" s="150"/>
+      <c r="AY2" s="150"/>
+      <c r="AZ2" s="151"/>
       <c r="BA2" s="7"/>
       <c r="BF2" s="25"/>
       <c r="BG2" s="25"/>
       <c r="BH2" s="25"/>
     </row>
     <row r="3" spans="1:60" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="174"/>
-      <c r="B3" s="175"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="176"/>
+      <c r="A3" s="143"/>
+      <c r="B3" s="144"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="145"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -9917,80 +9971,80 @@
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
       <c r="AR3" s="4"/>
-      <c r="AS3" s="183"/>
-      <c r="AT3" s="184"/>
-      <c r="AU3" s="184"/>
-      <c r="AV3" s="184"/>
-      <c r="AW3" s="184"/>
-      <c r="AX3" s="184"/>
-      <c r="AY3" s="184"/>
-      <c r="AZ3" s="185"/>
+      <c r="AS3" s="152"/>
+      <c r="AT3" s="153"/>
+      <c r="AU3" s="153"/>
+      <c r="AV3" s="153"/>
+      <c r="AW3" s="153"/>
+      <c r="AX3" s="153"/>
+      <c r="AY3" s="153"/>
+      <c r="AZ3" s="154"/>
     </row>
     <row r="4" spans="1:60" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="189" t="s">
+      <c r="A4" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="190"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="190"/>
-      <c r="K4" s="190"/>
-      <c r="L4" s="190"/>
-      <c r="M4" s="190"/>
-      <c r="N4" s="190"/>
-      <c r="O4" s="190"/>
-      <c r="P4" s="190"/>
-      <c r="Q4" s="190"/>
-      <c r="R4" s="190"/>
-      <c r="S4" s="190"/>
-      <c r="T4" s="190"/>
-      <c r="U4" s="190"/>
-      <c r="V4" s="190"/>
-      <c r="W4" s="190"/>
-      <c r="X4" s="190"/>
-      <c r="Y4" s="190"/>
-      <c r="Z4" s="190"/>
-      <c r="AA4" s="190"/>
-      <c r="AB4" s="190"/>
-      <c r="AC4" s="190"/>
-      <c r="AD4" s="190"/>
-      <c r="AE4" s="190"/>
-      <c r="AF4" s="190"/>
-      <c r="AG4" s="190"/>
-      <c r="AH4" s="190"/>
-      <c r="AI4" s="190"/>
-      <c r="AJ4" s="190"/>
-      <c r="AK4" s="190"/>
-      <c r="AL4" s="190"/>
-      <c r="AM4" s="190"/>
-      <c r="AN4" s="190"/>
-      <c r="AO4" s="190"/>
-      <c r="AP4" s="190"/>
-      <c r="AQ4" s="190"/>
-      <c r="AR4" s="190"/>
-      <c r="AS4" s="190"/>
-      <c r="AT4" s="190"/>
-      <c r="AU4" s="190"/>
-      <c r="AV4" s="190"/>
-      <c r="AW4" s="190"/>
-      <c r="AX4" s="190"/>
-      <c r="AY4" s="190"/>
-      <c r="AZ4" s="191"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="101"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="101"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="101"/>
+      <c r="S4" s="101"/>
+      <c r="T4" s="101"/>
+      <c r="U4" s="101"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="101"/>
+      <c r="X4" s="101"/>
+      <c r="Y4" s="101"/>
+      <c r="Z4" s="101"/>
+      <c r="AA4" s="101"/>
+      <c r="AB4" s="101"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="101"/>
+      <c r="AE4" s="101"/>
+      <c r="AF4" s="101"/>
+      <c r="AG4" s="101"/>
+      <c r="AH4" s="101"/>
+      <c r="AI4" s="101"/>
+      <c r="AJ4" s="101"/>
+      <c r="AK4" s="101"/>
+      <c r="AL4" s="101"/>
+      <c r="AM4" s="101"/>
+      <c r="AN4" s="101"/>
+      <c r="AO4" s="101"/>
+      <c r="AP4" s="101"/>
+      <c r="AQ4" s="101"/>
+      <c r="AR4" s="101"/>
+      <c r="AS4" s="101"/>
+      <c r="AT4" s="101"/>
+      <c r="AU4" s="101"/>
+      <c r="AV4" s="101"/>
+      <c r="AW4" s="101"/>
+      <c r="AX4" s="101"/>
+      <c r="AY4" s="101"/>
+      <c r="AZ4" s="102"/>
       <c r="BA4" s="9"/>
       <c r="BB4" s="9"/>
       <c r="BC4" s="9"/>
     </row>
     <row r="5" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="253" t="s">
+      <c r="A5" s="247" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="254"/>
-      <c r="C5" s="254"/>
+      <c r="B5" s="248"/>
+      <c r="C5" s="248"/>
       <c r="D5" s="11"/>
       <c r="E5" s="6" t="s">
         <v>105</v>
@@ -10047,63 +10101,63 @@
       <c r="BC5" s="9"/>
     </row>
     <row r="6" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="248"/>
-      <c r="B6" s="249"/>
-      <c r="C6" s="249"/>
+      <c r="A6" s="244"/>
+      <c r="B6" s="245"/>
+      <c r="C6" s="245"/>
       <c r="D6" s="10"/>
-      <c r="E6" s="255"/>
-      <c r="F6" s="255"/>
-      <c r="G6" s="255"/>
-      <c r="H6" s="255"/>
-      <c r="I6" s="255"/>
-      <c r="J6" s="255"/>
-      <c r="K6" s="255"/>
-      <c r="L6" s="255"/>
-      <c r="M6" s="255"/>
-      <c r="N6" s="255"/>
-      <c r="O6" s="255"/>
-      <c r="P6" s="255"/>
-      <c r="Q6" s="255"/>
-      <c r="R6" s="255"/>
-      <c r="S6" s="255"/>
-      <c r="T6" s="255"/>
-      <c r="U6" s="255"/>
-      <c r="V6" s="255"/>
-      <c r="W6" s="255"/>
-      <c r="X6" s="255"/>
-      <c r="Y6" s="255"/>
-      <c r="Z6" s="255"/>
-      <c r="AA6" s="255"/>
-      <c r="AB6" s="255"/>
-      <c r="AC6" s="255"/>
-      <c r="AD6" s="255"/>
-      <c r="AE6" s="255"/>
-      <c r="AF6" s="255"/>
-      <c r="AG6" s="255"/>
-      <c r="AH6" s="255"/>
-      <c r="AI6" s="255"/>
-      <c r="AJ6" s="255"/>
-      <c r="AK6" s="255"/>
-      <c r="AL6" s="255"/>
-      <c r="AM6" s="255"/>
-      <c r="AN6" s="255"/>
-      <c r="AO6" s="255"/>
-      <c r="AP6" s="255"/>
-      <c r="AQ6" s="255"/>
-      <c r="AR6" s="255"/>
-      <c r="AS6" s="255"/>
-      <c r="AT6" s="255"/>
-      <c r="AU6" s="255"/>
-      <c r="AV6" s="255"/>
-      <c r="AW6" s="255"/>
-      <c r="AX6" s="255"/>
-      <c r="AY6" s="255"/>
-      <c r="AZ6" s="256"/>
+      <c r="E6" s="249"/>
+      <c r="F6" s="249"/>
+      <c r="G6" s="249"/>
+      <c r="H6" s="249"/>
+      <c r="I6" s="249"/>
+      <c r="J6" s="249"/>
+      <c r="K6" s="249"/>
+      <c r="L6" s="249"/>
+      <c r="M6" s="249"/>
+      <c r="N6" s="249"/>
+      <c r="O6" s="249"/>
+      <c r="P6" s="249"/>
+      <c r="Q6" s="249"/>
+      <c r="R6" s="249"/>
+      <c r="S6" s="249"/>
+      <c r="T6" s="249"/>
+      <c r="U6" s="249"/>
+      <c r="V6" s="249"/>
+      <c r="W6" s="249"/>
+      <c r="X6" s="249"/>
+      <c r="Y6" s="249"/>
+      <c r="Z6" s="249"/>
+      <c r="AA6" s="249"/>
+      <c r="AB6" s="249"/>
+      <c r="AC6" s="249"/>
+      <c r="AD6" s="249"/>
+      <c r="AE6" s="249"/>
+      <c r="AF6" s="249"/>
+      <c r="AG6" s="249"/>
+      <c r="AH6" s="249"/>
+      <c r="AI6" s="249"/>
+      <c r="AJ6" s="249"/>
+      <c r="AK6" s="249"/>
+      <c r="AL6" s="249"/>
+      <c r="AM6" s="249"/>
+      <c r="AN6" s="249"/>
+      <c r="AO6" s="249"/>
+      <c r="AP6" s="249"/>
+      <c r="AQ6" s="249"/>
+      <c r="AR6" s="249"/>
+      <c r="AS6" s="249"/>
+      <c r="AT6" s="249"/>
+      <c r="AU6" s="249"/>
+      <c r="AV6" s="249"/>
+      <c r="AW6" s="249"/>
+      <c r="AX6" s="249"/>
+      <c r="AY6" s="249"/>
+      <c r="AZ6" s="250"/>
     </row>
     <row r="7" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="248"/>
-      <c r="B7" s="249"/>
-      <c r="C7" s="249"/>
+      <c r="A7" s="244"/>
+      <c r="B7" s="245"/>
+      <c r="C7" s="245"/>
       <c r="D7" s="10"/>
       <c r="E7" s="86"/>
       <c r="F7" s="87"/>
@@ -10155,9 +10209,9 @@
       <c r="AZ7" s="88"/>
     </row>
     <row r="8" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="257"/>
-      <c r="B8" s="258"/>
-      <c r="C8" s="258"/>
+      <c r="A8" s="242"/>
+      <c r="B8" s="243"/>
+      <c r="C8" s="243"/>
       <c r="D8" s="10"/>
       <c r="E8" s="87"/>
       <c r="F8" s="87"/>
@@ -10209,63 +10263,63 @@
       <c r="AZ8" s="88"/>
     </row>
     <row r="9" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="257"/>
-      <c r="B9" s="258"/>
-      <c r="C9" s="258"/>
+      <c r="A9" s="242"/>
+      <c r="B9" s="243"/>
+      <c r="C9" s="243"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="250"/>
-      <c r="F9" s="250"/>
-      <c r="G9" s="250"/>
-      <c r="H9" s="250"/>
-      <c r="I9" s="250"/>
-      <c r="J9" s="250"/>
-      <c r="K9" s="250"/>
-      <c r="L9" s="250"/>
-      <c r="M9" s="250"/>
-      <c r="N9" s="250"/>
-      <c r="O9" s="250"/>
-      <c r="P9" s="250"/>
-      <c r="Q9" s="250"/>
-      <c r="R9" s="250"/>
-      <c r="S9" s="250"/>
-      <c r="T9" s="250"/>
-      <c r="U9" s="250"/>
-      <c r="V9" s="250"/>
-      <c r="W9" s="250"/>
-      <c r="X9" s="250"/>
-      <c r="Y9" s="250"/>
-      <c r="Z9" s="250"/>
-      <c r="AA9" s="250"/>
-      <c r="AB9" s="250"/>
-      <c r="AC9" s="250"/>
-      <c r="AD9" s="250"/>
-      <c r="AE9" s="250"/>
-      <c r="AF9" s="250"/>
-      <c r="AG9" s="250"/>
-      <c r="AH9" s="250"/>
-      <c r="AI9" s="250"/>
-      <c r="AJ9" s="250"/>
-      <c r="AK9" s="250"/>
-      <c r="AL9" s="250"/>
-      <c r="AM9" s="250"/>
-      <c r="AN9" s="250"/>
-      <c r="AO9" s="250"/>
-      <c r="AP9" s="250"/>
-      <c r="AQ9" s="250"/>
-      <c r="AR9" s="250"/>
-      <c r="AS9" s="250"/>
-      <c r="AT9" s="250"/>
-      <c r="AU9" s="250"/>
-      <c r="AV9" s="250"/>
-      <c r="AW9" s="250"/>
-      <c r="AX9" s="250"/>
-      <c r="AY9" s="250"/>
-      <c r="AZ9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
+      <c r="M9" s="251"/>
+      <c r="N9" s="251"/>
+      <c r="O9" s="251"/>
+      <c r="P9" s="251"/>
+      <c r="Q9" s="251"/>
+      <c r="R9" s="251"/>
+      <c r="S9" s="251"/>
+      <c r="T9" s="251"/>
+      <c r="U9" s="251"/>
+      <c r="V9" s="251"/>
+      <c r="W9" s="251"/>
+      <c r="X9" s="251"/>
+      <c r="Y9" s="251"/>
+      <c r="Z9" s="251"/>
+      <c r="AA9" s="251"/>
+      <c r="AB9" s="251"/>
+      <c r="AC9" s="251"/>
+      <c r="AD9" s="251"/>
+      <c r="AE9" s="251"/>
+      <c r="AF9" s="251"/>
+      <c r="AG9" s="251"/>
+      <c r="AH9" s="251"/>
+      <c r="AI9" s="251"/>
+      <c r="AJ9" s="251"/>
+      <c r="AK9" s="251"/>
+      <c r="AL9" s="251"/>
+      <c r="AM9" s="251"/>
+      <c r="AN9" s="251"/>
+      <c r="AO9" s="251"/>
+      <c r="AP9" s="251"/>
+      <c r="AQ9" s="251"/>
+      <c r="AR9" s="251"/>
+      <c r="AS9" s="251"/>
+      <c r="AT9" s="251"/>
+      <c r="AU9" s="251"/>
+      <c r="AV9" s="251"/>
+      <c r="AW9" s="251"/>
+      <c r="AX9" s="251"/>
+      <c r="AY9" s="251"/>
+      <c r="AZ9" s="252"/>
     </row>
     <row r="10" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="257"/>
-      <c r="B10" s="258"/>
-      <c r="C10" s="258"/>
+      <c r="A10" s="242"/>
+      <c r="B10" s="243"/>
+      <c r="C10" s="243"/>
       <c r="D10" s="10"/>
       <c r="E10" s="86"/>
       <c r="F10" s="87"/>
@@ -10317,9 +10371,9 @@
       <c r="AZ10" s="88"/>
     </row>
     <row r="11" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="248"/>
-      <c r="B11" s="249"/>
-      <c r="C11" s="249"/>
+      <c r="A11" s="244"/>
+      <c r="B11" s="245"/>
+      <c r="C11" s="245"/>
       <c r="D11" s="10"/>
       <c r="E11" s="87"/>
       <c r="F11" s="87"/>
@@ -10371,9 +10425,9 @@
       <c r="AZ11" s="88"/>
     </row>
     <row r="12" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="248"/>
-      <c r="B12" s="249"/>
-      <c r="C12" s="249"/>
+      <c r="A12" s="244"/>
+      <c r="B12" s="245"/>
+      <c r="C12" s="245"/>
       <c r="D12" s="10"/>
       <c r="E12" s="87"/>
       <c r="F12" s="87"/>
@@ -10425,9 +10479,9 @@
       <c r="AZ12" s="88"/>
     </row>
     <row r="13" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="248"/>
-      <c r="B13" s="249"/>
-      <c r="C13" s="249"/>
+      <c r="A13" s="244"/>
+      <c r="B13" s="245"/>
+      <c r="C13" s="245"/>
       <c r="D13" s="10"/>
       <c r="E13" s="87"/>
       <c r="F13" s="87"/>
@@ -10479,9 +10533,9 @@
       <c r="AZ13" s="88"/>
     </row>
     <row r="14" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="248"/>
-      <c r="B14" s="249"/>
-      <c r="C14" s="249"/>
+      <c r="A14" s="244"/>
+      <c r="B14" s="245"/>
+      <c r="C14" s="245"/>
       <c r="D14" s="10"/>
       <c r="E14" s="87"/>
       <c r="F14" s="87"/>
@@ -10533,9 +10587,9 @@
       <c r="AZ14" s="88"/>
     </row>
     <row r="15" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="248"/>
-      <c r="B15" s="249"/>
-      <c r="C15" s="249"/>
+      <c r="A15" s="244"/>
+      <c r="B15" s="245"/>
+      <c r="C15" s="245"/>
       <c r="D15" s="10"/>
       <c r="E15" s="86"/>
       <c r="F15" s="87"/>
@@ -10587,9 +10641,9 @@
       <c r="AZ15" s="88"/>
     </row>
     <row r="16" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="248"/>
-      <c r="B16" s="249"/>
-      <c r="C16" s="249"/>
+      <c r="A16" s="244"/>
+      <c r="B16" s="245"/>
+      <c r="C16" s="245"/>
       <c r="D16" s="10"/>
       <c r="E16" s="86"/>
       <c r="F16" s="87"/>
@@ -10641,9 +10695,9 @@
       <c r="AZ16" s="88"/>
     </row>
     <row r="17" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="248"/>
-      <c r="B17" s="249"/>
-      <c r="C17" s="249"/>
+      <c r="A17" s="244"/>
+      <c r="B17" s="245"/>
+      <c r="C17" s="245"/>
       <c r="D17" s="10"/>
       <c r="E17" s="86"/>
       <c r="F17" s="87"/>
@@ -10695,9 +10749,9 @@
       <c r="AZ17" s="88"/>
     </row>
     <row r="18" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="248"/>
-      <c r="B18" s="249"/>
-      <c r="C18" s="249"/>
+      <c r="A18" s="244"/>
+      <c r="B18" s="245"/>
+      <c r="C18" s="245"/>
       <c r="D18" s="10"/>
       <c r="E18" s="86"/>
       <c r="F18" s="87"/>
@@ -10749,9 +10803,9 @@
       <c r="AZ18" s="88"/>
     </row>
     <row r="19" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="248"/>
-      <c r="B19" s="249"/>
-      <c r="C19" s="249"/>
+      <c r="A19" s="244"/>
+      <c r="B19" s="245"/>
+      <c r="C19" s="245"/>
       <c r="D19" s="10"/>
       <c r="E19" s="86"/>
       <c r="F19" s="87"/>
@@ -10803,9 +10857,9 @@
       <c r="AZ19" s="88"/>
     </row>
     <row r="20" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="248"/>
-      <c r="B20" s="249"/>
-      <c r="C20" s="249"/>
+      <c r="A20" s="244"/>
+      <c r="B20" s="245"/>
+      <c r="C20" s="245"/>
       <c r="D20" s="10"/>
       <c r="E20" s="86"/>
       <c r="F20" s="87"/>
@@ -10857,9 +10911,9 @@
       <c r="AZ20" s="88"/>
     </row>
     <row r="21" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="248"/>
-      <c r="B21" s="249"/>
-      <c r="C21" s="249"/>
+      <c r="A21" s="244"/>
+      <c r="B21" s="245"/>
+      <c r="C21" s="245"/>
       <c r="D21" s="10"/>
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
@@ -10911,9 +10965,9 @@
       <c r="AZ21" s="88"/>
     </row>
     <row r="22" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="248"/>
-      <c r="B22" s="249"/>
-      <c r="C22" s="249"/>
+      <c r="A22" s="244"/>
+      <c r="B22" s="245"/>
+      <c r="C22" s="245"/>
       <c r="D22" s="10"/>
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
@@ -10965,9 +11019,9 @@
       <c r="AZ22" s="88"/>
     </row>
     <row r="23" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="248"/>
-      <c r="B23" s="249"/>
-      <c r="C23" s="249"/>
+      <c r="A23" s="244"/>
+      <c r="B23" s="245"/>
+      <c r="C23" s="245"/>
       <c r="D23" s="10"/>
       <c r="E23" s="86"/>
       <c r="F23" s="87"/>
@@ -11019,9 +11073,9 @@
       <c r="AZ23" s="88"/>
     </row>
     <row r="24" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="248"/>
-      <c r="B24" s="249"/>
-      <c r="C24" s="249"/>
+      <c r="A24" s="244"/>
+      <c r="B24" s="245"/>
+      <c r="C24" s="245"/>
       <c r="D24" s="10"/>
       <c r="E24" s="87"/>
       <c r="F24" s="87"/>
@@ -11073,9 +11127,9 @@
       <c r="AZ24" s="88"/>
     </row>
     <row r="25" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="248"/>
-      <c r="B25" s="249"/>
-      <c r="C25" s="249"/>
+      <c r="A25" s="244"/>
+      <c r="B25" s="245"/>
+      <c r="C25" s="245"/>
       <c r="D25" s="10"/>
       <c r="E25" s="86"/>
       <c r="F25" s="87"/>
@@ -11127,922 +11181,922 @@
       <c r="AZ25" s="88"/>
     </row>
     <row r="26" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="248"/>
-      <c r="B26" s="249"/>
-      <c r="C26" s="249"/>
+      <c r="A26" s="244"/>
+      <c r="B26" s="245"/>
+      <c r="C26" s="245"/>
       <c r="D26" s="10"/>
-      <c r="E26" s="243"/>
-      <c r="F26" s="243"/>
-      <c r="G26" s="243"/>
-      <c r="H26" s="243"/>
-      <c r="I26" s="243"/>
-      <c r="J26" s="243"/>
-      <c r="K26" s="243"/>
-      <c r="L26" s="243"/>
-      <c r="M26" s="243"/>
-      <c r="N26" s="243"/>
-      <c r="O26" s="243"/>
-      <c r="P26" s="243"/>
-      <c r="Q26" s="243"/>
-      <c r="R26" s="243"/>
-      <c r="S26" s="243"/>
-      <c r="T26" s="243"/>
-      <c r="U26" s="243"/>
-      <c r="V26" s="243"/>
-      <c r="W26" s="243"/>
-      <c r="X26" s="243"/>
-      <c r="Y26" s="243"/>
-      <c r="Z26" s="243"/>
-      <c r="AA26" s="243"/>
-      <c r="AB26" s="243"/>
-      <c r="AC26" s="243"/>
-      <c r="AD26" s="243"/>
-      <c r="AE26" s="243"/>
-      <c r="AF26" s="243"/>
-      <c r="AG26" s="243"/>
-      <c r="AH26" s="243"/>
-      <c r="AI26" s="243"/>
-      <c r="AJ26" s="243"/>
-      <c r="AK26" s="243"/>
-      <c r="AL26" s="243"/>
-      <c r="AM26" s="243"/>
-      <c r="AN26" s="243"/>
-      <c r="AO26" s="243"/>
-      <c r="AP26" s="243"/>
-      <c r="AQ26" s="243"/>
-      <c r="AR26" s="243"/>
-      <c r="AS26" s="243"/>
-      <c r="AT26" s="243"/>
-      <c r="AU26" s="243"/>
-      <c r="AV26" s="243"/>
-      <c r="AW26" s="243"/>
-      <c r="AX26" s="243"/>
-      <c r="AY26" s="243"/>
-      <c r="AZ26" s="244"/>
+      <c r="E26" s="253"/>
+      <c r="F26" s="253"/>
+      <c r="G26" s="253"/>
+      <c r="H26" s="253"/>
+      <c r="I26" s="253"/>
+      <c r="J26" s="253"/>
+      <c r="K26" s="253"/>
+      <c r="L26" s="253"/>
+      <c r="M26" s="253"/>
+      <c r="N26" s="253"/>
+      <c r="O26" s="253"/>
+      <c r="P26" s="253"/>
+      <c r="Q26" s="253"/>
+      <c r="R26" s="253"/>
+      <c r="S26" s="253"/>
+      <c r="T26" s="253"/>
+      <c r="U26" s="253"/>
+      <c r="V26" s="253"/>
+      <c r="W26" s="253"/>
+      <c r="X26" s="253"/>
+      <c r="Y26" s="253"/>
+      <c r="Z26" s="253"/>
+      <c r="AA26" s="253"/>
+      <c r="AB26" s="253"/>
+      <c r="AC26" s="253"/>
+      <c r="AD26" s="253"/>
+      <c r="AE26" s="253"/>
+      <c r="AF26" s="253"/>
+      <c r="AG26" s="253"/>
+      <c r="AH26" s="253"/>
+      <c r="AI26" s="253"/>
+      <c r="AJ26" s="253"/>
+      <c r="AK26" s="253"/>
+      <c r="AL26" s="253"/>
+      <c r="AM26" s="253"/>
+      <c r="AN26" s="253"/>
+      <c r="AO26" s="253"/>
+      <c r="AP26" s="253"/>
+      <c r="AQ26" s="253"/>
+      <c r="AR26" s="253"/>
+      <c r="AS26" s="253"/>
+      <c r="AT26" s="253"/>
+      <c r="AU26" s="253"/>
+      <c r="AV26" s="253"/>
+      <c r="AW26" s="253"/>
+      <c r="AX26" s="253"/>
+      <c r="AY26" s="253"/>
+      <c r="AZ26" s="254"/>
     </row>
     <row r="27" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="248"/>
-      <c r="B27" s="249"/>
-      <c r="C27" s="249"/>
+      <c r="A27" s="244"/>
+      <c r="B27" s="245"/>
+      <c r="C27" s="245"/>
       <c r="D27" s="10"/>
-      <c r="E27" s="243"/>
-      <c r="F27" s="243"/>
-      <c r="G27" s="243"/>
-      <c r="H27" s="243"/>
-      <c r="I27" s="243"/>
-      <c r="J27" s="243"/>
-      <c r="K27" s="243"/>
-      <c r="L27" s="243"/>
-      <c r="M27" s="243"/>
-      <c r="N27" s="243"/>
-      <c r="O27" s="243"/>
-      <c r="P27" s="243"/>
-      <c r="Q27" s="243"/>
-      <c r="R27" s="243"/>
-      <c r="S27" s="243"/>
-      <c r="T27" s="243"/>
-      <c r="U27" s="243"/>
-      <c r="V27" s="243"/>
-      <c r="W27" s="243"/>
-      <c r="X27" s="243"/>
-      <c r="Y27" s="243"/>
-      <c r="Z27" s="243"/>
-      <c r="AA27" s="243"/>
-      <c r="AB27" s="243"/>
-      <c r="AC27" s="243"/>
-      <c r="AD27" s="243"/>
-      <c r="AE27" s="243"/>
-      <c r="AF27" s="243"/>
-      <c r="AG27" s="243"/>
-      <c r="AH27" s="243"/>
-      <c r="AI27" s="243"/>
-      <c r="AJ27" s="243"/>
-      <c r="AK27" s="243"/>
-      <c r="AL27" s="243"/>
-      <c r="AM27" s="243"/>
-      <c r="AN27" s="243"/>
-      <c r="AO27" s="243"/>
-      <c r="AP27" s="243"/>
-      <c r="AQ27" s="243"/>
-      <c r="AR27" s="243"/>
-      <c r="AS27" s="243"/>
-      <c r="AT27" s="243"/>
-      <c r="AU27" s="243"/>
-      <c r="AV27" s="243"/>
-      <c r="AW27" s="243"/>
-      <c r="AX27" s="243"/>
-      <c r="AY27" s="243"/>
-      <c r="AZ27" s="244"/>
+      <c r="E27" s="253"/>
+      <c r="F27" s="253"/>
+      <c r="G27" s="253"/>
+      <c r="H27" s="253"/>
+      <c r="I27" s="253"/>
+      <c r="J27" s="253"/>
+      <c r="K27" s="253"/>
+      <c r="L27" s="253"/>
+      <c r="M27" s="253"/>
+      <c r="N27" s="253"/>
+      <c r="O27" s="253"/>
+      <c r="P27" s="253"/>
+      <c r="Q27" s="253"/>
+      <c r="R27" s="253"/>
+      <c r="S27" s="253"/>
+      <c r="T27" s="253"/>
+      <c r="U27" s="253"/>
+      <c r="V27" s="253"/>
+      <c r="W27" s="253"/>
+      <c r="X27" s="253"/>
+      <c r="Y27" s="253"/>
+      <c r="Z27" s="253"/>
+      <c r="AA27" s="253"/>
+      <c r="AB27" s="253"/>
+      <c r="AC27" s="253"/>
+      <c r="AD27" s="253"/>
+      <c r="AE27" s="253"/>
+      <c r="AF27" s="253"/>
+      <c r="AG27" s="253"/>
+      <c r="AH27" s="253"/>
+      <c r="AI27" s="253"/>
+      <c r="AJ27" s="253"/>
+      <c r="AK27" s="253"/>
+      <c r="AL27" s="253"/>
+      <c r="AM27" s="253"/>
+      <c r="AN27" s="253"/>
+      <c r="AO27" s="253"/>
+      <c r="AP27" s="253"/>
+      <c r="AQ27" s="253"/>
+      <c r="AR27" s="253"/>
+      <c r="AS27" s="253"/>
+      <c r="AT27" s="253"/>
+      <c r="AU27" s="253"/>
+      <c r="AV27" s="253"/>
+      <c r="AW27" s="253"/>
+      <c r="AX27" s="253"/>
+      <c r="AY27" s="253"/>
+      <c r="AZ27" s="254"/>
     </row>
     <row r="28" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="248"/>
-      <c r="B28" s="249"/>
-      <c r="C28" s="249"/>
+      <c r="A28" s="244"/>
+      <c r="B28" s="245"/>
+      <c r="C28" s="245"/>
       <c r="D28" s="10"/>
-      <c r="E28" s="243"/>
-      <c r="F28" s="243"/>
-      <c r="G28" s="243"/>
-      <c r="H28" s="243"/>
-      <c r="I28" s="243"/>
-      <c r="J28" s="243"/>
-      <c r="K28" s="243"/>
-      <c r="L28" s="243"/>
-      <c r="M28" s="243"/>
-      <c r="N28" s="243"/>
-      <c r="O28" s="243"/>
-      <c r="P28" s="243"/>
-      <c r="Q28" s="243"/>
-      <c r="R28" s="243"/>
-      <c r="S28" s="243"/>
-      <c r="T28" s="243"/>
-      <c r="U28" s="243"/>
-      <c r="V28" s="243"/>
-      <c r="W28" s="243"/>
-      <c r="X28" s="243"/>
-      <c r="Y28" s="243"/>
-      <c r="Z28" s="243"/>
-      <c r="AA28" s="243"/>
-      <c r="AB28" s="243"/>
-      <c r="AC28" s="243"/>
-      <c r="AD28" s="243"/>
-      <c r="AE28" s="243"/>
-      <c r="AF28" s="243"/>
-      <c r="AG28" s="243"/>
-      <c r="AH28" s="243"/>
-      <c r="AI28" s="243"/>
-      <c r="AJ28" s="243"/>
-      <c r="AK28" s="243"/>
-      <c r="AL28" s="243"/>
-      <c r="AM28" s="243"/>
-      <c r="AN28" s="243"/>
-      <c r="AO28" s="243"/>
-      <c r="AP28" s="243"/>
-      <c r="AQ28" s="243"/>
-      <c r="AR28" s="243"/>
-      <c r="AS28" s="243"/>
-      <c r="AT28" s="243"/>
-      <c r="AU28" s="243"/>
-      <c r="AV28" s="243"/>
-      <c r="AW28" s="243"/>
-      <c r="AX28" s="243"/>
-      <c r="AY28" s="243"/>
-      <c r="AZ28" s="244"/>
+      <c r="E28" s="253"/>
+      <c r="F28" s="253"/>
+      <c r="G28" s="253"/>
+      <c r="H28" s="253"/>
+      <c r="I28" s="253"/>
+      <c r="J28" s="253"/>
+      <c r="K28" s="253"/>
+      <c r="L28" s="253"/>
+      <c r="M28" s="253"/>
+      <c r="N28" s="253"/>
+      <c r="O28" s="253"/>
+      <c r="P28" s="253"/>
+      <c r="Q28" s="253"/>
+      <c r="R28" s="253"/>
+      <c r="S28" s="253"/>
+      <c r="T28" s="253"/>
+      <c r="U28" s="253"/>
+      <c r="V28" s="253"/>
+      <c r="W28" s="253"/>
+      <c r="X28" s="253"/>
+      <c r="Y28" s="253"/>
+      <c r="Z28" s="253"/>
+      <c r="AA28" s="253"/>
+      <c r="AB28" s="253"/>
+      <c r="AC28" s="253"/>
+      <c r="AD28" s="253"/>
+      <c r="AE28" s="253"/>
+      <c r="AF28" s="253"/>
+      <c r="AG28" s="253"/>
+      <c r="AH28" s="253"/>
+      <c r="AI28" s="253"/>
+      <c r="AJ28" s="253"/>
+      <c r="AK28" s="253"/>
+      <c r="AL28" s="253"/>
+      <c r="AM28" s="253"/>
+      <c r="AN28" s="253"/>
+      <c r="AO28" s="253"/>
+      <c r="AP28" s="253"/>
+      <c r="AQ28" s="253"/>
+      <c r="AR28" s="253"/>
+      <c r="AS28" s="253"/>
+      <c r="AT28" s="253"/>
+      <c r="AU28" s="253"/>
+      <c r="AV28" s="253"/>
+      <c r="AW28" s="253"/>
+      <c r="AX28" s="253"/>
+      <c r="AY28" s="253"/>
+      <c r="AZ28" s="254"/>
     </row>
     <row r="29" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="248"/>
-      <c r="B29" s="249"/>
-      <c r="C29" s="249"/>
+      <c r="A29" s="244"/>
+      <c r="B29" s="245"/>
+      <c r="C29" s="245"/>
       <c r="D29" s="10"/>
-      <c r="E29" s="243"/>
-      <c r="F29" s="243"/>
-      <c r="G29" s="243"/>
-      <c r="H29" s="243"/>
-      <c r="I29" s="243"/>
-      <c r="J29" s="243"/>
-      <c r="K29" s="243"/>
-      <c r="L29" s="243"/>
-      <c r="M29" s="243"/>
-      <c r="N29" s="243"/>
-      <c r="O29" s="243"/>
-      <c r="P29" s="243"/>
-      <c r="Q29" s="243"/>
-      <c r="R29" s="243"/>
-      <c r="S29" s="243"/>
-      <c r="T29" s="243"/>
-      <c r="U29" s="243"/>
-      <c r="V29" s="243"/>
-      <c r="W29" s="243"/>
-      <c r="X29" s="243"/>
-      <c r="Y29" s="243"/>
-      <c r="Z29" s="243"/>
-      <c r="AA29" s="243"/>
-      <c r="AB29" s="243"/>
-      <c r="AC29" s="243"/>
-      <c r="AD29" s="243"/>
-      <c r="AE29" s="243"/>
-      <c r="AF29" s="243"/>
-      <c r="AG29" s="243"/>
-      <c r="AH29" s="243"/>
-      <c r="AI29" s="243"/>
-      <c r="AJ29" s="243"/>
-      <c r="AK29" s="243"/>
-      <c r="AL29" s="243"/>
-      <c r="AM29" s="243"/>
-      <c r="AN29" s="243"/>
-      <c r="AO29" s="243"/>
-      <c r="AP29" s="243"/>
-      <c r="AQ29" s="243"/>
-      <c r="AR29" s="243"/>
-      <c r="AS29" s="243"/>
-      <c r="AT29" s="243"/>
-      <c r="AU29" s="243"/>
-      <c r="AV29" s="243"/>
-      <c r="AW29" s="243"/>
-      <c r="AX29" s="243"/>
-      <c r="AY29" s="243"/>
-      <c r="AZ29" s="244"/>
+      <c r="E29" s="253"/>
+      <c r="F29" s="253"/>
+      <c r="G29" s="253"/>
+      <c r="H29" s="253"/>
+      <c r="I29" s="253"/>
+      <c r="J29" s="253"/>
+      <c r="K29" s="253"/>
+      <c r="L29" s="253"/>
+      <c r="M29" s="253"/>
+      <c r="N29" s="253"/>
+      <c r="O29" s="253"/>
+      <c r="P29" s="253"/>
+      <c r="Q29" s="253"/>
+      <c r="R29" s="253"/>
+      <c r="S29" s="253"/>
+      <c r="T29" s="253"/>
+      <c r="U29" s="253"/>
+      <c r="V29" s="253"/>
+      <c r="W29" s="253"/>
+      <c r="X29" s="253"/>
+      <c r="Y29" s="253"/>
+      <c r="Z29" s="253"/>
+      <c r="AA29" s="253"/>
+      <c r="AB29" s="253"/>
+      <c r="AC29" s="253"/>
+      <c r="AD29" s="253"/>
+      <c r="AE29" s="253"/>
+      <c r="AF29" s="253"/>
+      <c r="AG29" s="253"/>
+      <c r="AH29" s="253"/>
+      <c r="AI29" s="253"/>
+      <c r="AJ29" s="253"/>
+      <c r="AK29" s="253"/>
+      <c r="AL29" s="253"/>
+      <c r="AM29" s="253"/>
+      <c r="AN29" s="253"/>
+      <c r="AO29" s="253"/>
+      <c r="AP29" s="253"/>
+      <c r="AQ29" s="253"/>
+      <c r="AR29" s="253"/>
+      <c r="AS29" s="253"/>
+      <c r="AT29" s="253"/>
+      <c r="AU29" s="253"/>
+      <c r="AV29" s="253"/>
+      <c r="AW29" s="253"/>
+      <c r="AX29" s="253"/>
+      <c r="AY29" s="253"/>
+      <c r="AZ29" s="254"/>
     </row>
     <row r="30" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="248"/>
-      <c r="B30" s="249"/>
-      <c r="C30" s="249"/>
+      <c r="A30" s="244"/>
+      <c r="B30" s="245"/>
+      <c r="C30" s="245"/>
       <c r="D30" s="10"/>
-      <c r="E30" s="243"/>
-      <c r="F30" s="243"/>
-      <c r="G30" s="243"/>
-      <c r="H30" s="243"/>
-      <c r="I30" s="243"/>
-      <c r="J30" s="243"/>
-      <c r="K30" s="243"/>
-      <c r="L30" s="243"/>
-      <c r="M30" s="243"/>
-      <c r="N30" s="243"/>
-      <c r="O30" s="243"/>
-      <c r="P30" s="243"/>
-      <c r="Q30" s="243"/>
-      <c r="R30" s="243"/>
-      <c r="S30" s="243"/>
-      <c r="T30" s="243"/>
-      <c r="U30" s="243"/>
-      <c r="V30" s="243"/>
-      <c r="W30" s="243"/>
-      <c r="X30" s="243"/>
-      <c r="Y30" s="243"/>
-      <c r="Z30" s="243"/>
-      <c r="AA30" s="243"/>
-      <c r="AB30" s="243"/>
-      <c r="AC30" s="243"/>
-      <c r="AD30" s="243"/>
-      <c r="AE30" s="243"/>
-      <c r="AF30" s="243"/>
-      <c r="AG30" s="243"/>
-      <c r="AH30" s="243"/>
-      <c r="AI30" s="243"/>
-      <c r="AJ30" s="243"/>
-      <c r="AK30" s="243"/>
-      <c r="AL30" s="243"/>
-      <c r="AM30" s="243"/>
-      <c r="AN30" s="243"/>
-      <c r="AO30" s="243"/>
-      <c r="AP30" s="243"/>
-      <c r="AQ30" s="243"/>
-      <c r="AR30" s="243"/>
-      <c r="AS30" s="243"/>
-      <c r="AT30" s="243"/>
-      <c r="AU30" s="243"/>
-      <c r="AV30" s="243"/>
-      <c r="AW30" s="243"/>
-      <c r="AX30" s="243"/>
-      <c r="AY30" s="243"/>
-      <c r="AZ30" s="244"/>
+      <c r="E30" s="253"/>
+      <c r="F30" s="253"/>
+      <c r="G30" s="253"/>
+      <c r="H30" s="253"/>
+      <c r="I30" s="253"/>
+      <c r="J30" s="253"/>
+      <c r="K30" s="253"/>
+      <c r="L30" s="253"/>
+      <c r="M30" s="253"/>
+      <c r="N30" s="253"/>
+      <c r="O30" s="253"/>
+      <c r="P30" s="253"/>
+      <c r="Q30" s="253"/>
+      <c r="R30" s="253"/>
+      <c r="S30" s="253"/>
+      <c r="T30" s="253"/>
+      <c r="U30" s="253"/>
+      <c r="V30" s="253"/>
+      <c r="W30" s="253"/>
+      <c r="X30" s="253"/>
+      <c r="Y30" s="253"/>
+      <c r="Z30" s="253"/>
+      <c r="AA30" s="253"/>
+      <c r="AB30" s="253"/>
+      <c r="AC30" s="253"/>
+      <c r="AD30" s="253"/>
+      <c r="AE30" s="253"/>
+      <c r="AF30" s="253"/>
+      <c r="AG30" s="253"/>
+      <c r="AH30" s="253"/>
+      <c r="AI30" s="253"/>
+      <c r="AJ30" s="253"/>
+      <c r="AK30" s="253"/>
+      <c r="AL30" s="253"/>
+      <c r="AM30" s="253"/>
+      <c r="AN30" s="253"/>
+      <c r="AO30" s="253"/>
+      <c r="AP30" s="253"/>
+      <c r="AQ30" s="253"/>
+      <c r="AR30" s="253"/>
+      <c r="AS30" s="253"/>
+      <c r="AT30" s="253"/>
+      <c r="AU30" s="253"/>
+      <c r="AV30" s="253"/>
+      <c r="AW30" s="253"/>
+      <c r="AX30" s="253"/>
+      <c r="AY30" s="253"/>
+      <c r="AZ30" s="254"/>
     </row>
     <row r="31" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="248"/>
-      <c r="B31" s="249"/>
-      <c r="C31" s="249"/>
+      <c r="A31" s="244"/>
+      <c r="B31" s="245"/>
+      <c r="C31" s="245"/>
       <c r="D31" s="10"/>
-      <c r="E31" s="243"/>
-      <c r="F31" s="243"/>
-      <c r="G31" s="243"/>
-      <c r="H31" s="243"/>
-      <c r="I31" s="243"/>
-      <c r="J31" s="243"/>
-      <c r="K31" s="243"/>
-      <c r="L31" s="243"/>
-      <c r="M31" s="243"/>
-      <c r="N31" s="243"/>
-      <c r="O31" s="243"/>
-      <c r="P31" s="243"/>
-      <c r="Q31" s="243"/>
-      <c r="R31" s="243"/>
-      <c r="S31" s="243"/>
-      <c r="T31" s="243"/>
-      <c r="U31" s="243"/>
-      <c r="V31" s="243"/>
-      <c r="W31" s="243"/>
-      <c r="X31" s="243"/>
-      <c r="Y31" s="243"/>
-      <c r="Z31" s="243"/>
-      <c r="AA31" s="243"/>
-      <c r="AB31" s="243"/>
-      <c r="AC31" s="243"/>
-      <c r="AD31" s="243"/>
-      <c r="AE31" s="243"/>
-      <c r="AF31" s="243"/>
-      <c r="AG31" s="243"/>
-      <c r="AH31" s="243"/>
-      <c r="AI31" s="243"/>
-      <c r="AJ31" s="243"/>
-      <c r="AK31" s="243"/>
-      <c r="AL31" s="243"/>
-      <c r="AM31" s="243"/>
-      <c r="AN31" s="243"/>
-      <c r="AO31" s="243"/>
-      <c r="AP31" s="243"/>
-      <c r="AQ31" s="243"/>
-      <c r="AR31" s="243"/>
-      <c r="AS31" s="243"/>
-      <c r="AT31" s="243"/>
-      <c r="AU31" s="243"/>
-      <c r="AV31" s="243"/>
-      <c r="AW31" s="243"/>
-      <c r="AX31" s="243"/>
-      <c r="AY31" s="243"/>
-      <c r="AZ31" s="244"/>
+      <c r="E31" s="253"/>
+      <c r="F31" s="253"/>
+      <c r="G31" s="253"/>
+      <c r="H31" s="253"/>
+      <c r="I31" s="253"/>
+      <c r="J31" s="253"/>
+      <c r="K31" s="253"/>
+      <c r="L31" s="253"/>
+      <c r="M31" s="253"/>
+      <c r="N31" s="253"/>
+      <c r="O31" s="253"/>
+      <c r="P31" s="253"/>
+      <c r="Q31" s="253"/>
+      <c r="R31" s="253"/>
+      <c r="S31" s="253"/>
+      <c r="T31" s="253"/>
+      <c r="U31" s="253"/>
+      <c r="V31" s="253"/>
+      <c r="W31" s="253"/>
+      <c r="X31" s="253"/>
+      <c r="Y31" s="253"/>
+      <c r="Z31" s="253"/>
+      <c r="AA31" s="253"/>
+      <c r="AB31" s="253"/>
+      <c r="AC31" s="253"/>
+      <c r="AD31" s="253"/>
+      <c r="AE31" s="253"/>
+      <c r="AF31" s="253"/>
+      <c r="AG31" s="253"/>
+      <c r="AH31" s="253"/>
+      <c r="AI31" s="253"/>
+      <c r="AJ31" s="253"/>
+      <c r="AK31" s="253"/>
+      <c r="AL31" s="253"/>
+      <c r="AM31" s="253"/>
+      <c r="AN31" s="253"/>
+      <c r="AO31" s="253"/>
+      <c r="AP31" s="253"/>
+      <c r="AQ31" s="253"/>
+      <c r="AR31" s="253"/>
+      <c r="AS31" s="253"/>
+      <c r="AT31" s="253"/>
+      <c r="AU31" s="253"/>
+      <c r="AV31" s="253"/>
+      <c r="AW31" s="253"/>
+      <c r="AX31" s="253"/>
+      <c r="AY31" s="253"/>
+      <c r="AZ31" s="254"/>
     </row>
     <row r="32" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="248"/>
-      <c r="B32" s="249"/>
-      <c r="C32" s="249"/>
+      <c r="A32" s="244"/>
+      <c r="B32" s="245"/>
+      <c r="C32" s="245"/>
       <c r="D32" s="10"/>
-      <c r="E32" s="243"/>
-      <c r="F32" s="243"/>
-      <c r="G32" s="243"/>
-      <c r="H32" s="243"/>
-      <c r="I32" s="243"/>
-      <c r="J32" s="243"/>
-      <c r="K32" s="243"/>
-      <c r="L32" s="243"/>
-      <c r="M32" s="243"/>
-      <c r="N32" s="243"/>
-      <c r="O32" s="243"/>
-      <c r="P32" s="243"/>
-      <c r="Q32" s="243"/>
-      <c r="R32" s="243"/>
-      <c r="S32" s="243"/>
-      <c r="T32" s="243"/>
-      <c r="U32" s="243"/>
-      <c r="V32" s="243"/>
-      <c r="W32" s="243"/>
-      <c r="X32" s="243"/>
-      <c r="Y32" s="243"/>
-      <c r="Z32" s="243"/>
-      <c r="AA32" s="243"/>
-      <c r="AB32" s="243"/>
-      <c r="AC32" s="243"/>
-      <c r="AD32" s="243"/>
-      <c r="AE32" s="243"/>
-      <c r="AF32" s="243"/>
-      <c r="AG32" s="243"/>
-      <c r="AH32" s="243"/>
-      <c r="AI32" s="243"/>
-      <c r="AJ32" s="243"/>
-      <c r="AK32" s="243"/>
-      <c r="AL32" s="243"/>
-      <c r="AM32" s="243"/>
-      <c r="AN32" s="243"/>
-      <c r="AO32" s="243"/>
-      <c r="AP32" s="243"/>
-      <c r="AQ32" s="243"/>
-      <c r="AR32" s="243"/>
-      <c r="AS32" s="243"/>
-      <c r="AT32" s="243"/>
-      <c r="AU32" s="243"/>
-      <c r="AV32" s="243"/>
-      <c r="AW32" s="243"/>
-      <c r="AX32" s="243"/>
-      <c r="AY32" s="243"/>
-      <c r="AZ32" s="244"/>
+      <c r="E32" s="253"/>
+      <c r="F32" s="253"/>
+      <c r="G32" s="253"/>
+      <c r="H32" s="253"/>
+      <c r="I32" s="253"/>
+      <c r="J32" s="253"/>
+      <c r="K32" s="253"/>
+      <c r="L32" s="253"/>
+      <c r="M32" s="253"/>
+      <c r="N32" s="253"/>
+      <c r="O32" s="253"/>
+      <c r="P32" s="253"/>
+      <c r="Q32" s="253"/>
+      <c r="R32" s="253"/>
+      <c r="S32" s="253"/>
+      <c r="T32" s="253"/>
+      <c r="U32" s="253"/>
+      <c r="V32" s="253"/>
+      <c r="W32" s="253"/>
+      <c r="X32" s="253"/>
+      <c r="Y32" s="253"/>
+      <c r="Z32" s="253"/>
+      <c r="AA32" s="253"/>
+      <c r="AB32" s="253"/>
+      <c r="AC32" s="253"/>
+      <c r="AD32" s="253"/>
+      <c r="AE32" s="253"/>
+      <c r="AF32" s="253"/>
+      <c r="AG32" s="253"/>
+      <c r="AH32" s="253"/>
+      <c r="AI32" s="253"/>
+      <c r="AJ32" s="253"/>
+      <c r="AK32" s="253"/>
+      <c r="AL32" s="253"/>
+      <c r="AM32" s="253"/>
+      <c r="AN32" s="253"/>
+      <c r="AO32" s="253"/>
+      <c r="AP32" s="253"/>
+      <c r="AQ32" s="253"/>
+      <c r="AR32" s="253"/>
+      <c r="AS32" s="253"/>
+      <c r="AT32" s="253"/>
+      <c r="AU32" s="253"/>
+      <c r="AV32" s="253"/>
+      <c r="AW32" s="253"/>
+      <c r="AX32" s="253"/>
+      <c r="AY32" s="253"/>
+      <c r="AZ32" s="254"/>
     </row>
     <row r="33" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="248"/>
-      <c r="B33" s="249"/>
-      <c r="C33" s="249"/>
+      <c r="A33" s="244"/>
+      <c r="B33" s="245"/>
+      <c r="C33" s="245"/>
       <c r="D33" s="10"/>
-      <c r="E33" s="243"/>
-      <c r="F33" s="243"/>
-      <c r="G33" s="243"/>
-      <c r="H33" s="243"/>
-      <c r="I33" s="243"/>
-      <c r="J33" s="243"/>
-      <c r="K33" s="243"/>
-      <c r="L33" s="243"/>
-      <c r="M33" s="243"/>
-      <c r="N33" s="243"/>
-      <c r="O33" s="243"/>
-      <c r="P33" s="243"/>
-      <c r="Q33" s="243"/>
-      <c r="R33" s="243"/>
-      <c r="S33" s="243"/>
-      <c r="T33" s="243"/>
-      <c r="U33" s="243"/>
-      <c r="V33" s="243"/>
-      <c r="W33" s="243"/>
-      <c r="X33" s="243"/>
-      <c r="Y33" s="243"/>
-      <c r="Z33" s="243"/>
-      <c r="AA33" s="243"/>
-      <c r="AB33" s="243"/>
-      <c r="AC33" s="243"/>
-      <c r="AD33" s="243"/>
-      <c r="AE33" s="243"/>
-      <c r="AF33" s="243"/>
-      <c r="AG33" s="243"/>
-      <c r="AH33" s="243"/>
-      <c r="AI33" s="243"/>
-      <c r="AJ33" s="243"/>
-      <c r="AK33" s="243"/>
-      <c r="AL33" s="243"/>
-      <c r="AM33" s="243"/>
-      <c r="AN33" s="243"/>
-      <c r="AO33" s="243"/>
-      <c r="AP33" s="243"/>
-      <c r="AQ33" s="243"/>
-      <c r="AR33" s="243"/>
-      <c r="AS33" s="243"/>
-      <c r="AT33" s="243"/>
-      <c r="AU33" s="243"/>
-      <c r="AV33" s="243"/>
-      <c r="AW33" s="243"/>
-      <c r="AX33" s="243"/>
-      <c r="AY33" s="243"/>
-      <c r="AZ33" s="244"/>
+      <c r="E33" s="253"/>
+      <c r="F33" s="253"/>
+      <c r="G33" s="253"/>
+      <c r="H33" s="253"/>
+      <c r="I33" s="253"/>
+      <c r="J33" s="253"/>
+      <c r="K33" s="253"/>
+      <c r="L33" s="253"/>
+      <c r="M33" s="253"/>
+      <c r="N33" s="253"/>
+      <c r="O33" s="253"/>
+      <c r="P33" s="253"/>
+      <c r="Q33" s="253"/>
+      <c r="R33" s="253"/>
+      <c r="S33" s="253"/>
+      <c r="T33" s="253"/>
+      <c r="U33" s="253"/>
+      <c r="V33" s="253"/>
+      <c r="W33" s="253"/>
+      <c r="X33" s="253"/>
+      <c r="Y33" s="253"/>
+      <c r="Z33" s="253"/>
+      <c r="AA33" s="253"/>
+      <c r="AB33" s="253"/>
+      <c r="AC33" s="253"/>
+      <c r="AD33" s="253"/>
+      <c r="AE33" s="253"/>
+      <c r="AF33" s="253"/>
+      <c r="AG33" s="253"/>
+      <c r="AH33" s="253"/>
+      <c r="AI33" s="253"/>
+      <c r="AJ33" s="253"/>
+      <c r="AK33" s="253"/>
+      <c r="AL33" s="253"/>
+      <c r="AM33" s="253"/>
+      <c r="AN33" s="253"/>
+      <c r="AO33" s="253"/>
+      <c r="AP33" s="253"/>
+      <c r="AQ33" s="253"/>
+      <c r="AR33" s="253"/>
+      <c r="AS33" s="253"/>
+      <c r="AT33" s="253"/>
+      <c r="AU33" s="253"/>
+      <c r="AV33" s="253"/>
+      <c r="AW33" s="253"/>
+      <c r="AX33" s="253"/>
+      <c r="AY33" s="253"/>
+      <c r="AZ33" s="254"/>
     </row>
     <row r="34" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="248"/>
-      <c r="B34" s="249"/>
-      <c r="C34" s="249"/>
+      <c r="A34" s="244"/>
+      <c r="B34" s="245"/>
+      <c r="C34" s="245"/>
       <c r="D34" s="10"/>
-      <c r="E34" s="243"/>
-      <c r="F34" s="243"/>
-      <c r="G34" s="243"/>
-      <c r="H34" s="243"/>
-      <c r="I34" s="243"/>
-      <c r="J34" s="243"/>
-      <c r="K34" s="243"/>
-      <c r="L34" s="243"/>
-      <c r="M34" s="243"/>
-      <c r="N34" s="243"/>
-      <c r="O34" s="243"/>
-      <c r="P34" s="243"/>
-      <c r="Q34" s="243"/>
-      <c r="R34" s="243"/>
-      <c r="S34" s="243"/>
-      <c r="T34" s="243"/>
-      <c r="U34" s="243"/>
-      <c r="V34" s="243"/>
-      <c r="W34" s="243"/>
-      <c r="X34" s="243"/>
-      <c r="Y34" s="243"/>
-      <c r="Z34" s="243"/>
-      <c r="AA34" s="243"/>
-      <c r="AB34" s="243"/>
-      <c r="AC34" s="243"/>
-      <c r="AD34" s="243"/>
-      <c r="AE34" s="243"/>
-      <c r="AF34" s="243"/>
-      <c r="AG34" s="243"/>
-      <c r="AH34" s="243"/>
-      <c r="AI34" s="243"/>
-      <c r="AJ34" s="243"/>
-      <c r="AK34" s="243"/>
-      <c r="AL34" s="243"/>
-      <c r="AM34" s="243"/>
-      <c r="AN34" s="243"/>
-      <c r="AO34" s="243"/>
-      <c r="AP34" s="243"/>
-      <c r="AQ34" s="243"/>
-      <c r="AR34" s="243"/>
-      <c r="AS34" s="243"/>
-      <c r="AT34" s="243"/>
-      <c r="AU34" s="243"/>
-      <c r="AV34" s="243"/>
-      <c r="AW34" s="243"/>
-      <c r="AX34" s="243"/>
-      <c r="AY34" s="243"/>
-      <c r="AZ34" s="244"/>
+      <c r="E34" s="253"/>
+      <c r="F34" s="253"/>
+      <c r="G34" s="253"/>
+      <c r="H34" s="253"/>
+      <c r="I34" s="253"/>
+      <c r="J34" s="253"/>
+      <c r="K34" s="253"/>
+      <c r="L34" s="253"/>
+      <c r="M34" s="253"/>
+      <c r="N34" s="253"/>
+      <c r="O34" s="253"/>
+      <c r="P34" s="253"/>
+      <c r="Q34" s="253"/>
+      <c r="R34" s="253"/>
+      <c r="S34" s="253"/>
+      <c r="T34" s="253"/>
+      <c r="U34" s="253"/>
+      <c r="V34" s="253"/>
+      <c r="W34" s="253"/>
+      <c r="X34" s="253"/>
+      <c r="Y34" s="253"/>
+      <c r="Z34" s="253"/>
+      <c r="AA34" s="253"/>
+      <c r="AB34" s="253"/>
+      <c r="AC34" s="253"/>
+      <c r="AD34" s="253"/>
+      <c r="AE34" s="253"/>
+      <c r="AF34" s="253"/>
+      <c r="AG34" s="253"/>
+      <c r="AH34" s="253"/>
+      <c r="AI34" s="253"/>
+      <c r="AJ34" s="253"/>
+      <c r="AK34" s="253"/>
+      <c r="AL34" s="253"/>
+      <c r="AM34" s="253"/>
+      <c r="AN34" s="253"/>
+      <c r="AO34" s="253"/>
+      <c r="AP34" s="253"/>
+      <c r="AQ34" s="253"/>
+      <c r="AR34" s="253"/>
+      <c r="AS34" s="253"/>
+      <c r="AT34" s="253"/>
+      <c r="AU34" s="253"/>
+      <c r="AV34" s="253"/>
+      <c r="AW34" s="253"/>
+      <c r="AX34" s="253"/>
+      <c r="AY34" s="253"/>
+      <c r="AZ34" s="254"/>
     </row>
     <row r="35" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="248"/>
-      <c r="B35" s="249"/>
-      <c r="C35" s="249"/>
+      <c r="A35" s="244"/>
+      <c r="B35" s="245"/>
+      <c r="C35" s="245"/>
       <c r="D35" s="10"/>
-      <c r="E35" s="243"/>
-      <c r="F35" s="243"/>
-      <c r="G35" s="243"/>
-      <c r="H35" s="243"/>
-      <c r="I35" s="243"/>
-      <c r="J35" s="243"/>
-      <c r="K35" s="243"/>
-      <c r="L35" s="243"/>
-      <c r="M35" s="243"/>
-      <c r="N35" s="243"/>
-      <c r="O35" s="243"/>
-      <c r="P35" s="243"/>
-      <c r="Q35" s="243"/>
-      <c r="R35" s="243"/>
-      <c r="S35" s="243"/>
-      <c r="T35" s="243"/>
-      <c r="U35" s="243"/>
-      <c r="V35" s="243"/>
-      <c r="W35" s="243"/>
-      <c r="X35" s="243"/>
-      <c r="Y35" s="243"/>
-      <c r="Z35" s="243"/>
-      <c r="AA35" s="243"/>
-      <c r="AB35" s="243"/>
-      <c r="AC35" s="243"/>
-      <c r="AD35" s="243"/>
-      <c r="AE35" s="243"/>
-      <c r="AF35" s="243"/>
-      <c r="AG35" s="243"/>
-      <c r="AH35" s="243"/>
-      <c r="AI35" s="243"/>
-      <c r="AJ35" s="243"/>
-      <c r="AK35" s="243"/>
-      <c r="AL35" s="243"/>
-      <c r="AM35" s="243"/>
-      <c r="AN35" s="243"/>
-      <c r="AO35" s="243"/>
-      <c r="AP35" s="243"/>
-      <c r="AQ35" s="243"/>
-      <c r="AR35" s="243"/>
-      <c r="AS35" s="243"/>
-      <c r="AT35" s="243"/>
-      <c r="AU35" s="243"/>
-      <c r="AV35" s="243"/>
-      <c r="AW35" s="243"/>
-      <c r="AX35" s="243"/>
-      <c r="AY35" s="243"/>
-      <c r="AZ35" s="244"/>
+      <c r="E35" s="253"/>
+      <c r="F35" s="253"/>
+      <c r="G35" s="253"/>
+      <c r="H35" s="253"/>
+      <c r="I35" s="253"/>
+      <c r="J35" s="253"/>
+      <c r="K35" s="253"/>
+      <c r="L35" s="253"/>
+      <c r="M35" s="253"/>
+      <c r="N35" s="253"/>
+      <c r="O35" s="253"/>
+      <c r="P35" s="253"/>
+      <c r="Q35" s="253"/>
+      <c r="R35" s="253"/>
+      <c r="S35" s="253"/>
+      <c r="T35" s="253"/>
+      <c r="U35" s="253"/>
+      <c r="V35" s="253"/>
+      <c r="W35" s="253"/>
+      <c r="X35" s="253"/>
+      <c r="Y35" s="253"/>
+      <c r="Z35" s="253"/>
+      <c r="AA35" s="253"/>
+      <c r="AB35" s="253"/>
+      <c r="AC35" s="253"/>
+      <c r="AD35" s="253"/>
+      <c r="AE35" s="253"/>
+      <c r="AF35" s="253"/>
+      <c r="AG35" s="253"/>
+      <c r="AH35" s="253"/>
+      <c r="AI35" s="253"/>
+      <c r="AJ35" s="253"/>
+      <c r="AK35" s="253"/>
+      <c r="AL35" s="253"/>
+      <c r="AM35" s="253"/>
+      <c r="AN35" s="253"/>
+      <c r="AO35" s="253"/>
+      <c r="AP35" s="253"/>
+      <c r="AQ35" s="253"/>
+      <c r="AR35" s="253"/>
+      <c r="AS35" s="253"/>
+      <c r="AT35" s="253"/>
+      <c r="AU35" s="253"/>
+      <c r="AV35" s="253"/>
+      <c r="AW35" s="253"/>
+      <c r="AX35" s="253"/>
+      <c r="AY35" s="253"/>
+      <c r="AZ35" s="254"/>
     </row>
     <row r="36" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="248"/>
-      <c r="B36" s="249"/>
-      <c r="C36" s="249"/>
+      <c r="A36" s="244"/>
+      <c r="B36" s="245"/>
+      <c r="C36" s="245"/>
       <c r="D36" s="10"/>
-      <c r="E36" s="243"/>
-      <c r="F36" s="243"/>
-      <c r="G36" s="243"/>
-      <c r="H36" s="243"/>
-      <c r="I36" s="243"/>
-      <c r="J36" s="243"/>
-      <c r="K36" s="243"/>
-      <c r="L36" s="243"/>
-      <c r="M36" s="243"/>
-      <c r="N36" s="243"/>
-      <c r="O36" s="243"/>
-      <c r="P36" s="243"/>
-      <c r="Q36" s="243"/>
-      <c r="R36" s="243"/>
-      <c r="S36" s="243"/>
-      <c r="T36" s="243"/>
-      <c r="U36" s="243"/>
-      <c r="V36" s="243"/>
-      <c r="W36" s="243"/>
-      <c r="X36" s="243"/>
-      <c r="Y36" s="243"/>
-      <c r="Z36" s="243"/>
-      <c r="AA36" s="243"/>
-      <c r="AB36" s="243"/>
-      <c r="AC36" s="243"/>
-      <c r="AD36" s="243"/>
-      <c r="AE36" s="243"/>
-      <c r="AF36" s="243"/>
-      <c r="AG36" s="243"/>
-      <c r="AH36" s="243"/>
-      <c r="AI36" s="243"/>
-      <c r="AJ36" s="243"/>
-      <c r="AK36" s="243"/>
-      <c r="AL36" s="243"/>
-      <c r="AM36" s="243"/>
-      <c r="AN36" s="243"/>
-      <c r="AO36" s="243"/>
-      <c r="AP36" s="243"/>
-      <c r="AQ36" s="243"/>
-      <c r="AR36" s="243"/>
-      <c r="AS36" s="243"/>
-      <c r="AT36" s="243"/>
-      <c r="AU36" s="243"/>
-      <c r="AV36" s="243"/>
-      <c r="AW36" s="243"/>
-      <c r="AX36" s="243"/>
-      <c r="AY36" s="243"/>
-      <c r="AZ36" s="244"/>
+      <c r="E36" s="253"/>
+      <c r="F36" s="253"/>
+      <c r="G36" s="253"/>
+      <c r="H36" s="253"/>
+      <c r="I36" s="253"/>
+      <c r="J36" s="253"/>
+      <c r="K36" s="253"/>
+      <c r="L36" s="253"/>
+      <c r="M36" s="253"/>
+      <c r="N36" s="253"/>
+      <c r="O36" s="253"/>
+      <c r="P36" s="253"/>
+      <c r="Q36" s="253"/>
+      <c r="R36" s="253"/>
+      <c r="S36" s="253"/>
+      <c r="T36" s="253"/>
+      <c r="U36" s="253"/>
+      <c r="V36" s="253"/>
+      <c r="W36" s="253"/>
+      <c r="X36" s="253"/>
+      <c r="Y36" s="253"/>
+      <c r="Z36" s="253"/>
+      <c r="AA36" s="253"/>
+      <c r="AB36" s="253"/>
+      <c r="AC36" s="253"/>
+      <c r="AD36" s="253"/>
+      <c r="AE36" s="253"/>
+      <c r="AF36" s="253"/>
+      <c r="AG36" s="253"/>
+      <c r="AH36" s="253"/>
+      <c r="AI36" s="253"/>
+      <c r="AJ36" s="253"/>
+      <c r="AK36" s="253"/>
+      <c r="AL36" s="253"/>
+      <c r="AM36" s="253"/>
+      <c r="AN36" s="253"/>
+      <c r="AO36" s="253"/>
+      <c r="AP36" s="253"/>
+      <c r="AQ36" s="253"/>
+      <c r="AR36" s="253"/>
+      <c r="AS36" s="253"/>
+      <c r="AT36" s="253"/>
+      <c r="AU36" s="253"/>
+      <c r="AV36" s="253"/>
+      <c r="AW36" s="253"/>
+      <c r="AX36" s="253"/>
+      <c r="AY36" s="253"/>
+      <c r="AZ36" s="254"/>
     </row>
     <row r="37" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="248"/>
-      <c r="B37" s="249"/>
-      <c r="C37" s="249"/>
+      <c r="A37" s="244"/>
+      <c r="B37" s="245"/>
+      <c r="C37" s="245"/>
       <c r="D37" s="10"/>
-      <c r="E37" s="243"/>
-      <c r="F37" s="243"/>
-      <c r="G37" s="243"/>
-      <c r="H37" s="243"/>
-      <c r="I37" s="243"/>
-      <c r="J37" s="243"/>
-      <c r="K37" s="243"/>
-      <c r="L37" s="243"/>
-      <c r="M37" s="243"/>
-      <c r="N37" s="243"/>
-      <c r="O37" s="243"/>
-      <c r="P37" s="243"/>
-      <c r="Q37" s="243"/>
-      <c r="R37" s="243"/>
-      <c r="S37" s="243"/>
-      <c r="T37" s="243"/>
-      <c r="U37" s="243"/>
-      <c r="V37" s="243"/>
-      <c r="W37" s="243"/>
-      <c r="X37" s="243"/>
-      <c r="Y37" s="243"/>
-      <c r="Z37" s="243"/>
-      <c r="AA37" s="243"/>
-      <c r="AB37" s="243"/>
-      <c r="AC37" s="243"/>
-      <c r="AD37" s="243"/>
-      <c r="AE37" s="243"/>
-      <c r="AF37" s="243"/>
-      <c r="AG37" s="243"/>
-      <c r="AH37" s="243"/>
-      <c r="AI37" s="243"/>
-      <c r="AJ37" s="243"/>
-      <c r="AK37" s="243"/>
-      <c r="AL37" s="243"/>
-      <c r="AM37" s="243"/>
-      <c r="AN37" s="243"/>
-      <c r="AO37" s="243"/>
-      <c r="AP37" s="243"/>
-      <c r="AQ37" s="243"/>
-      <c r="AR37" s="243"/>
-      <c r="AS37" s="243"/>
-      <c r="AT37" s="243"/>
-      <c r="AU37" s="243"/>
-      <c r="AV37" s="243"/>
-      <c r="AW37" s="243"/>
-      <c r="AX37" s="243"/>
-      <c r="AY37" s="243"/>
-      <c r="AZ37" s="244"/>
+      <c r="E37" s="253"/>
+      <c r="F37" s="253"/>
+      <c r="G37" s="253"/>
+      <c r="H37" s="253"/>
+      <c r="I37" s="253"/>
+      <c r="J37" s="253"/>
+      <c r="K37" s="253"/>
+      <c r="L37" s="253"/>
+      <c r="M37" s="253"/>
+      <c r="N37" s="253"/>
+      <c r="O37" s="253"/>
+      <c r="P37" s="253"/>
+      <c r="Q37" s="253"/>
+      <c r="R37" s="253"/>
+      <c r="S37" s="253"/>
+      <c r="T37" s="253"/>
+      <c r="U37" s="253"/>
+      <c r="V37" s="253"/>
+      <c r="W37" s="253"/>
+      <c r="X37" s="253"/>
+      <c r="Y37" s="253"/>
+      <c r="Z37" s="253"/>
+      <c r="AA37" s="253"/>
+      <c r="AB37" s="253"/>
+      <c r="AC37" s="253"/>
+      <c r="AD37" s="253"/>
+      <c r="AE37" s="253"/>
+      <c r="AF37" s="253"/>
+      <c r="AG37" s="253"/>
+      <c r="AH37" s="253"/>
+      <c r="AI37" s="253"/>
+      <c r="AJ37" s="253"/>
+      <c r="AK37" s="253"/>
+      <c r="AL37" s="253"/>
+      <c r="AM37" s="253"/>
+      <c r="AN37" s="253"/>
+      <c r="AO37" s="253"/>
+      <c r="AP37" s="253"/>
+      <c r="AQ37" s="253"/>
+      <c r="AR37" s="253"/>
+      <c r="AS37" s="253"/>
+      <c r="AT37" s="253"/>
+      <c r="AU37" s="253"/>
+      <c r="AV37" s="253"/>
+      <c r="AW37" s="253"/>
+      <c r="AX37" s="253"/>
+      <c r="AY37" s="253"/>
+      <c r="AZ37" s="254"/>
     </row>
     <row r="38" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="248"/>
-      <c r="B38" s="249"/>
-      <c r="C38" s="249"/>
+      <c r="A38" s="244"/>
+      <c r="B38" s="245"/>
+      <c r="C38" s="245"/>
       <c r="D38" s="10"/>
-      <c r="E38" s="243"/>
-      <c r="F38" s="243"/>
-      <c r="G38" s="243"/>
-      <c r="H38" s="243"/>
-      <c r="I38" s="243"/>
-      <c r="J38" s="243"/>
-      <c r="K38" s="243"/>
-      <c r="L38" s="243"/>
-      <c r="M38" s="243"/>
-      <c r="N38" s="243"/>
-      <c r="O38" s="243"/>
-      <c r="P38" s="243"/>
-      <c r="Q38" s="243"/>
-      <c r="R38" s="243"/>
-      <c r="S38" s="243"/>
-      <c r="T38" s="243"/>
-      <c r="U38" s="243"/>
-      <c r="V38" s="243"/>
-      <c r="W38" s="243"/>
-      <c r="X38" s="243"/>
-      <c r="Y38" s="243"/>
-      <c r="Z38" s="243"/>
-      <c r="AA38" s="243"/>
-      <c r="AB38" s="243"/>
-      <c r="AC38" s="243"/>
-      <c r="AD38" s="243"/>
-      <c r="AE38" s="243"/>
-      <c r="AF38" s="243"/>
-      <c r="AG38" s="243"/>
-      <c r="AH38" s="243"/>
-      <c r="AI38" s="243"/>
-      <c r="AJ38" s="243"/>
-      <c r="AK38" s="243"/>
-      <c r="AL38" s="243"/>
-      <c r="AM38" s="243"/>
-      <c r="AN38" s="243"/>
-      <c r="AO38" s="243"/>
-      <c r="AP38" s="243"/>
-      <c r="AQ38" s="243"/>
-      <c r="AR38" s="243"/>
-      <c r="AS38" s="243"/>
-      <c r="AT38" s="243"/>
-      <c r="AU38" s="243"/>
-      <c r="AV38" s="243"/>
-      <c r="AW38" s="243"/>
-      <c r="AX38" s="243"/>
-      <c r="AY38" s="243"/>
-      <c r="AZ38" s="244"/>
+      <c r="E38" s="253"/>
+      <c r="F38" s="253"/>
+      <c r="G38" s="253"/>
+      <c r="H38" s="253"/>
+      <c r="I38" s="253"/>
+      <c r="J38" s="253"/>
+      <c r="K38" s="253"/>
+      <c r="L38" s="253"/>
+      <c r="M38" s="253"/>
+      <c r="N38" s="253"/>
+      <c r="O38" s="253"/>
+      <c r="P38" s="253"/>
+      <c r="Q38" s="253"/>
+      <c r="R38" s="253"/>
+      <c r="S38" s="253"/>
+      <c r="T38" s="253"/>
+      <c r="U38" s="253"/>
+      <c r="V38" s="253"/>
+      <c r="W38" s="253"/>
+      <c r="X38" s="253"/>
+      <c r="Y38" s="253"/>
+      <c r="Z38" s="253"/>
+      <c r="AA38" s="253"/>
+      <c r="AB38" s="253"/>
+      <c r="AC38" s="253"/>
+      <c r="AD38" s="253"/>
+      <c r="AE38" s="253"/>
+      <c r="AF38" s="253"/>
+      <c r="AG38" s="253"/>
+      <c r="AH38" s="253"/>
+      <c r="AI38" s="253"/>
+      <c r="AJ38" s="253"/>
+      <c r="AK38" s="253"/>
+      <c r="AL38" s="253"/>
+      <c r="AM38" s="253"/>
+      <c r="AN38" s="253"/>
+      <c r="AO38" s="253"/>
+      <c r="AP38" s="253"/>
+      <c r="AQ38" s="253"/>
+      <c r="AR38" s="253"/>
+      <c r="AS38" s="253"/>
+      <c r="AT38" s="253"/>
+      <c r="AU38" s="253"/>
+      <c r="AV38" s="253"/>
+      <c r="AW38" s="253"/>
+      <c r="AX38" s="253"/>
+      <c r="AY38" s="253"/>
+      <c r="AZ38" s="254"/>
     </row>
     <row r="39" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="248"/>
-      <c r="B39" s="249"/>
-      <c r="C39" s="249"/>
+      <c r="A39" s="244"/>
+      <c r="B39" s="245"/>
+      <c r="C39" s="245"/>
       <c r="D39" s="10"/>
-      <c r="E39" s="243"/>
-      <c r="F39" s="243"/>
-      <c r="G39" s="243"/>
-      <c r="H39" s="243"/>
-      <c r="I39" s="243"/>
-      <c r="J39" s="243"/>
-      <c r="K39" s="243"/>
-      <c r="L39" s="243"/>
-      <c r="M39" s="243"/>
-      <c r="N39" s="243"/>
-      <c r="O39" s="243"/>
-      <c r="P39" s="243"/>
-      <c r="Q39" s="243"/>
-      <c r="R39" s="243"/>
-      <c r="S39" s="243"/>
-      <c r="T39" s="243"/>
-      <c r="U39" s="243"/>
-      <c r="V39" s="243"/>
-      <c r="W39" s="243"/>
-      <c r="X39" s="243"/>
-      <c r="Y39" s="243"/>
-      <c r="Z39" s="243"/>
-      <c r="AA39" s="243"/>
-      <c r="AB39" s="243"/>
-      <c r="AC39" s="243"/>
-      <c r="AD39" s="243"/>
-      <c r="AE39" s="243"/>
-      <c r="AF39" s="243"/>
-      <c r="AG39" s="243"/>
-      <c r="AH39" s="243"/>
-      <c r="AI39" s="243"/>
-      <c r="AJ39" s="243"/>
-      <c r="AK39" s="243"/>
-      <c r="AL39" s="243"/>
-      <c r="AM39" s="243"/>
-      <c r="AN39" s="243"/>
-      <c r="AO39" s="243"/>
-      <c r="AP39" s="243"/>
-      <c r="AQ39" s="243"/>
-      <c r="AR39" s="243"/>
-      <c r="AS39" s="243"/>
-      <c r="AT39" s="243"/>
-      <c r="AU39" s="243"/>
-      <c r="AV39" s="243"/>
-      <c r="AW39" s="243"/>
-      <c r="AX39" s="243"/>
-      <c r="AY39" s="243"/>
-      <c r="AZ39" s="244"/>
+      <c r="E39" s="253"/>
+      <c r="F39" s="253"/>
+      <c r="G39" s="253"/>
+      <c r="H39" s="253"/>
+      <c r="I39" s="253"/>
+      <c r="J39" s="253"/>
+      <c r="K39" s="253"/>
+      <c r="L39" s="253"/>
+      <c r="M39" s="253"/>
+      <c r="N39" s="253"/>
+      <c r="O39" s="253"/>
+      <c r="P39" s="253"/>
+      <c r="Q39" s="253"/>
+      <c r="R39" s="253"/>
+      <c r="S39" s="253"/>
+      <c r="T39" s="253"/>
+      <c r="U39" s="253"/>
+      <c r="V39" s="253"/>
+      <c r="W39" s="253"/>
+      <c r="X39" s="253"/>
+      <c r="Y39" s="253"/>
+      <c r="Z39" s="253"/>
+      <c r="AA39" s="253"/>
+      <c r="AB39" s="253"/>
+      <c r="AC39" s="253"/>
+      <c r="AD39" s="253"/>
+      <c r="AE39" s="253"/>
+      <c r="AF39" s="253"/>
+      <c r="AG39" s="253"/>
+      <c r="AH39" s="253"/>
+      <c r="AI39" s="253"/>
+      <c r="AJ39" s="253"/>
+      <c r="AK39" s="253"/>
+      <c r="AL39" s="253"/>
+      <c r="AM39" s="253"/>
+      <c r="AN39" s="253"/>
+      <c r="AO39" s="253"/>
+      <c r="AP39" s="253"/>
+      <c r="AQ39" s="253"/>
+      <c r="AR39" s="253"/>
+      <c r="AS39" s="253"/>
+      <c r="AT39" s="253"/>
+      <c r="AU39" s="253"/>
+      <c r="AV39" s="253"/>
+      <c r="AW39" s="253"/>
+      <c r="AX39" s="253"/>
+      <c r="AY39" s="253"/>
+      <c r="AZ39" s="254"/>
     </row>
     <row r="40" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="248"/>
-      <c r="B40" s="249"/>
-      <c r="C40" s="249"/>
+      <c r="A40" s="244"/>
+      <c r="B40" s="245"/>
+      <c r="C40" s="245"/>
       <c r="D40" s="10"/>
-      <c r="E40" s="243"/>
-      <c r="F40" s="243"/>
-      <c r="G40" s="243"/>
-      <c r="H40" s="243"/>
-      <c r="I40" s="243"/>
-      <c r="J40" s="243"/>
-      <c r="K40" s="243"/>
-      <c r="L40" s="243"/>
-      <c r="M40" s="243"/>
-      <c r="N40" s="243"/>
-      <c r="O40" s="243"/>
-      <c r="P40" s="243"/>
-      <c r="Q40" s="243"/>
-      <c r="R40" s="243"/>
-      <c r="S40" s="243"/>
-      <c r="T40" s="243"/>
-      <c r="U40" s="243"/>
-      <c r="V40" s="243"/>
-      <c r="W40" s="243"/>
-      <c r="X40" s="243"/>
-      <c r="Y40" s="243"/>
-      <c r="Z40" s="243"/>
-      <c r="AA40" s="243"/>
-      <c r="AB40" s="243"/>
-      <c r="AC40" s="243"/>
-      <c r="AD40" s="243"/>
-      <c r="AE40" s="243"/>
-      <c r="AF40" s="243"/>
-      <c r="AG40" s="243"/>
-      <c r="AH40" s="243"/>
-      <c r="AI40" s="243"/>
-      <c r="AJ40" s="243"/>
-      <c r="AK40" s="243"/>
-      <c r="AL40" s="243"/>
-      <c r="AM40" s="243"/>
-      <c r="AN40" s="243"/>
-      <c r="AO40" s="243"/>
-      <c r="AP40" s="243"/>
-      <c r="AQ40" s="243"/>
-      <c r="AR40" s="243"/>
-      <c r="AS40" s="243"/>
-      <c r="AT40" s="243"/>
-      <c r="AU40" s="243"/>
-      <c r="AV40" s="243"/>
-      <c r="AW40" s="243"/>
-      <c r="AX40" s="243"/>
-      <c r="AY40" s="243"/>
-      <c r="AZ40" s="244"/>
+      <c r="E40" s="253"/>
+      <c r="F40" s="253"/>
+      <c r="G40" s="253"/>
+      <c r="H40" s="253"/>
+      <c r="I40" s="253"/>
+      <c r="J40" s="253"/>
+      <c r="K40" s="253"/>
+      <c r="L40" s="253"/>
+      <c r="M40" s="253"/>
+      <c r="N40" s="253"/>
+      <c r="O40" s="253"/>
+      <c r="P40" s="253"/>
+      <c r="Q40" s="253"/>
+      <c r="R40" s="253"/>
+      <c r="S40" s="253"/>
+      <c r="T40" s="253"/>
+      <c r="U40" s="253"/>
+      <c r="V40" s="253"/>
+      <c r="W40" s="253"/>
+      <c r="X40" s="253"/>
+      <c r="Y40" s="253"/>
+      <c r="Z40" s="253"/>
+      <c r="AA40" s="253"/>
+      <c r="AB40" s="253"/>
+      <c r="AC40" s="253"/>
+      <c r="AD40" s="253"/>
+      <c r="AE40" s="253"/>
+      <c r="AF40" s="253"/>
+      <c r="AG40" s="253"/>
+      <c r="AH40" s="253"/>
+      <c r="AI40" s="253"/>
+      <c r="AJ40" s="253"/>
+      <c r="AK40" s="253"/>
+      <c r="AL40" s="253"/>
+      <c r="AM40" s="253"/>
+      <c r="AN40" s="253"/>
+      <c r="AO40" s="253"/>
+      <c r="AP40" s="253"/>
+      <c r="AQ40" s="253"/>
+      <c r="AR40" s="253"/>
+      <c r="AS40" s="253"/>
+      <c r="AT40" s="253"/>
+      <c r="AU40" s="253"/>
+      <c r="AV40" s="253"/>
+      <c r="AW40" s="253"/>
+      <c r="AX40" s="253"/>
+      <c r="AY40" s="253"/>
+      <c r="AZ40" s="254"/>
     </row>
     <row r="41" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="248"/>
-      <c r="B41" s="249"/>
-      <c r="C41" s="249"/>
+      <c r="A41" s="244"/>
+      <c r="B41" s="245"/>
+      <c r="C41" s="245"/>
       <c r="D41" s="10"/>
-      <c r="E41" s="243"/>
-      <c r="F41" s="243"/>
-      <c r="G41" s="243"/>
-      <c r="H41" s="243"/>
-      <c r="I41" s="243"/>
-      <c r="J41" s="243"/>
-      <c r="K41" s="243"/>
-      <c r="L41" s="243"/>
-      <c r="M41" s="243"/>
-      <c r="N41" s="243"/>
-      <c r="O41" s="243"/>
-      <c r="P41" s="243"/>
-      <c r="Q41" s="243"/>
-      <c r="R41" s="243"/>
-      <c r="S41" s="243"/>
-      <c r="T41" s="243"/>
-      <c r="U41" s="243"/>
-      <c r="V41" s="243"/>
-      <c r="W41" s="243"/>
-      <c r="X41" s="243"/>
-      <c r="Y41" s="243"/>
-      <c r="Z41" s="243"/>
-      <c r="AA41" s="243"/>
-      <c r="AB41" s="243"/>
-      <c r="AC41" s="243"/>
-      <c r="AD41" s="243"/>
-      <c r="AE41" s="243"/>
-      <c r="AF41" s="243"/>
-      <c r="AG41" s="243"/>
-      <c r="AH41" s="243"/>
-      <c r="AI41" s="243"/>
-      <c r="AJ41" s="243"/>
-      <c r="AK41" s="243"/>
-      <c r="AL41" s="243"/>
-      <c r="AM41" s="243"/>
-      <c r="AN41" s="243"/>
-      <c r="AO41" s="243"/>
-      <c r="AP41" s="243"/>
-      <c r="AQ41" s="243"/>
-      <c r="AR41" s="243"/>
-      <c r="AS41" s="243"/>
-      <c r="AT41" s="243"/>
-      <c r="AU41" s="243"/>
-      <c r="AV41" s="243"/>
-      <c r="AW41" s="243"/>
-      <c r="AX41" s="243"/>
-      <c r="AY41" s="243"/>
-      <c r="AZ41" s="244"/>
+      <c r="E41" s="253"/>
+      <c r="F41" s="253"/>
+      <c r="G41" s="253"/>
+      <c r="H41" s="253"/>
+      <c r="I41" s="253"/>
+      <c r="J41" s="253"/>
+      <c r="K41" s="253"/>
+      <c r="L41" s="253"/>
+      <c r="M41" s="253"/>
+      <c r="N41" s="253"/>
+      <c r="O41" s="253"/>
+      <c r="P41" s="253"/>
+      <c r="Q41" s="253"/>
+      <c r="R41" s="253"/>
+      <c r="S41" s="253"/>
+      <c r="T41" s="253"/>
+      <c r="U41" s="253"/>
+      <c r="V41" s="253"/>
+      <c r="W41" s="253"/>
+      <c r="X41" s="253"/>
+      <c r="Y41" s="253"/>
+      <c r="Z41" s="253"/>
+      <c r="AA41" s="253"/>
+      <c r="AB41" s="253"/>
+      <c r="AC41" s="253"/>
+      <c r="AD41" s="253"/>
+      <c r="AE41" s="253"/>
+      <c r="AF41" s="253"/>
+      <c r="AG41" s="253"/>
+      <c r="AH41" s="253"/>
+      <c r="AI41" s="253"/>
+      <c r="AJ41" s="253"/>
+      <c r="AK41" s="253"/>
+      <c r="AL41" s="253"/>
+      <c r="AM41" s="253"/>
+      <c r="AN41" s="253"/>
+      <c r="AO41" s="253"/>
+      <c r="AP41" s="253"/>
+      <c r="AQ41" s="253"/>
+      <c r="AR41" s="253"/>
+      <c r="AS41" s="253"/>
+      <c r="AT41" s="253"/>
+      <c r="AU41" s="253"/>
+      <c r="AV41" s="253"/>
+      <c r="AW41" s="253"/>
+      <c r="AX41" s="253"/>
+      <c r="AY41" s="253"/>
+      <c r="AZ41" s="254"/>
     </row>
     <row r="42" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="248"/>
-      <c r="B42" s="249"/>
-      <c r="C42" s="249"/>
+      <c r="A42" s="244"/>
+      <c r="B42" s="245"/>
+      <c r="C42" s="245"/>
       <c r="D42" s="10"/>
-      <c r="E42" s="243"/>
-      <c r="F42" s="243"/>
-      <c r="G42" s="243"/>
-      <c r="H42" s="243"/>
-      <c r="I42" s="243"/>
-      <c r="J42" s="243"/>
-      <c r="K42" s="243"/>
-      <c r="L42" s="243"/>
-      <c r="M42" s="243"/>
-      <c r="N42" s="243"/>
-      <c r="O42" s="243"/>
-      <c r="P42" s="243"/>
-      <c r="Q42" s="243"/>
-      <c r="R42" s="243"/>
-      <c r="S42" s="243"/>
-      <c r="T42" s="243"/>
-      <c r="U42" s="243"/>
-      <c r="V42" s="243"/>
-      <c r="W42" s="243"/>
-      <c r="X42" s="243"/>
-      <c r="Y42" s="243"/>
-      <c r="Z42" s="243"/>
-      <c r="AA42" s="243"/>
-      <c r="AB42" s="243"/>
-      <c r="AC42" s="243"/>
-      <c r="AD42" s="243"/>
-      <c r="AE42" s="243"/>
-      <c r="AF42" s="243"/>
-      <c r="AG42" s="243"/>
-      <c r="AH42" s="243"/>
-      <c r="AI42" s="243"/>
-      <c r="AJ42" s="243"/>
-      <c r="AK42" s="243"/>
-      <c r="AL42" s="243"/>
-      <c r="AM42" s="243"/>
-      <c r="AN42" s="243"/>
-      <c r="AO42" s="243"/>
-      <c r="AP42" s="243"/>
-      <c r="AQ42" s="243"/>
-      <c r="AR42" s="243"/>
-      <c r="AS42" s="243"/>
-      <c r="AT42" s="243"/>
-      <c r="AU42" s="243"/>
-      <c r="AV42" s="243"/>
-      <c r="AW42" s="243"/>
-      <c r="AX42" s="243"/>
-      <c r="AY42" s="243"/>
-      <c r="AZ42" s="244"/>
+      <c r="E42" s="253"/>
+      <c r="F42" s="253"/>
+      <c r="G42" s="253"/>
+      <c r="H42" s="253"/>
+      <c r="I42" s="253"/>
+      <c r="J42" s="253"/>
+      <c r="K42" s="253"/>
+      <c r="L42" s="253"/>
+      <c r="M42" s="253"/>
+      <c r="N42" s="253"/>
+      <c r="O42" s="253"/>
+      <c r="P42" s="253"/>
+      <c r="Q42" s="253"/>
+      <c r="R42" s="253"/>
+      <c r="S42" s="253"/>
+      <c r="T42" s="253"/>
+      <c r="U42" s="253"/>
+      <c r="V42" s="253"/>
+      <c r="W42" s="253"/>
+      <c r="X42" s="253"/>
+      <c r="Y42" s="253"/>
+      <c r="Z42" s="253"/>
+      <c r="AA42" s="253"/>
+      <c r="AB42" s="253"/>
+      <c r="AC42" s="253"/>
+      <c r="AD42" s="253"/>
+      <c r="AE42" s="253"/>
+      <c r="AF42" s="253"/>
+      <c r="AG42" s="253"/>
+      <c r="AH42" s="253"/>
+      <c r="AI42" s="253"/>
+      <c r="AJ42" s="253"/>
+      <c r="AK42" s="253"/>
+      <c r="AL42" s="253"/>
+      <c r="AM42" s="253"/>
+      <c r="AN42" s="253"/>
+      <c r="AO42" s="253"/>
+      <c r="AP42" s="253"/>
+      <c r="AQ42" s="253"/>
+      <c r="AR42" s="253"/>
+      <c r="AS42" s="253"/>
+      <c r="AT42" s="253"/>
+      <c r="AU42" s="253"/>
+      <c r="AV42" s="253"/>
+      <c r="AW42" s="253"/>
+      <c r="AX42" s="253"/>
+      <c r="AY42" s="253"/>
+      <c r="AZ42" s="254"/>
     </row>
     <row r="43" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="62"/>
@@ -12154,181 +12208,226 @@
       <c r="AZ44"/>
     </row>
     <row r="45" spans="1:53" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="147"/>
-      <c r="B45" s="147"/>
-      <c r="C45" s="147"/>
-      <c r="D45" s="147"/>
-      <c r="E45" s="147"/>
-      <c r="F45" s="147"/>
-      <c r="G45" s="147"/>
-      <c r="H45" s="147"/>
-      <c r="I45" s="147"/>
-      <c r="J45" s="147"/>
-      <c r="K45" s="147"/>
-      <c r="L45" s="147"/>
-      <c r="M45" s="147"/>
-      <c r="N45" s="147"/>
-      <c r="O45" s="147"/>
-      <c r="P45" s="147"/>
+      <c r="A45" s="117"/>
+      <c r="B45" s="117"/>
+      <c r="C45" s="117"/>
+      <c r="D45" s="117"/>
+      <c r="E45" s="117"/>
+      <c r="F45" s="117"/>
+      <c r="G45" s="117"/>
+      <c r="H45" s="117"/>
+      <c r="I45" s="117"/>
+      <c r="J45" s="117"/>
+      <c r="K45" s="117"/>
+      <c r="L45" s="117"/>
+      <c r="M45" s="117"/>
+      <c r="N45" s="117"/>
+      <c r="O45" s="117"/>
+      <c r="P45" s="117"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
-      <c r="S45" s="147"/>
-      <c r="T45" s="147"/>
-      <c r="U45" s="147"/>
-      <c r="V45" s="147"/>
-      <c r="W45" s="147"/>
-      <c r="X45" s="147"/>
-      <c r="Y45" s="147"/>
-      <c r="Z45" s="147"/>
-      <c r="AA45" s="147"/>
-      <c r="AB45" s="147"/>
-      <c r="AC45" s="147"/>
-      <c r="AD45" s="147"/>
-      <c r="AE45" s="147"/>
-      <c r="AF45" s="147"/>
-      <c r="AG45" s="147"/>
-      <c r="AH45" s="147"/>
+      <c r="S45" s="117"/>
+      <c r="T45" s="117"/>
+      <c r="U45" s="117"/>
+      <c r="V45" s="117"/>
+      <c r="W45" s="117"/>
+      <c r="X45" s="117"/>
+      <c r="Y45" s="117"/>
+      <c r="Z45" s="117"/>
+      <c r="AA45" s="117"/>
+      <c r="AB45" s="117"/>
+      <c r="AC45" s="117"/>
+      <c r="AD45" s="117"/>
+      <c r="AE45" s="117"/>
+      <c r="AF45" s="117"/>
+      <c r="AG45" s="117"/>
+      <c r="AH45" s="117"/>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
-      <c r="AK45" s="147"/>
-      <c r="AL45" s="147"/>
-      <c r="AM45" s="147"/>
-      <c r="AN45" s="147"/>
-      <c r="AO45" s="147"/>
-      <c r="AP45" s="147"/>
-      <c r="AQ45" s="147"/>
-      <c r="AR45" s="147"/>
-      <c r="AS45" s="147"/>
-      <c r="AT45" s="147"/>
-      <c r="AU45" s="147"/>
-      <c r="AV45" s="147"/>
-      <c r="AW45" s="147"/>
-      <c r="AX45" s="147"/>
-      <c r="AY45" s="147"/>
-      <c r="AZ45" s="147"/>
+      <c r="AK45" s="117"/>
+      <c r="AL45" s="117"/>
+      <c r="AM45" s="117"/>
+      <c r="AN45" s="117"/>
+      <c r="AO45" s="117"/>
+      <c r="AP45" s="117"/>
+      <c r="AQ45" s="117"/>
+      <c r="AR45" s="117"/>
+      <c r="AS45" s="117"/>
+      <c r="AT45" s="117"/>
+      <c r="AU45" s="117"/>
+      <c r="AV45" s="117"/>
+      <c r="AW45" s="117"/>
+      <c r="AX45" s="117"/>
+      <c r="AY45" s="117"/>
+      <c r="AZ45" s="117"/>
     </row>
     <row r="46" spans="1:53" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="211" t="s">
+      <c r="A46" s="118" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="211"/>
-      <c r="C46" s="211"/>
-      <c r="D46" s="211"/>
-      <c r="E46" s="211"/>
-      <c r="F46" s="211"/>
-      <c r="G46" s="211"/>
-      <c r="H46" s="211"/>
-      <c r="I46" s="211"/>
-      <c r="J46" s="211"/>
-      <c r="K46" s="211"/>
-      <c r="L46" s="211"/>
-      <c r="M46" s="211"/>
-      <c r="N46" s="211"/>
-      <c r="O46" s="211"/>
-      <c r="P46" s="211"/>
+      <c r="B46" s="118"/>
+      <c r="C46" s="118"/>
+      <c r="D46" s="118"/>
+      <c r="E46" s="118"/>
+      <c r="F46" s="118"/>
+      <c r="G46" s="118"/>
+      <c r="H46" s="118"/>
+      <c r="I46" s="118"/>
+      <c r="J46" s="118"/>
+      <c r="K46" s="118"/>
+      <c r="L46" s="118"/>
+      <c r="M46" s="118"/>
+      <c r="N46" s="118"/>
+      <c r="O46" s="118"/>
+      <c r="P46" s="118"/>
       <c r="Q46" s="54"/>
       <c r="R46" s="54"/>
-      <c r="S46" s="122" t="s">
+      <c r="S46" s="195" t="s">
         <v>78</v>
       </c>
-      <c r="T46" s="122"/>
-      <c r="U46" s="122"/>
-      <c r="V46" s="122"/>
-      <c r="W46" s="122"/>
-      <c r="X46" s="122"/>
-      <c r="Y46" s="122"/>
-      <c r="Z46" s="122"/>
-      <c r="AA46" s="122"/>
-      <c r="AB46" s="122"/>
-      <c r="AC46" s="122"/>
-      <c r="AD46" s="122"/>
-      <c r="AE46" s="122"/>
-      <c r="AF46" s="122"/>
-      <c r="AG46" s="122"/>
-      <c r="AH46" s="122"/>
+      <c r="T46" s="195"/>
+      <c r="U46" s="195"/>
+      <c r="V46" s="195"/>
+      <c r="W46" s="195"/>
+      <c r="X46" s="195"/>
+      <c r="Y46" s="195"/>
+      <c r="Z46" s="195"/>
+      <c r="AA46" s="195"/>
+      <c r="AB46" s="195"/>
+      <c r="AC46" s="195"/>
+      <c r="AD46" s="195"/>
+      <c r="AE46" s="195"/>
+      <c r="AF46" s="195"/>
+      <c r="AG46" s="195"/>
+      <c r="AH46" s="195"/>
       <c r="AI46" s="54"/>
       <c r="AJ46" s="54"/>
-      <c r="AK46" s="211" t="s">
+      <c r="AK46" s="118" t="s">
         <v>79</v>
       </c>
-      <c r="AL46" s="211"/>
-      <c r="AM46" s="211"/>
-      <c r="AN46" s="211"/>
-      <c r="AO46" s="211"/>
-      <c r="AP46" s="211"/>
-      <c r="AQ46" s="211"/>
-      <c r="AR46" s="211"/>
-      <c r="AS46" s="211"/>
-      <c r="AT46" s="211"/>
-      <c r="AU46" s="211"/>
-      <c r="AV46" s="211"/>
-      <c r="AW46" s="211"/>
-      <c r="AX46" s="211"/>
-      <c r="AY46" s="211"/>
-      <c r="AZ46" s="211"/>
+      <c r="AL46" s="118"/>
+      <c r="AM46" s="118"/>
+      <c r="AN46" s="118"/>
+      <c r="AO46" s="118"/>
+      <c r="AP46" s="118"/>
+      <c r="AQ46" s="118"/>
+      <c r="AR46" s="118"/>
+      <c r="AS46" s="118"/>
+      <c r="AT46" s="118"/>
+      <c r="AU46" s="118"/>
+      <c r="AV46" s="118"/>
+      <c r="AW46" s="118"/>
+      <c r="AX46" s="118"/>
+      <c r="AY46" s="118"/>
+      <c r="AZ46" s="118"/>
     </row>
     <row r="47" spans="1:53" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="245"/>
-      <c r="B47" s="245"/>
-      <c r="C47" s="245"/>
-      <c r="D47" s="245"/>
-      <c r="E47" s="245"/>
-      <c r="F47" s="245"/>
-      <c r="G47" s="245"/>
-      <c r="H47" s="245"/>
-      <c r="I47" s="245"/>
-      <c r="J47" s="245"/>
-      <c r="K47" s="245"/>
-      <c r="L47" s="245"/>
-      <c r="M47" s="245"/>
-      <c r="N47" s="245"/>
-      <c r="O47" s="245"/>
-      <c r="P47" s="245"/>
-      <c r="S47" s="245"/>
-      <c r="T47" s="245"/>
-      <c r="U47" s="245"/>
-      <c r="V47" s="246"/>
-      <c r="W47" s="247"/>
-      <c r="X47" s="247"/>
-      <c r="Y47" s="247"/>
-      <c r="Z47" s="247"/>
-      <c r="AA47" s="247"/>
-      <c r="AB47" s="247"/>
-      <c r="AC47" s="247"/>
-      <c r="AD47" s="247"/>
-      <c r="AE47" s="247"/>
-      <c r="AF47" s="247"/>
-      <c r="AG47" s="247"/>
-      <c r="AH47" s="247"/>
-      <c r="AK47" s="212" t="s">
+      <c r="A47" s="255"/>
+      <c r="B47" s="255"/>
+      <c r="C47" s="255"/>
+      <c r="D47" s="255"/>
+      <c r="E47" s="255"/>
+      <c r="F47" s="255"/>
+      <c r="G47" s="255"/>
+      <c r="H47" s="255"/>
+      <c r="I47" s="255"/>
+      <c r="J47" s="255"/>
+      <c r="K47" s="255"/>
+      <c r="L47" s="255"/>
+      <c r="M47" s="255"/>
+      <c r="N47" s="255"/>
+      <c r="O47" s="255"/>
+      <c r="P47" s="255"/>
+      <c r="S47" s="255"/>
+      <c r="T47" s="255"/>
+      <c r="U47" s="255"/>
+      <c r="V47" s="256"/>
+      <c r="W47" s="257"/>
+      <c r="X47" s="257"/>
+      <c r="Y47" s="257"/>
+      <c r="Z47" s="257"/>
+      <c r="AA47" s="257"/>
+      <c r="AB47" s="257"/>
+      <c r="AC47" s="257"/>
+      <c r="AD47" s="257"/>
+      <c r="AE47" s="257"/>
+      <c r="AF47" s="257"/>
+      <c r="AG47" s="257"/>
+      <c r="AH47" s="257"/>
+      <c r="AK47" s="119" t="s">
         <v>792</v>
       </c>
-      <c r="AL47" s="212"/>
-      <c r="AM47" s="212"/>
-      <c r="AN47" s="212"/>
-      <c r="AO47" s="212"/>
-      <c r="AP47" s="212"/>
-      <c r="AQ47" s="212"/>
-      <c r="AR47" s="212"/>
-      <c r="AS47" s="212"/>
-      <c r="AT47" s="212"/>
-      <c r="AU47" s="212"/>
-      <c r="AV47" s="212"/>
-      <c r="AW47" s="212"/>
-      <c r="AX47" s="212"/>
-      <c r="AY47" s="212"/>
-      <c r="AZ47" s="212"/>
+      <c r="AL47" s="119"/>
+      <c r="AM47" s="119"/>
+      <c r="AN47" s="119"/>
+      <c r="AO47" s="119"/>
+      <c r="AP47" s="119"/>
+      <c r="AQ47" s="119"/>
+      <c r="AR47" s="119"/>
+      <c r="AS47" s="119"/>
+      <c r="AT47" s="119"/>
+      <c r="AU47" s="119"/>
+      <c r="AV47" s="119"/>
+      <c r="AW47" s="119"/>
+      <c r="AX47" s="119"/>
+      <c r="AY47" s="119"/>
+      <c r="AZ47" s="119"/>
     </row>
     <row r="48" spans="1:53" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E30:AZ30"/>
+    <mergeCell ref="E31:AZ31"/>
+    <mergeCell ref="E32:AZ32"/>
+    <mergeCell ref="E26:AZ26"/>
+    <mergeCell ref="E27:AZ27"/>
+    <mergeCell ref="E28:AZ28"/>
+    <mergeCell ref="E29:AZ29"/>
+    <mergeCell ref="A46:P46"/>
+    <mergeCell ref="S46:AH46"/>
+    <mergeCell ref="AK46:AZ46"/>
+    <mergeCell ref="A47:P47"/>
+    <mergeCell ref="AK47:AZ47"/>
+    <mergeCell ref="S47:U47"/>
+    <mergeCell ref="V47:AH47"/>
+    <mergeCell ref="E42:AZ42"/>
+    <mergeCell ref="E39:AZ39"/>
+    <mergeCell ref="E40:AZ40"/>
+    <mergeCell ref="E41:AZ41"/>
+    <mergeCell ref="E38:AZ38"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="E9:AZ9"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="E33:AZ33"/>
+    <mergeCell ref="E34:AZ34"/>
+    <mergeCell ref="E37:AZ37"/>
+    <mergeCell ref="E35:AZ35"/>
+    <mergeCell ref="E36:AZ36"/>
+    <mergeCell ref="A4:AZ4"/>
+    <mergeCell ref="K2:AP2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="E6:AZ6"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="AS1:AZ3"/>
+    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A45:P45"/>
     <mergeCell ref="S45:AH45"/>
@@ -12345,56 +12444,11 @@
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A4:AZ4"/>
-    <mergeCell ref="K2:AP2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="E6:AZ6"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="AS1:AZ3"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="E9:AZ9"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="E33:AZ33"/>
-    <mergeCell ref="E34:AZ34"/>
-    <mergeCell ref="E37:AZ37"/>
-    <mergeCell ref="E35:AZ35"/>
-    <mergeCell ref="E36:AZ36"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="E42:AZ42"/>
-    <mergeCell ref="E39:AZ39"/>
-    <mergeCell ref="E40:AZ40"/>
-    <mergeCell ref="E41:AZ41"/>
-    <mergeCell ref="E38:AZ38"/>
-    <mergeCell ref="A46:P46"/>
-    <mergeCell ref="S46:AH46"/>
-    <mergeCell ref="AK46:AZ46"/>
-    <mergeCell ref="A47:P47"/>
-    <mergeCell ref="AK47:AZ47"/>
-    <mergeCell ref="S47:U47"/>
-    <mergeCell ref="V47:AH47"/>
-    <mergeCell ref="E30:AZ30"/>
-    <mergeCell ref="E31:AZ31"/>
-    <mergeCell ref="E32:AZ32"/>
-    <mergeCell ref="E26:AZ26"/>
-    <mergeCell ref="E27:AZ27"/>
-    <mergeCell ref="E28:AZ28"/>
-    <mergeCell ref="E29:AZ29"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -12428,126 +12482,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="14" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="264" t="e" vm="1">
+      <c r="A1" s="263" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
-      <c r="N1" s="265"/>
-      <c r="O1" s="266"/>
+      <c r="B1" s="264"/>
+      <c r="C1" s="264"/>
+      <c r="D1" s="264"/>
+      <c r="E1" s="264"/>
+      <c r="F1" s="264"/>
+      <c r="G1" s="264"/>
+      <c r="H1" s="264"/>
+      <c r="I1" s="264"/>
+      <c r="J1" s="264"/>
+      <c r="K1" s="264"/>
+      <c r="L1" s="264"/>
+      <c r="M1" s="264"/>
+      <c r="N1" s="264"/>
+      <c r="O1" s="265"/>
     </row>
     <row r="2" spans="1:15" s="14" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="267"/>
-      <c r="B2" s="268"/>
-      <c r="C2" s="268"/>
-      <c r="D2" s="268"/>
-      <c r="E2" s="268"/>
-      <c r="F2" s="268"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="268"/>
-      <c r="I2" s="268"/>
-      <c r="J2" s="268"/>
-      <c r="K2" s="268"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="268"/>
-      <c r="N2" s="268"/>
-      <c r="O2" s="269"/>
+      <c r="A2" s="266"/>
+      <c r="B2" s="267"/>
+      <c r="C2" s="267"/>
+      <c r="D2" s="267"/>
+      <c r="E2" s="267"/>
+      <c r="F2" s="267"/>
+      <c r="G2" s="267"/>
+      <c r="H2" s="267"/>
+      <c r="I2" s="267"/>
+      <c r="J2" s="267"/>
+      <c r="K2" s="267"/>
+      <c r="L2" s="267"/>
+      <c r="M2" s="267"/>
+      <c r="N2" s="267"/>
+      <c r="O2" s="268"/>
     </row>
     <row r="3" spans="1:15" s="14" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="270"/>
-      <c r="B3" s="271"/>
-      <c r="C3" s="271"/>
-      <c r="D3" s="271"/>
-      <c r="E3" s="271"/>
-      <c r="F3" s="271"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="271"/>
-      <c r="I3" s="271"/>
-      <c r="J3" s="271"/>
-      <c r="K3" s="271"/>
-      <c r="L3" s="271"/>
-      <c r="M3" s="271"/>
-      <c r="N3" s="271"/>
-      <c r="O3" s="272"/>
+      <c r="A3" s="269"/>
+      <c r="B3" s="270"/>
+      <c r="C3" s="270"/>
+      <c r="D3" s="270"/>
+      <c r="E3" s="270"/>
+      <c r="F3" s="270"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="270"/>
+      <c r="I3" s="270"/>
+      <c r="J3" s="270"/>
+      <c r="K3" s="270"/>
+      <c r="L3" s="270"/>
+      <c r="M3" s="270"/>
+      <c r="N3" s="270"/>
+      <c r="O3" s="271"/>
     </row>
     <row r="4" spans="1:15" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="261" t="s">
+      <c r="A4" s="260" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="262"/>
-      <c r="C4" s="262"/>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
-      <c r="M4" s="262"/>
-      <c r="N4" s="262"/>
-      <c r="O4" s="263"/>
+      <c r="B4" s="261"/>
+      <c r="C4" s="261"/>
+      <c r="D4" s="261"/>
+      <c r="E4" s="261"/>
+      <c r="F4" s="261"/>
+      <c r="G4" s="261"/>
+      <c r="H4" s="261"/>
+      <c r="I4" s="261"/>
+      <c r="J4" s="261"/>
+      <c r="K4" s="261"/>
+      <c r="L4" s="261"/>
+      <c r="M4" s="261"/>
+      <c r="N4" s="261"/>
+      <c r="O4" s="262"/>
     </row>
     <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="273" t="s">
+      <c r="A5" s="272" t="s">
         <v>106</v>
       </c>
-      <c r="B5" s="259" t="s">
+      <c r="B5" s="258" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="259" t="s">
+      <c r="C5" s="258" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="259" t="s">
+      <c r="D5" s="258" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="259" t="s">
+      <c r="E5" s="258" t="s">
         <v>110</v>
       </c>
-      <c r="F5" s="259" t="s">
+      <c r="F5" s="258" t="s">
         <v>111</v>
       </c>
-      <c r="G5" s="259" t="s">
+      <c r="G5" s="258" t="s">
         <v>112</v>
       </c>
-      <c r="H5" s="259" t="s">
+      <c r="H5" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="I5" s="259" t="s">
+      <c r="I5" s="258" t="s">
         <v>114</v>
       </c>
-      <c r="J5" s="275" t="s">
+      <c r="J5" s="274" t="s">
         <v>115</v>
       </c>
-      <c r="K5" s="276"/>
-      <c r="L5" s="277"/>
-      <c r="M5" s="275" t="s">
+      <c r="K5" s="275"/>
+      <c r="L5" s="276"/>
+      <c r="M5" s="274" t="s">
         <v>116</v>
       </c>
-      <c r="N5" s="276"/>
-      <c r="O5" s="278"/>
+      <c r="N5" s="275"/>
+      <c r="O5" s="277"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="274"/>
-      <c r="B6" s="260"/>
-      <c r="C6" s="260"/>
-      <c r="D6" s="260"/>
-      <c r="E6" s="260"/>
-      <c r="F6" s="260"/>
-      <c r="G6" s="260"/>
-      <c r="H6" s="260"/>
-      <c r="I6" s="260"/>
+      <c r="A6" s="273"/>
+      <c r="B6" s="259"/>
+      <c r="C6" s="259"/>
+      <c r="D6" s="259"/>
+      <c r="E6" s="259"/>
+      <c r="F6" s="259"/>
+      <c r="G6" s="259"/>
+      <c r="H6" s="259"/>
+      <c r="I6" s="259"/>
       <c r="J6" s="84" t="s">
         <v>117</v>
       </c>
@@ -18227,7 +18281,7 @@
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="29" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId56"/>
+  <pageSetup paperSize="9" scale="30" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId56"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;L
 &amp;G</oddHeader>
@@ -18255,110 +18309,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="14" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="264" t="e" vm="1">
+      <c r="A1" s="263" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="266"/>
+      <c r="B1" s="264"/>
+      <c r="C1" s="264"/>
+      <c r="D1" s="264"/>
+      <c r="E1" s="264"/>
+      <c r="F1" s="264"/>
+      <c r="G1" s="264"/>
+      <c r="H1" s="264"/>
+      <c r="I1" s="264"/>
+      <c r="J1" s="264"/>
+      <c r="K1" s="264"/>
+      <c r="L1" s="264"/>
+      <c r="M1" s="265"/>
     </row>
     <row r="2" spans="1:13" s="14" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="267"/>
-      <c r="B2" s="268"/>
-      <c r="C2" s="268"/>
-      <c r="D2" s="268"/>
-      <c r="E2" s="268"/>
-      <c r="F2" s="268"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="268"/>
-      <c r="I2" s="268"/>
-      <c r="J2" s="268"/>
-      <c r="K2" s="268"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="269"/>
+      <c r="A2" s="266"/>
+      <c r="B2" s="267"/>
+      <c r="C2" s="267"/>
+      <c r="D2" s="267"/>
+      <c r="E2" s="267"/>
+      <c r="F2" s="267"/>
+      <c r="G2" s="267"/>
+      <c r="H2" s="267"/>
+      <c r="I2" s="267"/>
+      <c r="J2" s="267"/>
+      <c r="K2" s="267"/>
+      <c r="L2" s="267"/>
+      <c r="M2" s="268"/>
     </row>
     <row r="3" spans="1:13" s="14" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="270"/>
-      <c r="B3" s="271"/>
-      <c r="C3" s="271"/>
-      <c r="D3" s="271"/>
-      <c r="E3" s="271"/>
-      <c r="F3" s="271"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="271"/>
-      <c r="I3" s="271"/>
-      <c r="J3" s="271"/>
-      <c r="K3" s="271"/>
-      <c r="L3" s="271"/>
-      <c r="M3" s="272"/>
+      <c r="A3" s="269"/>
+      <c r="B3" s="270"/>
+      <c r="C3" s="270"/>
+      <c r="D3" s="270"/>
+      <c r="E3" s="270"/>
+      <c r="F3" s="270"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="270"/>
+      <c r="I3" s="270"/>
+      <c r="J3" s="270"/>
+      <c r="K3" s="270"/>
+      <c r="L3" s="270"/>
+      <c r="M3" s="271"/>
     </row>
     <row r="4" spans="1:13" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="261" t="s">
+      <c r="A4" s="260" t="s">
         <v>660</v>
       </c>
-      <c r="B4" s="262"/>
-      <c r="C4" s="262"/>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
-      <c r="M4" s="263"/>
+      <c r="B4" s="261"/>
+      <c r="C4" s="261"/>
+      <c r="D4" s="261"/>
+      <c r="E4" s="261"/>
+      <c r="F4" s="261"/>
+      <c r="G4" s="261"/>
+      <c r="H4" s="261"/>
+      <c r="I4" s="261"/>
+      <c r="J4" s="261"/>
+      <c r="K4" s="261"/>
+      <c r="L4" s="261"/>
+      <c r="M4" s="262"/>
     </row>
     <row r="5" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="285" t="s">
+      <c r="A5" s="284" t="s">
         <v>661</v>
       </c>
-      <c r="B5" s="279" t="s">
+      <c r="B5" s="278" t="s">
         <v>662</v>
       </c>
-      <c r="C5" s="279" t="s">
+      <c r="C5" s="278" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="279" t="s">
+      <c r="D5" s="278" t="s">
         <v>108</v>
       </c>
-      <c r="E5" s="279" t="s">
+      <c r="E5" s="278" t="s">
         <v>109</v>
       </c>
-      <c r="F5" s="279" t="s">
+      <c r="F5" s="278" t="s">
         <v>110</v>
       </c>
-      <c r="G5" s="279" t="s">
+      <c r="G5" s="278" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="281" t="s">
+      <c r="H5" s="280" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="282"/>
-      <c r="J5" s="283"/>
-      <c r="K5" s="281" t="s">
+      <c r="I5" s="281"/>
+      <c r="J5" s="282"/>
+      <c r="K5" s="280" t="s">
         <v>116</v>
       </c>
-      <c r="L5" s="282"/>
-      <c r="M5" s="284"/>
+      <c r="L5" s="281"/>
+      <c r="M5" s="283"/>
     </row>
     <row r="6" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="286"/>
-      <c r="B6" s="280"/>
-      <c r="C6" s="280"/>
-      <c r="D6" s="280"/>
-      <c r="E6" s="280"/>
-      <c r="F6" s="280"/>
-      <c r="G6" s="280"/>
+      <c r="A6" s="285"/>
+      <c r="B6" s="279"/>
+      <c r="C6" s="279"/>
+      <c r="D6" s="279"/>
+      <c r="E6" s="279"/>
+      <c r="F6" s="279"/>
+      <c r="G6" s="279"/>
       <c r="H6" s="50" t="s">
         <v>117</v>
       </c>
@@ -19445,6 +19499,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c24bca33-91ee-4c94-9d6c-305b441d02fd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e46781df-dd49-4a0f-be02-040bfbf345c5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2EBC4C97F3EED4F8F99B50CD61D9AF7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0ffa3ef56536b291ffb1e746207cdfaf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e46781df-dd49-4a0f-be02-040bfbf345c5" xmlns:ns3="c24bca33-91ee-4c94-9d6c-305b441d02fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="82d71f54c8a292e50b13588301f7fd2c" ns2:_="" ns3:_="">
     <xsd:import namespace="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
@@ -19673,27 +19747,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c24bca33-91ee-4c94-9d6c-305b441d02fd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e46781df-dd49-4a0f-be02-040bfbf345c5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA908177-54FE-4386-8E64-F855D4FAA630}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F87E2A-9E0E-44C0-A603-7E661F8ABEB3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c24bca33-91ee-4c94-9d6c-305b441d02fd"/>
+    <ds:schemaRef ds:uri="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDAB891A-AABF-4B04-8872-1A9CED3578DB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19710,23 +19783,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F87E2A-9E0E-44C0-A603-7E661F8ABEB3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c24bca33-91ee-4c94-9d6c-305b441d02fd"/>
-    <ds:schemaRef ds:uri="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA908177-54FE-4386-8E64-F855D4FAA630}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/RSC 08.0000.25 - Relatório de Serviço de Campo - Padrão - Rev.38.xlsx
+++ b/RSC 08.0000.25 - Relatório de Serviço de Campo - Padrão - Rev.38.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ktsabr-my.sharepoint.com/personal/gustavo_arruda_ktsa_com_br/Documents/PROJETOS/Engenharia/RSC - Relatório de Serviço de Campo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{F948FEA9-3545-4234-B576-12B0A63E47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{354B54C3-8341-42D5-BFC4-9813F2A749B8}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{F948FEA9-3545-4234-B576-12B0A63E47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25BA8208-61D9-401D-84D6-D1DD524DA5D2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2688,7 +2688,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -3269,51 +3269,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3325,7 +3280,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="290">
+  <cellXfs count="289">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3543,31 +3498,460 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3576,18 +3960,6 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3612,473 +3984,59 @@
     <xf numFmtId="4" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="4" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4146,16 +4104,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5217,14 +5169,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="137"/>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="139"/>
+      <c r="A1" s="168"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
+      <c r="H1" s="170"/>
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
       <c r="K1" s="21"/>
@@ -5261,87 +5213,87 @@
       <c r="AP1" s="22"/>
       <c r="AQ1" s="22"/>
       <c r="AR1" s="22"/>
-      <c r="AS1" s="146" t="s">
+      <c r="AS1" s="177" t="s">
         <v>0</v>
       </c>
-      <c r="AT1" s="147"/>
-      <c r="AU1" s="147"/>
-      <c r="AV1" s="147"/>
-      <c r="AW1" s="147"/>
-      <c r="AX1" s="147"/>
-      <c r="AY1" s="147"/>
-      <c r="AZ1" s="148"/>
+      <c r="AT1" s="178"/>
+      <c r="AU1" s="178"/>
+      <c r="AV1" s="178"/>
+      <c r="AW1" s="178"/>
+      <c r="AX1" s="178"/>
+      <c r="AY1" s="178"/>
+      <c r="AZ1" s="179"/>
       <c r="BD1" s="23"/>
       <c r="BF1" s="27"/>
       <c r="BG1" s="27"/>
     </row>
     <row r="2" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="140"/>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="142"/>
-      <c r="K2" s="156" t="s">
+      <c r="A2" s="171"/>
+      <c r="B2" s="172"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="173"/>
+      <c r="K2" s="187" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="157"/>
-      <c r="R2" s="157"/>
-      <c r="S2" s="157"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="157"/>
-      <c r="W2" s="157"/>
-      <c r="X2" s="157"/>
-      <c r="Y2" s="157"/>
-      <c r="Z2" s="157"/>
-      <c r="AA2" s="157"/>
-      <c r="AB2" s="157"/>
-      <c r="AC2" s="157"/>
-      <c r="AD2" s="157"/>
-      <c r="AE2" s="157"/>
-      <c r="AF2" s="157"/>
-      <c r="AG2" s="157"/>
-      <c r="AH2" s="157"/>
-      <c r="AI2" s="157"/>
-      <c r="AJ2" s="157"/>
-      <c r="AK2" s="157"/>
-      <c r="AL2" s="157"/>
-      <c r="AM2" s="157"/>
-      <c r="AN2" s="157"/>
-      <c r="AO2" s="157"/>
-      <c r="AP2" s="157"/>
+      <c r="L2" s="188"/>
+      <c r="M2" s="188"/>
+      <c r="N2" s="188"/>
+      <c r="O2" s="188"/>
+      <c r="P2" s="188"/>
+      <c r="Q2" s="188"/>
+      <c r="R2" s="188"/>
+      <c r="S2" s="188"/>
+      <c r="T2" s="188"/>
+      <c r="U2" s="188"/>
+      <c r="V2" s="188"/>
+      <c r="W2" s="188"/>
+      <c r="X2" s="188"/>
+      <c r="Y2" s="188"/>
+      <c r="Z2" s="188"/>
+      <c r="AA2" s="188"/>
+      <c r="AB2" s="188"/>
+      <c r="AC2" s="188"/>
+      <c r="AD2" s="188"/>
+      <c r="AE2" s="188"/>
+      <c r="AF2" s="188"/>
+      <c r="AG2" s="188"/>
+      <c r="AH2" s="188"/>
+      <c r="AI2" s="188"/>
+      <c r="AJ2" s="188"/>
+      <c r="AK2" s="188"/>
+      <c r="AL2" s="188"/>
+      <c r="AM2" s="188"/>
+      <c r="AN2" s="188"/>
+      <c r="AO2" s="188"/>
+      <c r="AP2" s="188"/>
       <c r="AQ2" s="17"/>
       <c r="AR2" s="17"/>
-      <c r="AS2" s="149"/>
-      <c r="AT2" s="150"/>
-      <c r="AU2" s="150"/>
-      <c r="AV2" s="150"/>
-      <c r="AW2" s="150"/>
-      <c r="AX2" s="150"/>
-      <c r="AY2" s="150"/>
-      <c r="AZ2" s="151"/>
+      <c r="AS2" s="180"/>
+      <c r="AT2" s="181"/>
+      <c r="AU2" s="181"/>
+      <c r="AV2" s="181"/>
+      <c r="AW2" s="181"/>
+      <c r="AX2" s="181"/>
+      <c r="AY2" s="181"/>
+      <c r="AZ2" s="182"/>
       <c r="BA2" s="7"/>
       <c r="BF2" s="25"/>
       <c r="BG2" s="25"/>
       <c r="BH2" s="25"/>
     </row>
     <row r="3" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="143"/>
-      <c r="B3" s="144"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="144"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="145"/>
+      <c r="A3" s="174"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="176"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -5378,392 +5330,392 @@
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
       <c r="AR3" s="4"/>
-      <c r="AS3" s="152"/>
-      <c r="AT3" s="153"/>
-      <c r="AU3" s="153"/>
-      <c r="AV3" s="153"/>
-      <c r="AW3" s="153"/>
-      <c r="AX3" s="153"/>
-      <c r="AY3" s="153"/>
-      <c r="AZ3" s="154"/>
+      <c r="AS3" s="183"/>
+      <c r="AT3" s="184"/>
+      <c r="AU3" s="184"/>
+      <c r="AV3" s="184"/>
+      <c r="AW3" s="184"/>
+      <c r="AX3" s="184"/>
+      <c r="AY3" s="184"/>
+      <c r="AZ3" s="185"/>
     </row>
     <row r="4" spans="1:60" s="3" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="101"/>
-      <c r="L4" s="101"/>
-      <c r="M4" s="101"/>
-      <c r="N4" s="101"/>
-      <c r="O4" s="101"/>
-      <c r="P4" s="101"/>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="101"/>
-      <c r="S4" s="101"/>
-      <c r="T4" s="101"/>
-      <c r="U4" s="101"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="101"/>
-      <c r="X4" s="101"/>
-      <c r="Y4" s="101"/>
-      <c r="Z4" s="101"/>
-      <c r="AA4" s="101"/>
-      <c r="AB4" s="101"/>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="101"/>
-      <c r="AE4" s="101"/>
-      <c r="AF4" s="101"/>
-      <c r="AG4" s="101"/>
-      <c r="AH4" s="101"/>
-      <c r="AI4" s="101"/>
-      <c r="AJ4" s="101"/>
-      <c r="AK4" s="101"/>
-      <c r="AL4" s="101"/>
-      <c r="AM4" s="101"/>
-      <c r="AN4" s="101"/>
-      <c r="AO4" s="101"/>
-      <c r="AP4" s="101"/>
-      <c r="AQ4" s="101"/>
-      <c r="AR4" s="101"/>
-      <c r="AS4" s="101"/>
-      <c r="AT4" s="101"/>
-      <c r="AU4" s="101"/>
-      <c r="AV4" s="101"/>
-      <c r="AW4" s="101"/>
-      <c r="AX4" s="101"/>
-      <c r="AY4" s="101"/>
-      <c r="AZ4" s="102"/>
+      <c r="B4" s="190"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="190"/>
+      <c r="K4" s="190"/>
+      <c r="L4" s="190"/>
+      <c r="M4" s="190"/>
+      <c r="N4" s="190"/>
+      <c r="O4" s="190"/>
+      <c r="P4" s="190"/>
+      <c r="Q4" s="190"/>
+      <c r="R4" s="190"/>
+      <c r="S4" s="190"/>
+      <c r="T4" s="190"/>
+      <c r="U4" s="190"/>
+      <c r="V4" s="190"/>
+      <c r="W4" s="190"/>
+      <c r="X4" s="190"/>
+      <c r="Y4" s="190"/>
+      <c r="Z4" s="190"/>
+      <c r="AA4" s="190"/>
+      <c r="AB4" s="190"/>
+      <c r="AC4" s="190"/>
+      <c r="AD4" s="190"/>
+      <c r="AE4" s="190"/>
+      <c r="AF4" s="190"/>
+      <c r="AG4" s="190"/>
+      <c r="AH4" s="190"/>
+      <c r="AI4" s="190"/>
+      <c r="AJ4" s="190"/>
+      <c r="AK4" s="190"/>
+      <c r="AL4" s="190"/>
+      <c r="AM4" s="190"/>
+      <c r="AN4" s="190"/>
+      <c r="AO4" s="190"/>
+      <c r="AP4" s="190"/>
+      <c r="AQ4" s="190"/>
+      <c r="AR4" s="190"/>
+      <c r="AS4" s="190"/>
+      <c r="AT4" s="190"/>
+      <c r="AU4" s="190"/>
+      <c r="AV4" s="190"/>
+      <c r="AW4" s="190"/>
+      <c r="AX4" s="190"/>
+      <c r="AY4" s="190"/>
+      <c r="AZ4" s="191"/>
       <c r="BA4" s="9"/>
       <c r="BB4" s="9"/>
       <c r="BC4" s="9"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="161" t="s">
+      <c r="A5" s="195" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="162"/>
-      <c r="C5" s="162"/>
-      <c r="D5" s="162"/>
-      <c r="E5" s="162"/>
-      <c r="F5" s="162"/>
-      <c r="G5" s="171"/>
-      <c r="H5" s="171"/>
-      <c r="I5" s="171"/>
-      <c r="J5" s="171"/>
-      <c r="K5" s="171"/>
-      <c r="L5" s="171"/>
-      <c r="M5" s="171"/>
-      <c r="N5" s="171"/>
-      <c r="O5" s="171"/>
-      <c r="P5" s="171"/>
-      <c r="Q5" s="171"/>
-      <c r="R5" s="171"/>
-      <c r="S5" s="171"/>
-      <c r="T5" s="171"/>
-      <c r="U5" s="171"/>
-      <c r="V5" s="171"/>
-      <c r="W5" s="171"/>
-      <c r="X5" s="171"/>
-      <c r="Y5" s="171"/>
-      <c r="Z5" s="171"/>
-      <c r="AA5" s="171"/>
-      <c r="AB5" s="171"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="196"/>
+      <c r="D5" s="196"/>
+      <c r="E5" s="196"/>
+      <c r="F5" s="196"/>
+      <c r="G5" s="201"/>
+      <c r="H5" s="201"/>
+      <c r="I5" s="201"/>
+      <c r="J5" s="201"/>
+      <c r="K5" s="201"/>
+      <c r="L5" s="201"/>
+      <c r="M5" s="201"/>
+      <c r="N5" s="201"/>
+      <c r="O5" s="201"/>
+      <c r="P5" s="201"/>
+      <c r="Q5" s="201"/>
+      <c r="R5" s="201"/>
+      <c r="S5" s="201"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="201"/>
+      <c r="V5" s="201"/>
+      <c r="W5" s="201"/>
+      <c r="X5" s="201"/>
+      <c r="Y5" s="201"/>
+      <c r="Z5" s="201"/>
+      <c r="AA5" s="201"/>
+      <c r="AB5" s="201"/>
       <c r="AC5" s="55"/>
       <c r="AD5" s="58"/>
-      <c r="AE5" s="170" t="s">
+      <c r="AE5" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="AF5" s="170"/>
-      <c r="AG5" s="170"/>
-      <c r="AH5" s="170"/>
-      <c r="AI5" s="170"/>
-      <c r="AJ5" s="170"/>
-      <c r="AK5" s="170"/>
-      <c r="AL5" s="181"/>
-      <c r="AM5" s="181"/>
-      <c r="AN5" s="181"/>
-      <c r="AO5" s="181"/>
-      <c r="AP5" s="181"/>
-      <c r="AQ5" s="181"/>
-      <c r="AR5" s="181"/>
-      <c r="AS5" s="181"/>
-      <c r="AT5" s="181"/>
-      <c r="AU5" s="181"/>
-      <c r="AV5" s="181"/>
-      <c r="AW5" s="181"/>
-      <c r="AX5" s="181"/>
-      <c r="AY5" s="181"/>
-      <c r="AZ5" s="182"/>
+      <c r="AF5" s="106"/>
+      <c r="AG5" s="106"/>
+      <c r="AH5" s="106"/>
+      <c r="AI5" s="106"/>
+      <c r="AJ5" s="106"/>
+      <c r="AK5" s="106"/>
+      <c r="AL5" s="208"/>
+      <c r="AM5" s="208"/>
+      <c r="AN5" s="208"/>
+      <c r="AO5" s="208"/>
+      <c r="AP5" s="208"/>
+      <c r="AQ5" s="208"/>
+      <c r="AR5" s="208"/>
+      <c r="AS5" s="208"/>
+      <c r="AT5" s="208"/>
+      <c r="AU5" s="208"/>
+      <c r="AV5" s="208"/>
+      <c r="AW5" s="208"/>
+      <c r="AX5" s="208"/>
+      <c r="AY5" s="208"/>
+      <c r="AZ5" s="209"/>
       <c r="BA5"/>
       <c r="BB5" s="9"/>
       <c r="BC5" s="9"/>
       <c r="BD5" s="9"/>
     </row>
     <row r="6" spans="1:60" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="161" t="s">
+      <c r="A6" s="195" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="162"/>
-      <c r="C6" s="162"/>
-      <c r="D6" s="162"/>
-      <c r="E6" s="162"/>
-      <c r="F6" s="162"/>
-      <c r="G6" s="136" t="str">
+      <c r="B6" s="196"/>
+      <c r="C6" s="196"/>
+      <c r="D6" s="196"/>
+      <c r="E6" s="196"/>
+      <c r="F6" s="196"/>
+      <c r="G6" s="91" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,4,0))</f>
         <v/>
       </c>
-      <c r="H6" s="136"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="136"/>
-      <c r="K6" s="136"/>
-      <c r="L6" s="136"/>
-      <c r="M6" s="136"/>
-      <c r="N6" s="136"/>
-      <c r="O6" s="136"/>
-      <c r="P6" s="136"/>
-      <c r="Q6" s="136"/>
-      <c r="R6" s="136"/>
-      <c r="S6" s="136"/>
-      <c r="T6" s="136"/>
-      <c r="U6" s="136"/>
-      <c r="V6" s="136"/>
-      <c r="W6" s="136"/>
-      <c r="X6" s="136"/>
-      <c r="Y6" s="136"/>
-      <c r="Z6" s="136"/>
-      <c r="AA6" s="136"/>
-      <c r="AB6" s="136"/>
-      <c r="AC6" s="136"/>
-      <c r="AD6" s="136"/>
-      <c r="AE6" s="136"/>
-      <c r="AF6" s="136"/>
-      <c r="AG6" s="136"/>
-      <c r="AH6" s="136"/>
-      <c r="AI6" s="136"/>
-      <c r="AJ6" s="136"/>
-      <c r="AK6" s="136"/>
-      <c r="AL6" s="136"/>
-      <c r="AM6" s="136"/>
-      <c r="AN6" s="136"/>
-      <c r="AO6" s="136"/>
-      <c r="AP6" s="136"/>
-      <c r="AQ6" s="136"/>
-      <c r="AR6" s="136"/>
-      <c r="AS6" s="136"/>
-      <c r="AT6" s="136"/>
-      <c r="AU6" s="136"/>
-      <c r="AV6" s="136"/>
-      <c r="AW6" s="136"/>
-      <c r="AX6" s="136"/>
-      <c r="AY6" s="136"/>
-      <c r="AZ6" s="155"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="91"/>
+      <c r="K6" s="91"/>
+      <c r="L6" s="91"/>
+      <c r="M6" s="91"/>
+      <c r="N6" s="91"/>
+      <c r="O6" s="91"/>
+      <c r="P6" s="91"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
+      <c r="V6" s="91"/>
+      <c r="W6" s="91"/>
+      <c r="X6" s="91"/>
+      <c r="Y6" s="91"/>
+      <c r="Z6" s="91"/>
+      <c r="AA6" s="91"/>
+      <c r="AB6" s="91"/>
+      <c r="AC6" s="91"/>
+      <c r="AD6" s="91"/>
+      <c r="AE6" s="91"/>
+      <c r="AF6" s="91"/>
+      <c r="AG6" s="91"/>
+      <c r="AH6" s="91"/>
+      <c r="AI6" s="91"/>
+      <c r="AJ6" s="91"/>
+      <c r="AK6" s="91"/>
+      <c r="AL6" s="91"/>
+      <c r="AM6" s="91"/>
+      <c r="AN6" s="91"/>
+      <c r="AO6" s="91"/>
+      <c r="AP6" s="91"/>
+      <c r="AQ6" s="91"/>
+      <c r="AR6" s="91"/>
+      <c r="AS6" s="91"/>
+      <c r="AT6" s="91"/>
+      <c r="AU6" s="91"/>
+      <c r="AV6" s="91"/>
+      <c r="AW6" s="91"/>
+      <c r="AX6" s="91"/>
+      <c r="AY6" s="91"/>
+      <c r="AZ6" s="186"/>
     </row>
     <row r="7" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="161" t="s">
+      <c r="A7" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="162"/>
-      <c r="C7" s="162"/>
-      <c r="D7" s="162"/>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="136" t="str">
+      <c r="B7" s="196"/>
+      <c r="C7" s="196"/>
+      <c r="D7" s="196"/>
+      <c r="E7" s="196"/>
+      <c r="F7" s="196"/>
+      <c r="G7" s="91" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,5,0))</f>
         <v/>
       </c>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="136"/>
-      <c r="L7" s="136"/>
-      <c r="M7" s="136"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="136"/>
-      <c r="P7" s="136"/>
-      <c r="Q7" s="136"/>
-      <c r="R7" s="136"/>
-      <c r="S7" s="136"/>
-      <c r="T7" s="136"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="91"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="91"/>
+      <c r="Q7" s="91"/>
+      <c r="R7" s="91"/>
+      <c r="S7" s="91"/>
+      <c r="T7" s="91"/>
       <c r="U7" s="57"/>
-      <c r="V7" s="176" t="s">
+      <c r="V7" s="161" t="s">
         <v>8</v>
       </c>
-      <c r="W7" s="176"/>
-      <c r="X7" s="176"/>
-      <c r="Y7" s="176"/>
-      <c r="Z7" s="136" t="str">
+      <c r="W7" s="161"/>
+      <c r="X7" s="161"/>
+      <c r="Y7" s="161"/>
+      <c r="Z7" s="91" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,2,0))</f>
         <v/>
       </c>
-      <c r="AA7" s="136"/>
-      <c r="AB7" s="136"/>
-      <c r="AC7" s="136"/>
-      <c r="AD7" s="136"/>
-      <c r="AE7" s="136"/>
-      <c r="AF7" s="136"/>
-      <c r="AG7" s="136"/>
-      <c r="AH7" s="136"/>
-      <c r="AI7" s="136"/>
-      <c r="AJ7" s="136"/>
-      <c r="AK7" s="136"/>
-      <c r="AL7" s="136"/>
-      <c r="AM7" s="136"/>
-      <c r="AN7" s="136"/>
-      <c r="AO7" s="136"/>
-      <c r="AP7" s="136"/>
+      <c r="AA7" s="91"/>
+      <c r="AB7" s="91"/>
+      <c r="AC7" s="91"/>
+      <c r="AD7" s="91"/>
+      <c r="AE7" s="91"/>
+      <c r="AF7" s="91"/>
+      <c r="AG7" s="91"/>
+      <c r="AH7" s="91"/>
+      <c r="AI7" s="91"/>
+      <c r="AJ7" s="91"/>
+      <c r="AK7" s="91"/>
+      <c r="AL7" s="91"/>
+      <c r="AM7" s="91"/>
+      <c r="AN7" s="91"/>
+      <c r="AO7" s="91"/>
+      <c r="AP7" s="91"/>
       <c r="AQ7" s="57"/>
-      <c r="AR7" s="176" t="s">
+      <c r="AR7" s="161" t="s">
         <v>9</v>
       </c>
-      <c r="AS7" s="176"/>
-      <c r="AT7" s="176"/>
-      <c r="AU7" s="176"/>
-      <c r="AV7" s="187" t="str">
+      <c r="AS7" s="161"/>
+      <c r="AT7" s="161"/>
+      <c r="AU7" s="161"/>
+      <c r="AV7" s="104" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,3,0))</f>
         <v/>
       </c>
-      <c r="AW7" s="187"/>
-      <c r="AX7" s="187"/>
-      <c r="AY7" s="187"/>
-      <c r="AZ7" s="188"/>
+      <c r="AW7" s="104"/>
+      <c r="AX7" s="104"/>
+      <c r="AY7" s="104"/>
+      <c r="AZ7" s="105"/>
       <c r="BA7"/>
     </row>
     <row r="8" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="172" t="s">
+      <c r="A8" s="202" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="173"/>
-      <c r="C8" s="173"/>
-      <c r="D8" s="173"/>
-      <c r="E8" s="173"/>
-      <c r="F8" s="173"/>
-      <c r="G8" s="174" t="str">
+      <c r="B8" s="203"/>
+      <c r="C8" s="203"/>
+      <c r="D8" s="203"/>
+      <c r="E8" s="203"/>
+      <c r="F8" s="203"/>
+      <c r="G8" s="204" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,6,0))</f>
         <v/>
       </c>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
-      <c r="J8" s="175"/>
-      <c r="K8" s="175"/>
-      <c r="L8" s="175"/>
-      <c r="M8" s="175"/>
-      <c r="N8" s="175"/>
-      <c r="O8" s="175"/>
-      <c r="P8" s="175"/>
-      <c r="Q8" s="175"/>
-      <c r="R8" s="175"/>
-      <c r="S8" s="175"/>
-      <c r="T8" s="175"/>
-      <c r="U8" s="175"/>
-      <c r="V8" s="175"/>
-      <c r="W8" s="175"/>
-      <c r="X8" s="175"/>
-      <c r="Y8" s="175"/>
-      <c r="Z8" s="175"/>
-      <c r="AA8" s="175"/>
-      <c r="AB8" s="175"/>
-      <c r="AC8" s="175"/>
+      <c r="H8" s="205"/>
+      <c r="I8" s="205"/>
+      <c r="J8" s="205"/>
+      <c r="K8" s="205"/>
+      <c r="L8" s="205"/>
+      <c r="M8" s="205"/>
+      <c r="N8" s="205"/>
+      <c r="O8" s="205"/>
+      <c r="P8" s="205"/>
+      <c r="Q8" s="205"/>
+      <c r="R8" s="205"/>
+      <c r="S8" s="205"/>
+      <c r="T8" s="205"/>
+      <c r="U8" s="205"/>
+      <c r="V8" s="205"/>
+      <c r="W8" s="205"/>
+      <c r="X8" s="205"/>
+      <c r="Y8" s="205"/>
+      <c r="Z8" s="205"/>
+      <c r="AA8" s="205"/>
+      <c r="AB8" s="205"/>
+      <c r="AC8" s="205"/>
       <c r="AD8" s="59"/>
-      <c r="AE8" s="186" t="s">
+      <c r="AE8" s="162" t="s">
         <v>13</v>
       </c>
-      <c r="AF8" s="186"/>
-      <c r="AG8" s="186"/>
-      <c r="AH8" s="186"/>
-      <c r="AI8" s="186"/>
-      <c r="AJ8" s="186"/>
-      <c r="AK8" s="186"/>
-      <c r="AL8" s="179" t="str">
+      <c r="AF8" s="162"/>
+      <c r="AG8" s="162"/>
+      <c r="AH8" s="162"/>
+      <c r="AI8" s="162"/>
+      <c r="AJ8" s="162"/>
+      <c r="AK8" s="162"/>
+      <c r="AL8" s="93" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,7,0))</f>
         <v/>
       </c>
-      <c r="AM8" s="179"/>
-      <c r="AN8" s="179"/>
-      <c r="AO8" s="179"/>
-      <c r="AP8" s="179"/>
-      <c r="AQ8" s="179"/>
-      <c r="AR8" s="179"/>
-      <c r="AS8" s="179"/>
-      <c r="AT8" s="179"/>
-      <c r="AU8" s="179"/>
-      <c r="AV8" s="179"/>
-      <c r="AW8" s="179"/>
-      <c r="AX8" s="179"/>
-      <c r="AY8" s="179"/>
-      <c r="AZ8" s="180"/>
+      <c r="AM8" s="93"/>
+      <c r="AN8" s="93"/>
+      <c r="AO8" s="93"/>
+      <c r="AP8" s="93"/>
+      <c r="AQ8" s="93"/>
+      <c r="AR8" s="93"/>
+      <c r="AS8" s="93"/>
+      <c r="AT8" s="93"/>
+      <c r="AU8" s="93"/>
+      <c r="AV8" s="93"/>
+      <c r="AW8" s="93"/>
+      <c r="AX8" s="93"/>
+      <c r="AY8" s="93"/>
+      <c r="AZ8" s="94"/>
     </row>
     <row r="9" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="172" t="s">
+      <c r="A9" s="202" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="173"/>
-      <c r="C9" s="173"/>
-      <c r="D9" s="173"/>
-      <c r="E9" s="173"/>
-      <c r="F9" s="173"/>
-      <c r="G9" s="177" t="str">
+      <c r="B9" s="203"/>
+      <c r="C9" s="203"/>
+      <c r="D9" s="203"/>
+      <c r="E9" s="203"/>
+      <c r="F9" s="203"/>
+      <c r="G9" s="206" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,8,0))</f>
         <v/>
       </c>
-      <c r="H9" s="178"/>
-      <c r="I9" s="178"/>
-      <c r="J9" s="178"/>
-      <c r="K9" s="178"/>
-      <c r="L9" s="178"/>
-      <c r="M9" s="178"/>
-      <c r="N9" s="178"/>
-      <c r="O9" s="178"/>
-      <c r="P9" s="178"/>
-      <c r="Q9" s="178"/>
-      <c r="R9" s="178"/>
-      <c r="S9" s="178"/>
-      <c r="T9" s="178"/>
-      <c r="U9" s="178"/>
-      <c r="V9" s="178"/>
-      <c r="W9" s="178"/>
-      <c r="X9" s="178"/>
-      <c r="Y9" s="178"/>
-      <c r="Z9" s="178"/>
-      <c r="AA9" s="178"/>
-      <c r="AB9" s="178"/>
-      <c r="AC9" s="178"/>
+      <c r="H9" s="207"/>
+      <c r="I9" s="207"/>
+      <c r="J9" s="207"/>
+      <c r="K9" s="207"/>
+      <c r="L9" s="207"/>
+      <c r="M9" s="207"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="207"/>
+      <c r="P9" s="207"/>
+      <c r="Q9" s="207"/>
+      <c r="R9" s="207"/>
+      <c r="S9" s="207"/>
+      <c r="T9" s="207"/>
+      <c r="U9" s="207"/>
+      <c r="V9" s="207"/>
+      <c r="W9" s="207"/>
+      <c r="X9" s="207"/>
+      <c r="Y9" s="207"/>
+      <c r="Z9" s="207"/>
+      <c r="AA9" s="207"/>
+      <c r="AB9" s="207"/>
+      <c r="AC9" s="207"/>
       <c r="AD9" s="59"/>
-      <c r="AE9" s="170" t="s">
+      <c r="AE9" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="AF9" s="170"/>
-      <c r="AG9" s="170"/>
-      <c r="AH9" s="170"/>
-      <c r="AI9" s="170"/>
-      <c r="AJ9" s="170"/>
-      <c r="AK9" s="170"/>
-      <c r="AL9" s="158" t="str">
+      <c r="AF9" s="106"/>
+      <c r="AG9" s="106"/>
+      <c r="AH9" s="106"/>
+      <c r="AI9" s="106"/>
+      <c r="AJ9" s="106"/>
+      <c r="AK9" s="106"/>
+      <c r="AL9" s="192" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,9,0))</f>
         <v/>
       </c>
-      <c r="AM9" s="159"/>
-      <c r="AN9" s="159"/>
-      <c r="AO9" s="159"/>
-      <c r="AP9" s="159"/>
-      <c r="AQ9" s="159"/>
-      <c r="AR9" s="159"/>
-      <c r="AS9" s="159"/>
-      <c r="AT9" s="159"/>
-      <c r="AU9" s="159"/>
-      <c r="AV9" s="159"/>
-      <c r="AW9" s="159"/>
-      <c r="AX9" s="159"/>
-      <c r="AY9" s="159"/>
-      <c r="AZ9" s="160"/>
+      <c r="AM9" s="193"/>
+      <c r="AN9" s="193"/>
+      <c r="AO9" s="193"/>
+      <c r="AP9" s="193"/>
+      <c r="AQ9" s="193"/>
+      <c r="AR9" s="193"/>
+      <c r="AS9" s="193"/>
+      <c r="AT9" s="193"/>
+      <c r="AU9" s="193"/>
+      <c r="AV9" s="193"/>
+      <c r="AW9" s="193"/>
+      <c r="AX9" s="193"/>
+      <c r="AY9" s="193"/>
+      <c r="AZ9" s="194"/>
     </row>
     <row r="10" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
@@ -5825,48 +5777,48 @@
       <c r="H12" s="59"/>
       <c r="I12" s="59"/>
       <c r="J12" s="59"/>
-      <c r="K12" s="230"/>
-      <c r="L12" s="179"/>
-      <c r="M12" s="179"/>
-      <c r="N12" s="179"/>
-      <c r="O12" s="179"/>
-      <c r="P12" s="179"/>
-      <c r="Q12" s="179"/>
-      <c r="R12" s="179"/>
-      <c r="S12" s="179"/>
-      <c r="T12" s="179"/>
-      <c r="U12" s="179"/>
-      <c r="V12" s="179"/>
-      <c r="W12" s="179"/>
-      <c r="X12" s="179"/>
-      <c r="Y12" s="179"/>
-      <c r="Z12" s="179"/>
-      <c r="AA12" s="179"/>
-      <c r="AB12" s="179"/>
-      <c r="AC12" s="179"/>
-      <c r="AD12" s="179"/>
-      <c r="AE12" s="179"/>
-      <c r="AF12" s="179"/>
-      <c r="AG12" s="179"/>
-      <c r="AH12" s="179"/>
-      <c r="AI12" s="179"/>
-      <c r="AJ12" s="179"/>
-      <c r="AK12" s="179"/>
-      <c r="AL12" s="179"/>
-      <c r="AM12" s="179"/>
-      <c r="AN12" s="179"/>
-      <c r="AO12" s="179"/>
-      <c r="AP12" s="179"/>
-      <c r="AQ12" s="179"/>
-      <c r="AR12" s="179"/>
-      <c r="AS12" s="179"/>
-      <c r="AT12" s="179"/>
-      <c r="AU12" s="179"/>
-      <c r="AV12" s="179"/>
-      <c r="AW12" s="179"/>
-      <c r="AX12" s="179"/>
-      <c r="AY12" s="179"/>
-      <c r="AZ12" s="180"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="93"/>
+      <c r="N12" s="93"/>
+      <c r="O12" s="93"/>
+      <c r="P12" s="93"/>
+      <c r="Q12" s="93"/>
+      <c r="R12" s="93"/>
+      <c r="S12" s="93"/>
+      <c r="T12" s="93"/>
+      <c r="U12" s="93"/>
+      <c r="V12" s="93"/>
+      <c r="W12" s="93"/>
+      <c r="X12" s="93"/>
+      <c r="Y12" s="93"/>
+      <c r="Z12" s="93"/>
+      <c r="AA12" s="93"/>
+      <c r="AB12" s="93"/>
+      <c r="AC12" s="93"/>
+      <c r="AD12" s="93"/>
+      <c r="AE12" s="93"/>
+      <c r="AF12" s="93"/>
+      <c r="AG12" s="93"/>
+      <c r="AH12" s="93"/>
+      <c r="AI12" s="93"/>
+      <c r="AJ12" s="93"/>
+      <c r="AK12" s="93"/>
+      <c r="AL12" s="93"/>
+      <c r="AM12" s="93"/>
+      <c r="AN12" s="93"/>
+      <c r="AO12" s="93"/>
+      <c r="AP12" s="93"/>
+      <c r="AQ12" s="93"/>
+      <c r="AR12" s="93"/>
+      <c r="AS12" s="93"/>
+      <c r="AT12" s="93"/>
+      <c r="AU12" s="93"/>
+      <c r="AV12" s="93"/>
+      <c r="AW12" s="93"/>
+      <c r="AX12" s="93"/>
+      <c r="AY12" s="93"/>
+      <c r="AZ12" s="94"/>
     </row>
     <row r="13" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56" t="s">
@@ -5881,398 +5833,398 @@
       <c r="H13" s="59"/>
       <c r="I13" s="59"/>
       <c r="J13" s="59"/>
-      <c r="K13" s="187"/>
-      <c r="L13" s="187"/>
-      <c r="M13" s="187"/>
-      <c r="N13" s="187"/>
-      <c r="O13" s="187"/>
-      <c r="P13" s="187"/>
-      <c r="Q13" s="187"/>
-      <c r="R13" s="187"/>
-      <c r="S13" s="187"/>
-      <c r="T13" s="187"/>
-      <c r="U13" s="187"/>
-      <c r="V13" s="187"/>
-      <c r="W13" s="187"/>
-      <c r="X13" s="187"/>
-      <c r="Y13" s="187"/>
-      <c r="Z13" s="187"/>
-      <c r="AA13" s="187"/>
-      <c r="AB13" s="187"/>
-      <c r="AC13" s="187"/>
-      <c r="AD13" s="187"/>
-      <c r="AE13" s="187"/>
-      <c r="AF13" s="187"/>
-      <c r="AG13" s="187"/>
-      <c r="AH13" s="187"/>
-      <c r="AI13" s="187"/>
-      <c r="AJ13" s="187"/>
-      <c r="AK13" s="187"/>
-      <c r="AL13" s="187"/>
-      <c r="AM13" s="187"/>
-      <c r="AN13" s="187"/>
-      <c r="AO13" s="187"/>
-      <c r="AP13" s="187"/>
-      <c r="AQ13" s="187"/>
-      <c r="AR13" s="187"/>
-      <c r="AS13" s="187"/>
-      <c r="AT13" s="187"/>
-      <c r="AU13" s="187"/>
-      <c r="AV13" s="187"/>
-      <c r="AW13" s="187"/>
-      <c r="AX13" s="187"/>
-      <c r="AY13" s="187"/>
-      <c r="AZ13" s="188"/>
+      <c r="K13" s="104"/>
+      <c r="L13" s="104"/>
+      <c r="M13" s="104"/>
+      <c r="N13" s="104"/>
+      <c r="O13" s="104"/>
+      <c r="P13" s="104"/>
+      <c r="Q13" s="104"/>
+      <c r="R13" s="104"/>
+      <c r="S13" s="104"/>
+      <c r="T13" s="104"/>
+      <c r="U13" s="104"/>
+      <c r="V13" s="104"/>
+      <c r="W13" s="104"/>
+      <c r="X13" s="104"/>
+      <c r="Y13" s="104"/>
+      <c r="Z13" s="104"/>
+      <c r="AA13" s="104"/>
+      <c r="AB13" s="104"/>
+      <c r="AC13" s="104"/>
+      <c r="AD13" s="104"/>
+      <c r="AE13" s="104"/>
+      <c r="AF13" s="104"/>
+      <c r="AG13" s="104"/>
+      <c r="AH13" s="104"/>
+      <c r="AI13" s="104"/>
+      <c r="AJ13" s="104"/>
+      <c r="AK13" s="104"/>
+      <c r="AL13" s="104"/>
+      <c r="AM13" s="104"/>
+      <c r="AN13" s="104"/>
+      <c r="AO13" s="104"/>
+      <c r="AP13" s="104"/>
+      <c r="AQ13" s="104"/>
+      <c r="AR13" s="104"/>
+      <c r="AS13" s="104"/>
+      <c r="AT13" s="104"/>
+      <c r="AU13" s="104"/>
+      <c r="AV13" s="104"/>
+      <c r="AW13" s="104"/>
+      <c r="AX13" s="104"/>
+      <c r="AY13" s="104"/>
+      <c r="AZ13" s="105"/>
     </row>
     <row r="14" spans="1:60" s="10" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="233"/>
-      <c r="B14" s="234"/>
-      <c r="C14" s="234"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="234"/>
-      <c r="F14" s="234"/>
-      <c r="G14" s="234"/>
-      <c r="H14" s="234"/>
-      <c r="I14" s="234"/>
-      <c r="J14" s="234"/>
-      <c r="K14" s="234"/>
-      <c r="L14" s="234"/>
-      <c r="M14" s="234"/>
-      <c r="N14" s="234"/>
-      <c r="O14" s="234"/>
-      <c r="P14" s="234"/>
-      <c r="Q14" s="234"/>
-      <c r="R14" s="234"/>
-      <c r="S14" s="234"/>
-      <c r="T14" s="234"/>
-      <c r="U14" s="234"/>
-      <c r="V14" s="234"/>
-      <c r="W14" s="234"/>
-      <c r="X14" s="234"/>
-      <c r="Y14" s="234"/>
-      <c r="Z14" s="234"/>
-      <c r="AA14" s="234"/>
-      <c r="AB14" s="234"/>
-      <c r="AC14" s="234"/>
-      <c r="AD14" s="234"/>
-      <c r="AE14" s="234"/>
-      <c r="AF14" s="234"/>
-      <c r="AG14" s="234"/>
-      <c r="AH14" s="234"/>
-      <c r="AI14" s="234"/>
-      <c r="AJ14" s="234"/>
-      <c r="AK14" s="234"/>
-      <c r="AL14" s="234"/>
-      <c r="AM14" s="234"/>
-      <c r="AN14" s="234"/>
-      <c r="AO14" s="234"/>
-      <c r="AP14" s="234"/>
-      <c r="AQ14" s="234"/>
-      <c r="AR14" s="234"/>
-      <c r="AS14" s="234"/>
-      <c r="AT14" s="234"/>
-      <c r="AU14" s="234"/>
-      <c r="AV14" s="234"/>
-      <c r="AW14" s="234"/>
-      <c r="AX14" s="234"/>
-      <c r="AY14" s="234"/>
-      <c r="AZ14" s="235"/>
+      <c r="A14" s="107"/>
+      <c r="B14" s="108"/>
+      <c r="C14" s="108"/>
+      <c r="D14" s="108"/>
+      <c r="E14" s="108"/>
+      <c r="F14" s="108"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="108"/>
+      <c r="I14" s="108"/>
+      <c r="J14" s="108"/>
+      <c r="K14" s="108"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="108"/>
+      <c r="N14" s="108"/>
+      <c r="O14" s="108"/>
+      <c r="P14" s="108"/>
+      <c r="Q14" s="108"/>
+      <c r="R14" s="108"/>
+      <c r="S14" s="108"/>
+      <c r="T14" s="108"/>
+      <c r="U14" s="108"/>
+      <c r="V14" s="108"/>
+      <c r="W14" s="108"/>
+      <c r="X14" s="108"/>
+      <c r="Y14" s="108"/>
+      <c r="Z14" s="108"/>
+      <c r="AA14" s="108"/>
+      <c r="AB14" s="108"/>
+      <c r="AC14" s="108"/>
+      <c r="AD14" s="108"/>
+      <c r="AE14" s="108"/>
+      <c r="AF14" s="108"/>
+      <c r="AG14" s="108"/>
+      <c r="AH14" s="108"/>
+      <c r="AI14" s="108"/>
+      <c r="AJ14" s="108"/>
+      <c r="AK14" s="108"/>
+      <c r="AL14" s="108"/>
+      <c r="AM14" s="108"/>
+      <c r="AN14" s="108"/>
+      <c r="AO14" s="108"/>
+      <c r="AP14" s="108"/>
+      <c r="AQ14" s="108"/>
+      <c r="AR14" s="108"/>
+      <c r="AS14" s="108"/>
+      <c r="AT14" s="108"/>
+      <c r="AU14" s="108"/>
+      <c r="AV14" s="108"/>
+      <c r="AW14" s="108"/>
+      <c r="AX14" s="108"/>
+      <c r="AY14" s="108"/>
+      <c r="AZ14" s="109"/>
       <c r="BC14" s="24"/>
     </row>
     <row r="15" spans="1:60" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="99"/>
-      <c r="B15" s="99"/>
-      <c r="C15" s="99"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="99"/>
-      <c r="G15" s="99"/>
-      <c r="H15" s="99"/>
-      <c r="I15" s="99"/>
-      <c r="J15" s="99"/>
-      <c r="K15" s="99"/>
-      <c r="L15" s="99"/>
-      <c r="M15" s="99"/>
-      <c r="N15" s="99"/>
-      <c r="O15" s="99"/>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="99"/>
-      <c r="R15" s="99"/>
-      <c r="S15" s="99"/>
-      <c r="T15" s="99"/>
-      <c r="U15" s="99"/>
-      <c r="V15" s="99"/>
-      <c r="W15" s="99"/>
-      <c r="X15" s="99"/>
-      <c r="Y15" s="99"/>
-      <c r="Z15" s="99"/>
-      <c r="AA15" s="99"/>
-      <c r="AB15" s="99"/>
-      <c r="AC15" s="99"/>
-      <c r="AD15" s="99"/>
-      <c r="AE15" s="99"/>
-      <c r="AF15" s="99"/>
-      <c r="AG15" s="99"/>
-      <c r="AH15" s="99"/>
-      <c r="AI15" s="99"/>
-      <c r="AJ15" s="99"/>
-      <c r="AK15" s="99"/>
-      <c r="AL15" s="99"/>
-      <c r="AM15" s="99"/>
-      <c r="AN15" s="99"/>
-      <c r="AO15" s="99"/>
-      <c r="AP15" s="99"/>
-      <c r="AQ15" s="99"/>
-      <c r="AR15" s="99"/>
-      <c r="AS15" s="99"/>
-      <c r="AT15" s="99"/>
-      <c r="AU15" s="99"/>
-      <c r="AV15" s="99"/>
-      <c r="AW15" s="99"/>
-      <c r="AX15" s="99"/>
-      <c r="AY15" s="99"/>
-      <c r="AZ15" s="99"/>
+      <c r="A15" s="146"/>
+      <c r="B15" s="146"/>
+      <c r="C15" s="146"/>
+      <c r="D15" s="146"/>
+      <c r="E15" s="146"/>
+      <c r="F15" s="146"/>
+      <c r="G15" s="146"/>
+      <c r="H15" s="146"/>
+      <c r="I15" s="146"/>
+      <c r="J15" s="146"/>
+      <c r="K15" s="146"/>
+      <c r="L15" s="146"/>
+      <c r="M15" s="146"/>
+      <c r="N15" s="146"/>
+      <c r="O15" s="146"/>
+      <c r="P15" s="146"/>
+      <c r="Q15" s="146"/>
+      <c r="R15" s="146"/>
+      <c r="S15" s="146"/>
+      <c r="T15" s="146"/>
+      <c r="U15" s="146"/>
+      <c r="V15" s="146"/>
+      <c r="W15" s="146"/>
+      <c r="X15" s="146"/>
+      <c r="Y15" s="146"/>
+      <c r="Z15" s="146"/>
+      <c r="AA15" s="146"/>
+      <c r="AB15" s="146"/>
+      <c r="AC15" s="146"/>
+      <c r="AD15" s="146"/>
+      <c r="AE15" s="146"/>
+      <c r="AF15" s="146"/>
+      <c r="AG15" s="146"/>
+      <c r="AH15" s="146"/>
+      <c r="AI15" s="146"/>
+      <c r="AJ15" s="146"/>
+      <c r="AK15" s="146"/>
+      <c r="AL15" s="146"/>
+      <c r="AM15" s="146"/>
+      <c r="AN15" s="146"/>
+      <c r="AO15" s="146"/>
+      <c r="AP15" s="146"/>
+      <c r="AQ15" s="146"/>
+      <c r="AR15" s="146"/>
+      <c r="AS15" s="146"/>
+      <c r="AT15" s="146"/>
+      <c r="AU15" s="146"/>
+      <c r="AV15" s="146"/>
+      <c r="AW15" s="146"/>
+      <c r="AX15" s="146"/>
+      <c r="AY15" s="146"/>
+      <c r="AZ15" s="146"/>
     </row>
     <row r="16" spans="1:60" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="236" t="s">
+      <c r="A16" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="237"/>
-      <c r="C16" s="237"/>
-      <c r="D16" s="237"/>
-      <c r="E16" s="237"/>
-      <c r="F16" s="237"/>
-      <c r="G16" s="237"/>
-      <c r="H16" s="237"/>
-      <c r="I16" s="237"/>
-      <c r="J16" s="237"/>
-      <c r="K16" s="237"/>
-      <c r="L16" s="237"/>
-      <c r="M16" s="237"/>
-      <c r="N16" s="237"/>
-      <c r="O16" s="237"/>
-      <c r="P16" s="237"/>
-      <c r="Q16" s="237"/>
-      <c r="R16" s="237"/>
-      <c r="S16" s="237"/>
-      <c r="T16" s="237"/>
-      <c r="U16" s="237"/>
-      <c r="V16" s="237"/>
-      <c r="W16" s="237"/>
-      <c r="X16" s="237"/>
-      <c r="Y16" s="237"/>
-      <c r="Z16" s="237"/>
-      <c r="AA16" s="237"/>
-      <c r="AB16" s="237"/>
-      <c r="AC16" s="237"/>
-      <c r="AD16" s="237"/>
-      <c r="AE16" s="237"/>
-      <c r="AF16" s="237"/>
-      <c r="AG16" s="237"/>
-      <c r="AH16" s="237"/>
-      <c r="AI16" s="237"/>
-      <c r="AJ16" s="237"/>
-      <c r="AK16" s="237"/>
-      <c r="AL16" s="237"/>
-      <c r="AM16" s="237"/>
-      <c r="AN16" s="237"/>
-      <c r="AO16" s="237"/>
-      <c r="AP16" s="237"/>
-      <c r="AQ16" s="237"/>
-      <c r="AR16" s="237"/>
-      <c r="AS16" s="237"/>
-      <c r="AT16" s="237"/>
-      <c r="AU16" s="237"/>
-      <c r="AV16" s="237"/>
-      <c r="AW16" s="237"/>
-      <c r="AX16" s="237"/>
-      <c r="AY16" s="237"/>
-      <c r="AZ16" s="238"/>
-    </row>
-    <row r="17" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="168" t="s">
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="111"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="111"/>
+      <c r="S16" s="111"/>
+      <c r="T16" s="111"/>
+      <c r="U16" s="111"/>
+      <c r="V16" s="111"/>
+      <c r="W16" s="111"/>
+      <c r="X16" s="111"/>
+      <c r="Y16" s="111"/>
+      <c r="Z16" s="111"/>
+      <c r="AA16" s="111"/>
+      <c r="AB16" s="111"/>
+      <c r="AC16" s="111"/>
+      <c r="AD16" s="111"/>
+      <c r="AE16" s="111"/>
+      <c r="AF16" s="111"/>
+      <c r="AG16" s="111"/>
+      <c r="AH16" s="111"/>
+      <c r="AI16" s="111"/>
+      <c r="AJ16" s="111"/>
+      <c r="AK16" s="111"/>
+      <c r="AL16" s="111"/>
+      <c r="AM16" s="111"/>
+      <c r="AN16" s="111"/>
+      <c r="AO16" s="111"/>
+      <c r="AP16" s="111"/>
+      <c r="AQ16" s="111"/>
+      <c r="AR16" s="111"/>
+      <c r="AS16" s="111"/>
+      <c r="AT16" s="111"/>
+      <c r="AU16" s="111"/>
+      <c r="AV16" s="111"/>
+      <c r="AW16" s="111"/>
+      <c r="AX16" s="111"/>
+      <c r="AY16" s="111"/>
+      <c r="AZ16" s="112"/>
+    </row>
+    <row r="17" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="199" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="169"/>
-      <c r="C17" s="169"/>
-      <c r="D17" s="169"/>
-      <c r="E17" s="169"/>
-      <c r="F17" s="169"/>
-      <c r="G17" s="169"/>
-      <c r="H17" s="169"/>
-      <c r="I17" s="169"/>
-      <c r="J17" s="169"/>
-      <c r="K17" s="169"/>
-      <c r="L17" s="169"/>
-      <c r="M17" s="166" t="s">
+      <c r="B17" s="200"/>
+      <c r="C17" s="200"/>
+      <c r="D17" s="200"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="200"/>
+      <c r="G17" s="200"/>
+      <c r="H17" s="200"/>
+      <c r="I17" s="200"/>
+      <c r="J17" s="200"/>
+      <c r="K17" s="200"/>
+      <c r="L17" s="200"/>
+      <c r="M17" s="197" t="s">
         <v>32</v>
       </c>
-      <c r="N17" s="167"/>
-      <c r="O17" s="167"/>
-      <c r="P17" s="167"/>
-      <c r="Q17" s="167"/>
-      <c r="R17" s="163" t="s">
+      <c r="N17" s="198"/>
+      <c r="O17" s="198"/>
+      <c r="P17" s="198"/>
+      <c r="Q17" s="198"/>
+      <c r="R17" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="S17" s="164"/>
-      <c r="T17" s="164"/>
-      <c r="U17" s="164"/>
-      <c r="V17" s="165"/>
-      <c r="W17" s="163" t="s">
+      <c r="S17" s="117"/>
+      <c r="T17" s="117"/>
+      <c r="U17" s="117"/>
+      <c r="V17" s="118"/>
+      <c r="W17" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="X17" s="164"/>
-      <c r="Y17" s="164"/>
-      <c r="Z17" s="164"/>
-      <c r="AA17" s="165"/>
-      <c r="AB17" s="163" t="s">
+      <c r="X17" s="117"/>
+      <c r="Y17" s="117"/>
+      <c r="Z17" s="117"/>
+      <c r="AA17" s="118"/>
+      <c r="AB17" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="AC17" s="164"/>
-      <c r="AD17" s="164"/>
-      <c r="AE17" s="164"/>
-      <c r="AF17" s="165"/>
-      <c r="AG17" s="163" t="s">
+      <c r="AC17" s="117"/>
+      <c r="AD17" s="117"/>
+      <c r="AE17" s="117"/>
+      <c r="AF17" s="118"/>
+      <c r="AG17" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="AH17" s="164"/>
-      <c r="AI17" s="164"/>
-      <c r="AJ17" s="164"/>
-      <c r="AK17" s="165"/>
-      <c r="AL17" s="163" t="s">
+      <c r="AH17" s="117"/>
+      <c r="AI17" s="117"/>
+      <c r="AJ17" s="117"/>
+      <c r="AK17" s="118"/>
+      <c r="AL17" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="AM17" s="164"/>
-      <c r="AN17" s="164"/>
-      <c r="AO17" s="164"/>
-      <c r="AP17" s="165"/>
-      <c r="AQ17" s="163" t="s">
+      <c r="AM17" s="117"/>
+      <c r="AN17" s="117"/>
+      <c r="AO17" s="117"/>
+      <c r="AP17" s="118"/>
+      <c r="AQ17" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="AR17" s="164"/>
-      <c r="AS17" s="164"/>
-      <c r="AT17" s="164"/>
-      <c r="AU17" s="165"/>
-      <c r="AV17" s="239" t="s">
+      <c r="AR17" s="117"/>
+      <c r="AS17" s="117"/>
+      <c r="AT17" s="117"/>
+      <c r="AU17" s="118"/>
+      <c r="AV17" s="113" t="s">
         <v>32</v>
       </c>
-      <c r="AW17" s="240"/>
-      <c r="AX17" s="240"/>
-      <c r="AY17" s="240"/>
-      <c r="AZ17" s="241"/>
+      <c r="AW17" s="114"/>
+      <c r="AX17" s="114"/>
+      <c r="AY17" s="114"/>
+      <c r="AZ17" s="115"/>
     </row>
     <row r="18" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="92" t="s">
+      <c r="A18" s="228" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="93"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="93"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="93"/>
-      <c r="J18" s="93"/>
-      <c r="K18" s="93"/>
-      <c r="L18" s="94"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="90"/>
-      <c r="O18" s="90"/>
-      <c r="P18" s="90"/>
-      <c r="Q18" s="90"/>
-      <c r="R18" s="89"/>
-      <c r="S18" s="90"/>
-      <c r="T18" s="90"/>
-      <c r="U18" s="90"/>
-      <c r="V18" s="90"/>
-      <c r="W18" s="89"/>
-      <c r="X18" s="90"/>
-      <c r="Y18" s="90"/>
-      <c r="Z18" s="90"/>
-      <c r="AA18" s="90"/>
-      <c r="AB18" s="89"/>
-      <c r="AC18" s="90"/>
-      <c r="AD18" s="90"/>
-      <c r="AE18" s="90"/>
-      <c r="AF18" s="90"/>
-      <c r="AG18" s="89"/>
-      <c r="AH18" s="90"/>
-      <c r="AI18" s="90"/>
-      <c r="AJ18" s="90"/>
-      <c r="AK18" s="90"/>
-      <c r="AL18" s="89"/>
-      <c r="AM18" s="90"/>
-      <c r="AN18" s="90"/>
-      <c r="AO18" s="90"/>
-      <c r="AP18" s="90"/>
-      <c r="AQ18" s="89"/>
-      <c r="AR18" s="90"/>
-      <c r="AS18" s="90"/>
-      <c r="AT18" s="90"/>
-      <c r="AU18" s="286"/>
-      <c r="AV18" s="287"/>
-      <c r="AW18" s="288"/>
-      <c r="AX18" s="288"/>
-      <c r="AY18" s="288"/>
-      <c r="AZ18" s="289"/>
+      <c r="B18" s="229"/>
+      <c r="C18" s="229"/>
+      <c r="D18" s="229"/>
+      <c r="E18" s="229"/>
+      <c r="F18" s="229"/>
+      <c r="G18" s="229"/>
+      <c r="H18" s="229"/>
+      <c r="I18" s="229"/>
+      <c r="J18" s="229"/>
+      <c r="K18" s="229"/>
+      <c r="L18" s="230"/>
+      <c r="M18" s="227"/>
+      <c r="N18" s="120"/>
+      <c r="O18" s="120"/>
+      <c r="P18" s="120"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="120"/>
+      <c r="T18" s="120"/>
+      <c r="U18" s="120"/>
+      <c r="V18" s="120"/>
+      <c r="W18" s="119"/>
+      <c r="X18" s="120"/>
+      <c r="Y18" s="120"/>
+      <c r="Z18" s="120"/>
+      <c r="AA18" s="120"/>
+      <c r="AB18" s="119"/>
+      <c r="AC18" s="120"/>
+      <c r="AD18" s="120"/>
+      <c r="AE18" s="120"/>
+      <c r="AF18" s="120"/>
+      <c r="AG18" s="119"/>
+      <c r="AH18" s="120"/>
+      <c r="AI18" s="120"/>
+      <c r="AJ18" s="120"/>
+      <c r="AK18" s="120"/>
+      <c r="AL18" s="119"/>
+      <c r="AM18" s="120"/>
+      <c r="AN18" s="120"/>
+      <c r="AO18" s="120"/>
+      <c r="AP18" s="120"/>
+      <c r="AQ18" s="119"/>
+      <c r="AR18" s="120"/>
+      <c r="AS18" s="120"/>
+      <c r="AT18" s="120"/>
+      <c r="AU18" s="120"/>
+      <c r="AV18" s="121"/>
+      <c r="AW18" s="287"/>
+      <c r="AX18" s="287"/>
+      <c r="AY18" s="287"/>
+      <c r="AZ18" s="288"/>
       <c r="BD18" s="26"/>
     </row>
     <row r="19" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="129" t="s">
+      <c r="A19" s="218" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="130"/>
-      <c r="C19" s="130"/>
-      <c r="D19" s="130"/>
-      <c r="E19" s="130"/>
-      <c r="F19" s="130"/>
-      <c r="G19" s="130"/>
-      <c r="H19" s="130"/>
-      <c r="I19" s="130"/>
-      <c r="J19" s="130"/>
-      <c r="K19" s="130"/>
-      <c r="L19" s="131"/>
-      <c r="M19" s="121"/>
-      <c r="N19" s="96"/>
-      <c r="O19" s="96"/>
-      <c r="P19" s="96"/>
-      <c r="Q19" s="96"/>
-      <c r="R19" s="96"/>
-      <c r="S19" s="96"/>
-      <c r="T19" s="96"/>
-      <c r="U19" s="96"/>
-      <c r="V19" s="96"/>
-      <c r="W19" s="96"/>
-      <c r="X19" s="96"/>
-      <c r="Y19" s="96"/>
-      <c r="Z19" s="96"/>
-      <c r="AA19" s="96"/>
-      <c r="AB19" s="95"/>
-      <c r="AC19" s="96"/>
-      <c r="AD19" s="96"/>
-      <c r="AE19" s="96"/>
-      <c r="AF19" s="96"/>
-      <c r="AG19" s="95"/>
-      <c r="AH19" s="96"/>
-      <c r="AI19" s="96"/>
-      <c r="AJ19" s="96"/>
-      <c r="AK19" s="96"/>
-      <c r="AL19" s="95"/>
-      <c r="AM19" s="96"/>
-      <c r="AN19" s="96"/>
-      <c r="AO19" s="96"/>
-      <c r="AP19" s="96"/>
-      <c r="AQ19" s="95"/>
-      <c r="AR19" s="96"/>
-      <c r="AS19" s="96"/>
-      <c r="AT19" s="96"/>
-      <c r="AU19" s="96"/>
-      <c r="AV19" s="95"/>
-      <c r="AW19" s="96"/>
-      <c r="AX19" s="96"/>
-      <c r="AY19" s="96"/>
-      <c r="AZ19" s="97"/>
+      <c r="B19" s="219"/>
+      <c r="C19" s="219"/>
+      <c r="D19" s="219"/>
+      <c r="E19" s="219"/>
+      <c r="F19" s="219"/>
+      <c r="G19" s="219"/>
+      <c r="H19" s="219"/>
+      <c r="I19" s="219"/>
+      <c r="J19" s="219"/>
+      <c r="K19" s="219"/>
+      <c r="L19" s="220"/>
+      <c r="M19" s="213"/>
+      <c r="N19" s="163"/>
+      <c r="O19" s="163"/>
+      <c r="P19" s="163"/>
+      <c r="Q19" s="163"/>
+      <c r="R19" s="163"/>
+      <c r="S19" s="163"/>
+      <c r="T19" s="163"/>
+      <c r="U19" s="163"/>
+      <c r="V19" s="163"/>
+      <c r="W19" s="163"/>
+      <c r="X19" s="163"/>
+      <c r="Y19" s="163"/>
+      <c r="Z19" s="163"/>
+      <c r="AA19" s="163"/>
+      <c r="AB19" s="210"/>
+      <c r="AC19" s="163"/>
+      <c r="AD19" s="163"/>
+      <c r="AE19" s="163"/>
+      <c r="AF19" s="163"/>
+      <c r="AG19" s="210"/>
+      <c r="AH19" s="163"/>
+      <c r="AI19" s="163"/>
+      <c r="AJ19" s="163"/>
+      <c r="AK19" s="163"/>
+      <c r="AL19" s="210"/>
+      <c r="AM19" s="163"/>
+      <c r="AN19" s="163"/>
+      <c r="AO19" s="163"/>
+      <c r="AP19" s="163"/>
+      <c r="AQ19" s="210"/>
+      <c r="AR19" s="163"/>
+      <c r="AS19" s="163"/>
+      <c r="AT19" s="163"/>
+      <c r="AU19" s="163"/>
+      <c r="AV19" s="210"/>
+      <c r="AW19" s="163"/>
+      <c r="AX19" s="163"/>
+      <c r="AY19" s="163"/>
+      <c r="AZ19" s="231"/>
       <c r="BC19" s="29"/>
       <c r="BD19" s="49"/>
       <c r="BE19" s="30"/>
@@ -6283,60 +6235,60 @@
       <c r="BJ19" s="49"/>
     </row>
     <row r="20" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="132" t="s">
+      <c r="A20" s="221" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="133"/>
-      <c r="C20" s="133"/>
-      <c r="D20" s="133"/>
-      <c r="E20" s="133"/>
-      <c r="F20" s="133"/>
-      <c r="G20" s="133"/>
-      <c r="H20" s="133"/>
-      <c r="I20" s="133"/>
-      <c r="J20" s="133"/>
-      <c r="K20" s="133"/>
-      <c r="L20" s="134"/>
-      <c r="M20" s="122"/>
-      <c r="N20" s="123"/>
-      <c r="O20" s="123"/>
-      <c r="P20" s="123"/>
-      <c r="Q20" s="123"/>
-      <c r="R20" s="123"/>
-      <c r="S20" s="123"/>
-      <c r="T20" s="123"/>
-      <c r="U20" s="123"/>
-      <c r="V20" s="123"/>
-      <c r="W20" s="123"/>
-      <c r="X20" s="123"/>
-      <c r="Y20" s="123"/>
-      <c r="Z20" s="123"/>
-      <c r="AA20" s="123"/>
-      <c r="AB20" s="123"/>
-      <c r="AC20" s="123"/>
-      <c r="AD20" s="123"/>
-      <c r="AE20" s="123"/>
-      <c r="AF20" s="123"/>
-      <c r="AG20" s="123"/>
-      <c r="AH20" s="123"/>
-      <c r="AI20" s="123"/>
-      <c r="AJ20" s="123"/>
-      <c r="AK20" s="123"/>
-      <c r="AL20" s="123"/>
-      <c r="AM20" s="123"/>
-      <c r="AN20" s="123"/>
-      <c r="AO20" s="123"/>
-      <c r="AP20" s="123"/>
-      <c r="AQ20" s="123"/>
-      <c r="AR20" s="123"/>
-      <c r="AS20" s="123"/>
-      <c r="AT20" s="123"/>
-      <c r="AU20" s="123"/>
-      <c r="AV20" s="123"/>
-      <c r="AW20" s="123"/>
-      <c r="AX20" s="123"/>
-      <c r="AY20" s="123"/>
-      <c r="AZ20" s="192"/>
+      <c r="B20" s="222"/>
+      <c r="C20" s="222"/>
+      <c r="D20" s="222"/>
+      <c r="E20" s="222"/>
+      <c r="F20" s="222"/>
+      <c r="G20" s="222"/>
+      <c r="H20" s="222"/>
+      <c r="I20" s="222"/>
+      <c r="J20" s="222"/>
+      <c r="K20" s="222"/>
+      <c r="L20" s="223"/>
+      <c r="M20" s="214"/>
+      <c r="N20" s="164"/>
+      <c r="O20" s="164"/>
+      <c r="P20" s="164"/>
+      <c r="Q20" s="164"/>
+      <c r="R20" s="164"/>
+      <c r="S20" s="164"/>
+      <c r="T20" s="164"/>
+      <c r="U20" s="164"/>
+      <c r="V20" s="164"/>
+      <c r="W20" s="164"/>
+      <c r="X20" s="164"/>
+      <c r="Y20" s="164"/>
+      <c r="Z20" s="164"/>
+      <c r="AA20" s="164"/>
+      <c r="AB20" s="164"/>
+      <c r="AC20" s="164"/>
+      <c r="AD20" s="164"/>
+      <c r="AE20" s="164"/>
+      <c r="AF20" s="164"/>
+      <c r="AG20" s="164"/>
+      <c r="AH20" s="164"/>
+      <c r="AI20" s="164"/>
+      <c r="AJ20" s="164"/>
+      <c r="AK20" s="164"/>
+      <c r="AL20" s="164"/>
+      <c r="AM20" s="164"/>
+      <c r="AN20" s="164"/>
+      <c r="AO20" s="164"/>
+      <c r="AP20" s="164"/>
+      <c r="AQ20" s="164"/>
+      <c r="AR20" s="164"/>
+      <c r="AS20" s="164"/>
+      <c r="AT20" s="164"/>
+      <c r="AU20" s="164"/>
+      <c r="AV20" s="164"/>
+      <c r="AW20" s="164"/>
+      <c r="AX20" s="164"/>
+      <c r="AY20" s="164"/>
+      <c r="AZ20" s="166"/>
       <c r="BC20" s="29"/>
       <c r="BD20" s="31"/>
       <c r="BE20" s="31"/>
@@ -6347,63 +6299,63 @@
       <c r="BJ20" s="31"/>
     </row>
     <row r="21" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="132" t="s">
+      <c r="A21" s="221" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="133"/>
-      <c r="C21" s="133"/>
-      <c r="D21" s="133"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="133"/>
-      <c r="I21" s="133"/>
-      <c r="J21" s="133"/>
-      <c r="K21" s="133"/>
-      <c r="L21" s="134"/>
-      <c r="M21" s="124"/>
-      <c r="N21" s="115"/>
-      <c r="O21" s="115"/>
-      <c r="P21" s="115"/>
-      <c r="Q21" s="115"/>
-      <c r="R21" s="115"/>
-      <c r="S21" s="115"/>
-      <c r="T21" s="115"/>
-      <c r="U21" s="115"/>
-      <c r="V21" s="115"/>
-      <c r="W21" s="115"/>
-      <c r="X21" s="115"/>
-      <c r="Y21" s="115"/>
-      <c r="Z21" s="115"/>
-      <c r="AA21" s="115"/>
-      <c r="AB21" s="115"/>
-      <c r="AC21" s="115"/>
-      <c r="AD21" s="115"/>
-      <c r="AE21" s="115"/>
-      <c r="AF21" s="115"/>
-      <c r="AG21" s="115"/>
-      <c r="AH21" s="115"/>
-      <c r="AI21" s="115"/>
-      <c r="AJ21" s="115"/>
-      <c r="AK21" s="115"/>
-      <c r="AL21" s="115"/>
-      <c r="AM21" s="115"/>
-      <c r="AN21" s="115"/>
-      <c r="AO21" s="115"/>
-      <c r="AP21" s="115"/>
-      <c r="AQ21" s="115"/>
-      <c r="AR21" s="115"/>
-      <c r="AS21" s="115"/>
-      <c r="AT21" s="115"/>
-      <c r="AU21" s="115"/>
-      <c r="AV21" s="115"/>
-      <c r="AW21" s="115"/>
-      <c r="AX21" s="115"/>
-      <c r="AY21" s="115"/>
-      <c r="AZ21" s="116"/>
+      <c r="B21" s="222"/>
+      <c r="C21" s="222"/>
+      <c r="D21" s="222"/>
+      <c r="E21" s="222"/>
+      <c r="F21" s="222"/>
+      <c r="G21" s="222"/>
+      <c r="H21" s="222"/>
+      <c r="I21" s="222"/>
+      <c r="J21" s="222"/>
+      <c r="K21" s="222"/>
+      <c r="L21" s="223"/>
+      <c r="M21" s="215"/>
+      <c r="N21" s="165"/>
+      <c r="O21" s="165"/>
+      <c r="P21" s="165"/>
+      <c r="Q21" s="165"/>
+      <c r="R21" s="165"/>
+      <c r="S21" s="165"/>
+      <c r="T21" s="165"/>
+      <c r="U21" s="165"/>
+      <c r="V21" s="165"/>
+      <c r="W21" s="165"/>
+      <c r="X21" s="165"/>
+      <c r="Y21" s="165"/>
+      <c r="Z21" s="165"/>
+      <c r="AA21" s="165"/>
+      <c r="AB21" s="165"/>
+      <c r="AC21" s="165"/>
+      <c r="AD21" s="165"/>
+      <c r="AE21" s="165"/>
+      <c r="AF21" s="165"/>
+      <c r="AG21" s="165"/>
+      <c r="AH21" s="165"/>
+      <c r="AI21" s="165"/>
+      <c r="AJ21" s="165"/>
+      <c r="AK21" s="165"/>
+      <c r="AL21" s="165"/>
+      <c r="AM21" s="165"/>
+      <c r="AN21" s="165"/>
+      <c r="AO21" s="165"/>
+      <c r="AP21" s="165"/>
+      <c r="AQ21" s="165"/>
+      <c r="AR21" s="165"/>
+      <c r="AS21" s="165"/>
+      <c r="AT21" s="165"/>
+      <c r="AU21" s="165"/>
+      <c r="AV21" s="165"/>
+      <c r="AW21" s="165"/>
+      <c r="AX21" s="165"/>
+      <c r="AY21" s="165"/>
+      <c r="AZ21" s="167"/>
       <c r="BC21" s="29"/>
-      <c r="BD21" s="229"/>
-      <c r="BE21" s="229"/>
+      <c r="BD21" s="90"/>
+      <c r="BE21" s="90"/>
       <c r="BF21" s="29"/>
       <c r="BG21" s="29"/>
       <c r="BH21" s="29"/>
@@ -6411,84 +6363,84 @@
       <c r="BJ21" s="29"/>
     </row>
     <row r="22" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="132" t="s">
+      <c r="A22" s="221" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="133"/>
-      <c r="C22" s="133"/>
-      <c r="D22" s="133"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="133"/>
-      <c r="H22" s="133"/>
-      <c r="I22" s="133"/>
-      <c r="J22" s="133"/>
-      <c r="K22" s="133"/>
-      <c r="L22" s="134"/>
-      <c r="M22" s="124" t="str">
+      <c r="B22" s="222"/>
+      <c r="C22" s="222"/>
+      <c r="D22" s="222"/>
+      <c r="E22" s="222"/>
+      <c r="F22" s="222"/>
+      <c r="G22" s="222"/>
+      <c r="H22" s="222"/>
+      <c r="I22" s="222"/>
+      <c r="J22" s="222"/>
+      <c r="K22" s="222"/>
+      <c r="L22" s="223"/>
+      <c r="M22" s="215" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="N22" s="115"/>
-      <c r="O22" s="115"/>
-      <c r="P22" s="115"/>
-      <c r="Q22" s="115"/>
-      <c r="R22" s="115" t="str">
+      <c r="N22" s="165"/>
+      <c r="O22" s="165"/>
+      <c r="P22" s="165"/>
+      <c r="Q22" s="165"/>
+      <c r="R22" s="165" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="S22" s="115"/>
-      <c r="T22" s="115"/>
-      <c r="U22" s="115"/>
-      <c r="V22" s="115"/>
-      <c r="W22" s="115" t="str">
+      <c r="S22" s="165"/>
+      <c r="T22" s="165"/>
+      <c r="U22" s="165"/>
+      <c r="V22" s="165"/>
+      <c r="W22" s="165" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="X22" s="115"/>
-      <c r="Y22" s="115"/>
-      <c r="Z22" s="115"/>
-      <c r="AA22" s="115"/>
-      <c r="AB22" s="115" t="str">
+      <c r="X22" s="165"/>
+      <c r="Y22" s="165"/>
+      <c r="Z22" s="165"/>
+      <c r="AA22" s="165"/>
+      <c r="AB22" s="165" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AC22" s="115"/>
-      <c r="AD22" s="115"/>
-      <c r="AE22" s="115"/>
-      <c r="AF22" s="115"/>
-      <c r="AG22" s="115" t="str">
+      <c r="AC22" s="165"/>
+      <c r="AD22" s="165"/>
+      <c r="AE22" s="165"/>
+      <c r="AF22" s="165"/>
+      <c r="AG22" s="165" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AH22" s="115"/>
-      <c r="AI22" s="115"/>
-      <c r="AJ22" s="115"/>
-      <c r="AK22" s="115"/>
-      <c r="AL22" s="115" t="str">
+      <c r="AH22" s="165"/>
+      <c r="AI22" s="165"/>
+      <c r="AJ22" s="165"/>
+      <c r="AK22" s="165"/>
+      <c r="AL22" s="165" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AM22" s="115"/>
-      <c r="AN22" s="115"/>
-      <c r="AO22" s="115"/>
-      <c r="AP22" s="115"/>
-      <c r="AQ22" s="115" t="str">
+      <c r="AM22" s="165"/>
+      <c r="AN22" s="165"/>
+      <c r="AO22" s="165"/>
+      <c r="AP22" s="165"/>
+      <c r="AQ22" s="165" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AR22" s="115"/>
-      <c r="AS22" s="115"/>
-      <c r="AT22" s="115"/>
-      <c r="AU22" s="115"/>
-      <c r="AV22" s="115" t="str">
+      <c r="AR22" s="165"/>
+      <c r="AS22" s="165"/>
+      <c r="AT22" s="165"/>
+      <c r="AU22" s="165"/>
+      <c r="AV22" s="165" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AW22" s="115"/>
-      <c r="AX22" s="115"/>
-      <c r="AY22" s="115"/>
-      <c r="AZ22" s="116"/>
+      <c r="AW22" s="165"/>
+      <c r="AX22" s="165"/>
+      <c r="AY22" s="165"/>
+      <c r="AZ22" s="167"/>
       <c r="BC22" s="29"/>
       <c r="BD22" s="31"/>
       <c r="BE22" s="31"/>
@@ -6499,87 +6451,87 @@
       <c r="BJ22" s="29"/>
     </row>
     <row r="23" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="132" t="s">
+      <c r="A23" s="221" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="133"/>
-      <c r="C23" s="133"/>
-      <c r="D23" s="133"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="133"/>
-      <c r="I23" s="133"/>
-      <c r="J23" s="133"/>
-      <c r="K23" s="133"/>
-      <c r="L23" s="134"/>
-      <c r="M23" s="124" t="str">
+      <c r="B23" s="222"/>
+      <c r="C23" s="222"/>
+      <c r="D23" s="222"/>
+      <c r="E23" s="222"/>
+      <c r="F23" s="222"/>
+      <c r="G23" s="222"/>
+      <c r="H23" s="222"/>
+      <c r="I23" s="222"/>
+      <c r="J23" s="222"/>
+      <c r="K23" s="222"/>
+      <c r="L23" s="223"/>
+      <c r="M23" s="215" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="N23" s="115"/>
-      <c r="O23" s="115"/>
-      <c r="P23" s="115"/>
-      <c r="Q23" s="115"/>
-      <c r="R23" s="115" t="str">
+      <c r="N23" s="165"/>
+      <c r="O23" s="165"/>
+      <c r="P23" s="165"/>
+      <c r="Q23" s="165"/>
+      <c r="R23" s="165" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="S23" s="115"/>
-      <c r="T23" s="115"/>
-      <c r="U23" s="115"/>
-      <c r="V23" s="115"/>
-      <c r="W23" s="115" t="str">
+      <c r="S23" s="165"/>
+      <c r="T23" s="165"/>
+      <c r="U23" s="165"/>
+      <c r="V23" s="165"/>
+      <c r="W23" s="165" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="X23" s="115"/>
-      <c r="Y23" s="115"/>
-      <c r="Z23" s="115"/>
-      <c r="AA23" s="115"/>
-      <c r="AB23" s="115" t="str">
+      <c r="X23" s="165"/>
+      <c r="Y23" s="165"/>
+      <c r="Z23" s="165"/>
+      <c r="AA23" s="165"/>
+      <c r="AB23" s="165" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AC23" s="115"/>
-      <c r="AD23" s="115"/>
-      <c r="AE23" s="115"/>
-      <c r="AF23" s="115"/>
-      <c r="AG23" s="115" t="str">
+      <c r="AC23" s="165"/>
+      <c r="AD23" s="165"/>
+      <c r="AE23" s="165"/>
+      <c r="AF23" s="165"/>
+      <c r="AG23" s="165" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AH23" s="115"/>
-      <c r="AI23" s="115"/>
-      <c r="AJ23" s="115"/>
-      <c r="AK23" s="115"/>
-      <c r="AL23" s="115" t="str">
+      <c r="AH23" s="165"/>
+      <c r="AI23" s="165"/>
+      <c r="AJ23" s="165"/>
+      <c r="AK23" s="165"/>
+      <c r="AL23" s="165" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AM23" s="115"/>
-      <c r="AN23" s="115"/>
-      <c r="AO23" s="115"/>
-      <c r="AP23" s="115"/>
-      <c r="AQ23" s="115" t="str">
+      <c r="AM23" s="165"/>
+      <c r="AN23" s="165"/>
+      <c r="AO23" s="165"/>
+      <c r="AP23" s="165"/>
+      <c r="AQ23" s="165" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AR23" s="115"/>
-      <c r="AS23" s="115"/>
-      <c r="AT23" s="115"/>
-      <c r="AU23" s="115"/>
-      <c r="AV23" s="115" t="str">
+      <c r="AR23" s="165"/>
+      <c r="AS23" s="165"/>
+      <c r="AT23" s="165"/>
+      <c r="AU23" s="165"/>
+      <c r="AV23" s="165" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AW23" s="115"/>
-      <c r="AX23" s="115"/>
-      <c r="AY23" s="115"/>
-      <c r="AZ23" s="116"/>
+      <c r="AW23" s="165"/>
+      <c r="AX23" s="165"/>
+      <c r="AY23" s="165"/>
+      <c r="AZ23" s="167"/>
       <c r="BC23" s="32"/>
-      <c r="BD23" s="229"/>
-      <c r="BE23" s="229"/>
+      <c r="BD23" s="90"/>
+      <c r="BE23" s="90"/>
       <c r="BF23" s="32"/>
       <c r="BG23" s="32"/>
       <c r="BH23" s="32"/>
@@ -6587,84 +6539,84 @@
       <c r="BJ23" s="32"/>
     </row>
     <row r="24" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="132" t="s">
+      <c r="A24" s="221" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="133"/>
-      <c r="C24" s="133"/>
-      <c r="D24" s="133"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="133"/>
-      <c r="I24" s="133"/>
-      <c r="J24" s="133"/>
-      <c r="K24" s="133"/>
-      <c r="L24" s="134"/>
-      <c r="M24" s="125" t="str">
+      <c r="B24" s="222"/>
+      <c r="C24" s="222"/>
+      <c r="D24" s="222"/>
+      <c r="E24" s="222"/>
+      <c r="F24" s="222"/>
+      <c r="G24" s="222"/>
+      <c r="H24" s="222"/>
+      <c r="I24" s="222"/>
+      <c r="J24" s="222"/>
+      <c r="K24" s="222"/>
+      <c r="L24" s="223"/>
+      <c r="M24" s="216" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="N24" s="126"/>
-      <c r="O24" s="126"/>
-      <c r="P24" s="126"/>
-      <c r="Q24" s="126"/>
-      <c r="R24" s="126" t="str">
+      <c r="N24" s="158"/>
+      <c r="O24" s="158"/>
+      <c r="P24" s="158"/>
+      <c r="Q24" s="158"/>
+      <c r="R24" s="158" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="S24" s="126"/>
-      <c r="T24" s="126"/>
-      <c r="U24" s="126"/>
-      <c r="V24" s="126"/>
-      <c r="W24" s="126" t="str">
+      <c r="S24" s="158"/>
+      <c r="T24" s="158"/>
+      <c r="U24" s="158"/>
+      <c r="V24" s="158"/>
+      <c r="W24" s="158" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="X24" s="126"/>
-      <c r="Y24" s="126"/>
-      <c r="Z24" s="126"/>
-      <c r="AA24" s="126"/>
-      <c r="AB24" s="126" t="str">
+      <c r="X24" s="158"/>
+      <c r="Y24" s="158"/>
+      <c r="Z24" s="158"/>
+      <c r="AA24" s="158"/>
+      <c r="AB24" s="158" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AC24" s="126"/>
-      <c r="AD24" s="126"/>
-      <c r="AE24" s="126"/>
-      <c r="AF24" s="126"/>
-      <c r="AG24" s="126" t="str">
+      <c r="AC24" s="158"/>
+      <c r="AD24" s="158"/>
+      <c r="AE24" s="158"/>
+      <c r="AF24" s="158"/>
+      <c r="AG24" s="158" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AH24" s="126"/>
-      <c r="AI24" s="126"/>
-      <c r="AJ24" s="126"/>
-      <c r="AK24" s="126"/>
-      <c r="AL24" s="126" t="str">
+      <c r="AH24" s="158"/>
+      <c r="AI24" s="158"/>
+      <c r="AJ24" s="158"/>
+      <c r="AK24" s="158"/>
+      <c r="AL24" s="158" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AM24" s="126"/>
-      <c r="AN24" s="126"/>
-      <c r="AO24" s="126"/>
-      <c r="AP24" s="126"/>
-      <c r="AQ24" s="126" t="str">
+      <c r="AM24" s="158"/>
+      <c r="AN24" s="158"/>
+      <c r="AO24" s="158"/>
+      <c r="AP24" s="158"/>
+      <c r="AQ24" s="158" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AR24" s="126"/>
-      <c r="AS24" s="126"/>
-      <c r="AT24" s="126"/>
-      <c r="AU24" s="126"/>
-      <c r="AV24" s="126" t="str">
+      <c r="AR24" s="158"/>
+      <c r="AS24" s="158"/>
+      <c r="AT24" s="158"/>
+      <c r="AU24" s="158"/>
+      <c r="AV24" s="158" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AW24" s="126"/>
-      <c r="AX24" s="126"/>
-      <c r="AY24" s="126"/>
-      <c r="AZ24" s="193"/>
+      <c r="AW24" s="158"/>
+      <c r="AX24" s="158"/>
+      <c r="AY24" s="158"/>
+      <c r="AZ24" s="159"/>
       <c r="BC24" s="29"/>
       <c r="BD24" s="31"/>
       <c r="BE24" s="31"/>
@@ -6675,87 +6627,87 @@
       <c r="BJ24" s="29"/>
     </row>
     <row r="25" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="111" t="s">
+      <c r="A25" s="224" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="112"/>
-      <c r="C25" s="112"/>
-      <c r="D25" s="112"/>
-      <c r="E25" s="112"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="112"/>
-      <c r="H25" s="112"/>
-      <c r="I25" s="112"/>
-      <c r="J25" s="112"/>
-      <c r="K25" s="112"/>
-      <c r="L25" s="135"/>
-      <c r="M25" s="127" t="str">
+      <c r="B25" s="225"/>
+      <c r="C25" s="225"/>
+      <c r="D25" s="225"/>
+      <c r="E25" s="225"/>
+      <c r="F25" s="225"/>
+      <c r="G25" s="225"/>
+      <c r="H25" s="225"/>
+      <c r="I25" s="225"/>
+      <c r="J25" s="225"/>
+      <c r="K25" s="225"/>
+      <c r="L25" s="226"/>
+      <c r="M25" s="217" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="N25" s="128"/>
-      <c r="O25" s="128"/>
-      <c r="P25" s="128"/>
-      <c r="Q25" s="128"/>
-      <c r="R25" s="128" t="str">
+      <c r="N25" s="157"/>
+      <c r="O25" s="157"/>
+      <c r="P25" s="157"/>
+      <c r="Q25" s="157"/>
+      <c r="R25" s="157" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="S25" s="128"/>
-      <c r="T25" s="128"/>
-      <c r="U25" s="128"/>
-      <c r="V25" s="128"/>
-      <c r="W25" s="128" t="str">
+      <c r="S25" s="157"/>
+      <c r="T25" s="157"/>
+      <c r="U25" s="157"/>
+      <c r="V25" s="157"/>
+      <c r="W25" s="157" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="X25" s="128"/>
-      <c r="Y25" s="128"/>
-      <c r="Z25" s="128"/>
-      <c r="AA25" s="128"/>
-      <c r="AB25" s="128" t="str">
+      <c r="X25" s="157"/>
+      <c r="Y25" s="157"/>
+      <c r="Z25" s="157"/>
+      <c r="AA25" s="157"/>
+      <c r="AB25" s="157" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AC25" s="128"/>
-      <c r="AD25" s="128"/>
-      <c r="AE25" s="128"/>
-      <c r="AF25" s="128"/>
-      <c r="AG25" s="128" t="str">
+      <c r="AC25" s="157"/>
+      <c r="AD25" s="157"/>
+      <c r="AE25" s="157"/>
+      <c r="AF25" s="157"/>
+      <c r="AG25" s="157" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AH25" s="128"/>
-      <c r="AI25" s="128"/>
-      <c r="AJ25" s="128"/>
-      <c r="AK25" s="128"/>
-      <c r="AL25" s="128" t="str">
+      <c r="AH25" s="157"/>
+      <c r="AI25" s="157"/>
+      <c r="AJ25" s="157"/>
+      <c r="AK25" s="157"/>
+      <c r="AL25" s="157" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AM25" s="128"/>
-      <c r="AN25" s="128"/>
-      <c r="AO25" s="128"/>
-      <c r="AP25" s="128"/>
-      <c r="AQ25" s="128" t="str">
+      <c r="AM25" s="157"/>
+      <c r="AN25" s="157"/>
+      <c r="AO25" s="157"/>
+      <c r="AP25" s="157"/>
+      <c r="AQ25" s="157" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AR25" s="128"/>
-      <c r="AS25" s="128"/>
-      <c r="AT25" s="128"/>
-      <c r="AU25" s="128"/>
-      <c r="AV25" s="128" t="str">
+      <c r="AR25" s="157"/>
+      <c r="AS25" s="157"/>
+      <c r="AT25" s="157"/>
+      <c r="AU25" s="157"/>
+      <c r="AV25" s="157" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AW25" s="128"/>
-      <c r="AX25" s="128"/>
-      <c r="AY25" s="128"/>
-      <c r="AZ25" s="194"/>
+      <c r="AW25" s="157"/>
+      <c r="AX25" s="157"/>
+      <c r="AY25" s="157"/>
+      <c r="AZ25" s="160"/>
       <c r="BC25" s="29"/>
-      <c r="BD25" s="229"/>
-      <c r="BE25" s="229"/>
+      <c r="BD25" s="90"/>
+      <c r="BE25" s="90"/>
       <c r="BF25" s="29"/>
       <c r="BG25" s="29"/>
       <c r="BH25" s="29"/>
@@ -6763,1150 +6715,1150 @@
       <c r="BJ25" s="29"/>
     </row>
     <row r="26" spans="1:62" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="99"/>
-      <c r="B26" s="99"/>
-      <c r="C26" s="99"/>
-      <c r="D26" s="99"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="99"/>
-      <c r="G26" s="99"/>
-      <c r="H26" s="99"/>
-      <c r="I26" s="99"/>
-      <c r="J26" s="99"/>
-      <c r="K26" s="99"/>
-      <c r="L26" s="99"/>
-      <c r="M26" s="99"/>
-      <c r="N26" s="99"/>
-      <c r="O26" s="99"/>
-      <c r="P26" s="99"/>
-      <c r="Q26" s="99"/>
-      <c r="R26" s="99"/>
-      <c r="S26" s="99"/>
-      <c r="T26" s="99"/>
-      <c r="U26" s="99"/>
-      <c r="V26" s="99"/>
-      <c r="W26" s="99"/>
-      <c r="X26" s="99"/>
-      <c r="Y26" s="99"/>
-      <c r="Z26" s="99"/>
-      <c r="AA26" s="99"/>
-      <c r="AB26" s="99"/>
-      <c r="AC26" s="99"/>
-      <c r="AD26" s="99"/>
-      <c r="AE26" s="99"/>
-      <c r="AF26" s="99"/>
-      <c r="AG26" s="99"/>
-      <c r="AH26" s="99"/>
-      <c r="AI26" s="99"/>
-      <c r="AJ26" s="99"/>
-      <c r="AK26" s="99"/>
-      <c r="AL26" s="99"/>
-      <c r="AM26" s="99"/>
-      <c r="AN26" s="99"/>
-      <c r="AO26" s="99"/>
-      <c r="AP26" s="99"/>
-      <c r="AQ26" s="99"/>
-      <c r="AR26" s="99"/>
-      <c r="AS26" s="99"/>
-      <c r="AT26" s="99"/>
-      <c r="AU26" s="99"/>
-      <c r="AV26" s="99"/>
-      <c r="AW26" s="99"/>
-      <c r="AX26" s="99"/>
-      <c r="AY26" s="99"/>
-      <c r="AZ26" s="99"/>
+      <c r="A26" s="146"/>
+      <c r="B26" s="146"/>
+      <c r="C26" s="146"/>
+      <c r="D26" s="146"/>
+      <c r="E26" s="146"/>
+      <c r="F26" s="146"/>
+      <c r="G26" s="146"/>
+      <c r="H26" s="146"/>
+      <c r="I26" s="146"/>
+      <c r="J26" s="146"/>
+      <c r="K26" s="146"/>
+      <c r="L26" s="146"/>
+      <c r="M26" s="146"/>
+      <c r="N26" s="146"/>
+      <c r="O26" s="146"/>
+      <c r="P26" s="146"/>
+      <c r="Q26" s="146"/>
+      <c r="R26" s="146"/>
+      <c r="S26" s="146"/>
+      <c r="T26" s="146"/>
+      <c r="U26" s="146"/>
+      <c r="V26" s="146"/>
+      <c r="W26" s="146"/>
+      <c r="X26" s="146"/>
+      <c r="Y26" s="146"/>
+      <c r="Z26" s="146"/>
+      <c r="AA26" s="146"/>
+      <c r="AB26" s="146"/>
+      <c r="AC26" s="146"/>
+      <c r="AD26" s="146"/>
+      <c r="AE26" s="146"/>
+      <c r="AF26" s="146"/>
+      <c r="AG26" s="146"/>
+      <c r="AH26" s="146"/>
+      <c r="AI26" s="146"/>
+      <c r="AJ26" s="146"/>
+      <c r="AK26" s="146"/>
+      <c r="AL26" s="146"/>
+      <c r="AM26" s="146"/>
+      <c r="AN26" s="146"/>
+      <c r="AO26" s="146"/>
+      <c r="AP26" s="146"/>
+      <c r="AQ26" s="146"/>
+      <c r="AR26" s="146"/>
+      <c r="AS26" s="146"/>
+      <c r="AT26" s="146"/>
+      <c r="AU26" s="146"/>
+      <c r="AV26" s="146"/>
+      <c r="AW26" s="146"/>
+      <c r="AX26" s="146"/>
+      <c r="AY26" s="146"/>
+      <c r="AZ26" s="146"/>
     </row>
     <row r="27" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="100" t="s">
+      <c r="A27" s="189" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="101"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="101"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="101"/>
-      <c r="H27" s="101"/>
-      <c r="I27" s="101"/>
-      <c r="J27" s="101"/>
-      <c r="K27" s="101"/>
-      <c r="L27" s="101"/>
-      <c r="M27" s="101"/>
-      <c r="N27" s="101"/>
-      <c r="O27" s="101"/>
-      <c r="P27" s="101"/>
-      <c r="Q27" s="101"/>
-      <c r="R27" s="101"/>
-      <c r="S27" s="101"/>
-      <c r="T27" s="101"/>
-      <c r="U27" s="101"/>
-      <c r="V27" s="101"/>
-      <c r="W27" s="101"/>
-      <c r="X27" s="101"/>
-      <c r="Y27" s="101"/>
-      <c r="Z27" s="101"/>
-      <c r="AA27" s="101"/>
-      <c r="AB27" s="101"/>
-      <c r="AC27" s="101"/>
-      <c r="AD27" s="101"/>
-      <c r="AE27" s="101"/>
-      <c r="AF27" s="101"/>
-      <c r="AG27" s="101"/>
-      <c r="AH27" s="101"/>
-      <c r="AI27" s="101"/>
-      <c r="AJ27" s="101"/>
-      <c r="AK27" s="101"/>
-      <c r="AL27" s="101"/>
-      <c r="AM27" s="101"/>
-      <c r="AN27" s="101"/>
-      <c r="AO27" s="101"/>
-      <c r="AP27" s="101"/>
-      <c r="AQ27" s="101"/>
-      <c r="AR27" s="101"/>
-      <c r="AS27" s="101"/>
-      <c r="AT27" s="101"/>
-      <c r="AU27" s="101"/>
-      <c r="AV27" s="101"/>
-      <c r="AW27" s="101"/>
-      <c r="AX27" s="101"/>
-      <c r="AY27" s="101"/>
-      <c r="AZ27" s="102"/>
+      <c r="B27" s="190"/>
+      <c r="C27" s="190"/>
+      <c r="D27" s="190"/>
+      <c r="E27" s="190"/>
+      <c r="F27" s="190"/>
+      <c r="G27" s="190"/>
+      <c r="H27" s="190"/>
+      <c r="I27" s="190"/>
+      <c r="J27" s="190"/>
+      <c r="K27" s="190"/>
+      <c r="L27" s="190"/>
+      <c r="M27" s="190"/>
+      <c r="N27" s="190"/>
+      <c r="O27" s="190"/>
+      <c r="P27" s="190"/>
+      <c r="Q27" s="190"/>
+      <c r="R27" s="190"/>
+      <c r="S27" s="190"/>
+      <c r="T27" s="190"/>
+      <c r="U27" s="190"/>
+      <c r="V27" s="190"/>
+      <c r="W27" s="190"/>
+      <c r="X27" s="190"/>
+      <c r="Y27" s="190"/>
+      <c r="Z27" s="190"/>
+      <c r="AA27" s="190"/>
+      <c r="AB27" s="190"/>
+      <c r="AC27" s="190"/>
+      <c r="AD27" s="190"/>
+      <c r="AE27" s="190"/>
+      <c r="AF27" s="190"/>
+      <c r="AG27" s="190"/>
+      <c r="AH27" s="190"/>
+      <c r="AI27" s="190"/>
+      <c r="AJ27" s="190"/>
+      <c r="AK27" s="190"/>
+      <c r="AL27" s="190"/>
+      <c r="AM27" s="190"/>
+      <c r="AN27" s="190"/>
+      <c r="AO27" s="190"/>
+      <c r="AP27" s="190"/>
+      <c r="AQ27" s="190"/>
+      <c r="AR27" s="190"/>
+      <c r="AS27" s="190"/>
+      <c r="AT27" s="190"/>
+      <c r="AU27" s="190"/>
+      <c r="AV27" s="190"/>
+      <c r="AW27" s="190"/>
+      <c r="AX27" s="190"/>
+      <c r="AY27" s="190"/>
+      <c r="AZ27" s="191"/>
     </row>
     <row r="28" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="103" t="s">
+      <c r="A28" s="233" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="104"/>
-      <c r="C28" s="104"/>
-      <c r="D28" s="104"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="104"/>
-      <c r="I28" s="104"/>
-      <c r="J28" s="104"/>
-      <c r="K28" s="104"/>
-      <c r="L28" s="104"/>
-      <c r="M28" s="104"/>
-      <c r="N28" s="104"/>
-      <c r="O28" s="104"/>
-      <c r="P28" s="104"/>
-      <c r="Q28" s="104"/>
-      <c r="R28" s="104"/>
-      <c r="S28" s="104"/>
-      <c r="T28" s="105" t="s">
+      <c r="B28" s="234"/>
+      <c r="C28" s="234"/>
+      <c r="D28" s="234"/>
+      <c r="E28" s="234"/>
+      <c r="F28" s="234"/>
+      <c r="G28" s="234"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="234"/>
+      <c r="J28" s="234"/>
+      <c r="K28" s="234"/>
+      <c r="L28" s="234"/>
+      <c r="M28" s="234"/>
+      <c r="N28" s="234"/>
+      <c r="O28" s="234"/>
+      <c r="P28" s="234"/>
+      <c r="Q28" s="234"/>
+      <c r="R28" s="234"/>
+      <c r="S28" s="234"/>
+      <c r="T28" s="235" t="s">
         <v>49</v>
       </c>
-      <c r="U28" s="105"/>
-      <c r="V28" s="105"/>
-      <c r="W28" s="105"/>
-      <c r="X28" s="105"/>
-      <c r="Y28" s="105"/>
-      <c r="Z28" s="105"/>
-      <c r="AA28" s="104" t="s">
+      <c r="U28" s="235"/>
+      <c r="V28" s="235"/>
+      <c r="W28" s="235"/>
+      <c r="X28" s="235"/>
+      <c r="Y28" s="235"/>
+      <c r="Z28" s="235"/>
+      <c r="AA28" s="234" t="s">
         <v>48</v>
       </c>
-      <c r="AB28" s="104"/>
-      <c r="AC28" s="104"/>
-      <c r="AD28" s="104"/>
-      <c r="AE28" s="104"/>
-      <c r="AF28" s="104"/>
-      <c r="AG28" s="104"/>
-      <c r="AH28" s="104"/>
-      <c r="AI28" s="104"/>
-      <c r="AJ28" s="104"/>
-      <c r="AK28" s="104"/>
-      <c r="AL28" s="104"/>
-      <c r="AM28" s="104"/>
-      <c r="AN28" s="104"/>
-      <c r="AO28" s="104"/>
-      <c r="AP28" s="104"/>
-      <c r="AQ28" s="104"/>
-      <c r="AR28" s="104"/>
-      <c r="AS28" s="104"/>
-      <c r="AT28" s="105" t="s">
+      <c r="AB28" s="234"/>
+      <c r="AC28" s="234"/>
+      <c r="AD28" s="234"/>
+      <c r="AE28" s="234"/>
+      <c r="AF28" s="234"/>
+      <c r="AG28" s="234"/>
+      <c r="AH28" s="234"/>
+      <c r="AI28" s="234"/>
+      <c r="AJ28" s="234"/>
+      <c r="AK28" s="234"/>
+      <c r="AL28" s="234"/>
+      <c r="AM28" s="234"/>
+      <c r="AN28" s="234"/>
+      <c r="AO28" s="234"/>
+      <c r="AP28" s="234"/>
+      <c r="AQ28" s="234"/>
+      <c r="AR28" s="234"/>
+      <c r="AS28" s="234"/>
+      <c r="AT28" s="235" t="s">
         <v>49</v>
       </c>
-      <c r="AU28" s="105"/>
-      <c r="AV28" s="105"/>
-      <c r="AW28" s="105"/>
-      <c r="AX28" s="105"/>
-      <c r="AY28" s="105"/>
-      <c r="AZ28" s="106"/>
+      <c r="AU28" s="235"/>
+      <c r="AV28" s="235"/>
+      <c r="AW28" s="235"/>
+      <c r="AX28" s="235"/>
+      <c r="AY28" s="235"/>
+      <c r="AZ28" s="236"/>
     </row>
     <row r="29" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="107" t="s">
+      <c r="A29" s="237" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="108"/>
-      <c r="C29" s="108"/>
-      <c r="D29" s="108"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="108"/>
-      <c r="G29" s="108"/>
-      <c r="H29" s="108"/>
-      <c r="I29" s="108"/>
-      <c r="J29" s="108"/>
-      <c r="K29" s="108"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="108"/>
-      <c r="N29" s="108"/>
-      <c r="O29" s="108"/>
-      <c r="P29" s="108"/>
-      <c r="Q29" s="108"/>
-      <c r="R29" s="108"/>
-      <c r="S29" s="108"/>
-      <c r="T29" s="109"/>
-      <c r="U29" s="109"/>
-      <c r="V29" s="109"/>
-      <c r="W29" s="109"/>
-      <c r="X29" s="109"/>
-      <c r="Y29" s="109"/>
-      <c r="Z29" s="109"/>
-      <c r="AA29" s="108" t="s">
+      <c r="B29" s="238"/>
+      <c r="C29" s="238"/>
+      <c r="D29" s="238"/>
+      <c r="E29" s="238"/>
+      <c r="F29" s="238"/>
+      <c r="G29" s="238"/>
+      <c r="H29" s="238"/>
+      <c r="I29" s="238"/>
+      <c r="J29" s="238"/>
+      <c r="K29" s="238"/>
+      <c r="L29" s="238"/>
+      <c r="M29" s="238"/>
+      <c r="N29" s="238"/>
+      <c r="O29" s="238"/>
+      <c r="P29" s="238"/>
+      <c r="Q29" s="238"/>
+      <c r="R29" s="238"/>
+      <c r="S29" s="238"/>
+      <c r="T29" s="239"/>
+      <c r="U29" s="239"/>
+      <c r="V29" s="239"/>
+      <c r="W29" s="239"/>
+      <c r="X29" s="239"/>
+      <c r="Y29" s="239"/>
+      <c r="Z29" s="239"/>
+      <c r="AA29" s="238" t="s">
         <v>51</v>
       </c>
-      <c r="AB29" s="108"/>
-      <c r="AC29" s="108"/>
-      <c r="AD29" s="108"/>
-      <c r="AE29" s="108"/>
-      <c r="AF29" s="108"/>
-      <c r="AG29" s="108"/>
-      <c r="AH29" s="108"/>
-      <c r="AI29" s="108"/>
-      <c r="AJ29" s="108"/>
-      <c r="AK29" s="108"/>
-      <c r="AL29" s="108"/>
-      <c r="AM29" s="108"/>
-      <c r="AN29" s="108"/>
-      <c r="AO29" s="108"/>
-      <c r="AP29" s="108"/>
-      <c r="AQ29" s="108"/>
-      <c r="AR29" s="108"/>
-      <c r="AS29" s="108"/>
-      <c r="AT29" s="109"/>
-      <c r="AU29" s="109"/>
-      <c r="AV29" s="109"/>
-      <c r="AW29" s="109"/>
-      <c r="AX29" s="109"/>
-      <c r="AY29" s="109"/>
-      <c r="AZ29" s="110"/>
+      <c r="AB29" s="238"/>
+      <c r="AC29" s="238"/>
+      <c r="AD29" s="238"/>
+      <c r="AE29" s="238"/>
+      <c r="AF29" s="238"/>
+      <c r="AG29" s="238"/>
+      <c r="AH29" s="238"/>
+      <c r="AI29" s="238"/>
+      <c r="AJ29" s="238"/>
+      <c r="AK29" s="238"/>
+      <c r="AL29" s="238"/>
+      <c r="AM29" s="238"/>
+      <c r="AN29" s="238"/>
+      <c r="AO29" s="238"/>
+      <c r="AP29" s="238"/>
+      <c r="AQ29" s="238"/>
+      <c r="AR29" s="238"/>
+      <c r="AS29" s="238"/>
+      <c r="AT29" s="239"/>
+      <c r="AU29" s="239"/>
+      <c r="AV29" s="239"/>
+      <c r="AW29" s="239"/>
+      <c r="AX29" s="239"/>
+      <c r="AY29" s="239"/>
+      <c r="AZ29" s="240"/>
     </row>
     <row r="30" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="107" t="s">
+      <c r="A30" s="237" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="108"/>
-      <c r="C30" s="108"/>
-      <c r="D30" s="108"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="108"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="108"/>
-      <c r="I30" s="108"/>
-      <c r="J30" s="108"/>
-      <c r="K30" s="108"/>
-      <c r="L30" s="108"/>
-      <c r="M30" s="108"/>
-      <c r="N30" s="108"/>
-      <c r="O30" s="108"/>
-      <c r="P30" s="108"/>
-      <c r="Q30" s="108"/>
-      <c r="R30" s="108"/>
-      <c r="S30" s="108"/>
-      <c r="T30" s="109"/>
-      <c r="U30" s="109"/>
-      <c r="V30" s="109"/>
-      <c r="W30" s="109"/>
-      <c r="X30" s="109"/>
-      <c r="Y30" s="109"/>
-      <c r="Z30" s="109"/>
-      <c r="AA30" s="108" t="s">
+      <c r="B30" s="238"/>
+      <c r="C30" s="238"/>
+      <c r="D30" s="238"/>
+      <c r="E30" s="238"/>
+      <c r="F30" s="238"/>
+      <c r="G30" s="238"/>
+      <c r="H30" s="238"/>
+      <c r="I30" s="238"/>
+      <c r="J30" s="238"/>
+      <c r="K30" s="238"/>
+      <c r="L30" s="238"/>
+      <c r="M30" s="238"/>
+      <c r="N30" s="238"/>
+      <c r="O30" s="238"/>
+      <c r="P30" s="238"/>
+      <c r="Q30" s="238"/>
+      <c r="R30" s="238"/>
+      <c r="S30" s="238"/>
+      <c r="T30" s="239"/>
+      <c r="U30" s="239"/>
+      <c r="V30" s="239"/>
+      <c r="W30" s="239"/>
+      <c r="X30" s="239"/>
+      <c r="Y30" s="239"/>
+      <c r="Z30" s="239"/>
+      <c r="AA30" s="238" t="s">
         <v>53</v>
       </c>
-      <c r="AB30" s="108"/>
-      <c r="AC30" s="108"/>
-      <c r="AD30" s="108"/>
-      <c r="AE30" s="108"/>
-      <c r="AF30" s="108"/>
-      <c r="AG30" s="108"/>
-      <c r="AH30" s="108"/>
-      <c r="AI30" s="108"/>
-      <c r="AJ30" s="108"/>
-      <c r="AK30" s="108"/>
-      <c r="AL30" s="108"/>
-      <c r="AM30" s="108"/>
-      <c r="AN30" s="108"/>
-      <c r="AO30" s="108"/>
-      <c r="AP30" s="108"/>
-      <c r="AQ30" s="108"/>
-      <c r="AR30" s="108"/>
-      <c r="AS30" s="108"/>
-      <c r="AT30" s="109"/>
-      <c r="AU30" s="109"/>
-      <c r="AV30" s="109"/>
-      <c r="AW30" s="109"/>
-      <c r="AX30" s="109"/>
-      <c r="AY30" s="109"/>
-      <c r="AZ30" s="110"/>
+      <c r="AB30" s="238"/>
+      <c r="AC30" s="238"/>
+      <c r="AD30" s="238"/>
+      <c r="AE30" s="238"/>
+      <c r="AF30" s="238"/>
+      <c r="AG30" s="238"/>
+      <c r="AH30" s="238"/>
+      <c r="AI30" s="238"/>
+      <c r="AJ30" s="238"/>
+      <c r="AK30" s="238"/>
+      <c r="AL30" s="238"/>
+      <c r="AM30" s="238"/>
+      <c r="AN30" s="238"/>
+      <c r="AO30" s="238"/>
+      <c r="AP30" s="238"/>
+      <c r="AQ30" s="238"/>
+      <c r="AR30" s="238"/>
+      <c r="AS30" s="238"/>
+      <c r="AT30" s="239"/>
+      <c r="AU30" s="239"/>
+      <c r="AV30" s="239"/>
+      <c r="AW30" s="239"/>
+      <c r="AX30" s="239"/>
+      <c r="AY30" s="239"/>
+      <c r="AZ30" s="240"/>
     </row>
     <row r="31" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="111" t="s">
+      <c r="A31" s="224" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="112"/>
-      <c r="C31" s="112"/>
-      <c r="D31" s="112"/>
-      <c r="E31" s="112"/>
-      <c r="F31" s="112"/>
-      <c r="G31" s="112"/>
-      <c r="H31" s="112"/>
-      <c r="I31" s="112"/>
-      <c r="J31" s="112"/>
-      <c r="K31" s="112"/>
-      <c r="L31" s="112"/>
-      <c r="M31" s="112"/>
-      <c r="N31" s="112"/>
-      <c r="O31" s="112"/>
-      <c r="P31" s="112"/>
-      <c r="Q31" s="112"/>
-      <c r="R31" s="112"/>
-      <c r="S31" s="112"/>
-      <c r="T31" s="113"/>
-      <c r="U31" s="113"/>
-      <c r="V31" s="113"/>
-      <c r="W31" s="113"/>
-      <c r="X31" s="113"/>
-      <c r="Y31" s="113"/>
-      <c r="Z31" s="113"/>
-      <c r="AA31" s="112" t="s">
+      <c r="B31" s="225"/>
+      <c r="C31" s="225"/>
+      <c r="D31" s="225"/>
+      <c r="E31" s="225"/>
+      <c r="F31" s="225"/>
+      <c r="G31" s="225"/>
+      <c r="H31" s="225"/>
+      <c r="I31" s="225"/>
+      <c r="J31" s="225"/>
+      <c r="K31" s="225"/>
+      <c r="L31" s="225"/>
+      <c r="M31" s="225"/>
+      <c r="N31" s="225"/>
+      <c r="O31" s="225"/>
+      <c r="P31" s="225"/>
+      <c r="Q31" s="225"/>
+      <c r="R31" s="225"/>
+      <c r="S31" s="225"/>
+      <c r="T31" s="241"/>
+      <c r="U31" s="241"/>
+      <c r="V31" s="241"/>
+      <c r="W31" s="241"/>
+      <c r="X31" s="241"/>
+      <c r="Y31" s="241"/>
+      <c r="Z31" s="241"/>
+      <c r="AA31" s="225" t="s">
         <v>54</v>
       </c>
-      <c r="AB31" s="112"/>
-      <c r="AC31" s="112"/>
-      <c r="AD31" s="112"/>
-      <c r="AE31" s="112"/>
-      <c r="AF31" s="112"/>
-      <c r="AG31" s="112"/>
-      <c r="AH31" s="112"/>
-      <c r="AI31" s="112"/>
-      <c r="AJ31" s="112"/>
-      <c r="AK31" s="112"/>
-      <c r="AL31" s="112"/>
-      <c r="AM31" s="112"/>
-      <c r="AN31" s="112"/>
-      <c r="AO31" s="112"/>
-      <c r="AP31" s="112"/>
-      <c r="AQ31" s="112"/>
-      <c r="AR31" s="112"/>
-      <c r="AS31" s="112"/>
-      <c r="AT31" s="113"/>
-      <c r="AU31" s="113"/>
-      <c r="AV31" s="113"/>
-      <c r="AW31" s="113"/>
-      <c r="AX31" s="113"/>
-      <c r="AY31" s="113"/>
-      <c r="AZ31" s="114"/>
+      <c r="AB31" s="225"/>
+      <c r="AC31" s="225"/>
+      <c r="AD31" s="225"/>
+      <c r="AE31" s="225"/>
+      <c r="AF31" s="225"/>
+      <c r="AG31" s="225"/>
+      <c r="AH31" s="225"/>
+      <c r="AI31" s="225"/>
+      <c r="AJ31" s="225"/>
+      <c r="AK31" s="225"/>
+      <c r="AL31" s="225"/>
+      <c r="AM31" s="225"/>
+      <c r="AN31" s="225"/>
+      <c r="AO31" s="225"/>
+      <c r="AP31" s="225"/>
+      <c r="AQ31" s="225"/>
+      <c r="AR31" s="225"/>
+      <c r="AS31" s="225"/>
+      <c r="AT31" s="241"/>
+      <c r="AU31" s="241"/>
+      <c r="AV31" s="241"/>
+      <c r="AW31" s="241"/>
+      <c r="AX31" s="241"/>
+      <c r="AY31" s="241"/>
+      <c r="AZ31" s="242"/>
     </row>
     <row r="32" spans="1:62" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="98"/>
-      <c r="B32" s="98"/>
-      <c r="C32" s="98"/>
-      <c r="D32" s="98"/>
-      <c r="E32" s="98"/>
-      <c r="F32" s="98"/>
-      <c r="G32" s="98"/>
-      <c r="H32" s="98"/>
-      <c r="I32" s="98"/>
-      <c r="J32" s="98"/>
-      <c r="K32" s="98"/>
-      <c r="L32" s="98"/>
-      <c r="M32" s="98"/>
-      <c r="N32" s="98"/>
-      <c r="O32" s="98"/>
-      <c r="P32" s="98"/>
-      <c r="Q32" s="98"/>
-      <c r="R32" s="98"/>
-      <c r="S32" s="98"/>
-      <c r="T32" s="98"/>
-      <c r="U32" s="98"/>
-      <c r="V32" s="98"/>
-      <c r="W32" s="98"/>
-      <c r="X32" s="98"/>
-      <c r="Y32" s="98"/>
-      <c r="Z32" s="98"/>
-      <c r="AA32" s="98"/>
-      <c r="AB32" s="98"/>
-      <c r="AC32" s="98"/>
-      <c r="AD32" s="98"/>
-      <c r="AE32" s="98"/>
-      <c r="AF32" s="98"/>
-      <c r="AG32" s="98"/>
-      <c r="AH32" s="98"/>
-      <c r="AI32" s="98"/>
-      <c r="AJ32" s="98"/>
-      <c r="AK32" s="98"/>
-      <c r="AL32" s="98"/>
-      <c r="AM32" s="98"/>
-      <c r="AN32" s="98"/>
-      <c r="AO32" s="98"/>
-      <c r="AP32" s="98"/>
-      <c r="AQ32" s="98"/>
-      <c r="AR32" s="98"/>
-      <c r="AS32" s="98"/>
-      <c r="AT32" s="98"/>
-      <c r="AU32" s="98"/>
-      <c r="AV32" s="98"/>
-      <c r="AW32" s="98"/>
-      <c r="AX32" s="98"/>
-      <c r="AY32" s="98"/>
-      <c r="AZ32" s="98"/>
+      <c r="A32" s="232"/>
+      <c r="B32" s="232"/>
+      <c r="C32" s="232"/>
+      <c r="D32" s="232"/>
+      <c r="E32" s="232"/>
+      <c r="F32" s="232"/>
+      <c r="G32" s="232"/>
+      <c r="H32" s="232"/>
+      <c r="I32" s="232"/>
+      <c r="J32" s="232"/>
+      <c r="K32" s="232"/>
+      <c r="L32" s="232"/>
+      <c r="M32" s="232"/>
+      <c r="N32" s="232"/>
+      <c r="O32" s="232"/>
+      <c r="P32" s="232"/>
+      <c r="Q32" s="232"/>
+      <c r="R32" s="232"/>
+      <c r="S32" s="232"/>
+      <c r="T32" s="232"/>
+      <c r="U32" s="232"/>
+      <c r="V32" s="232"/>
+      <c r="W32" s="232"/>
+      <c r="X32" s="232"/>
+      <c r="Y32" s="232"/>
+      <c r="Z32" s="232"/>
+      <c r="AA32" s="232"/>
+      <c r="AB32" s="232"/>
+      <c r="AC32" s="232"/>
+      <c r="AD32" s="232"/>
+      <c r="AE32" s="232"/>
+      <c r="AF32" s="232"/>
+      <c r="AG32" s="232"/>
+      <c r="AH32" s="232"/>
+      <c r="AI32" s="232"/>
+      <c r="AJ32" s="232"/>
+      <c r="AK32" s="232"/>
+      <c r="AL32" s="232"/>
+      <c r="AM32" s="232"/>
+      <c r="AN32" s="232"/>
+      <c r="AO32" s="232"/>
+      <c r="AP32" s="232"/>
+      <c r="AQ32" s="232"/>
+      <c r="AR32" s="232"/>
+      <c r="AS32" s="232"/>
+      <c r="AT32" s="232"/>
+      <c r="AU32" s="232"/>
+      <c r="AV32" s="232"/>
+      <c r="AW32" s="232"/>
+      <c r="AX32" s="232"/>
+      <c r="AY32" s="232"/>
+      <c r="AZ32" s="232"/>
     </row>
     <row r="33" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="205" t="s">
+      <c r="A33" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="206"/>
-      <c r="C33" s="206"/>
-      <c r="D33" s="206"/>
-      <c r="E33" s="206"/>
-      <c r="F33" s="206"/>
-      <c r="G33" s="206"/>
-      <c r="H33" s="206"/>
-      <c r="I33" s="206"/>
-      <c r="J33" s="206"/>
-      <c r="K33" s="206"/>
-      <c r="L33" s="206"/>
-      <c r="M33" s="206"/>
-      <c r="N33" s="206"/>
-      <c r="O33" s="206"/>
-      <c r="P33" s="206"/>
-      <c r="Q33" s="206"/>
-      <c r="R33" s="207"/>
-      <c r="S33" s="196" t="s">
+      <c r="B33" s="132"/>
+      <c r="C33" s="132"/>
+      <c r="D33" s="132"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="132"/>
+      <c r="H33" s="132"/>
+      <c r="I33" s="132"/>
+      <c r="J33" s="132"/>
+      <c r="K33" s="132"/>
+      <c r="L33" s="132"/>
+      <c r="M33" s="132"/>
+      <c r="N33" s="132"/>
+      <c r="O33" s="132"/>
+      <c r="P33" s="132"/>
+      <c r="Q33" s="132"/>
+      <c r="R33" s="133"/>
+      <c r="S33" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="T33" s="197"/>
-      <c r="U33" s="197"/>
-      <c r="V33" s="197"/>
-      <c r="W33" s="197"/>
-      <c r="X33" s="197"/>
-      <c r="Y33" s="197"/>
-      <c r="Z33" s="197"/>
-      <c r="AA33" s="197"/>
-      <c r="AB33" s="197"/>
-      <c r="AC33" s="197"/>
-      <c r="AD33" s="197"/>
-      <c r="AE33" s="197"/>
-      <c r="AF33" s="197"/>
-      <c r="AG33" s="198"/>
-      <c r="AH33" s="196" t="s">
+      <c r="T33" s="99"/>
+      <c r="U33" s="99"/>
+      <c r="V33" s="99"/>
+      <c r="W33" s="99"/>
+      <c r="X33" s="99"/>
+      <c r="Y33" s="99"/>
+      <c r="Z33" s="99"/>
+      <c r="AA33" s="99"/>
+      <c r="AB33" s="99"/>
+      <c r="AC33" s="99"/>
+      <c r="AD33" s="99"/>
+      <c r="AE33" s="99"/>
+      <c r="AF33" s="99"/>
+      <c r="AG33" s="123"/>
+      <c r="AH33" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="AI33" s="197"/>
-      <c r="AJ33" s="197"/>
-      <c r="AK33" s="197"/>
-      <c r="AL33" s="197"/>
-      <c r="AM33" s="197"/>
-      <c r="AN33" s="197"/>
-      <c r="AO33" s="197"/>
-      <c r="AP33" s="197"/>
-      <c r="AQ33" s="197"/>
-      <c r="AR33" s="197"/>
-      <c r="AS33" s="197"/>
-      <c r="AT33" s="197"/>
-      <c r="AU33" s="197"/>
-      <c r="AV33" s="197"/>
-      <c r="AW33" s="197"/>
-      <c r="AX33" s="197"/>
-      <c r="AY33" s="197"/>
-      <c r="AZ33" s="231"/>
+      <c r="AI33" s="99"/>
+      <c r="AJ33" s="99"/>
+      <c r="AK33" s="99"/>
+      <c r="AL33" s="99"/>
+      <c r="AM33" s="99"/>
+      <c r="AN33" s="99"/>
+      <c r="AO33" s="99"/>
+      <c r="AP33" s="99"/>
+      <c r="AQ33" s="99"/>
+      <c r="AR33" s="99"/>
+      <c r="AS33" s="99"/>
+      <c r="AT33" s="99"/>
+      <c r="AU33" s="99"/>
+      <c r="AV33" s="99"/>
+      <c r="AW33" s="99"/>
+      <c r="AX33" s="99"/>
+      <c r="AY33" s="99"/>
+      <c r="AZ33" s="100"/>
     </row>
     <row r="34" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="208"/>
-      <c r="B34" s="209"/>
-      <c r="C34" s="209"/>
-      <c r="D34" s="209"/>
-      <c r="E34" s="209"/>
-      <c r="F34" s="209"/>
-      <c r="G34" s="209"/>
-      <c r="H34" s="209"/>
-      <c r="I34" s="209"/>
-      <c r="J34" s="209"/>
-      <c r="K34" s="209"/>
-      <c r="L34" s="209"/>
-      <c r="M34" s="209"/>
-      <c r="N34" s="209"/>
-      <c r="O34" s="209"/>
-      <c r="P34" s="209"/>
-      <c r="Q34" s="209"/>
-      <c r="R34" s="210"/>
-      <c r="S34" s="199"/>
-      <c r="T34" s="200"/>
-      <c r="U34" s="200"/>
-      <c r="V34" s="200"/>
-      <c r="W34" s="200"/>
-      <c r="X34" s="200"/>
-      <c r="Y34" s="200"/>
-      <c r="Z34" s="200"/>
-      <c r="AA34" s="200"/>
-      <c r="AB34" s="200"/>
-      <c r="AC34" s="200"/>
-      <c r="AD34" s="200"/>
-      <c r="AE34" s="200"/>
-      <c r="AF34" s="200"/>
-      <c r="AG34" s="201"/>
-      <c r="AH34" s="199"/>
-      <c r="AI34" s="200"/>
-      <c r="AJ34" s="200"/>
-      <c r="AK34" s="200"/>
-      <c r="AL34" s="200"/>
-      <c r="AM34" s="200"/>
-      <c r="AN34" s="200"/>
-      <c r="AO34" s="200"/>
-      <c r="AP34" s="200"/>
-      <c r="AQ34" s="200"/>
-      <c r="AR34" s="200"/>
-      <c r="AS34" s="200"/>
-      <c r="AT34" s="200"/>
-      <c r="AU34" s="200"/>
-      <c r="AV34" s="200"/>
-      <c r="AW34" s="200"/>
-      <c r="AX34" s="200"/>
-      <c r="AY34" s="200"/>
-      <c r="AZ34" s="232"/>
+      <c r="A34" s="134"/>
+      <c r="B34" s="135"/>
+      <c r="C34" s="135"/>
+      <c r="D34" s="135"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="135"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="135"/>
+      <c r="I34" s="135"/>
+      <c r="J34" s="135"/>
+      <c r="K34" s="135"/>
+      <c r="L34" s="135"/>
+      <c r="M34" s="135"/>
+      <c r="N34" s="135"/>
+      <c r="O34" s="135"/>
+      <c r="P34" s="135"/>
+      <c r="Q34" s="135"/>
+      <c r="R34" s="136"/>
+      <c r="S34" s="101"/>
+      <c r="T34" s="102"/>
+      <c r="U34" s="102"/>
+      <c r="V34" s="102"/>
+      <c r="W34" s="102"/>
+      <c r="X34" s="102"/>
+      <c r="Y34" s="102"/>
+      <c r="Z34" s="102"/>
+      <c r="AA34" s="102"/>
+      <c r="AB34" s="102"/>
+      <c r="AC34" s="102"/>
+      <c r="AD34" s="102"/>
+      <c r="AE34" s="102"/>
+      <c r="AF34" s="102"/>
+      <c r="AG34" s="124"/>
+      <c r="AH34" s="101"/>
+      <c r="AI34" s="102"/>
+      <c r="AJ34" s="102"/>
+      <c r="AK34" s="102"/>
+      <c r="AL34" s="102"/>
+      <c r="AM34" s="102"/>
+      <c r="AN34" s="102"/>
+      <c r="AO34" s="102"/>
+      <c r="AP34" s="102"/>
+      <c r="AQ34" s="102"/>
+      <c r="AR34" s="102"/>
+      <c r="AS34" s="102"/>
+      <c r="AT34" s="102"/>
+      <c r="AU34" s="102"/>
+      <c r="AV34" s="102"/>
+      <c r="AW34" s="102"/>
+      <c r="AX34" s="102"/>
+      <c r="AY34" s="102"/>
+      <c r="AZ34" s="103"/>
     </row>
     <row r="35" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="183" t="s">
+      <c r="A35" s="125" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="184"/>
-      <c r="C35" s="184"/>
-      <c r="D35" s="184"/>
-      <c r="E35" s="184"/>
-      <c r="F35" s="184"/>
-      <c r="G35" s="184"/>
-      <c r="H35" s="184"/>
-      <c r="I35" s="184"/>
-      <c r="J35" s="184"/>
-      <c r="K35" s="184"/>
-      <c r="L35" s="184"/>
-      <c r="M35" s="184"/>
-      <c r="N35" s="184"/>
-      <c r="O35" s="184"/>
-      <c r="P35" s="184"/>
-      <c r="Q35" s="184"/>
-      <c r="R35" s="185"/>
-      <c r="S35" s="189" t="s">
+      <c r="B35" s="126"/>
+      <c r="C35" s="126"/>
+      <c r="D35" s="126"/>
+      <c r="E35" s="126"/>
+      <c r="F35" s="126"/>
+      <c r="G35" s="126"/>
+      <c r="H35" s="126"/>
+      <c r="I35" s="126"/>
+      <c r="J35" s="126"/>
+      <c r="K35" s="126"/>
+      <c r="L35" s="126"/>
+      <c r="M35" s="126"/>
+      <c r="N35" s="126"/>
+      <c r="O35" s="126"/>
+      <c r="P35" s="126"/>
+      <c r="Q35" s="126"/>
+      <c r="R35" s="127"/>
+      <c r="S35" s="128" t="s">
         <v>59</v>
       </c>
-      <c r="T35" s="190"/>
-      <c r="U35" s="190"/>
-      <c r="V35" s="190"/>
-      <c r="W35" s="190"/>
-      <c r="X35" s="190"/>
-      <c r="Y35" s="190"/>
-      <c r="Z35" s="190"/>
-      <c r="AA35" s="190"/>
-      <c r="AB35" s="190"/>
-      <c r="AC35" s="190"/>
-      <c r="AD35" s="190"/>
-      <c r="AE35" s="190"/>
-      <c r="AF35" s="190"/>
-      <c r="AG35" s="191"/>
-      <c r="AH35" s="202" t="s">
+      <c r="T35" s="129"/>
+      <c r="U35" s="129"/>
+      <c r="V35" s="129"/>
+      <c r="W35" s="129"/>
+      <c r="X35" s="129"/>
+      <c r="Y35" s="129"/>
+      <c r="Z35" s="129"/>
+      <c r="AA35" s="129"/>
+      <c r="AB35" s="129"/>
+      <c r="AC35" s="129"/>
+      <c r="AD35" s="129"/>
+      <c r="AE35" s="129"/>
+      <c r="AF35" s="129"/>
+      <c r="AG35" s="130"/>
+      <c r="AH35" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="AI35" s="203"/>
-      <c r="AJ35" s="203"/>
-      <c r="AK35" s="203"/>
-      <c r="AL35" s="203"/>
-      <c r="AM35" s="203"/>
-      <c r="AN35" s="203"/>
-      <c r="AO35" s="203"/>
-      <c r="AP35" s="203"/>
-      <c r="AQ35" s="203"/>
-      <c r="AR35" s="203"/>
-      <c r="AS35" s="203"/>
-      <c r="AT35" s="203"/>
-      <c r="AU35" s="203"/>
-      <c r="AV35" s="203"/>
-      <c r="AW35" s="203"/>
-      <c r="AX35" s="203"/>
-      <c r="AY35" s="203"/>
-      <c r="AZ35" s="204"/>
+      <c r="AI35" s="96"/>
+      <c r="AJ35" s="96"/>
+      <c r="AK35" s="96"/>
+      <c r="AL35" s="96"/>
+      <c r="AM35" s="96"/>
+      <c r="AN35" s="96"/>
+      <c r="AO35" s="96"/>
+      <c r="AP35" s="96"/>
+      <c r="AQ35" s="96"/>
+      <c r="AR35" s="96"/>
+      <c r="AS35" s="96"/>
+      <c r="AT35" s="96"/>
+      <c r="AU35" s="96"/>
+      <c r="AV35" s="96"/>
+      <c r="AW35" s="96"/>
+      <c r="AX35" s="96"/>
+      <c r="AY35" s="96"/>
+      <c r="AZ35" s="97"/>
     </row>
     <row r="36" spans="1:52" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="183" t="s">
+      <c r="A36" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="184"/>
-      <c r="C36" s="184"/>
-      <c r="D36" s="184"/>
-      <c r="E36" s="184"/>
-      <c r="F36" s="184"/>
-      <c r="G36" s="184"/>
-      <c r="H36" s="184"/>
-      <c r="I36" s="184"/>
-      <c r="J36" s="184"/>
-      <c r="K36" s="184"/>
-      <c r="L36" s="184"/>
-      <c r="M36" s="184"/>
-      <c r="N36" s="184"/>
-      <c r="O36" s="184"/>
-      <c r="P36" s="184"/>
-      <c r="Q36" s="184"/>
-      <c r="R36" s="185"/>
-      <c r="S36" s="189" t="s">
+      <c r="B36" s="126"/>
+      <c r="C36" s="126"/>
+      <c r="D36" s="126"/>
+      <c r="E36" s="126"/>
+      <c r="F36" s="126"/>
+      <c r="G36" s="126"/>
+      <c r="H36" s="126"/>
+      <c r="I36" s="126"/>
+      <c r="J36" s="126"/>
+      <c r="K36" s="126"/>
+      <c r="L36" s="126"/>
+      <c r="M36" s="126"/>
+      <c r="N36" s="126"/>
+      <c r="O36" s="126"/>
+      <c r="P36" s="126"/>
+      <c r="Q36" s="126"/>
+      <c r="R36" s="127"/>
+      <c r="S36" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="T36" s="190"/>
-      <c r="U36" s="190"/>
-      <c r="V36" s="190"/>
-      <c r="W36" s="190"/>
-      <c r="X36" s="190"/>
-      <c r="Y36" s="190"/>
-      <c r="Z36" s="190"/>
-      <c r="AA36" s="190"/>
-      <c r="AB36" s="190"/>
-      <c r="AC36" s="190"/>
-      <c r="AD36" s="190"/>
-      <c r="AE36" s="190"/>
-      <c r="AF36" s="190"/>
-      <c r="AG36" s="191"/>
-      <c r="AH36" s="202" t="s">
+      <c r="T36" s="129"/>
+      <c r="U36" s="129"/>
+      <c r="V36" s="129"/>
+      <c r="W36" s="129"/>
+      <c r="X36" s="129"/>
+      <c r="Y36" s="129"/>
+      <c r="Z36" s="129"/>
+      <c r="AA36" s="129"/>
+      <c r="AB36" s="129"/>
+      <c r="AC36" s="129"/>
+      <c r="AD36" s="129"/>
+      <c r="AE36" s="129"/>
+      <c r="AF36" s="129"/>
+      <c r="AG36" s="130"/>
+      <c r="AH36" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="AI36" s="203"/>
-      <c r="AJ36" s="203"/>
-      <c r="AK36" s="203"/>
-      <c r="AL36" s="203"/>
-      <c r="AM36" s="203"/>
-      <c r="AN36" s="203"/>
-      <c r="AO36" s="203"/>
-      <c r="AP36" s="203"/>
-      <c r="AQ36" s="203"/>
-      <c r="AR36" s="203"/>
-      <c r="AS36" s="203"/>
-      <c r="AT36" s="203"/>
-      <c r="AU36" s="203"/>
-      <c r="AV36" s="203"/>
-      <c r="AW36" s="203"/>
-      <c r="AX36" s="203"/>
-      <c r="AY36" s="203"/>
-      <c r="AZ36" s="204"/>
+      <c r="AI36" s="96"/>
+      <c r="AJ36" s="96"/>
+      <c r="AK36" s="96"/>
+      <c r="AL36" s="96"/>
+      <c r="AM36" s="96"/>
+      <c r="AN36" s="96"/>
+      <c r="AO36" s="96"/>
+      <c r="AP36" s="96"/>
+      <c r="AQ36" s="96"/>
+      <c r="AR36" s="96"/>
+      <c r="AS36" s="96"/>
+      <c r="AT36" s="96"/>
+      <c r="AU36" s="96"/>
+      <c r="AV36" s="96"/>
+      <c r="AW36" s="96"/>
+      <c r="AX36" s="96"/>
+      <c r="AY36" s="96"/>
+      <c r="AZ36" s="97"/>
     </row>
     <row r="37" spans="1:52" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="183" t="s">
+      <c r="A37" s="125" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="184"/>
-      <c r="C37" s="184"/>
-      <c r="D37" s="184"/>
-      <c r="E37" s="184"/>
-      <c r="F37" s="184"/>
-      <c r="G37" s="184"/>
-      <c r="H37" s="184"/>
-      <c r="I37" s="184"/>
-      <c r="J37" s="184"/>
-      <c r="K37" s="184"/>
-      <c r="L37" s="184"/>
-      <c r="M37" s="184"/>
-      <c r="N37" s="184"/>
-      <c r="O37" s="184"/>
-      <c r="P37" s="184"/>
-      <c r="Q37" s="184"/>
-      <c r="R37" s="185"/>
-      <c r="S37" s="189" t="s">
+      <c r="B37" s="126"/>
+      <c r="C37" s="126"/>
+      <c r="D37" s="126"/>
+      <c r="E37" s="126"/>
+      <c r="F37" s="126"/>
+      <c r="G37" s="126"/>
+      <c r="H37" s="126"/>
+      <c r="I37" s="126"/>
+      <c r="J37" s="126"/>
+      <c r="K37" s="126"/>
+      <c r="L37" s="126"/>
+      <c r="M37" s="126"/>
+      <c r="N37" s="126"/>
+      <c r="O37" s="126"/>
+      <c r="P37" s="126"/>
+      <c r="Q37" s="126"/>
+      <c r="R37" s="127"/>
+      <c r="S37" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="T37" s="190"/>
-      <c r="U37" s="190"/>
-      <c r="V37" s="190"/>
-      <c r="W37" s="190"/>
-      <c r="X37" s="190"/>
-      <c r="Y37" s="190"/>
-      <c r="Z37" s="190"/>
-      <c r="AA37" s="190"/>
-      <c r="AB37" s="190"/>
-      <c r="AC37" s="190"/>
-      <c r="AD37" s="190"/>
-      <c r="AE37" s="190"/>
-      <c r="AF37" s="190"/>
-      <c r="AG37" s="191"/>
-      <c r="AH37" s="202" t="s">
+      <c r="T37" s="129"/>
+      <c r="U37" s="129"/>
+      <c r="V37" s="129"/>
+      <c r="W37" s="129"/>
+      <c r="X37" s="129"/>
+      <c r="Y37" s="129"/>
+      <c r="Z37" s="129"/>
+      <c r="AA37" s="129"/>
+      <c r="AB37" s="129"/>
+      <c r="AC37" s="129"/>
+      <c r="AD37" s="129"/>
+      <c r="AE37" s="129"/>
+      <c r="AF37" s="129"/>
+      <c r="AG37" s="130"/>
+      <c r="AH37" s="95" t="s">
         <v>66</v>
       </c>
-      <c r="AI37" s="203"/>
-      <c r="AJ37" s="203"/>
-      <c r="AK37" s="203"/>
-      <c r="AL37" s="203"/>
-      <c r="AM37" s="203"/>
-      <c r="AN37" s="203"/>
-      <c r="AO37" s="203"/>
-      <c r="AP37" s="203"/>
-      <c r="AQ37" s="203"/>
-      <c r="AR37" s="203"/>
-      <c r="AS37" s="203"/>
-      <c r="AT37" s="203"/>
-      <c r="AU37" s="203"/>
-      <c r="AV37" s="203"/>
-      <c r="AW37" s="203"/>
-      <c r="AX37" s="203"/>
-      <c r="AY37" s="203"/>
-      <c r="AZ37" s="204"/>
+      <c r="AI37" s="96"/>
+      <c r="AJ37" s="96"/>
+      <c r="AK37" s="96"/>
+      <c r="AL37" s="96"/>
+      <c r="AM37" s="96"/>
+      <c r="AN37" s="96"/>
+      <c r="AO37" s="96"/>
+      <c r="AP37" s="96"/>
+      <c r="AQ37" s="96"/>
+      <c r="AR37" s="96"/>
+      <c r="AS37" s="96"/>
+      <c r="AT37" s="96"/>
+      <c r="AU37" s="96"/>
+      <c r="AV37" s="96"/>
+      <c r="AW37" s="96"/>
+      <c r="AX37" s="96"/>
+      <c r="AY37" s="96"/>
+      <c r="AZ37" s="97"/>
     </row>
     <row r="38" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="183" t="s">
+      <c r="A38" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="184"/>
-      <c r="C38" s="184"/>
-      <c r="D38" s="184"/>
-      <c r="E38" s="184"/>
-      <c r="F38" s="184"/>
-      <c r="G38" s="184"/>
-      <c r="H38" s="184"/>
-      <c r="I38" s="184"/>
-      <c r="J38" s="184"/>
-      <c r="K38" s="184"/>
-      <c r="L38" s="184"/>
-      <c r="M38" s="184"/>
-      <c r="N38" s="184"/>
-      <c r="O38" s="184"/>
-      <c r="P38" s="184"/>
-      <c r="Q38" s="184"/>
-      <c r="R38" s="185"/>
-      <c r="S38" s="189" t="s">
+      <c r="B38" s="126"/>
+      <c r="C38" s="126"/>
+      <c r="D38" s="126"/>
+      <c r="E38" s="126"/>
+      <c r="F38" s="126"/>
+      <c r="G38" s="126"/>
+      <c r="H38" s="126"/>
+      <c r="I38" s="126"/>
+      <c r="J38" s="126"/>
+      <c r="K38" s="126"/>
+      <c r="L38" s="126"/>
+      <c r="M38" s="126"/>
+      <c r="N38" s="126"/>
+      <c r="O38" s="126"/>
+      <c r="P38" s="126"/>
+      <c r="Q38" s="126"/>
+      <c r="R38" s="127"/>
+      <c r="S38" s="128" t="s">
         <v>68</v>
       </c>
-      <c r="T38" s="190"/>
-      <c r="U38" s="190"/>
-      <c r="V38" s="190"/>
-      <c r="W38" s="190"/>
-      <c r="X38" s="190"/>
-      <c r="Y38" s="190"/>
-      <c r="Z38" s="190"/>
-      <c r="AA38" s="190"/>
-      <c r="AB38" s="190"/>
-      <c r="AC38" s="190"/>
-      <c r="AD38" s="190"/>
-      <c r="AE38" s="190"/>
-      <c r="AF38" s="190"/>
-      <c r="AG38" s="191"/>
-      <c r="AH38" s="202" t="s">
+      <c r="T38" s="129"/>
+      <c r="U38" s="129"/>
+      <c r="V38" s="129"/>
+      <c r="W38" s="129"/>
+      <c r="X38" s="129"/>
+      <c r="Y38" s="129"/>
+      <c r="Z38" s="129"/>
+      <c r="AA38" s="129"/>
+      <c r="AB38" s="129"/>
+      <c r="AC38" s="129"/>
+      <c r="AD38" s="129"/>
+      <c r="AE38" s="129"/>
+      <c r="AF38" s="129"/>
+      <c r="AG38" s="130"/>
+      <c r="AH38" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="AI38" s="203"/>
-      <c r="AJ38" s="203"/>
-      <c r="AK38" s="203"/>
-      <c r="AL38" s="203"/>
-      <c r="AM38" s="203"/>
-      <c r="AN38" s="203"/>
-      <c r="AO38" s="203"/>
-      <c r="AP38" s="203"/>
-      <c r="AQ38" s="203"/>
-      <c r="AR38" s="203"/>
-      <c r="AS38" s="203"/>
-      <c r="AT38" s="203"/>
-      <c r="AU38" s="203"/>
-      <c r="AV38" s="203"/>
-      <c r="AW38" s="203"/>
-      <c r="AX38" s="203"/>
-      <c r="AY38" s="203"/>
-      <c r="AZ38" s="204"/>
+      <c r="AI38" s="96"/>
+      <c r="AJ38" s="96"/>
+      <c r="AK38" s="96"/>
+      <c r="AL38" s="96"/>
+      <c r="AM38" s="96"/>
+      <c r="AN38" s="96"/>
+      <c r="AO38" s="96"/>
+      <c r="AP38" s="96"/>
+      <c r="AQ38" s="96"/>
+      <c r="AR38" s="96"/>
+      <c r="AS38" s="96"/>
+      <c r="AT38" s="96"/>
+      <c r="AU38" s="96"/>
+      <c r="AV38" s="96"/>
+      <c r="AW38" s="96"/>
+      <c r="AX38" s="96"/>
+      <c r="AY38" s="96"/>
+      <c r="AZ38" s="97"/>
     </row>
     <row r="39" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="183" t="s">
+      <c r="A39" s="125" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="184"/>
-      <c r="C39" s="184"/>
-      <c r="D39" s="184"/>
-      <c r="E39" s="184"/>
-      <c r="F39" s="184"/>
-      <c r="G39" s="184"/>
-      <c r="H39" s="184"/>
-      <c r="I39" s="184"/>
-      <c r="J39" s="184"/>
-      <c r="K39" s="184"/>
-      <c r="L39" s="184"/>
-      <c r="M39" s="184"/>
-      <c r="N39" s="184"/>
-      <c r="O39" s="184"/>
-      <c r="P39" s="184"/>
-      <c r="Q39" s="184"/>
-      <c r="R39" s="185"/>
-      <c r="S39" s="189" t="s">
+      <c r="B39" s="126"/>
+      <c r="C39" s="126"/>
+      <c r="D39" s="126"/>
+      <c r="E39" s="126"/>
+      <c r="F39" s="126"/>
+      <c r="G39" s="126"/>
+      <c r="H39" s="126"/>
+      <c r="I39" s="126"/>
+      <c r="J39" s="126"/>
+      <c r="K39" s="126"/>
+      <c r="L39" s="126"/>
+      <c r="M39" s="126"/>
+      <c r="N39" s="126"/>
+      <c r="O39" s="126"/>
+      <c r="P39" s="126"/>
+      <c r="Q39" s="126"/>
+      <c r="R39" s="127"/>
+      <c r="S39" s="128" t="s">
         <v>71</v>
       </c>
-      <c r="T39" s="190"/>
-      <c r="U39" s="190"/>
-      <c r="V39" s="190"/>
-      <c r="W39" s="190"/>
-      <c r="X39" s="190"/>
-      <c r="Y39" s="190"/>
-      <c r="Z39" s="190"/>
-      <c r="AA39" s="190"/>
-      <c r="AB39" s="190"/>
-      <c r="AC39" s="190"/>
-      <c r="AD39" s="190"/>
-      <c r="AE39" s="190"/>
-      <c r="AF39" s="190"/>
-      <c r="AG39" s="191"/>
-      <c r="AH39" s="220"/>
-      <c r="AI39" s="221"/>
-      <c r="AJ39" s="221"/>
-      <c r="AK39" s="221"/>
-      <c r="AL39" s="221"/>
-      <c r="AM39" s="221"/>
-      <c r="AN39" s="221"/>
-      <c r="AO39" s="221"/>
-      <c r="AP39" s="221"/>
-      <c r="AQ39" s="221"/>
-      <c r="AR39" s="221"/>
-      <c r="AS39" s="221"/>
-      <c r="AT39" s="221"/>
-      <c r="AU39" s="221"/>
-      <c r="AV39" s="221"/>
-      <c r="AW39" s="221"/>
-      <c r="AX39" s="221"/>
-      <c r="AY39" s="221"/>
-      <c r="AZ39" s="222"/>
+      <c r="T39" s="129"/>
+      <c r="U39" s="129"/>
+      <c r="V39" s="129"/>
+      <c r="W39" s="129"/>
+      <c r="X39" s="129"/>
+      <c r="Y39" s="129"/>
+      <c r="Z39" s="129"/>
+      <c r="AA39" s="129"/>
+      <c r="AB39" s="129"/>
+      <c r="AC39" s="129"/>
+      <c r="AD39" s="129"/>
+      <c r="AE39" s="129"/>
+      <c r="AF39" s="129"/>
+      <c r="AG39" s="130"/>
+      <c r="AH39" s="148"/>
+      <c r="AI39" s="149"/>
+      <c r="AJ39" s="149"/>
+      <c r="AK39" s="149"/>
+      <c r="AL39" s="149"/>
+      <c r="AM39" s="149"/>
+      <c r="AN39" s="149"/>
+      <c r="AO39" s="149"/>
+      <c r="AP39" s="149"/>
+      <c r="AQ39" s="149"/>
+      <c r="AR39" s="149"/>
+      <c r="AS39" s="149"/>
+      <c r="AT39" s="149"/>
+      <c r="AU39" s="149"/>
+      <c r="AV39" s="149"/>
+      <c r="AW39" s="149"/>
+      <c r="AX39" s="149"/>
+      <c r="AY39" s="149"/>
+      <c r="AZ39" s="150"/>
     </row>
     <row r="40" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="183" t="s">
+      <c r="A40" s="125" t="s">
         <v>72</v>
       </c>
-      <c r="B40" s="184"/>
-      <c r="C40" s="184"/>
-      <c r="D40" s="184"/>
-      <c r="E40" s="184"/>
-      <c r="F40" s="184"/>
-      <c r="G40" s="184"/>
-      <c r="H40" s="184"/>
-      <c r="I40" s="184"/>
-      <c r="J40" s="184"/>
-      <c r="K40" s="184"/>
-      <c r="L40" s="184"/>
-      <c r="M40" s="184"/>
-      <c r="N40" s="184"/>
-      <c r="O40" s="184"/>
-      <c r="P40" s="184"/>
-      <c r="Q40" s="184"/>
-      <c r="R40" s="185"/>
-      <c r="S40" s="189" t="s">
+      <c r="B40" s="126"/>
+      <c r="C40" s="126"/>
+      <c r="D40" s="126"/>
+      <c r="E40" s="126"/>
+      <c r="F40" s="126"/>
+      <c r="G40" s="126"/>
+      <c r="H40" s="126"/>
+      <c r="I40" s="126"/>
+      <c r="J40" s="126"/>
+      <c r="K40" s="126"/>
+      <c r="L40" s="126"/>
+      <c r="M40" s="126"/>
+      <c r="N40" s="126"/>
+      <c r="O40" s="126"/>
+      <c r="P40" s="126"/>
+      <c r="Q40" s="126"/>
+      <c r="R40" s="127"/>
+      <c r="S40" s="128" t="s">
         <v>73</v>
       </c>
-      <c r="T40" s="190"/>
-      <c r="U40" s="190"/>
-      <c r="V40" s="190"/>
-      <c r="W40" s="190"/>
-      <c r="X40" s="190"/>
-      <c r="Y40" s="190"/>
-      <c r="Z40" s="190"/>
-      <c r="AA40" s="190"/>
-      <c r="AB40" s="190"/>
-      <c r="AC40" s="190"/>
-      <c r="AD40" s="190"/>
-      <c r="AE40" s="190"/>
-      <c r="AF40" s="190"/>
-      <c r="AG40" s="191"/>
-      <c r="AH40" s="220"/>
-      <c r="AI40" s="221"/>
-      <c r="AJ40" s="221"/>
-      <c r="AK40" s="221"/>
-      <c r="AL40" s="221"/>
-      <c r="AM40" s="221"/>
-      <c r="AN40" s="221"/>
-      <c r="AO40" s="221"/>
-      <c r="AP40" s="221"/>
-      <c r="AQ40" s="221"/>
-      <c r="AR40" s="221"/>
-      <c r="AS40" s="221"/>
-      <c r="AT40" s="221"/>
-      <c r="AU40" s="221"/>
-      <c r="AV40" s="221"/>
-      <c r="AW40" s="221"/>
-      <c r="AX40" s="221"/>
-      <c r="AY40" s="221"/>
-      <c r="AZ40" s="222"/>
+      <c r="T40" s="129"/>
+      <c r="U40" s="129"/>
+      <c r="V40" s="129"/>
+      <c r="W40" s="129"/>
+      <c r="X40" s="129"/>
+      <c r="Y40" s="129"/>
+      <c r="Z40" s="129"/>
+      <c r="AA40" s="129"/>
+      <c r="AB40" s="129"/>
+      <c r="AC40" s="129"/>
+      <c r="AD40" s="129"/>
+      <c r="AE40" s="129"/>
+      <c r="AF40" s="129"/>
+      <c r="AG40" s="130"/>
+      <c r="AH40" s="148"/>
+      <c r="AI40" s="149"/>
+      <c r="AJ40" s="149"/>
+      <c r="AK40" s="149"/>
+      <c r="AL40" s="149"/>
+      <c r="AM40" s="149"/>
+      <c r="AN40" s="149"/>
+      <c r="AO40" s="149"/>
+      <c r="AP40" s="149"/>
+      <c r="AQ40" s="149"/>
+      <c r="AR40" s="149"/>
+      <c r="AS40" s="149"/>
+      <c r="AT40" s="149"/>
+      <c r="AU40" s="149"/>
+      <c r="AV40" s="149"/>
+      <c r="AW40" s="149"/>
+      <c r="AX40" s="149"/>
+      <c r="AY40" s="149"/>
+      <c r="AZ40" s="150"/>
     </row>
     <row r="41" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="183"/>
-      <c r="B41" s="184"/>
-      <c r="C41" s="184"/>
-      <c r="D41" s="184"/>
-      <c r="E41" s="184"/>
-      <c r="F41" s="184"/>
-      <c r="G41" s="184"/>
-      <c r="H41" s="184"/>
-      <c r="I41" s="184"/>
-      <c r="J41" s="184"/>
-      <c r="K41" s="184"/>
-      <c r="L41" s="184"/>
-      <c r="M41" s="184"/>
-      <c r="N41" s="184"/>
-      <c r="O41" s="184"/>
-      <c r="P41" s="184"/>
-      <c r="Q41" s="184"/>
-      <c r="R41" s="185"/>
-      <c r="S41" s="189" t="s">
+      <c r="A41" s="125"/>
+      <c r="B41" s="126"/>
+      <c r="C41" s="126"/>
+      <c r="D41" s="126"/>
+      <c r="E41" s="126"/>
+      <c r="F41" s="126"/>
+      <c r="G41" s="126"/>
+      <c r="H41" s="126"/>
+      <c r="I41" s="126"/>
+      <c r="J41" s="126"/>
+      <c r="K41" s="126"/>
+      <c r="L41" s="126"/>
+      <c r="M41" s="126"/>
+      <c r="N41" s="126"/>
+      <c r="O41" s="126"/>
+      <c r="P41" s="126"/>
+      <c r="Q41" s="126"/>
+      <c r="R41" s="127"/>
+      <c r="S41" s="128" t="s">
         <v>74</v>
       </c>
-      <c r="T41" s="190"/>
-      <c r="U41" s="190"/>
-      <c r="V41" s="190"/>
-      <c r="W41" s="190"/>
-      <c r="X41" s="190"/>
-      <c r="Y41" s="190"/>
-      <c r="Z41" s="190"/>
-      <c r="AA41" s="190"/>
-      <c r="AB41" s="190"/>
-      <c r="AC41" s="190"/>
-      <c r="AD41" s="190"/>
-      <c r="AE41" s="190"/>
-      <c r="AF41" s="190"/>
-      <c r="AG41" s="191"/>
-      <c r="AH41" s="220"/>
-      <c r="AI41" s="221"/>
-      <c r="AJ41" s="221"/>
-      <c r="AK41" s="221"/>
-      <c r="AL41" s="221"/>
-      <c r="AM41" s="221"/>
-      <c r="AN41" s="221"/>
-      <c r="AO41" s="221"/>
-      <c r="AP41" s="221"/>
-      <c r="AQ41" s="221"/>
-      <c r="AR41" s="221"/>
-      <c r="AS41" s="221"/>
-      <c r="AT41" s="221"/>
-      <c r="AU41" s="221"/>
-      <c r="AV41" s="221"/>
-      <c r="AW41" s="221"/>
-      <c r="AX41" s="221"/>
-      <c r="AY41" s="221"/>
-      <c r="AZ41" s="222"/>
+      <c r="T41" s="129"/>
+      <c r="U41" s="129"/>
+      <c r="V41" s="129"/>
+      <c r="W41" s="129"/>
+      <c r="X41" s="129"/>
+      <c r="Y41" s="129"/>
+      <c r="Z41" s="129"/>
+      <c r="AA41" s="129"/>
+      <c r="AB41" s="129"/>
+      <c r="AC41" s="129"/>
+      <c r="AD41" s="129"/>
+      <c r="AE41" s="129"/>
+      <c r="AF41" s="129"/>
+      <c r="AG41" s="130"/>
+      <c r="AH41" s="148"/>
+      <c r="AI41" s="149"/>
+      <c r="AJ41" s="149"/>
+      <c r="AK41" s="149"/>
+      <c r="AL41" s="149"/>
+      <c r="AM41" s="149"/>
+      <c r="AN41" s="149"/>
+      <c r="AO41" s="149"/>
+      <c r="AP41" s="149"/>
+      <c r="AQ41" s="149"/>
+      <c r="AR41" s="149"/>
+      <c r="AS41" s="149"/>
+      <c r="AT41" s="149"/>
+      <c r="AU41" s="149"/>
+      <c r="AV41" s="149"/>
+      <c r="AW41" s="149"/>
+      <c r="AX41" s="149"/>
+      <c r="AY41" s="149"/>
+      <c r="AZ41" s="150"/>
     </row>
     <row r="42" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="223"/>
-      <c r="B42" s="224"/>
-      <c r="C42" s="224"/>
-      <c r="D42" s="224"/>
-      <c r="E42" s="224"/>
-      <c r="F42" s="224"/>
-      <c r="G42" s="224"/>
-      <c r="H42" s="224"/>
-      <c r="I42" s="224"/>
-      <c r="J42" s="224"/>
-      <c r="K42" s="224"/>
-      <c r="L42" s="224"/>
-      <c r="M42" s="224"/>
-      <c r="N42" s="224"/>
-      <c r="O42" s="224"/>
-      <c r="P42" s="224"/>
-      <c r="Q42" s="224"/>
-      <c r="R42" s="225"/>
-      <c r="S42" s="211" t="s">
+      <c r="A42" s="151"/>
+      <c r="B42" s="152"/>
+      <c r="C42" s="152"/>
+      <c r="D42" s="152"/>
+      <c r="E42" s="152"/>
+      <c r="F42" s="152"/>
+      <c r="G42" s="152"/>
+      <c r="H42" s="152"/>
+      <c r="I42" s="152"/>
+      <c r="J42" s="152"/>
+      <c r="K42" s="152"/>
+      <c r="L42" s="152"/>
+      <c r="M42" s="152"/>
+      <c r="N42" s="152"/>
+      <c r="O42" s="152"/>
+      <c r="P42" s="152"/>
+      <c r="Q42" s="152"/>
+      <c r="R42" s="153"/>
+      <c r="S42" s="137" t="s">
         <v>75</v>
       </c>
-      <c r="T42" s="212"/>
-      <c r="U42" s="212"/>
-      <c r="V42" s="212"/>
-      <c r="W42" s="212"/>
-      <c r="X42" s="212"/>
-      <c r="Y42" s="212"/>
-      <c r="Z42" s="212"/>
-      <c r="AA42" s="212"/>
-      <c r="AB42" s="212"/>
-      <c r="AC42" s="212"/>
-      <c r="AD42" s="212"/>
-      <c r="AE42" s="212"/>
-      <c r="AF42" s="212"/>
-      <c r="AG42" s="213"/>
-      <c r="AH42" s="226"/>
-      <c r="AI42" s="227"/>
-      <c r="AJ42" s="227"/>
-      <c r="AK42" s="227"/>
-      <c r="AL42" s="227"/>
-      <c r="AM42" s="227"/>
-      <c r="AN42" s="227"/>
-      <c r="AO42" s="227"/>
-      <c r="AP42" s="227"/>
-      <c r="AQ42" s="227"/>
-      <c r="AR42" s="227"/>
-      <c r="AS42" s="227"/>
-      <c r="AT42" s="227"/>
-      <c r="AU42" s="227"/>
-      <c r="AV42" s="227"/>
-      <c r="AW42" s="227"/>
-      <c r="AX42" s="227"/>
-      <c r="AY42" s="227"/>
-      <c r="AZ42" s="228"/>
+      <c r="T42" s="138"/>
+      <c r="U42" s="138"/>
+      <c r="V42" s="138"/>
+      <c r="W42" s="138"/>
+      <c r="X42" s="138"/>
+      <c r="Y42" s="138"/>
+      <c r="Z42" s="138"/>
+      <c r="AA42" s="138"/>
+      <c r="AB42" s="138"/>
+      <c r="AC42" s="138"/>
+      <c r="AD42" s="138"/>
+      <c r="AE42" s="138"/>
+      <c r="AF42" s="138"/>
+      <c r="AG42" s="139"/>
+      <c r="AH42" s="154"/>
+      <c r="AI42" s="155"/>
+      <c r="AJ42" s="155"/>
+      <c r="AK42" s="155"/>
+      <c r="AL42" s="155"/>
+      <c r="AM42" s="155"/>
+      <c r="AN42" s="155"/>
+      <c r="AO42" s="155"/>
+      <c r="AP42" s="155"/>
+      <c r="AQ42" s="155"/>
+      <c r="AR42" s="155"/>
+      <c r="AS42" s="155"/>
+      <c r="AT42" s="155"/>
+      <c r="AU42" s="155"/>
+      <c r="AV42" s="155"/>
+      <c r="AW42" s="155"/>
+      <c r="AX42" s="155"/>
+      <c r="AY42" s="155"/>
+      <c r="AZ42" s="156"/>
     </row>
     <row r="43" spans="1:52" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="99"/>
-      <c r="B43" s="99"/>
-      <c r="C43" s="99"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="99"/>
-      <c r="N43" s="99"/>
-      <c r="O43" s="99"/>
-      <c r="P43" s="99"/>
-      <c r="Q43" s="99"/>
-      <c r="R43" s="99"/>
-      <c r="S43" s="99"/>
-      <c r="T43" s="99"/>
-      <c r="U43" s="99"/>
-      <c r="V43" s="99"/>
-      <c r="W43" s="99"/>
-      <c r="X43" s="99"/>
-      <c r="Y43" s="99"/>
-      <c r="Z43" s="99"/>
-      <c r="AA43" s="99"/>
-      <c r="AB43" s="99"/>
-      <c r="AC43" s="99"/>
-      <c r="AD43" s="99"/>
-      <c r="AE43" s="99"/>
-      <c r="AF43" s="99"/>
-      <c r="AG43" s="99"/>
-      <c r="AH43" s="99"/>
-      <c r="AI43" s="99"/>
-      <c r="AJ43" s="99"/>
-      <c r="AK43" s="99"/>
-      <c r="AL43" s="99"/>
-      <c r="AM43" s="99"/>
-      <c r="AN43" s="99"/>
-      <c r="AO43" s="99"/>
-      <c r="AP43" s="99"/>
-      <c r="AQ43" s="99"/>
-      <c r="AR43" s="99"/>
-      <c r="AS43" s="99"/>
-      <c r="AT43" s="99"/>
-      <c r="AU43" s="99"/>
-      <c r="AV43" s="99"/>
-      <c r="AW43" s="99"/>
-      <c r="AX43" s="99"/>
-      <c r="AY43" s="99"/>
-      <c r="AZ43" s="99"/>
+      <c r="A43" s="146"/>
+      <c r="B43" s="146"/>
+      <c r="C43" s="146"/>
+      <c r="D43" s="146"/>
+      <c r="E43" s="146"/>
+      <c r="F43" s="146"/>
+      <c r="G43" s="146"/>
+      <c r="H43" s="146"/>
+      <c r="I43" s="146"/>
+      <c r="J43" s="146"/>
+      <c r="K43" s="146"/>
+      <c r="L43" s="146"/>
+      <c r="M43" s="146"/>
+      <c r="N43" s="146"/>
+      <c r="O43" s="146"/>
+      <c r="P43" s="146"/>
+      <c r="Q43" s="146"/>
+      <c r="R43" s="146"/>
+      <c r="S43" s="146"/>
+      <c r="T43" s="146"/>
+      <c r="U43" s="146"/>
+      <c r="V43" s="146"/>
+      <c r="W43" s="146"/>
+      <c r="X43" s="146"/>
+      <c r="Y43" s="146"/>
+      <c r="Z43" s="146"/>
+      <c r="AA43" s="146"/>
+      <c r="AB43" s="146"/>
+      <c r="AC43" s="146"/>
+      <c r="AD43" s="146"/>
+      <c r="AE43" s="146"/>
+      <c r="AF43" s="146"/>
+      <c r="AG43" s="146"/>
+      <c r="AH43" s="146"/>
+      <c r="AI43" s="146"/>
+      <c r="AJ43" s="146"/>
+      <c r="AK43" s="146"/>
+      <c r="AL43" s="146"/>
+      <c r="AM43" s="146"/>
+      <c r="AN43" s="146"/>
+      <c r="AO43" s="146"/>
+      <c r="AP43" s="146"/>
+      <c r="AQ43" s="146"/>
+      <c r="AR43" s="146"/>
+      <c r="AS43" s="146"/>
+      <c r="AT43" s="146"/>
+      <c r="AU43" s="146"/>
+      <c r="AV43" s="146"/>
+      <c r="AW43" s="146"/>
+      <c r="AX43" s="146"/>
+      <c r="AY43" s="146"/>
+      <c r="AZ43" s="146"/>
     </row>
     <row r="44" spans="1:52" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="214" t="s">
+      <c r="A44" s="140" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="215"/>
-      <c r="C44" s="215"/>
-      <c r="D44" s="215"/>
-      <c r="E44" s="215"/>
-      <c r="F44" s="215"/>
-      <c r="G44" s="215"/>
-      <c r="H44" s="215"/>
-      <c r="I44" s="215"/>
-      <c r="J44" s="215"/>
-      <c r="K44" s="215"/>
-      <c r="L44" s="215"/>
-      <c r="M44" s="215"/>
-      <c r="N44" s="215"/>
-      <c r="O44" s="215"/>
-      <c r="P44" s="215"/>
-      <c r="Q44" s="215"/>
-      <c r="R44" s="215"/>
-      <c r="S44" s="215"/>
-      <c r="T44" s="215"/>
-      <c r="U44" s="215"/>
-      <c r="V44" s="215"/>
-      <c r="W44" s="215"/>
-      <c r="X44" s="215"/>
-      <c r="Y44" s="215"/>
-      <c r="Z44" s="215"/>
-      <c r="AA44" s="215"/>
-      <c r="AB44" s="215"/>
-      <c r="AC44" s="215"/>
-      <c r="AD44" s="215"/>
-      <c r="AE44" s="215"/>
-      <c r="AF44" s="215"/>
-      <c r="AG44" s="215"/>
-      <c r="AH44" s="215"/>
-      <c r="AI44" s="215"/>
-      <c r="AJ44" s="215"/>
-      <c r="AK44" s="215"/>
-      <c r="AL44" s="215"/>
-      <c r="AM44" s="215"/>
-      <c r="AN44" s="215"/>
-      <c r="AO44" s="215"/>
-      <c r="AP44" s="215"/>
-      <c r="AQ44" s="215"/>
-      <c r="AR44" s="215"/>
-      <c r="AS44" s="215"/>
-      <c r="AT44" s="215"/>
-      <c r="AU44" s="215"/>
-      <c r="AV44" s="215"/>
-      <c r="AW44" s="215"/>
-      <c r="AX44" s="215"/>
-      <c r="AY44" s="215"/>
-      <c r="AZ44" s="216"/>
+      <c r="B44" s="141"/>
+      <c r="C44" s="141"/>
+      <c r="D44" s="141"/>
+      <c r="E44" s="141"/>
+      <c r="F44" s="141"/>
+      <c r="G44" s="141"/>
+      <c r="H44" s="141"/>
+      <c r="I44" s="141"/>
+      <c r="J44" s="141"/>
+      <c r="K44" s="141"/>
+      <c r="L44" s="141"/>
+      <c r="M44" s="141"/>
+      <c r="N44" s="141"/>
+      <c r="O44" s="141"/>
+      <c r="P44" s="141"/>
+      <c r="Q44" s="141"/>
+      <c r="R44" s="141"/>
+      <c r="S44" s="141"/>
+      <c r="T44" s="141"/>
+      <c r="U44" s="141"/>
+      <c r="V44" s="141"/>
+      <c r="W44" s="141"/>
+      <c r="X44" s="141"/>
+      <c r="Y44" s="141"/>
+      <c r="Z44" s="141"/>
+      <c r="AA44" s="141"/>
+      <c r="AB44" s="141"/>
+      <c r="AC44" s="141"/>
+      <c r="AD44" s="141"/>
+      <c r="AE44" s="141"/>
+      <c r="AF44" s="141"/>
+      <c r="AG44" s="141"/>
+      <c r="AH44" s="141"/>
+      <c r="AI44" s="141"/>
+      <c r="AJ44" s="141"/>
+      <c r="AK44" s="141"/>
+      <c r="AL44" s="141"/>
+      <c r="AM44" s="141"/>
+      <c r="AN44" s="141"/>
+      <c r="AO44" s="141"/>
+      <c r="AP44" s="141"/>
+      <c r="AQ44" s="141"/>
+      <c r="AR44" s="141"/>
+      <c r="AS44" s="141"/>
+      <c r="AT44" s="141"/>
+      <c r="AU44" s="141"/>
+      <c r="AV44" s="141"/>
+      <c r="AW44" s="141"/>
+      <c r="AX44" s="141"/>
+      <c r="AY44" s="141"/>
+      <c r="AZ44" s="142"/>
     </row>
     <row r="45" spans="1:52" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="217"/>
-      <c r="B45" s="218"/>
-      <c r="C45" s="218"/>
-      <c r="D45" s="218"/>
-      <c r="E45" s="218"/>
-      <c r="F45" s="218"/>
-      <c r="G45" s="218"/>
-      <c r="H45" s="218"/>
-      <c r="I45" s="218"/>
-      <c r="J45" s="218"/>
-      <c r="K45" s="218"/>
-      <c r="L45" s="218"/>
-      <c r="M45" s="218"/>
-      <c r="N45" s="218"/>
-      <c r="O45" s="218"/>
-      <c r="P45" s="218"/>
-      <c r="Q45" s="218"/>
-      <c r="R45" s="218"/>
-      <c r="S45" s="218"/>
-      <c r="T45" s="218"/>
-      <c r="U45" s="218"/>
-      <c r="V45" s="218"/>
-      <c r="W45" s="218"/>
-      <c r="X45" s="218"/>
-      <c r="Y45" s="218"/>
-      <c r="Z45" s="218"/>
-      <c r="AA45" s="218"/>
-      <c r="AB45" s="218"/>
-      <c r="AC45" s="218"/>
-      <c r="AD45" s="218"/>
-      <c r="AE45" s="218"/>
-      <c r="AF45" s="218"/>
-      <c r="AG45" s="218"/>
-      <c r="AH45" s="218"/>
-      <c r="AI45" s="218"/>
-      <c r="AJ45" s="218"/>
-      <c r="AK45" s="218"/>
-      <c r="AL45" s="218"/>
-      <c r="AM45" s="218"/>
-      <c r="AN45" s="218"/>
-      <c r="AO45" s="218"/>
-      <c r="AP45" s="218"/>
-      <c r="AQ45" s="218"/>
-      <c r="AR45" s="218"/>
-      <c r="AS45" s="218"/>
-      <c r="AT45" s="218"/>
-      <c r="AU45" s="218"/>
-      <c r="AV45" s="218"/>
-      <c r="AW45" s="218"/>
-      <c r="AX45" s="218"/>
-      <c r="AY45" s="218"/>
-      <c r="AZ45" s="219"/>
+      <c r="A45" s="143"/>
+      <c r="B45" s="144"/>
+      <c r="C45" s="144"/>
+      <c r="D45" s="144"/>
+      <c r="E45" s="144"/>
+      <c r="F45" s="144"/>
+      <c r="G45" s="144"/>
+      <c r="H45" s="144"/>
+      <c r="I45" s="144"/>
+      <c r="J45" s="144"/>
+      <c r="K45" s="144"/>
+      <c r="L45" s="144"/>
+      <c r="M45" s="144"/>
+      <c r="N45" s="144"/>
+      <c r="O45" s="144"/>
+      <c r="P45" s="144"/>
+      <c r="Q45" s="144"/>
+      <c r="R45" s="144"/>
+      <c r="S45" s="144"/>
+      <c r="T45" s="144"/>
+      <c r="U45" s="144"/>
+      <c r="V45" s="144"/>
+      <c r="W45" s="144"/>
+      <c r="X45" s="144"/>
+      <c r="Y45" s="144"/>
+      <c r="Z45" s="144"/>
+      <c r="AA45" s="144"/>
+      <c r="AB45" s="144"/>
+      <c r="AC45" s="144"/>
+      <c r="AD45" s="144"/>
+      <c r="AE45" s="144"/>
+      <c r="AF45" s="144"/>
+      <c r="AG45" s="144"/>
+      <c r="AH45" s="144"/>
+      <c r="AI45" s="144"/>
+      <c r="AJ45" s="144"/>
+      <c r="AK45" s="144"/>
+      <c r="AL45" s="144"/>
+      <c r="AM45" s="144"/>
+      <c r="AN45" s="144"/>
+      <c r="AO45" s="144"/>
+      <c r="AP45" s="144"/>
+      <c r="AQ45" s="144"/>
+      <c r="AR45" s="144"/>
+      <c r="AS45" s="144"/>
+      <c r="AT45" s="144"/>
+      <c r="AU45" s="144"/>
+      <c r="AV45" s="144"/>
+      <c r="AW45" s="144"/>
+      <c r="AX45" s="144"/>
+      <c r="AY45" s="144"/>
+      <c r="AZ45" s="145"/>
     </row>
     <row r="46" spans="1:52" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
@@ -7963,174 +7915,174 @@
       <c r="AZ46"/>
     </row>
     <row r="47" spans="1:52" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="117"/>
-      <c r="B47" s="117"/>
-      <c r="C47" s="117"/>
-      <c r="D47" s="117"/>
-      <c r="E47" s="117"/>
-      <c r="F47" s="117"/>
-      <c r="G47" s="117"/>
-      <c r="H47" s="117"/>
-      <c r="I47" s="117"/>
-      <c r="J47" s="117"/>
-      <c r="K47" s="117"/>
-      <c r="L47" s="117"/>
-      <c r="M47" s="117"/>
-      <c r="N47" s="117"/>
-      <c r="O47" s="117"/>
-      <c r="P47" s="117"/>
+      <c r="A47" s="147"/>
+      <c r="B47" s="147"/>
+      <c r="C47" s="147"/>
+      <c r="D47" s="147"/>
+      <c r="E47" s="147"/>
+      <c r="F47" s="147"/>
+      <c r="G47" s="147"/>
+      <c r="H47" s="147"/>
+      <c r="I47" s="147"/>
+      <c r="J47" s="147"/>
+      <c r="K47" s="147"/>
+      <c r="L47" s="147"/>
+      <c r="M47" s="147"/>
+      <c r="N47" s="147"/>
+      <c r="O47" s="147"/>
+      <c r="P47" s="147"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
-      <c r="S47" s="117"/>
-      <c r="T47" s="117"/>
-      <c r="U47" s="117"/>
-      <c r="V47" s="117"/>
-      <c r="W47" s="117"/>
-      <c r="X47" s="117"/>
-      <c r="Y47" s="117"/>
-      <c r="Z47" s="117"/>
-      <c r="AA47" s="117"/>
-      <c r="AB47" s="117"/>
-      <c r="AC47" s="117"/>
-      <c r="AD47" s="117"/>
-      <c r="AE47" s="117"/>
-      <c r="AF47" s="117"/>
-      <c r="AG47" s="117"/>
-      <c r="AH47" s="117"/>
+      <c r="S47" s="147"/>
+      <c r="T47" s="147"/>
+      <c r="U47" s="147"/>
+      <c r="V47" s="147"/>
+      <c r="W47" s="147"/>
+      <c r="X47" s="147"/>
+      <c r="Y47" s="147"/>
+      <c r="Z47" s="147"/>
+      <c r="AA47" s="147"/>
+      <c r="AB47" s="147"/>
+      <c r="AC47" s="147"/>
+      <c r="AD47" s="147"/>
+      <c r="AE47" s="147"/>
+      <c r="AF47" s="147"/>
+      <c r="AG47" s="147"/>
+      <c r="AH47" s="147"/>
       <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
-      <c r="AK47" s="117"/>
-      <c r="AL47" s="117"/>
-      <c r="AM47" s="117"/>
-      <c r="AN47" s="117"/>
-      <c r="AO47" s="117"/>
-      <c r="AP47" s="117"/>
-      <c r="AQ47" s="117"/>
-      <c r="AR47" s="117"/>
-      <c r="AS47" s="117"/>
-      <c r="AT47" s="117"/>
-      <c r="AU47" s="117"/>
-      <c r="AV47" s="117"/>
-      <c r="AW47" s="117"/>
-      <c r="AX47" s="117"/>
-      <c r="AY47" s="117"/>
-      <c r="AZ47" s="117"/>
+      <c r="AK47" s="147"/>
+      <c r="AL47" s="147"/>
+      <c r="AM47" s="147"/>
+      <c r="AN47" s="147"/>
+      <c r="AO47" s="147"/>
+      <c r="AP47" s="147"/>
+      <c r="AQ47" s="147"/>
+      <c r="AR47" s="147"/>
+      <c r="AS47" s="147"/>
+      <c r="AT47" s="147"/>
+      <c r="AU47" s="147"/>
+      <c r="AV47" s="147"/>
+      <c r="AW47" s="147"/>
+      <c r="AX47" s="147"/>
+      <c r="AY47" s="147"/>
+      <c r="AZ47" s="147"/>
     </row>
     <row r="48" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="118" t="s">
+      <c r="A48" s="211" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="118"/>
-      <c r="C48" s="118"/>
-      <c r="D48" s="118"/>
-      <c r="E48" s="118"/>
-      <c r="F48" s="118"/>
-      <c r="G48" s="118"/>
-      <c r="H48" s="118"/>
-      <c r="I48" s="118"/>
-      <c r="J48" s="118"/>
-      <c r="K48" s="118"/>
-      <c r="L48" s="118"/>
-      <c r="M48" s="118"/>
-      <c r="N48" s="118"/>
-      <c r="O48" s="118"/>
-      <c r="P48" s="118"/>
+      <c r="B48" s="211"/>
+      <c r="C48" s="211"/>
+      <c r="D48" s="211"/>
+      <c r="E48" s="211"/>
+      <c r="F48" s="211"/>
+      <c r="G48" s="211"/>
+      <c r="H48" s="211"/>
+      <c r="I48" s="211"/>
+      <c r="J48" s="211"/>
+      <c r="K48" s="211"/>
+      <c r="L48" s="211"/>
+      <c r="M48" s="211"/>
+      <c r="N48" s="211"/>
+      <c r="O48" s="211"/>
+      <c r="P48" s="211"/>
       <c r="Q48" s="54"/>
       <c r="R48" s="54"/>
-      <c r="S48" s="195" t="s">
+      <c r="S48" s="122" t="s">
         <v>78</v>
       </c>
-      <c r="T48" s="195"/>
-      <c r="U48" s="195"/>
-      <c r="V48" s="195"/>
-      <c r="W48" s="195"/>
-      <c r="X48" s="195"/>
-      <c r="Y48" s="195"/>
-      <c r="Z48" s="195"/>
-      <c r="AA48" s="195"/>
-      <c r="AB48" s="195"/>
-      <c r="AC48" s="195"/>
-      <c r="AD48" s="195"/>
-      <c r="AE48" s="195"/>
-      <c r="AF48" s="195"/>
-      <c r="AG48" s="195"/>
-      <c r="AH48" s="195"/>
+      <c r="T48" s="122"/>
+      <c r="U48" s="122"/>
+      <c r="V48" s="122"/>
+      <c r="W48" s="122"/>
+      <c r="X48" s="122"/>
+      <c r="Y48" s="122"/>
+      <c r="Z48" s="122"/>
+      <c r="AA48" s="122"/>
+      <c r="AB48" s="122"/>
+      <c r="AC48" s="122"/>
+      <c r="AD48" s="122"/>
+      <c r="AE48" s="122"/>
+      <c r="AF48" s="122"/>
+      <c r="AG48" s="122"/>
+      <c r="AH48" s="122"/>
       <c r="AI48" s="54"/>
       <c r="AJ48" s="54"/>
-      <c r="AK48" s="118" t="s">
+      <c r="AK48" s="211" t="s">
         <v>79</v>
       </c>
-      <c r="AL48" s="118"/>
-      <c r="AM48" s="118"/>
-      <c r="AN48" s="118"/>
-      <c r="AO48" s="118"/>
-      <c r="AP48" s="118"/>
-      <c r="AQ48" s="118"/>
-      <c r="AR48" s="118"/>
-      <c r="AS48" s="118"/>
-      <c r="AT48" s="118"/>
-      <c r="AU48" s="118"/>
-      <c r="AV48" s="118"/>
-      <c r="AW48" s="118"/>
-      <c r="AX48" s="118"/>
-      <c r="AY48" s="118"/>
-      <c r="AZ48" s="118"/>
+      <c r="AL48" s="211"/>
+      <c r="AM48" s="211"/>
+      <c r="AN48" s="211"/>
+      <c r="AO48" s="211"/>
+      <c r="AP48" s="211"/>
+      <c r="AQ48" s="211"/>
+      <c r="AR48" s="211"/>
+      <c r="AS48" s="211"/>
+      <c r="AT48" s="211"/>
+      <c r="AU48" s="211"/>
+      <c r="AV48" s="211"/>
+      <c r="AW48" s="211"/>
+      <c r="AX48" s="211"/>
+      <c r="AY48" s="211"/>
+      <c r="AZ48" s="211"/>
     </row>
     <row r="49" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="120" t="s">
+      <c r="A49" s="89" t="s">
         <v>80</v>
       </c>
-      <c r="B49" s="120"/>
-      <c r="C49" s="120"/>
-      <c r="D49" s="120"/>
-      <c r="E49" s="120"/>
-      <c r="F49" s="120"/>
-      <c r="G49" s="120"/>
-      <c r="H49" s="120"/>
-      <c r="I49" s="120"/>
-      <c r="J49" s="120"/>
-      <c r="K49" s="120"/>
-      <c r="L49" s="120"/>
-      <c r="M49" s="120"/>
-      <c r="N49" s="120"/>
-      <c r="O49" s="120"/>
-      <c r="P49" s="120"/>
-      <c r="S49" s="120" t="s">
+      <c r="B49" s="89"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="89"/>
+      <c r="E49" s="89"/>
+      <c r="F49" s="89"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="89"/>
+      <c r="I49" s="89"/>
+      <c r="J49" s="89"/>
+      <c r="K49" s="89"/>
+      <c r="L49" s="89"/>
+      <c r="M49" s="89"/>
+      <c r="N49" s="89"/>
+      <c r="O49" s="89"/>
+      <c r="P49" s="89"/>
+      <c r="S49" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="T49" s="120"/>
-      <c r="U49" s="120"/>
-      <c r="V49" s="120"/>
-      <c r="W49" s="120"/>
-      <c r="X49" s="120"/>
-      <c r="Y49" s="120"/>
-      <c r="Z49" s="120"/>
-      <c r="AA49" s="120"/>
-      <c r="AB49" s="120"/>
-      <c r="AC49" s="120"/>
-      <c r="AD49" s="120"/>
-      <c r="AE49" s="120"/>
-      <c r="AF49" s="120"/>
-      <c r="AG49" s="120"/>
-      <c r="AH49" s="120"/>
-      <c r="AK49" s="119" t="s">
+      <c r="T49" s="89"/>
+      <c r="U49" s="89"/>
+      <c r="V49" s="89"/>
+      <c r="W49" s="89"/>
+      <c r="X49" s="89"/>
+      <c r="Y49" s="89"/>
+      <c r="Z49" s="89"/>
+      <c r="AA49" s="89"/>
+      <c r="AB49" s="89"/>
+      <c r="AC49" s="89"/>
+      <c r="AD49" s="89"/>
+      <c r="AE49" s="89"/>
+      <c r="AF49" s="89"/>
+      <c r="AG49" s="89"/>
+      <c r="AH49" s="89"/>
+      <c r="AK49" s="212" t="s">
         <v>792</v>
       </c>
-      <c r="AL49" s="119"/>
-      <c r="AM49" s="119"/>
-      <c r="AN49" s="119"/>
-      <c r="AO49" s="119"/>
-      <c r="AP49" s="119"/>
-      <c r="AQ49" s="119"/>
-      <c r="AR49" s="119"/>
-      <c r="AS49" s="119"/>
-      <c r="AT49" s="119"/>
-      <c r="AU49" s="119"/>
-      <c r="AV49" s="119"/>
-      <c r="AW49" s="119"/>
-      <c r="AX49" s="119"/>
-      <c r="AY49" s="119"/>
-      <c r="AZ49" s="119"/>
+      <c r="AL49" s="212"/>
+      <c r="AM49" s="212"/>
+      <c r="AN49" s="212"/>
+      <c r="AO49" s="212"/>
+      <c r="AP49" s="212"/>
+      <c r="AQ49" s="212"/>
+      <c r="AR49" s="212"/>
+      <c r="AS49" s="212"/>
+      <c r="AT49" s="212"/>
+      <c r="AU49" s="212"/>
+      <c r="AV49" s="212"/>
+      <c r="AW49" s="212"/>
+      <c r="AX49" s="212"/>
+      <c r="AY49" s="212"/>
+      <c r="AZ49" s="212"/>
     </row>
     <row r="50" spans="1:52" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
@@ -9600,6 +9552,153 @@
   </sortState>
   <dataConsolidate function="count"/>
   <mergeCells count="171">
+    <mergeCell ref="R18:V18"/>
+    <mergeCell ref="M18:Q18"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="AV19:AZ19"/>
+    <mergeCell ref="A32:AZ32"/>
+    <mergeCell ref="A26:AZ26"/>
+    <mergeCell ref="A27:AZ27"/>
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="T28:Z28"/>
+    <mergeCell ref="AA28:AS28"/>
+    <mergeCell ref="AT28:AZ28"/>
+    <mergeCell ref="A29:S29"/>
+    <mergeCell ref="T29:Z29"/>
+    <mergeCell ref="AA29:AS29"/>
+    <mergeCell ref="AT29:AZ29"/>
+    <mergeCell ref="A30:S30"/>
+    <mergeCell ref="T30:Z30"/>
+    <mergeCell ref="AA30:AS30"/>
+    <mergeCell ref="AT30:AZ30"/>
+    <mergeCell ref="A31:S31"/>
+    <mergeCell ref="T31:Z31"/>
+    <mergeCell ref="AA31:AS31"/>
+    <mergeCell ref="AT31:AZ31"/>
+    <mergeCell ref="AV22:AZ22"/>
+    <mergeCell ref="A47:P47"/>
+    <mergeCell ref="AK47:AZ47"/>
+    <mergeCell ref="AK48:AZ48"/>
+    <mergeCell ref="A48:P48"/>
+    <mergeCell ref="AK49:AZ49"/>
+    <mergeCell ref="A49:P49"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="M23:Q23"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="AB19:AF19"/>
+    <mergeCell ref="AB20:AF20"/>
+    <mergeCell ref="W19:AA19"/>
+    <mergeCell ref="AB22:AF22"/>
+    <mergeCell ref="AB23:AF23"/>
+    <mergeCell ref="AB24:AF24"/>
+    <mergeCell ref="Z7:AP7"/>
+    <mergeCell ref="AV23:AZ23"/>
+    <mergeCell ref="AQ19:AU19"/>
+    <mergeCell ref="AQ20:AU20"/>
+    <mergeCell ref="AQ21:AU21"/>
+    <mergeCell ref="AQ22:AU22"/>
+    <mergeCell ref="AQ23:AU23"/>
+    <mergeCell ref="W20:AA20"/>
+    <mergeCell ref="W21:AA21"/>
+    <mergeCell ref="W22:AA22"/>
+    <mergeCell ref="W23:AA23"/>
+    <mergeCell ref="AL19:AP19"/>
+    <mergeCell ref="AL20:AP20"/>
+    <mergeCell ref="AL21:AP21"/>
+    <mergeCell ref="AL22:AP22"/>
+    <mergeCell ref="AL23:AP23"/>
+    <mergeCell ref="AG19:AK19"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="AS1:AZ3"/>
+    <mergeCell ref="G6:AZ6"/>
+    <mergeCell ref="K2:AP2"/>
+    <mergeCell ref="A4:AZ4"/>
+    <mergeCell ref="AL9:AZ9"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="R17:V17"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="AE5:AK5"/>
+    <mergeCell ref="G5:AB5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="G8:AC8"/>
+    <mergeCell ref="V7:Y7"/>
+    <mergeCell ref="G9:AC9"/>
+    <mergeCell ref="AL8:AZ8"/>
+    <mergeCell ref="AL5:AZ5"/>
+    <mergeCell ref="A38:R38"/>
+    <mergeCell ref="AR7:AU7"/>
+    <mergeCell ref="AE8:AK8"/>
+    <mergeCell ref="AV7:AZ7"/>
+    <mergeCell ref="S40:AG40"/>
+    <mergeCell ref="A39:R39"/>
+    <mergeCell ref="R19:V19"/>
+    <mergeCell ref="R20:V20"/>
+    <mergeCell ref="R21:V21"/>
+    <mergeCell ref="R22:V22"/>
+    <mergeCell ref="R23:V23"/>
+    <mergeCell ref="R24:V24"/>
+    <mergeCell ref="AG20:AK20"/>
+    <mergeCell ref="AG21:AK21"/>
+    <mergeCell ref="AG22:AK22"/>
+    <mergeCell ref="AG23:AK23"/>
+    <mergeCell ref="AG18:AK18"/>
+    <mergeCell ref="AB18:AF18"/>
+    <mergeCell ref="AB21:AF21"/>
+    <mergeCell ref="W18:AA18"/>
+    <mergeCell ref="A15:AZ15"/>
+    <mergeCell ref="AG24:AK24"/>
+    <mergeCell ref="AV20:AZ20"/>
+    <mergeCell ref="AV21:AZ21"/>
+    <mergeCell ref="R25:V25"/>
+    <mergeCell ref="AV24:AZ24"/>
+    <mergeCell ref="AV25:AZ25"/>
+    <mergeCell ref="AQ24:AU24"/>
+    <mergeCell ref="AQ25:AU25"/>
+    <mergeCell ref="W24:AA24"/>
+    <mergeCell ref="W25:AA25"/>
+    <mergeCell ref="AL24:AP24"/>
+    <mergeCell ref="AL25:AP25"/>
+    <mergeCell ref="AB25:AF25"/>
+    <mergeCell ref="AG25:AK25"/>
+    <mergeCell ref="S48:AH48"/>
+    <mergeCell ref="S33:AG34"/>
+    <mergeCell ref="AH36:AZ36"/>
+    <mergeCell ref="A36:R36"/>
+    <mergeCell ref="A37:R37"/>
+    <mergeCell ref="A35:R35"/>
+    <mergeCell ref="S35:AG35"/>
+    <mergeCell ref="A33:R34"/>
+    <mergeCell ref="S42:AG42"/>
+    <mergeCell ref="S41:AG41"/>
+    <mergeCell ref="A44:AZ45"/>
+    <mergeCell ref="A43:AZ43"/>
+    <mergeCell ref="S47:AH47"/>
+    <mergeCell ref="AH39:AZ39"/>
+    <mergeCell ref="S36:AG36"/>
+    <mergeCell ref="A40:R40"/>
+    <mergeCell ref="A42:R42"/>
+    <mergeCell ref="S39:AG39"/>
+    <mergeCell ref="S38:AG38"/>
+    <mergeCell ref="S37:AG37"/>
+    <mergeCell ref="AH42:AZ42"/>
+    <mergeCell ref="AH41:AZ41"/>
+    <mergeCell ref="AH40:AZ40"/>
+    <mergeCell ref="A41:R41"/>
     <mergeCell ref="S49:U49"/>
     <mergeCell ref="V49:AH49"/>
     <mergeCell ref="BD21:BE21"/>
@@ -9624,153 +9723,6 @@
     <mergeCell ref="AV18:AZ18"/>
     <mergeCell ref="AQ18:AU18"/>
     <mergeCell ref="AL18:AP18"/>
-    <mergeCell ref="S48:AH48"/>
-    <mergeCell ref="S33:AG34"/>
-    <mergeCell ref="AH36:AZ36"/>
-    <mergeCell ref="A36:R36"/>
-    <mergeCell ref="A37:R37"/>
-    <mergeCell ref="A35:R35"/>
-    <mergeCell ref="S35:AG35"/>
-    <mergeCell ref="A33:R34"/>
-    <mergeCell ref="S42:AG42"/>
-    <mergeCell ref="S41:AG41"/>
-    <mergeCell ref="A44:AZ45"/>
-    <mergeCell ref="A43:AZ43"/>
-    <mergeCell ref="S47:AH47"/>
-    <mergeCell ref="AH39:AZ39"/>
-    <mergeCell ref="S36:AG36"/>
-    <mergeCell ref="A40:R40"/>
-    <mergeCell ref="A42:R42"/>
-    <mergeCell ref="S39:AG39"/>
-    <mergeCell ref="S38:AG38"/>
-    <mergeCell ref="S37:AG37"/>
-    <mergeCell ref="AH42:AZ42"/>
-    <mergeCell ref="AH41:AZ41"/>
-    <mergeCell ref="AH40:AZ40"/>
-    <mergeCell ref="A41:R41"/>
-    <mergeCell ref="R25:V25"/>
-    <mergeCell ref="AV24:AZ24"/>
-    <mergeCell ref="AV25:AZ25"/>
-    <mergeCell ref="AQ24:AU24"/>
-    <mergeCell ref="AQ25:AU25"/>
-    <mergeCell ref="W24:AA24"/>
-    <mergeCell ref="W25:AA25"/>
-    <mergeCell ref="AL24:AP24"/>
-    <mergeCell ref="AL25:AP25"/>
-    <mergeCell ref="AB25:AF25"/>
-    <mergeCell ref="AG25:AK25"/>
-    <mergeCell ref="A38:R38"/>
-    <mergeCell ref="AR7:AU7"/>
-    <mergeCell ref="AE8:AK8"/>
-    <mergeCell ref="AV7:AZ7"/>
-    <mergeCell ref="S40:AG40"/>
-    <mergeCell ref="A39:R39"/>
-    <mergeCell ref="R19:V19"/>
-    <mergeCell ref="R20:V20"/>
-    <mergeCell ref="R21:V21"/>
-    <mergeCell ref="R22:V22"/>
-    <mergeCell ref="R23:V23"/>
-    <mergeCell ref="R24:V24"/>
-    <mergeCell ref="AG20:AK20"/>
-    <mergeCell ref="AG21:AK21"/>
-    <mergeCell ref="AG22:AK22"/>
-    <mergeCell ref="AG23:AK23"/>
-    <mergeCell ref="AG18:AK18"/>
-    <mergeCell ref="AB18:AF18"/>
-    <mergeCell ref="AB21:AF21"/>
-    <mergeCell ref="W18:AA18"/>
-    <mergeCell ref="A15:AZ15"/>
-    <mergeCell ref="AG24:AK24"/>
-    <mergeCell ref="AV20:AZ20"/>
-    <mergeCell ref="AV21:AZ21"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="AS1:AZ3"/>
-    <mergeCell ref="G6:AZ6"/>
-    <mergeCell ref="K2:AP2"/>
-    <mergeCell ref="A4:AZ4"/>
-    <mergeCell ref="AL9:AZ9"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="R17:V17"/>
-    <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="AE5:AK5"/>
-    <mergeCell ref="G5:AB5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="G8:AC8"/>
-    <mergeCell ref="V7:Y7"/>
-    <mergeCell ref="G9:AC9"/>
-    <mergeCell ref="AL8:AZ8"/>
-    <mergeCell ref="AL5:AZ5"/>
-    <mergeCell ref="AB23:AF23"/>
-    <mergeCell ref="AB24:AF24"/>
-    <mergeCell ref="Z7:AP7"/>
-    <mergeCell ref="AV23:AZ23"/>
-    <mergeCell ref="AQ19:AU19"/>
-    <mergeCell ref="AQ20:AU20"/>
-    <mergeCell ref="AQ21:AU21"/>
-    <mergeCell ref="AQ22:AU22"/>
-    <mergeCell ref="AQ23:AU23"/>
-    <mergeCell ref="W20:AA20"/>
-    <mergeCell ref="W21:AA21"/>
-    <mergeCell ref="W22:AA22"/>
-    <mergeCell ref="W23:AA23"/>
-    <mergeCell ref="AL19:AP19"/>
-    <mergeCell ref="AL20:AP20"/>
-    <mergeCell ref="AL21:AP21"/>
-    <mergeCell ref="AL22:AP22"/>
-    <mergeCell ref="AL23:AP23"/>
-    <mergeCell ref="AG19:AK19"/>
-    <mergeCell ref="A47:P47"/>
-    <mergeCell ref="AK47:AZ47"/>
-    <mergeCell ref="AK48:AZ48"/>
-    <mergeCell ref="A48:P48"/>
-    <mergeCell ref="AK49:AZ49"/>
-    <mergeCell ref="A49:P49"/>
-    <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="M21:Q21"/>
-    <mergeCell ref="M22:Q22"/>
-    <mergeCell ref="M23:Q23"/>
-    <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="M25:Q25"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A21:L21"/>
-    <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="AB19:AF19"/>
-    <mergeCell ref="AB20:AF20"/>
-    <mergeCell ref="W19:AA19"/>
-    <mergeCell ref="AB22:AF22"/>
-    <mergeCell ref="R18:V18"/>
-    <mergeCell ref="M18:Q18"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="AV19:AZ19"/>
-    <mergeCell ref="A32:AZ32"/>
-    <mergeCell ref="A26:AZ26"/>
-    <mergeCell ref="A27:AZ27"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="T28:Z28"/>
-    <mergeCell ref="AA28:AS28"/>
-    <mergeCell ref="AT28:AZ28"/>
-    <mergeCell ref="A29:S29"/>
-    <mergeCell ref="T29:Z29"/>
-    <mergeCell ref="AA29:AS29"/>
-    <mergeCell ref="AT29:AZ29"/>
-    <mergeCell ref="A30:S30"/>
-    <mergeCell ref="T30:Z30"/>
-    <mergeCell ref="AA30:AS30"/>
-    <mergeCell ref="AT30:AZ30"/>
-    <mergeCell ref="A31:S31"/>
-    <mergeCell ref="T31:Z31"/>
-    <mergeCell ref="AA31:AS31"/>
-    <mergeCell ref="AT31:AZ31"/>
-    <mergeCell ref="AV22:AZ22"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations count="1">
@@ -9810,14 +9762,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="137"/>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="139"/>
+      <c r="A1" s="168"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
+      <c r="H1" s="170"/>
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
       <c r="K1" s="21"/>
@@ -9854,87 +9806,87 @@
       <c r="AP1" s="22"/>
       <c r="AQ1" s="22"/>
       <c r="AR1" s="22"/>
-      <c r="AS1" s="146" t="s">
+      <c r="AS1" s="177" t="s">
         <v>0</v>
       </c>
-      <c r="AT1" s="147"/>
-      <c r="AU1" s="147"/>
-      <c r="AV1" s="147"/>
-      <c r="AW1" s="147"/>
-      <c r="AX1" s="147"/>
-      <c r="AY1" s="147"/>
-      <c r="AZ1" s="148"/>
+      <c r="AT1" s="178"/>
+      <c r="AU1" s="178"/>
+      <c r="AV1" s="178"/>
+      <c r="AW1" s="178"/>
+      <c r="AX1" s="178"/>
+      <c r="AY1" s="178"/>
+      <c r="AZ1" s="179"/>
       <c r="BD1" s="23"/>
       <c r="BF1" s="27"/>
       <c r="BG1" s="27"/>
     </row>
     <row r="2" spans="1:60" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="140"/>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="142"/>
-      <c r="K2" s="156" t="s">
+      <c r="A2" s="171"/>
+      <c r="B2" s="172"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="173"/>
+      <c r="K2" s="187" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="246"/>
-      <c r="M2" s="246"/>
-      <c r="N2" s="246"/>
-      <c r="O2" s="246"/>
-      <c r="P2" s="246"/>
-      <c r="Q2" s="246"/>
-      <c r="R2" s="246"/>
-      <c r="S2" s="246"/>
-      <c r="T2" s="246"/>
-      <c r="U2" s="246"/>
-      <c r="V2" s="246"/>
-      <c r="W2" s="246"/>
-      <c r="X2" s="246"/>
-      <c r="Y2" s="246"/>
-      <c r="Z2" s="246"/>
-      <c r="AA2" s="246"/>
-      <c r="AB2" s="246"/>
-      <c r="AC2" s="246"/>
-      <c r="AD2" s="246"/>
-      <c r="AE2" s="246"/>
-      <c r="AF2" s="246"/>
-      <c r="AG2" s="246"/>
-      <c r="AH2" s="246"/>
-      <c r="AI2" s="246"/>
-      <c r="AJ2" s="246"/>
-      <c r="AK2" s="246"/>
-      <c r="AL2" s="246"/>
-      <c r="AM2" s="246"/>
-      <c r="AN2" s="246"/>
-      <c r="AO2" s="246"/>
-      <c r="AP2" s="246"/>
+      <c r="L2" s="252"/>
+      <c r="M2" s="252"/>
+      <c r="N2" s="252"/>
+      <c r="O2" s="252"/>
+      <c r="P2" s="252"/>
+      <c r="Q2" s="252"/>
+      <c r="R2" s="252"/>
+      <c r="S2" s="252"/>
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
+      <c r="AA2" s="252"/>
+      <c r="AB2" s="252"/>
+      <c r="AC2" s="252"/>
+      <c r="AD2" s="252"/>
+      <c r="AE2" s="252"/>
+      <c r="AF2" s="252"/>
+      <c r="AG2" s="252"/>
+      <c r="AH2" s="252"/>
+      <c r="AI2" s="252"/>
+      <c r="AJ2" s="252"/>
+      <c r="AK2" s="252"/>
+      <c r="AL2" s="252"/>
+      <c r="AM2" s="252"/>
+      <c r="AN2" s="252"/>
+      <c r="AO2" s="252"/>
+      <c r="AP2" s="252"/>
       <c r="AQ2" s="17"/>
       <c r="AR2" s="17"/>
-      <c r="AS2" s="149"/>
-      <c r="AT2" s="150"/>
-      <c r="AU2" s="150"/>
-      <c r="AV2" s="150"/>
-      <c r="AW2" s="150"/>
-      <c r="AX2" s="150"/>
-      <c r="AY2" s="150"/>
-      <c r="AZ2" s="151"/>
+      <c r="AS2" s="180"/>
+      <c r="AT2" s="181"/>
+      <c r="AU2" s="181"/>
+      <c r="AV2" s="181"/>
+      <c r="AW2" s="181"/>
+      <c r="AX2" s="181"/>
+      <c r="AY2" s="181"/>
+      <c r="AZ2" s="182"/>
       <c r="BA2" s="7"/>
       <c r="BF2" s="25"/>
       <c r="BG2" s="25"/>
       <c r="BH2" s="25"/>
     </row>
     <row r="3" spans="1:60" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="143"/>
-      <c r="B3" s="144"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="144"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="145"/>
+      <c r="A3" s="174"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="176"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -9971,80 +9923,80 @@
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
       <c r="AR3" s="4"/>
-      <c r="AS3" s="152"/>
-      <c r="AT3" s="153"/>
-      <c r="AU3" s="153"/>
-      <c r="AV3" s="153"/>
-      <c r="AW3" s="153"/>
-      <c r="AX3" s="153"/>
-      <c r="AY3" s="153"/>
-      <c r="AZ3" s="154"/>
+      <c r="AS3" s="183"/>
+      <c r="AT3" s="184"/>
+      <c r="AU3" s="184"/>
+      <c r="AV3" s="184"/>
+      <c r="AW3" s="184"/>
+      <c r="AX3" s="184"/>
+      <c r="AY3" s="184"/>
+      <c r="AZ3" s="185"/>
     </row>
     <row r="4" spans="1:60" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="101"/>
-      <c r="L4" s="101"/>
-      <c r="M4" s="101"/>
-      <c r="N4" s="101"/>
-      <c r="O4" s="101"/>
-      <c r="P4" s="101"/>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="101"/>
-      <c r="S4" s="101"/>
-      <c r="T4" s="101"/>
-      <c r="U4" s="101"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="101"/>
-      <c r="X4" s="101"/>
-      <c r="Y4" s="101"/>
-      <c r="Z4" s="101"/>
-      <c r="AA4" s="101"/>
-      <c r="AB4" s="101"/>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="101"/>
-      <c r="AE4" s="101"/>
-      <c r="AF4" s="101"/>
-      <c r="AG4" s="101"/>
-      <c r="AH4" s="101"/>
-      <c r="AI4" s="101"/>
-      <c r="AJ4" s="101"/>
-      <c r="AK4" s="101"/>
-      <c r="AL4" s="101"/>
-      <c r="AM4" s="101"/>
-      <c r="AN4" s="101"/>
-      <c r="AO4" s="101"/>
-      <c r="AP4" s="101"/>
-      <c r="AQ4" s="101"/>
-      <c r="AR4" s="101"/>
-      <c r="AS4" s="101"/>
-      <c r="AT4" s="101"/>
-      <c r="AU4" s="101"/>
-      <c r="AV4" s="101"/>
-      <c r="AW4" s="101"/>
-      <c r="AX4" s="101"/>
-      <c r="AY4" s="101"/>
-      <c r="AZ4" s="102"/>
+      <c r="B4" s="190"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="190"/>
+      <c r="K4" s="190"/>
+      <c r="L4" s="190"/>
+      <c r="M4" s="190"/>
+      <c r="N4" s="190"/>
+      <c r="O4" s="190"/>
+      <c r="P4" s="190"/>
+      <c r="Q4" s="190"/>
+      <c r="R4" s="190"/>
+      <c r="S4" s="190"/>
+      <c r="T4" s="190"/>
+      <c r="U4" s="190"/>
+      <c r="V4" s="190"/>
+      <c r="W4" s="190"/>
+      <c r="X4" s="190"/>
+      <c r="Y4" s="190"/>
+      <c r="Z4" s="190"/>
+      <c r="AA4" s="190"/>
+      <c r="AB4" s="190"/>
+      <c r="AC4" s="190"/>
+      <c r="AD4" s="190"/>
+      <c r="AE4" s="190"/>
+      <c r="AF4" s="190"/>
+      <c r="AG4" s="190"/>
+      <c r="AH4" s="190"/>
+      <c r="AI4" s="190"/>
+      <c r="AJ4" s="190"/>
+      <c r="AK4" s="190"/>
+      <c r="AL4" s="190"/>
+      <c r="AM4" s="190"/>
+      <c r="AN4" s="190"/>
+      <c r="AO4" s="190"/>
+      <c r="AP4" s="190"/>
+      <c r="AQ4" s="190"/>
+      <c r="AR4" s="190"/>
+      <c r="AS4" s="190"/>
+      <c r="AT4" s="190"/>
+      <c r="AU4" s="190"/>
+      <c r="AV4" s="190"/>
+      <c r="AW4" s="190"/>
+      <c r="AX4" s="190"/>
+      <c r="AY4" s="190"/>
+      <c r="AZ4" s="191"/>
       <c r="BA4" s="9"/>
       <c r="BB4" s="9"/>
       <c r="BC4" s="9"/>
     </row>
     <row r="5" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="247" t="s">
+      <c r="A5" s="253" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="248"/>
-      <c r="C5" s="248"/>
+      <c r="B5" s="254"/>
+      <c r="C5" s="254"/>
       <c r="D5" s="11"/>
       <c r="E5" s="6" t="s">
         <v>105</v>
@@ -10101,63 +10053,63 @@
       <c r="BC5" s="9"/>
     </row>
     <row r="6" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="244"/>
-      <c r="B6" s="245"/>
-      <c r="C6" s="245"/>
+      <c r="A6" s="248"/>
+      <c r="B6" s="249"/>
+      <c r="C6" s="249"/>
       <c r="D6" s="10"/>
-      <c r="E6" s="249"/>
-      <c r="F6" s="249"/>
-      <c r="G6" s="249"/>
-      <c r="H6" s="249"/>
-      <c r="I6" s="249"/>
-      <c r="J6" s="249"/>
-      <c r="K6" s="249"/>
-      <c r="L6" s="249"/>
-      <c r="M6" s="249"/>
-      <c r="N6" s="249"/>
-      <c r="O6" s="249"/>
-      <c r="P6" s="249"/>
-      <c r="Q6" s="249"/>
-      <c r="R6" s="249"/>
-      <c r="S6" s="249"/>
-      <c r="T6" s="249"/>
-      <c r="U6" s="249"/>
-      <c r="V6" s="249"/>
-      <c r="W6" s="249"/>
-      <c r="X6" s="249"/>
-      <c r="Y6" s="249"/>
-      <c r="Z6" s="249"/>
-      <c r="AA6" s="249"/>
-      <c r="AB6" s="249"/>
-      <c r="AC6" s="249"/>
-      <c r="AD6" s="249"/>
-      <c r="AE6" s="249"/>
-      <c r="AF6" s="249"/>
-      <c r="AG6" s="249"/>
-      <c r="AH6" s="249"/>
-      <c r="AI6" s="249"/>
-      <c r="AJ6" s="249"/>
-      <c r="AK6" s="249"/>
-      <c r="AL6" s="249"/>
-      <c r="AM6" s="249"/>
-      <c r="AN6" s="249"/>
-      <c r="AO6" s="249"/>
-      <c r="AP6" s="249"/>
-      <c r="AQ6" s="249"/>
-      <c r="AR6" s="249"/>
-      <c r="AS6" s="249"/>
-      <c r="AT6" s="249"/>
-      <c r="AU6" s="249"/>
-      <c r="AV6" s="249"/>
-      <c r="AW6" s="249"/>
-      <c r="AX6" s="249"/>
-      <c r="AY6" s="249"/>
-      <c r="AZ6" s="250"/>
+      <c r="E6" s="255"/>
+      <c r="F6" s="255"/>
+      <c r="G6" s="255"/>
+      <c r="H6" s="255"/>
+      <c r="I6" s="255"/>
+      <c r="J6" s="255"/>
+      <c r="K6" s="255"/>
+      <c r="L6" s="255"/>
+      <c r="M6" s="255"/>
+      <c r="N6" s="255"/>
+      <c r="O6" s="255"/>
+      <c r="P6" s="255"/>
+      <c r="Q6" s="255"/>
+      <c r="R6" s="255"/>
+      <c r="S6" s="255"/>
+      <c r="T6" s="255"/>
+      <c r="U6" s="255"/>
+      <c r="V6" s="255"/>
+      <c r="W6" s="255"/>
+      <c r="X6" s="255"/>
+      <c r="Y6" s="255"/>
+      <c r="Z6" s="255"/>
+      <c r="AA6" s="255"/>
+      <c r="AB6" s="255"/>
+      <c r="AC6" s="255"/>
+      <c r="AD6" s="255"/>
+      <c r="AE6" s="255"/>
+      <c r="AF6" s="255"/>
+      <c r="AG6" s="255"/>
+      <c r="AH6" s="255"/>
+      <c r="AI6" s="255"/>
+      <c r="AJ6" s="255"/>
+      <c r="AK6" s="255"/>
+      <c r="AL6" s="255"/>
+      <c r="AM6" s="255"/>
+      <c r="AN6" s="255"/>
+      <c r="AO6" s="255"/>
+      <c r="AP6" s="255"/>
+      <c r="AQ6" s="255"/>
+      <c r="AR6" s="255"/>
+      <c r="AS6" s="255"/>
+      <c r="AT6" s="255"/>
+      <c r="AU6" s="255"/>
+      <c r="AV6" s="255"/>
+      <c r="AW6" s="255"/>
+      <c r="AX6" s="255"/>
+      <c r="AY6" s="255"/>
+      <c r="AZ6" s="256"/>
     </row>
     <row r="7" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="244"/>
-      <c r="B7" s="245"/>
-      <c r="C7" s="245"/>
+      <c r="A7" s="248"/>
+      <c r="B7" s="249"/>
+      <c r="C7" s="249"/>
       <c r="D7" s="10"/>
       <c r="E7" s="86"/>
       <c r="F7" s="87"/>
@@ -10209,9 +10161,9 @@
       <c r="AZ7" s="88"/>
     </row>
     <row r="8" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="242"/>
-      <c r="B8" s="243"/>
-      <c r="C8" s="243"/>
+      <c r="A8" s="257"/>
+      <c r="B8" s="258"/>
+      <c r="C8" s="258"/>
       <c r="D8" s="10"/>
       <c r="E8" s="87"/>
       <c r="F8" s="87"/>
@@ -10263,63 +10215,63 @@
       <c r="AZ8" s="88"/>
     </row>
     <row r="9" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="242"/>
-      <c r="B9" s="243"/>
-      <c r="C9" s="243"/>
+      <c r="A9" s="257"/>
+      <c r="B9" s="258"/>
+      <c r="C9" s="258"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="251"/>
-      <c r="F9" s="251"/>
-      <c r="G9" s="251"/>
-      <c r="H9" s="251"/>
-      <c r="I9" s="251"/>
-      <c r="J9" s="251"/>
-      <c r="K9" s="251"/>
-      <c r="L9" s="251"/>
-      <c r="M9" s="251"/>
-      <c r="N9" s="251"/>
-      <c r="O9" s="251"/>
-      <c r="P9" s="251"/>
-      <c r="Q9" s="251"/>
-      <c r="R9" s="251"/>
-      <c r="S9" s="251"/>
-      <c r="T9" s="251"/>
-      <c r="U9" s="251"/>
-      <c r="V9" s="251"/>
-      <c r="W9" s="251"/>
-      <c r="X9" s="251"/>
-      <c r="Y9" s="251"/>
-      <c r="Z9" s="251"/>
-      <c r="AA9" s="251"/>
-      <c r="AB9" s="251"/>
-      <c r="AC9" s="251"/>
-      <c r="AD9" s="251"/>
-      <c r="AE9" s="251"/>
-      <c r="AF9" s="251"/>
-      <c r="AG9" s="251"/>
-      <c r="AH9" s="251"/>
-      <c r="AI9" s="251"/>
-      <c r="AJ9" s="251"/>
-      <c r="AK9" s="251"/>
-      <c r="AL9" s="251"/>
-      <c r="AM9" s="251"/>
-      <c r="AN9" s="251"/>
-      <c r="AO9" s="251"/>
-      <c r="AP9" s="251"/>
-      <c r="AQ9" s="251"/>
-      <c r="AR9" s="251"/>
-      <c r="AS9" s="251"/>
-      <c r="AT9" s="251"/>
-      <c r="AU9" s="251"/>
-      <c r="AV9" s="251"/>
-      <c r="AW9" s="251"/>
-      <c r="AX9" s="251"/>
-      <c r="AY9" s="251"/>
-      <c r="AZ9" s="252"/>
+      <c r="E9" s="250"/>
+      <c r="F9" s="250"/>
+      <c r="G9" s="250"/>
+      <c r="H9" s="250"/>
+      <c r="I9" s="250"/>
+      <c r="J9" s="250"/>
+      <c r="K9" s="250"/>
+      <c r="L9" s="250"/>
+      <c r="M9" s="250"/>
+      <c r="N9" s="250"/>
+      <c r="O9" s="250"/>
+      <c r="P9" s="250"/>
+      <c r="Q9" s="250"/>
+      <c r="R9" s="250"/>
+      <c r="S9" s="250"/>
+      <c r="T9" s="250"/>
+      <c r="U9" s="250"/>
+      <c r="V9" s="250"/>
+      <c r="W9" s="250"/>
+      <c r="X9" s="250"/>
+      <c r="Y9" s="250"/>
+      <c r="Z9" s="250"/>
+      <c r="AA9" s="250"/>
+      <c r="AB9" s="250"/>
+      <c r="AC9" s="250"/>
+      <c r="AD9" s="250"/>
+      <c r="AE9" s="250"/>
+      <c r="AF9" s="250"/>
+      <c r="AG9" s="250"/>
+      <c r="AH9" s="250"/>
+      <c r="AI9" s="250"/>
+      <c r="AJ9" s="250"/>
+      <c r="AK9" s="250"/>
+      <c r="AL9" s="250"/>
+      <c r="AM9" s="250"/>
+      <c r="AN9" s="250"/>
+      <c r="AO9" s="250"/>
+      <c r="AP9" s="250"/>
+      <c r="AQ9" s="250"/>
+      <c r="AR9" s="250"/>
+      <c r="AS9" s="250"/>
+      <c r="AT9" s="250"/>
+      <c r="AU9" s="250"/>
+      <c r="AV9" s="250"/>
+      <c r="AW9" s="250"/>
+      <c r="AX9" s="250"/>
+      <c r="AY9" s="250"/>
+      <c r="AZ9" s="251"/>
     </row>
     <row r="10" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="242"/>
-      <c r="B10" s="243"/>
-      <c r="C10" s="243"/>
+      <c r="A10" s="257"/>
+      <c r="B10" s="258"/>
+      <c r="C10" s="258"/>
       <c r="D10" s="10"/>
       <c r="E10" s="86"/>
       <c r="F10" s="87"/>
@@ -10371,9 +10323,9 @@
       <c r="AZ10" s="88"/>
     </row>
     <row r="11" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="244"/>
-      <c r="B11" s="245"/>
-      <c r="C11" s="245"/>
+      <c r="A11" s="248"/>
+      <c r="B11" s="249"/>
+      <c r="C11" s="249"/>
       <c r="D11" s="10"/>
       <c r="E11" s="87"/>
       <c r="F11" s="87"/>
@@ -10425,9 +10377,9 @@
       <c r="AZ11" s="88"/>
     </row>
     <row r="12" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="244"/>
-      <c r="B12" s="245"/>
-      <c r="C12" s="245"/>
+      <c r="A12" s="248"/>
+      <c r="B12" s="249"/>
+      <c r="C12" s="249"/>
       <c r="D12" s="10"/>
       <c r="E12" s="87"/>
       <c r="F12" s="87"/>
@@ -10479,9 +10431,9 @@
       <c r="AZ12" s="88"/>
     </row>
     <row r="13" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="244"/>
-      <c r="B13" s="245"/>
-      <c r="C13" s="245"/>
+      <c r="A13" s="248"/>
+      <c r="B13" s="249"/>
+      <c r="C13" s="249"/>
       <c r="D13" s="10"/>
       <c r="E13" s="87"/>
       <c r="F13" s="87"/>
@@ -10533,9 +10485,9 @@
       <c r="AZ13" s="88"/>
     </row>
     <row r="14" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="244"/>
-      <c r="B14" s="245"/>
-      <c r="C14" s="245"/>
+      <c r="A14" s="248"/>
+      <c r="B14" s="249"/>
+      <c r="C14" s="249"/>
       <c r="D14" s="10"/>
       <c r="E14" s="87"/>
       <c r="F14" s="87"/>
@@ -10587,9 +10539,9 @@
       <c r="AZ14" s="88"/>
     </row>
     <row r="15" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="244"/>
-      <c r="B15" s="245"/>
-      <c r="C15" s="245"/>
+      <c r="A15" s="248"/>
+      <c r="B15" s="249"/>
+      <c r="C15" s="249"/>
       <c r="D15" s="10"/>
       <c r="E15" s="86"/>
       <c r="F15" s="87"/>
@@ -10641,9 +10593,9 @@
       <c r="AZ15" s="88"/>
     </row>
     <row r="16" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="244"/>
-      <c r="B16" s="245"/>
-      <c r="C16" s="245"/>
+      <c r="A16" s="248"/>
+      <c r="B16" s="249"/>
+      <c r="C16" s="249"/>
       <c r="D16" s="10"/>
       <c r="E16" s="86"/>
       <c r="F16" s="87"/>
@@ -10695,9 +10647,9 @@
       <c r="AZ16" s="88"/>
     </row>
     <row r="17" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="244"/>
-      <c r="B17" s="245"/>
-      <c r="C17" s="245"/>
+      <c r="A17" s="248"/>
+      <c r="B17" s="249"/>
+      <c r="C17" s="249"/>
       <c r="D17" s="10"/>
       <c r="E17" s="86"/>
       <c r="F17" s="87"/>
@@ -10749,9 +10701,9 @@
       <c r="AZ17" s="88"/>
     </row>
     <row r="18" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="244"/>
-      <c r="B18" s="245"/>
-      <c r="C18" s="245"/>
+      <c r="A18" s="248"/>
+      <c r="B18" s="249"/>
+      <c r="C18" s="249"/>
       <c r="D18" s="10"/>
       <c r="E18" s="86"/>
       <c r="F18" s="87"/>
@@ -10803,9 +10755,9 @@
       <c r="AZ18" s="88"/>
     </row>
     <row r="19" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="244"/>
-      <c r="B19" s="245"/>
-      <c r="C19" s="245"/>
+      <c r="A19" s="248"/>
+      <c r="B19" s="249"/>
+      <c r="C19" s="249"/>
       <c r="D19" s="10"/>
       <c r="E19" s="86"/>
       <c r="F19" s="87"/>
@@ -10857,9 +10809,9 @@
       <c r="AZ19" s="88"/>
     </row>
     <row r="20" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="244"/>
-      <c r="B20" s="245"/>
-      <c r="C20" s="245"/>
+      <c r="A20" s="248"/>
+      <c r="B20" s="249"/>
+      <c r="C20" s="249"/>
       <c r="D20" s="10"/>
       <c r="E20" s="86"/>
       <c r="F20" s="87"/>
@@ -10911,9 +10863,9 @@
       <c r="AZ20" s="88"/>
     </row>
     <row r="21" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="244"/>
-      <c r="B21" s="245"/>
-      <c r="C21" s="245"/>
+      <c r="A21" s="248"/>
+      <c r="B21" s="249"/>
+      <c r="C21" s="249"/>
       <c r="D21" s="10"/>
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
@@ -10965,9 +10917,9 @@
       <c r="AZ21" s="88"/>
     </row>
     <row r="22" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="244"/>
-      <c r="B22" s="245"/>
-      <c r="C22" s="245"/>
+      <c r="A22" s="248"/>
+      <c r="B22" s="249"/>
+      <c r="C22" s="249"/>
       <c r="D22" s="10"/>
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
@@ -11019,9 +10971,9 @@
       <c r="AZ22" s="88"/>
     </row>
     <row r="23" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="244"/>
-      <c r="B23" s="245"/>
-      <c r="C23" s="245"/>
+      <c r="A23" s="248"/>
+      <c r="B23" s="249"/>
+      <c r="C23" s="249"/>
       <c r="D23" s="10"/>
       <c r="E23" s="86"/>
       <c r="F23" s="87"/>
@@ -11073,9 +11025,9 @@
       <c r="AZ23" s="88"/>
     </row>
     <row r="24" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="244"/>
-      <c r="B24" s="245"/>
-      <c r="C24" s="245"/>
+      <c r="A24" s="248"/>
+      <c r="B24" s="249"/>
+      <c r="C24" s="249"/>
       <c r="D24" s="10"/>
       <c r="E24" s="87"/>
       <c r="F24" s="87"/>
@@ -11127,9 +11079,9 @@
       <c r="AZ24" s="88"/>
     </row>
     <row r="25" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="244"/>
-      <c r="B25" s="245"/>
-      <c r="C25" s="245"/>
+      <c r="A25" s="248"/>
+      <c r="B25" s="249"/>
+      <c r="C25" s="249"/>
       <c r="D25" s="10"/>
       <c r="E25" s="86"/>
       <c r="F25" s="87"/>
@@ -11181,922 +11133,922 @@
       <c r="AZ25" s="88"/>
     </row>
     <row r="26" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="244"/>
-      <c r="B26" s="245"/>
-      <c r="C26" s="245"/>
+      <c r="A26" s="248"/>
+      <c r="B26" s="249"/>
+      <c r="C26" s="249"/>
       <c r="D26" s="10"/>
-      <c r="E26" s="253"/>
-      <c r="F26" s="253"/>
-      <c r="G26" s="253"/>
-      <c r="H26" s="253"/>
-      <c r="I26" s="253"/>
-      <c r="J26" s="253"/>
-      <c r="K26" s="253"/>
-      <c r="L26" s="253"/>
-      <c r="M26" s="253"/>
-      <c r="N26" s="253"/>
-      <c r="O26" s="253"/>
-      <c r="P26" s="253"/>
-      <c r="Q26" s="253"/>
-      <c r="R26" s="253"/>
-      <c r="S26" s="253"/>
-      <c r="T26" s="253"/>
-      <c r="U26" s="253"/>
-      <c r="V26" s="253"/>
-      <c r="W26" s="253"/>
-      <c r="X26" s="253"/>
-      <c r="Y26" s="253"/>
-      <c r="Z26" s="253"/>
-      <c r="AA26" s="253"/>
-      <c r="AB26" s="253"/>
-      <c r="AC26" s="253"/>
-      <c r="AD26" s="253"/>
-      <c r="AE26" s="253"/>
-      <c r="AF26" s="253"/>
-      <c r="AG26" s="253"/>
-      <c r="AH26" s="253"/>
-      <c r="AI26" s="253"/>
-      <c r="AJ26" s="253"/>
-      <c r="AK26" s="253"/>
-      <c r="AL26" s="253"/>
-      <c r="AM26" s="253"/>
-      <c r="AN26" s="253"/>
-      <c r="AO26" s="253"/>
-      <c r="AP26" s="253"/>
-      <c r="AQ26" s="253"/>
-      <c r="AR26" s="253"/>
-      <c r="AS26" s="253"/>
-      <c r="AT26" s="253"/>
-      <c r="AU26" s="253"/>
-      <c r="AV26" s="253"/>
-      <c r="AW26" s="253"/>
-      <c r="AX26" s="253"/>
-      <c r="AY26" s="253"/>
-      <c r="AZ26" s="254"/>
+      <c r="E26" s="243"/>
+      <c r="F26" s="243"/>
+      <c r="G26" s="243"/>
+      <c r="H26" s="243"/>
+      <c r="I26" s="243"/>
+      <c r="J26" s="243"/>
+      <c r="K26" s="243"/>
+      <c r="L26" s="243"/>
+      <c r="M26" s="243"/>
+      <c r="N26" s="243"/>
+      <c r="O26" s="243"/>
+      <c r="P26" s="243"/>
+      <c r="Q26" s="243"/>
+      <c r="R26" s="243"/>
+      <c r="S26" s="243"/>
+      <c r="T26" s="243"/>
+      <c r="U26" s="243"/>
+      <c r="V26" s="243"/>
+      <c r="W26" s="243"/>
+      <c r="X26" s="243"/>
+      <c r="Y26" s="243"/>
+      <c r="Z26" s="243"/>
+      <c r="AA26" s="243"/>
+      <c r="AB26" s="243"/>
+      <c r="AC26" s="243"/>
+      <c r="AD26" s="243"/>
+      <c r="AE26" s="243"/>
+      <c r="AF26" s="243"/>
+      <c r="AG26" s="243"/>
+      <c r="AH26" s="243"/>
+      <c r="AI26" s="243"/>
+      <c r="AJ26" s="243"/>
+      <c r="AK26" s="243"/>
+      <c r="AL26" s="243"/>
+      <c r="AM26" s="243"/>
+      <c r="AN26" s="243"/>
+      <c r="AO26" s="243"/>
+      <c r="AP26" s="243"/>
+      <c r="AQ26" s="243"/>
+      <c r="AR26" s="243"/>
+      <c r="AS26" s="243"/>
+      <c r="AT26" s="243"/>
+      <c r="AU26" s="243"/>
+      <c r="AV26" s="243"/>
+      <c r="AW26" s="243"/>
+      <c r="AX26" s="243"/>
+      <c r="AY26" s="243"/>
+      <c r="AZ26" s="244"/>
     </row>
     <row r="27" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="244"/>
-      <c r="B27" s="245"/>
-      <c r="C27" s="245"/>
+      <c r="A27" s="248"/>
+      <c r="B27" s="249"/>
+      <c r="C27" s="249"/>
       <c r="D27" s="10"/>
-      <c r="E27" s="253"/>
-      <c r="F27" s="253"/>
-      <c r="G27" s="253"/>
-      <c r="H27" s="253"/>
-      <c r="I27" s="253"/>
-      <c r="J27" s="253"/>
-      <c r="K27" s="253"/>
-      <c r="L27" s="253"/>
-      <c r="M27" s="253"/>
-      <c r="N27" s="253"/>
-      <c r="O27" s="253"/>
-      <c r="P27" s="253"/>
-      <c r="Q27" s="253"/>
-      <c r="R27" s="253"/>
-      <c r="S27" s="253"/>
-      <c r="T27" s="253"/>
-      <c r="U27" s="253"/>
-      <c r="V27" s="253"/>
-      <c r="W27" s="253"/>
-      <c r="X27" s="253"/>
-      <c r="Y27" s="253"/>
-      <c r="Z27" s="253"/>
-      <c r="AA27" s="253"/>
-      <c r="AB27" s="253"/>
-      <c r="AC27" s="253"/>
-      <c r="AD27" s="253"/>
-      <c r="AE27" s="253"/>
-      <c r="AF27" s="253"/>
-      <c r="AG27" s="253"/>
-      <c r="AH27" s="253"/>
-      <c r="AI27" s="253"/>
-      <c r="AJ27" s="253"/>
-      <c r="AK27" s="253"/>
-      <c r="AL27" s="253"/>
-      <c r="AM27" s="253"/>
-      <c r="AN27" s="253"/>
-      <c r="AO27" s="253"/>
-      <c r="AP27" s="253"/>
-      <c r="AQ27" s="253"/>
-      <c r="AR27" s="253"/>
-      <c r="AS27" s="253"/>
-      <c r="AT27" s="253"/>
-      <c r="AU27" s="253"/>
-      <c r="AV27" s="253"/>
-      <c r="AW27" s="253"/>
-      <c r="AX27" s="253"/>
-      <c r="AY27" s="253"/>
-      <c r="AZ27" s="254"/>
+      <c r="E27" s="243"/>
+      <c r="F27" s="243"/>
+      <c r="G27" s="243"/>
+      <c r="H27" s="243"/>
+      <c r="I27" s="243"/>
+      <c r="J27" s="243"/>
+      <c r="K27" s="243"/>
+      <c r="L27" s="243"/>
+      <c r="M27" s="243"/>
+      <c r="N27" s="243"/>
+      <c r="O27" s="243"/>
+      <c r="P27" s="243"/>
+      <c r="Q27" s="243"/>
+      <c r="R27" s="243"/>
+      <c r="S27" s="243"/>
+      <c r="T27" s="243"/>
+      <c r="U27" s="243"/>
+      <c r="V27" s="243"/>
+      <c r="W27" s="243"/>
+      <c r="X27" s="243"/>
+      <c r="Y27" s="243"/>
+      <c r="Z27" s="243"/>
+      <c r="AA27" s="243"/>
+      <c r="AB27" s="243"/>
+      <c r="AC27" s="243"/>
+      <c r="AD27" s="243"/>
+      <c r="AE27" s="243"/>
+      <c r="AF27" s="243"/>
+      <c r="AG27" s="243"/>
+      <c r="AH27" s="243"/>
+      <c r="AI27" s="243"/>
+      <c r="AJ27" s="243"/>
+      <c r="AK27" s="243"/>
+      <c r="AL27" s="243"/>
+      <c r="AM27" s="243"/>
+      <c r="AN27" s="243"/>
+      <c r="AO27" s="243"/>
+      <c r="AP27" s="243"/>
+      <c r="AQ27" s="243"/>
+      <c r="AR27" s="243"/>
+      <c r="AS27" s="243"/>
+      <c r="AT27" s="243"/>
+      <c r="AU27" s="243"/>
+      <c r="AV27" s="243"/>
+      <c r="AW27" s="243"/>
+      <c r="AX27" s="243"/>
+      <c r="AY27" s="243"/>
+      <c r="AZ27" s="244"/>
     </row>
     <row r="28" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="244"/>
-      <c r="B28" s="245"/>
-      <c r="C28" s="245"/>
+      <c r="A28" s="248"/>
+      <c r="B28" s="249"/>
+      <c r="C28" s="249"/>
       <c r="D28" s="10"/>
-      <c r="E28" s="253"/>
-      <c r="F28" s="253"/>
-      <c r="G28" s="253"/>
-      <c r="H28" s="253"/>
-      <c r="I28" s="253"/>
-      <c r="J28" s="253"/>
-      <c r="K28" s="253"/>
-      <c r="L28" s="253"/>
-      <c r="M28" s="253"/>
-      <c r="N28" s="253"/>
-      <c r="O28" s="253"/>
-      <c r="P28" s="253"/>
-      <c r="Q28" s="253"/>
-      <c r="R28" s="253"/>
-      <c r="S28" s="253"/>
-      <c r="T28" s="253"/>
-      <c r="U28" s="253"/>
-      <c r="V28" s="253"/>
-      <c r="W28" s="253"/>
-      <c r="X28" s="253"/>
-      <c r="Y28" s="253"/>
-      <c r="Z28" s="253"/>
-      <c r="AA28" s="253"/>
-      <c r="AB28" s="253"/>
-      <c r="AC28" s="253"/>
-      <c r="AD28" s="253"/>
-      <c r="AE28" s="253"/>
-      <c r="AF28" s="253"/>
-      <c r="AG28" s="253"/>
-      <c r="AH28" s="253"/>
-      <c r="AI28" s="253"/>
-      <c r="AJ28" s="253"/>
-      <c r="AK28" s="253"/>
-      <c r="AL28" s="253"/>
-      <c r="AM28" s="253"/>
-      <c r="AN28" s="253"/>
-      <c r="AO28" s="253"/>
-      <c r="AP28" s="253"/>
-      <c r="AQ28" s="253"/>
-      <c r="AR28" s="253"/>
-      <c r="AS28" s="253"/>
-      <c r="AT28" s="253"/>
-      <c r="AU28" s="253"/>
-      <c r="AV28" s="253"/>
-      <c r="AW28" s="253"/>
-      <c r="AX28" s="253"/>
-      <c r="AY28" s="253"/>
-      <c r="AZ28" s="254"/>
+      <c r="E28" s="243"/>
+      <c r="F28" s="243"/>
+      <c r="G28" s="243"/>
+      <c r="H28" s="243"/>
+      <c r="I28" s="243"/>
+      <c r="J28" s="243"/>
+      <c r="K28" s="243"/>
+      <c r="L28" s="243"/>
+      <c r="M28" s="243"/>
+      <c r="N28" s="243"/>
+      <c r="O28" s="243"/>
+      <c r="P28" s="243"/>
+      <c r="Q28" s="243"/>
+      <c r="R28" s="243"/>
+      <c r="S28" s="243"/>
+      <c r="T28" s="243"/>
+      <c r="U28" s="243"/>
+      <c r="V28" s="243"/>
+      <c r="W28" s="243"/>
+      <c r="X28" s="243"/>
+      <c r="Y28" s="243"/>
+      <c r="Z28" s="243"/>
+      <c r="AA28" s="243"/>
+      <c r="AB28" s="243"/>
+      <c r="AC28" s="243"/>
+      <c r="AD28" s="243"/>
+      <c r="AE28" s="243"/>
+      <c r="AF28" s="243"/>
+      <c r="AG28" s="243"/>
+      <c r="AH28" s="243"/>
+      <c r="AI28" s="243"/>
+      <c r="AJ28" s="243"/>
+      <c r="AK28" s="243"/>
+      <c r="AL28" s="243"/>
+      <c r="AM28" s="243"/>
+      <c r="AN28" s="243"/>
+      <c r="AO28" s="243"/>
+      <c r="AP28" s="243"/>
+      <c r="AQ28" s="243"/>
+      <c r="AR28" s="243"/>
+      <c r="AS28" s="243"/>
+      <c r="AT28" s="243"/>
+      <c r="AU28" s="243"/>
+      <c r="AV28" s="243"/>
+      <c r="AW28" s="243"/>
+      <c r="AX28" s="243"/>
+      <c r="AY28" s="243"/>
+      <c r="AZ28" s="244"/>
     </row>
     <row r="29" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="244"/>
-      <c r="B29" s="245"/>
-      <c r="C29" s="245"/>
+      <c r="A29" s="248"/>
+      <c r="B29" s="249"/>
+      <c r="C29" s="249"/>
       <c r="D29" s="10"/>
-      <c r="E29" s="253"/>
-      <c r="F29" s="253"/>
-      <c r="G29" s="253"/>
-      <c r="H29" s="253"/>
-      <c r="I29" s="253"/>
-      <c r="J29" s="253"/>
-      <c r="K29" s="253"/>
-      <c r="L29" s="253"/>
-      <c r="M29" s="253"/>
-      <c r="N29" s="253"/>
-      <c r="O29" s="253"/>
-      <c r="P29" s="253"/>
-      <c r="Q29" s="253"/>
-      <c r="R29" s="253"/>
-      <c r="S29" s="253"/>
-      <c r="T29" s="253"/>
-      <c r="U29" s="253"/>
-      <c r="V29" s="253"/>
-      <c r="W29" s="253"/>
-      <c r="X29" s="253"/>
-      <c r="Y29" s="253"/>
-      <c r="Z29" s="253"/>
-      <c r="AA29" s="253"/>
-      <c r="AB29" s="253"/>
-      <c r="AC29" s="253"/>
-      <c r="AD29" s="253"/>
-      <c r="AE29" s="253"/>
-      <c r="AF29" s="253"/>
-      <c r="AG29" s="253"/>
-      <c r="AH29" s="253"/>
-      <c r="AI29" s="253"/>
-      <c r="AJ29" s="253"/>
-      <c r="AK29" s="253"/>
-      <c r="AL29" s="253"/>
-      <c r="AM29" s="253"/>
-      <c r="AN29" s="253"/>
-      <c r="AO29" s="253"/>
-      <c r="AP29" s="253"/>
-      <c r="AQ29" s="253"/>
-      <c r="AR29" s="253"/>
-      <c r="AS29" s="253"/>
-      <c r="AT29" s="253"/>
-      <c r="AU29" s="253"/>
-      <c r="AV29" s="253"/>
-      <c r="AW29" s="253"/>
-      <c r="AX29" s="253"/>
-      <c r="AY29" s="253"/>
-      <c r="AZ29" s="254"/>
+      <c r="E29" s="243"/>
+      <c r="F29" s="243"/>
+      <c r="G29" s="243"/>
+      <c r="H29" s="243"/>
+      <c r="I29" s="243"/>
+      <c r="J29" s="243"/>
+      <c r="K29" s="243"/>
+      <c r="L29" s="243"/>
+      <c r="M29" s="243"/>
+      <c r="N29" s="243"/>
+      <c r="O29" s="243"/>
+      <c r="P29" s="243"/>
+      <c r="Q29" s="243"/>
+      <c r="R29" s="243"/>
+      <c r="S29" s="243"/>
+      <c r="T29" s="243"/>
+      <c r="U29" s="243"/>
+      <c r="V29" s="243"/>
+      <c r="W29" s="243"/>
+      <c r="X29" s="243"/>
+      <c r="Y29" s="243"/>
+      <c r="Z29" s="243"/>
+      <c r="AA29" s="243"/>
+      <c r="AB29" s="243"/>
+      <c r="AC29" s="243"/>
+      <c r="AD29" s="243"/>
+      <c r="AE29" s="243"/>
+      <c r="AF29" s="243"/>
+      <c r="AG29" s="243"/>
+      <c r="AH29" s="243"/>
+      <c r="AI29" s="243"/>
+      <c r="AJ29" s="243"/>
+      <c r="AK29" s="243"/>
+      <c r="AL29" s="243"/>
+      <c r="AM29" s="243"/>
+      <c r="AN29" s="243"/>
+      <c r="AO29" s="243"/>
+      <c r="AP29" s="243"/>
+      <c r="AQ29" s="243"/>
+      <c r="AR29" s="243"/>
+      <c r="AS29" s="243"/>
+      <c r="AT29" s="243"/>
+      <c r="AU29" s="243"/>
+      <c r="AV29" s="243"/>
+      <c r="AW29" s="243"/>
+      <c r="AX29" s="243"/>
+      <c r="AY29" s="243"/>
+      <c r="AZ29" s="244"/>
     </row>
     <row r="30" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="244"/>
-      <c r="B30" s="245"/>
-      <c r="C30" s="245"/>
+      <c r="A30" s="248"/>
+      <c r="B30" s="249"/>
+      <c r="C30" s="249"/>
       <c r="D30" s="10"/>
-      <c r="E30" s="253"/>
-      <c r="F30" s="253"/>
-      <c r="G30" s="253"/>
-      <c r="H30" s="253"/>
-      <c r="I30" s="253"/>
-      <c r="J30" s="253"/>
-      <c r="K30" s="253"/>
-      <c r="L30" s="253"/>
-      <c r="M30" s="253"/>
-      <c r="N30" s="253"/>
-      <c r="O30" s="253"/>
-      <c r="P30" s="253"/>
-      <c r="Q30" s="253"/>
-      <c r="R30" s="253"/>
-      <c r="S30" s="253"/>
-      <c r="T30" s="253"/>
-      <c r="U30" s="253"/>
-      <c r="V30" s="253"/>
-      <c r="W30" s="253"/>
-      <c r="X30" s="253"/>
-      <c r="Y30" s="253"/>
-      <c r="Z30" s="253"/>
-      <c r="AA30" s="253"/>
-      <c r="AB30" s="253"/>
-      <c r="AC30" s="253"/>
-      <c r="AD30" s="253"/>
-      <c r="AE30" s="253"/>
-      <c r="AF30" s="253"/>
-      <c r="AG30" s="253"/>
-      <c r="AH30" s="253"/>
-      <c r="AI30" s="253"/>
-      <c r="AJ30" s="253"/>
-      <c r="AK30" s="253"/>
-      <c r="AL30" s="253"/>
-      <c r="AM30" s="253"/>
-      <c r="AN30" s="253"/>
-      <c r="AO30" s="253"/>
-      <c r="AP30" s="253"/>
-      <c r="AQ30" s="253"/>
-      <c r="AR30" s="253"/>
-      <c r="AS30" s="253"/>
-      <c r="AT30" s="253"/>
-      <c r="AU30" s="253"/>
-      <c r="AV30" s="253"/>
-      <c r="AW30" s="253"/>
-      <c r="AX30" s="253"/>
-      <c r="AY30" s="253"/>
-      <c r="AZ30" s="254"/>
+      <c r="E30" s="243"/>
+      <c r="F30" s="243"/>
+      <c r="G30" s="243"/>
+      <c r="H30" s="243"/>
+      <c r="I30" s="243"/>
+      <c r="J30" s="243"/>
+      <c r="K30" s="243"/>
+      <c r="L30" s="243"/>
+      <c r="M30" s="243"/>
+      <c r="N30" s="243"/>
+      <c r="O30" s="243"/>
+      <c r="P30" s="243"/>
+      <c r="Q30" s="243"/>
+      <c r="R30" s="243"/>
+      <c r="S30" s="243"/>
+      <c r="T30" s="243"/>
+      <c r="U30" s="243"/>
+      <c r="V30" s="243"/>
+      <c r="W30" s="243"/>
+      <c r="X30" s="243"/>
+      <c r="Y30" s="243"/>
+      <c r="Z30" s="243"/>
+      <c r="AA30" s="243"/>
+      <c r="AB30" s="243"/>
+      <c r="AC30" s="243"/>
+      <c r="AD30" s="243"/>
+      <c r="AE30" s="243"/>
+      <c r="AF30" s="243"/>
+      <c r="AG30" s="243"/>
+      <c r="AH30" s="243"/>
+      <c r="AI30" s="243"/>
+      <c r="AJ30" s="243"/>
+      <c r="AK30" s="243"/>
+      <c r="AL30" s="243"/>
+      <c r="AM30" s="243"/>
+      <c r="AN30" s="243"/>
+      <c r="AO30" s="243"/>
+      <c r="AP30" s="243"/>
+      <c r="AQ30" s="243"/>
+      <c r="AR30" s="243"/>
+      <c r="AS30" s="243"/>
+      <c r="AT30" s="243"/>
+      <c r="AU30" s="243"/>
+      <c r="AV30" s="243"/>
+      <c r="AW30" s="243"/>
+      <c r="AX30" s="243"/>
+      <c r="AY30" s="243"/>
+      <c r="AZ30" s="244"/>
     </row>
     <row r="31" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="244"/>
-      <c r="B31" s="245"/>
-      <c r="C31" s="245"/>
+      <c r="A31" s="248"/>
+      <c r="B31" s="249"/>
+      <c r="C31" s="249"/>
       <c r="D31" s="10"/>
-      <c r="E31" s="253"/>
-      <c r="F31" s="253"/>
-      <c r="G31" s="253"/>
-      <c r="H31" s="253"/>
-      <c r="I31" s="253"/>
-      <c r="J31" s="253"/>
-      <c r="K31" s="253"/>
-      <c r="L31" s="253"/>
-      <c r="M31" s="253"/>
-      <c r="N31" s="253"/>
-      <c r="O31" s="253"/>
-      <c r="P31" s="253"/>
-      <c r="Q31" s="253"/>
-      <c r="R31" s="253"/>
-      <c r="S31" s="253"/>
-      <c r="T31" s="253"/>
-      <c r="U31" s="253"/>
-      <c r="V31" s="253"/>
-      <c r="W31" s="253"/>
-      <c r="X31" s="253"/>
-      <c r="Y31" s="253"/>
-      <c r="Z31" s="253"/>
-      <c r="AA31" s="253"/>
-      <c r="AB31" s="253"/>
-      <c r="AC31" s="253"/>
-      <c r="AD31" s="253"/>
-      <c r="AE31" s="253"/>
-      <c r="AF31" s="253"/>
-      <c r="AG31" s="253"/>
-      <c r="AH31" s="253"/>
-      <c r="AI31" s="253"/>
-      <c r="AJ31" s="253"/>
-      <c r="AK31" s="253"/>
-      <c r="AL31" s="253"/>
-      <c r="AM31" s="253"/>
-      <c r="AN31" s="253"/>
-      <c r="AO31" s="253"/>
-      <c r="AP31" s="253"/>
-      <c r="AQ31" s="253"/>
-      <c r="AR31" s="253"/>
-      <c r="AS31" s="253"/>
-      <c r="AT31" s="253"/>
-      <c r="AU31" s="253"/>
-      <c r="AV31" s="253"/>
-      <c r="AW31" s="253"/>
-      <c r="AX31" s="253"/>
-      <c r="AY31" s="253"/>
-      <c r="AZ31" s="254"/>
+      <c r="E31" s="243"/>
+      <c r="F31" s="243"/>
+      <c r="G31" s="243"/>
+      <c r="H31" s="243"/>
+      <c r="I31" s="243"/>
+      <c r="J31" s="243"/>
+      <c r="K31" s="243"/>
+      <c r="L31" s="243"/>
+      <c r="M31" s="243"/>
+      <c r="N31" s="243"/>
+      <c r="O31" s="243"/>
+      <c r="P31" s="243"/>
+      <c r="Q31" s="243"/>
+      <c r="R31" s="243"/>
+      <c r="S31" s="243"/>
+      <c r="T31" s="243"/>
+      <c r="U31" s="243"/>
+      <c r="V31" s="243"/>
+      <c r="W31" s="243"/>
+      <c r="X31" s="243"/>
+      <c r="Y31" s="243"/>
+      <c r="Z31" s="243"/>
+      <c r="AA31" s="243"/>
+      <c r="AB31" s="243"/>
+      <c r="AC31" s="243"/>
+      <c r="AD31" s="243"/>
+      <c r="AE31" s="243"/>
+      <c r="AF31" s="243"/>
+      <c r="AG31" s="243"/>
+      <c r="AH31" s="243"/>
+      <c r="AI31" s="243"/>
+      <c r="AJ31" s="243"/>
+      <c r="AK31" s="243"/>
+      <c r="AL31" s="243"/>
+      <c r="AM31" s="243"/>
+      <c r="AN31" s="243"/>
+      <c r="AO31" s="243"/>
+      <c r="AP31" s="243"/>
+      <c r="AQ31" s="243"/>
+      <c r="AR31" s="243"/>
+      <c r="AS31" s="243"/>
+      <c r="AT31" s="243"/>
+      <c r="AU31" s="243"/>
+      <c r="AV31" s="243"/>
+      <c r="AW31" s="243"/>
+      <c r="AX31" s="243"/>
+      <c r="AY31" s="243"/>
+      <c r="AZ31" s="244"/>
     </row>
     <row r="32" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="244"/>
-      <c r="B32" s="245"/>
-      <c r="C32" s="245"/>
+      <c r="A32" s="248"/>
+      <c r="B32" s="249"/>
+      <c r="C32" s="249"/>
       <c r="D32" s="10"/>
-      <c r="E32" s="253"/>
-      <c r="F32" s="253"/>
-      <c r="G32" s="253"/>
-      <c r="H32" s="253"/>
-      <c r="I32" s="253"/>
-      <c r="J32" s="253"/>
-      <c r="K32" s="253"/>
-      <c r="L32" s="253"/>
-      <c r="M32" s="253"/>
-      <c r="N32" s="253"/>
-      <c r="O32" s="253"/>
-      <c r="P32" s="253"/>
-      <c r="Q32" s="253"/>
-      <c r="R32" s="253"/>
-      <c r="S32" s="253"/>
-      <c r="T32" s="253"/>
-      <c r="U32" s="253"/>
-      <c r="V32" s="253"/>
-      <c r="W32" s="253"/>
-      <c r="X32" s="253"/>
-      <c r="Y32" s="253"/>
-      <c r="Z32" s="253"/>
-      <c r="AA32" s="253"/>
-      <c r="AB32" s="253"/>
-      <c r="AC32" s="253"/>
-      <c r="AD32" s="253"/>
-      <c r="AE32" s="253"/>
-      <c r="AF32" s="253"/>
-      <c r="AG32" s="253"/>
-      <c r="AH32" s="253"/>
-      <c r="AI32" s="253"/>
-      <c r="AJ32" s="253"/>
-      <c r="AK32" s="253"/>
-      <c r="AL32" s="253"/>
-      <c r="AM32" s="253"/>
-      <c r="AN32" s="253"/>
-      <c r="AO32" s="253"/>
-      <c r="AP32" s="253"/>
-      <c r="AQ32" s="253"/>
-      <c r="AR32" s="253"/>
-      <c r="AS32" s="253"/>
-      <c r="AT32" s="253"/>
-      <c r="AU32" s="253"/>
-      <c r="AV32" s="253"/>
-      <c r="AW32" s="253"/>
-      <c r="AX32" s="253"/>
-      <c r="AY32" s="253"/>
-      <c r="AZ32" s="254"/>
+      <c r="E32" s="243"/>
+      <c r="F32" s="243"/>
+      <c r="G32" s="243"/>
+      <c r="H32" s="243"/>
+      <c r="I32" s="243"/>
+      <c r="J32" s="243"/>
+      <c r="K32" s="243"/>
+      <c r="L32" s="243"/>
+      <c r="M32" s="243"/>
+      <c r="N32" s="243"/>
+      <c r="O32" s="243"/>
+      <c r="P32" s="243"/>
+      <c r="Q32" s="243"/>
+      <c r="R32" s="243"/>
+      <c r="S32" s="243"/>
+      <c r="T32" s="243"/>
+      <c r="U32" s="243"/>
+      <c r="V32" s="243"/>
+      <c r="W32" s="243"/>
+      <c r="X32" s="243"/>
+      <c r="Y32" s="243"/>
+      <c r="Z32" s="243"/>
+      <c r="AA32" s="243"/>
+      <c r="AB32" s="243"/>
+      <c r="AC32" s="243"/>
+      <c r="AD32" s="243"/>
+      <c r="AE32" s="243"/>
+      <c r="AF32" s="243"/>
+      <c r="AG32" s="243"/>
+      <c r="AH32" s="243"/>
+      <c r="AI32" s="243"/>
+      <c r="AJ32" s="243"/>
+      <c r="AK32" s="243"/>
+      <c r="AL32" s="243"/>
+      <c r="AM32" s="243"/>
+      <c r="AN32" s="243"/>
+      <c r="AO32" s="243"/>
+      <c r="AP32" s="243"/>
+      <c r="AQ32" s="243"/>
+      <c r="AR32" s="243"/>
+      <c r="AS32" s="243"/>
+      <c r="AT32" s="243"/>
+      <c r="AU32" s="243"/>
+      <c r="AV32" s="243"/>
+      <c r="AW32" s="243"/>
+      <c r="AX32" s="243"/>
+      <c r="AY32" s="243"/>
+      <c r="AZ32" s="244"/>
     </row>
     <row r="33" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="244"/>
-      <c r="B33" s="245"/>
-      <c r="C33" s="245"/>
+      <c r="A33" s="248"/>
+      <c r="B33" s="249"/>
+      <c r="C33" s="249"/>
       <c r="D33" s="10"/>
-      <c r="E33" s="253"/>
-      <c r="F33" s="253"/>
-      <c r="G33" s="253"/>
-      <c r="H33" s="253"/>
-      <c r="I33" s="253"/>
-      <c r="J33" s="253"/>
-      <c r="K33" s="253"/>
-      <c r="L33" s="253"/>
-      <c r="M33" s="253"/>
-      <c r="N33" s="253"/>
-      <c r="O33" s="253"/>
-      <c r="P33" s="253"/>
-      <c r="Q33" s="253"/>
-      <c r="R33" s="253"/>
-      <c r="S33" s="253"/>
-      <c r="T33" s="253"/>
-      <c r="U33" s="253"/>
-      <c r="V33" s="253"/>
-      <c r="W33" s="253"/>
-      <c r="X33" s="253"/>
-      <c r="Y33" s="253"/>
-      <c r="Z33" s="253"/>
-      <c r="AA33" s="253"/>
-      <c r="AB33" s="253"/>
-      <c r="AC33" s="253"/>
-      <c r="AD33" s="253"/>
-      <c r="AE33" s="253"/>
-      <c r="AF33" s="253"/>
-      <c r="AG33" s="253"/>
-      <c r="AH33" s="253"/>
-      <c r="AI33" s="253"/>
-      <c r="AJ33" s="253"/>
-      <c r="AK33" s="253"/>
-      <c r="AL33" s="253"/>
-      <c r="AM33" s="253"/>
-      <c r="AN33" s="253"/>
-      <c r="AO33" s="253"/>
-      <c r="AP33" s="253"/>
-      <c r="AQ33" s="253"/>
-      <c r="AR33" s="253"/>
-      <c r="AS33" s="253"/>
-      <c r="AT33" s="253"/>
-      <c r="AU33" s="253"/>
-      <c r="AV33" s="253"/>
-      <c r="AW33" s="253"/>
-      <c r="AX33" s="253"/>
-      <c r="AY33" s="253"/>
-      <c r="AZ33" s="254"/>
+      <c r="E33" s="243"/>
+      <c r="F33" s="243"/>
+      <c r="G33" s="243"/>
+      <c r="H33" s="243"/>
+      <c r="I33" s="243"/>
+      <c r="J33" s="243"/>
+      <c r="K33" s="243"/>
+      <c r="L33" s="243"/>
+      <c r="M33" s="243"/>
+      <c r="N33" s="243"/>
+      <c r="O33" s="243"/>
+      <c r="P33" s="243"/>
+      <c r="Q33" s="243"/>
+      <c r="R33" s="243"/>
+      <c r="S33" s="243"/>
+      <c r="T33" s="243"/>
+      <c r="U33" s="243"/>
+      <c r="V33" s="243"/>
+      <c r="W33" s="243"/>
+      <c r="X33" s="243"/>
+      <c r="Y33" s="243"/>
+      <c r="Z33" s="243"/>
+      <c r="AA33" s="243"/>
+      <c r="AB33" s="243"/>
+      <c r="AC33" s="243"/>
+      <c r="AD33" s="243"/>
+      <c r="AE33" s="243"/>
+      <c r="AF33" s="243"/>
+      <c r="AG33" s="243"/>
+      <c r="AH33" s="243"/>
+      <c r="AI33" s="243"/>
+      <c r="AJ33" s="243"/>
+      <c r="AK33" s="243"/>
+      <c r="AL33" s="243"/>
+      <c r="AM33" s="243"/>
+      <c r="AN33" s="243"/>
+      <c r="AO33" s="243"/>
+      <c r="AP33" s="243"/>
+      <c r="AQ33" s="243"/>
+      <c r="AR33" s="243"/>
+      <c r="AS33" s="243"/>
+      <c r="AT33" s="243"/>
+      <c r="AU33" s="243"/>
+      <c r="AV33" s="243"/>
+      <c r="AW33" s="243"/>
+      <c r="AX33" s="243"/>
+      <c r="AY33" s="243"/>
+      <c r="AZ33" s="244"/>
     </row>
     <row r="34" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="244"/>
-      <c r="B34" s="245"/>
-      <c r="C34" s="245"/>
+      <c r="A34" s="248"/>
+      <c r="B34" s="249"/>
+      <c r="C34" s="249"/>
       <c r="D34" s="10"/>
-      <c r="E34" s="253"/>
-      <c r="F34" s="253"/>
-      <c r="G34" s="253"/>
-      <c r="H34" s="253"/>
-      <c r="I34" s="253"/>
-      <c r="J34" s="253"/>
-      <c r="K34" s="253"/>
-      <c r="L34" s="253"/>
-      <c r="M34" s="253"/>
-      <c r="N34" s="253"/>
-      <c r="O34" s="253"/>
-      <c r="P34" s="253"/>
-      <c r="Q34" s="253"/>
-      <c r="R34" s="253"/>
-      <c r="S34" s="253"/>
-      <c r="T34" s="253"/>
-      <c r="U34" s="253"/>
-      <c r="V34" s="253"/>
-      <c r="W34" s="253"/>
-      <c r="X34" s="253"/>
-      <c r="Y34" s="253"/>
-      <c r="Z34" s="253"/>
-      <c r="AA34" s="253"/>
-      <c r="AB34" s="253"/>
-      <c r="AC34" s="253"/>
-      <c r="AD34" s="253"/>
-      <c r="AE34" s="253"/>
-      <c r="AF34" s="253"/>
-      <c r="AG34" s="253"/>
-      <c r="AH34" s="253"/>
-      <c r="AI34" s="253"/>
-      <c r="AJ34" s="253"/>
-      <c r="AK34" s="253"/>
-      <c r="AL34" s="253"/>
-      <c r="AM34" s="253"/>
-      <c r="AN34" s="253"/>
-      <c r="AO34" s="253"/>
-      <c r="AP34" s="253"/>
-      <c r="AQ34" s="253"/>
-      <c r="AR34" s="253"/>
-      <c r="AS34" s="253"/>
-      <c r="AT34" s="253"/>
-      <c r="AU34" s="253"/>
-      <c r="AV34" s="253"/>
-      <c r="AW34" s="253"/>
-      <c r="AX34" s="253"/>
-      <c r="AY34" s="253"/>
-      <c r="AZ34" s="254"/>
+      <c r="E34" s="243"/>
+      <c r="F34" s="243"/>
+      <c r="G34" s="243"/>
+      <c r="H34" s="243"/>
+      <c r="I34" s="243"/>
+      <c r="J34" s="243"/>
+      <c r="K34" s="243"/>
+      <c r="L34" s="243"/>
+      <c r="M34" s="243"/>
+      <c r="N34" s="243"/>
+      <c r="O34" s="243"/>
+      <c r="P34" s="243"/>
+      <c r="Q34" s="243"/>
+      <c r="R34" s="243"/>
+      <c r="S34" s="243"/>
+      <c r="T34" s="243"/>
+      <c r="U34" s="243"/>
+      <c r="V34" s="243"/>
+      <c r="W34" s="243"/>
+      <c r="X34" s="243"/>
+      <c r="Y34" s="243"/>
+      <c r="Z34" s="243"/>
+      <c r="AA34" s="243"/>
+      <c r="AB34" s="243"/>
+      <c r="AC34" s="243"/>
+      <c r="AD34" s="243"/>
+      <c r="AE34" s="243"/>
+      <c r="AF34" s="243"/>
+      <c r="AG34" s="243"/>
+      <c r="AH34" s="243"/>
+      <c r="AI34" s="243"/>
+      <c r="AJ34" s="243"/>
+      <c r="AK34" s="243"/>
+      <c r="AL34" s="243"/>
+      <c r="AM34" s="243"/>
+      <c r="AN34" s="243"/>
+      <c r="AO34" s="243"/>
+      <c r="AP34" s="243"/>
+      <c r="AQ34" s="243"/>
+      <c r="AR34" s="243"/>
+      <c r="AS34" s="243"/>
+      <c r="AT34" s="243"/>
+      <c r="AU34" s="243"/>
+      <c r="AV34" s="243"/>
+      <c r="AW34" s="243"/>
+      <c r="AX34" s="243"/>
+      <c r="AY34" s="243"/>
+      <c r="AZ34" s="244"/>
     </row>
     <row r="35" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="244"/>
-      <c r="B35" s="245"/>
-      <c r="C35" s="245"/>
+      <c r="A35" s="248"/>
+      <c r="B35" s="249"/>
+      <c r="C35" s="249"/>
       <c r="D35" s="10"/>
-      <c r="E35" s="253"/>
-      <c r="F35" s="253"/>
-      <c r="G35" s="253"/>
-      <c r="H35" s="253"/>
-      <c r="I35" s="253"/>
-      <c r="J35" s="253"/>
-      <c r="K35" s="253"/>
-      <c r="L35" s="253"/>
-      <c r="M35" s="253"/>
-      <c r="N35" s="253"/>
-      <c r="O35" s="253"/>
-      <c r="P35" s="253"/>
-      <c r="Q35" s="253"/>
-      <c r="R35" s="253"/>
-      <c r="S35" s="253"/>
-      <c r="T35" s="253"/>
-      <c r="U35" s="253"/>
-      <c r="V35" s="253"/>
-      <c r="W35" s="253"/>
-      <c r="X35" s="253"/>
-      <c r="Y35" s="253"/>
-      <c r="Z35" s="253"/>
-      <c r="AA35" s="253"/>
-      <c r="AB35" s="253"/>
-      <c r="AC35" s="253"/>
-      <c r="AD35" s="253"/>
-      <c r="AE35" s="253"/>
-      <c r="AF35" s="253"/>
-      <c r="AG35" s="253"/>
-      <c r="AH35" s="253"/>
-      <c r="AI35" s="253"/>
-      <c r="AJ35" s="253"/>
-      <c r="AK35" s="253"/>
-      <c r="AL35" s="253"/>
-      <c r="AM35" s="253"/>
-      <c r="AN35" s="253"/>
-      <c r="AO35" s="253"/>
-      <c r="AP35" s="253"/>
-      <c r="AQ35" s="253"/>
-      <c r="AR35" s="253"/>
-      <c r="AS35" s="253"/>
-      <c r="AT35" s="253"/>
-      <c r="AU35" s="253"/>
-      <c r="AV35" s="253"/>
-      <c r="AW35" s="253"/>
-      <c r="AX35" s="253"/>
-      <c r="AY35" s="253"/>
-      <c r="AZ35" s="254"/>
+      <c r="E35" s="243"/>
+      <c r="F35" s="243"/>
+      <c r="G35" s="243"/>
+      <c r="H35" s="243"/>
+      <c r="I35" s="243"/>
+      <c r="J35" s="243"/>
+      <c r="K35" s="243"/>
+      <c r="L35" s="243"/>
+      <c r="M35" s="243"/>
+      <c r="N35" s="243"/>
+      <c r="O35" s="243"/>
+      <c r="P35" s="243"/>
+      <c r="Q35" s="243"/>
+      <c r="R35" s="243"/>
+      <c r="S35" s="243"/>
+      <c r="T35" s="243"/>
+      <c r="U35" s="243"/>
+      <c r="V35" s="243"/>
+      <c r="W35" s="243"/>
+      <c r="X35" s="243"/>
+      <c r="Y35" s="243"/>
+      <c r="Z35" s="243"/>
+      <c r="AA35" s="243"/>
+      <c r="AB35" s="243"/>
+      <c r="AC35" s="243"/>
+      <c r="AD35" s="243"/>
+      <c r="AE35" s="243"/>
+      <c r="AF35" s="243"/>
+      <c r="AG35" s="243"/>
+      <c r="AH35" s="243"/>
+      <c r="AI35" s="243"/>
+      <c r="AJ35" s="243"/>
+      <c r="AK35" s="243"/>
+      <c r="AL35" s="243"/>
+      <c r="AM35" s="243"/>
+      <c r="AN35" s="243"/>
+      <c r="AO35" s="243"/>
+      <c r="AP35" s="243"/>
+      <c r="AQ35" s="243"/>
+      <c r="AR35" s="243"/>
+      <c r="AS35" s="243"/>
+      <c r="AT35" s="243"/>
+      <c r="AU35" s="243"/>
+      <c r="AV35" s="243"/>
+      <c r="AW35" s="243"/>
+      <c r="AX35" s="243"/>
+      <c r="AY35" s="243"/>
+      <c r="AZ35" s="244"/>
     </row>
     <row r="36" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="244"/>
-      <c r="B36" s="245"/>
-      <c r="C36" s="245"/>
+      <c r="A36" s="248"/>
+      <c r="B36" s="249"/>
+      <c r="C36" s="249"/>
       <c r="D36" s="10"/>
-      <c r="E36" s="253"/>
-      <c r="F36" s="253"/>
-      <c r="G36" s="253"/>
-      <c r="H36" s="253"/>
-      <c r="I36" s="253"/>
-      <c r="J36" s="253"/>
-      <c r="K36" s="253"/>
-      <c r="L36" s="253"/>
-      <c r="M36" s="253"/>
-      <c r="N36" s="253"/>
-      <c r="O36" s="253"/>
-      <c r="P36" s="253"/>
-      <c r="Q36" s="253"/>
-      <c r="R36" s="253"/>
-      <c r="S36" s="253"/>
-      <c r="T36" s="253"/>
-      <c r="U36" s="253"/>
-      <c r="V36" s="253"/>
-      <c r="W36" s="253"/>
-      <c r="X36" s="253"/>
-      <c r="Y36" s="253"/>
-      <c r="Z36" s="253"/>
-      <c r="AA36" s="253"/>
-      <c r="AB36" s="253"/>
-      <c r="AC36" s="253"/>
-      <c r="AD36" s="253"/>
-      <c r="AE36" s="253"/>
-      <c r="AF36" s="253"/>
-      <c r="AG36" s="253"/>
-      <c r="AH36" s="253"/>
-      <c r="AI36" s="253"/>
-      <c r="AJ36" s="253"/>
-      <c r="AK36" s="253"/>
-      <c r="AL36" s="253"/>
-      <c r="AM36" s="253"/>
-      <c r="AN36" s="253"/>
-      <c r="AO36" s="253"/>
-      <c r="AP36" s="253"/>
-      <c r="AQ36" s="253"/>
-      <c r="AR36" s="253"/>
-      <c r="AS36" s="253"/>
-      <c r="AT36" s="253"/>
-      <c r="AU36" s="253"/>
-      <c r="AV36" s="253"/>
-      <c r="AW36" s="253"/>
-      <c r="AX36" s="253"/>
-      <c r="AY36" s="253"/>
-      <c r="AZ36" s="254"/>
+      <c r="E36" s="243"/>
+      <c r="F36" s="243"/>
+      <c r="G36" s="243"/>
+      <c r="H36" s="243"/>
+      <c r="I36" s="243"/>
+      <c r="J36" s="243"/>
+      <c r="K36" s="243"/>
+      <c r="L36" s="243"/>
+      <c r="M36" s="243"/>
+      <c r="N36" s="243"/>
+      <c r="O36" s="243"/>
+      <c r="P36" s="243"/>
+      <c r="Q36" s="243"/>
+      <c r="R36" s="243"/>
+      <c r="S36" s="243"/>
+      <c r="T36" s="243"/>
+      <c r="U36" s="243"/>
+      <c r="V36" s="243"/>
+      <c r="W36" s="243"/>
+      <c r="X36" s="243"/>
+      <c r="Y36" s="243"/>
+      <c r="Z36" s="243"/>
+      <c r="AA36" s="243"/>
+      <c r="AB36" s="243"/>
+      <c r="AC36" s="243"/>
+      <c r="AD36" s="243"/>
+      <c r="AE36" s="243"/>
+      <c r="AF36" s="243"/>
+      <c r="AG36" s="243"/>
+      <c r="AH36" s="243"/>
+      <c r="AI36" s="243"/>
+      <c r="AJ36" s="243"/>
+      <c r="AK36" s="243"/>
+      <c r="AL36" s="243"/>
+      <c r="AM36" s="243"/>
+      <c r="AN36" s="243"/>
+      <c r="AO36" s="243"/>
+      <c r="AP36" s="243"/>
+      <c r="AQ36" s="243"/>
+      <c r="AR36" s="243"/>
+      <c r="AS36" s="243"/>
+      <c r="AT36" s="243"/>
+      <c r="AU36" s="243"/>
+      <c r="AV36" s="243"/>
+      <c r="AW36" s="243"/>
+      <c r="AX36" s="243"/>
+      <c r="AY36" s="243"/>
+      <c r="AZ36" s="244"/>
     </row>
     <row r="37" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="244"/>
-      <c r="B37" s="245"/>
-      <c r="C37" s="245"/>
+      <c r="A37" s="248"/>
+      <c r="B37" s="249"/>
+      <c r="C37" s="249"/>
       <c r="D37" s="10"/>
-      <c r="E37" s="253"/>
-      <c r="F37" s="253"/>
-      <c r="G37" s="253"/>
-      <c r="H37" s="253"/>
-      <c r="I37" s="253"/>
-      <c r="J37" s="253"/>
-      <c r="K37" s="253"/>
-      <c r="L37" s="253"/>
-      <c r="M37" s="253"/>
-      <c r="N37" s="253"/>
-      <c r="O37" s="253"/>
-      <c r="P37" s="253"/>
-      <c r="Q37" s="253"/>
-      <c r="R37" s="253"/>
-      <c r="S37" s="253"/>
-      <c r="T37" s="253"/>
-      <c r="U37" s="253"/>
-      <c r="V37" s="253"/>
-      <c r="W37" s="253"/>
-      <c r="X37" s="253"/>
-      <c r="Y37" s="253"/>
-      <c r="Z37" s="253"/>
-      <c r="AA37" s="253"/>
-      <c r="AB37" s="253"/>
-      <c r="AC37" s="253"/>
-      <c r="AD37" s="253"/>
-      <c r="AE37" s="253"/>
-      <c r="AF37" s="253"/>
-      <c r="AG37" s="253"/>
-      <c r="AH37" s="253"/>
-      <c r="AI37" s="253"/>
-      <c r="AJ37" s="253"/>
-      <c r="AK37" s="253"/>
-      <c r="AL37" s="253"/>
-      <c r="AM37" s="253"/>
-      <c r="AN37" s="253"/>
-      <c r="AO37" s="253"/>
-      <c r="AP37" s="253"/>
-      <c r="AQ37" s="253"/>
-      <c r="AR37" s="253"/>
-      <c r="AS37" s="253"/>
-      <c r="AT37" s="253"/>
-      <c r="AU37" s="253"/>
-      <c r="AV37" s="253"/>
-      <c r="AW37" s="253"/>
-      <c r="AX37" s="253"/>
-      <c r="AY37" s="253"/>
-      <c r="AZ37" s="254"/>
+      <c r="E37" s="243"/>
+      <c r="F37" s="243"/>
+      <c r="G37" s="243"/>
+      <c r="H37" s="243"/>
+      <c r="I37" s="243"/>
+      <c r="J37" s="243"/>
+      <c r="K37" s="243"/>
+      <c r="L37" s="243"/>
+      <c r="M37" s="243"/>
+      <c r="N37" s="243"/>
+      <c r="O37" s="243"/>
+      <c r="P37" s="243"/>
+      <c r="Q37" s="243"/>
+      <c r="R37" s="243"/>
+      <c r="S37" s="243"/>
+      <c r="T37" s="243"/>
+      <c r="U37" s="243"/>
+      <c r="V37" s="243"/>
+      <c r="W37" s="243"/>
+      <c r="X37" s="243"/>
+      <c r="Y37" s="243"/>
+      <c r="Z37" s="243"/>
+      <c r="AA37" s="243"/>
+      <c r="AB37" s="243"/>
+      <c r="AC37" s="243"/>
+      <c r="AD37" s="243"/>
+      <c r="AE37" s="243"/>
+      <c r="AF37" s="243"/>
+      <c r="AG37" s="243"/>
+      <c r="AH37" s="243"/>
+      <c r="AI37" s="243"/>
+      <c r="AJ37" s="243"/>
+      <c r="AK37" s="243"/>
+      <c r="AL37" s="243"/>
+      <c r="AM37" s="243"/>
+      <c r="AN37" s="243"/>
+      <c r="AO37" s="243"/>
+      <c r="AP37" s="243"/>
+      <c r="AQ37" s="243"/>
+      <c r="AR37" s="243"/>
+      <c r="AS37" s="243"/>
+      <c r="AT37" s="243"/>
+      <c r="AU37" s="243"/>
+      <c r="AV37" s="243"/>
+      <c r="AW37" s="243"/>
+      <c r="AX37" s="243"/>
+      <c r="AY37" s="243"/>
+      <c r="AZ37" s="244"/>
     </row>
     <row r="38" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="244"/>
-      <c r="B38" s="245"/>
-      <c r="C38" s="245"/>
+      <c r="A38" s="248"/>
+      <c r="B38" s="249"/>
+      <c r="C38" s="249"/>
       <c r="D38" s="10"/>
-      <c r="E38" s="253"/>
-      <c r="F38" s="253"/>
-      <c r="G38" s="253"/>
-      <c r="H38" s="253"/>
-      <c r="I38" s="253"/>
-      <c r="J38" s="253"/>
-      <c r="K38" s="253"/>
-      <c r="L38" s="253"/>
-      <c r="M38" s="253"/>
-      <c r="N38" s="253"/>
-      <c r="O38" s="253"/>
-      <c r="P38" s="253"/>
-      <c r="Q38" s="253"/>
-      <c r="R38" s="253"/>
-      <c r="S38" s="253"/>
-      <c r="T38" s="253"/>
-      <c r="U38" s="253"/>
-      <c r="V38" s="253"/>
-      <c r="W38" s="253"/>
-      <c r="X38" s="253"/>
-      <c r="Y38" s="253"/>
-      <c r="Z38" s="253"/>
-      <c r="AA38" s="253"/>
-      <c r="AB38" s="253"/>
-      <c r="AC38" s="253"/>
-      <c r="AD38" s="253"/>
-      <c r="AE38" s="253"/>
-      <c r="AF38" s="253"/>
-      <c r="AG38" s="253"/>
-      <c r="AH38" s="253"/>
-      <c r="AI38" s="253"/>
-      <c r="AJ38" s="253"/>
-      <c r="AK38" s="253"/>
-      <c r="AL38" s="253"/>
-      <c r="AM38" s="253"/>
-      <c r="AN38" s="253"/>
-      <c r="AO38" s="253"/>
-      <c r="AP38" s="253"/>
-      <c r="AQ38" s="253"/>
-      <c r="AR38" s="253"/>
-      <c r="AS38" s="253"/>
-      <c r="AT38" s="253"/>
-      <c r="AU38" s="253"/>
-      <c r="AV38" s="253"/>
-      <c r="AW38" s="253"/>
-      <c r="AX38" s="253"/>
-      <c r="AY38" s="253"/>
-      <c r="AZ38" s="254"/>
+      <c r="E38" s="243"/>
+      <c r="F38" s="243"/>
+      <c r="G38" s="243"/>
+      <c r="H38" s="243"/>
+      <c r="I38" s="243"/>
+      <c r="J38" s="243"/>
+      <c r="K38" s="243"/>
+      <c r="L38" s="243"/>
+      <c r="M38" s="243"/>
+      <c r="N38" s="243"/>
+      <c r="O38" s="243"/>
+      <c r="P38" s="243"/>
+      <c r="Q38" s="243"/>
+      <c r="R38" s="243"/>
+      <c r="S38" s="243"/>
+      <c r="T38" s="243"/>
+      <c r="U38" s="243"/>
+      <c r="V38" s="243"/>
+      <c r="W38" s="243"/>
+      <c r="X38" s="243"/>
+      <c r="Y38" s="243"/>
+      <c r="Z38" s="243"/>
+      <c r="AA38" s="243"/>
+      <c r="AB38" s="243"/>
+      <c r="AC38" s="243"/>
+      <c r="AD38" s="243"/>
+      <c r="AE38" s="243"/>
+      <c r="AF38" s="243"/>
+      <c r="AG38" s="243"/>
+      <c r="AH38" s="243"/>
+      <c r="AI38" s="243"/>
+      <c r="AJ38" s="243"/>
+      <c r="AK38" s="243"/>
+      <c r="AL38" s="243"/>
+      <c r="AM38" s="243"/>
+      <c r="AN38" s="243"/>
+      <c r="AO38" s="243"/>
+      <c r="AP38" s="243"/>
+      <c r="AQ38" s="243"/>
+      <c r="AR38" s="243"/>
+      <c r="AS38" s="243"/>
+      <c r="AT38" s="243"/>
+      <c r="AU38" s="243"/>
+      <c r="AV38" s="243"/>
+      <c r="AW38" s="243"/>
+      <c r="AX38" s="243"/>
+      <c r="AY38" s="243"/>
+      <c r="AZ38" s="244"/>
     </row>
     <row r="39" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="244"/>
-      <c r="B39" s="245"/>
-      <c r="C39" s="245"/>
+      <c r="A39" s="248"/>
+      <c r="B39" s="249"/>
+      <c r="C39" s="249"/>
       <c r="D39" s="10"/>
-      <c r="E39" s="253"/>
-      <c r="F39" s="253"/>
-      <c r="G39" s="253"/>
-      <c r="H39" s="253"/>
-      <c r="I39" s="253"/>
-      <c r="J39" s="253"/>
-      <c r="K39" s="253"/>
-      <c r="L39" s="253"/>
-      <c r="M39" s="253"/>
-      <c r="N39" s="253"/>
-      <c r="O39" s="253"/>
-      <c r="P39" s="253"/>
-      <c r="Q39" s="253"/>
-      <c r="R39" s="253"/>
-      <c r="S39" s="253"/>
-      <c r="T39" s="253"/>
-      <c r="U39" s="253"/>
-      <c r="V39" s="253"/>
-      <c r="W39" s="253"/>
-      <c r="X39" s="253"/>
-      <c r="Y39" s="253"/>
-      <c r="Z39" s="253"/>
-      <c r="AA39" s="253"/>
-      <c r="AB39" s="253"/>
-      <c r="AC39" s="253"/>
-      <c r="AD39" s="253"/>
-      <c r="AE39" s="253"/>
-      <c r="AF39" s="253"/>
-      <c r="AG39" s="253"/>
-      <c r="AH39" s="253"/>
-      <c r="AI39" s="253"/>
-      <c r="AJ39" s="253"/>
-      <c r="AK39" s="253"/>
-      <c r="AL39" s="253"/>
-      <c r="AM39" s="253"/>
-      <c r="AN39" s="253"/>
-      <c r="AO39" s="253"/>
-      <c r="AP39" s="253"/>
-      <c r="AQ39" s="253"/>
-      <c r="AR39" s="253"/>
-      <c r="AS39" s="253"/>
-      <c r="AT39" s="253"/>
-      <c r="AU39" s="253"/>
-      <c r="AV39" s="253"/>
-      <c r="AW39" s="253"/>
-      <c r="AX39" s="253"/>
-      <c r="AY39" s="253"/>
-      <c r="AZ39" s="254"/>
+      <c r="E39" s="243"/>
+      <c r="F39" s="243"/>
+      <c r="G39" s="243"/>
+      <c r="H39" s="243"/>
+      <c r="I39" s="243"/>
+      <c r="J39" s="243"/>
+      <c r="K39" s="243"/>
+      <c r="L39" s="243"/>
+      <c r="M39" s="243"/>
+      <c r="N39" s="243"/>
+      <c r="O39" s="243"/>
+      <c r="P39" s="243"/>
+      <c r="Q39" s="243"/>
+      <c r="R39" s="243"/>
+      <c r="S39" s="243"/>
+      <c r="T39" s="243"/>
+      <c r="U39" s="243"/>
+      <c r="V39" s="243"/>
+      <c r="W39" s="243"/>
+      <c r="X39" s="243"/>
+      <c r="Y39" s="243"/>
+      <c r="Z39" s="243"/>
+      <c r="AA39" s="243"/>
+      <c r="AB39" s="243"/>
+      <c r="AC39" s="243"/>
+      <c r="AD39" s="243"/>
+      <c r="AE39" s="243"/>
+      <c r="AF39" s="243"/>
+      <c r="AG39" s="243"/>
+      <c r="AH39" s="243"/>
+      <c r="AI39" s="243"/>
+      <c r="AJ39" s="243"/>
+      <c r="AK39" s="243"/>
+      <c r="AL39" s="243"/>
+      <c r="AM39" s="243"/>
+      <c r="AN39" s="243"/>
+      <c r="AO39" s="243"/>
+      <c r="AP39" s="243"/>
+      <c r="AQ39" s="243"/>
+      <c r="AR39" s="243"/>
+      <c r="AS39" s="243"/>
+      <c r="AT39" s="243"/>
+      <c r="AU39" s="243"/>
+      <c r="AV39" s="243"/>
+      <c r="AW39" s="243"/>
+      <c r="AX39" s="243"/>
+      <c r="AY39" s="243"/>
+      <c r="AZ39" s="244"/>
     </row>
     <row r="40" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="244"/>
-      <c r="B40" s="245"/>
-      <c r="C40" s="245"/>
+      <c r="A40" s="248"/>
+      <c r="B40" s="249"/>
+      <c r="C40" s="249"/>
       <c r="D40" s="10"/>
-      <c r="E40" s="253"/>
-      <c r="F40" s="253"/>
-      <c r="G40" s="253"/>
-      <c r="H40" s="253"/>
-      <c r="I40" s="253"/>
-      <c r="J40" s="253"/>
-      <c r="K40" s="253"/>
-      <c r="L40" s="253"/>
-      <c r="M40" s="253"/>
-      <c r="N40" s="253"/>
-      <c r="O40" s="253"/>
-      <c r="P40" s="253"/>
-      <c r="Q40" s="253"/>
-      <c r="R40" s="253"/>
-      <c r="S40" s="253"/>
-      <c r="T40" s="253"/>
-      <c r="U40" s="253"/>
-      <c r="V40" s="253"/>
-      <c r="W40" s="253"/>
-      <c r="X40" s="253"/>
-      <c r="Y40" s="253"/>
-      <c r="Z40" s="253"/>
-      <c r="AA40" s="253"/>
-      <c r="AB40" s="253"/>
-      <c r="AC40" s="253"/>
-      <c r="AD40" s="253"/>
-      <c r="AE40" s="253"/>
-      <c r="AF40" s="253"/>
-      <c r="AG40" s="253"/>
-      <c r="AH40" s="253"/>
-      <c r="AI40" s="253"/>
-      <c r="AJ40" s="253"/>
-      <c r="AK40" s="253"/>
-      <c r="AL40" s="253"/>
-      <c r="AM40" s="253"/>
-      <c r="AN40" s="253"/>
-      <c r="AO40" s="253"/>
-      <c r="AP40" s="253"/>
-      <c r="AQ40" s="253"/>
-      <c r="AR40" s="253"/>
-      <c r="AS40" s="253"/>
-      <c r="AT40" s="253"/>
-      <c r="AU40" s="253"/>
-      <c r="AV40" s="253"/>
-      <c r="AW40" s="253"/>
-      <c r="AX40" s="253"/>
-      <c r="AY40" s="253"/>
-      <c r="AZ40" s="254"/>
+      <c r="E40" s="243"/>
+      <c r="F40" s="243"/>
+      <c r="G40" s="243"/>
+      <c r="H40" s="243"/>
+      <c r="I40" s="243"/>
+      <c r="J40" s="243"/>
+      <c r="K40" s="243"/>
+      <c r="L40" s="243"/>
+      <c r="M40" s="243"/>
+      <c r="N40" s="243"/>
+      <c r="O40" s="243"/>
+      <c r="P40" s="243"/>
+      <c r="Q40" s="243"/>
+      <c r="R40" s="243"/>
+      <c r="S40" s="243"/>
+      <c r="T40" s="243"/>
+      <c r="U40" s="243"/>
+      <c r="V40" s="243"/>
+      <c r="W40" s="243"/>
+      <c r="X40" s="243"/>
+      <c r="Y40" s="243"/>
+      <c r="Z40" s="243"/>
+      <c r="AA40" s="243"/>
+      <c r="AB40" s="243"/>
+      <c r="AC40" s="243"/>
+      <c r="AD40" s="243"/>
+      <c r="AE40" s="243"/>
+      <c r="AF40" s="243"/>
+      <c r="AG40" s="243"/>
+      <c r="AH40" s="243"/>
+      <c r="AI40" s="243"/>
+      <c r="AJ40" s="243"/>
+      <c r="AK40" s="243"/>
+      <c r="AL40" s="243"/>
+      <c r="AM40" s="243"/>
+      <c r="AN40" s="243"/>
+      <c r="AO40" s="243"/>
+      <c r="AP40" s="243"/>
+      <c r="AQ40" s="243"/>
+      <c r="AR40" s="243"/>
+      <c r="AS40" s="243"/>
+      <c r="AT40" s="243"/>
+      <c r="AU40" s="243"/>
+      <c r="AV40" s="243"/>
+      <c r="AW40" s="243"/>
+      <c r="AX40" s="243"/>
+      <c r="AY40" s="243"/>
+      <c r="AZ40" s="244"/>
     </row>
     <row r="41" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="244"/>
-      <c r="B41" s="245"/>
-      <c r="C41" s="245"/>
+      <c r="A41" s="248"/>
+      <c r="B41" s="249"/>
+      <c r="C41" s="249"/>
       <c r="D41" s="10"/>
-      <c r="E41" s="253"/>
-      <c r="F41" s="253"/>
-      <c r="G41" s="253"/>
-      <c r="H41" s="253"/>
-      <c r="I41" s="253"/>
-      <c r="J41" s="253"/>
-      <c r="K41" s="253"/>
-      <c r="L41" s="253"/>
-      <c r="M41" s="253"/>
-      <c r="N41" s="253"/>
-      <c r="O41" s="253"/>
-      <c r="P41" s="253"/>
-      <c r="Q41" s="253"/>
-      <c r="R41" s="253"/>
-      <c r="S41" s="253"/>
-      <c r="T41" s="253"/>
-      <c r="U41" s="253"/>
-      <c r="V41" s="253"/>
-      <c r="W41" s="253"/>
-      <c r="X41" s="253"/>
-      <c r="Y41" s="253"/>
-      <c r="Z41" s="253"/>
-      <c r="AA41" s="253"/>
-      <c r="AB41" s="253"/>
-      <c r="AC41" s="253"/>
-      <c r="AD41" s="253"/>
-      <c r="AE41" s="253"/>
-      <c r="AF41" s="253"/>
-      <c r="AG41" s="253"/>
-      <c r="AH41" s="253"/>
-      <c r="AI41" s="253"/>
-      <c r="AJ41" s="253"/>
-      <c r="AK41" s="253"/>
-      <c r="AL41" s="253"/>
-      <c r="AM41" s="253"/>
-      <c r="AN41" s="253"/>
-      <c r="AO41" s="253"/>
-      <c r="AP41" s="253"/>
-      <c r="AQ41" s="253"/>
-      <c r="AR41" s="253"/>
-      <c r="AS41" s="253"/>
-      <c r="AT41" s="253"/>
-      <c r="AU41" s="253"/>
-      <c r="AV41" s="253"/>
-      <c r="AW41" s="253"/>
-      <c r="AX41" s="253"/>
-      <c r="AY41" s="253"/>
-      <c r="AZ41" s="254"/>
+      <c r="E41" s="243"/>
+      <c r="F41" s="243"/>
+      <c r="G41" s="243"/>
+      <c r="H41" s="243"/>
+      <c r="I41" s="243"/>
+      <c r="J41" s="243"/>
+      <c r="K41" s="243"/>
+      <c r="L41" s="243"/>
+      <c r="M41" s="243"/>
+      <c r="N41" s="243"/>
+      <c r="O41" s="243"/>
+      <c r="P41" s="243"/>
+      <c r="Q41" s="243"/>
+      <c r="R41" s="243"/>
+      <c r="S41" s="243"/>
+      <c r="T41" s="243"/>
+      <c r="U41" s="243"/>
+      <c r="V41" s="243"/>
+      <c r="W41" s="243"/>
+      <c r="X41" s="243"/>
+      <c r="Y41" s="243"/>
+      <c r="Z41" s="243"/>
+      <c r="AA41" s="243"/>
+      <c r="AB41" s="243"/>
+      <c r="AC41" s="243"/>
+      <c r="AD41" s="243"/>
+      <c r="AE41" s="243"/>
+      <c r="AF41" s="243"/>
+      <c r="AG41" s="243"/>
+      <c r="AH41" s="243"/>
+      <c r="AI41" s="243"/>
+      <c r="AJ41" s="243"/>
+      <c r="AK41" s="243"/>
+      <c r="AL41" s="243"/>
+      <c r="AM41" s="243"/>
+      <c r="AN41" s="243"/>
+      <c r="AO41" s="243"/>
+      <c r="AP41" s="243"/>
+      <c r="AQ41" s="243"/>
+      <c r="AR41" s="243"/>
+      <c r="AS41" s="243"/>
+      <c r="AT41" s="243"/>
+      <c r="AU41" s="243"/>
+      <c r="AV41" s="243"/>
+      <c r="AW41" s="243"/>
+      <c r="AX41" s="243"/>
+      <c r="AY41" s="243"/>
+      <c r="AZ41" s="244"/>
     </row>
     <row r="42" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="244"/>
-      <c r="B42" s="245"/>
-      <c r="C42" s="245"/>
+      <c r="A42" s="248"/>
+      <c r="B42" s="249"/>
+      <c r="C42" s="249"/>
       <c r="D42" s="10"/>
-      <c r="E42" s="253"/>
-      <c r="F42" s="253"/>
-      <c r="G42" s="253"/>
-      <c r="H42" s="253"/>
-      <c r="I42" s="253"/>
-      <c r="J42" s="253"/>
-      <c r="K42" s="253"/>
-      <c r="L42" s="253"/>
-      <c r="M42" s="253"/>
-      <c r="N42" s="253"/>
-      <c r="O42" s="253"/>
-      <c r="P42" s="253"/>
-      <c r="Q42" s="253"/>
-      <c r="R42" s="253"/>
-      <c r="S42" s="253"/>
-      <c r="T42" s="253"/>
-      <c r="U42" s="253"/>
-      <c r="V42" s="253"/>
-      <c r="W42" s="253"/>
-      <c r="X42" s="253"/>
-      <c r="Y42" s="253"/>
-      <c r="Z42" s="253"/>
-      <c r="AA42" s="253"/>
-      <c r="AB42" s="253"/>
-      <c r="AC42" s="253"/>
-      <c r="AD42" s="253"/>
-      <c r="AE42" s="253"/>
-      <c r="AF42" s="253"/>
-      <c r="AG42" s="253"/>
-      <c r="AH42" s="253"/>
-      <c r="AI42" s="253"/>
-      <c r="AJ42" s="253"/>
-      <c r="AK42" s="253"/>
-      <c r="AL42" s="253"/>
-      <c r="AM42" s="253"/>
-      <c r="AN42" s="253"/>
-      <c r="AO42" s="253"/>
-      <c r="AP42" s="253"/>
-      <c r="AQ42" s="253"/>
-      <c r="AR42" s="253"/>
-      <c r="AS42" s="253"/>
-      <c r="AT42" s="253"/>
-      <c r="AU42" s="253"/>
-      <c r="AV42" s="253"/>
-      <c r="AW42" s="253"/>
-      <c r="AX42" s="253"/>
-      <c r="AY42" s="253"/>
-      <c r="AZ42" s="254"/>
+      <c r="E42" s="243"/>
+      <c r="F42" s="243"/>
+      <c r="G42" s="243"/>
+      <c r="H42" s="243"/>
+      <c r="I42" s="243"/>
+      <c r="J42" s="243"/>
+      <c r="K42" s="243"/>
+      <c r="L42" s="243"/>
+      <c r="M42" s="243"/>
+      <c r="N42" s="243"/>
+      <c r="O42" s="243"/>
+      <c r="P42" s="243"/>
+      <c r="Q42" s="243"/>
+      <c r="R42" s="243"/>
+      <c r="S42" s="243"/>
+      <c r="T42" s="243"/>
+      <c r="U42" s="243"/>
+      <c r="V42" s="243"/>
+      <c r="W42" s="243"/>
+      <c r="X42" s="243"/>
+      <c r="Y42" s="243"/>
+      <c r="Z42" s="243"/>
+      <c r="AA42" s="243"/>
+      <c r="AB42" s="243"/>
+      <c r="AC42" s="243"/>
+      <c r="AD42" s="243"/>
+      <c r="AE42" s="243"/>
+      <c r="AF42" s="243"/>
+      <c r="AG42" s="243"/>
+      <c r="AH42" s="243"/>
+      <c r="AI42" s="243"/>
+      <c r="AJ42" s="243"/>
+      <c r="AK42" s="243"/>
+      <c r="AL42" s="243"/>
+      <c r="AM42" s="243"/>
+      <c r="AN42" s="243"/>
+      <c r="AO42" s="243"/>
+      <c r="AP42" s="243"/>
+      <c r="AQ42" s="243"/>
+      <c r="AR42" s="243"/>
+      <c r="AS42" s="243"/>
+      <c r="AT42" s="243"/>
+      <c r="AU42" s="243"/>
+      <c r="AV42" s="243"/>
+      <c r="AW42" s="243"/>
+      <c r="AX42" s="243"/>
+      <c r="AY42" s="243"/>
+      <c r="AZ42" s="244"/>
     </row>
     <row r="43" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="62"/>
@@ -12208,203 +12160,204 @@
       <c r="AZ44"/>
     </row>
     <row r="45" spans="1:53" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="117"/>
-      <c r="B45" s="117"/>
-      <c r="C45" s="117"/>
-      <c r="D45" s="117"/>
-      <c r="E45" s="117"/>
-      <c r="F45" s="117"/>
-      <c r="G45" s="117"/>
-      <c r="H45" s="117"/>
-      <c r="I45" s="117"/>
-      <c r="J45" s="117"/>
-      <c r="K45" s="117"/>
-      <c r="L45" s="117"/>
-      <c r="M45" s="117"/>
-      <c r="N45" s="117"/>
-      <c r="O45" s="117"/>
-      <c r="P45" s="117"/>
+      <c r="A45" s="147"/>
+      <c r="B45" s="147"/>
+      <c r="C45" s="147"/>
+      <c r="D45" s="147"/>
+      <c r="E45" s="147"/>
+      <c r="F45" s="147"/>
+      <c r="G45" s="147"/>
+      <c r="H45" s="147"/>
+      <c r="I45" s="147"/>
+      <c r="J45" s="147"/>
+      <c r="K45" s="147"/>
+      <c r="L45" s="147"/>
+      <c r="M45" s="147"/>
+      <c r="N45" s="147"/>
+      <c r="O45" s="147"/>
+      <c r="P45" s="147"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
-      <c r="S45" s="117"/>
-      <c r="T45" s="117"/>
-      <c r="U45" s="117"/>
-      <c r="V45" s="117"/>
-      <c r="W45" s="117"/>
-      <c r="X45" s="117"/>
-      <c r="Y45" s="117"/>
-      <c r="Z45" s="117"/>
-      <c r="AA45" s="117"/>
-      <c r="AB45" s="117"/>
-      <c r="AC45" s="117"/>
-      <c r="AD45" s="117"/>
-      <c r="AE45" s="117"/>
-      <c r="AF45" s="117"/>
-      <c r="AG45" s="117"/>
-      <c r="AH45" s="117"/>
+      <c r="S45" s="147"/>
+      <c r="T45" s="147"/>
+      <c r="U45" s="147"/>
+      <c r="V45" s="147"/>
+      <c r="W45" s="147"/>
+      <c r="X45" s="147"/>
+      <c r="Y45" s="147"/>
+      <c r="Z45" s="147"/>
+      <c r="AA45" s="147"/>
+      <c r="AB45" s="147"/>
+      <c r="AC45" s="147"/>
+      <c r="AD45" s="147"/>
+      <c r="AE45" s="147"/>
+      <c r="AF45" s="147"/>
+      <c r="AG45" s="147"/>
+      <c r="AH45" s="147"/>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
-      <c r="AK45" s="117"/>
-      <c r="AL45" s="117"/>
-      <c r="AM45" s="117"/>
-      <c r="AN45" s="117"/>
-      <c r="AO45" s="117"/>
-      <c r="AP45" s="117"/>
-      <c r="AQ45" s="117"/>
-      <c r="AR45" s="117"/>
-      <c r="AS45" s="117"/>
-      <c r="AT45" s="117"/>
-      <c r="AU45" s="117"/>
-      <c r="AV45" s="117"/>
-      <c r="AW45" s="117"/>
-      <c r="AX45" s="117"/>
-      <c r="AY45" s="117"/>
-      <c r="AZ45" s="117"/>
+      <c r="AK45" s="147"/>
+      <c r="AL45" s="147"/>
+      <c r="AM45" s="147"/>
+      <c r="AN45" s="147"/>
+      <c r="AO45" s="147"/>
+      <c r="AP45" s="147"/>
+      <c r="AQ45" s="147"/>
+      <c r="AR45" s="147"/>
+      <c r="AS45" s="147"/>
+      <c r="AT45" s="147"/>
+      <c r="AU45" s="147"/>
+      <c r="AV45" s="147"/>
+      <c r="AW45" s="147"/>
+      <c r="AX45" s="147"/>
+      <c r="AY45" s="147"/>
+      <c r="AZ45" s="147"/>
     </row>
     <row r="46" spans="1:53" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="118" t="s">
+      <c r="A46" s="211" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="118"/>
-      <c r="C46" s="118"/>
-      <c r="D46" s="118"/>
-      <c r="E46" s="118"/>
-      <c r="F46" s="118"/>
-      <c r="G46" s="118"/>
-      <c r="H46" s="118"/>
-      <c r="I46" s="118"/>
-      <c r="J46" s="118"/>
-      <c r="K46" s="118"/>
-      <c r="L46" s="118"/>
-      <c r="M46" s="118"/>
-      <c r="N46" s="118"/>
-      <c r="O46" s="118"/>
-      <c r="P46" s="118"/>
+      <c r="B46" s="211"/>
+      <c r="C46" s="211"/>
+      <c r="D46" s="211"/>
+      <c r="E46" s="211"/>
+      <c r="F46" s="211"/>
+      <c r="G46" s="211"/>
+      <c r="H46" s="211"/>
+      <c r="I46" s="211"/>
+      <c r="J46" s="211"/>
+      <c r="K46" s="211"/>
+      <c r="L46" s="211"/>
+      <c r="M46" s="211"/>
+      <c r="N46" s="211"/>
+      <c r="O46" s="211"/>
+      <c r="P46" s="211"/>
       <c r="Q46" s="54"/>
       <c r="R46" s="54"/>
-      <c r="S46" s="195" t="s">
+      <c r="S46" s="122" t="s">
         <v>78</v>
       </c>
-      <c r="T46" s="195"/>
-      <c r="U46" s="195"/>
-      <c r="V46" s="195"/>
-      <c r="W46" s="195"/>
-      <c r="X46" s="195"/>
-      <c r="Y46" s="195"/>
-      <c r="Z46" s="195"/>
-      <c r="AA46" s="195"/>
-      <c r="AB46" s="195"/>
-      <c r="AC46" s="195"/>
-      <c r="AD46" s="195"/>
-      <c r="AE46" s="195"/>
-      <c r="AF46" s="195"/>
-      <c r="AG46" s="195"/>
-      <c r="AH46" s="195"/>
+      <c r="T46" s="122"/>
+      <c r="U46" s="122"/>
+      <c r="V46" s="122"/>
+      <c r="W46" s="122"/>
+      <c r="X46" s="122"/>
+      <c r="Y46" s="122"/>
+      <c r="Z46" s="122"/>
+      <c r="AA46" s="122"/>
+      <c r="AB46" s="122"/>
+      <c r="AC46" s="122"/>
+      <c r="AD46" s="122"/>
+      <c r="AE46" s="122"/>
+      <c r="AF46" s="122"/>
+      <c r="AG46" s="122"/>
+      <c r="AH46" s="122"/>
       <c r="AI46" s="54"/>
       <c r="AJ46" s="54"/>
-      <c r="AK46" s="118" t="s">
+      <c r="AK46" s="211" t="s">
         <v>79</v>
       </c>
-      <c r="AL46" s="118"/>
-      <c r="AM46" s="118"/>
-      <c r="AN46" s="118"/>
-      <c r="AO46" s="118"/>
-      <c r="AP46" s="118"/>
-      <c r="AQ46" s="118"/>
-      <c r="AR46" s="118"/>
-      <c r="AS46" s="118"/>
-      <c r="AT46" s="118"/>
-      <c r="AU46" s="118"/>
-      <c r="AV46" s="118"/>
-      <c r="AW46" s="118"/>
-      <c r="AX46" s="118"/>
-      <c r="AY46" s="118"/>
-      <c r="AZ46" s="118"/>
+      <c r="AL46" s="211"/>
+      <c r="AM46" s="211"/>
+      <c r="AN46" s="211"/>
+      <c r="AO46" s="211"/>
+      <c r="AP46" s="211"/>
+      <c r="AQ46" s="211"/>
+      <c r="AR46" s="211"/>
+      <c r="AS46" s="211"/>
+      <c r="AT46" s="211"/>
+      <c r="AU46" s="211"/>
+      <c r="AV46" s="211"/>
+      <c r="AW46" s="211"/>
+      <c r="AX46" s="211"/>
+      <c r="AY46" s="211"/>
+      <c r="AZ46" s="211"/>
     </row>
     <row r="47" spans="1:53" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="255"/>
-      <c r="B47" s="255"/>
-      <c r="C47" s="255"/>
-      <c r="D47" s="255"/>
-      <c r="E47" s="255"/>
-      <c r="F47" s="255"/>
-      <c r="G47" s="255"/>
-      <c r="H47" s="255"/>
-      <c r="I47" s="255"/>
-      <c r="J47" s="255"/>
-      <c r="K47" s="255"/>
-      <c r="L47" s="255"/>
-      <c r="M47" s="255"/>
-      <c r="N47" s="255"/>
-      <c r="O47" s="255"/>
-      <c r="P47" s="255"/>
-      <c r="S47" s="255"/>
-      <c r="T47" s="255"/>
-      <c r="U47" s="255"/>
-      <c r="V47" s="256"/>
-      <c r="W47" s="257"/>
-      <c r="X47" s="257"/>
-      <c r="Y47" s="257"/>
-      <c r="Z47" s="257"/>
-      <c r="AA47" s="257"/>
-      <c r="AB47" s="257"/>
-      <c r="AC47" s="257"/>
-      <c r="AD47" s="257"/>
-      <c r="AE47" s="257"/>
-      <c r="AF47" s="257"/>
-      <c r="AG47" s="257"/>
-      <c r="AH47" s="257"/>
-      <c r="AK47" s="119" t="s">
+      <c r="A47" s="245"/>
+      <c r="B47" s="245"/>
+      <c r="C47" s="245"/>
+      <c r="D47" s="245"/>
+      <c r="E47" s="245"/>
+      <c r="F47" s="245"/>
+      <c r="G47" s="245"/>
+      <c r="H47" s="245"/>
+      <c r="I47" s="245"/>
+      <c r="J47" s="245"/>
+      <c r="K47" s="245"/>
+      <c r="L47" s="245"/>
+      <c r="M47" s="245"/>
+      <c r="N47" s="245"/>
+      <c r="O47" s="245"/>
+      <c r="P47" s="245"/>
+      <c r="S47" s="245"/>
+      <c r="T47" s="245"/>
+      <c r="U47" s="245"/>
+      <c r="V47" s="246"/>
+      <c r="W47" s="247"/>
+      <c r="X47" s="247"/>
+      <c r="Y47" s="247"/>
+      <c r="Z47" s="247"/>
+      <c r="AA47" s="247"/>
+      <c r="AB47" s="247"/>
+      <c r="AC47" s="247"/>
+      <c r="AD47" s="247"/>
+      <c r="AE47" s="247"/>
+      <c r="AF47" s="247"/>
+      <c r="AG47" s="247"/>
+      <c r="AH47" s="247"/>
+      <c r="AK47" s="212" t="s">
         <v>792</v>
       </c>
-      <c r="AL47" s="119"/>
-      <c r="AM47" s="119"/>
-      <c r="AN47" s="119"/>
-      <c r="AO47" s="119"/>
-      <c r="AP47" s="119"/>
-      <c r="AQ47" s="119"/>
-      <c r="AR47" s="119"/>
-      <c r="AS47" s="119"/>
-      <c r="AT47" s="119"/>
-      <c r="AU47" s="119"/>
-      <c r="AV47" s="119"/>
-      <c r="AW47" s="119"/>
-      <c r="AX47" s="119"/>
-      <c r="AY47" s="119"/>
-      <c r="AZ47" s="119"/>
+      <c r="AL47" s="212"/>
+      <c r="AM47" s="212"/>
+      <c r="AN47" s="212"/>
+      <c r="AO47" s="212"/>
+      <c r="AP47" s="212"/>
+      <c r="AQ47" s="212"/>
+      <c r="AR47" s="212"/>
+      <c r="AS47" s="212"/>
+      <c r="AT47" s="212"/>
+      <c r="AU47" s="212"/>
+      <c r="AV47" s="212"/>
+      <c r="AW47" s="212"/>
+      <c r="AX47" s="212"/>
+      <c r="AY47" s="212"/>
+      <c r="AZ47" s="212"/>
     </row>
     <row r="48" spans="1:53" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="E30:AZ30"/>
-    <mergeCell ref="E31:AZ31"/>
-    <mergeCell ref="E32:AZ32"/>
-    <mergeCell ref="E26:AZ26"/>
-    <mergeCell ref="E27:AZ27"/>
-    <mergeCell ref="E28:AZ28"/>
-    <mergeCell ref="E29:AZ29"/>
-    <mergeCell ref="A46:P46"/>
-    <mergeCell ref="S46:AH46"/>
-    <mergeCell ref="AK46:AZ46"/>
-    <mergeCell ref="A47:P47"/>
-    <mergeCell ref="AK47:AZ47"/>
-    <mergeCell ref="S47:U47"/>
-    <mergeCell ref="V47:AH47"/>
-    <mergeCell ref="E42:AZ42"/>
-    <mergeCell ref="E39:AZ39"/>
-    <mergeCell ref="E40:AZ40"/>
-    <mergeCell ref="E41:AZ41"/>
-    <mergeCell ref="E38:AZ38"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A45:P45"/>
+    <mergeCell ref="S45:AH45"/>
+    <mergeCell ref="AK45:AZ45"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A4:AZ4"/>
+    <mergeCell ref="K2:AP2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="E6:AZ6"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="AS1:AZ3"/>
+    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="E9:AZ9"/>
     <mergeCell ref="A31:C31"/>
@@ -12421,34 +12374,33 @@
     <mergeCell ref="E37:AZ37"/>
     <mergeCell ref="E35:AZ35"/>
     <mergeCell ref="E36:AZ36"/>
-    <mergeCell ref="A4:AZ4"/>
-    <mergeCell ref="K2:AP2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="E6:AZ6"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="AS1:AZ3"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A45:P45"/>
-    <mergeCell ref="S45:AH45"/>
-    <mergeCell ref="AK45:AZ45"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="E42:AZ42"/>
+    <mergeCell ref="E39:AZ39"/>
+    <mergeCell ref="E40:AZ40"/>
+    <mergeCell ref="E41:AZ41"/>
+    <mergeCell ref="E38:AZ38"/>
+    <mergeCell ref="A46:P46"/>
+    <mergeCell ref="S46:AH46"/>
+    <mergeCell ref="AK46:AZ46"/>
+    <mergeCell ref="A47:P47"/>
+    <mergeCell ref="AK47:AZ47"/>
+    <mergeCell ref="S47:U47"/>
+    <mergeCell ref="V47:AH47"/>
+    <mergeCell ref="E30:AZ30"/>
+    <mergeCell ref="E31:AZ31"/>
+    <mergeCell ref="E32:AZ32"/>
+    <mergeCell ref="E26:AZ26"/>
+    <mergeCell ref="E27:AZ27"/>
+    <mergeCell ref="E28:AZ28"/>
+    <mergeCell ref="E29:AZ29"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -12482,126 +12434,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="14" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="263" t="e" vm="1">
+      <c r="A1" s="264" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="264"/>
-      <c r="C1" s="264"/>
-      <c r="D1" s="264"/>
-      <c r="E1" s="264"/>
-      <c r="F1" s="264"/>
-      <c r="G1" s="264"/>
-      <c r="H1" s="264"/>
-      <c r="I1" s="264"/>
-      <c r="J1" s="264"/>
-      <c r="K1" s="264"/>
-      <c r="L1" s="264"/>
-      <c r="M1" s="264"/>
-      <c r="N1" s="264"/>
-      <c r="O1" s="265"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
+      <c r="N1" s="265"/>
+      <c r="O1" s="266"/>
     </row>
     <row r="2" spans="1:15" s="14" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="266"/>
-      <c r="B2" s="267"/>
-      <c r="C2" s="267"/>
-      <c r="D2" s="267"/>
-      <c r="E2" s="267"/>
-      <c r="F2" s="267"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="267"/>
-      <c r="I2" s="267"/>
-      <c r="J2" s="267"/>
-      <c r="K2" s="267"/>
-      <c r="L2" s="267"/>
-      <c r="M2" s="267"/>
-      <c r="N2" s="267"/>
-      <c r="O2" s="268"/>
+      <c r="A2" s="267"/>
+      <c r="B2" s="268"/>
+      <c r="C2" s="268"/>
+      <c r="D2" s="268"/>
+      <c r="E2" s="268"/>
+      <c r="F2" s="268"/>
+      <c r="G2" s="268"/>
+      <c r="H2" s="268"/>
+      <c r="I2" s="268"/>
+      <c r="J2" s="268"/>
+      <c r="K2" s="268"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="268"/>
+      <c r="N2" s="268"/>
+      <c r="O2" s="269"/>
     </row>
     <row r="3" spans="1:15" s="14" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="269"/>
-      <c r="B3" s="270"/>
-      <c r="C3" s="270"/>
-      <c r="D3" s="270"/>
-      <c r="E3" s="270"/>
-      <c r="F3" s="270"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="270"/>
-      <c r="I3" s="270"/>
-      <c r="J3" s="270"/>
-      <c r="K3" s="270"/>
-      <c r="L3" s="270"/>
-      <c r="M3" s="270"/>
-      <c r="N3" s="270"/>
-      <c r="O3" s="271"/>
+      <c r="A3" s="270"/>
+      <c r="B3" s="271"/>
+      <c r="C3" s="271"/>
+      <c r="D3" s="271"/>
+      <c r="E3" s="271"/>
+      <c r="F3" s="271"/>
+      <c r="G3" s="271"/>
+      <c r="H3" s="271"/>
+      <c r="I3" s="271"/>
+      <c r="J3" s="271"/>
+      <c r="K3" s="271"/>
+      <c r="L3" s="271"/>
+      <c r="M3" s="271"/>
+      <c r="N3" s="271"/>
+      <c r="O3" s="272"/>
     </row>
     <row r="4" spans="1:15" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="260" t="s">
+      <c r="A4" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="261"/>
-      <c r="C4" s="261"/>
-      <c r="D4" s="261"/>
-      <c r="E4" s="261"/>
-      <c r="F4" s="261"/>
-      <c r="G4" s="261"/>
-      <c r="H4" s="261"/>
-      <c r="I4" s="261"/>
-      <c r="J4" s="261"/>
-      <c r="K4" s="261"/>
-      <c r="L4" s="261"/>
-      <c r="M4" s="261"/>
-      <c r="N4" s="261"/>
-      <c r="O4" s="262"/>
+      <c r="B4" s="262"/>
+      <c r="C4" s="262"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
+      <c r="M4" s="262"/>
+      <c r="N4" s="262"/>
+      <c r="O4" s="263"/>
     </row>
     <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="272" t="s">
+      <c r="A5" s="273" t="s">
         <v>106</v>
       </c>
-      <c r="B5" s="258" t="s">
+      <c r="B5" s="259" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="259" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="258" t="s">
+      <c r="D5" s="259" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="258" t="s">
+      <c r="E5" s="259" t="s">
         <v>110</v>
       </c>
-      <c r="F5" s="258" t="s">
+      <c r="F5" s="259" t="s">
         <v>111</v>
       </c>
-      <c r="G5" s="258" t="s">
+      <c r="G5" s="259" t="s">
         <v>112</v>
       </c>
-      <c r="H5" s="258" t="s">
+      <c r="H5" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="I5" s="258" t="s">
+      <c r="I5" s="259" t="s">
         <v>114</v>
       </c>
-      <c r="J5" s="274" t="s">
+      <c r="J5" s="275" t="s">
         <v>115</v>
       </c>
-      <c r="K5" s="275"/>
-      <c r="L5" s="276"/>
-      <c r="M5" s="274" t="s">
+      <c r="K5" s="276"/>
+      <c r="L5" s="277"/>
+      <c r="M5" s="275" t="s">
         <v>116</v>
       </c>
-      <c r="N5" s="275"/>
-      <c r="O5" s="277"/>
+      <c r="N5" s="276"/>
+      <c r="O5" s="278"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="273"/>
-      <c r="B6" s="259"/>
-      <c r="C6" s="259"/>
-      <c r="D6" s="259"/>
-      <c r="E6" s="259"/>
-      <c r="F6" s="259"/>
-      <c r="G6" s="259"/>
-      <c r="H6" s="259"/>
-      <c r="I6" s="259"/>
+      <c r="A6" s="274"/>
+      <c r="B6" s="260"/>
+      <c r="C6" s="260"/>
+      <c r="D6" s="260"/>
+      <c r="E6" s="260"/>
+      <c r="F6" s="260"/>
+      <c r="G6" s="260"/>
+      <c r="H6" s="260"/>
+      <c r="I6" s="260"/>
       <c r="J6" s="84" t="s">
         <v>117</v>
       </c>
@@ -18309,110 +18261,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="14" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="263" t="e" vm="1">
+      <c r="A1" s="264" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="264"/>
-      <c r="C1" s="264"/>
-      <c r="D1" s="264"/>
-      <c r="E1" s="264"/>
-      <c r="F1" s="264"/>
-      <c r="G1" s="264"/>
-      <c r="H1" s="264"/>
-      <c r="I1" s="264"/>
-      <c r="J1" s="264"/>
-      <c r="K1" s="264"/>
-      <c r="L1" s="264"/>
-      <c r="M1" s="265"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="266"/>
     </row>
     <row r="2" spans="1:13" s="14" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="266"/>
-      <c r="B2" s="267"/>
-      <c r="C2" s="267"/>
-      <c r="D2" s="267"/>
-      <c r="E2" s="267"/>
-      <c r="F2" s="267"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="267"/>
-      <c r="I2" s="267"/>
-      <c r="J2" s="267"/>
-      <c r="K2" s="267"/>
-      <c r="L2" s="267"/>
-      <c r="M2" s="268"/>
+      <c r="A2" s="267"/>
+      <c r="B2" s="268"/>
+      <c r="C2" s="268"/>
+      <c r="D2" s="268"/>
+      <c r="E2" s="268"/>
+      <c r="F2" s="268"/>
+      <c r="G2" s="268"/>
+      <c r="H2" s="268"/>
+      <c r="I2" s="268"/>
+      <c r="J2" s="268"/>
+      <c r="K2" s="268"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="269"/>
     </row>
     <row r="3" spans="1:13" s="14" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="269"/>
-      <c r="B3" s="270"/>
-      <c r="C3" s="270"/>
-      <c r="D3" s="270"/>
-      <c r="E3" s="270"/>
-      <c r="F3" s="270"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="270"/>
-      <c r="I3" s="270"/>
-      <c r="J3" s="270"/>
-      <c r="K3" s="270"/>
-      <c r="L3" s="270"/>
-      <c r="M3" s="271"/>
+      <c r="A3" s="270"/>
+      <c r="B3" s="271"/>
+      <c r="C3" s="271"/>
+      <c r="D3" s="271"/>
+      <c r="E3" s="271"/>
+      <c r="F3" s="271"/>
+      <c r="G3" s="271"/>
+      <c r="H3" s="271"/>
+      <c r="I3" s="271"/>
+      <c r="J3" s="271"/>
+      <c r="K3" s="271"/>
+      <c r="L3" s="271"/>
+      <c r="M3" s="272"/>
     </row>
     <row r="4" spans="1:13" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="260" t="s">
+      <c r="A4" s="261" t="s">
         <v>660</v>
       </c>
-      <c r="B4" s="261"/>
-      <c r="C4" s="261"/>
-      <c r="D4" s="261"/>
-      <c r="E4" s="261"/>
-      <c r="F4" s="261"/>
-      <c r="G4" s="261"/>
-      <c r="H4" s="261"/>
-      <c r="I4" s="261"/>
-      <c r="J4" s="261"/>
-      <c r="K4" s="261"/>
-      <c r="L4" s="261"/>
-      <c r="M4" s="262"/>
+      <c r="B4" s="262"/>
+      <c r="C4" s="262"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
+      <c r="M4" s="263"/>
     </row>
     <row r="5" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="284" t="s">
+      <c r="A5" s="285" t="s">
         <v>661</v>
       </c>
-      <c r="B5" s="278" t="s">
+      <c r="B5" s="279" t="s">
         <v>662</v>
       </c>
-      <c r="C5" s="278" t="s">
+      <c r="C5" s="279" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="278" t="s">
+      <c r="D5" s="279" t="s">
         <v>108</v>
       </c>
-      <c r="E5" s="278" t="s">
+      <c r="E5" s="279" t="s">
         <v>109</v>
       </c>
-      <c r="F5" s="278" t="s">
+      <c r="F5" s="279" t="s">
         <v>110</v>
       </c>
-      <c r="G5" s="278" t="s">
+      <c r="G5" s="279" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="280" t="s">
+      <c r="H5" s="281" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="281"/>
-      <c r="J5" s="282"/>
-      <c r="K5" s="280" t="s">
+      <c r="I5" s="282"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="281" t="s">
         <v>116</v>
       </c>
-      <c r="L5" s="281"/>
-      <c r="M5" s="283"/>
+      <c r="L5" s="282"/>
+      <c r="M5" s="284"/>
     </row>
     <row r="6" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="285"/>
-      <c r="B6" s="279"/>
-      <c r="C6" s="279"/>
-      <c r="D6" s="279"/>
-      <c r="E6" s="279"/>
-      <c r="F6" s="279"/>
-      <c r="G6" s="279"/>
+      <c r="A6" s="286"/>
+      <c r="B6" s="280"/>
+      <c r="C6" s="280"/>
+      <c r="D6" s="280"/>
+      <c r="E6" s="280"/>
+      <c r="F6" s="280"/>
+      <c r="G6" s="280"/>
       <c r="H6" s="50" t="s">
         <v>117</v>
       </c>
@@ -19499,26 +19451,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c24bca33-91ee-4c94-9d6c-305b441d02fd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e46781df-dd49-4a0f-be02-040bfbf345c5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2EBC4C97F3EED4F8F99B50CD61D9AF7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0ffa3ef56536b291ffb1e746207cdfaf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e46781df-dd49-4a0f-be02-040bfbf345c5" xmlns:ns3="c24bca33-91ee-4c94-9d6c-305b441d02fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="82d71f54c8a292e50b13588301f7fd2c" ns2:_="" ns3:_="">
     <xsd:import namespace="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
@@ -19747,10 +19679,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c24bca33-91ee-4c94-9d6c-305b441d02fd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e46781df-dd49-4a0f-be02-040bfbf345c5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA908177-54FE-4386-8E64-F855D4FAA630}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDAB891A-AABF-4B04-8872-1A9CED3578DB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
+    <ds:schemaRef ds:uri="c24bca33-91ee-4c94-9d6c-305b441d02fd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19767,20 +19730,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDAB891A-AABF-4B04-8872-1A9CED3578DB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA908177-54FE-4386-8E64-F855D4FAA630}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
-    <ds:schemaRef ds:uri="c24bca33-91ee-4c94-9d6c-305b441d02fd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/RSC 08.0000.25 - Relatório de Serviço de Campo - Padrão - Rev.38.xlsx
+++ b/RSC 08.0000.25 - Relatório de Serviço de Campo - Padrão - Rev.38.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ktsabr-my.sharepoint.com/personal/gustavo_arruda_ktsa_com_br/Documents/PROJETOS/Engenharia/RSC - Relatório de Serviço de Campo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{F948FEA9-3545-4234-B576-12B0A63E47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25BA8208-61D9-401D-84D6-D1DD524DA5D2}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{F948FEA9-3545-4234-B576-12B0A63E47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63DB7B7C-6AA0-4CC0-89C3-D60F6F85F75F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3498,67 +3498,468 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3586,409 +3987,47 @@
     <xf numFmtId="164" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4004,39 +4043,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4103,12 +4109,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4743,6 +4743,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -5169,14 +5173,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="168"/>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="170"/>
+      <c r="A1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="139"/>
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
       <c r="K1" s="21"/>
@@ -5213,87 +5217,87 @@
       <c r="AP1" s="22"/>
       <c r="AQ1" s="22"/>
       <c r="AR1" s="22"/>
-      <c r="AS1" s="177" t="s">
+      <c r="AS1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="AT1" s="178"/>
-      <c r="AU1" s="178"/>
-      <c r="AV1" s="178"/>
-      <c r="AW1" s="178"/>
-      <c r="AX1" s="178"/>
-      <c r="AY1" s="178"/>
-      <c r="AZ1" s="179"/>
+      <c r="AT1" s="147"/>
+      <c r="AU1" s="147"/>
+      <c r="AV1" s="147"/>
+      <c r="AW1" s="147"/>
+      <c r="AX1" s="147"/>
+      <c r="AY1" s="147"/>
+      <c r="AZ1" s="148"/>
       <c r="BD1" s="23"/>
       <c r="BF1" s="27"/>
       <c r="BG1" s="27"/>
     </row>
     <row r="2" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="171"/>
-      <c r="B2" s="172"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="173"/>
-      <c r="K2" s="187" t="s">
+      <c r="A2" s="140"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="142"/>
+      <c r="K2" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="188"/>
-      <c r="M2" s="188"/>
-      <c r="N2" s="188"/>
-      <c r="O2" s="188"/>
-      <c r="P2" s="188"/>
-      <c r="Q2" s="188"/>
-      <c r="R2" s="188"/>
-      <c r="S2" s="188"/>
-      <c r="T2" s="188"/>
-      <c r="U2" s="188"/>
-      <c r="V2" s="188"/>
-      <c r="W2" s="188"/>
-      <c r="X2" s="188"/>
-      <c r="Y2" s="188"/>
-      <c r="Z2" s="188"/>
-      <c r="AA2" s="188"/>
-      <c r="AB2" s="188"/>
-      <c r="AC2" s="188"/>
-      <c r="AD2" s="188"/>
-      <c r="AE2" s="188"/>
-      <c r="AF2" s="188"/>
-      <c r="AG2" s="188"/>
-      <c r="AH2" s="188"/>
-      <c r="AI2" s="188"/>
-      <c r="AJ2" s="188"/>
-      <c r="AK2" s="188"/>
-      <c r="AL2" s="188"/>
-      <c r="AM2" s="188"/>
-      <c r="AN2" s="188"/>
-      <c r="AO2" s="188"/>
-      <c r="AP2" s="188"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="157"/>
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="157"/>
+      <c r="U2" s="157"/>
+      <c r="V2" s="157"/>
+      <c r="W2" s="157"/>
+      <c r="X2" s="157"/>
+      <c r="Y2" s="157"/>
+      <c r="Z2" s="157"/>
+      <c r="AA2" s="157"/>
+      <c r="AB2" s="157"/>
+      <c r="AC2" s="157"/>
+      <c r="AD2" s="157"/>
+      <c r="AE2" s="157"/>
+      <c r="AF2" s="157"/>
+      <c r="AG2" s="157"/>
+      <c r="AH2" s="157"/>
+      <c r="AI2" s="157"/>
+      <c r="AJ2" s="157"/>
+      <c r="AK2" s="157"/>
+      <c r="AL2" s="157"/>
+      <c r="AM2" s="157"/>
+      <c r="AN2" s="157"/>
+      <c r="AO2" s="157"/>
+      <c r="AP2" s="157"/>
       <c r="AQ2" s="17"/>
       <c r="AR2" s="17"/>
-      <c r="AS2" s="180"/>
-      <c r="AT2" s="181"/>
-      <c r="AU2" s="181"/>
-      <c r="AV2" s="181"/>
-      <c r="AW2" s="181"/>
-      <c r="AX2" s="181"/>
-      <c r="AY2" s="181"/>
-      <c r="AZ2" s="182"/>
+      <c r="AS2" s="149"/>
+      <c r="AT2" s="150"/>
+      <c r="AU2" s="150"/>
+      <c r="AV2" s="150"/>
+      <c r="AW2" s="150"/>
+      <c r="AX2" s="150"/>
+      <c r="AY2" s="150"/>
+      <c r="AZ2" s="151"/>
       <c r="BA2" s="7"/>
       <c r="BF2" s="25"/>
       <c r="BG2" s="25"/>
       <c r="BH2" s="25"/>
     </row>
     <row r="3" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="174"/>
-      <c r="B3" s="175"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="176"/>
+      <c r="A3" s="143"/>
+      <c r="B3" s="144"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="145"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -5330,392 +5334,392 @@
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
       <c r="AR3" s="4"/>
-      <c r="AS3" s="183"/>
-      <c r="AT3" s="184"/>
-      <c r="AU3" s="184"/>
-      <c r="AV3" s="184"/>
-      <c r="AW3" s="184"/>
-      <c r="AX3" s="184"/>
-      <c r="AY3" s="184"/>
-      <c r="AZ3" s="185"/>
+      <c r="AS3" s="152"/>
+      <c r="AT3" s="153"/>
+      <c r="AU3" s="153"/>
+      <c r="AV3" s="153"/>
+      <c r="AW3" s="153"/>
+      <c r="AX3" s="153"/>
+      <c r="AY3" s="153"/>
+      <c r="AZ3" s="154"/>
     </row>
     <row r="4" spans="1:60" s="3" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="189" t="s">
+      <c r="A4" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="190"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="190"/>
-      <c r="K4" s="190"/>
-      <c r="L4" s="190"/>
-      <c r="M4" s="190"/>
-      <c r="N4" s="190"/>
-      <c r="O4" s="190"/>
-      <c r="P4" s="190"/>
-      <c r="Q4" s="190"/>
-      <c r="R4" s="190"/>
-      <c r="S4" s="190"/>
-      <c r="T4" s="190"/>
-      <c r="U4" s="190"/>
-      <c r="V4" s="190"/>
-      <c r="W4" s="190"/>
-      <c r="X4" s="190"/>
-      <c r="Y4" s="190"/>
-      <c r="Z4" s="190"/>
-      <c r="AA4" s="190"/>
-      <c r="AB4" s="190"/>
-      <c r="AC4" s="190"/>
-      <c r="AD4" s="190"/>
-      <c r="AE4" s="190"/>
-      <c r="AF4" s="190"/>
-      <c r="AG4" s="190"/>
-      <c r="AH4" s="190"/>
-      <c r="AI4" s="190"/>
-      <c r="AJ4" s="190"/>
-      <c r="AK4" s="190"/>
-      <c r="AL4" s="190"/>
-      <c r="AM4" s="190"/>
-      <c r="AN4" s="190"/>
-      <c r="AO4" s="190"/>
-      <c r="AP4" s="190"/>
-      <c r="AQ4" s="190"/>
-      <c r="AR4" s="190"/>
-      <c r="AS4" s="190"/>
-      <c r="AT4" s="190"/>
-      <c r="AU4" s="190"/>
-      <c r="AV4" s="190"/>
-      <c r="AW4" s="190"/>
-      <c r="AX4" s="190"/>
-      <c r="AY4" s="190"/>
-      <c r="AZ4" s="191"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="101"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="101"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="101"/>
+      <c r="S4" s="101"/>
+      <c r="T4" s="101"/>
+      <c r="U4" s="101"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="101"/>
+      <c r="X4" s="101"/>
+      <c r="Y4" s="101"/>
+      <c r="Z4" s="101"/>
+      <c r="AA4" s="101"/>
+      <c r="AB4" s="101"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="101"/>
+      <c r="AE4" s="101"/>
+      <c r="AF4" s="101"/>
+      <c r="AG4" s="101"/>
+      <c r="AH4" s="101"/>
+      <c r="AI4" s="101"/>
+      <c r="AJ4" s="101"/>
+      <c r="AK4" s="101"/>
+      <c r="AL4" s="101"/>
+      <c r="AM4" s="101"/>
+      <c r="AN4" s="101"/>
+      <c r="AO4" s="101"/>
+      <c r="AP4" s="101"/>
+      <c r="AQ4" s="101"/>
+      <c r="AR4" s="101"/>
+      <c r="AS4" s="101"/>
+      <c r="AT4" s="101"/>
+      <c r="AU4" s="101"/>
+      <c r="AV4" s="101"/>
+      <c r="AW4" s="101"/>
+      <c r="AX4" s="101"/>
+      <c r="AY4" s="101"/>
+      <c r="AZ4" s="102"/>
       <c r="BA4" s="9"/>
       <c r="BB4" s="9"/>
       <c r="BC4" s="9"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="195" t="s">
+      <c r="A5" s="161" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="196"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="196"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="201"/>
-      <c r="H5" s="201"/>
-      <c r="I5" s="201"/>
-      <c r="J5" s="201"/>
-      <c r="K5" s="201"/>
-      <c r="L5" s="201"/>
-      <c r="M5" s="201"/>
-      <c r="N5" s="201"/>
-      <c r="O5" s="201"/>
-      <c r="P5" s="201"/>
-      <c r="Q5" s="201"/>
-      <c r="R5" s="201"/>
-      <c r="S5" s="201"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="201"/>
-      <c r="V5" s="201"/>
-      <c r="W5" s="201"/>
-      <c r="X5" s="201"/>
-      <c r="Y5" s="201"/>
-      <c r="Z5" s="201"/>
-      <c r="AA5" s="201"/>
-      <c r="AB5" s="201"/>
+      <c r="B5" s="162"/>
+      <c r="C5" s="162"/>
+      <c r="D5" s="162"/>
+      <c r="E5" s="162"/>
+      <c r="F5" s="162"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="171"/>
+      <c r="J5" s="171"/>
+      <c r="K5" s="171"/>
+      <c r="L5" s="171"/>
+      <c r="M5" s="171"/>
+      <c r="N5" s="171"/>
+      <c r="O5" s="171"/>
+      <c r="P5" s="171"/>
+      <c r="Q5" s="171"/>
+      <c r="R5" s="171"/>
+      <c r="S5" s="171"/>
+      <c r="T5" s="171"/>
+      <c r="U5" s="171"/>
+      <c r="V5" s="171"/>
+      <c r="W5" s="171"/>
+      <c r="X5" s="171"/>
+      <c r="Y5" s="171"/>
+      <c r="Z5" s="171"/>
+      <c r="AA5" s="171"/>
+      <c r="AB5" s="171"/>
       <c r="AC5" s="55"/>
       <c r="AD5" s="58"/>
-      <c r="AE5" s="106" t="s">
+      <c r="AE5" s="170" t="s">
         <v>5</v>
       </c>
-      <c r="AF5" s="106"/>
-      <c r="AG5" s="106"/>
-      <c r="AH5" s="106"/>
-      <c r="AI5" s="106"/>
-      <c r="AJ5" s="106"/>
-      <c r="AK5" s="106"/>
-      <c r="AL5" s="208"/>
-      <c r="AM5" s="208"/>
-      <c r="AN5" s="208"/>
-      <c r="AO5" s="208"/>
-      <c r="AP5" s="208"/>
-      <c r="AQ5" s="208"/>
-      <c r="AR5" s="208"/>
-      <c r="AS5" s="208"/>
-      <c r="AT5" s="208"/>
-      <c r="AU5" s="208"/>
-      <c r="AV5" s="208"/>
-      <c r="AW5" s="208"/>
-      <c r="AX5" s="208"/>
-      <c r="AY5" s="208"/>
-      <c r="AZ5" s="209"/>
+      <c r="AF5" s="170"/>
+      <c r="AG5" s="170"/>
+      <c r="AH5" s="170"/>
+      <c r="AI5" s="170"/>
+      <c r="AJ5" s="170"/>
+      <c r="AK5" s="170"/>
+      <c r="AL5" s="181"/>
+      <c r="AM5" s="181"/>
+      <c r="AN5" s="181"/>
+      <c r="AO5" s="181"/>
+      <c r="AP5" s="181"/>
+      <c r="AQ5" s="181"/>
+      <c r="AR5" s="181"/>
+      <c r="AS5" s="181"/>
+      <c r="AT5" s="181"/>
+      <c r="AU5" s="181"/>
+      <c r="AV5" s="181"/>
+      <c r="AW5" s="181"/>
+      <c r="AX5" s="181"/>
+      <c r="AY5" s="181"/>
+      <c r="AZ5" s="182"/>
       <c r="BA5"/>
       <c r="BB5" s="9"/>
       <c r="BC5" s="9"/>
       <c r="BD5" s="9"/>
     </row>
     <row r="6" spans="1:60" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="195" t="s">
+      <c r="A6" s="161" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="196"/>
-      <c r="C6" s="196"/>
-      <c r="D6" s="196"/>
-      <c r="E6" s="196"/>
-      <c r="F6" s="196"/>
-      <c r="G6" s="91" t="str">
+      <c r="B6" s="162"/>
+      <c r="C6" s="162"/>
+      <c r="D6" s="162"/>
+      <c r="E6" s="162"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="136" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,4,0))</f>
         <v/>
       </c>
-      <c r="H6" s="91"/>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
-      <c r="K6" s="91"/>
-      <c r="L6" s="91"/>
-      <c r="M6" s="91"/>
-      <c r="N6" s="91"/>
-      <c r="O6" s="91"/>
-      <c r="P6" s="91"/>
-      <c r="Q6" s="91"/>
-      <c r="R6" s="91"/>
-      <c r="S6" s="91"/>
-      <c r="T6" s="91"/>
-      <c r="U6" s="91"/>
-      <c r="V6" s="91"/>
-      <c r="W6" s="91"/>
-      <c r="X6" s="91"/>
-      <c r="Y6" s="91"/>
-      <c r="Z6" s="91"/>
-      <c r="AA6" s="91"/>
-      <c r="AB6" s="91"/>
-      <c r="AC6" s="91"/>
-      <c r="AD6" s="91"/>
-      <c r="AE6" s="91"/>
-      <c r="AF6" s="91"/>
-      <c r="AG6" s="91"/>
-      <c r="AH6" s="91"/>
-      <c r="AI6" s="91"/>
-      <c r="AJ6" s="91"/>
-      <c r="AK6" s="91"/>
-      <c r="AL6" s="91"/>
-      <c r="AM6" s="91"/>
-      <c r="AN6" s="91"/>
-      <c r="AO6" s="91"/>
-      <c r="AP6" s="91"/>
-      <c r="AQ6" s="91"/>
-      <c r="AR6" s="91"/>
-      <c r="AS6" s="91"/>
-      <c r="AT6" s="91"/>
-      <c r="AU6" s="91"/>
-      <c r="AV6" s="91"/>
-      <c r="AW6" s="91"/>
-      <c r="AX6" s="91"/>
-      <c r="AY6" s="91"/>
-      <c r="AZ6" s="186"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
+      <c r="N6" s="136"/>
+      <c r="O6" s="136"/>
+      <c r="P6" s="136"/>
+      <c r="Q6" s="136"/>
+      <c r="R6" s="136"/>
+      <c r="S6" s="136"/>
+      <c r="T6" s="136"/>
+      <c r="U6" s="136"/>
+      <c r="V6" s="136"/>
+      <c r="W6" s="136"/>
+      <c r="X6" s="136"/>
+      <c r="Y6" s="136"/>
+      <c r="Z6" s="136"/>
+      <c r="AA6" s="136"/>
+      <c r="AB6" s="136"/>
+      <c r="AC6" s="136"/>
+      <c r="AD6" s="136"/>
+      <c r="AE6" s="136"/>
+      <c r="AF6" s="136"/>
+      <c r="AG6" s="136"/>
+      <c r="AH6" s="136"/>
+      <c r="AI6" s="136"/>
+      <c r="AJ6" s="136"/>
+      <c r="AK6" s="136"/>
+      <c r="AL6" s="136"/>
+      <c r="AM6" s="136"/>
+      <c r="AN6" s="136"/>
+      <c r="AO6" s="136"/>
+      <c r="AP6" s="136"/>
+      <c r="AQ6" s="136"/>
+      <c r="AR6" s="136"/>
+      <c r="AS6" s="136"/>
+      <c r="AT6" s="136"/>
+      <c r="AU6" s="136"/>
+      <c r="AV6" s="136"/>
+      <c r="AW6" s="136"/>
+      <c r="AX6" s="136"/>
+      <c r="AY6" s="136"/>
+      <c r="AZ6" s="155"/>
     </row>
     <row r="7" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="195" t="s">
+      <c r="A7" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="196"/>
-      <c r="C7" s="196"/>
-      <c r="D7" s="196"/>
-      <c r="E7" s="196"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="91" t="str">
+      <c r="B7" s="162"/>
+      <c r="C7" s="162"/>
+      <c r="D7" s="162"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="136" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,5,0))</f>
         <v/>
       </c>
-      <c r="H7" s="91"/>
-      <c r="I7" s="91"/>
-      <c r="J7" s="91"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="91"/>
-      <c r="N7" s="91"/>
-      <c r="O7" s="91"/>
-      <c r="P7" s="91"/>
-      <c r="Q7" s="91"/>
-      <c r="R7" s="91"/>
-      <c r="S7" s="91"/>
-      <c r="T7" s="91"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="136"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="136"/>
+      <c r="P7" s="136"/>
+      <c r="Q7" s="136"/>
+      <c r="R7" s="136"/>
+      <c r="S7" s="136"/>
+      <c r="T7" s="136"/>
       <c r="U7" s="57"/>
-      <c r="V7" s="161" t="s">
+      <c r="V7" s="176" t="s">
         <v>8</v>
       </c>
-      <c r="W7" s="161"/>
-      <c r="X7" s="161"/>
-      <c r="Y7" s="161"/>
-      <c r="Z7" s="91" t="str">
+      <c r="W7" s="176"/>
+      <c r="X7" s="176"/>
+      <c r="Y7" s="176"/>
+      <c r="Z7" s="136" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,2,0))</f>
         <v/>
       </c>
-      <c r="AA7" s="91"/>
-      <c r="AB7" s="91"/>
-      <c r="AC7" s="91"/>
-      <c r="AD7" s="91"/>
-      <c r="AE7" s="91"/>
-      <c r="AF7" s="91"/>
-      <c r="AG7" s="91"/>
-      <c r="AH7" s="91"/>
-      <c r="AI7" s="91"/>
-      <c r="AJ7" s="91"/>
-      <c r="AK7" s="91"/>
-      <c r="AL7" s="91"/>
-      <c r="AM7" s="91"/>
-      <c r="AN7" s="91"/>
-      <c r="AO7" s="91"/>
-      <c r="AP7" s="91"/>
+      <c r="AA7" s="136"/>
+      <c r="AB7" s="136"/>
+      <c r="AC7" s="136"/>
+      <c r="AD7" s="136"/>
+      <c r="AE7" s="136"/>
+      <c r="AF7" s="136"/>
+      <c r="AG7" s="136"/>
+      <c r="AH7" s="136"/>
+      <c r="AI7" s="136"/>
+      <c r="AJ7" s="136"/>
+      <c r="AK7" s="136"/>
+      <c r="AL7" s="136"/>
+      <c r="AM7" s="136"/>
+      <c r="AN7" s="136"/>
+      <c r="AO7" s="136"/>
+      <c r="AP7" s="136"/>
       <c r="AQ7" s="57"/>
-      <c r="AR7" s="161" t="s">
+      <c r="AR7" s="176" t="s">
         <v>9</v>
       </c>
-      <c r="AS7" s="161"/>
-      <c r="AT7" s="161"/>
-      <c r="AU7" s="161"/>
-      <c r="AV7" s="104" t="str">
+      <c r="AS7" s="176"/>
+      <c r="AT7" s="176"/>
+      <c r="AU7" s="176"/>
+      <c r="AV7" s="187" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,3,0))</f>
         <v/>
       </c>
-      <c r="AW7" s="104"/>
-      <c r="AX7" s="104"/>
-      <c r="AY7" s="104"/>
-      <c r="AZ7" s="105"/>
+      <c r="AW7" s="187"/>
+      <c r="AX7" s="187"/>
+      <c r="AY7" s="187"/>
+      <c r="AZ7" s="188"/>
       <c r="BA7"/>
     </row>
     <row r="8" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="202" t="s">
+      <c r="A8" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="203"/>
-      <c r="C8" s="203"/>
-      <c r="D8" s="203"/>
-      <c r="E8" s="203"/>
-      <c r="F8" s="203"/>
-      <c r="G8" s="204" t="str">
+      <c r="B8" s="173"/>
+      <c r="C8" s="173"/>
+      <c r="D8" s="173"/>
+      <c r="E8" s="173"/>
+      <c r="F8" s="173"/>
+      <c r="G8" s="174" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,6,0))</f>
         <v/>
       </c>
-      <c r="H8" s="205"/>
-      <c r="I8" s="205"/>
-      <c r="J8" s="205"/>
-      <c r="K8" s="205"/>
-      <c r="L8" s="205"/>
-      <c r="M8" s="205"/>
-      <c r="N8" s="205"/>
-      <c r="O8" s="205"/>
-      <c r="P8" s="205"/>
-      <c r="Q8" s="205"/>
-      <c r="R8" s="205"/>
-      <c r="S8" s="205"/>
-      <c r="T8" s="205"/>
-      <c r="U8" s="205"/>
-      <c r="V8" s="205"/>
-      <c r="W8" s="205"/>
-      <c r="X8" s="205"/>
-      <c r="Y8" s="205"/>
-      <c r="Z8" s="205"/>
-      <c r="AA8" s="205"/>
-      <c r="AB8" s="205"/>
-      <c r="AC8" s="205"/>
+      <c r="H8" s="175"/>
+      <c r="I8" s="175"/>
+      <c r="J8" s="175"/>
+      <c r="K8" s="175"/>
+      <c r="L8" s="175"/>
+      <c r="M8" s="175"/>
+      <c r="N8" s="175"/>
+      <c r="O8" s="175"/>
+      <c r="P8" s="175"/>
+      <c r="Q8" s="175"/>
+      <c r="R8" s="175"/>
+      <c r="S8" s="175"/>
+      <c r="T8" s="175"/>
+      <c r="U8" s="175"/>
+      <c r="V8" s="175"/>
+      <c r="W8" s="175"/>
+      <c r="X8" s="175"/>
+      <c r="Y8" s="175"/>
+      <c r="Z8" s="175"/>
+      <c r="AA8" s="175"/>
+      <c r="AB8" s="175"/>
+      <c r="AC8" s="175"/>
       <c r="AD8" s="59"/>
-      <c r="AE8" s="162" t="s">
+      <c r="AE8" s="186" t="s">
         <v>13</v>
       </c>
-      <c r="AF8" s="162"/>
-      <c r="AG8" s="162"/>
-      <c r="AH8" s="162"/>
-      <c r="AI8" s="162"/>
-      <c r="AJ8" s="162"/>
-      <c r="AK8" s="162"/>
-      <c r="AL8" s="93" t="str">
+      <c r="AF8" s="186"/>
+      <c r="AG8" s="186"/>
+      <c r="AH8" s="186"/>
+      <c r="AI8" s="186"/>
+      <c r="AJ8" s="186"/>
+      <c r="AK8" s="186"/>
+      <c r="AL8" s="179" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,7,0))</f>
         <v/>
       </c>
-      <c r="AM8" s="93"/>
-      <c r="AN8" s="93"/>
-      <c r="AO8" s="93"/>
-      <c r="AP8" s="93"/>
-      <c r="AQ8" s="93"/>
-      <c r="AR8" s="93"/>
-      <c r="AS8" s="93"/>
-      <c r="AT8" s="93"/>
-      <c r="AU8" s="93"/>
-      <c r="AV8" s="93"/>
-      <c r="AW8" s="93"/>
-      <c r="AX8" s="93"/>
-      <c r="AY8" s="93"/>
-      <c r="AZ8" s="94"/>
+      <c r="AM8" s="179"/>
+      <c r="AN8" s="179"/>
+      <c r="AO8" s="179"/>
+      <c r="AP8" s="179"/>
+      <c r="AQ8" s="179"/>
+      <c r="AR8" s="179"/>
+      <c r="AS8" s="179"/>
+      <c r="AT8" s="179"/>
+      <c r="AU8" s="179"/>
+      <c r="AV8" s="179"/>
+      <c r="AW8" s="179"/>
+      <c r="AX8" s="179"/>
+      <c r="AY8" s="179"/>
+      <c r="AZ8" s="180"/>
     </row>
     <row r="9" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="202" t="s">
+      <c r="A9" s="172" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="203"/>
-      <c r="C9" s="203"/>
-      <c r="D9" s="203"/>
-      <c r="E9" s="203"/>
-      <c r="F9" s="203"/>
-      <c r="G9" s="206" t="str">
+      <c r="B9" s="173"/>
+      <c r="C9" s="173"/>
+      <c r="D9" s="173"/>
+      <c r="E9" s="173"/>
+      <c r="F9" s="173"/>
+      <c r="G9" s="177" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,8,0))</f>
         <v/>
       </c>
-      <c r="H9" s="207"/>
-      <c r="I9" s="207"/>
-      <c r="J9" s="207"/>
-      <c r="K9" s="207"/>
-      <c r="L9" s="207"/>
-      <c r="M9" s="207"/>
-      <c r="N9" s="207"/>
-      <c r="O9" s="207"/>
-      <c r="P9" s="207"/>
-      <c r="Q9" s="207"/>
-      <c r="R9" s="207"/>
-      <c r="S9" s="207"/>
-      <c r="T9" s="207"/>
-      <c r="U9" s="207"/>
-      <c r="V9" s="207"/>
-      <c r="W9" s="207"/>
-      <c r="X9" s="207"/>
-      <c r="Y9" s="207"/>
-      <c r="Z9" s="207"/>
-      <c r="AA9" s="207"/>
-      <c r="AB9" s="207"/>
-      <c r="AC9" s="207"/>
+      <c r="H9" s="178"/>
+      <c r="I9" s="178"/>
+      <c r="J9" s="178"/>
+      <c r="K9" s="178"/>
+      <c r="L9" s="178"/>
+      <c r="M9" s="178"/>
+      <c r="N9" s="178"/>
+      <c r="O9" s="178"/>
+      <c r="P9" s="178"/>
+      <c r="Q9" s="178"/>
+      <c r="R9" s="178"/>
+      <c r="S9" s="178"/>
+      <c r="T9" s="178"/>
+      <c r="U9" s="178"/>
+      <c r="V9" s="178"/>
+      <c r="W9" s="178"/>
+      <c r="X9" s="178"/>
+      <c r="Y9" s="178"/>
+      <c r="Z9" s="178"/>
+      <c r="AA9" s="178"/>
+      <c r="AB9" s="178"/>
+      <c r="AC9" s="178"/>
       <c r="AD9" s="59"/>
-      <c r="AE9" s="106" t="s">
+      <c r="AE9" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="AF9" s="106"/>
-      <c r="AG9" s="106"/>
-      <c r="AH9" s="106"/>
-      <c r="AI9" s="106"/>
-      <c r="AJ9" s="106"/>
-      <c r="AK9" s="106"/>
-      <c r="AL9" s="192" t="str">
+      <c r="AF9" s="170"/>
+      <c r="AG9" s="170"/>
+      <c r="AH9" s="170"/>
+      <c r="AI9" s="170"/>
+      <c r="AJ9" s="170"/>
+      <c r="AK9" s="170"/>
+      <c r="AL9" s="158" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,9,0))</f>
         <v/>
       </c>
-      <c r="AM9" s="193"/>
-      <c r="AN9" s="193"/>
-      <c r="AO9" s="193"/>
-      <c r="AP9" s="193"/>
-      <c r="AQ9" s="193"/>
-      <c r="AR9" s="193"/>
-      <c r="AS9" s="193"/>
-      <c r="AT9" s="193"/>
-      <c r="AU9" s="193"/>
-      <c r="AV9" s="193"/>
-      <c r="AW9" s="193"/>
-      <c r="AX9" s="193"/>
-      <c r="AY9" s="193"/>
-      <c r="AZ9" s="194"/>
+      <c r="AM9" s="159"/>
+      <c r="AN9" s="159"/>
+      <c r="AO9" s="159"/>
+      <c r="AP9" s="159"/>
+      <c r="AQ9" s="159"/>
+      <c r="AR9" s="159"/>
+      <c r="AS9" s="159"/>
+      <c r="AT9" s="159"/>
+      <c r="AU9" s="159"/>
+      <c r="AV9" s="159"/>
+      <c r="AW9" s="159"/>
+      <c r="AX9" s="159"/>
+      <c r="AY9" s="159"/>
+      <c r="AZ9" s="160"/>
     </row>
     <row r="10" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
@@ -5777,48 +5781,48 @@
       <c r="H12" s="59"/>
       <c r="I12" s="59"/>
       <c r="J12" s="59"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="93"/>
-      <c r="N12" s="93"/>
-      <c r="O12" s="93"/>
-      <c r="P12" s="93"/>
-      <c r="Q12" s="93"/>
-      <c r="R12" s="93"/>
-      <c r="S12" s="93"/>
-      <c r="T12" s="93"/>
-      <c r="U12" s="93"/>
-      <c r="V12" s="93"/>
-      <c r="W12" s="93"/>
-      <c r="X12" s="93"/>
-      <c r="Y12" s="93"/>
-      <c r="Z12" s="93"/>
-      <c r="AA12" s="93"/>
-      <c r="AB12" s="93"/>
-      <c r="AC12" s="93"/>
-      <c r="AD12" s="93"/>
-      <c r="AE12" s="93"/>
-      <c r="AF12" s="93"/>
-      <c r="AG12" s="93"/>
-      <c r="AH12" s="93"/>
-      <c r="AI12" s="93"/>
-      <c r="AJ12" s="93"/>
-      <c r="AK12" s="93"/>
-      <c r="AL12" s="93"/>
-      <c r="AM12" s="93"/>
-      <c r="AN12" s="93"/>
-      <c r="AO12" s="93"/>
-      <c r="AP12" s="93"/>
-      <c r="AQ12" s="93"/>
-      <c r="AR12" s="93"/>
-      <c r="AS12" s="93"/>
-      <c r="AT12" s="93"/>
-      <c r="AU12" s="93"/>
-      <c r="AV12" s="93"/>
-      <c r="AW12" s="93"/>
-      <c r="AX12" s="93"/>
-      <c r="AY12" s="93"/>
-      <c r="AZ12" s="94"/>
+      <c r="K12" s="230"/>
+      <c r="L12" s="179"/>
+      <c r="M12" s="179"/>
+      <c r="N12" s="179"/>
+      <c r="O12" s="179"/>
+      <c r="P12" s="179"/>
+      <c r="Q12" s="179"/>
+      <c r="R12" s="179"/>
+      <c r="S12" s="179"/>
+      <c r="T12" s="179"/>
+      <c r="U12" s="179"/>
+      <c r="V12" s="179"/>
+      <c r="W12" s="179"/>
+      <c r="X12" s="179"/>
+      <c r="Y12" s="179"/>
+      <c r="Z12" s="179"/>
+      <c r="AA12" s="179"/>
+      <c r="AB12" s="179"/>
+      <c r="AC12" s="179"/>
+      <c r="AD12" s="179"/>
+      <c r="AE12" s="179"/>
+      <c r="AF12" s="179"/>
+      <c r="AG12" s="179"/>
+      <c r="AH12" s="179"/>
+      <c r="AI12" s="179"/>
+      <c r="AJ12" s="179"/>
+      <c r="AK12" s="179"/>
+      <c r="AL12" s="179"/>
+      <c r="AM12" s="179"/>
+      <c r="AN12" s="179"/>
+      <c r="AO12" s="179"/>
+      <c r="AP12" s="179"/>
+      <c r="AQ12" s="179"/>
+      <c r="AR12" s="179"/>
+      <c r="AS12" s="179"/>
+      <c r="AT12" s="179"/>
+      <c r="AU12" s="179"/>
+      <c r="AV12" s="179"/>
+      <c r="AW12" s="179"/>
+      <c r="AX12" s="179"/>
+      <c r="AY12" s="179"/>
+      <c r="AZ12" s="180"/>
     </row>
     <row r="13" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56" t="s">
@@ -5833,398 +5837,398 @@
       <c r="H13" s="59"/>
       <c r="I13" s="59"/>
       <c r="J13" s="59"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="104"/>
-      <c r="O13" s="104"/>
-      <c r="P13" s="104"/>
-      <c r="Q13" s="104"/>
-      <c r="R13" s="104"/>
-      <c r="S13" s="104"/>
-      <c r="T13" s="104"/>
-      <c r="U13" s="104"/>
-      <c r="V13" s="104"/>
-      <c r="W13" s="104"/>
-      <c r="X13" s="104"/>
-      <c r="Y13" s="104"/>
-      <c r="Z13" s="104"/>
-      <c r="AA13" s="104"/>
-      <c r="AB13" s="104"/>
-      <c r="AC13" s="104"/>
-      <c r="AD13" s="104"/>
-      <c r="AE13" s="104"/>
-      <c r="AF13" s="104"/>
-      <c r="AG13" s="104"/>
-      <c r="AH13" s="104"/>
-      <c r="AI13" s="104"/>
-      <c r="AJ13" s="104"/>
-      <c r="AK13" s="104"/>
-      <c r="AL13" s="104"/>
-      <c r="AM13" s="104"/>
-      <c r="AN13" s="104"/>
-      <c r="AO13" s="104"/>
-      <c r="AP13" s="104"/>
-      <c r="AQ13" s="104"/>
-      <c r="AR13" s="104"/>
-      <c r="AS13" s="104"/>
-      <c r="AT13" s="104"/>
-      <c r="AU13" s="104"/>
-      <c r="AV13" s="104"/>
-      <c r="AW13" s="104"/>
-      <c r="AX13" s="104"/>
-      <c r="AY13" s="104"/>
-      <c r="AZ13" s="105"/>
+      <c r="K13" s="187"/>
+      <c r="L13" s="187"/>
+      <c r="M13" s="187"/>
+      <c r="N13" s="187"/>
+      <c r="O13" s="187"/>
+      <c r="P13" s="187"/>
+      <c r="Q13" s="187"/>
+      <c r="R13" s="187"/>
+      <c r="S13" s="187"/>
+      <c r="T13" s="187"/>
+      <c r="U13" s="187"/>
+      <c r="V13" s="187"/>
+      <c r="W13" s="187"/>
+      <c r="X13" s="187"/>
+      <c r="Y13" s="187"/>
+      <c r="Z13" s="187"/>
+      <c r="AA13" s="187"/>
+      <c r="AB13" s="187"/>
+      <c r="AC13" s="187"/>
+      <c r="AD13" s="187"/>
+      <c r="AE13" s="187"/>
+      <c r="AF13" s="187"/>
+      <c r="AG13" s="187"/>
+      <c r="AH13" s="187"/>
+      <c r="AI13" s="187"/>
+      <c r="AJ13" s="187"/>
+      <c r="AK13" s="187"/>
+      <c r="AL13" s="187"/>
+      <c r="AM13" s="187"/>
+      <c r="AN13" s="187"/>
+      <c r="AO13" s="187"/>
+      <c r="AP13" s="187"/>
+      <c r="AQ13" s="187"/>
+      <c r="AR13" s="187"/>
+      <c r="AS13" s="187"/>
+      <c r="AT13" s="187"/>
+      <c r="AU13" s="187"/>
+      <c r="AV13" s="187"/>
+      <c r="AW13" s="187"/>
+      <c r="AX13" s="187"/>
+      <c r="AY13" s="187"/>
+      <c r="AZ13" s="188"/>
     </row>
     <row r="14" spans="1:60" s="10" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="107"/>
-      <c r="B14" s="108"/>
-      <c r="C14" s="108"/>
-      <c r="D14" s="108"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="108"/>
-      <c r="I14" s="108"/>
-      <c r="J14" s="108"/>
-      <c r="K14" s="108"/>
-      <c r="L14" s="108"/>
-      <c r="M14" s="108"/>
-      <c r="N14" s="108"/>
-      <c r="O14" s="108"/>
-      <c r="P14" s="108"/>
-      <c r="Q14" s="108"/>
-      <c r="R14" s="108"/>
-      <c r="S14" s="108"/>
-      <c r="T14" s="108"/>
-      <c r="U14" s="108"/>
-      <c r="V14" s="108"/>
-      <c r="W14" s="108"/>
-      <c r="X14" s="108"/>
-      <c r="Y14" s="108"/>
-      <c r="Z14" s="108"/>
-      <c r="AA14" s="108"/>
-      <c r="AB14" s="108"/>
-      <c r="AC14" s="108"/>
-      <c r="AD14" s="108"/>
-      <c r="AE14" s="108"/>
-      <c r="AF14" s="108"/>
-      <c r="AG14" s="108"/>
-      <c r="AH14" s="108"/>
-      <c r="AI14" s="108"/>
-      <c r="AJ14" s="108"/>
-      <c r="AK14" s="108"/>
-      <c r="AL14" s="108"/>
-      <c r="AM14" s="108"/>
-      <c r="AN14" s="108"/>
-      <c r="AO14" s="108"/>
-      <c r="AP14" s="108"/>
-      <c r="AQ14" s="108"/>
-      <c r="AR14" s="108"/>
-      <c r="AS14" s="108"/>
-      <c r="AT14" s="108"/>
-      <c r="AU14" s="108"/>
-      <c r="AV14" s="108"/>
-      <c r="AW14" s="108"/>
-      <c r="AX14" s="108"/>
-      <c r="AY14" s="108"/>
-      <c r="AZ14" s="109"/>
+      <c r="A14" s="233"/>
+      <c r="B14" s="234"/>
+      <c r="C14" s="234"/>
+      <c r="D14" s="234"/>
+      <c r="E14" s="234"/>
+      <c r="F14" s="234"/>
+      <c r="G14" s="234"/>
+      <c r="H14" s="234"/>
+      <c r="I14" s="234"/>
+      <c r="J14" s="234"/>
+      <c r="K14" s="234"/>
+      <c r="L14" s="234"/>
+      <c r="M14" s="234"/>
+      <c r="N14" s="234"/>
+      <c r="O14" s="234"/>
+      <c r="P14" s="234"/>
+      <c r="Q14" s="234"/>
+      <c r="R14" s="234"/>
+      <c r="S14" s="234"/>
+      <c r="T14" s="234"/>
+      <c r="U14" s="234"/>
+      <c r="V14" s="234"/>
+      <c r="W14" s="234"/>
+      <c r="X14" s="234"/>
+      <c r="Y14" s="234"/>
+      <c r="Z14" s="234"/>
+      <c r="AA14" s="234"/>
+      <c r="AB14" s="234"/>
+      <c r="AC14" s="234"/>
+      <c r="AD14" s="234"/>
+      <c r="AE14" s="234"/>
+      <c r="AF14" s="234"/>
+      <c r="AG14" s="234"/>
+      <c r="AH14" s="234"/>
+      <c r="AI14" s="234"/>
+      <c r="AJ14" s="234"/>
+      <c r="AK14" s="234"/>
+      <c r="AL14" s="234"/>
+      <c r="AM14" s="234"/>
+      <c r="AN14" s="234"/>
+      <c r="AO14" s="234"/>
+      <c r="AP14" s="234"/>
+      <c r="AQ14" s="234"/>
+      <c r="AR14" s="234"/>
+      <c r="AS14" s="234"/>
+      <c r="AT14" s="234"/>
+      <c r="AU14" s="234"/>
+      <c r="AV14" s="234"/>
+      <c r="AW14" s="234"/>
+      <c r="AX14" s="234"/>
+      <c r="AY14" s="234"/>
+      <c r="AZ14" s="235"/>
       <c r="BC14" s="24"/>
     </row>
     <row r="15" spans="1:60" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="146"/>
-      <c r="B15" s="146"/>
-      <c r="C15" s="146"/>
-      <c r="D15" s="146"/>
-      <c r="E15" s="146"/>
-      <c r="F15" s="146"/>
-      <c r="G15" s="146"/>
-      <c r="H15" s="146"/>
-      <c r="I15" s="146"/>
-      <c r="J15" s="146"/>
-      <c r="K15" s="146"/>
-      <c r="L15" s="146"/>
-      <c r="M15" s="146"/>
-      <c r="N15" s="146"/>
-      <c r="O15" s="146"/>
-      <c r="P15" s="146"/>
-      <c r="Q15" s="146"/>
-      <c r="R15" s="146"/>
-      <c r="S15" s="146"/>
-      <c r="T15" s="146"/>
-      <c r="U15" s="146"/>
-      <c r="V15" s="146"/>
-      <c r="W15" s="146"/>
-      <c r="X15" s="146"/>
-      <c r="Y15" s="146"/>
-      <c r="Z15" s="146"/>
-      <c r="AA15" s="146"/>
-      <c r="AB15" s="146"/>
-      <c r="AC15" s="146"/>
-      <c r="AD15" s="146"/>
-      <c r="AE15" s="146"/>
-      <c r="AF15" s="146"/>
-      <c r="AG15" s="146"/>
-      <c r="AH15" s="146"/>
-      <c r="AI15" s="146"/>
-      <c r="AJ15" s="146"/>
-      <c r="AK15" s="146"/>
-      <c r="AL15" s="146"/>
-      <c r="AM15" s="146"/>
-      <c r="AN15" s="146"/>
-      <c r="AO15" s="146"/>
-      <c r="AP15" s="146"/>
-      <c r="AQ15" s="146"/>
-      <c r="AR15" s="146"/>
-      <c r="AS15" s="146"/>
-      <c r="AT15" s="146"/>
-      <c r="AU15" s="146"/>
-      <c r="AV15" s="146"/>
-      <c r="AW15" s="146"/>
-      <c r="AX15" s="146"/>
-      <c r="AY15" s="146"/>
-      <c r="AZ15" s="146"/>
+      <c r="A15" s="99"/>
+      <c r="B15" s="99"/>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="99"/>
+      <c r="L15" s="99"/>
+      <c r="M15" s="99"/>
+      <c r="N15" s="99"/>
+      <c r="O15" s="99"/>
+      <c r="P15" s="99"/>
+      <c r="Q15" s="99"/>
+      <c r="R15" s="99"/>
+      <c r="S15" s="99"/>
+      <c r="T15" s="99"/>
+      <c r="U15" s="99"/>
+      <c r="V15" s="99"/>
+      <c r="W15" s="99"/>
+      <c r="X15" s="99"/>
+      <c r="Y15" s="99"/>
+      <c r="Z15" s="99"/>
+      <c r="AA15" s="99"/>
+      <c r="AB15" s="99"/>
+      <c r="AC15" s="99"/>
+      <c r="AD15" s="99"/>
+      <c r="AE15" s="99"/>
+      <c r="AF15" s="99"/>
+      <c r="AG15" s="99"/>
+      <c r="AH15" s="99"/>
+      <c r="AI15" s="99"/>
+      <c r="AJ15" s="99"/>
+      <c r="AK15" s="99"/>
+      <c r="AL15" s="99"/>
+      <c r="AM15" s="99"/>
+      <c r="AN15" s="99"/>
+      <c r="AO15" s="99"/>
+      <c r="AP15" s="99"/>
+      <c r="AQ15" s="99"/>
+      <c r="AR15" s="99"/>
+      <c r="AS15" s="99"/>
+      <c r="AT15" s="99"/>
+      <c r="AU15" s="99"/>
+      <c r="AV15" s="99"/>
+      <c r="AW15" s="99"/>
+      <c r="AX15" s="99"/>
+      <c r="AY15" s="99"/>
+      <c r="AZ15" s="99"/>
     </row>
     <row r="16" spans="1:60" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="110" t="s">
+      <c r="A16" s="236" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="111"/>
-      <c r="P16" s="111"/>
-      <c r="Q16" s="111"/>
-      <c r="R16" s="111"/>
-      <c r="S16" s="111"/>
-      <c r="T16" s="111"/>
-      <c r="U16" s="111"/>
-      <c r="V16" s="111"/>
-      <c r="W16" s="111"/>
-      <c r="X16" s="111"/>
-      <c r="Y16" s="111"/>
-      <c r="Z16" s="111"/>
-      <c r="AA16" s="111"/>
-      <c r="AB16" s="111"/>
-      <c r="AC16" s="111"/>
-      <c r="AD16" s="111"/>
-      <c r="AE16" s="111"/>
-      <c r="AF16" s="111"/>
-      <c r="AG16" s="111"/>
-      <c r="AH16" s="111"/>
-      <c r="AI16" s="111"/>
-      <c r="AJ16" s="111"/>
-      <c r="AK16" s="111"/>
-      <c r="AL16" s="111"/>
-      <c r="AM16" s="111"/>
-      <c r="AN16" s="111"/>
-      <c r="AO16" s="111"/>
-      <c r="AP16" s="111"/>
-      <c r="AQ16" s="111"/>
-      <c r="AR16" s="111"/>
-      <c r="AS16" s="111"/>
-      <c r="AT16" s="111"/>
-      <c r="AU16" s="111"/>
-      <c r="AV16" s="111"/>
-      <c r="AW16" s="111"/>
-      <c r="AX16" s="111"/>
-      <c r="AY16" s="111"/>
-      <c r="AZ16" s="112"/>
+      <c r="B16" s="237"/>
+      <c r="C16" s="237"/>
+      <c r="D16" s="237"/>
+      <c r="E16" s="237"/>
+      <c r="F16" s="237"/>
+      <c r="G16" s="237"/>
+      <c r="H16" s="237"/>
+      <c r="I16" s="237"/>
+      <c r="J16" s="237"/>
+      <c r="K16" s="237"/>
+      <c r="L16" s="237"/>
+      <c r="M16" s="237"/>
+      <c r="N16" s="237"/>
+      <c r="O16" s="237"/>
+      <c r="P16" s="237"/>
+      <c r="Q16" s="237"/>
+      <c r="R16" s="237"/>
+      <c r="S16" s="237"/>
+      <c r="T16" s="237"/>
+      <c r="U16" s="237"/>
+      <c r="V16" s="237"/>
+      <c r="W16" s="237"/>
+      <c r="X16" s="237"/>
+      <c r="Y16" s="237"/>
+      <c r="Z16" s="237"/>
+      <c r="AA16" s="237"/>
+      <c r="AB16" s="237"/>
+      <c r="AC16" s="237"/>
+      <c r="AD16" s="237"/>
+      <c r="AE16" s="237"/>
+      <c r="AF16" s="237"/>
+      <c r="AG16" s="237"/>
+      <c r="AH16" s="237"/>
+      <c r="AI16" s="237"/>
+      <c r="AJ16" s="237"/>
+      <c r="AK16" s="237"/>
+      <c r="AL16" s="237"/>
+      <c r="AM16" s="237"/>
+      <c r="AN16" s="237"/>
+      <c r="AO16" s="237"/>
+      <c r="AP16" s="237"/>
+      <c r="AQ16" s="237"/>
+      <c r="AR16" s="237"/>
+      <c r="AS16" s="237"/>
+      <c r="AT16" s="237"/>
+      <c r="AU16" s="237"/>
+      <c r="AV16" s="237"/>
+      <c r="AW16" s="237"/>
+      <c r="AX16" s="237"/>
+      <c r="AY16" s="237"/>
+      <c r="AZ16" s="238"/>
     </row>
     <row r="17" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="199" t="s">
+      <c r="A17" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="200"/>
-      <c r="C17" s="200"/>
-      <c r="D17" s="200"/>
-      <c r="E17" s="200"/>
-      <c r="F17" s="200"/>
-      <c r="G17" s="200"/>
-      <c r="H17" s="200"/>
-      <c r="I17" s="200"/>
-      <c r="J17" s="200"/>
-      <c r="K17" s="200"/>
-      <c r="L17" s="200"/>
-      <c r="M17" s="197" t="s">
+      <c r="B17" s="169"/>
+      <c r="C17" s="169"/>
+      <c r="D17" s="169"/>
+      <c r="E17" s="169"/>
+      <c r="F17" s="169"/>
+      <c r="G17" s="169"/>
+      <c r="H17" s="169"/>
+      <c r="I17" s="169"/>
+      <c r="J17" s="169"/>
+      <c r="K17" s="169"/>
+      <c r="L17" s="169"/>
+      <c r="M17" s="166" t="s">
         <v>32</v>
       </c>
-      <c r="N17" s="198"/>
-      <c r="O17" s="198"/>
-      <c r="P17" s="198"/>
-      <c r="Q17" s="198"/>
-      <c r="R17" s="116" t="s">
+      <c r="N17" s="167"/>
+      <c r="O17" s="167"/>
+      <c r="P17" s="167"/>
+      <c r="Q17" s="167"/>
+      <c r="R17" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="118"/>
-      <c r="W17" s="116" t="s">
+      <c r="S17" s="164"/>
+      <c r="T17" s="164"/>
+      <c r="U17" s="164"/>
+      <c r="V17" s="165"/>
+      <c r="W17" s="163" t="s">
         <v>34</v>
       </c>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="118"/>
-      <c r="AB17" s="116" t="s">
+      <c r="X17" s="164"/>
+      <c r="Y17" s="164"/>
+      <c r="Z17" s="164"/>
+      <c r="AA17" s="165"/>
+      <c r="AB17" s="163" t="s">
         <v>35</v>
       </c>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="118"/>
-      <c r="AG17" s="116" t="s">
+      <c r="AC17" s="164"/>
+      <c r="AD17" s="164"/>
+      <c r="AE17" s="164"/>
+      <c r="AF17" s="165"/>
+      <c r="AG17" s="163" t="s">
         <v>36</v>
       </c>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="117"/>
-      <c r="AJ17" s="117"/>
-      <c r="AK17" s="118"/>
-      <c r="AL17" s="116" t="s">
+      <c r="AH17" s="164"/>
+      <c r="AI17" s="164"/>
+      <c r="AJ17" s="164"/>
+      <c r="AK17" s="165"/>
+      <c r="AL17" s="163" t="s">
         <v>37</v>
       </c>
-      <c r="AM17" s="117"/>
-      <c r="AN17" s="117"/>
-      <c r="AO17" s="117"/>
-      <c r="AP17" s="118"/>
-      <c r="AQ17" s="116" t="s">
+      <c r="AM17" s="164"/>
+      <c r="AN17" s="164"/>
+      <c r="AO17" s="164"/>
+      <c r="AP17" s="165"/>
+      <c r="AQ17" s="163" t="s">
         <v>38</v>
       </c>
-      <c r="AR17" s="117"/>
-      <c r="AS17" s="117"/>
-      <c r="AT17" s="117"/>
-      <c r="AU17" s="118"/>
-      <c r="AV17" s="113" t="s">
+      <c r="AR17" s="164"/>
+      <c r="AS17" s="164"/>
+      <c r="AT17" s="164"/>
+      <c r="AU17" s="165"/>
+      <c r="AV17" s="239" t="s">
         <v>32</v>
       </c>
-      <c r="AW17" s="114"/>
-      <c r="AX17" s="114"/>
-      <c r="AY17" s="114"/>
-      <c r="AZ17" s="115"/>
+      <c r="AW17" s="240"/>
+      <c r="AX17" s="240"/>
+      <c r="AY17" s="240"/>
+      <c r="AZ17" s="241"/>
     </row>
     <row r="18" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="228" t="s">
+      <c r="A18" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="229"/>
-      <c r="C18" s="229"/>
-      <c r="D18" s="229"/>
-      <c r="E18" s="229"/>
-      <c r="F18" s="229"/>
-      <c r="G18" s="229"/>
-      <c r="H18" s="229"/>
-      <c r="I18" s="229"/>
-      <c r="J18" s="229"/>
-      <c r="K18" s="229"/>
-      <c r="L18" s="230"/>
-      <c r="M18" s="227"/>
-      <c r="N18" s="120"/>
-      <c r="O18" s="120"/>
-      <c r="P18" s="120"/>
-      <c r="Q18" s="120"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="120"/>
-      <c r="T18" s="120"/>
-      <c r="U18" s="120"/>
-      <c r="V18" s="120"/>
-      <c r="W18" s="119"/>
-      <c r="X18" s="120"/>
-      <c r="Y18" s="120"/>
-      <c r="Z18" s="120"/>
-      <c r="AA18" s="120"/>
-      <c r="AB18" s="119"/>
-      <c r="AC18" s="120"/>
-      <c r="AD18" s="120"/>
-      <c r="AE18" s="120"/>
-      <c r="AF18" s="120"/>
-      <c r="AG18" s="119"/>
-      <c r="AH18" s="120"/>
-      <c r="AI18" s="120"/>
-      <c r="AJ18" s="120"/>
-      <c r="AK18" s="120"/>
-      <c r="AL18" s="119"/>
-      <c r="AM18" s="120"/>
-      <c r="AN18" s="120"/>
-      <c r="AO18" s="120"/>
-      <c r="AP18" s="120"/>
-      <c r="AQ18" s="119"/>
-      <c r="AR18" s="120"/>
-      <c r="AS18" s="120"/>
-      <c r="AT18" s="120"/>
-      <c r="AU18" s="120"/>
-      <c r="AV18" s="121"/>
-      <c r="AW18" s="287"/>
-      <c r="AX18" s="287"/>
-      <c r="AY18" s="287"/>
-      <c r="AZ18" s="288"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="93"/>
+      <c r="K18" s="93"/>
+      <c r="L18" s="94"/>
+      <c r="M18" s="91"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="89"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="89"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="89"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="89"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="90"/>
+      <c r="AK18" s="90"/>
+      <c r="AL18" s="89"/>
+      <c r="AM18" s="90"/>
+      <c r="AN18" s="90"/>
+      <c r="AO18" s="90"/>
+      <c r="AP18" s="90"/>
+      <c r="AQ18" s="89"/>
+      <c r="AR18" s="90"/>
+      <c r="AS18" s="90"/>
+      <c r="AT18" s="90"/>
+      <c r="AU18" s="90"/>
+      <c r="AV18" s="242"/>
+      <c r="AW18" s="243"/>
+      <c r="AX18" s="243"/>
+      <c r="AY18" s="243"/>
+      <c r="AZ18" s="244"/>
       <c r="BD18" s="26"/>
     </row>
     <row r="19" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="218" t="s">
+      <c r="A19" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="219"/>
-      <c r="C19" s="219"/>
-      <c r="D19" s="219"/>
-      <c r="E19" s="219"/>
-      <c r="F19" s="219"/>
-      <c r="G19" s="219"/>
-      <c r="H19" s="219"/>
-      <c r="I19" s="219"/>
-      <c r="J19" s="219"/>
-      <c r="K19" s="219"/>
-      <c r="L19" s="220"/>
-      <c r="M19" s="213"/>
-      <c r="N19" s="163"/>
-      <c r="O19" s="163"/>
-      <c r="P19" s="163"/>
-      <c r="Q19" s="163"/>
-      <c r="R19" s="163"/>
-      <c r="S19" s="163"/>
-      <c r="T19" s="163"/>
-      <c r="U19" s="163"/>
-      <c r="V19" s="163"/>
-      <c r="W19" s="163"/>
-      <c r="X19" s="163"/>
-      <c r="Y19" s="163"/>
-      <c r="Z19" s="163"/>
-      <c r="AA19" s="163"/>
-      <c r="AB19" s="210"/>
-      <c r="AC19" s="163"/>
-      <c r="AD19" s="163"/>
-      <c r="AE19" s="163"/>
-      <c r="AF19" s="163"/>
-      <c r="AG19" s="210"/>
-      <c r="AH19" s="163"/>
-      <c r="AI19" s="163"/>
-      <c r="AJ19" s="163"/>
-      <c r="AK19" s="163"/>
-      <c r="AL19" s="210"/>
-      <c r="AM19" s="163"/>
-      <c r="AN19" s="163"/>
-      <c r="AO19" s="163"/>
-      <c r="AP19" s="163"/>
-      <c r="AQ19" s="210"/>
-      <c r="AR19" s="163"/>
-      <c r="AS19" s="163"/>
-      <c r="AT19" s="163"/>
-      <c r="AU19" s="163"/>
-      <c r="AV19" s="210"/>
-      <c r="AW19" s="163"/>
-      <c r="AX19" s="163"/>
-      <c r="AY19" s="163"/>
-      <c r="AZ19" s="231"/>
+      <c r="B19" s="130"/>
+      <c r="C19" s="130"/>
+      <c r="D19" s="130"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="130"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="130"/>
+      <c r="J19" s="130"/>
+      <c r="K19" s="130"/>
+      <c r="L19" s="131"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="96"/>
+      <c r="O19" s="96"/>
+      <c r="P19" s="96"/>
+      <c r="Q19" s="96"/>
+      <c r="R19" s="96"/>
+      <c r="S19" s="96"/>
+      <c r="T19" s="96"/>
+      <c r="U19" s="96"/>
+      <c r="V19" s="96"/>
+      <c r="W19" s="96"/>
+      <c r="X19" s="96"/>
+      <c r="Y19" s="96"/>
+      <c r="Z19" s="96"/>
+      <c r="AA19" s="96"/>
+      <c r="AB19" s="95"/>
+      <c r="AC19" s="96"/>
+      <c r="AD19" s="96"/>
+      <c r="AE19" s="96"/>
+      <c r="AF19" s="96"/>
+      <c r="AG19" s="95"/>
+      <c r="AH19" s="96"/>
+      <c r="AI19" s="96"/>
+      <c r="AJ19" s="96"/>
+      <c r="AK19" s="96"/>
+      <c r="AL19" s="95"/>
+      <c r="AM19" s="96"/>
+      <c r="AN19" s="96"/>
+      <c r="AO19" s="96"/>
+      <c r="AP19" s="96"/>
+      <c r="AQ19" s="95"/>
+      <c r="AR19" s="96"/>
+      <c r="AS19" s="96"/>
+      <c r="AT19" s="96"/>
+      <c r="AU19" s="96"/>
+      <c r="AV19" s="95"/>
+      <c r="AW19" s="96"/>
+      <c r="AX19" s="96"/>
+      <c r="AY19" s="96"/>
+      <c r="AZ19" s="97"/>
       <c r="BC19" s="29"/>
       <c r="BD19" s="49"/>
       <c r="BE19" s="30"/>
@@ -6235,60 +6239,60 @@
       <c r="BJ19" s="49"/>
     </row>
     <row r="20" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="221" t="s">
+      <c r="A20" s="132" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="222"/>
-      <c r="C20" s="222"/>
-      <c r="D20" s="222"/>
-      <c r="E20" s="222"/>
-      <c r="F20" s="222"/>
-      <c r="G20" s="222"/>
-      <c r="H20" s="222"/>
-      <c r="I20" s="222"/>
-      <c r="J20" s="222"/>
-      <c r="K20" s="222"/>
-      <c r="L20" s="223"/>
-      <c r="M20" s="214"/>
-      <c r="N20" s="164"/>
-      <c r="O20" s="164"/>
-      <c r="P20" s="164"/>
-      <c r="Q20" s="164"/>
-      <c r="R20" s="164"/>
-      <c r="S20" s="164"/>
-      <c r="T20" s="164"/>
-      <c r="U20" s="164"/>
-      <c r="V20" s="164"/>
-      <c r="W20" s="164"/>
-      <c r="X20" s="164"/>
-      <c r="Y20" s="164"/>
-      <c r="Z20" s="164"/>
-      <c r="AA20" s="164"/>
-      <c r="AB20" s="164"/>
-      <c r="AC20" s="164"/>
-      <c r="AD20" s="164"/>
-      <c r="AE20" s="164"/>
-      <c r="AF20" s="164"/>
-      <c r="AG20" s="164"/>
-      <c r="AH20" s="164"/>
-      <c r="AI20" s="164"/>
-      <c r="AJ20" s="164"/>
-      <c r="AK20" s="164"/>
-      <c r="AL20" s="164"/>
-      <c r="AM20" s="164"/>
-      <c r="AN20" s="164"/>
-      <c r="AO20" s="164"/>
-      <c r="AP20" s="164"/>
-      <c r="AQ20" s="164"/>
-      <c r="AR20" s="164"/>
-      <c r="AS20" s="164"/>
-      <c r="AT20" s="164"/>
-      <c r="AU20" s="164"/>
-      <c r="AV20" s="164"/>
-      <c r="AW20" s="164"/>
-      <c r="AX20" s="164"/>
-      <c r="AY20" s="164"/>
-      <c r="AZ20" s="166"/>
+      <c r="B20" s="133"/>
+      <c r="C20" s="133"/>
+      <c r="D20" s="133"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="133"/>
+      <c r="G20" s="133"/>
+      <c r="H20" s="133"/>
+      <c r="I20" s="133"/>
+      <c r="J20" s="133"/>
+      <c r="K20" s="133"/>
+      <c r="L20" s="134"/>
+      <c r="M20" s="122"/>
+      <c r="N20" s="123"/>
+      <c r="O20" s="123"/>
+      <c r="P20" s="123"/>
+      <c r="Q20" s="123"/>
+      <c r="R20" s="123"/>
+      <c r="S20" s="123"/>
+      <c r="T20" s="123"/>
+      <c r="U20" s="123"/>
+      <c r="V20" s="123"/>
+      <c r="W20" s="123"/>
+      <c r="X20" s="123"/>
+      <c r="Y20" s="123"/>
+      <c r="Z20" s="123"/>
+      <c r="AA20" s="123"/>
+      <c r="AB20" s="123"/>
+      <c r="AC20" s="123"/>
+      <c r="AD20" s="123"/>
+      <c r="AE20" s="123"/>
+      <c r="AF20" s="123"/>
+      <c r="AG20" s="123"/>
+      <c r="AH20" s="123"/>
+      <c r="AI20" s="123"/>
+      <c r="AJ20" s="123"/>
+      <c r="AK20" s="123"/>
+      <c r="AL20" s="123"/>
+      <c r="AM20" s="123"/>
+      <c r="AN20" s="123"/>
+      <c r="AO20" s="123"/>
+      <c r="AP20" s="123"/>
+      <c r="AQ20" s="123"/>
+      <c r="AR20" s="123"/>
+      <c r="AS20" s="123"/>
+      <c r="AT20" s="123"/>
+      <c r="AU20" s="123"/>
+      <c r="AV20" s="123"/>
+      <c r="AW20" s="123"/>
+      <c r="AX20" s="123"/>
+      <c r="AY20" s="123"/>
+      <c r="AZ20" s="192"/>
       <c r="BC20" s="29"/>
       <c r="BD20" s="31"/>
       <c r="BE20" s="31"/>
@@ -6299,63 +6303,63 @@
       <c r="BJ20" s="31"/>
     </row>
     <row r="21" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="221" t="s">
+      <c r="A21" s="132" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="222"/>
-      <c r="C21" s="222"/>
-      <c r="D21" s="222"/>
-      <c r="E21" s="222"/>
-      <c r="F21" s="222"/>
-      <c r="G21" s="222"/>
-      <c r="H21" s="222"/>
-      <c r="I21" s="222"/>
-      <c r="J21" s="222"/>
-      <c r="K21" s="222"/>
-      <c r="L21" s="223"/>
-      <c r="M21" s="215"/>
-      <c r="N21" s="165"/>
-      <c r="O21" s="165"/>
-      <c r="P21" s="165"/>
-      <c r="Q21" s="165"/>
-      <c r="R21" s="165"/>
-      <c r="S21" s="165"/>
-      <c r="T21" s="165"/>
-      <c r="U21" s="165"/>
-      <c r="V21" s="165"/>
-      <c r="W21" s="165"/>
-      <c r="X21" s="165"/>
-      <c r="Y21" s="165"/>
-      <c r="Z21" s="165"/>
-      <c r="AA21" s="165"/>
-      <c r="AB21" s="165"/>
-      <c r="AC21" s="165"/>
-      <c r="AD21" s="165"/>
-      <c r="AE21" s="165"/>
-      <c r="AF21" s="165"/>
-      <c r="AG21" s="165"/>
-      <c r="AH21" s="165"/>
-      <c r="AI21" s="165"/>
-      <c r="AJ21" s="165"/>
-      <c r="AK21" s="165"/>
-      <c r="AL21" s="165"/>
-      <c r="AM21" s="165"/>
-      <c r="AN21" s="165"/>
-      <c r="AO21" s="165"/>
-      <c r="AP21" s="165"/>
-      <c r="AQ21" s="165"/>
-      <c r="AR21" s="165"/>
-      <c r="AS21" s="165"/>
-      <c r="AT21" s="165"/>
-      <c r="AU21" s="165"/>
-      <c r="AV21" s="165"/>
-      <c r="AW21" s="165"/>
-      <c r="AX21" s="165"/>
-      <c r="AY21" s="165"/>
-      <c r="AZ21" s="167"/>
+      <c r="B21" s="133"/>
+      <c r="C21" s="133"/>
+      <c r="D21" s="133"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="133"/>
+      <c r="I21" s="133"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="134"/>
+      <c r="M21" s="124"/>
+      <c r="N21" s="115"/>
+      <c r="O21" s="115"/>
+      <c r="P21" s="115"/>
+      <c r="Q21" s="115"/>
+      <c r="R21" s="115"/>
+      <c r="S21" s="115"/>
+      <c r="T21" s="115"/>
+      <c r="U21" s="115"/>
+      <c r="V21" s="115"/>
+      <c r="W21" s="115"/>
+      <c r="X21" s="115"/>
+      <c r="Y21" s="115"/>
+      <c r="Z21" s="115"/>
+      <c r="AA21" s="115"/>
+      <c r="AB21" s="115"/>
+      <c r="AC21" s="115"/>
+      <c r="AD21" s="115"/>
+      <c r="AE21" s="115"/>
+      <c r="AF21" s="115"/>
+      <c r="AG21" s="115"/>
+      <c r="AH21" s="115"/>
+      <c r="AI21" s="115"/>
+      <c r="AJ21" s="115"/>
+      <c r="AK21" s="115"/>
+      <c r="AL21" s="115"/>
+      <c r="AM21" s="115"/>
+      <c r="AN21" s="115"/>
+      <c r="AO21" s="115"/>
+      <c r="AP21" s="115"/>
+      <c r="AQ21" s="115"/>
+      <c r="AR21" s="115"/>
+      <c r="AS21" s="115"/>
+      <c r="AT21" s="115"/>
+      <c r="AU21" s="115"/>
+      <c r="AV21" s="115"/>
+      <c r="AW21" s="115"/>
+      <c r="AX21" s="115"/>
+      <c r="AY21" s="115"/>
+      <c r="AZ21" s="116"/>
       <c r="BC21" s="29"/>
-      <c r="BD21" s="90"/>
-      <c r="BE21" s="90"/>
+      <c r="BD21" s="229"/>
+      <c r="BE21" s="229"/>
       <c r="BF21" s="29"/>
       <c r="BG21" s="29"/>
       <c r="BH21" s="29"/>
@@ -6363,84 +6367,84 @@
       <c r="BJ21" s="29"/>
     </row>
     <row r="22" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="221" t="s">
+      <c r="A22" s="132" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="222"/>
-      <c r="C22" s="222"/>
-      <c r="D22" s="222"/>
-      <c r="E22" s="222"/>
-      <c r="F22" s="222"/>
-      <c r="G22" s="222"/>
-      <c r="H22" s="222"/>
-      <c r="I22" s="222"/>
-      <c r="J22" s="222"/>
-      <c r="K22" s="222"/>
-      <c r="L22" s="223"/>
-      <c r="M22" s="215" t="str">
+      <c r="B22" s="133"/>
+      <c r="C22" s="133"/>
+      <c r="D22" s="133"/>
+      <c r="E22" s="133"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="133"/>
+      <c r="I22" s="133"/>
+      <c r="J22" s="133"/>
+      <c r="K22" s="133"/>
+      <c r="L22" s="134"/>
+      <c r="M22" s="124" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="N22" s="165"/>
-      <c r="O22" s="165"/>
-      <c r="P22" s="165"/>
-      <c r="Q22" s="165"/>
-      <c r="R22" s="165" t="str">
+      <c r="N22" s="115"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="115"/>
+      <c r="Q22" s="115"/>
+      <c r="R22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="S22" s="165"/>
-      <c r="T22" s="165"/>
-      <c r="U22" s="165"/>
-      <c r="V22" s="165"/>
-      <c r="W22" s="165" t="str">
+      <c r="S22" s="115"/>
+      <c r="T22" s="115"/>
+      <c r="U22" s="115"/>
+      <c r="V22" s="115"/>
+      <c r="W22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="X22" s="165"/>
-      <c r="Y22" s="165"/>
-      <c r="Z22" s="165"/>
-      <c r="AA22" s="165"/>
-      <c r="AB22" s="165" t="str">
+      <c r="X22" s="115"/>
+      <c r="Y22" s="115"/>
+      <c r="Z22" s="115"/>
+      <c r="AA22" s="115"/>
+      <c r="AB22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AC22" s="165"/>
-      <c r="AD22" s="165"/>
-      <c r="AE22" s="165"/>
-      <c r="AF22" s="165"/>
-      <c r="AG22" s="165" t="str">
+      <c r="AC22" s="115"/>
+      <c r="AD22" s="115"/>
+      <c r="AE22" s="115"/>
+      <c r="AF22" s="115"/>
+      <c r="AG22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AH22" s="165"/>
-      <c r="AI22" s="165"/>
-      <c r="AJ22" s="165"/>
-      <c r="AK22" s="165"/>
-      <c r="AL22" s="165" t="str">
+      <c r="AH22" s="115"/>
+      <c r="AI22" s="115"/>
+      <c r="AJ22" s="115"/>
+      <c r="AK22" s="115"/>
+      <c r="AL22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AM22" s="165"/>
-      <c r="AN22" s="165"/>
-      <c r="AO22" s="165"/>
-      <c r="AP22" s="165"/>
-      <c r="AQ22" s="165" t="str">
+      <c r="AM22" s="115"/>
+      <c r="AN22" s="115"/>
+      <c r="AO22" s="115"/>
+      <c r="AP22" s="115"/>
+      <c r="AQ22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AR22" s="165"/>
-      <c r="AS22" s="165"/>
-      <c r="AT22" s="165"/>
-      <c r="AU22" s="165"/>
-      <c r="AV22" s="165" t="str">
+      <c r="AR22" s="115"/>
+      <c r="AS22" s="115"/>
+      <c r="AT22" s="115"/>
+      <c r="AU22" s="115"/>
+      <c r="AV22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AW22" s="165"/>
-      <c r="AX22" s="165"/>
-      <c r="AY22" s="165"/>
-      <c r="AZ22" s="167"/>
+      <c r="AW22" s="115"/>
+      <c r="AX22" s="115"/>
+      <c r="AY22" s="115"/>
+      <c r="AZ22" s="116"/>
       <c r="BC22" s="29"/>
       <c r="BD22" s="31"/>
       <c r="BE22" s="31"/>
@@ -6451,87 +6455,87 @@
       <c r="BJ22" s="29"/>
     </row>
     <row r="23" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="221" t="s">
+      <c r="A23" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="222"/>
-      <c r="C23" s="222"/>
-      <c r="D23" s="222"/>
-      <c r="E23" s="222"/>
-      <c r="F23" s="222"/>
-      <c r="G23" s="222"/>
-      <c r="H23" s="222"/>
-      <c r="I23" s="222"/>
-      <c r="J23" s="222"/>
-      <c r="K23" s="222"/>
-      <c r="L23" s="223"/>
-      <c r="M23" s="215" t="str">
+      <c r="B23" s="133"/>
+      <c r="C23" s="133"/>
+      <c r="D23" s="133"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="133"/>
+      <c r="I23" s="133"/>
+      <c r="J23" s="133"/>
+      <c r="K23" s="133"/>
+      <c r="L23" s="134"/>
+      <c r="M23" s="124" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="N23" s="165"/>
-      <c r="O23" s="165"/>
-      <c r="P23" s="165"/>
-      <c r="Q23" s="165"/>
-      <c r="R23" s="165" t="str">
+      <c r="N23" s="115"/>
+      <c r="O23" s="115"/>
+      <c r="P23" s="115"/>
+      <c r="Q23" s="115"/>
+      <c r="R23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="S23" s="165"/>
-      <c r="T23" s="165"/>
-      <c r="U23" s="165"/>
-      <c r="V23" s="165"/>
-      <c r="W23" s="165" t="str">
+      <c r="S23" s="115"/>
+      <c r="T23" s="115"/>
+      <c r="U23" s="115"/>
+      <c r="V23" s="115"/>
+      <c r="W23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="X23" s="165"/>
-      <c r="Y23" s="165"/>
-      <c r="Z23" s="165"/>
-      <c r="AA23" s="165"/>
-      <c r="AB23" s="165" t="str">
+      <c r="X23" s="115"/>
+      <c r="Y23" s="115"/>
+      <c r="Z23" s="115"/>
+      <c r="AA23" s="115"/>
+      <c r="AB23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AC23" s="165"/>
-      <c r="AD23" s="165"/>
-      <c r="AE23" s="165"/>
-      <c r="AF23" s="165"/>
-      <c r="AG23" s="165" t="str">
+      <c r="AC23" s="115"/>
+      <c r="AD23" s="115"/>
+      <c r="AE23" s="115"/>
+      <c r="AF23" s="115"/>
+      <c r="AG23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AH23" s="165"/>
-      <c r="AI23" s="165"/>
-      <c r="AJ23" s="165"/>
-      <c r="AK23" s="165"/>
-      <c r="AL23" s="165" t="str">
+      <c r="AH23" s="115"/>
+      <c r="AI23" s="115"/>
+      <c r="AJ23" s="115"/>
+      <c r="AK23" s="115"/>
+      <c r="AL23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AM23" s="165"/>
-      <c r="AN23" s="165"/>
-      <c r="AO23" s="165"/>
-      <c r="AP23" s="165"/>
-      <c r="AQ23" s="165" t="str">
+      <c r="AM23" s="115"/>
+      <c r="AN23" s="115"/>
+      <c r="AO23" s="115"/>
+      <c r="AP23" s="115"/>
+      <c r="AQ23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AR23" s="165"/>
-      <c r="AS23" s="165"/>
-      <c r="AT23" s="165"/>
-      <c r="AU23" s="165"/>
-      <c r="AV23" s="165" t="str">
+      <c r="AR23" s="115"/>
+      <c r="AS23" s="115"/>
+      <c r="AT23" s="115"/>
+      <c r="AU23" s="115"/>
+      <c r="AV23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AW23" s="165"/>
-      <c r="AX23" s="165"/>
-      <c r="AY23" s="165"/>
-      <c r="AZ23" s="167"/>
+      <c r="AW23" s="115"/>
+      <c r="AX23" s="115"/>
+      <c r="AY23" s="115"/>
+      <c r="AZ23" s="116"/>
       <c r="BC23" s="32"/>
-      <c r="BD23" s="90"/>
-      <c r="BE23" s="90"/>
+      <c r="BD23" s="229"/>
+      <c r="BE23" s="229"/>
       <c r="BF23" s="32"/>
       <c r="BG23" s="32"/>
       <c r="BH23" s="32"/>
@@ -6539,84 +6543,84 @@
       <c r="BJ23" s="32"/>
     </row>
     <row r="24" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="221" t="s">
+      <c r="A24" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="222"/>
-      <c r="C24" s="222"/>
-      <c r="D24" s="222"/>
-      <c r="E24" s="222"/>
-      <c r="F24" s="222"/>
-      <c r="G24" s="222"/>
-      <c r="H24" s="222"/>
-      <c r="I24" s="222"/>
-      <c r="J24" s="222"/>
-      <c r="K24" s="222"/>
-      <c r="L24" s="223"/>
-      <c r="M24" s="216" t="str">
+      <c r="B24" s="133"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="133"/>
+      <c r="I24" s="133"/>
+      <c r="J24" s="133"/>
+      <c r="K24" s="133"/>
+      <c r="L24" s="134"/>
+      <c r="M24" s="125" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="N24" s="158"/>
-      <c r="O24" s="158"/>
-      <c r="P24" s="158"/>
-      <c r="Q24" s="158"/>
-      <c r="R24" s="158" t="str">
+      <c r="N24" s="126"/>
+      <c r="O24" s="126"/>
+      <c r="P24" s="126"/>
+      <c r="Q24" s="126"/>
+      <c r="R24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="S24" s="158"/>
-      <c r="T24" s="158"/>
-      <c r="U24" s="158"/>
-      <c r="V24" s="158"/>
-      <c r="W24" s="158" t="str">
+      <c r="S24" s="126"/>
+      <c r="T24" s="126"/>
+      <c r="U24" s="126"/>
+      <c r="V24" s="126"/>
+      <c r="W24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="X24" s="158"/>
-      <c r="Y24" s="158"/>
-      <c r="Z24" s="158"/>
-      <c r="AA24" s="158"/>
-      <c r="AB24" s="158" t="str">
+      <c r="X24" s="126"/>
+      <c r="Y24" s="126"/>
+      <c r="Z24" s="126"/>
+      <c r="AA24" s="126"/>
+      <c r="AB24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AC24" s="158"/>
-      <c r="AD24" s="158"/>
-      <c r="AE24" s="158"/>
-      <c r="AF24" s="158"/>
-      <c r="AG24" s="158" t="str">
+      <c r="AC24" s="126"/>
+      <c r="AD24" s="126"/>
+      <c r="AE24" s="126"/>
+      <c r="AF24" s="126"/>
+      <c r="AG24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AH24" s="158"/>
-      <c r="AI24" s="158"/>
-      <c r="AJ24" s="158"/>
-      <c r="AK24" s="158"/>
-      <c r="AL24" s="158" t="str">
+      <c r="AH24" s="126"/>
+      <c r="AI24" s="126"/>
+      <c r="AJ24" s="126"/>
+      <c r="AK24" s="126"/>
+      <c r="AL24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AM24" s="158"/>
-      <c r="AN24" s="158"/>
-      <c r="AO24" s="158"/>
-      <c r="AP24" s="158"/>
-      <c r="AQ24" s="158" t="str">
+      <c r="AM24" s="126"/>
+      <c r="AN24" s="126"/>
+      <c r="AO24" s="126"/>
+      <c r="AP24" s="126"/>
+      <c r="AQ24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AR24" s="158"/>
-      <c r="AS24" s="158"/>
-      <c r="AT24" s="158"/>
-      <c r="AU24" s="158"/>
-      <c r="AV24" s="158" t="str">
+      <c r="AR24" s="126"/>
+      <c r="AS24" s="126"/>
+      <c r="AT24" s="126"/>
+      <c r="AU24" s="126"/>
+      <c r="AV24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AW24" s="158"/>
-      <c r="AX24" s="158"/>
-      <c r="AY24" s="158"/>
-      <c r="AZ24" s="159"/>
+      <c r="AW24" s="126"/>
+      <c r="AX24" s="126"/>
+      <c r="AY24" s="126"/>
+      <c r="AZ24" s="193"/>
       <c r="BC24" s="29"/>
       <c r="BD24" s="31"/>
       <c r="BE24" s="31"/>
@@ -6627,87 +6631,87 @@
       <c r="BJ24" s="29"/>
     </row>
     <row r="25" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="224" t="s">
+      <c r="A25" s="111" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="225"/>
-      <c r="C25" s="225"/>
-      <c r="D25" s="225"/>
-      <c r="E25" s="225"/>
-      <c r="F25" s="225"/>
-      <c r="G25" s="225"/>
-      <c r="H25" s="225"/>
-      <c r="I25" s="225"/>
-      <c r="J25" s="225"/>
-      <c r="K25" s="225"/>
-      <c r="L25" s="226"/>
-      <c r="M25" s="217" t="str">
+      <c r="B25" s="112"/>
+      <c r="C25" s="112"/>
+      <c r="D25" s="112"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="112"/>
+      <c r="H25" s="112"/>
+      <c r="I25" s="112"/>
+      <c r="J25" s="112"/>
+      <c r="K25" s="112"/>
+      <c r="L25" s="135"/>
+      <c r="M25" s="127" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="N25" s="157"/>
-      <c r="O25" s="157"/>
-      <c r="P25" s="157"/>
-      <c r="Q25" s="157"/>
-      <c r="R25" s="157" t="str">
+      <c r="N25" s="128"/>
+      <c r="O25" s="128"/>
+      <c r="P25" s="128"/>
+      <c r="Q25" s="128"/>
+      <c r="R25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="S25" s="157"/>
-      <c r="T25" s="157"/>
-      <c r="U25" s="157"/>
-      <c r="V25" s="157"/>
-      <c r="W25" s="157" t="str">
+      <c r="S25" s="128"/>
+      <c r="T25" s="128"/>
+      <c r="U25" s="128"/>
+      <c r="V25" s="128"/>
+      <c r="W25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="X25" s="157"/>
-      <c r="Y25" s="157"/>
-      <c r="Z25" s="157"/>
-      <c r="AA25" s="157"/>
-      <c r="AB25" s="157" t="str">
+      <c r="X25" s="128"/>
+      <c r="Y25" s="128"/>
+      <c r="Z25" s="128"/>
+      <c r="AA25" s="128"/>
+      <c r="AB25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AC25" s="157"/>
-      <c r="AD25" s="157"/>
-      <c r="AE25" s="157"/>
-      <c r="AF25" s="157"/>
-      <c r="AG25" s="157" t="str">
+      <c r="AC25" s="128"/>
+      <c r="AD25" s="128"/>
+      <c r="AE25" s="128"/>
+      <c r="AF25" s="128"/>
+      <c r="AG25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AH25" s="157"/>
-      <c r="AI25" s="157"/>
-      <c r="AJ25" s="157"/>
-      <c r="AK25" s="157"/>
-      <c r="AL25" s="157" t="str">
+      <c r="AH25" s="128"/>
+      <c r="AI25" s="128"/>
+      <c r="AJ25" s="128"/>
+      <c r="AK25" s="128"/>
+      <c r="AL25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AM25" s="157"/>
-      <c r="AN25" s="157"/>
-      <c r="AO25" s="157"/>
-      <c r="AP25" s="157"/>
-      <c r="AQ25" s="157" t="str">
+      <c r="AM25" s="128"/>
+      <c r="AN25" s="128"/>
+      <c r="AO25" s="128"/>
+      <c r="AP25" s="128"/>
+      <c r="AQ25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AR25" s="157"/>
-      <c r="AS25" s="157"/>
-      <c r="AT25" s="157"/>
-      <c r="AU25" s="157"/>
-      <c r="AV25" s="157" t="str">
+      <c r="AR25" s="128"/>
+      <c r="AS25" s="128"/>
+      <c r="AT25" s="128"/>
+      <c r="AU25" s="128"/>
+      <c r="AV25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AW25" s="157"/>
-      <c r="AX25" s="157"/>
-      <c r="AY25" s="157"/>
-      <c r="AZ25" s="160"/>
+      <c r="AW25" s="128"/>
+      <c r="AX25" s="128"/>
+      <c r="AY25" s="128"/>
+      <c r="AZ25" s="194"/>
       <c r="BC25" s="29"/>
-      <c r="BD25" s="90"/>
-      <c r="BE25" s="90"/>
+      <c r="BD25" s="229"/>
+      <c r="BE25" s="229"/>
       <c r="BF25" s="29"/>
       <c r="BG25" s="29"/>
       <c r="BH25" s="29"/>
@@ -6715,1150 +6719,1150 @@
       <c r="BJ25" s="29"/>
     </row>
     <row r="26" spans="1:62" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="146"/>
-      <c r="B26" s="146"/>
-      <c r="C26" s="146"/>
-      <c r="D26" s="146"/>
-      <c r="E26" s="146"/>
-      <c r="F26" s="146"/>
-      <c r="G26" s="146"/>
-      <c r="H26" s="146"/>
-      <c r="I26" s="146"/>
-      <c r="J26" s="146"/>
-      <c r="K26" s="146"/>
-      <c r="L26" s="146"/>
-      <c r="M26" s="146"/>
-      <c r="N26" s="146"/>
-      <c r="O26" s="146"/>
-      <c r="P26" s="146"/>
-      <c r="Q26" s="146"/>
-      <c r="R26" s="146"/>
-      <c r="S26" s="146"/>
-      <c r="T26" s="146"/>
-      <c r="U26" s="146"/>
-      <c r="V26" s="146"/>
-      <c r="W26" s="146"/>
-      <c r="X26" s="146"/>
-      <c r="Y26" s="146"/>
-      <c r="Z26" s="146"/>
-      <c r="AA26" s="146"/>
-      <c r="AB26" s="146"/>
-      <c r="AC26" s="146"/>
-      <c r="AD26" s="146"/>
-      <c r="AE26" s="146"/>
-      <c r="AF26" s="146"/>
-      <c r="AG26" s="146"/>
-      <c r="AH26" s="146"/>
-      <c r="AI26" s="146"/>
-      <c r="AJ26" s="146"/>
-      <c r="AK26" s="146"/>
-      <c r="AL26" s="146"/>
-      <c r="AM26" s="146"/>
-      <c r="AN26" s="146"/>
-      <c r="AO26" s="146"/>
-      <c r="AP26" s="146"/>
-      <c r="AQ26" s="146"/>
-      <c r="AR26" s="146"/>
-      <c r="AS26" s="146"/>
-      <c r="AT26" s="146"/>
-      <c r="AU26" s="146"/>
-      <c r="AV26" s="146"/>
-      <c r="AW26" s="146"/>
-      <c r="AX26" s="146"/>
-      <c r="AY26" s="146"/>
-      <c r="AZ26" s="146"/>
+      <c r="A26" s="99"/>
+      <c r="B26" s="99"/>
+      <c r="C26" s="99"/>
+      <c r="D26" s="99"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="99"/>
+      <c r="H26" s="99"/>
+      <c r="I26" s="99"/>
+      <c r="J26" s="99"/>
+      <c r="K26" s="99"/>
+      <c r="L26" s="99"/>
+      <c r="M26" s="99"/>
+      <c r="N26" s="99"/>
+      <c r="O26" s="99"/>
+      <c r="P26" s="99"/>
+      <c r="Q26" s="99"/>
+      <c r="R26" s="99"/>
+      <c r="S26" s="99"/>
+      <c r="T26" s="99"/>
+      <c r="U26" s="99"/>
+      <c r="V26" s="99"/>
+      <c r="W26" s="99"/>
+      <c r="X26" s="99"/>
+      <c r="Y26" s="99"/>
+      <c r="Z26" s="99"/>
+      <c r="AA26" s="99"/>
+      <c r="AB26" s="99"/>
+      <c r="AC26" s="99"/>
+      <c r="AD26" s="99"/>
+      <c r="AE26" s="99"/>
+      <c r="AF26" s="99"/>
+      <c r="AG26" s="99"/>
+      <c r="AH26" s="99"/>
+      <c r="AI26" s="99"/>
+      <c r="AJ26" s="99"/>
+      <c r="AK26" s="99"/>
+      <c r="AL26" s="99"/>
+      <c r="AM26" s="99"/>
+      <c r="AN26" s="99"/>
+      <c r="AO26" s="99"/>
+      <c r="AP26" s="99"/>
+      <c r="AQ26" s="99"/>
+      <c r="AR26" s="99"/>
+      <c r="AS26" s="99"/>
+      <c r="AT26" s="99"/>
+      <c r="AU26" s="99"/>
+      <c r="AV26" s="99"/>
+      <c r="AW26" s="99"/>
+      <c r="AX26" s="99"/>
+      <c r="AY26" s="99"/>
+      <c r="AZ26" s="99"/>
     </row>
     <row r="27" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="189" t="s">
+      <c r="A27" s="100" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="190"/>
-      <c r="C27" s="190"/>
-      <c r="D27" s="190"/>
-      <c r="E27" s="190"/>
-      <c r="F27" s="190"/>
-      <c r="G27" s="190"/>
-      <c r="H27" s="190"/>
-      <c r="I27" s="190"/>
-      <c r="J27" s="190"/>
-      <c r="K27" s="190"/>
-      <c r="L27" s="190"/>
-      <c r="M27" s="190"/>
-      <c r="N27" s="190"/>
-      <c r="O27" s="190"/>
-      <c r="P27" s="190"/>
-      <c r="Q27" s="190"/>
-      <c r="R27" s="190"/>
-      <c r="S27" s="190"/>
-      <c r="T27" s="190"/>
-      <c r="U27" s="190"/>
-      <c r="V27" s="190"/>
-      <c r="W27" s="190"/>
-      <c r="X27" s="190"/>
-      <c r="Y27" s="190"/>
-      <c r="Z27" s="190"/>
-      <c r="AA27" s="190"/>
-      <c r="AB27" s="190"/>
-      <c r="AC27" s="190"/>
-      <c r="AD27" s="190"/>
-      <c r="AE27" s="190"/>
-      <c r="AF27" s="190"/>
-      <c r="AG27" s="190"/>
-      <c r="AH27" s="190"/>
-      <c r="AI27" s="190"/>
-      <c r="AJ27" s="190"/>
-      <c r="AK27" s="190"/>
-      <c r="AL27" s="190"/>
-      <c r="AM27" s="190"/>
-      <c r="AN27" s="190"/>
-      <c r="AO27" s="190"/>
-      <c r="AP27" s="190"/>
-      <c r="AQ27" s="190"/>
-      <c r="AR27" s="190"/>
-      <c r="AS27" s="190"/>
-      <c r="AT27" s="190"/>
-      <c r="AU27" s="190"/>
-      <c r="AV27" s="190"/>
-      <c r="AW27" s="190"/>
-      <c r="AX27" s="190"/>
-      <c r="AY27" s="190"/>
-      <c r="AZ27" s="191"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="101"/>
+      <c r="F27" s="101"/>
+      <c r="G27" s="101"/>
+      <c r="H27" s="101"/>
+      <c r="I27" s="101"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="101"/>
+      <c r="L27" s="101"/>
+      <c r="M27" s="101"/>
+      <c r="N27" s="101"/>
+      <c r="O27" s="101"/>
+      <c r="P27" s="101"/>
+      <c r="Q27" s="101"/>
+      <c r="R27" s="101"/>
+      <c r="S27" s="101"/>
+      <c r="T27" s="101"/>
+      <c r="U27" s="101"/>
+      <c r="V27" s="101"/>
+      <c r="W27" s="101"/>
+      <c r="X27" s="101"/>
+      <c r="Y27" s="101"/>
+      <c r="Z27" s="101"/>
+      <c r="AA27" s="101"/>
+      <c r="AB27" s="101"/>
+      <c r="AC27" s="101"/>
+      <c r="AD27" s="101"/>
+      <c r="AE27" s="101"/>
+      <c r="AF27" s="101"/>
+      <c r="AG27" s="101"/>
+      <c r="AH27" s="101"/>
+      <c r="AI27" s="101"/>
+      <c r="AJ27" s="101"/>
+      <c r="AK27" s="101"/>
+      <c r="AL27" s="101"/>
+      <c r="AM27" s="101"/>
+      <c r="AN27" s="101"/>
+      <c r="AO27" s="101"/>
+      <c r="AP27" s="101"/>
+      <c r="AQ27" s="101"/>
+      <c r="AR27" s="101"/>
+      <c r="AS27" s="101"/>
+      <c r="AT27" s="101"/>
+      <c r="AU27" s="101"/>
+      <c r="AV27" s="101"/>
+      <c r="AW27" s="101"/>
+      <c r="AX27" s="101"/>
+      <c r="AY27" s="101"/>
+      <c r="AZ27" s="102"/>
     </row>
     <row r="28" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="233" t="s">
+      <c r="A28" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="234"/>
-      <c r="C28" s="234"/>
-      <c r="D28" s="234"/>
-      <c r="E28" s="234"/>
-      <c r="F28" s="234"/>
-      <c r="G28" s="234"/>
-      <c r="H28" s="234"/>
-      <c r="I28" s="234"/>
-      <c r="J28" s="234"/>
-      <c r="K28" s="234"/>
-      <c r="L28" s="234"/>
-      <c r="M28" s="234"/>
-      <c r="N28" s="234"/>
-      <c r="O28" s="234"/>
-      <c r="P28" s="234"/>
-      <c r="Q28" s="234"/>
-      <c r="R28" s="234"/>
-      <c r="S28" s="234"/>
-      <c r="T28" s="235" t="s">
+      <c r="B28" s="104"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="104"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="104"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="104"/>
+      <c r="N28" s="104"/>
+      <c r="O28" s="104"/>
+      <c r="P28" s="104"/>
+      <c r="Q28" s="104"/>
+      <c r="R28" s="104"/>
+      <c r="S28" s="104"/>
+      <c r="T28" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="U28" s="235"/>
-      <c r="V28" s="235"/>
-      <c r="W28" s="235"/>
-      <c r="X28" s="235"/>
-      <c r="Y28" s="235"/>
-      <c r="Z28" s="235"/>
-      <c r="AA28" s="234" t="s">
+      <c r="U28" s="105"/>
+      <c r="V28" s="105"/>
+      <c r="W28" s="105"/>
+      <c r="X28" s="105"/>
+      <c r="Y28" s="105"/>
+      <c r="Z28" s="105"/>
+      <c r="AA28" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="AB28" s="234"/>
-      <c r="AC28" s="234"/>
-      <c r="AD28" s="234"/>
-      <c r="AE28" s="234"/>
-      <c r="AF28" s="234"/>
-      <c r="AG28" s="234"/>
-      <c r="AH28" s="234"/>
-      <c r="AI28" s="234"/>
-      <c r="AJ28" s="234"/>
-      <c r="AK28" s="234"/>
-      <c r="AL28" s="234"/>
-      <c r="AM28" s="234"/>
-      <c r="AN28" s="234"/>
-      <c r="AO28" s="234"/>
-      <c r="AP28" s="234"/>
-      <c r="AQ28" s="234"/>
-      <c r="AR28" s="234"/>
-      <c r="AS28" s="234"/>
-      <c r="AT28" s="235" t="s">
+      <c r="AB28" s="104"/>
+      <c r="AC28" s="104"/>
+      <c r="AD28" s="104"/>
+      <c r="AE28" s="104"/>
+      <c r="AF28" s="104"/>
+      <c r="AG28" s="104"/>
+      <c r="AH28" s="104"/>
+      <c r="AI28" s="104"/>
+      <c r="AJ28" s="104"/>
+      <c r="AK28" s="104"/>
+      <c r="AL28" s="104"/>
+      <c r="AM28" s="104"/>
+      <c r="AN28" s="104"/>
+      <c r="AO28" s="104"/>
+      <c r="AP28" s="104"/>
+      <c r="AQ28" s="104"/>
+      <c r="AR28" s="104"/>
+      <c r="AS28" s="104"/>
+      <c r="AT28" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="AU28" s="235"/>
-      <c r="AV28" s="235"/>
-      <c r="AW28" s="235"/>
-      <c r="AX28" s="235"/>
-      <c r="AY28" s="235"/>
-      <c r="AZ28" s="236"/>
+      <c r="AU28" s="105"/>
+      <c r="AV28" s="105"/>
+      <c r="AW28" s="105"/>
+      <c r="AX28" s="105"/>
+      <c r="AY28" s="105"/>
+      <c r="AZ28" s="106"/>
     </row>
     <row r="29" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="237" t="s">
+      <c r="A29" s="107" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="238"/>
-      <c r="C29" s="238"/>
-      <c r="D29" s="238"/>
-      <c r="E29" s="238"/>
-      <c r="F29" s="238"/>
-      <c r="G29" s="238"/>
-      <c r="H29" s="238"/>
-      <c r="I29" s="238"/>
-      <c r="J29" s="238"/>
-      <c r="K29" s="238"/>
-      <c r="L29" s="238"/>
-      <c r="M29" s="238"/>
-      <c r="N29" s="238"/>
-      <c r="O29" s="238"/>
-      <c r="P29" s="238"/>
-      <c r="Q29" s="238"/>
-      <c r="R29" s="238"/>
-      <c r="S29" s="238"/>
-      <c r="T29" s="239"/>
-      <c r="U29" s="239"/>
-      <c r="V29" s="239"/>
-      <c r="W29" s="239"/>
-      <c r="X29" s="239"/>
-      <c r="Y29" s="239"/>
-      <c r="Z29" s="239"/>
-      <c r="AA29" s="238" t="s">
+      <c r="B29" s="108"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="108"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="108"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="108"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="108"/>
+      <c r="K29" s="108"/>
+      <c r="L29" s="108"/>
+      <c r="M29" s="108"/>
+      <c r="N29" s="108"/>
+      <c r="O29" s="108"/>
+      <c r="P29" s="108"/>
+      <c r="Q29" s="108"/>
+      <c r="R29" s="108"/>
+      <c r="S29" s="108"/>
+      <c r="T29" s="109"/>
+      <c r="U29" s="109"/>
+      <c r="V29" s="109"/>
+      <c r="W29" s="109"/>
+      <c r="X29" s="109"/>
+      <c r="Y29" s="109"/>
+      <c r="Z29" s="109"/>
+      <c r="AA29" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="AB29" s="238"/>
-      <c r="AC29" s="238"/>
-      <c r="AD29" s="238"/>
-      <c r="AE29" s="238"/>
-      <c r="AF29" s="238"/>
-      <c r="AG29" s="238"/>
-      <c r="AH29" s="238"/>
-      <c r="AI29" s="238"/>
-      <c r="AJ29" s="238"/>
-      <c r="AK29" s="238"/>
-      <c r="AL29" s="238"/>
-      <c r="AM29" s="238"/>
-      <c r="AN29" s="238"/>
-      <c r="AO29" s="238"/>
-      <c r="AP29" s="238"/>
-      <c r="AQ29" s="238"/>
-      <c r="AR29" s="238"/>
-      <c r="AS29" s="238"/>
-      <c r="AT29" s="239"/>
-      <c r="AU29" s="239"/>
-      <c r="AV29" s="239"/>
-      <c r="AW29" s="239"/>
-      <c r="AX29" s="239"/>
-      <c r="AY29" s="239"/>
-      <c r="AZ29" s="240"/>
+      <c r="AB29" s="108"/>
+      <c r="AC29" s="108"/>
+      <c r="AD29" s="108"/>
+      <c r="AE29" s="108"/>
+      <c r="AF29" s="108"/>
+      <c r="AG29" s="108"/>
+      <c r="AH29" s="108"/>
+      <c r="AI29" s="108"/>
+      <c r="AJ29" s="108"/>
+      <c r="AK29" s="108"/>
+      <c r="AL29" s="108"/>
+      <c r="AM29" s="108"/>
+      <c r="AN29" s="108"/>
+      <c r="AO29" s="108"/>
+      <c r="AP29" s="108"/>
+      <c r="AQ29" s="108"/>
+      <c r="AR29" s="108"/>
+      <c r="AS29" s="108"/>
+      <c r="AT29" s="109"/>
+      <c r="AU29" s="109"/>
+      <c r="AV29" s="109"/>
+      <c r="AW29" s="109"/>
+      <c r="AX29" s="109"/>
+      <c r="AY29" s="109"/>
+      <c r="AZ29" s="110"/>
     </row>
     <row r="30" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="237" t="s">
+      <c r="A30" s="107" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="238"/>
-      <c r="C30" s="238"/>
-      <c r="D30" s="238"/>
-      <c r="E30" s="238"/>
-      <c r="F30" s="238"/>
-      <c r="G30" s="238"/>
-      <c r="H30" s="238"/>
-      <c r="I30" s="238"/>
-      <c r="J30" s="238"/>
-      <c r="K30" s="238"/>
-      <c r="L30" s="238"/>
-      <c r="M30" s="238"/>
-      <c r="N30" s="238"/>
-      <c r="O30" s="238"/>
-      <c r="P30" s="238"/>
-      <c r="Q30" s="238"/>
-      <c r="R30" s="238"/>
-      <c r="S30" s="238"/>
-      <c r="T30" s="239"/>
-      <c r="U30" s="239"/>
-      <c r="V30" s="239"/>
-      <c r="W30" s="239"/>
-      <c r="X30" s="239"/>
-      <c r="Y30" s="239"/>
-      <c r="Z30" s="239"/>
-      <c r="AA30" s="238" t="s">
+      <c r="B30" s="108"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="108"/>
+      <c r="I30" s="108"/>
+      <c r="J30" s="108"/>
+      <c r="K30" s="108"/>
+      <c r="L30" s="108"/>
+      <c r="M30" s="108"/>
+      <c r="N30" s="108"/>
+      <c r="O30" s="108"/>
+      <c r="P30" s="108"/>
+      <c r="Q30" s="108"/>
+      <c r="R30" s="108"/>
+      <c r="S30" s="108"/>
+      <c r="T30" s="109"/>
+      <c r="U30" s="109"/>
+      <c r="V30" s="109"/>
+      <c r="W30" s="109"/>
+      <c r="X30" s="109"/>
+      <c r="Y30" s="109"/>
+      <c r="Z30" s="109"/>
+      <c r="AA30" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="AB30" s="238"/>
-      <c r="AC30" s="238"/>
-      <c r="AD30" s="238"/>
-      <c r="AE30" s="238"/>
-      <c r="AF30" s="238"/>
-      <c r="AG30" s="238"/>
-      <c r="AH30" s="238"/>
-      <c r="AI30" s="238"/>
-      <c r="AJ30" s="238"/>
-      <c r="AK30" s="238"/>
-      <c r="AL30" s="238"/>
-      <c r="AM30" s="238"/>
-      <c r="AN30" s="238"/>
-      <c r="AO30" s="238"/>
-      <c r="AP30" s="238"/>
-      <c r="AQ30" s="238"/>
-      <c r="AR30" s="238"/>
-      <c r="AS30" s="238"/>
-      <c r="AT30" s="239"/>
-      <c r="AU30" s="239"/>
-      <c r="AV30" s="239"/>
-      <c r="AW30" s="239"/>
-      <c r="AX30" s="239"/>
-      <c r="AY30" s="239"/>
-      <c r="AZ30" s="240"/>
+      <c r="AB30" s="108"/>
+      <c r="AC30" s="108"/>
+      <c r="AD30" s="108"/>
+      <c r="AE30" s="108"/>
+      <c r="AF30" s="108"/>
+      <c r="AG30" s="108"/>
+      <c r="AH30" s="108"/>
+      <c r="AI30" s="108"/>
+      <c r="AJ30" s="108"/>
+      <c r="AK30" s="108"/>
+      <c r="AL30" s="108"/>
+      <c r="AM30" s="108"/>
+      <c r="AN30" s="108"/>
+      <c r="AO30" s="108"/>
+      <c r="AP30" s="108"/>
+      <c r="AQ30" s="108"/>
+      <c r="AR30" s="108"/>
+      <c r="AS30" s="108"/>
+      <c r="AT30" s="109"/>
+      <c r="AU30" s="109"/>
+      <c r="AV30" s="109"/>
+      <c r="AW30" s="109"/>
+      <c r="AX30" s="109"/>
+      <c r="AY30" s="109"/>
+      <c r="AZ30" s="110"/>
     </row>
     <row r="31" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="224" t="s">
+      <c r="A31" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="225"/>
-      <c r="C31" s="225"/>
-      <c r="D31" s="225"/>
-      <c r="E31" s="225"/>
-      <c r="F31" s="225"/>
-      <c r="G31" s="225"/>
-      <c r="H31" s="225"/>
-      <c r="I31" s="225"/>
-      <c r="J31" s="225"/>
-      <c r="K31" s="225"/>
-      <c r="L31" s="225"/>
-      <c r="M31" s="225"/>
-      <c r="N31" s="225"/>
-      <c r="O31" s="225"/>
-      <c r="P31" s="225"/>
-      <c r="Q31" s="225"/>
-      <c r="R31" s="225"/>
-      <c r="S31" s="225"/>
-      <c r="T31" s="241"/>
-      <c r="U31" s="241"/>
-      <c r="V31" s="241"/>
-      <c r="W31" s="241"/>
-      <c r="X31" s="241"/>
-      <c r="Y31" s="241"/>
-      <c r="Z31" s="241"/>
-      <c r="AA31" s="225" t="s">
+      <c r="B31" s="112"/>
+      <c r="C31" s="112"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="112"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="112"/>
+      <c r="J31" s="112"/>
+      <c r="K31" s="112"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="112"/>
+      <c r="R31" s="112"/>
+      <c r="S31" s="112"/>
+      <c r="T31" s="113"/>
+      <c r="U31" s="113"/>
+      <c r="V31" s="113"/>
+      <c r="W31" s="113"/>
+      <c r="X31" s="113"/>
+      <c r="Y31" s="113"/>
+      <c r="Z31" s="113"/>
+      <c r="AA31" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="AB31" s="225"/>
-      <c r="AC31" s="225"/>
-      <c r="AD31" s="225"/>
-      <c r="AE31" s="225"/>
-      <c r="AF31" s="225"/>
-      <c r="AG31" s="225"/>
-      <c r="AH31" s="225"/>
-      <c r="AI31" s="225"/>
-      <c r="AJ31" s="225"/>
-      <c r="AK31" s="225"/>
-      <c r="AL31" s="225"/>
-      <c r="AM31" s="225"/>
-      <c r="AN31" s="225"/>
-      <c r="AO31" s="225"/>
-      <c r="AP31" s="225"/>
-      <c r="AQ31" s="225"/>
-      <c r="AR31" s="225"/>
-      <c r="AS31" s="225"/>
-      <c r="AT31" s="241"/>
-      <c r="AU31" s="241"/>
-      <c r="AV31" s="241"/>
-      <c r="AW31" s="241"/>
-      <c r="AX31" s="241"/>
-      <c r="AY31" s="241"/>
-      <c r="AZ31" s="242"/>
+      <c r="AB31" s="112"/>
+      <c r="AC31" s="112"/>
+      <c r="AD31" s="112"/>
+      <c r="AE31" s="112"/>
+      <c r="AF31" s="112"/>
+      <c r="AG31" s="112"/>
+      <c r="AH31" s="112"/>
+      <c r="AI31" s="112"/>
+      <c r="AJ31" s="112"/>
+      <c r="AK31" s="112"/>
+      <c r="AL31" s="112"/>
+      <c r="AM31" s="112"/>
+      <c r="AN31" s="112"/>
+      <c r="AO31" s="112"/>
+      <c r="AP31" s="112"/>
+      <c r="AQ31" s="112"/>
+      <c r="AR31" s="112"/>
+      <c r="AS31" s="112"/>
+      <c r="AT31" s="113"/>
+      <c r="AU31" s="113"/>
+      <c r="AV31" s="113"/>
+      <c r="AW31" s="113"/>
+      <c r="AX31" s="113"/>
+      <c r="AY31" s="113"/>
+      <c r="AZ31" s="114"/>
     </row>
     <row r="32" spans="1:62" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="232"/>
-      <c r="B32" s="232"/>
-      <c r="C32" s="232"/>
-      <c r="D32" s="232"/>
-      <c r="E32" s="232"/>
-      <c r="F32" s="232"/>
-      <c r="G32" s="232"/>
-      <c r="H32" s="232"/>
-      <c r="I32" s="232"/>
-      <c r="J32" s="232"/>
-      <c r="K32" s="232"/>
-      <c r="L32" s="232"/>
-      <c r="M32" s="232"/>
-      <c r="N32" s="232"/>
-      <c r="O32" s="232"/>
-      <c r="P32" s="232"/>
-      <c r="Q32" s="232"/>
-      <c r="R32" s="232"/>
-      <c r="S32" s="232"/>
-      <c r="T32" s="232"/>
-      <c r="U32" s="232"/>
-      <c r="V32" s="232"/>
-      <c r="W32" s="232"/>
-      <c r="X32" s="232"/>
-      <c r="Y32" s="232"/>
-      <c r="Z32" s="232"/>
-      <c r="AA32" s="232"/>
-      <c r="AB32" s="232"/>
-      <c r="AC32" s="232"/>
-      <c r="AD32" s="232"/>
-      <c r="AE32" s="232"/>
-      <c r="AF32" s="232"/>
-      <c r="AG32" s="232"/>
-      <c r="AH32" s="232"/>
-      <c r="AI32" s="232"/>
-      <c r="AJ32" s="232"/>
-      <c r="AK32" s="232"/>
-      <c r="AL32" s="232"/>
-      <c r="AM32" s="232"/>
-      <c r="AN32" s="232"/>
-      <c r="AO32" s="232"/>
-      <c r="AP32" s="232"/>
-      <c r="AQ32" s="232"/>
-      <c r="AR32" s="232"/>
-      <c r="AS32" s="232"/>
-      <c r="AT32" s="232"/>
-      <c r="AU32" s="232"/>
-      <c r="AV32" s="232"/>
-      <c r="AW32" s="232"/>
-      <c r="AX32" s="232"/>
-      <c r="AY32" s="232"/>
-      <c r="AZ32" s="232"/>
+      <c r="A32" s="98"/>
+      <c r="B32" s="98"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="98"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="98"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="98"/>
+      <c r="N32" s="98"/>
+      <c r="O32" s="98"/>
+      <c r="P32" s="98"/>
+      <c r="Q32" s="98"/>
+      <c r="R32" s="98"/>
+      <c r="S32" s="98"/>
+      <c r="T32" s="98"/>
+      <c r="U32" s="98"/>
+      <c r="V32" s="98"/>
+      <c r="W32" s="98"/>
+      <c r="X32" s="98"/>
+      <c r="Y32" s="98"/>
+      <c r="Z32" s="98"/>
+      <c r="AA32" s="98"/>
+      <c r="AB32" s="98"/>
+      <c r="AC32" s="98"/>
+      <c r="AD32" s="98"/>
+      <c r="AE32" s="98"/>
+      <c r="AF32" s="98"/>
+      <c r="AG32" s="98"/>
+      <c r="AH32" s="98"/>
+      <c r="AI32" s="98"/>
+      <c r="AJ32" s="98"/>
+      <c r="AK32" s="98"/>
+      <c r="AL32" s="98"/>
+      <c r="AM32" s="98"/>
+      <c r="AN32" s="98"/>
+      <c r="AO32" s="98"/>
+      <c r="AP32" s="98"/>
+      <c r="AQ32" s="98"/>
+      <c r="AR32" s="98"/>
+      <c r="AS32" s="98"/>
+      <c r="AT32" s="98"/>
+      <c r="AU32" s="98"/>
+      <c r="AV32" s="98"/>
+      <c r="AW32" s="98"/>
+      <c r="AX32" s="98"/>
+      <c r="AY32" s="98"/>
+      <c r="AZ32" s="98"/>
     </row>
     <row r="33" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="131" t="s">
+      <c r="A33" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="132"/>
-      <c r="C33" s="132"/>
-      <c r="D33" s="132"/>
-      <c r="E33" s="132"/>
-      <c r="F33" s="132"/>
-      <c r="G33" s="132"/>
-      <c r="H33" s="132"/>
-      <c r="I33" s="132"/>
-      <c r="J33" s="132"/>
-      <c r="K33" s="132"/>
-      <c r="L33" s="132"/>
-      <c r="M33" s="132"/>
-      <c r="N33" s="132"/>
-      <c r="O33" s="132"/>
-      <c r="P33" s="132"/>
-      <c r="Q33" s="132"/>
-      <c r="R33" s="133"/>
-      <c r="S33" s="98" t="s">
+      <c r="B33" s="206"/>
+      <c r="C33" s="206"/>
+      <c r="D33" s="206"/>
+      <c r="E33" s="206"/>
+      <c r="F33" s="206"/>
+      <c r="G33" s="206"/>
+      <c r="H33" s="206"/>
+      <c r="I33" s="206"/>
+      <c r="J33" s="206"/>
+      <c r="K33" s="206"/>
+      <c r="L33" s="206"/>
+      <c r="M33" s="206"/>
+      <c r="N33" s="206"/>
+      <c r="O33" s="206"/>
+      <c r="P33" s="206"/>
+      <c r="Q33" s="206"/>
+      <c r="R33" s="207"/>
+      <c r="S33" s="196" t="s">
         <v>56</v>
       </c>
-      <c r="T33" s="99"/>
-      <c r="U33" s="99"/>
-      <c r="V33" s="99"/>
-      <c r="W33" s="99"/>
-      <c r="X33" s="99"/>
-      <c r="Y33" s="99"/>
-      <c r="Z33" s="99"/>
-      <c r="AA33" s="99"/>
-      <c r="AB33" s="99"/>
-      <c r="AC33" s="99"/>
-      <c r="AD33" s="99"/>
-      <c r="AE33" s="99"/>
-      <c r="AF33" s="99"/>
-      <c r="AG33" s="123"/>
-      <c r="AH33" s="98" t="s">
+      <c r="T33" s="197"/>
+      <c r="U33" s="197"/>
+      <c r="V33" s="197"/>
+      <c r="W33" s="197"/>
+      <c r="X33" s="197"/>
+      <c r="Y33" s="197"/>
+      <c r="Z33" s="197"/>
+      <c r="AA33" s="197"/>
+      <c r="AB33" s="197"/>
+      <c r="AC33" s="197"/>
+      <c r="AD33" s="197"/>
+      <c r="AE33" s="197"/>
+      <c r="AF33" s="197"/>
+      <c r="AG33" s="198"/>
+      <c r="AH33" s="196" t="s">
         <v>57</v>
       </c>
-      <c r="AI33" s="99"/>
-      <c r="AJ33" s="99"/>
-      <c r="AK33" s="99"/>
-      <c r="AL33" s="99"/>
-      <c r="AM33" s="99"/>
-      <c r="AN33" s="99"/>
-      <c r="AO33" s="99"/>
-      <c r="AP33" s="99"/>
-      <c r="AQ33" s="99"/>
-      <c r="AR33" s="99"/>
-      <c r="AS33" s="99"/>
-      <c r="AT33" s="99"/>
-      <c r="AU33" s="99"/>
-      <c r="AV33" s="99"/>
-      <c r="AW33" s="99"/>
-      <c r="AX33" s="99"/>
-      <c r="AY33" s="99"/>
-      <c r="AZ33" s="100"/>
+      <c r="AI33" s="197"/>
+      <c r="AJ33" s="197"/>
+      <c r="AK33" s="197"/>
+      <c r="AL33" s="197"/>
+      <c r="AM33" s="197"/>
+      <c r="AN33" s="197"/>
+      <c r="AO33" s="197"/>
+      <c r="AP33" s="197"/>
+      <c r="AQ33" s="197"/>
+      <c r="AR33" s="197"/>
+      <c r="AS33" s="197"/>
+      <c r="AT33" s="197"/>
+      <c r="AU33" s="197"/>
+      <c r="AV33" s="197"/>
+      <c r="AW33" s="197"/>
+      <c r="AX33" s="197"/>
+      <c r="AY33" s="197"/>
+      <c r="AZ33" s="231"/>
     </row>
     <row r="34" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="134"/>
-      <c r="B34" s="135"/>
-      <c r="C34" s="135"/>
-      <c r="D34" s="135"/>
-      <c r="E34" s="135"/>
-      <c r="F34" s="135"/>
-      <c r="G34" s="135"/>
-      <c r="H34" s="135"/>
-      <c r="I34" s="135"/>
-      <c r="J34" s="135"/>
-      <c r="K34" s="135"/>
-      <c r="L34" s="135"/>
-      <c r="M34" s="135"/>
-      <c r="N34" s="135"/>
-      <c r="O34" s="135"/>
-      <c r="P34" s="135"/>
-      <c r="Q34" s="135"/>
-      <c r="R34" s="136"/>
-      <c r="S34" s="101"/>
-      <c r="T34" s="102"/>
-      <c r="U34" s="102"/>
-      <c r="V34" s="102"/>
-      <c r="W34" s="102"/>
-      <c r="X34" s="102"/>
-      <c r="Y34" s="102"/>
-      <c r="Z34" s="102"/>
-      <c r="AA34" s="102"/>
-      <c r="AB34" s="102"/>
-      <c r="AC34" s="102"/>
-      <c r="AD34" s="102"/>
-      <c r="AE34" s="102"/>
-      <c r="AF34" s="102"/>
-      <c r="AG34" s="124"/>
-      <c r="AH34" s="101"/>
-      <c r="AI34" s="102"/>
-      <c r="AJ34" s="102"/>
-      <c r="AK34" s="102"/>
-      <c r="AL34" s="102"/>
-      <c r="AM34" s="102"/>
-      <c r="AN34" s="102"/>
-      <c r="AO34" s="102"/>
-      <c r="AP34" s="102"/>
-      <c r="AQ34" s="102"/>
-      <c r="AR34" s="102"/>
-      <c r="AS34" s="102"/>
-      <c r="AT34" s="102"/>
-      <c r="AU34" s="102"/>
-      <c r="AV34" s="102"/>
-      <c r="AW34" s="102"/>
-      <c r="AX34" s="102"/>
-      <c r="AY34" s="102"/>
-      <c r="AZ34" s="103"/>
+      <c r="A34" s="208"/>
+      <c r="B34" s="209"/>
+      <c r="C34" s="209"/>
+      <c r="D34" s="209"/>
+      <c r="E34" s="209"/>
+      <c r="F34" s="209"/>
+      <c r="G34" s="209"/>
+      <c r="H34" s="209"/>
+      <c r="I34" s="209"/>
+      <c r="J34" s="209"/>
+      <c r="K34" s="209"/>
+      <c r="L34" s="209"/>
+      <c r="M34" s="209"/>
+      <c r="N34" s="209"/>
+      <c r="O34" s="209"/>
+      <c r="P34" s="209"/>
+      <c r="Q34" s="209"/>
+      <c r="R34" s="210"/>
+      <c r="S34" s="199"/>
+      <c r="T34" s="200"/>
+      <c r="U34" s="200"/>
+      <c r="V34" s="200"/>
+      <c r="W34" s="200"/>
+      <c r="X34" s="200"/>
+      <c r="Y34" s="200"/>
+      <c r="Z34" s="200"/>
+      <c r="AA34" s="200"/>
+      <c r="AB34" s="200"/>
+      <c r="AC34" s="200"/>
+      <c r="AD34" s="200"/>
+      <c r="AE34" s="200"/>
+      <c r="AF34" s="200"/>
+      <c r="AG34" s="201"/>
+      <c r="AH34" s="199"/>
+      <c r="AI34" s="200"/>
+      <c r="AJ34" s="200"/>
+      <c r="AK34" s="200"/>
+      <c r="AL34" s="200"/>
+      <c r="AM34" s="200"/>
+      <c r="AN34" s="200"/>
+      <c r="AO34" s="200"/>
+      <c r="AP34" s="200"/>
+      <c r="AQ34" s="200"/>
+      <c r="AR34" s="200"/>
+      <c r="AS34" s="200"/>
+      <c r="AT34" s="200"/>
+      <c r="AU34" s="200"/>
+      <c r="AV34" s="200"/>
+      <c r="AW34" s="200"/>
+      <c r="AX34" s="200"/>
+      <c r="AY34" s="200"/>
+      <c r="AZ34" s="232"/>
     </row>
     <row r="35" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="125" t="s">
+      <c r="A35" s="183" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="126"/>
-      <c r="C35" s="126"/>
-      <c r="D35" s="126"/>
-      <c r="E35" s="126"/>
-      <c r="F35" s="126"/>
-      <c r="G35" s="126"/>
-      <c r="H35" s="126"/>
-      <c r="I35" s="126"/>
-      <c r="J35" s="126"/>
-      <c r="K35" s="126"/>
-      <c r="L35" s="126"/>
-      <c r="M35" s="126"/>
-      <c r="N35" s="126"/>
-      <c r="O35" s="126"/>
-      <c r="P35" s="126"/>
-      <c r="Q35" s="126"/>
-      <c r="R35" s="127"/>
-      <c r="S35" s="128" t="s">
+      <c r="B35" s="184"/>
+      <c r="C35" s="184"/>
+      <c r="D35" s="184"/>
+      <c r="E35" s="184"/>
+      <c r="F35" s="184"/>
+      <c r="G35" s="184"/>
+      <c r="H35" s="184"/>
+      <c r="I35" s="184"/>
+      <c r="J35" s="184"/>
+      <c r="K35" s="184"/>
+      <c r="L35" s="184"/>
+      <c r="M35" s="184"/>
+      <c r="N35" s="184"/>
+      <c r="O35" s="184"/>
+      <c r="P35" s="184"/>
+      <c r="Q35" s="184"/>
+      <c r="R35" s="185"/>
+      <c r="S35" s="189" t="s">
         <v>59</v>
       </c>
-      <c r="T35" s="129"/>
-      <c r="U35" s="129"/>
-      <c r="V35" s="129"/>
-      <c r="W35" s="129"/>
-      <c r="X35" s="129"/>
-      <c r="Y35" s="129"/>
-      <c r="Z35" s="129"/>
-      <c r="AA35" s="129"/>
-      <c r="AB35" s="129"/>
-      <c r="AC35" s="129"/>
-      <c r="AD35" s="129"/>
-      <c r="AE35" s="129"/>
-      <c r="AF35" s="129"/>
-      <c r="AG35" s="130"/>
-      <c r="AH35" s="95" t="s">
+      <c r="T35" s="190"/>
+      <c r="U35" s="190"/>
+      <c r="V35" s="190"/>
+      <c r="W35" s="190"/>
+      <c r="X35" s="190"/>
+      <c r="Y35" s="190"/>
+      <c r="Z35" s="190"/>
+      <c r="AA35" s="190"/>
+      <c r="AB35" s="190"/>
+      <c r="AC35" s="190"/>
+      <c r="AD35" s="190"/>
+      <c r="AE35" s="190"/>
+      <c r="AF35" s="190"/>
+      <c r="AG35" s="191"/>
+      <c r="AH35" s="202" t="s">
         <v>60</v>
       </c>
-      <c r="AI35" s="96"/>
-      <c r="AJ35" s="96"/>
-      <c r="AK35" s="96"/>
-      <c r="AL35" s="96"/>
-      <c r="AM35" s="96"/>
-      <c r="AN35" s="96"/>
-      <c r="AO35" s="96"/>
-      <c r="AP35" s="96"/>
-      <c r="AQ35" s="96"/>
-      <c r="AR35" s="96"/>
-      <c r="AS35" s="96"/>
-      <c r="AT35" s="96"/>
-      <c r="AU35" s="96"/>
-      <c r="AV35" s="96"/>
-      <c r="AW35" s="96"/>
-      <c r="AX35" s="96"/>
-      <c r="AY35" s="96"/>
-      <c r="AZ35" s="97"/>
+      <c r="AI35" s="203"/>
+      <c r="AJ35" s="203"/>
+      <c r="AK35" s="203"/>
+      <c r="AL35" s="203"/>
+      <c r="AM35" s="203"/>
+      <c r="AN35" s="203"/>
+      <c r="AO35" s="203"/>
+      <c r="AP35" s="203"/>
+      <c r="AQ35" s="203"/>
+      <c r="AR35" s="203"/>
+      <c r="AS35" s="203"/>
+      <c r="AT35" s="203"/>
+      <c r="AU35" s="203"/>
+      <c r="AV35" s="203"/>
+      <c r="AW35" s="203"/>
+      <c r="AX35" s="203"/>
+      <c r="AY35" s="203"/>
+      <c r="AZ35" s="204"/>
     </row>
     <row r="36" spans="1:52" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="125" t="s">
+      <c r="A36" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="126"/>
-      <c r="C36" s="126"/>
-      <c r="D36" s="126"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="126"/>
-      <c r="G36" s="126"/>
-      <c r="H36" s="126"/>
-      <c r="I36" s="126"/>
-      <c r="J36" s="126"/>
-      <c r="K36" s="126"/>
-      <c r="L36" s="126"/>
-      <c r="M36" s="126"/>
-      <c r="N36" s="126"/>
-      <c r="O36" s="126"/>
-      <c r="P36" s="126"/>
-      <c r="Q36" s="126"/>
-      <c r="R36" s="127"/>
-      <c r="S36" s="128" t="s">
+      <c r="B36" s="184"/>
+      <c r="C36" s="184"/>
+      <c r="D36" s="184"/>
+      <c r="E36" s="184"/>
+      <c r="F36" s="184"/>
+      <c r="G36" s="184"/>
+      <c r="H36" s="184"/>
+      <c r="I36" s="184"/>
+      <c r="J36" s="184"/>
+      <c r="K36" s="184"/>
+      <c r="L36" s="184"/>
+      <c r="M36" s="184"/>
+      <c r="N36" s="184"/>
+      <c r="O36" s="184"/>
+      <c r="P36" s="184"/>
+      <c r="Q36" s="184"/>
+      <c r="R36" s="185"/>
+      <c r="S36" s="189" t="s">
         <v>62</v>
       </c>
-      <c r="T36" s="129"/>
-      <c r="U36" s="129"/>
-      <c r="V36" s="129"/>
-      <c r="W36" s="129"/>
-      <c r="X36" s="129"/>
-      <c r="Y36" s="129"/>
-      <c r="Z36" s="129"/>
-      <c r="AA36" s="129"/>
-      <c r="AB36" s="129"/>
-      <c r="AC36" s="129"/>
-      <c r="AD36" s="129"/>
-      <c r="AE36" s="129"/>
-      <c r="AF36" s="129"/>
-      <c r="AG36" s="130"/>
-      <c r="AH36" s="95" t="s">
+      <c r="T36" s="190"/>
+      <c r="U36" s="190"/>
+      <c r="V36" s="190"/>
+      <c r="W36" s="190"/>
+      <c r="X36" s="190"/>
+      <c r="Y36" s="190"/>
+      <c r="Z36" s="190"/>
+      <c r="AA36" s="190"/>
+      <c r="AB36" s="190"/>
+      <c r="AC36" s="190"/>
+      <c r="AD36" s="190"/>
+      <c r="AE36" s="190"/>
+      <c r="AF36" s="190"/>
+      <c r="AG36" s="191"/>
+      <c r="AH36" s="202" t="s">
         <v>63</v>
       </c>
-      <c r="AI36" s="96"/>
-      <c r="AJ36" s="96"/>
-      <c r="AK36" s="96"/>
-      <c r="AL36" s="96"/>
-      <c r="AM36" s="96"/>
-      <c r="AN36" s="96"/>
-      <c r="AO36" s="96"/>
-      <c r="AP36" s="96"/>
-      <c r="AQ36" s="96"/>
-      <c r="AR36" s="96"/>
-      <c r="AS36" s="96"/>
-      <c r="AT36" s="96"/>
-      <c r="AU36" s="96"/>
-      <c r="AV36" s="96"/>
-      <c r="AW36" s="96"/>
-      <c r="AX36" s="96"/>
-      <c r="AY36" s="96"/>
-      <c r="AZ36" s="97"/>
+      <c r="AI36" s="203"/>
+      <c r="AJ36" s="203"/>
+      <c r="AK36" s="203"/>
+      <c r="AL36" s="203"/>
+      <c r="AM36" s="203"/>
+      <c r="AN36" s="203"/>
+      <c r="AO36" s="203"/>
+      <c r="AP36" s="203"/>
+      <c r="AQ36" s="203"/>
+      <c r="AR36" s="203"/>
+      <c r="AS36" s="203"/>
+      <c r="AT36" s="203"/>
+      <c r="AU36" s="203"/>
+      <c r="AV36" s="203"/>
+      <c r="AW36" s="203"/>
+      <c r="AX36" s="203"/>
+      <c r="AY36" s="203"/>
+      <c r="AZ36" s="204"/>
     </row>
     <row r="37" spans="1:52" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="125" t="s">
+      <c r="A37" s="183" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="126"/>
-      <c r="C37" s="126"/>
-      <c r="D37" s="126"/>
-      <c r="E37" s="126"/>
-      <c r="F37" s="126"/>
-      <c r="G37" s="126"/>
-      <c r="H37" s="126"/>
-      <c r="I37" s="126"/>
-      <c r="J37" s="126"/>
-      <c r="K37" s="126"/>
-      <c r="L37" s="126"/>
-      <c r="M37" s="126"/>
-      <c r="N37" s="126"/>
-      <c r="O37" s="126"/>
-      <c r="P37" s="126"/>
-      <c r="Q37" s="126"/>
-      <c r="R37" s="127"/>
-      <c r="S37" s="128" t="s">
+      <c r="B37" s="184"/>
+      <c r="C37" s="184"/>
+      <c r="D37" s="184"/>
+      <c r="E37" s="184"/>
+      <c r="F37" s="184"/>
+      <c r="G37" s="184"/>
+      <c r="H37" s="184"/>
+      <c r="I37" s="184"/>
+      <c r="J37" s="184"/>
+      <c r="K37" s="184"/>
+      <c r="L37" s="184"/>
+      <c r="M37" s="184"/>
+      <c r="N37" s="184"/>
+      <c r="O37" s="184"/>
+      <c r="P37" s="184"/>
+      <c r="Q37" s="184"/>
+      <c r="R37" s="185"/>
+      <c r="S37" s="189" t="s">
         <v>65</v>
       </c>
-      <c r="T37" s="129"/>
-      <c r="U37" s="129"/>
-      <c r="V37" s="129"/>
-      <c r="W37" s="129"/>
-      <c r="X37" s="129"/>
-      <c r="Y37" s="129"/>
-      <c r="Z37" s="129"/>
-      <c r="AA37" s="129"/>
-      <c r="AB37" s="129"/>
-      <c r="AC37" s="129"/>
-      <c r="AD37" s="129"/>
-      <c r="AE37" s="129"/>
-      <c r="AF37" s="129"/>
-      <c r="AG37" s="130"/>
-      <c r="AH37" s="95" t="s">
+      <c r="T37" s="190"/>
+      <c r="U37" s="190"/>
+      <c r="V37" s="190"/>
+      <c r="W37" s="190"/>
+      <c r="X37" s="190"/>
+      <c r="Y37" s="190"/>
+      <c r="Z37" s="190"/>
+      <c r="AA37" s="190"/>
+      <c r="AB37" s="190"/>
+      <c r="AC37" s="190"/>
+      <c r="AD37" s="190"/>
+      <c r="AE37" s="190"/>
+      <c r="AF37" s="190"/>
+      <c r="AG37" s="191"/>
+      <c r="AH37" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="AI37" s="96"/>
-      <c r="AJ37" s="96"/>
-      <c r="AK37" s="96"/>
-      <c r="AL37" s="96"/>
-      <c r="AM37" s="96"/>
-      <c r="AN37" s="96"/>
-      <c r="AO37" s="96"/>
-      <c r="AP37" s="96"/>
-      <c r="AQ37" s="96"/>
-      <c r="AR37" s="96"/>
-      <c r="AS37" s="96"/>
-      <c r="AT37" s="96"/>
-      <c r="AU37" s="96"/>
-      <c r="AV37" s="96"/>
-      <c r="AW37" s="96"/>
-      <c r="AX37" s="96"/>
-      <c r="AY37" s="96"/>
-      <c r="AZ37" s="97"/>
+      <c r="AI37" s="203"/>
+      <c r="AJ37" s="203"/>
+      <c r="AK37" s="203"/>
+      <c r="AL37" s="203"/>
+      <c r="AM37" s="203"/>
+      <c r="AN37" s="203"/>
+      <c r="AO37" s="203"/>
+      <c r="AP37" s="203"/>
+      <c r="AQ37" s="203"/>
+      <c r="AR37" s="203"/>
+      <c r="AS37" s="203"/>
+      <c r="AT37" s="203"/>
+      <c r="AU37" s="203"/>
+      <c r="AV37" s="203"/>
+      <c r="AW37" s="203"/>
+      <c r="AX37" s="203"/>
+      <c r="AY37" s="203"/>
+      <c r="AZ37" s="204"/>
     </row>
     <row r="38" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="125" t="s">
+      <c r="A38" s="183" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="126"/>
-      <c r="C38" s="126"/>
-      <c r="D38" s="126"/>
-      <c r="E38" s="126"/>
-      <c r="F38" s="126"/>
-      <c r="G38" s="126"/>
-      <c r="H38" s="126"/>
-      <c r="I38" s="126"/>
-      <c r="J38" s="126"/>
-      <c r="K38" s="126"/>
-      <c r="L38" s="126"/>
-      <c r="M38" s="126"/>
-      <c r="N38" s="126"/>
-      <c r="O38" s="126"/>
-      <c r="P38" s="126"/>
-      <c r="Q38" s="126"/>
-      <c r="R38" s="127"/>
-      <c r="S38" s="128" t="s">
+      <c r="B38" s="184"/>
+      <c r="C38" s="184"/>
+      <c r="D38" s="184"/>
+      <c r="E38" s="184"/>
+      <c r="F38" s="184"/>
+      <c r="G38" s="184"/>
+      <c r="H38" s="184"/>
+      <c r="I38" s="184"/>
+      <c r="J38" s="184"/>
+      <c r="K38" s="184"/>
+      <c r="L38" s="184"/>
+      <c r="M38" s="184"/>
+      <c r="N38" s="184"/>
+      <c r="O38" s="184"/>
+      <c r="P38" s="184"/>
+      <c r="Q38" s="184"/>
+      <c r="R38" s="185"/>
+      <c r="S38" s="189" t="s">
         <v>68</v>
       </c>
-      <c r="T38" s="129"/>
-      <c r="U38" s="129"/>
-      <c r="V38" s="129"/>
-      <c r="W38" s="129"/>
-      <c r="X38" s="129"/>
-      <c r="Y38" s="129"/>
-      <c r="Z38" s="129"/>
-      <c r="AA38" s="129"/>
-      <c r="AB38" s="129"/>
-      <c r="AC38" s="129"/>
-      <c r="AD38" s="129"/>
-      <c r="AE38" s="129"/>
-      <c r="AF38" s="129"/>
-      <c r="AG38" s="130"/>
-      <c r="AH38" s="95" t="s">
+      <c r="T38" s="190"/>
+      <c r="U38" s="190"/>
+      <c r="V38" s="190"/>
+      <c r="W38" s="190"/>
+      <c r="X38" s="190"/>
+      <c r="Y38" s="190"/>
+      <c r="Z38" s="190"/>
+      <c r="AA38" s="190"/>
+      <c r="AB38" s="190"/>
+      <c r="AC38" s="190"/>
+      <c r="AD38" s="190"/>
+      <c r="AE38" s="190"/>
+      <c r="AF38" s="190"/>
+      <c r="AG38" s="191"/>
+      <c r="AH38" s="202" t="s">
         <v>69</v>
       </c>
-      <c r="AI38" s="96"/>
-      <c r="AJ38" s="96"/>
-      <c r="AK38" s="96"/>
-      <c r="AL38" s="96"/>
-      <c r="AM38" s="96"/>
-      <c r="AN38" s="96"/>
-      <c r="AO38" s="96"/>
-      <c r="AP38" s="96"/>
-      <c r="AQ38" s="96"/>
-      <c r="AR38" s="96"/>
-      <c r="AS38" s="96"/>
-      <c r="AT38" s="96"/>
-      <c r="AU38" s="96"/>
-      <c r="AV38" s="96"/>
-      <c r="AW38" s="96"/>
-      <c r="AX38" s="96"/>
-      <c r="AY38" s="96"/>
-      <c r="AZ38" s="97"/>
+      <c r="AI38" s="203"/>
+      <c r="AJ38" s="203"/>
+      <c r="AK38" s="203"/>
+      <c r="AL38" s="203"/>
+      <c r="AM38" s="203"/>
+      <c r="AN38" s="203"/>
+      <c r="AO38" s="203"/>
+      <c r="AP38" s="203"/>
+      <c r="AQ38" s="203"/>
+      <c r="AR38" s="203"/>
+      <c r="AS38" s="203"/>
+      <c r="AT38" s="203"/>
+      <c r="AU38" s="203"/>
+      <c r="AV38" s="203"/>
+      <c r="AW38" s="203"/>
+      <c r="AX38" s="203"/>
+      <c r="AY38" s="203"/>
+      <c r="AZ38" s="204"/>
     </row>
     <row r="39" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="125" t="s">
+      <c r="A39" s="183" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="126"/>
-      <c r="C39" s="126"/>
-      <c r="D39" s="126"/>
-      <c r="E39" s="126"/>
-      <c r="F39" s="126"/>
-      <c r="G39" s="126"/>
-      <c r="H39" s="126"/>
-      <c r="I39" s="126"/>
-      <c r="J39" s="126"/>
-      <c r="K39" s="126"/>
-      <c r="L39" s="126"/>
-      <c r="M39" s="126"/>
-      <c r="N39" s="126"/>
-      <c r="O39" s="126"/>
-      <c r="P39" s="126"/>
-      <c r="Q39" s="126"/>
-      <c r="R39" s="127"/>
-      <c r="S39" s="128" t="s">
+      <c r="B39" s="184"/>
+      <c r="C39" s="184"/>
+      <c r="D39" s="184"/>
+      <c r="E39" s="184"/>
+      <c r="F39" s="184"/>
+      <c r="G39" s="184"/>
+      <c r="H39" s="184"/>
+      <c r="I39" s="184"/>
+      <c r="J39" s="184"/>
+      <c r="K39" s="184"/>
+      <c r="L39" s="184"/>
+      <c r="M39" s="184"/>
+      <c r="N39" s="184"/>
+      <c r="O39" s="184"/>
+      <c r="P39" s="184"/>
+      <c r="Q39" s="184"/>
+      <c r="R39" s="185"/>
+      <c r="S39" s="189" t="s">
         <v>71</v>
       </c>
-      <c r="T39" s="129"/>
-      <c r="U39" s="129"/>
-      <c r="V39" s="129"/>
-      <c r="W39" s="129"/>
-      <c r="X39" s="129"/>
-      <c r="Y39" s="129"/>
-      <c r="Z39" s="129"/>
-      <c r="AA39" s="129"/>
-      <c r="AB39" s="129"/>
-      <c r="AC39" s="129"/>
-      <c r="AD39" s="129"/>
-      <c r="AE39" s="129"/>
-      <c r="AF39" s="129"/>
-      <c r="AG39" s="130"/>
-      <c r="AH39" s="148"/>
-      <c r="AI39" s="149"/>
-      <c r="AJ39" s="149"/>
-      <c r="AK39" s="149"/>
-      <c r="AL39" s="149"/>
-      <c r="AM39" s="149"/>
-      <c r="AN39" s="149"/>
-      <c r="AO39" s="149"/>
-      <c r="AP39" s="149"/>
-      <c r="AQ39" s="149"/>
-      <c r="AR39" s="149"/>
-      <c r="AS39" s="149"/>
-      <c r="AT39" s="149"/>
-      <c r="AU39" s="149"/>
-      <c r="AV39" s="149"/>
-      <c r="AW39" s="149"/>
-      <c r="AX39" s="149"/>
-      <c r="AY39" s="149"/>
-      <c r="AZ39" s="150"/>
+      <c r="T39" s="190"/>
+      <c r="U39" s="190"/>
+      <c r="V39" s="190"/>
+      <c r="W39" s="190"/>
+      <c r="X39" s="190"/>
+      <c r="Y39" s="190"/>
+      <c r="Z39" s="190"/>
+      <c r="AA39" s="190"/>
+      <c r="AB39" s="190"/>
+      <c r="AC39" s="190"/>
+      <c r="AD39" s="190"/>
+      <c r="AE39" s="190"/>
+      <c r="AF39" s="190"/>
+      <c r="AG39" s="191"/>
+      <c r="AH39" s="220"/>
+      <c r="AI39" s="221"/>
+      <c r="AJ39" s="221"/>
+      <c r="AK39" s="221"/>
+      <c r="AL39" s="221"/>
+      <c r="AM39" s="221"/>
+      <c r="AN39" s="221"/>
+      <c r="AO39" s="221"/>
+      <c r="AP39" s="221"/>
+      <c r="AQ39" s="221"/>
+      <c r="AR39" s="221"/>
+      <c r="AS39" s="221"/>
+      <c r="AT39" s="221"/>
+      <c r="AU39" s="221"/>
+      <c r="AV39" s="221"/>
+      <c r="AW39" s="221"/>
+      <c r="AX39" s="221"/>
+      <c r="AY39" s="221"/>
+      <c r="AZ39" s="222"/>
     </row>
     <row r="40" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="125" t="s">
+      <c r="A40" s="183" t="s">
         <v>72</v>
       </c>
-      <c r="B40" s="126"/>
-      <c r="C40" s="126"/>
-      <c r="D40" s="126"/>
-      <c r="E40" s="126"/>
-      <c r="F40" s="126"/>
-      <c r="G40" s="126"/>
-      <c r="H40" s="126"/>
-      <c r="I40" s="126"/>
-      <c r="J40" s="126"/>
-      <c r="K40" s="126"/>
-      <c r="L40" s="126"/>
-      <c r="M40" s="126"/>
-      <c r="N40" s="126"/>
-      <c r="O40" s="126"/>
-      <c r="P40" s="126"/>
-      <c r="Q40" s="126"/>
-      <c r="R40" s="127"/>
-      <c r="S40" s="128" t="s">
+      <c r="B40" s="184"/>
+      <c r="C40" s="184"/>
+      <c r="D40" s="184"/>
+      <c r="E40" s="184"/>
+      <c r="F40" s="184"/>
+      <c r="G40" s="184"/>
+      <c r="H40" s="184"/>
+      <c r="I40" s="184"/>
+      <c r="J40" s="184"/>
+      <c r="K40" s="184"/>
+      <c r="L40" s="184"/>
+      <c r="M40" s="184"/>
+      <c r="N40" s="184"/>
+      <c r="O40" s="184"/>
+      <c r="P40" s="184"/>
+      <c r="Q40" s="184"/>
+      <c r="R40" s="185"/>
+      <c r="S40" s="189" t="s">
         <v>73</v>
       </c>
-      <c r="T40" s="129"/>
-      <c r="U40" s="129"/>
-      <c r="V40" s="129"/>
-      <c r="W40" s="129"/>
-      <c r="X40" s="129"/>
-      <c r="Y40" s="129"/>
-      <c r="Z40" s="129"/>
-      <c r="AA40" s="129"/>
-      <c r="AB40" s="129"/>
-      <c r="AC40" s="129"/>
-      <c r="AD40" s="129"/>
-      <c r="AE40" s="129"/>
-      <c r="AF40" s="129"/>
-      <c r="AG40" s="130"/>
-      <c r="AH40" s="148"/>
-      <c r="AI40" s="149"/>
-      <c r="AJ40" s="149"/>
-      <c r="AK40" s="149"/>
-      <c r="AL40" s="149"/>
-      <c r="AM40" s="149"/>
-      <c r="AN40" s="149"/>
-      <c r="AO40" s="149"/>
-      <c r="AP40" s="149"/>
-      <c r="AQ40" s="149"/>
-      <c r="AR40" s="149"/>
-      <c r="AS40" s="149"/>
-      <c r="AT40" s="149"/>
-      <c r="AU40" s="149"/>
-      <c r="AV40" s="149"/>
-      <c r="AW40" s="149"/>
-      <c r="AX40" s="149"/>
-      <c r="AY40" s="149"/>
-      <c r="AZ40" s="150"/>
+      <c r="T40" s="190"/>
+      <c r="U40" s="190"/>
+      <c r="V40" s="190"/>
+      <c r="W40" s="190"/>
+      <c r="X40" s="190"/>
+      <c r="Y40" s="190"/>
+      <c r="Z40" s="190"/>
+      <c r="AA40" s="190"/>
+      <c r="AB40" s="190"/>
+      <c r="AC40" s="190"/>
+      <c r="AD40" s="190"/>
+      <c r="AE40" s="190"/>
+      <c r="AF40" s="190"/>
+      <c r="AG40" s="191"/>
+      <c r="AH40" s="220"/>
+      <c r="AI40" s="221"/>
+      <c r="AJ40" s="221"/>
+      <c r="AK40" s="221"/>
+      <c r="AL40" s="221"/>
+      <c r="AM40" s="221"/>
+      <c r="AN40" s="221"/>
+      <c r="AO40" s="221"/>
+      <c r="AP40" s="221"/>
+      <c r="AQ40" s="221"/>
+      <c r="AR40" s="221"/>
+      <c r="AS40" s="221"/>
+      <c r="AT40" s="221"/>
+      <c r="AU40" s="221"/>
+      <c r="AV40" s="221"/>
+      <c r="AW40" s="221"/>
+      <c r="AX40" s="221"/>
+      <c r="AY40" s="221"/>
+      <c r="AZ40" s="222"/>
     </row>
     <row r="41" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="125"/>
-      <c r="B41" s="126"/>
-      <c r="C41" s="126"/>
-      <c r="D41" s="126"/>
-      <c r="E41" s="126"/>
-      <c r="F41" s="126"/>
-      <c r="G41" s="126"/>
-      <c r="H41" s="126"/>
-      <c r="I41" s="126"/>
-      <c r="J41" s="126"/>
-      <c r="K41" s="126"/>
-      <c r="L41" s="126"/>
-      <c r="M41" s="126"/>
-      <c r="N41" s="126"/>
-      <c r="O41" s="126"/>
-      <c r="P41" s="126"/>
-      <c r="Q41" s="126"/>
-      <c r="R41" s="127"/>
-      <c r="S41" s="128" t="s">
+      <c r="A41" s="183"/>
+      <c r="B41" s="184"/>
+      <c r="C41" s="184"/>
+      <c r="D41" s="184"/>
+      <c r="E41" s="184"/>
+      <c r="F41" s="184"/>
+      <c r="G41" s="184"/>
+      <c r="H41" s="184"/>
+      <c r="I41" s="184"/>
+      <c r="J41" s="184"/>
+      <c r="K41" s="184"/>
+      <c r="L41" s="184"/>
+      <c r="M41" s="184"/>
+      <c r="N41" s="184"/>
+      <c r="O41" s="184"/>
+      <c r="P41" s="184"/>
+      <c r="Q41" s="184"/>
+      <c r="R41" s="185"/>
+      <c r="S41" s="189" t="s">
         <v>74</v>
       </c>
-      <c r="T41" s="129"/>
-      <c r="U41" s="129"/>
-      <c r="V41" s="129"/>
-      <c r="W41" s="129"/>
-      <c r="X41" s="129"/>
-      <c r="Y41" s="129"/>
-      <c r="Z41" s="129"/>
-      <c r="AA41" s="129"/>
-      <c r="AB41" s="129"/>
-      <c r="AC41" s="129"/>
-      <c r="AD41" s="129"/>
-      <c r="AE41" s="129"/>
-      <c r="AF41" s="129"/>
-      <c r="AG41" s="130"/>
-      <c r="AH41" s="148"/>
-      <c r="AI41" s="149"/>
-      <c r="AJ41" s="149"/>
-      <c r="AK41" s="149"/>
-      <c r="AL41" s="149"/>
-      <c r="AM41" s="149"/>
-      <c r="AN41" s="149"/>
-      <c r="AO41" s="149"/>
-      <c r="AP41" s="149"/>
-      <c r="AQ41" s="149"/>
-      <c r="AR41" s="149"/>
-      <c r="AS41" s="149"/>
-      <c r="AT41" s="149"/>
-      <c r="AU41" s="149"/>
-      <c r="AV41" s="149"/>
-      <c r="AW41" s="149"/>
-      <c r="AX41" s="149"/>
-      <c r="AY41" s="149"/>
-      <c r="AZ41" s="150"/>
+      <c r="T41" s="190"/>
+      <c r="U41" s="190"/>
+      <c r="V41" s="190"/>
+      <c r="W41" s="190"/>
+      <c r="X41" s="190"/>
+      <c r="Y41" s="190"/>
+      <c r="Z41" s="190"/>
+      <c r="AA41" s="190"/>
+      <c r="AB41" s="190"/>
+      <c r="AC41" s="190"/>
+      <c r="AD41" s="190"/>
+      <c r="AE41" s="190"/>
+      <c r="AF41" s="190"/>
+      <c r="AG41" s="191"/>
+      <c r="AH41" s="220"/>
+      <c r="AI41" s="221"/>
+      <c r="AJ41" s="221"/>
+      <c r="AK41" s="221"/>
+      <c r="AL41" s="221"/>
+      <c r="AM41" s="221"/>
+      <c r="AN41" s="221"/>
+      <c r="AO41" s="221"/>
+      <c r="AP41" s="221"/>
+      <c r="AQ41" s="221"/>
+      <c r="AR41" s="221"/>
+      <c r="AS41" s="221"/>
+      <c r="AT41" s="221"/>
+      <c r="AU41" s="221"/>
+      <c r="AV41" s="221"/>
+      <c r="AW41" s="221"/>
+      <c r="AX41" s="221"/>
+      <c r="AY41" s="221"/>
+      <c r="AZ41" s="222"/>
     </row>
     <row r="42" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="151"/>
-      <c r="B42" s="152"/>
-      <c r="C42" s="152"/>
-      <c r="D42" s="152"/>
-      <c r="E42" s="152"/>
-      <c r="F42" s="152"/>
-      <c r="G42" s="152"/>
-      <c r="H42" s="152"/>
-      <c r="I42" s="152"/>
-      <c r="J42" s="152"/>
-      <c r="K42" s="152"/>
-      <c r="L42" s="152"/>
-      <c r="M42" s="152"/>
-      <c r="N42" s="152"/>
-      <c r="O42" s="152"/>
-      <c r="P42" s="152"/>
-      <c r="Q42" s="152"/>
-      <c r="R42" s="153"/>
-      <c r="S42" s="137" t="s">
+      <c r="A42" s="223"/>
+      <c r="B42" s="224"/>
+      <c r="C42" s="224"/>
+      <c r="D42" s="224"/>
+      <c r="E42" s="224"/>
+      <c r="F42" s="224"/>
+      <c r="G42" s="224"/>
+      <c r="H42" s="224"/>
+      <c r="I42" s="224"/>
+      <c r="J42" s="224"/>
+      <c r="K42" s="224"/>
+      <c r="L42" s="224"/>
+      <c r="M42" s="224"/>
+      <c r="N42" s="224"/>
+      <c r="O42" s="224"/>
+      <c r="P42" s="224"/>
+      <c r="Q42" s="224"/>
+      <c r="R42" s="225"/>
+      <c r="S42" s="211" t="s">
         <v>75</v>
       </c>
-      <c r="T42" s="138"/>
-      <c r="U42" s="138"/>
-      <c r="V42" s="138"/>
-      <c r="W42" s="138"/>
-      <c r="X42" s="138"/>
-      <c r="Y42" s="138"/>
-      <c r="Z42" s="138"/>
-      <c r="AA42" s="138"/>
-      <c r="AB42" s="138"/>
-      <c r="AC42" s="138"/>
-      <c r="AD42" s="138"/>
-      <c r="AE42" s="138"/>
-      <c r="AF42" s="138"/>
-      <c r="AG42" s="139"/>
-      <c r="AH42" s="154"/>
-      <c r="AI42" s="155"/>
-      <c r="AJ42" s="155"/>
-      <c r="AK42" s="155"/>
-      <c r="AL42" s="155"/>
-      <c r="AM42" s="155"/>
-      <c r="AN42" s="155"/>
-      <c r="AO42" s="155"/>
-      <c r="AP42" s="155"/>
-      <c r="AQ42" s="155"/>
-      <c r="AR42" s="155"/>
-      <c r="AS42" s="155"/>
-      <c r="AT42" s="155"/>
-      <c r="AU42" s="155"/>
-      <c r="AV42" s="155"/>
-      <c r="AW42" s="155"/>
-      <c r="AX42" s="155"/>
-      <c r="AY42" s="155"/>
-      <c r="AZ42" s="156"/>
+      <c r="T42" s="212"/>
+      <c r="U42" s="212"/>
+      <c r="V42" s="212"/>
+      <c r="W42" s="212"/>
+      <c r="X42" s="212"/>
+      <c r="Y42" s="212"/>
+      <c r="Z42" s="212"/>
+      <c r="AA42" s="212"/>
+      <c r="AB42" s="212"/>
+      <c r="AC42" s="212"/>
+      <c r="AD42" s="212"/>
+      <c r="AE42" s="212"/>
+      <c r="AF42" s="212"/>
+      <c r="AG42" s="213"/>
+      <c r="AH42" s="226"/>
+      <c r="AI42" s="227"/>
+      <c r="AJ42" s="227"/>
+      <c r="AK42" s="227"/>
+      <c r="AL42" s="227"/>
+      <c r="AM42" s="227"/>
+      <c r="AN42" s="227"/>
+      <c r="AO42" s="227"/>
+      <c r="AP42" s="227"/>
+      <c r="AQ42" s="227"/>
+      <c r="AR42" s="227"/>
+      <c r="AS42" s="227"/>
+      <c r="AT42" s="227"/>
+      <c r="AU42" s="227"/>
+      <c r="AV42" s="227"/>
+      <c r="AW42" s="227"/>
+      <c r="AX42" s="227"/>
+      <c r="AY42" s="227"/>
+      <c r="AZ42" s="228"/>
     </row>
     <row r="43" spans="1:52" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="146"/>
-      <c r="B43" s="146"/>
-      <c r="C43" s="146"/>
-      <c r="D43" s="146"/>
-      <c r="E43" s="146"/>
-      <c r="F43" s="146"/>
-      <c r="G43" s="146"/>
-      <c r="H43" s="146"/>
-      <c r="I43" s="146"/>
-      <c r="J43" s="146"/>
-      <c r="K43" s="146"/>
-      <c r="L43" s="146"/>
-      <c r="M43" s="146"/>
-      <c r="N43" s="146"/>
-      <c r="O43" s="146"/>
-      <c r="P43" s="146"/>
-      <c r="Q43" s="146"/>
-      <c r="R43" s="146"/>
-      <c r="S43" s="146"/>
-      <c r="T43" s="146"/>
-      <c r="U43" s="146"/>
-      <c r="V43" s="146"/>
-      <c r="W43" s="146"/>
-      <c r="X43" s="146"/>
-      <c r="Y43" s="146"/>
-      <c r="Z43" s="146"/>
-      <c r="AA43" s="146"/>
-      <c r="AB43" s="146"/>
-      <c r="AC43" s="146"/>
-      <c r="AD43" s="146"/>
-      <c r="AE43" s="146"/>
-      <c r="AF43" s="146"/>
-      <c r="AG43" s="146"/>
-      <c r="AH43" s="146"/>
-      <c r="AI43" s="146"/>
-      <c r="AJ43" s="146"/>
-      <c r="AK43" s="146"/>
-      <c r="AL43" s="146"/>
-      <c r="AM43" s="146"/>
-      <c r="AN43" s="146"/>
-      <c r="AO43" s="146"/>
-      <c r="AP43" s="146"/>
-      <c r="AQ43" s="146"/>
-      <c r="AR43" s="146"/>
-      <c r="AS43" s="146"/>
-      <c r="AT43" s="146"/>
-      <c r="AU43" s="146"/>
-      <c r="AV43" s="146"/>
-      <c r="AW43" s="146"/>
-      <c r="AX43" s="146"/>
-      <c r="AY43" s="146"/>
-      <c r="AZ43" s="146"/>
+      <c r="A43" s="99"/>
+      <c r="B43" s="99"/>
+      <c r="C43" s="99"/>
+      <c r="D43" s="99"/>
+      <c r="E43" s="99"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="99"/>
+      <c r="J43" s="99"/>
+      <c r="K43" s="99"/>
+      <c r="L43" s="99"/>
+      <c r="M43" s="99"/>
+      <c r="N43" s="99"/>
+      <c r="O43" s="99"/>
+      <c r="P43" s="99"/>
+      <c r="Q43" s="99"/>
+      <c r="R43" s="99"/>
+      <c r="S43" s="99"/>
+      <c r="T43" s="99"/>
+      <c r="U43" s="99"/>
+      <c r="V43" s="99"/>
+      <c r="W43" s="99"/>
+      <c r="X43" s="99"/>
+      <c r="Y43" s="99"/>
+      <c r="Z43" s="99"/>
+      <c r="AA43" s="99"/>
+      <c r="AB43" s="99"/>
+      <c r="AC43" s="99"/>
+      <c r="AD43" s="99"/>
+      <c r="AE43" s="99"/>
+      <c r="AF43" s="99"/>
+      <c r="AG43" s="99"/>
+      <c r="AH43" s="99"/>
+      <c r="AI43" s="99"/>
+      <c r="AJ43" s="99"/>
+      <c r="AK43" s="99"/>
+      <c r="AL43" s="99"/>
+      <c r="AM43" s="99"/>
+      <c r="AN43" s="99"/>
+      <c r="AO43" s="99"/>
+      <c r="AP43" s="99"/>
+      <c r="AQ43" s="99"/>
+      <c r="AR43" s="99"/>
+      <c r="AS43" s="99"/>
+      <c r="AT43" s="99"/>
+      <c r="AU43" s="99"/>
+      <c r="AV43" s="99"/>
+      <c r="AW43" s="99"/>
+      <c r="AX43" s="99"/>
+      <c r="AY43" s="99"/>
+      <c r="AZ43" s="99"/>
     </row>
     <row r="44" spans="1:52" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="140" t="s">
+      <c r="A44" s="214" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="141"/>
-      <c r="C44" s="141"/>
-      <c r="D44" s="141"/>
-      <c r="E44" s="141"/>
-      <c r="F44" s="141"/>
-      <c r="G44" s="141"/>
-      <c r="H44" s="141"/>
-      <c r="I44" s="141"/>
-      <c r="J44" s="141"/>
-      <c r="K44" s="141"/>
-      <c r="L44" s="141"/>
-      <c r="M44" s="141"/>
-      <c r="N44" s="141"/>
-      <c r="O44" s="141"/>
-      <c r="P44" s="141"/>
-      <c r="Q44" s="141"/>
-      <c r="R44" s="141"/>
-      <c r="S44" s="141"/>
-      <c r="T44" s="141"/>
-      <c r="U44" s="141"/>
-      <c r="V44" s="141"/>
-      <c r="W44" s="141"/>
-      <c r="X44" s="141"/>
-      <c r="Y44" s="141"/>
-      <c r="Z44" s="141"/>
-      <c r="AA44" s="141"/>
-      <c r="AB44" s="141"/>
-      <c r="AC44" s="141"/>
-      <c r="AD44" s="141"/>
-      <c r="AE44" s="141"/>
-      <c r="AF44" s="141"/>
-      <c r="AG44" s="141"/>
-      <c r="AH44" s="141"/>
-      <c r="AI44" s="141"/>
-      <c r="AJ44" s="141"/>
-      <c r="AK44" s="141"/>
-      <c r="AL44" s="141"/>
-      <c r="AM44" s="141"/>
-      <c r="AN44" s="141"/>
-      <c r="AO44" s="141"/>
-      <c r="AP44" s="141"/>
-      <c r="AQ44" s="141"/>
-      <c r="AR44" s="141"/>
-      <c r="AS44" s="141"/>
-      <c r="AT44" s="141"/>
-      <c r="AU44" s="141"/>
-      <c r="AV44" s="141"/>
-      <c r="AW44" s="141"/>
-      <c r="AX44" s="141"/>
-      <c r="AY44" s="141"/>
-      <c r="AZ44" s="142"/>
+      <c r="B44" s="215"/>
+      <c r="C44" s="215"/>
+      <c r="D44" s="215"/>
+      <c r="E44" s="215"/>
+      <c r="F44" s="215"/>
+      <c r="G44" s="215"/>
+      <c r="H44" s="215"/>
+      <c r="I44" s="215"/>
+      <c r="J44" s="215"/>
+      <c r="K44" s="215"/>
+      <c r="L44" s="215"/>
+      <c r="M44" s="215"/>
+      <c r="N44" s="215"/>
+      <c r="O44" s="215"/>
+      <c r="P44" s="215"/>
+      <c r="Q44" s="215"/>
+      <c r="R44" s="215"/>
+      <c r="S44" s="215"/>
+      <c r="T44" s="215"/>
+      <c r="U44" s="215"/>
+      <c r="V44" s="215"/>
+      <c r="W44" s="215"/>
+      <c r="X44" s="215"/>
+      <c r="Y44" s="215"/>
+      <c r="Z44" s="215"/>
+      <c r="AA44" s="215"/>
+      <c r="AB44" s="215"/>
+      <c r="AC44" s="215"/>
+      <c r="AD44" s="215"/>
+      <c r="AE44" s="215"/>
+      <c r="AF44" s="215"/>
+      <c r="AG44" s="215"/>
+      <c r="AH44" s="215"/>
+      <c r="AI44" s="215"/>
+      <c r="AJ44" s="215"/>
+      <c r="AK44" s="215"/>
+      <c r="AL44" s="215"/>
+      <c r="AM44" s="215"/>
+      <c r="AN44" s="215"/>
+      <c r="AO44" s="215"/>
+      <c r="AP44" s="215"/>
+      <c r="AQ44" s="215"/>
+      <c r="AR44" s="215"/>
+      <c r="AS44" s="215"/>
+      <c r="AT44" s="215"/>
+      <c r="AU44" s="215"/>
+      <c r="AV44" s="215"/>
+      <c r="AW44" s="215"/>
+      <c r="AX44" s="215"/>
+      <c r="AY44" s="215"/>
+      <c r="AZ44" s="216"/>
     </row>
     <row r="45" spans="1:52" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="143"/>
-      <c r="B45" s="144"/>
-      <c r="C45" s="144"/>
-      <c r="D45" s="144"/>
-      <c r="E45" s="144"/>
-      <c r="F45" s="144"/>
-      <c r="G45" s="144"/>
-      <c r="H45" s="144"/>
-      <c r="I45" s="144"/>
-      <c r="J45" s="144"/>
-      <c r="K45" s="144"/>
-      <c r="L45" s="144"/>
-      <c r="M45" s="144"/>
-      <c r="N45" s="144"/>
-      <c r="O45" s="144"/>
-      <c r="P45" s="144"/>
-      <c r="Q45" s="144"/>
-      <c r="R45" s="144"/>
-      <c r="S45" s="144"/>
-      <c r="T45" s="144"/>
-      <c r="U45" s="144"/>
-      <c r="V45" s="144"/>
-      <c r="W45" s="144"/>
-      <c r="X45" s="144"/>
-      <c r="Y45" s="144"/>
-      <c r="Z45" s="144"/>
-      <c r="AA45" s="144"/>
-      <c r="AB45" s="144"/>
-      <c r="AC45" s="144"/>
-      <c r="AD45" s="144"/>
-      <c r="AE45" s="144"/>
-      <c r="AF45" s="144"/>
-      <c r="AG45" s="144"/>
-      <c r="AH45" s="144"/>
-      <c r="AI45" s="144"/>
-      <c r="AJ45" s="144"/>
-      <c r="AK45" s="144"/>
-      <c r="AL45" s="144"/>
-      <c r="AM45" s="144"/>
-      <c r="AN45" s="144"/>
-      <c r="AO45" s="144"/>
-      <c r="AP45" s="144"/>
-      <c r="AQ45" s="144"/>
-      <c r="AR45" s="144"/>
-      <c r="AS45" s="144"/>
-      <c r="AT45" s="144"/>
-      <c r="AU45" s="144"/>
-      <c r="AV45" s="144"/>
-      <c r="AW45" s="144"/>
-      <c r="AX45" s="144"/>
-      <c r="AY45" s="144"/>
-      <c r="AZ45" s="145"/>
+      <c r="A45" s="217"/>
+      <c r="B45" s="218"/>
+      <c r="C45" s="218"/>
+      <c r="D45" s="218"/>
+      <c r="E45" s="218"/>
+      <c r="F45" s="218"/>
+      <c r="G45" s="218"/>
+      <c r="H45" s="218"/>
+      <c r="I45" s="218"/>
+      <c r="J45" s="218"/>
+      <c r="K45" s="218"/>
+      <c r="L45" s="218"/>
+      <c r="M45" s="218"/>
+      <c r="N45" s="218"/>
+      <c r="O45" s="218"/>
+      <c r="P45" s="218"/>
+      <c r="Q45" s="218"/>
+      <c r="R45" s="218"/>
+      <c r="S45" s="218"/>
+      <c r="T45" s="218"/>
+      <c r="U45" s="218"/>
+      <c r="V45" s="218"/>
+      <c r="W45" s="218"/>
+      <c r="X45" s="218"/>
+      <c r="Y45" s="218"/>
+      <c r="Z45" s="218"/>
+      <c r="AA45" s="218"/>
+      <c r="AB45" s="218"/>
+      <c r="AC45" s="218"/>
+      <c r="AD45" s="218"/>
+      <c r="AE45" s="218"/>
+      <c r="AF45" s="218"/>
+      <c r="AG45" s="218"/>
+      <c r="AH45" s="218"/>
+      <c r="AI45" s="218"/>
+      <c r="AJ45" s="218"/>
+      <c r="AK45" s="218"/>
+      <c r="AL45" s="218"/>
+      <c r="AM45" s="218"/>
+      <c r="AN45" s="218"/>
+      <c r="AO45" s="218"/>
+      <c r="AP45" s="218"/>
+      <c r="AQ45" s="218"/>
+      <c r="AR45" s="218"/>
+      <c r="AS45" s="218"/>
+      <c r="AT45" s="218"/>
+      <c r="AU45" s="218"/>
+      <c r="AV45" s="218"/>
+      <c r="AW45" s="218"/>
+      <c r="AX45" s="218"/>
+      <c r="AY45" s="218"/>
+      <c r="AZ45" s="219"/>
     </row>
     <row r="46" spans="1:52" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
@@ -7915,174 +7919,174 @@
       <c r="AZ46"/>
     </row>
     <row r="47" spans="1:52" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="147"/>
-      <c r="B47" s="147"/>
-      <c r="C47" s="147"/>
-      <c r="D47" s="147"/>
-      <c r="E47" s="147"/>
-      <c r="F47" s="147"/>
-      <c r="G47" s="147"/>
-      <c r="H47" s="147"/>
-      <c r="I47" s="147"/>
-      <c r="J47" s="147"/>
-      <c r="K47" s="147"/>
-      <c r="L47" s="147"/>
-      <c r="M47" s="147"/>
-      <c r="N47" s="147"/>
-      <c r="O47" s="147"/>
-      <c r="P47" s="147"/>
+      <c r="A47" s="117"/>
+      <c r="B47" s="117"/>
+      <c r="C47" s="117"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="117"/>
+      <c r="H47" s="117"/>
+      <c r="I47" s="117"/>
+      <c r="J47" s="117"/>
+      <c r="K47" s="117"/>
+      <c r="L47" s="117"/>
+      <c r="M47" s="117"/>
+      <c r="N47" s="117"/>
+      <c r="O47" s="117"/>
+      <c r="P47" s="117"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
-      <c r="S47" s="147"/>
-      <c r="T47" s="147"/>
-      <c r="U47" s="147"/>
-      <c r="V47" s="147"/>
-      <c r="W47" s="147"/>
-      <c r="X47" s="147"/>
-      <c r="Y47" s="147"/>
-      <c r="Z47" s="147"/>
-      <c r="AA47" s="147"/>
-      <c r="AB47" s="147"/>
-      <c r="AC47" s="147"/>
-      <c r="AD47" s="147"/>
-      <c r="AE47" s="147"/>
-      <c r="AF47" s="147"/>
-      <c r="AG47" s="147"/>
-      <c r="AH47" s="147"/>
+      <c r="S47" s="117"/>
+      <c r="T47" s="117"/>
+      <c r="U47" s="117"/>
+      <c r="V47" s="117"/>
+      <c r="W47" s="117"/>
+      <c r="X47" s="117"/>
+      <c r="Y47" s="117"/>
+      <c r="Z47" s="117"/>
+      <c r="AA47" s="117"/>
+      <c r="AB47" s="117"/>
+      <c r="AC47" s="117"/>
+      <c r="AD47" s="117"/>
+      <c r="AE47" s="117"/>
+      <c r="AF47" s="117"/>
+      <c r="AG47" s="117"/>
+      <c r="AH47" s="117"/>
       <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
-      <c r="AK47" s="147"/>
-      <c r="AL47" s="147"/>
-      <c r="AM47" s="147"/>
-      <c r="AN47" s="147"/>
-      <c r="AO47" s="147"/>
-      <c r="AP47" s="147"/>
-      <c r="AQ47" s="147"/>
-      <c r="AR47" s="147"/>
-      <c r="AS47" s="147"/>
-      <c r="AT47" s="147"/>
-      <c r="AU47" s="147"/>
-      <c r="AV47" s="147"/>
-      <c r="AW47" s="147"/>
-      <c r="AX47" s="147"/>
-      <c r="AY47" s="147"/>
-      <c r="AZ47" s="147"/>
+      <c r="AK47" s="117"/>
+      <c r="AL47" s="117"/>
+      <c r="AM47" s="117"/>
+      <c r="AN47" s="117"/>
+      <c r="AO47" s="117"/>
+      <c r="AP47" s="117"/>
+      <c r="AQ47" s="117"/>
+      <c r="AR47" s="117"/>
+      <c r="AS47" s="117"/>
+      <c r="AT47" s="117"/>
+      <c r="AU47" s="117"/>
+      <c r="AV47" s="117"/>
+      <c r="AW47" s="117"/>
+      <c r="AX47" s="117"/>
+      <c r="AY47" s="117"/>
+      <c r="AZ47" s="117"/>
     </row>
     <row r="48" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="211" t="s">
+      <c r="A48" s="118" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="211"/>
-      <c r="C48" s="211"/>
-      <c r="D48" s="211"/>
-      <c r="E48" s="211"/>
-      <c r="F48" s="211"/>
-      <c r="G48" s="211"/>
-      <c r="H48" s="211"/>
-      <c r="I48" s="211"/>
-      <c r="J48" s="211"/>
-      <c r="K48" s="211"/>
-      <c r="L48" s="211"/>
-      <c r="M48" s="211"/>
-      <c r="N48" s="211"/>
-      <c r="O48" s="211"/>
-      <c r="P48" s="211"/>
+      <c r="B48" s="118"/>
+      <c r="C48" s="118"/>
+      <c r="D48" s="118"/>
+      <c r="E48" s="118"/>
+      <c r="F48" s="118"/>
+      <c r="G48" s="118"/>
+      <c r="H48" s="118"/>
+      <c r="I48" s="118"/>
+      <c r="J48" s="118"/>
+      <c r="K48" s="118"/>
+      <c r="L48" s="118"/>
+      <c r="M48" s="118"/>
+      <c r="N48" s="118"/>
+      <c r="O48" s="118"/>
+      <c r="P48" s="118"/>
       <c r="Q48" s="54"/>
       <c r="R48" s="54"/>
-      <c r="S48" s="122" t="s">
+      <c r="S48" s="195" t="s">
         <v>78</v>
       </c>
-      <c r="T48" s="122"/>
-      <c r="U48" s="122"/>
-      <c r="V48" s="122"/>
-      <c r="W48" s="122"/>
-      <c r="X48" s="122"/>
-      <c r="Y48" s="122"/>
-      <c r="Z48" s="122"/>
-      <c r="AA48" s="122"/>
-      <c r="AB48" s="122"/>
-      <c r="AC48" s="122"/>
-      <c r="AD48" s="122"/>
-      <c r="AE48" s="122"/>
-      <c r="AF48" s="122"/>
-      <c r="AG48" s="122"/>
-      <c r="AH48" s="122"/>
+      <c r="T48" s="195"/>
+      <c r="U48" s="195"/>
+      <c r="V48" s="195"/>
+      <c r="W48" s="195"/>
+      <c r="X48" s="195"/>
+      <c r="Y48" s="195"/>
+      <c r="Z48" s="195"/>
+      <c r="AA48" s="195"/>
+      <c r="AB48" s="195"/>
+      <c r="AC48" s="195"/>
+      <c r="AD48" s="195"/>
+      <c r="AE48" s="195"/>
+      <c r="AF48" s="195"/>
+      <c r="AG48" s="195"/>
+      <c r="AH48" s="195"/>
       <c r="AI48" s="54"/>
       <c r="AJ48" s="54"/>
-      <c r="AK48" s="211" t="s">
+      <c r="AK48" s="118" t="s">
         <v>79</v>
       </c>
-      <c r="AL48" s="211"/>
-      <c r="AM48" s="211"/>
-      <c r="AN48" s="211"/>
-      <c r="AO48" s="211"/>
-      <c r="AP48" s="211"/>
-      <c r="AQ48" s="211"/>
-      <c r="AR48" s="211"/>
-      <c r="AS48" s="211"/>
-      <c r="AT48" s="211"/>
-      <c r="AU48" s="211"/>
-      <c r="AV48" s="211"/>
-      <c r="AW48" s="211"/>
-      <c r="AX48" s="211"/>
-      <c r="AY48" s="211"/>
-      <c r="AZ48" s="211"/>
+      <c r="AL48" s="118"/>
+      <c r="AM48" s="118"/>
+      <c r="AN48" s="118"/>
+      <c r="AO48" s="118"/>
+      <c r="AP48" s="118"/>
+      <c r="AQ48" s="118"/>
+      <c r="AR48" s="118"/>
+      <c r="AS48" s="118"/>
+      <c r="AT48" s="118"/>
+      <c r="AU48" s="118"/>
+      <c r="AV48" s="118"/>
+      <c r="AW48" s="118"/>
+      <c r="AX48" s="118"/>
+      <c r="AY48" s="118"/>
+      <c r="AZ48" s="118"/>
     </row>
     <row r="49" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="89" t="s">
+      <c r="A49" s="120" t="s">
         <v>80</v>
       </c>
-      <c r="B49" s="89"/>
-      <c r="C49" s="89"/>
-      <c r="D49" s="89"/>
-      <c r="E49" s="89"/>
-      <c r="F49" s="89"/>
-      <c r="G49" s="89"/>
-      <c r="H49" s="89"/>
-      <c r="I49" s="89"/>
-      <c r="J49" s="89"/>
-      <c r="K49" s="89"/>
-      <c r="L49" s="89"/>
-      <c r="M49" s="89"/>
-      <c r="N49" s="89"/>
-      <c r="O49" s="89"/>
-      <c r="P49" s="89"/>
-      <c r="S49" s="89" t="s">
+      <c r="B49" s="120"/>
+      <c r="C49" s="120"/>
+      <c r="D49" s="120"/>
+      <c r="E49" s="120"/>
+      <c r="F49" s="120"/>
+      <c r="G49" s="120"/>
+      <c r="H49" s="120"/>
+      <c r="I49" s="120"/>
+      <c r="J49" s="120"/>
+      <c r="K49" s="120"/>
+      <c r="L49" s="120"/>
+      <c r="M49" s="120"/>
+      <c r="N49" s="120"/>
+      <c r="O49" s="120"/>
+      <c r="P49" s="120"/>
+      <c r="S49" s="120" t="s">
         <v>81</v>
       </c>
-      <c r="T49" s="89"/>
-      <c r="U49" s="89"/>
-      <c r="V49" s="89"/>
-      <c r="W49" s="89"/>
-      <c r="X49" s="89"/>
-      <c r="Y49" s="89"/>
-      <c r="Z49" s="89"/>
-      <c r="AA49" s="89"/>
-      <c r="AB49" s="89"/>
-      <c r="AC49" s="89"/>
-      <c r="AD49" s="89"/>
-      <c r="AE49" s="89"/>
-      <c r="AF49" s="89"/>
-      <c r="AG49" s="89"/>
-      <c r="AH49" s="89"/>
-      <c r="AK49" s="212" t="s">
+      <c r="T49" s="120"/>
+      <c r="U49" s="120"/>
+      <c r="V49" s="120"/>
+      <c r="W49" s="120"/>
+      <c r="X49" s="120"/>
+      <c r="Y49" s="120"/>
+      <c r="Z49" s="120"/>
+      <c r="AA49" s="120"/>
+      <c r="AB49" s="120"/>
+      <c r="AC49" s="120"/>
+      <c r="AD49" s="120"/>
+      <c r="AE49" s="120"/>
+      <c r="AF49" s="120"/>
+      <c r="AG49" s="120"/>
+      <c r="AH49" s="120"/>
+      <c r="AK49" s="119" t="s">
         <v>792</v>
       </c>
-      <c r="AL49" s="212"/>
-      <c r="AM49" s="212"/>
-      <c r="AN49" s="212"/>
-      <c r="AO49" s="212"/>
-      <c r="AP49" s="212"/>
-      <c r="AQ49" s="212"/>
-      <c r="AR49" s="212"/>
-      <c r="AS49" s="212"/>
-      <c r="AT49" s="212"/>
-      <c r="AU49" s="212"/>
-      <c r="AV49" s="212"/>
-      <c r="AW49" s="212"/>
-      <c r="AX49" s="212"/>
-      <c r="AY49" s="212"/>
-      <c r="AZ49" s="212"/>
+      <c r="AL49" s="119"/>
+      <c r="AM49" s="119"/>
+      <c r="AN49" s="119"/>
+      <c r="AO49" s="119"/>
+      <c r="AP49" s="119"/>
+      <c r="AQ49" s="119"/>
+      <c r="AR49" s="119"/>
+      <c r="AS49" s="119"/>
+      <c r="AT49" s="119"/>
+      <c r="AU49" s="119"/>
+      <c r="AV49" s="119"/>
+      <c r="AW49" s="119"/>
+      <c r="AX49" s="119"/>
+      <c r="AY49" s="119"/>
+      <c r="AZ49" s="119"/>
     </row>
     <row r="50" spans="1:52" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
@@ -9552,6 +9556,153 @@
   </sortState>
   <dataConsolidate function="count"/>
   <mergeCells count="171">
+    <mergeCell ref="S49:U49"/>
+    <mergeCell ref="V49:AH49"/>
+    <mergeCell ref="BD21:BE21"/>
+    <mergeCell ref="BD23:BE23"/>
+    <mergeCell ref="BD25:BE25"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="K12:AZ12"/>
+    <mergeCell ref="AH37:AZ37"/>
+    <mergeCell ref="AH38:AZ38"/>
+    <mergeCell ref="AH33:AZ34"/>
+    <mergeCell ref="AH35:AZ35"/>
+    <mergeCell ref="K13:AZ13"/>
+    <mergeCell ref="AE9:AK9"/>
+    <mergeCell ref="A14:AZ14"/>
+    <mergeCell ref="A16:AZ16"/>
+    <mergeCell ref="AV17:AZ17"/>
+    <mergeCell ref="AQ17:AU17"/>
+    <mergeCell ref="AL17:AP17"/>
+    <mergeCell ref="AG17:AK17"/>
+    <mergeCell ref="AB17:AF17"/>
+    <mergeCell ref="W17:AA17"/>
+    <mergeCell ref="AV18:AZ18"/>
+    <mergeCell ref="AQ18:AU18"/>
+    <mergeCell ref="AL18:AP18"/>
+    <mergeCell ref="S48:AH48"/>
+    <mergeCell ref="S33:AG34"/>
+    <mergeCell ref="AH36:AZ36"/>
+    <mergeCell ref="A36:R36"/>
+    <mergeCell ref="A37:R37"/>
+    <mergeCell ref="A35:R35"/>
+    <mergeCell ref="S35:AG35"/>
+    <mergeCell ref="A33:R34"/>
+    <mergeCell ref="S42:AG42"/>
+    <mergeCell ref="S41:AG41"/>
+    <mergeCell ref="A44:AZ45"/>
+    <mergeCell ref="A43:AZ43"/>
+    <mergeCell ref="S47:AH47"/>
+    <mergeCell ref="AH39:AZ39"/>
+    <mergeCell ref="S36:AG36"/>
+    <mergeCell ref="A40:R40"/>
+    <mergeCell ref="A42:R42"/>
+    <mergeCell ref="S39:AG39"/>
+    <mergeCell ref="S38:AG38"/>
+    <mergeCell ref="S37:AG37"/>
+    <mergeCell ref="AH42:AZ42"/>
+    <mergeCell ref="AH41:AZ41"/>
+    <mergeCell ref="AH40:AZ40"/>
+    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="R25:V25"/>
+    <mergeCell ref="AV24:AZ24"/>
+    <mergeCell ref="AV25:AZ25"/>
+    <mergeCell ref="AQ24:AU24"/>
+    <mergeCell ref="AQ25:AU25"/>
+    <mergeCell ref="W24:AA24"/>
+    <mergeCell ref="W25:AA25"/>
+    <mergeCell ref="AL24:AP24"/>
+    <mergeCell ref="AL25:AP25"/>
+    <mergeCell ref="AB25:AF25"/>
+    <mergeCell ref="AG25:AK25"/>
+    <mergeCell ref="A38:R38"/>
+    <mergeCell ref="AR7:AU7"/>
+    <mergeCell ref="AE8:AK8"/>
+    <mergeCell ref="AV7:AZ7"/>
+    <mergeCell ref="S40:AG40"/>
+    <mergeCell ref="A39:R39"/>
+    <mergeCell ref="R19:V19"/>
+    <mergeCell ref="R20:V20"/>
+    <mergeCell ref="R21:V21"/>
+    <mergeCell ref="R22:V22"/>
+    <mergeCell ref="R23:V23"/>
+    <mergeCell ref="R24:V24"/>
+    <mergeCell ref="AG20:AK20"/>
+    <mergeCell ref="AG21:AK21"/>
+    <mergeCell ref="AG22:AK22"/>
+    <mergeCell ref="AG23:AK23"/>
+    <mergeCell ref="AG18:AK18"/>
+    <mergeCell ref="AB18:AF18"/>
+    <mergeCell ref="AB21:AF21"/>
+    <mergeCell ref="W18:AA18"/>
+    <mergeCell ref="A15:AZ15"/>
+    <mergeCell ref="AG24:AK24"/>
+    <mergeCell ref="AV20:AZ20"/>
+    <mergeCell ref="AV21:AZ21"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="AS1:AZ3"/>
+    <mergeCell ref="G6:AZ6"/>
+    <mergeCell ref="K2:AP2"/>
+    <mergeCell ref="A4:AZ4"/>
+    <mergeCell ref="AL9:AZ9"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="R17:V17"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="AE5:AK5"/>
+    <mergeCell ref="G5:AB5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="G8:AC8"/>
+    <mergeCell ref="V7:Y7"/>
+    <mergeCell ref="G9:AC9"/>
+    <mergeCell ref="AL8:AZ8"/>
+    <mergeCell ref="AL5:AZ5"/>
+    <mergeCell ref="AB23:AF23"/>
+    <mergeCell ref="AB24:AF24"/>
+    <mergeCell ref="Z7:AP7"/>
+    <mergeCell ref="AV23:AZ23"/>
+    <mergeCell ref="AQ19:AU19"/>
+    <mergeCell ref="AQ20:AU20"/>
+    <mergeCell ref="AQ21:AU21"/>
+    <mergeCell ref="AQ22:AU22"/>
+    <mergeCell ref="AQ23:AU23"/>
+    <mergeCell ref="W20:AA20"/>
+    <mergeCell ref="W21:AA21"/>
+    <mergeCell ref="W22:AA22"/>
+    <mergeCell ref="W23:AA23"/>
+    <mergeCell ref="AL19:AP19"/>
+    <mergeCell ref="AL20:AP20"/>
+    <mergeCell ref="AL21:AP21"/>
+    <mergeCell ref="AL22:AP22"/>
+    <mergeCell ref="AL23:AP23"/>
+    <mergeCell ref="AG19:AK19"/>
+    <mergeCell ref="A47:P47"/>
+    <mergeCell ref="AK47:AZ47"/>
+    <mergeCell ref="AK48:AZ48"/>
+    <mergeCell ref="A48:P48"/>
+    <mergeCell ref="AK49:AZ49"/>
+    <mergeCell ref="A49:P49"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="M23:Q23"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="AB19:AF19"/>
+    <mergeCell ref="AB20:AF20"/>
+    <mergeCell ref="W19:AA19"/>
+    <mergeCell ref="AB22:AF22"/>
     <mergeCell ref="R18:V18"/>
     <mergeCell ref="M18:Q18"/>
     <mergeCell ref="A18:L18"/>
@@ -9576,153 +9727,6 @@
     <mergeCell ref="AA31:AS31"/>
     <mergeCell ref="AT31:AZ31"/>
     <mergeCell ref="AV22:AZ22"/>
-    <mergeCell ref="A47:P47"/>
-    <mergeCell ref="AK47:AZ47"/>
-    <mergeCell ref="AK48:AZ48"/>
-    <mergeCell ref="A48:P48"/>
-    <mergeCell ref="AK49:AZ49"/>
-    <mergeCell ref="A49:P49"/>
-    <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="M21:Q21"/>
-    <mergeCell ref="M22:Q22"/>
-    <mergeCell ref="M23:Q23"/>
-    <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="M25:Q25"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A21:L21"/>
-    <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="AB19:AF19"/>
-    <mergeCell ref="AB20:AF20"/>
-    <mergeCell ref="W19:AA19"/>
-    <mergeCell ref="AB22:AF22"/>
-    <mergeCell ref="AB23:AF23"/>
-    <mergeCell ref="AB24:AF24"/>
-    <mergeCell ref="Z7:AP7"/>
-    <mergeCell ref="AV23:AZ23"/>
-    <mergeCell ref="AQ19:AU19"/>
-    <mergeCell ref="AQ20:AU20"/>
-    <mergeCell ref="AQ21:AU21"/>
-    <mergeCell ref="AQ22:AU22"/>
-    <mergeCell ref="AQ23:AU23"/>
-    <mergeCell ref="W20:AA20"/>
-    <mergeCell ref="W21:AA21"/>
-    <mergeCell ref="W22:AA22"/>
-    <mergeCell ref="W23:AA23"/>
-    <mergeCell ref="AL19:AP19"/>
-    <mergeCell ref="AL20:AP20"/>
-    <mergeCell ref="AL21:AP21"/>
-    <mergeCell ref="AL22:AP22"/>
-    <mergeCell ref="AL23:AP23"/>
-    <mergeCell ref="AG19:AK19"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="AS1:AZ3"/>
-    <mergeCell ref="G6:AZ6"/>
-    <mergeCell ref="K2:AP2"/>
-    <mergeCell ref="A4:AZ4"/>
-    <mergeCell ref="AL9:AZ9"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="R17:V17"/>
-    <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="AE5:AK5"/>
-    <mergeCell ref="G5:AB5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="G8:AC8"/>
-    <mergeCell ref="V7:Y7"/>
-    <mergeCell ref="G9:AC9"/>
-    <mergeCell ref="AL8:AZ8"/>
-    <mergeCell ref="AL5:AZ5"/>
-    <mergeCell ref="A38:R38"/>
-    <mergeCell ref="AR7:AU7"/>
-    <mergeCell ref="AE8:AK8"/>
-    <mergeCell ref="AV7:AZ7"/>
-    <mergeCell ref="S40:AG40"/>
-    <mergeCell ref="A39:R39"/>
-    <mergeCell ref="R19:V19"/>
-    <mergeCell ref="R20:V20"/>
-    <mergeCell ref="R21:V21"/>
-    <mergeCell ref="R22:V22"/>
-    <mergeCell ref="R23:V23"/>
-    <mergeCell ref="R24:V24"/>
-    <mergeCell ref="AG20:AK20"/>
-    <mergeCell ref="AG21:AK21"/>
-    <mergeCell ref="AG22:AK22"/>
-    <mergeCell ref="AG23:AK23"/>
-    <mergeCell ref="AG18:AK18"/>
-    <mergeCell ref="AB18:AF18"/>
-    <mergeCell ref="AB21:AF21"/>
-    <mergeCell ref="W18:AA18"/>
-    <mergeCell ref="A15:AZ15"/>
-    <mergeCell ref="AG24:AK24"/>
-    <mergeCell ref="AV20:AZ20"/>
-    <mergeCell ref="AV21:AZ21"/>
-    <mergeCell ref="R25:V25"/>
-    <mergeCell ref="AV24:AZ24"/>
-    <mergeCell ref="AV25:AZ25"/>
-    <mergeCell ref="AQ24:AU24"/>
-    <mergeCell ref="AQ25:AU25"/>
-    <mergeCell ref="W24:AA24"/>
-    <mergeCell ref="W25:AA25"/>
-    <mergeCell ref="AL24:AP24"/>
-    <mergeCell ref="AL25:AP25"/>
-    <mergeCell ref="AB25:AF25"/>
-    <mergeCell ref="AG25:AK25"/>
-    <mergeCell ref="S48:AH48"/>
-    <mergeCell ref="S33:AG34"/>
-    <mergeCell ref="AH36:AZ36"/>
-    <mergeCell ref="A36:R36"/>
-    <mergeCell ref="A37:R37"/>
-    <mergeCell ref="A35:R35"/>
-    <mergeCell ref="S35:AG35"/>
-    <mergeCell ref="A33:R34"/>
-    <mergeCell ref="S42:AG42"/>
-    <mergeCell ref="S41:AG41"/>
-    <mergeCell ref="A44:AZ45"/>
-    <mergeCell ref="A43:AZ43"/>
-    <mergeCell ref="S47:AH47"/>
-    <mergeCell ref="AH39:AZ39"/>
-    <mergeCell ref="S36:AG36"/>
-    <mergeCell ref="A40:R40"/>
-    <mergeCell ref="A42:R42"/>
-    <mergeCell ref="S39:AG39"/>
-    <mergeCell ref="S38:AG38"/>
-    <mergeCell ref="S37:AG37"/>
-    <mergeCell ref="AH42:AZ42"/>
-    <mergeCell ref="AH41:AZ41"/>
-    <mergeCell ref="AH40:AZ40"/>
-    <mergeCell ref="A41:R41"/>
-    <mergeCell ref="S49:U49"/>
-    <mergeCell ref="V49:AH49"/>
-    <mergeCell ref="BD21:BE21"/>
-    <mergeCell ref="BD23:BE23"/>
-    <mergeCell ref="BD25:BE25"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="K12:AZ12"/>
-    <mergeCell ref="AH37:AZ37"/>
-    <mergeCell ref="AH38:AZ38"/>
-    <mergeCell ref="AH33:AZ34"/>
-    <mergeCell ref="AH35:AZ35"/>
-    <mergeCell ref="K13:AZ13"/>
-    <mergeCell ref="AE9:AK9"/>
-    <mergeCell ref="A14:AZ14"/>
-    <mergeCell ref="A16:AZ16"/>
-    <mergeCell ref="AV17:AZ17"/>
-    <mergeCell ref="AQ17:AU17"/>
-    <mergeCell ref="AL17:AP17"/>
-    <mergeCell ref="AG17:AK17"/>
-    <mergeCell ref="AB17:AF17"/>
-    <mergeCell ref="W17:AA17"/>
-    <mergeCell ref="AV18:AZ18"/>
-    <mergeCell ref="AQ18:AU18"/>
-    <mergeCell ref="AL18:AP18"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations count="1">
@@ -9762,14 +9766,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="168"/>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="170"/>
+      <c r="A1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="139"/>
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
       <c r="K1" s="21"/>
@@ -9806,87 +9810,87 @@
       <c r="AP1" s="22"/>
       <c r="AQ1" s="22"/>
       <c r="AR1" s="22"/>
-      <c r="AS1" s="177" t="s">
+      <c r="AS1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="AT1" s="178"/>
-      <c r="AU1" s="178"/>
-      <c r="AV1" s="178"/>
-      <c r="AW1" s="178"/>
-      <c r="AX1" s="178"/>
-      <c r="AY1" s="178"/>
-      <c r="AZ1" s="179"/>
+      <c r="AT1" s="147"/>
+      <c r="AU1" s="147"/>
+      <c r="AV1" s="147"/>
+      <c r="AW1" s="147"/>
+      <c r="AX1" s="147"/>
+      <c r="AY1" s="147"/>
+      <c r="AZ1" s="148"/>
       <c r="BD1" s="23"/>
       <c r="BF1" s="27"/>
       <c r="BG1" s="27"/>
     </row>
     <row r="2" spans="1:60" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="171"/>
-      <c r="B2" s="172"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="173"/>
-      <c r="K2" s="187" t="s">
+      <c r="A2" s="140"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="142"/>
+      <c r="K2" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="252"/>
-      <c r="M2" s="252"/>
-      <c r="N2" s="252"/>
-      <c r="O2" s="252"/>
-      <c r="P2" s="252"/>
-      <c r="Q2" s="252"/>
-      <c r="R2" s="252"/>
-      <c r="S2" s="252"/>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252"/>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
-      <c r="AA2" s="252"/>
-      <c r="AB2" s="252"/>
-      <c r="AC2" s="252"/>
-      <c r="AD2" s="252"/>
-      <c r="AE2" s="252"/>
-      <c r="AF2" s="252"/>
-      <c r="AG2" s="252"/>
-      <c r="AH2" s="252"/>
-      <c r="AI2" s="252"/>
-      <c r="AJ2" s="252"/>
-      <c r="AK2" s="252"/>
-      <c r="AL2" s="252"/>
-      <c r="AM2" s="252"/>
-      <c r="AN2" s="252"/>
-      <c r="AO2" s="252"/>
-      <c r="AP2" s="252"/>
+      <c r="L2" s="249"/>
+      <c r="M2" s="249"/>
+      <c r="N2" s="249"/>
+      <c r="O2" s="249"/>
+      <c r="P2" s="249"/>
+      <c r="Q2" s="249"/>
+      <c r="R2" s="249"/>
+      <c r="S2" s="249"/>
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
+      <c r="AA2" s="249"/>
+      <c r="AB2" s="249"/>
+      <c r="AC2" s="249"/>
+      <c r="AD2" s="249"/>
+      <c r="AE2" s="249"/>
+      <c r="AF2" s="249"/>
+      <c r="AG2" s="249"/>
+      <c r="AH2" s="249"/>
+      <c r="AI2" s="249"/>
+      <c r="AJ2" s="249"/>
+      <c r="AK2" s="249"/>
+      <c r="AL2" s="249"/>
+      <c r="AM2" s="249"/>
+      <c r="AN2" s="249"/>
+      <c r="AO2" s="249"/>
+      <c r="AP2" s="249"/>
       <c r="AQ2" s="17"/>
       <c r="AR2" s="17"/>
-      <c r="AS2" s="180"/>
-      <c r="AT2" s="181"/>
-      <c r="AU2" s="181"/>
-      <c r="AV2" s="181"/>
-      <c r="AW2" s="181"/>
-      <c r="AX2" s="181"/>
-      <c r="AY2" s="181"/>
-      <c r="AZ2" s="182"/>
+      <c r="AS2" s="149"/>
+      <c r="AT2" s="150"/>
+      <c r="AU2" s="150"/>
+      <c r="AV2" s="150"/>
+      <c r="AW2" s="150"/>
+      <c r="AX2" s="150"/>
+      <c r="AY2" s="150"/>
+      <c r="AZ2" s="151"/>
       <c r="BA2" s="7"/>
       <c r="BF2" s="25"/>
       <c r="BG2" s="25"/>
       <c r="BH2" s="25"/>
     </row>
     <row r="3" spans="1:60" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="174"/>
-      <c r="B3" s="175"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="176"/>
+      <c r="A3" s="143"/>
+      <c r="B3" s="144"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="145"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -9923,80 +9927,80 @@
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
       <c r="AR3" s="4"/>
-      <c r="AS3" s="183"/>
-      <c r="AT3" s="184"/>
-      <c r="AU3" s="184"/>
-      <c r="AV3" s="184"/>
-      <c r="AW3" s="184"/>
-      <c r="AX3" s="184"/>
-      <c r="AY3" s="184"/>
-      <c r="AZ3" s="185"/>
+      <c r="AS3" s="152"/>
+      <c r="AT3" s="153"/>
+      <c r="AU3" s="153"/>
+      <c r="AV3" s="153"/>
+      <c r="AW3" s="153"/>
+      <c r="AX3" s="153"/>
+      <c r="AY3" s="153"/>
+      <c r="AZ3" s="154"/>
     </row>
     <row r="4" spans="1:60" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="189" t="s">
+      <c r="A4" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="190"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="190"/>
-      <c r="K4" s="190"/>
-      <c r="L4" s="190"/>
-      <c r="M4" s="190"/>
-      <c r="N4" s="190"/>
-      <c r="O4" s="190"/>
-      <c r="P4" s="190"/>
-      <c r="Q4" s="190"/>
-      <c r="R4" s="190"/>
-      <c r="S4" s="190"/>
-      <c r="T4" s="190"/>
-      <c r="U4" s="190"/>
-      <c r="V4" s="190"/>
-      <c r="W4" s="190"/>
-      <c r="X4" s="190"/>
-      <c r="Y4" s="190"/>
-      <c r="Z4" s="190"/>
-      <c r="AA4" s="190"/>
-      <c r="AB4" s="190"/>
-      <c r="AC4" s="190"/>
-      <c r="AD4" s="190"/>
-      <c r="AE4" s="190"/>
-      <c r="AF4" s="190"/>
-      <c r="AG4" s="190"/>
-      <c r="AH4" s="190"/>
-      <c r="AI4" s="190"/>
-      <c r="AJ4" s="190"/>
-      <c r="AK4" s="190"/>
-      <c r="AL4" s="190"/>
-      <c r="AM4" s="190"/>
-      <c r="AN4" s="190"/>
-      <c r="AO4" s="190"/>
-      <c r="AP4" s="190"/>
-      <c r="AQ4" s="190"/>
-      <c r="AR4" s="190"/>
-      <c r="AS4" s="190"/>
-      <c r="AT4" s="190"/>
-      <c r="AU4" s="190"/>
-      <c r="AV4" s="190"/>
-      <c r="AW4" s="190"/>
-      <c r="AX4" s="190"/>
-      <c r="AY4" s="190"/>
-      <c r="AZ4" s="191"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="101"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="101"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="101"/>
+      <c r="S4" s="101"/>
+      <c r="T4" s="101"/>
+      <c r="U4" s="101"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="101"/>
+      <c r="X4" s="101"/>
+      <c r="Y4" s="101"/>
+      <c r="Z4" s="101"/>
+      <c r="AA4" s="101"/>
+      <c r="AB4" s="101"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="101"/>
+      <c r="AE4" s="101"/>
+      <c r="AF4" s="101"/>
+      <c r="AG4" s="101"/>
+      <c r="AH4" s="101"/>
+      <c r="AI4" s="101"/>
+      <c r="AJ4" s="101"/>
+      <c r="AK4" s="101"/>
+      <c r="AL4" s="101"/>
+      <c r="AM4" s="101"/>
+      <c r="AN4" s="101"/>
+      <c r="AO4" s="101"/>
+      <c r="AP4" s="101"/>
+      <c r="AQ4" s="101"/>
+      <c r="AR4" s="101"/>
+      <c r="AS4" s="101"/>
+      <c r="AT4" s="101"/>
+      <c r="AU4" s="101"/>
+      <c r="AV4" s="101"/>
+      <c r="AW4" s="101"/>
+      <c r="AX4" s="101"/>
+      <c r="AY4" s="101"/>
+      <c r="AZ4" s="102"/>
       <c r="BA4" s="9"/>
       <c r="BB4" s="9"/>
       <c r="BC4" s="9"/>
     </row>
     <row r="5" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="253" t="s">
+      <c r="A5" s="250" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="254"/>
-      <c r="C5" s="254"/>
+      <c r="B5" s="251"/>
+      <c r="C5" s="251"/>
       <c r="D5" s="11"/>
       <c r="E5" s="6" t="s">
         <v>105</v>
@@ -10053,63 +10057,63 @@
       <c r="BC5" s="9"/>
     </row>
     <row r="6" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="248"/>
-      <c r="B6" s="249"/>
-      <c r="C6" s="249"/>
+      <c r="A6" s="247"/>
+      <c r="B6" s="248"/>
+      <c r="C6" s="248"/>
       <c r="D6" s="10"/>
-      <c r="E6" s="255"/>
-      <c r="F6" s="255"/>
-      <c r="G6" s="255"/>
-      <c r="H6" s="255"/>
-      <c r="I6" s="255"/>
-      <c r="J6" s="255"/>
-      <c r="K6" s="255"/>
-      <c r="L6" s="255"/>
-      <c r="M6" s="255"/>
-      <c r="N6" s="255"/>
-      <c r="O6" s="255"/>
-      <c r="P6" s="255"/>
-      <c r="Q6" s="255"/>
-      <c r="R6" s="255"/>
-      <c r="S6" s="255"/>
-      <c r="T6" s="255"/>
-      <c r="U6" s="255"/>
-      <c r="V6" s="255"/>
-      <c r="W6" s="255"/>
-      <c r="X6" s="255"/>
-      <c r="Y6" s="255"/>
-      <c r="Z6" s="255"/>
-      <c r="AA6" s="255"/>
-      <c r="AB6" s="255"/>
-      <c r="AC6" s="255"/>
-      <c r="AD6" s="255"/>
-      <c r="AE6" s="255"/>
-      <c r="AF6" s="255"/>
-      <c r="AG6" s="255"/>
-      <c r="AH6" s="255"/>
-      <c r="AI6" s="255"/>
-      <c r="AJ6" s="255"/>
-      <c r="AK6" s="255"/>
-      <c r="AL6" s="255"/>
-      <c r="AM6" s="255"/>
-      <c r="AN6" s="255"/>
-      <c r="AO6" s="255"/>
-      <c r="AP6" s="255"/>
-      <c r="AQ6" s="255"/>
-      <c r="AR6" s="255"/>
-      <c r="AS6" s="255"/>
-      <c r="AT6" s="255"/>
-      <c r="AU6" s="255"/>
-      <c r="AV6" s="255"/>
-      <c r="AW6" s="255"/>
-      <c r="AX6" s="255"/>
-      <c r="AY6" s="255"/>
-      <c r="AZ6" s="256"/>
+      <c r="E6" s="252"/>
+      <c r="F6" s="252"/>
+      <c r="G6" s="252"/>
+      <c r="H6" s="252"/>
+      <c r="I6" s="252"/>
+      <c r="J6" s="252"/>
+      <c r="K6" s="252"/>
+      <c r="L6" s="252"/>
+      <c r="M6" s="252"/>
+      <c r="N6" s="252"/>
+      <c r="O6" s="252"/>
+      <c r="P6" s="252"/>
+      <c r="Q6" s="252"/>
+      <c r="R6" s="252"/>
+      <c r="S6" s="252"/>
+      <c r="T6" s="252"/>
+      <c r="U6" s="252"/>
+      <c r="V6" s="252"/>
+      <c r="W6" s="252"/>
+      <c r="X6" s="252"/>
+      <c r="Y6" s="252"/>
+      <c r="Z6" s="252"/>
+      <c r="AA6" s="252"/>
+      <c r="AB6" s="252"/>
+      <c r="AC6" s="252"/>
+      <c r="AD6" s="252"/>
+      <c r="AE6" s="252"/>
+      <c r="AF6" s="252"/>
+      <c r="AG6" s="252"/>
+      <c r="AH6" s="252"/>
+      <c r="AI6" s="252"/>
+      <c r="AJ6" s="252"/>
+      <c r="AK6" s="252"/>
+      <c r="AL6" s="252"/>
+      <c r="AM6" s="252"/>
+      <c r="AN6" s="252"/>
+      <c r="AO6" s="252"/>
+      <c r="AP6" s="252"/>
+      <c r="AQ6" s="252"/>
+      <c r="AR6" s="252"/>
+      <c r="AS6" s="252"/>
+      <c r="AT6" s="252"/>
+      <c r="AU6" s="252"/>
+      <c r="AV6" s="252"/>
+      <c r="AW6" s="252"/>
+      <c r="AX6" s="252"/>
+      <c r="AY6" s="252"/>
+      <c r="AZ6" s="253"/>
     </row>
     <row r="7" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="248"/>
-      <c r="B7" s="249"/>
-      <c r="C7" s="249"/>
+      <c r="A7" s="247"/>
+      <c r="B7" s="248"/>
+      <c r="C7" s="248"/>
       <c r="D7" s="10"/>
       <c r="E7" s="86"/>
       <c r="F7" s="87"/>
@@ -10161,9 +10165,9 @@
       <c r="AZ7" s="88"/>
     </row>
     <row r="8" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="257"/>
-      <c r="B8" s="258"/>
-      <c r="C8" s="258"/>
+      <c r="A8" s="245"/>
+      <c r="B8" s="246"/>
+      <c r="C8" s="246"/>
       <c r="D8" s="10"/>
       <c r="E8" s="87"/>
       <c r="F8" s="87"/>
@@ -10215,63 +10219,63 @@
       <c r="AZ8" s="88"/>
     </row>
     <row r="9" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="257"/>
-      <c r="B9" s="258"/>
-      <c r="C9" s="258"/>
+      <c r="A9" s="245"/>
+      <c r="B9" s="246"/>
+      <c r="C9" s="246"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="250"/>
-      <c r="F9" s="250"/>
-      <c r="G9" s="250"/>
-      <c r="H9" s="250"/>
-      <c r="I9" s="250"/>
-      <c r="J9" s="250"/>
-      <c r="K9" s="250"/>
-      <c r="L9" s="250"/>
-      <c r="M9" s="250"/>
-      <c r="N9" s="250"/>
-      <c r="O9" s="250"/>
-      <c r="P9" s="250"/>
-      <c r="Q9" s="250"/>
-      <c r="R9" s="250"/>
-      <c r="S9" s="250"/>
-      <c r="T9" s="250"/>
-      <c r="U9" s="250"/>
-      <c r="V9" s="250"/>
-      <c r="W9" s="250"/>
-      <c r="X9" s="250"/>
-      <c r="Y9" s="250"/>
-      <c r="Z9" s="250"/>
-      <c r="AA9" s="250"/>
-      <c r="AB9" s="250"/>
-      <c r="AC9" s="250"/>
-      <c r="AD9" s="250"/>
-      <c r="AE9" s="250"/>
-      <c r="AF9" s="250"/>
-      <c r="AG9" s="250"/>
-      <c r="AH9" s="250"/>
-      <c r="AI9" s="250"/>
-      <c r="AJ9" s="250"/>
-      <c r="AK9" s="250"/>
-      <c r="AL9" s="250"/>
-      <c r="AM9" s="250"/>
-      <c r="AN9" s="250"/>
-      <c r="AO9" s="250"/>
-      <c r="AP9" s="250"/>
-      <c r="AQ9" s="250"/>
-      <c r="AR9" s="250"/>
-      <c r="AS9" s="250"/>
-      <c r="AT9" s="250"/>
-      <c r="AU9" s="250"/>
-      <c r="AV9" s="250"/>
-      <c r="AW9" s="250"/>
-      <c r="AX9" s="250"/>
-      <c r="AY9" s="250"/>
-      <c r="AZ9" s="251"/>
+      <c r="E9" s="254"/>
+      <c r="F9" s="254"/>
+      <c r="G9" s="254"/>
+      <c r="H9" s="254"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="254"/>
+      <c r="K9" s="254"/>
+      <c r="L9" s="254"/>
+      <c r="M9" s="254"/>
+      <c r="N9" s="254"/>
+      <c r="O9" s="254"/>
+      <c r="P9" s="254"/>
+      <c r="Q9" s="254"/>
+      <c r="R9" s="254"/>
+      <c r="S9" s="254"/>
+      <c r="T9" s="254"/>
+      <c r="U9" s="254"/>
+      <c r="V9" s="254"/>
+      <c r="W9" s="254"/>
+      <c r="X9" s="254"/>
+      <c r="Y9" s="254"/>
+      <c r="Z9" s="254"/>
+      <c r="AA9" s="254"/>
+      <c r="AB9" s="254"/>
+      <c r="AC9" s="254"/>
+      <c r="AD9" s="254"/>
+      <c r="AE9" s="254"/>
+      <c r="AF9" s="254"/>
+      <c r="AG9" s="254"/>
+      <c r="AH9" s="254"/>
+      <c r="AI9" s="254"/>
+      <c r="AJ9" s="254"/>
+      <c r="AK9" s="254"/>
+      <c r="AL9" s="254"/>
+      <c r="AM9" s="254"/>
+      <c r="AN9" s="254"/>
+      <c r="AO9" s="254"/>
+      <c r="AP9" s="254"/>
+      <c r="AQ9" s="254"/>
+      <c r="AR9" s="254"/>
+      <c r="AS9" s="254"/>
+      <c r="AT9" s="254"/>
+      <c r="AU9" s="254"/>
+      <c r="AV9" s="254"/>
+      <c r="AW9" s="254"/>
+      <c r="AX9" s="254"/>
+      <c r="AY9" s="254"/>
+      <c r="AZ9" s="255"/>
     </row>
     <row r="10" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="257"/>
-      <c r="B10" s="258"/>
-      <c r="C10" s="258"/>
+      <c r="A10" s="245"/>
+      <c r="B10" s="246"/>
+      <c r="C10" s="246"/>
       <c r="D10" s="10"/>
       <c r="E10" s="86"/>
       <c r="F10" s="87"/>
@@ -10323,9 +10327,9 @@
       <c r="AZ10" s="88"/>
     </row>
     <row r="11" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="248"/>
-      <c r="B11" s="249"/>
-      <c r="C11" s="249"/>
+      <c r="A11" s="247"/>
+      <c r="B11" s="248"/>
+      <c r="C11" s="248"/>
       <c r="D11" s="10"/>
       <c r="E11" s="87"/>
       <c r="F11" s="87"/>
@@ -10377,9 +10381,9 @@
       <c r="AZ11" s="88"/>
     </row>
     <row r="12" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="248"/>
-      <c r="B12" s="249"/>
-      <c r="C12" s="249"/>
+      <c r="A12" s="247"/>
+      <c r="B12" s="248"/>
+      <c r="C12" s="248"/>
       <c r="D12" s="10"/>
       <c r="E12" s="87"/>
       <c r="F12" s="87"/>
@@ -10431,9 +10435,9 @@
       <c r="AZ12" s="88"/>
     </row>
     <row r="13" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="248"/>
-      <c r="B13" s="249"/>
-      <c r="C13" s="249"/>
+      <c r="A13" s="247"/>
+      <c r="B13" s="248"/>
+      <c r="C13" s="248"/>
       <c r="D13" s="10"/>
       <c r="E13" s="87"/>
       <c r="F13" s="87"/>
@@ -10485,9 +10489,9 @@
       <c r="AZ13" s="88"/>
     </row>
     <row r="14" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="248"/>
-      <c r="B14" s="249"/>
-      <c r="C14" s="249"/>
+      <c r="A14" s="247"/>
+      <c r="B14" s="248"/>
+      <c r="C14" s="248"/>
       <c r="D14" s="10"/>
       <c r="E14" s="87"/>
       <c r="F14" s="87"/>
@@ -10539,9 +10543,9 @@
       <c r="AZ14" s="88"/>
     </row>
     <row r="15" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="248"/>
-      <c r="B15" s="249"/>
-      <c r="C15" s="249"/>
+      <c r="A15" s="247"/>
+      <c r="B15" s="248"/>
+      <c r="C15" s="248"/>
       <c r="D15" s="10"/>
       <c r="E15" s="86"/>
       <c r="F15" s="87"/>
@@ -10593,9 +10597,9 @@
       <c r="AZ15" s="88"/>
     </row>
     <row r="16" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="248"/>
-      <c r="B16" s="249"/>
-      <c r="C16" s="249"/>
+      <c r="A16" s="247"/>
+      <c r="B16" s="248"/>
+      <c r="C16" s="248"/>
       <c r="D16" s="10"/>
       <c r="E16" s="86"/>
       <c r="F16" s="87"/>
@@ -10647,9 +10651,9 @@
       <c r="AZ16" s="88"/>
     </row>
     <row r="17" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="248"/>
-      <c r="B17" s="249"/>
-      <c r="C17" s="249"/>
+      <c r="A17" s="247"/>
+      <c r="B17" s="248"/>
+      <c r="C17" s="248"/>
       <c r="D17" s="10"/>
       <c r="E17" s="86"/>
       <c r="F17" s="87"/>
@@ -10701,9 +10705,9 @@
       <c r="AZ17" s="88"/>
     </row>
     <row r="18" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="248"/>
-      <c r="B18" s="249"/>
-      <c r="C18" s="249"/>
+      <c r="A18" s="247"/>
+      <c r="B18" s="248"/>
+      <c r="C18" s="248"/>
       <c r="D18" s="10"/>
       <c r="E18" s="86"/>
       <c r="F18" s="87"/>
@@ -10755,9 +10759,9 @@
       <c r="AZ18" s="88"/>
     </row>
     <row r="19" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="248"/>
-      <c r="B19" s="249"/>
-      <c r="C19" s="249"/>
+      <c r="A19" s="247"/>
+      <c r="B19" s="248"/>
+      <c r="C19" s="248"/>
       <c r="D19" s="10"/>
       <c r="E19" s="86"/>
       <c r="F19" s="87"/>
@@ -10809,9 +10813,9 @@
       <c r="AZ19" s="88"/>
     </row>
     <row r="20" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="248"/>
-      <c r="B20" s="249"/>
-      <c r="C20" s="249"/>
+      <c r="A20" s="247"/>
+      <c r="B20" s="248"/>
+      <c r="C20" s="248"/>
       <c r="D20" s="10"/>
       <c r="E20" s="86"/>
       <c r="F20" s="87"/>
@@ -10863,9 +10867,9 @@
       <c r="AZ20" s="88"/>
     </row>
     <row r="21" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="248"/>
-      <c r="B21" s="249"/>
-      <c r="C21" s="249"/>
+      <c r="A21" s="247"/>
+      <c r="B21" s="248"/>
+      <c r="C21" s="248"/>
       <c r="D21" s="10"/>
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
@@ -10917,9 +10921,9 @@
       <c r="AZ21" s="88"/>
     </row>
     <row r="22" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="248"/>
-      <c r="B22" s="249"/>
-      <c r="C22" s="249"/>
+      <c r="A22" s="247"/>
+      <c r="B22" s="248"/>
+      <c r="C22" s="248"/>
       <c r="D22" s="10"/>
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
@@ -10971,9 +10975,9 @@
       <c r="AZ22" s="88"/>
     </row>
     <row r="23" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="248"/>
-      <c r="B23" s="249"/>
-      <c r="C23" s="249"/>
+      <c r="A23" s="247"/>
+      <c r="B23" s="248"/>
+      <c r="C23" s="248"/>
       <c r="D23" s="10"/>
       <c r="E23" s="86"/>
       <c r="F23" s="87"/>
@@ -11025,9 +11029,9 @@
       <c r="AZ23" s="88"/>
     </row>
     <row r="24" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="248"/>
-      <c r="B24" s="249"/>
-      <c r="C24" s="249"/>
+      <c r="A24" s="247"/>
+      <c r="B24" s="248"/>
+      <c r="C24" s="248"/>
       <c r="D24" s="10"/>
       <c r="E24" s="87"/>
       <c r="F24" s="87"/>
@@ -11079,9 +11083,9 @@
       <c r="AZ24" s="88"/>
     </row>
     <row r="25" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="248"/>
-      <c r="B25" s="249"/>
-      <c r="C25" s="249"/>
+      <c r="A25" s="247"/>
+      <c r="B25" s="248"/>
+      <c r="C25" s="248"/>
       <c r="D25" s="10"/>
       <c r="E25" s="86"/>
       <c r="F25" s="87"/>
@@ -11133,922 +11137,922 @@
       <c r="AZ25" s="88"/>
     </row>
     <row r="26" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="248"/>
-      <c r="B26" s="249"/>
-      <c r="C26" s="249"/>
+      <c r="A26" s="247"/>
+      <c r="B26" s="248"/>
+      <c r="C26" s="248"/>
       <c r="D26" s="10"/>
-      <c r="E26" s="243"/>
-      <c r="F26" s="243"/>
-      <c r="G26" s="243"/>
-      <c r="H26" s="243"/>
-      <c r="I26" s="243"/>
-      <c r="J26" s="243"/>
-      <c r="K26" s="243"/>
-      <c r="L26" s="243"/>
-      <c r="M26" s="243"/>
-      <c r="N26" s="243"/>
-      <c r="O26" s="243"/>
-      <c r="P26" s="243"/>
-      <c r="Q26" s="243"/>
-      <c r="R26" s="243"/>
-      <c r="S26" s="243"/>
-      <c r="T26" s="243"/>
-      <c r="U26" s="243"/>
-      <c r="V26" s="243"/>
-      <c r="W26" s="243"/>
-      <c r="X26" s="243"/>
-      <c r="Y26" s="243"/>
-      <c r="Z26" s="243"/>
-      <c r="AA26" s="243"/>
-      <c r="AB26" s="243"/>
-      <c r="AC26" s="243"/>
-      <c r="AD26" s="243"/>
-      <c r="AE26" s="243"/>
-      <c r="AF26" s="243"/>
-      <c r="AG26" s="243"/>
-      <c r="AH26" s="243"/>
-      <c r="AI26" s="243"/>
-      <c r="AJ26" s="243"/>
-      <c r="AK26" s="243"/>
-      <c r="AL26" s="243"/>
-      <c r="AM26" s="243"/>
-      <c r="AN26" s="243"/>
-      <c r="AO26" s="243"/>
-      <c r="AP26" s="243"/>
-      <c r="AQ26" s="243"/>
-      <c r="AR26" s="243"/>
-      <c r="AS26" s="243"/>
-      <c r="AT26" s="243"/>
-      <c r="AU26" s="243"/>
-      <c r="AV26" s="243"/>
-      <c r="AW26" s="243"/>
-      <c r="AX26" s="243"/>
-      <c r="AY26" s="243"/>
-      <c r="AZ26" s="244"/>
+      <c r="E26" s="256"/>
+      <c r="F26" s="256"/>
+      <c r="G26" s="256"/>
+      <c r="H26" s="256"/>
+      <c r="I26" s="256"/>
+      <c r="J26" s="256"/>
+      <c r="K26" s="256"/>
+      <c r="L26" s="256"/>
+      <c r="M26" s="256"/>
+      <c r="N26" s="256"/>
+      <c r="O26" s="256"/>
+      <c r="P26" s="256"/>
+      <c r="Q26" s="256"/>
+      <c r="R26" s="256"/>
+      <c r="S26" s="256"/>
+      <c r="T26" s="256"/>
+      <c r="U26" s="256"/>
+      <c r="V26" s="256"/>
+      <c r="W26" s="256"/>
+      <c r="X26" s="256"/>
+      <c r="Y26" s="256"/>
+      <c r="Z26" s="256"/>
+      <c r="AA26" s="256"/>
+      <c r="AB26" s="256"/>
+      <c r="AC26" s="256"/>
+      <c r="AD26" s="256"/>
+      <c r="AE26" s="256"/>
+      <c r="AF26" s="256"/>
+      <c r="AG26" s="256"/>
+      <c r="AH26" s="256"/>
+      <c r="AI26" s="256"/>
+      <c r="AJ26" s="256"/>
+      <c r="AK26" s="256"/>
+      <c r="AL26" s="256"/>
+      <c r="AM26" s="256"/>
+      <c r="AN26" s="256"/>
+      <c r="AO26" s="256"/>
+      <c r="AP26" s="256"/>
+      <c r="AQ26" s="256"/>
+      <c r="AR26" s="256"/>
+      <c r="AS26" s="256"/>
+      <c r="AT26" s="256"/>
+      <c r="AU26" s="256"/>
+      <c r="AV26" s="256"/>
+      <c r="AW26" s="256"/>
+      <c r="AX26" s="256"/>
+      <c r="AY26" s="256"/>
+      <c r="AZ26" s="257"/>
     </row>
     <row r="27" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="248"/>
-      <c r="B27" s="249"/>
-      <c r="C27" s="249"/>
+      <c r="A27" s="247"/>
+      <c r="B27" s="248"/>
+      <c r="C27" s="248"/>
       <c r="D27" s="10"/>
-      <c r="E27" s="243"/>
-      <c r="F27" s="243"/>
-      <c r="G27" s="243"/>
-      <c r="H27" s="243"/>
-      <c r="I27" s="243"/>
-      <c r="J27" s="243"/>
-      <c r="K27" s="243"/>
-      <c r="L27" s="243"/>
-      <c r="M27" s="243"/>
-      <c r="N27" s="243"/>
-      <c r="O27" s="243"/>
-      <c r="P27" s="243"/>
-      <c r="Q27" s="243"/>
-      <c r="R27" s="243"/>
-      <c r="S27" s="243"/>
-      <c r="T27" s="243"/>
-      <c r="U27" s="243"/>
-      <c r="V27" s="243"/>
-      <c r="W27" s="243"/>
-      <c r="X27" s="243"/>
-      <c r="Y27" s="243"/>
-      <c r="Z27" s="243"/>
-      <c r="AA27" s="243"/>
-      <c r="AB27" s="243"/>
-      <c r="AC27" s="243"/>
-      <c r="AD27" s="243"/>
-      <c r="AE27" s="243"/>
-      <c r="AF27" s="243"/>
-      <c r="AG27" s="243"/>
-      <c r="AH27" s="243"/>
-      <c r="AI27" s="243"/>
-      <c r="AJ27" s="243"/>
-      <c r="AK27" s="243"/>
-      <c r="AL27" s="243"/>
-      <c r="AM27" s="243"/>
-      <c r="AN27" s="243"/>
-      <c r="AO27" s="243"/>
-      <c r="AP27" s="243"/>
-      <c r="AQ27" s="243"/>
-      <c r="AR27" s="243"/>
-      <c r="AS27" s="243"/>
-      <c r="AT27" s="243"/>
-      <c r="AU27" s="243"/>
-      <c r="AV27" s="243"/>
-      <c r="AW27" s="243"/>
-      <c r="AX27" s="243"/>
-      <c r="AY27" s="243"/>
-      <c r="AZ27" s="244"/>
+      <c r="E27" s="256"/>
+      <c r="F27" s="256"/>
+      <c r="G27" s="256"/>
+      <c r="H27" s="256"/>
+      <c r="I27" s="256"/>
+      <c r="J27" s="256"/>
+      <c r="K27" s="256"/>
+      <c r="L27" s="256"/>
+      <c r="M27" s="256"/>
+      <c r="N27" s="256"/>
+      <c r="O27" s="256"/>
+      <c r="P27" s="256"/>
+      <c r="Q27" s="256"/>
+      <c r="R27" s="256"/>
+      <c r="S27" s="256"/>
+      <c r="T27" s="256"/>
+      <c r="U27" s="256"/>
+      <c r="V27" s="256"/>
+      <c r="W27" s="256"/>
+      <c r="X27" s="256"/>
+      <c r="Y27" s="256"/>
+      <c r="Z27" s="256"/>
+      <c r="AA27" s="256"/>
+      <c r="AB27" s="256"/>
+      <c r="AC27" s="256"/>
+      <c r="AD27" s="256"/>
+      <c r="AE27" s="256"/>
+      <c r="AF27" s="256"/>
+      <c r="AG27" s="256"/>
+      <c r="AH27" s="256"/>
+      <c r="AI27" s="256"/>
+      <c r="AJ27" s="256"/>
+      <c r="AK27" s="256"/>
+      <c r="AL27" s="256"/>
+      <c r="AM27" s="256"/>
+      <c r="AN27" s="256"/>
+      <c r="AO27" s="256"/>
+      <c r="AP27" s="256"/>
+      <c r="AQ27" s="256"/>
+      <c r="AR27" s="256"/>
+      <c r="AS27" s="256"/>
+      <c r="AT27" s="256"/>
+      <c r="AU27" s="256"/>
+      <c r="AV27" s="256"/>
+      <c r="AW27" s="256"/>
+      <c r="AX27" s="256"/>
+      <c r="AY27" s="256"/>
+      <c r="AZ27" s="257"/>
     </row>
     <row r="28" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="248"/>
-      <c r="B28" s="249"/>
-      <c r="C28" s="249"/>
+      <c r="A28" s="247"/>
+      <c r="B28" s="248"/>
+      <c r="C28" s="248"/>
       <c r="D28" s="10"/>
-      <c r="E28" s="243"/>
-      <c r="F28" s="243"/>
-      <c r="G28" s="243"/>
-      <c r="H28" s="243"/>
-      <c r="I28" s="243"/>
-      <c r="J28" s="243"/>
-      <c r="K28" s="243"/>
-      <c r="L28" s="243"/>
-      <c r="M28" s="243"/>
-      <c r="N28" s="243"/>
-      <c r="O28" s="243"/>
-      <c r="P28" s="243"/>
-      <c r="Q28" s="243"/>
-      <c r="R28" s="243"/>
-      <c r="S28" s="243"/>
-      <c r="T28" s="243"/>
-      <c r="U28" s="243"/>
-      <c r="V28" s="243"/>
-      <c r="W28" s="243"/>
-      <c r="X28" s="243"/>
-      <c r="Y28" s="243"/>
-      <c r="Z28" s="243"/>
-      <c r="AA28" s="243"/>
-      <c r="AB28" s="243"/>
-      <c r="AC28" s="243"/>
-      <c r="AD28" s="243"/>
-      <c r="AE28" s="243"/>
-      <c r="AF28" s="243"/>
-      <c r="AG28" s="243"/>
-      <c r="AH28" s="243"/>
-      <c r="AI28" s="243"/>
-      <c r="AJ28" s="243"/>
-      <c r="AK28" s="243"/>
-      <c r="AL28" s="243"/>
-      <c r="AM28" s="243"/>
-      <c r="AN28" s="243"/>
-      <c r="AO28" s="243"/>
-      <c r="AP28" s="243"/>
-      <c r="AQ28" s="243"/>
-      <c r="AR28" s="243"/>
-      <c r="AS28" s="243"/>
-      <c r="AT28" s="243"/>
-      <c r="AU28" s="243"/>
-      <c r="AV28" s="243"/>
-      <c r="AW28" s="243"/>
-      <c r="AX28" s="243"/>
-      <c r="AY28" s="243"/>
-      <c r="AZ28" s="244"/>
+      <c r="E28" s="256"/>
+      <c r="F28" s="256"/>
+      <c r="G28" s="256"/>
+      <c r="H28" s="256"/>
+      <c r="I28" s="256"/>
+      <c r="J28" s="256"/>
+      <c r="K28" s="256"/>
+      <c r="L28" s="256"/>
+      <c r="M28" s="256"/>
+      <c r="N28" s="256"/>
+      <c r="O28" s="256"/>
+      <c r="P28" s="256"/>
+      <c r="Q28" s="256"/>
+      <c r="R28" s="256"/>
+      <c r="S28" s="256"/>
+      <c r="T28" s="256"/>
+      <c r="U28" s="256"/>
+      <c r="V28" s="256"/>
+      <c r="W28" s="256"/>
+      <c r="X28" s="256"/>
+      <c r="Y28" s="256"/>
+      <c r="Z28" s="256"/>
+      <c r="AA28" s="256"/>
+      <c r="AB28" s="256"/>
+      <c r="AC28" s="256"/>
+      <c r="AD28" s="256"/>
+      <c r="AE28" s="256"/>
+      <c r="AF28" s="256"/>
+      <c r="AG28" s="256"/>
+      <c r="AH28" s="256"/>
+      <c r="AI28" s="256"/>
+      <c r="AJ28" s="256"/>
+      <c r="AK28" s="256"/>
+      <c r="AL28" s="256"/>
+      <c r="AM28" s="256"/>
+      <c r="AN28" s="256"/>
+      <c r="AO28" s="256"/>
+      <c r="AP28" s="256"/>
+      <c r="AQ28" s="256"/>
+      <c r="AR28" s="256"/>
+      <c r="AS28" s="256"/>
+      <c r="AT28" s="256"/>
+      <c r="AU28" s="256"/>
+      <c r="AV28" s="256"/>
+      <c r="AW28" s="256"/>
+      <c r="AX28" s="256"/>
+      <c r="AY28" s="256"/>
+      <c r="AZ28" s="257"/>
     </row>
     <row r="29" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="248"/>
-      <c r="B29" s="249"/>
-      <c r="C29" s="249"/>
+      <c r="A29" s="247"/>
+      <c r="B29" s="248"/>
+      <c r="C29" s="248"/>
       <c r="D29" s="10"/>
-      <c r="E29" s="243"/>
-      <c r="F29" s="243"/>
-      <c r="G29" s="243"/>
-      <c r="H29" s="243"/>
-      <c r="I29" s="243"/>
-      <c r="J29" s="243"/>
-      <c r="K29" s="243"/>
-      <c r="L29" s="243"/>
-      <c r="M29" s="243"/>
-      <c r="N29" s="243"/>
-      <c r="O29" s="243"/>
-      <c r="P29" s="243"/>
-      <c r="Q29" s="243"/>
-      <c r="R29" s="243"/>
-      <c r="S29" s="243"/>
-      <c r="T29" s="243"/>
-      <c r="U29" s="243"/>
-      <c r="V29" s="243"/>
-      <c r="W29" s="243"/>
-      <c r="X29" s="243"/>
-      <c r="Y29" s="243"/>
-      <c r="Z29" s="243"/>
-      <c r="AA29" s="243"/>
-      <c r="AB29" s="243"/>
-      <c r="AC29" s="243"/>
-      <c r="AD29" s="243"/>
-      <c r="AE29" s="243"/>
-      <c r="AF29" s="243"/>
-      <c r="AG29" s="243"/>
-      <c r="AH29" s="243"/>
-      <c r="AI29" s="243"/>
-      <c r="AJ29" s="243"/>
-      <c r="AK29" s="243"/>
-      <c r="AL29" s="243"/>
-      <c r="AM29" s="243"/>
-      <c r="AN29" s="243"/>
-      <c r="AO29" s="243"/>
-      <c r="AP29" s="243"/>
-      <c r="AQ29" s="243"/>
-      <c r="AR29" s="243"/>
-      <c r="AS29" s="243"/>
-      <c r="AT29" s="243"/>
-      <c r="AU29" s="243"/>
-      <c r="AV29" s="243"/>
-      <c r="AW29" s="243"/>
-      <c r="AX29" s="243"/>
-      <c r="AY29" s="243"/>
-      <c r="AZ29" s="244"/>
+      <c r="E29" s="256"/>
+      <c r="F29" s="256"/>
+      <c r="G29" s="256"/>
+      <c r="H29" s="256"/>
+      <c r="I29" s="256"/>
+      <c r="J29" s="256"/>
+      <c r="K29" s="256"/>
+      <c r="L29" s="256"/>
+      <c r="M29" s="256"/>
+      <c r="N29" s="256"/>
+      <c r="O29" s="256"/>
+      <c r="P29" s="256"/>
+      <c r="Q29" s="256"/>
+      <c r="R29" s="256"/>
+      <c r="S29" s="256"/>
+      <c r="T29" s="256"/>
+      <c r="U29" s="256"/>
+      <c r="V29" s="256"/>
+      <c r="W29" s="256"/>
+      <c r="X29" s="256"/>
+      <c r="Y29" s="256"/>
+      <c r="Z29" s="256"/>
+      <c r="AA29" s="256"/>
+      <c r="AB29" s="256"/>
+      <c r="AC29" s="256"/>
+      <c r="AD29" s="256"/>
+      <c r="AE29" s="256"/>
+      <c r="AF29" s="256"/>
+      <c r="AG29" s="256"/>
+      <c r="AH29" s="256"/>
+      <c r="AI29" s="256"/>
+      <c r="AJ29" s="256"/>
+      <c r="AK29" s="256"/>
+      <c r="AL29" s="256"/>
+      <c r="AM29" s="256"/>
+      <c r="AN29" s="256"/>
+      <c r="AO29" s="256"/>
+      <c r="AP29" s="256"/>
+      <c r="AQ29" s="256"/>
+      <c r="AR29" s="256"/>
+      <c r="AS29" s="256"/>
+      <c r="AT29" s="256"/>
+      <c r="AU29" s="256"/>
+      <c r="AV29" s="256"/>
+      <c r="AW29" s="256"/>
+      <c r="AX29" s="256"/>
+      <c r="AY29" s="256"/>
+      <c r="AZ29" s="257"/>
     </row>
     <row r="30" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="248"/>
-      <c r="B30" s="249"/>
-      <c r="C30" s="249"/>
+      <c r="A30" s="247"/>
+      <c r="B30" s="248"/>
+      <c r="C30" s="248"/>
       <c r="D30" s="10"/>
-      <c r="E30" s="243"/>
-      <c r="F30" s="243"/>
-      <c r="G30" s="243"/>
-      <c r="H30" s="243"/>
-      <c r="I30" s="243"/>
-      <c r="J30" s="243"/>
-      <c r="K30" s="243"/>
-      <c r="L30" s="243"/>
-      <c r="M30" s="243"/>
-      <c r="N30" s="243"/>
-      <c r="O30" s="243"/>
-      <c r="P30" s="243"/>
-      <c r="Q30" s="243"/>
-      <c r="R30" s="243"/>
-      <c r="S30" s="243"/>
-      <c r="T30" s="243"/>
-      <c r="U30" s="243"/>
-      <c r="V30" s="243"/>
-      <c r="W30" s="243"/>
-      <c r="X30" s="243"/>
-      <c r="Y30" s="243"/>
-      <c r="Z30" s="243"/>
-      <c r="AA30" s="243"/>
-      <c r="AB30" s="243"/>
-      <c r="AC30" s="243"/>
-      <c r="AD30" s="243"/>
-      <c r="AE30" s="243"/>
-      <c r="AF30" s="243"/>
-      <c r="AG30" s="243"/>
-      <c r="AH30" s="243"/>
-      <c r="AI30" s="243"/>
-      <c r="AJ30" s="243"/>
-      <c r="AK30" s="243"/>
-      <c r="AL30" s="243"/>
-      <c r="AM30" s="243"/>
-      <c r="AN30" s="243"/>
-      <c r="AO30" s="243"/>
-      <c r="AP30" s="243"/>
-      <c r="AQ30" s="243"/>
-      <c r="AR30" s="243"/>
-      <c r="AS30" s="243"/>
-      <c r="AT30" s="243"/>
-      <c r="AU30" s="243"/>
-      <c r="AV30" s="243"/>
-      <c r="AW30" s="243"/>
-      <c r="AX30" s="243"/>
-      <c r="AY30" s="243"/>
-      <c r="AZ30" s="244"/>
+      <c r="E30" s="256"/>
+      <c r="F30" s="256"/>
+      <c r="G30" s="256"/>
+      <c r="H30" s="256"/>
+      <c r="I30" s="256"/>
+      <c r="J30" s="256"/>
+      <c r="K30" s="256"/>
+      <c r="L30" s="256"/>
+      <c r="M30" s="256"/>
+      <c r="N30" s="256"/>
+      <c r="O30" s="256"/>
+      <c r="P30" s="256"/>
+      <c r="Q30" s="256"/>
+      <c r="R30" s="256"/>
+      <c r="S30" s="256"/>
+      <c r="T30" s="256"/>
+      <c r="U30" s="256"/>
+      <c r="V30" s="256"/>
+      <c r="W30" s="256"/>
+      <c r="X30" s="256"/>
+      <c r="Y30" s="256"/>
+      <c r="Z30" s="256"/>
+      <c r="AA30" s="256"/>
+      <c r="AB30" s="256"/>
+      <c r="AC30" s="256"/>
+      <c r="AD30" s="256"/>
+      <c r="AE30" s="256"/>
+      <c r="AF30" s="256"/>
+      <c r="AG30" s="256"/>
+      <c r="AH30" s="256"/>
+      <c r="AI30" s="256"/>
+      <c r="AJ30" s="256"/>
+      <c r="AK30" s="256"/>
+      <c r="AL30" s="256"/>
+      <c r="AM30" s="256"/>
+      <c r="AN30" s="256"/>
+      <c r="AO30" s="256"/>
+      <c r="AP30" s="256"/>
+      <c r="AQ30" s="256"/>
+      <c r="AR30" s="256"/>
+      <c r="AS30" s="256"/>
+      <c r="AT30" s="256"/>
+      <c r="AU30" s="256"/>
+      <c r="AV30" s="256"/>
+      <c r="AW30" s="256"/>
+      <c r="AX30" s="256"/>
+      <c r="AY30" s="256"/>
+      <c r="AZ30" s="257"/>
     </row>
     <row r="31" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="248"/>
-      <c r="B31" s="249"/>
-      <c r="C31" s="249"/>
+      <c r="A31" s="247"/>
+      <c r="B31" s="248"/>
+      <c r="C31" s="248"/>
       <c r="D31" s="10"/>
-      <c r="E31" s="243"/>
-      <c r="F31" s="243"/>
-      <c r="G31" s="243"/>
-      <c r="H31" s="243"/>
-      <c r="I31" s="243"/>
-      <c r="J31" s="243"/>
-      <c r="K31" s="243"/>
-      <c r="L31" s="243"/>
-      <c r="M31" s="243"/>
-      <c r="N31" s="243"/>
-      <c r="O31" s="243"/>
-      <c r="P31" s="243"/>
-      <c r="Q31" s="243"/>
-      <c r="R31" s="243"/>
-      <c r="S31" s="243"/>
-      <c r="T31" s="243"/>
-      <c r="U31" s="243"/>
-      <c r="V31" s="243"/>
-      <c r="W31" s="243"/>
-      <c r="X31" s="243"/>
-      <c r="Y31" s="243"/>
-      <c r="Z31" s="243"/>
-      <c r="AA31" s="243"/>
-      <c r="AB31" s="243"/>
-      <c r="AC31" s="243"/>
-      <c r="AD31" s="243"/>
-      <c r="AE31" s="243"/>
-      <c r="AF31" s="243"/>
-      <c r="AG31" s="243"/>
-      <c r="AH31" s="243"/>
-      <c r="AI31" s="243"/>
-      <c r="AJ31" s="243"/>
-      <c r="AK31" s="243"/>
-      <c r="AL31" s="243"/>
-      <c r="AM31" s="243"/>
-      <c r="AN31" s="243"/>
-      <c r="AO31" s="243"/>
-      <c r="AP31" s="243"/>
-      <c r="AQ31" s="243"/>
-      <c r="AR31" s="243"/>
-      <c r="AS31" s="243"/>
-      <c r="AT31" s="243"/>
-      <c r="AU31" s="243"/>
-      <c r="AV31" s="243"/>
-      <c r="AW31" s="243"/>
-      <c r="AX31" s="243"/>
-      <c r="AY31" s="243"/>
-      <c r="AZ31" s="244"/>
+      <c r="E31" s="256"/>
+      <c r="F31" s="256"/>
+      <c r="G31" s="256"/>
+      <c r="H31" s="256"/>
+      <c r="I31" s="256"/>
+      <c r="J31" s="256"/>
+      <c r="K31" s="256"/>
+      <c r="L31" s="256"/>
+      <c r="M31" s="256"/>
+      <c r="N31" s="256"/>
+      <c r="O31" s="256"/>
+      <c r="P31" s="256"/>
+      <c r="Q31" s="256"/>
+      <c r="R31" s="256"/>
+      <c r="S31" s="256"/>
+      <c r="T31" s="256"/>
+      <c r="U31" s="256"/>
+      <c r="V31" s="256"/>
+      <c r="W31" s="256"/>
+      <c r="X31" s="256"/>
+      <c r="Y31" s="256"/>
+      <c r="Z31" s="256"/>
+      <c r="AA31" s="256"/>
+      <c r="AB31" s="256"/>
+      <c r="AC31" s="256"/>
+      <c r="AD31" s="256"/>
+      <c r="AE31" s="256"/>
+      <c r="AF31" s="256"/>
+      <c r="AG31" s="256"/>
+      <c r="AH31" s="256"/>
+      <c r="AI31" s="256"/>
+      <c r="AJ31" s="256"/>
+      <c r="AK31" s="256"/>
+      <c r="AL31" s="256"/>
+      <c r="AM31" s="256"/>
+      <c r="AN31" s="256"/>
+      <c r="AO31" s="256"/>
+      <c r="AP31" s="256"/>
+      <c r="AQ31" s="256"/>
+      <c r="AR31" s="256"/>
+      <c r="AS31" s="256"/>
+      <c r="AT31" s="256"/>
+      <c r="AU31" s="256"/>
+      <c r="AV31" s="256"/>
+      <c r="AW31" s="256"/>
+      <c r="AX31" s="256"/>
+      <c r="AY31" s="256"/>
+      <c r="AZ31" s="257"/>
     </row>
     <row r="32" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="248"/>
-      <c r="B32" s="249"/>
-      <c r="C32" s="249"/>
+      <c r="A32" s="247"/>
+      <c r="B32" s="248"/>
+      <c r="C32" s="248"/>
       <c r="D32" s="10"/>
-      <c r="E32" s="243"/>
-      <c r="F32" s="243"/>
-      <c r="G32" s="243"/>
-      <c r="H32" s="243"/>
-      <c r="I32" s="243"/>
-      <c r="J32" s="243"/>
-      <c r="K32" s="243"/>
-      <c r="L32" s="243"/>
-      <c r="M32" s="243"/>
-      <c r="N32" s="243"/>
-      <c r="O32" s="243"/>
-      <c r="P32" s="243"/>
-      <c r="Q32" s="243"/>
-      <c r="R32" s="243"/>
-      <c r="S32" s="243"/>
-      <c r="T32" s="243"/>
-      <c r="U32" s="243"/>
-      <c r="V32" s="243"/>
-      <c r="W32" s="243"/>
-      <c r="X32" s="243"/>
-      <c r="Y32" s="243"/>
-      <c r="Z32" s="243"/>
-      <c r="AA32" s="243"/>
-      <c r="AB32" s="243"/>
-      <c r="AC32" s="243"/>
-      <c r="AD32" s="243"/>
-      <c r="AE32" s="243"/>
-      <c r="AF32" s="243"/>
-      <c r="AG32" s="243"/>
-      <c r="AH32" s="243"/>
-      <c r="AI32" s="243"/>
-      <c r="AJ32" s="243"/>
-      <c r="AK32" s="243"/>
-      <c r="AL32" s="243"/>
-      <c r="AM32" s="243"/>
-      <c r="AN32" s="243"/>
-      <c r="AO32" s="243"/>
-      <c r="AP32" s="243"/>
-      <c r="AQ32" s="243"/>
-      <c r="AR32" s="243"/>
-      <c r="AS32" s="243"/>
-      <c r="AT32" s="243"/>
-      <c r="AU32" s="243"/>
-      <c r="AV32" s="243"/>
-      <c r="AW32" s="243"/>
-      <c r="AX32" s="243"/>
-      <c r="AY32" s="243"/>
-      <c r="AZ32" s="244"/>
+      <c r="E32" s="256"/>
+      <c r="F32" s="256"/>
+      <c r="G32" s="256"/>
+      <c r="H32" s="256"/>
+      <c r="I32" s="256"/>
+      <c r="J32" s="256"/>
+      <c r="K32" s="256"/>
+      <c r="L32" s="256"/>
+      <c r="M32" s="256"/>
+      <c r="N32" s="256"/>
+      <c r="O32" s="256"/>
+      <c r="P32" s="256"/>
+      <c r="Q32" s="256"/>
+      <c r="R32" s="256"/>
+      <c r="S32" s="256"/>
+      <c r="T32" s="256"/>
+      <c r="U32" s="256"/>
+      <c r="V32" s="256"/>
+      <c r="W32" s="256"/>
+      <c r="X32" s="256"/>
+      <c r="Y32" s="256"/>
+      <c r="Z32" s="256"/>
+      <c r="AA32" s="256"/>
+      <c r="AB32" s="256"/>
+      <c r="AC32" s="256"/>
+      <c r="AD32" s="256"/>
+      <c r="AE32" s="256"/>
+      <c r="AF32" s="256"/>
+      <c r="AG32" s="256"/>
+      <c r="AH32" s="256"/>
+      <c r="AI32" s="256"/>
+      <c r="AJ32" s="256"/>
+      <c r="AK32" s="256"/>
+      <c r="AL32" s="256"/>
+      <c r="AM32" s="256"/>
+      <c r="AN32" s="256"/>
+      <c r="AO32" s="256"/>
+      <c r="AP32" s="256"/>
+      <c r="AQ32" s="256"/>
+      <c r="AR32" s="256"/>
+      <c r="AS32" s="256"/>
+      <c r="AT32" s="256"/>
+      <c r="AU32" s="256"/>
+      <c r="AV32" s="256"/>
+      <c r="AW32" s="256"/>
+      <c r="AX32" s="256"/>
+      <c r="AY32" s="256"/>
+      <c r="AZ32" s="257"/>
     </row>
     <row r="33" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="248"/>
-      <c r="B33" s="249"/>
-      <c r="C33" s="249"/>
+      <c r="A33" s="247"/>
+      <c r="B33" s="248"/>
+      <c r="C33" s="248"/>
       <c r="D33" s="10"/>
-      <c r="E33" s="243"/>
-      <c r="F33" s="243"/>
-      <c r="G33" s="243"/>
-      <c r="H33" s="243"/>
-      <c r="I33" s="243"/>
-      <c r="J33" s="243"/>
-      <c r="K33" s="243"/>
-      <c r="L33" s="243"/>
-      <c r="M33" s="243"/>
-      <c r="N33" s="243"/>
-      <c r="O33" s="243"/>
-      <c r="P33" s="243"/>
-      <c r="Q33" s="243"/>
-      <c r="R33" s="243"/>
-      <c r="S33" s="243"/>
-      <c r="T33" s="243"/>
-      <c r="U33" s="243"/>
-      <c r="V33" s="243"/>
-      <c r="W33" s="243"/>
-      <c r="X33" s="243"/>
-      <c r="Y33" s="243"/>
-      <c r="Z33" s="243"/>
-      <c r="AA33" s="243"/>
-      <c r="AB33" s="243"/>
-      <c r="AC33" s="243"/>
-      <c r="AD33" s="243"/>
-      <c r="AE33" s="243"/>
-      <c r="AF33" s="243"/>
-      <c r="AG33" s="243"/>
-      <c r="AH33" s="243"/>
-      <c r="AI33" s="243"/>
-      <c r="AJ33" s="243"/>
-      <c r="AK33" s="243"/>
-      <c r="AL33" s="243"/>
-      <c r="AM33" s="243"/>
-      <c r="AN33" s="243"/>
-      <c r="AO33" s="243"/>
-      <c r="AP33" s="243"/>
-      <c r="AQ33" s="243"/>
-      <c r="AR33" s="243"/>
-      <c r="AS33" s="243"/>
-      <c r="AT33" s="243"/>
-      <c r="AU33" s="243"/>
-      <c r="AV33" s="243"/>
-      <c r="AW33" s="243"/>
-      <c r="AX33" s="243"/>
-      <c r="AY33" s="243"/>
-      <c r="AZ33" s="244"/>
+      <c r="E33" s="256"/>
+      <c r="F33" s="256"/>
+      <c r="G33" s="256"/>
+      <c r="H33" s="256"/>
+      <c r="I33" s="256"/>
+      <c r="J33" s="256"/>
+      <c r="K33" s="256"/>
+      <c r="L33" s="256"/>
+      <c r="M33" s="256"/>
+      <c r="N33" s="256"/>
+      <c r="O33" s="256"/>
+      <c r="P33" s="256"/>
+      <c r="Q33" s="256"/>
+      <c r="R33" s="256"/>
+      <c r="S33" s="256"/>
+      <c r="T33" s="256"/>
+      <c r="U33" s="256"/>
+      <c r="V33" s="256"/>
+      <c r="W33" s="256"/>
+      <c r="X33" s="256"/>
+      <c r="Y33" s="256"/>
+      <c r="Z33" s="256"/>
+      <c r="AA33" s="256"/>
+      <c r="AB33" s="256"/>
+      <c r="AC33" s="256"/>
+      <c r="AD33" s="256"/>
+      <c r="AE33" s="256"/>
+      <c r="AF33" s="256"/>
+      <c r="AG33" s="256"/>
+      <c r="AH33" s="256"/>
+      <c r="AI33" s="256"/>
+      <c r="AJ33" s="256"/>
+      <c r="AK33" s="256"/>
+      <c r="AL33" s="256"/>
+      <c r="AM33" s="256"/>
+      <c r="AN33" s="256"/>
+      <c r="AO33" s="256"/>
+      <c r="AP33" s="256"/>
+      <c r="AQ33" s="256"/>
+      <c r="AR33" s="256"/>
+      <c r="AS33" s="256"/>
+      <c r="AT33" s="256"/>
+      <c r="AU33" s="256"/>
+      <c r="AV33" s="256"/>
+      <c r="AW33" s="256"/>
+      <c r="AX33" s="256"/>
+      <c r="AY33" s="256"/>
+      <c r="AZ33" s="257"/>
     </row>
     <row r="34" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="248"/>
-      <c r="B34" s="249"/>
-      <c r="C34" s="249"/>
+      <c r="A34" s="247"/>
+      <c r="B34" s="248"/>
+      <c r="C34" s="248"/>
       <c r="D34" s="10"/>
-      <c r="E34" s="243"/>
-      <c r="F34" s="243"/>
-      <c r="G34" s="243"/>
-      <c r="H34" s="243"/>
-      <c r="I34" s="243"/>
-      <c r="J34" s="243"/>
-      <c r="K34" s="243"/>
-      <c r="L34" s="243"/>
-      <c r="M34" s="243"/>
-      <c r="N34" s="243"/>
-      <c r="O34" s="243"/>
-      <c r="P34" s="243"/>
-      <c r="Q34" s="243"/>
-      <c r="R34" s="243"/>
-      <c r="S34" s="243"/>
-      <c r="T34" s="243"/>
-      <c r="U34" s="243"/>
-      <c r="V34" s="243"/>
-      <c r="W34" s="243"/>
-      <c r="X34" s="243"/>
-      <c r="Y34" s="243"/>
-      <c r="Z34" s="243"/>
-      <c r="AA34" s="243"/>
-      <c r="AB34" s="243"/>
-      <c r="AC34" s="243"/>
-      <c r="AD34" s="243"/>
-      <c r="AE34" s="243"/>
-      <c r="AF34" s="243"/>
-      <c r="AG34" s="243"/>
-      <c r="AH34" s="243"/>
-      <c r="AI34" s="243"/>
-      <c r="AJ34" s="243"/>
-      <c r="AK34" s="243"/>
-      <c r="AL34" s="243"/>
-      <c r="AM34" s="243"/>
-      <c r="AN34" s="243"/>
-      <c r="AO34" s="243"/>
-      <c r="AP34" s="243"/>
-      <c r="AQ34" s="243"/>
-      <c r="AR34" s="243"/>
-      <c r="AS34" s="243"/>
-      <c r="AT34" s="243"/>
-      <c r="AU34" s="243"/>
-      <c r="AV34" s="243"/>
-      <c r="AW34" s="243"/>
-      <c r="AX34" s="243"/>
-      <c r="AY34" s="243"/>
-      <c r="AZ34" s="244"/>
+      <c r="E34" s="256"/>
+      <c r="F34" s="256"/>
+      <c r="G34" s="256"/>
+      <c r="H34" s="256"/>
+      <c r="I34" s="256"/>
+      <c r="J34" s="256"/>
+      <c r="K34" s="256"/>
+      <c r="L34" s="256"/>
+      <c r="M34" s="256"/>
+      <c r="N34" s="256"/>
+      <c r="O34" s="256"/>
+      <c r="P34" s="256"/>
+      <c r="Q34" s="256"/>
+      <c r="R34" s="256"/>
+      <c r="S34" s="256"/>
+      <c r="T34" s="256"/>
+      <c r="U34" s="256"/>
+      <c r="V34" s="256"/>
+      <c r="W34" s="256"/>
+      <c r="X34" s="256"/>
+      <c r="Y34" s="256"/>
+      <c r="Z34" s="256"/>
+      <c r="AA34" s="256"/>
+      <c r="AB34" s="256"/>
+      <c r="AC34" s="256"/>
+      <c r="AD34" s="256"/>
+      <c r="AE34" s="256"/>
+      <c r="AF34" s="256"/>
+      <c r="AG34" s="256"/>
+      <c r="AH34" s="256"/>
+      <c r="AI34" s="256"/>
+      <c r="AJ34" s="256"/>
+      <c r="AK34" s="256"/>
+      <c r="AL34" s="256"/>
+      <c r="AM34" s="256"/>
+      <c r="AN34" s="256"/>
+      <c r="AO34" s="256"/>
+      <c r="AP34" s="256"/>
+      <c r="AQ34" s="256"/>
+      <c r="AR34" s="256"/>
+      <c r="AS34" s="256"/>
+      <c r="AT34" s="256"/>
+      <c r="AU34" s="256"/>
+      <c r="AV34" s="256"/>
+      <c r="AW34" s="256"/>
+      <c r="AX34" s="256"/>
+      <c r="AY34" s="256"/>
+      <c r="AZ34" s="257"/>
     </row>
     <row r="35" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="248"/>
-      <c r="B35" s="249"/>
-      <c r="C35" s="249"/>
+      <c r="A35" s="247"/>
+      <c r="B35" s="248"/>
+      <c r="C35" s="248"/>
       <c r="D35" s="10"/>
-      <c r="E35" s="243"/>
-      <c r="F35" s="243"/>
-      <c r="G35" s="243"/>
-      <c r="H35" s="243"/>
-      <c r="I35" s="243"/>
-      <c r="J35" s="243"/>
-      <c r="K35" s="243"/>
-      <c r="L35" s="243"/>
-      <c r="M35" s="243"/>
-      <c r="N35" s="243"/>
-      <c r="O35" s="243"/>
-      <c r="P35" s="243"/>
-      <c r="Q35" s="243"/>
-      <c r="R35" s="243"/>
-      <c r="S35" s="243"/>
-      <c r="T35" s="243"/>
-      <c r="U35" s="243"/>
-      <c r="V35" s="243"/>
-      <c r="W35" s="243"/>
-      <c r="X35" s="243"/>
-      <c r="Y35" s="243"/>
-      <c r="Z35" s="243"/>
-      <c r="AA35" s="243"/>
-      <c r="AB35" s="243"/>
-      <c r="AC35" s="243"/>
-      <c r="AD35" s="243"/>
-      <c r="AE35" s="243"/>
-      <c r="AF35" s="243"/>
-      <c r="AG35" s="243"/>
-      <c r="AH35" s="243"/>
-      <c r="AI35" s="243"/>
-      <c r="AJ35" s="243"/>
-      <c r="AK35" s="243"/>
-      <c r="AL35" s="243"/>
-      <c r="AM35" s="243"/>
-      <c r="AN35" s="243"/>
-      <c r="AO35" s="243"/>
-      <c r="AP35" s="243"/>
-      <c r="AQ35" s="243"/>
-      <c r="AR35" s="243"/>
-      <c r="AS35" s="243"/>
-      <c r="AT35" s="243"/>
-      <c r="AU35" s="243"/>
-      <c r="AV35" s="243"/>
-      <c r="AW35" s="243"/>
-      <c r="AX35" s="243"/>
-      <c r="AY35" s="243"/>
-      <c r="AZ35" s="244"/>
+      <c r="E35" s="256"/>
+      <c r="F35" s="256"/>
+      <c r="G35" s="256"/>
+      <c r="H35" s="256"/>
+      <c r="I35" s="256"/>
+      <c r="J35" s="256"/>
+      <c r="K35" s="256"/>
+      <c r="L35" s="256"/>
+      <c r="M35" s="256"/>
+      <c r="N35" s="256"/>
+      <c r="O35" s="256"/>
+      <c r="P35" s="256"/>
+      <c r="Q35" s="256"/>
+      <c r="R35" s="256"/>
+      <c r="S35" s="256"/>
+      <c r="T35" s="256"/>
+      <c r="U35" s="256"/>
+      <c r="V35" s="256"/>
+      <c r="W35" s="256"/>
+      <c r="X35" s="256"/>
+      <c r="Y35" s="256"/>
+      <c r="Z35" s="256"/>
+      <c r="AA35" s="256"/>
+      <c r="AB35" s="256"/>
+      <c r="AC35" s="256"/>
+      <c r="AD35" s="256"/>
+      <c r="AE35" s="256"/>
+      <c r="AF35" s="256"/>
+      <c r="AG35" s="256"/>
+      <c r="AH35" s="256"/>
+      <c r="AI35" s="256"/>
+      <c r="AJ35" s="256"/>
+      <c r="AK35" s="256"/>
+      <c r="AL35" s="256"/>
+      <c r="AM35" s="256"/>
+      <c r="AN35" s="256"/>
+      <c r="AO35" s="256"/>
+      <c r="AP35" s="256"/>
+      <c r="AQ35" s="256"/>
+      <c r="AR35" s="256"/>
+      <c r="AS35" s="256"/>
+      <c r="AT35" s="256"/>
+      <c r="AU35" s="256"/>
+      <c r="AV35" s="256"/>
+      <c r="AW35" s="256"/>
+      <c r="AX35" s="256"/>
+      <c r="AY35" s="256"/>
+      <c r="AZ35" s="257"/>
     </row>
     <row r="36" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="248"/>
-      <c r="B36" s="249"/>
-      <c r="C36" s="249"/>
+      <c r="A36" s="247"/>
+      <c r="B36" s="248"/>
+      <c r="C36" s="248"/>
       <c r="D36" s="10"/>
-      <c r="E36" s="243"/>
-      <c r="F36" s="243"/>
-      <c r="G36" s="243"/>
-      <c r="H36" s="243"/>
-      <c r="I36" s="243"/>
-      <c r="J36" s="243"/>
-      <c r="K36" s="243"/>
-      <c r="L36" s="243"/>
-      <c r="M36" s="243"/>
-      <c r="N36" s="243"/>
-      <c r="O36" s="243"/>
-      <c r="P36" s="243"/>
-      <c r="Q36" s="243"/>
-      <c r="R36" s="243"/>
-      <c r="S36" s="243"/>
-      <c r="T36" s="243"/>
-      <c r="U36" s="243"/>
-      <c r="V36" s="243"/>
-      <c r="W36" s="243"/>
-      <c r="X36" s="243"/>
-      <c r="Y36" s="243"/>
-      <c r="Z36" s="243"/>
-      <c r="AA36" s="243"/>
-      <c r="AB36" s="243"/>
-      <c r="AC36" s="243"/>
-      <c r="AD36" s="243"/>
-      <c r="AE36" s="243"/>
-      <c r="AF36" s="243"/>
-      <c r="AG36" s="243"/>
-      <c r="AH36" s="243"/>
-      <c r="AI36" s="243"/>
-      <c r="AJ36" s="243"/>
-      <c r="AK36" s="243"/>
-      <c r="AL36" s="243"/>
-      <c r="AM36" s="243"/>
-      <c r="AN36" s="243"/>
-      <c r="AO36" s="243"/>
-      <c r="AP36" s="243"/>
-      <c r="AQ36" s="243"/>
-      <c r="AR36" s="243"/>
-      <c r="AS36" s="243"/>
-      <c r="AT36" s="243"/>
-      <c r="AU36" s="243"/>
-      <c r="AV36" s="243"/>
-      <c r="AW36" s="243"/>
-      <c r="AX36" s="243"/>
-      <c r="AY36" s="243"/>
-      <c r="AZ36" s="244"/>
+      <c r="E36" s="256"/>
+      <c r="F36" s="256"/>
+      <c r="G36" s="256"/>
+      <c r="H36" s="256"/>
+      <c r="I36" s="256"/>
+      <c r="J36" s="256"/>
+      <c r="K36" s="256"/>
+      <c r="L36" s="256"/>
+      <c r="M36" s="256"/>
+      <c r="N36" s="256"/>
+      <c r="O36" s="256"/>
+      <c r="P36" s="256"/>
+      <c r="Q36" s="256"/>
+      <c r="R36" s="256"/>
+      <c r="S36" s="256"/>
+      <c r="T36" s="256"/>
+      <c r="U36" s="256"/>
+      <c r="V36" s="256"/>
+      <c r="W36" s="256"/>
+      <c r="X36" s="256"/>
+      <c r="Y36" s="256"/>
+      <c r="Z36" s="256"/>
+      <c r="AA36" s="256"/>
+      <c r="AB36" s="256"/>
+      <c r="AC36" s="256"/>
+      <c r="AD36" s="256"/>
+      <c r="AE36" s="256"/>
+      <c r="AF36" s="256"/>
+      <c r="AG36" s="256"/>
+      <c r="AH36" s="256"/>
+      <c r="AI36" s="256"/>
+      <c r="AJ36" s="256"/>
+      <c r="AK36" s="256"/>
+      <c r="AL36" s="256"/>
+      <c r="AM36" s="256"/>
+      <c r="AN36" s="256"/>
+      <c r="AO36" s="256"/>
+      <c r="AP36" s="256"/>
+      <c r="AQ36" s="256"/>
+      <c r="AR36" s="256"/>
+      <c r="AS36" s="256"/>
+      <c r="AT36" s="256"/>
+      <c r="AU36" s="256"/>
+      <c r="AV36" s="256"/>
+      <c r="AW36" s="256"/>
+      <c r="AX36" s="256"/>
+      <c r="AY36" s="256"/>
+      <c r="AZ36" s="257"/>
     </row>
     <row r="37" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="248"/>
-      <c r="B37" s="249"/>
-      <c r="C37" s="249"/>
+      <c r="A37" s="247"/>
+      <c r="B37" s="248"/>
+      <c r="C37" s="248"/>
       <c r="D37" s="10"/>
-      <c r="E37" s="243"/>
-      <c r="F37" s="243"/>
-      <c r="G37" s="243"/>
-      <c r="H37" s="243"/>
-      <c r="I37" s="243"/>
-      <c r="J37" s="243"/>
-      <c r="K37" s="243"/>
-      <c r="L37" s="243"/>
-      <c r="M37" s="243"/>
-      <c r="N37" s="243"/>
-      <c r="O37" s="243"/>
-      <c r="P37" s="243"/>
-      <c r="Q37" s="243"/>
-      <c r="R37" s="243"/>
-      <c r="S37" s="243"/>
-      <c r="T37" s="243"/>
-      <c r="U37" s="243"/>
-      <c r="V37" s="243"/>
-      <c r="W37" s="243"/>
-      <c r="X37" s="243"/>
-      <c r="Y37" s="243"/>
-      <c r="Z37" s="243"/>
-      <c r="AA37" s="243"/>
-      <c r="AB37" s="243"/>
-      <c r="AC37" s="243"/>
-      <c r="AD37" s="243"/>
-      <c r="AE37" s="243"/>
-      <c r="AF37" s="243"/>
-      <c r="AG37" s="243"/>
-      <c r="AH37" s="243"/>
-      <c r="AI37" s="243"/>
-      <c r="AJ37" s="243"/>
-      <c r="AK37" s="243"/>
-      <c r="AL37" s="243"/>
-      <c r="AM37" s="243"/>
-      <c r="AN37" s="243"/>
-      <c r="AO37" s="243"/>
-      <c r="AP37" s="243"/>
-      <c r="AQ37" s="243"/>
-      <c r="AR37" s="243"/>
-      <c r="AS37" s="243"/>
-      <c r="AT37" s="243"/>
-      <c r="AU37" s="243"/>
-      <c r="AV37" s="243"/>
-      <c r="AW37" s="243"/>
-      <c r="AX37" s="243"/>
-      <c r="AY37" s="243"/>
-      <c r="AZ37" s="244"/>
+      <c r="E37" s="256"/>
+      <c r="F37" s="256"/>
+      <c r="G37" s="256"/>
+      <c r="H37" s="256"/>
+      <c r="I37" s="256"/>
+      <c r="J37" s="256"/>
+      <c r="K37" s="256"/>
+      <c r="L37" s="256"/>
+      <c r="M37" s="256"/>
+      <c r="N37" s="256"/>
+      <c r="O37" s="256"/>
+      <c r="P37" s="256"/>
+      <c r="Q37" s="256"/>
+      <c r="R37" s="256"/>
+      <c r="S37" s="256"/>
+      <c r="T37" s="256"/>
+      <c r="U37" s="256"/>
+      <c r="V37" s="256"/>
+      <c r="W37" s="256"/>
+      <c r="X37" s="256"/>
+      <c r="Y37" s="256"/>
+      <c r="Z37" s="256"/>
+      <c r="AA37" s="256"/>
+      <c r="AB37" s="256"/>
+      <c r="AC37" s="256"/>
+      <c r="AD37" s="256"/>
+      <c r="AE37" s="256"/>
+      <c r="AF37" s="256"/>
+      <c r="AG37" s="256"/>
+      <c r="AH37" s="256"/>
+      <c r="AI37" s="256"/>
+      <c r="AJ37" s="256"/>
+      <c r="AK37" s="256"/>
+      <c r="AL37" s="256"/>
+      <c r="AM37" s="256"/>
+      <c r="AN37" s="256"/>
+      <c r="AO37" s="256"/>
+      <c r="AP37" s="256"/>
+      <c r="AQ37" s="256"/>
+      <c r="AR37" s="256"/>
+      <c r="AS37" s="256"/>
+      <c r="AT37" s="256"/>
+      <c r="AU37" s="256"/>
+      <c r="AV37" s="256"/>
+      <c r="AW37" s="256"/>
+      <c r="AX37" s="256"/>
+      <c r="AY37" s="256"/>
+      <c r="AZ37" s="257"/>
     </row>
     <row r="38" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="248"/>
-      <c r="B38" s="249"/>
-      <c r="C38" s="249"/>
+      <c r="A38" s="247"/>
+      <c r="B38" s="248"/>
+      <c r="C38" s="248"/>
       <c r="D38" s="10"/>
-      <c r="E38" s="243"/>
-      <c r="F38" s="243"/>
-      <c r="G38" s="243"/>
-      <c r="H38" s="243"/>
-      <c r="I38" s="243"/>
-      <c r="J38" s="243"/>
-      <c r="K38" s="243"/>
-      <c r="L38" s="243"/>
-      <c r="M38" s="243"/>
-      <c r="N38" s="243"/>
-      <c r="O38" s="243"/>
-      <c r="P38" s="243"/>
-      <c r="Q38" s="243"/>
-      <c r="R38" s="243"/>
-      <c r="S38" s="243"/>
-      <c r="T38" s="243"/>
-      <c r="U38" s="243"/>
-      <c r="V38" s="243"/>
-      <c r="W38" s="243"/>
-      <c r="X38" s="243"/>
-      <c r="Y38" s="243"/>
-      <c r="Z38" s="243"/>
-      <c r="AA38" s="243"/>
-      <c r="AB38" s="243"/>
-      <c r="AC38" s="243"/>
-      <c r="AD38" s="243"/>
-      <c r="AE38" s="243"/>
-      <c r="AF38" s="243"/>
-      <c r="AG38" s="243"/>
-      <c r="AH38" s="243"/>
-      <c r="AI38" s="243"/>
-      <c r="AJ38" s="243"/>
-      <c r="AK38" s="243"/>
-      <c r="AL38" s="243"/>
-      <c r="AM38" s="243"/>
-      <c r="AN38" s="243"/>
-      <c r="AO38" s="243"/>
-      <c r="AP38" s="243"/>
-      <c r="AQ38" s="243"/>
-      <c r="AR38" s="243"/>
-      <c r="AS38" s="243"/>
-      <c r="AT38" s="243"/>
-      <c r="AU38" s="243"/>
-      <c r="AV38" s="243"/>
-      <c r="AW38" s="243"/>
-      <c r="AX38" s="243"/>
-      <c r="AY38" s="243"/>
-      <c r="AZ38" s="244"/>
+      <c r="E38" s="256"/>
+      <c r="F38" s="256"/>
+      <c r="G38" s="256"/>
+      <c r="H38" s="256"/>
+      <c r="I38" s="256"/>
+      <c r="J38" s="256"/>
+      <c r="K38" s="256"/>
+      <c r="L38" s="256"/>
+      <c r="M38" s="256"/>
+      <c r="N38" s="256"/>
+      <c r="O38" s="256"/>
+      <c r="P38" s="256"/>
+      <c r="Q38" s="256"/>
+      <c r="R38" s="256"/>
+      <c r="S38" s="256"/>
+      <c r="T38" s="256"/>
+      <c r="U38" s="256"/>
+      <c r="V38" s="256"/>
+      <c r="W38" s="256"/>
+      <c r="X38" s="256"/>
+      <c r="Y38" s="256"/>
+      <c r="Z38" s="256"/>
+      <c r="AA38" s="256"/>
+      <c r="AB38" s="256"/>
+      <c r="AC38" s="256"/>
+      <c r="AD38" s="256"/>
+      <c r="AE38" s="256"/>
+      <c r="AF38" s="256"/>
+      <c r="AG38" s="256"/>
+      <c r="AH38" s="256"/>
+      <c r="AI38" s="256"/>
+      <c r="AJ38" s="256"/>
+      <c r="AK38" s="256"/>
+      <c r="AL38" s="256"/>
+      <c r="AM38" s="256"/>
+      <c r="AN38" s="256"/>
+      <c r="AO38" s="256"/>
+      <c r="AP38" s="256"/>
+      <c r="AQ38" s="256"/>
+      <c r="AR38" s="256"/>
+      <c r="AS38" s="256"/>
+      <c r="AT38" s="256"/>
+      <c r="AU38" s="256"/>
+      <c r="AV38" s="256"/>
+      <c r="AW38" s="256"/>
+      <c r="AX38" s="256"/>
+      <c r="AY38" s="256"/>
+      <c r="AZ38" s="257"/>
     </row>
     <row r="39" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="248"/>
-      <c r="B39" s="249"/>
-      <c r="C39" s="249"/>
+      <c r="A39" s="247"/>
+      <c r="B39" s="248"/>
+      <c r="C39" s="248"/>
       <c r="D39" s="10"/>
-      <c r="E39" s="243"/>
-      <c r="F39" s="243"/>
-      <c r="G39" s="243"/>
-      <c r="H39" s="243"/>
-      <c r="I39" s="243"/>
-      <c r="J39" s="243"/>
-      <c r="K39" s="243"/>
-      <c r="L39" s="243"/>
-      <c r="M39" s="243"/>
-      <c r="N39" s="243"/>
-      <c r="O39" s="243"/>
-      <c r="P39" s="243"/>
-      <c r="Q39" s="243"/>
-      <c r="R39" s="243"/>
-      <c r="S39" s="243"/>
-      <c r="T39" s="243"/>
-      <c r="U39" s="243"/>
-      <c r="V39" s="243"/>
-      <c r="W39" s="243"/>
-      <c r="X39" s="243"/>
-      <c r="Y39" s="243"/>
-      <c r="Z39" s="243"/>
-      <c r="AA39" s="243"/>
-      <c r="AB39" s="243"/>
-      <c r="AC39" s="243"/>
-      <c r="AD39" s="243"/>
-      <c r="AE39" s="243"/>
-      <c r="AF39" s="243"/>
-      <c r="AG39" s="243"/>
-      <c r="AH39" s="243"/>
-      <c r="AI39" s="243"/>
-      <c r="AJ39" s="243"/>
-      <c r="AK39" s="243"/>
-      <c r="AL39" s="243"/>
-      <c r="AM39" s="243"/>
-      <c r="AN39" s="243"/>
-      <c r="AO39" s="243"/>
-      <c r="AP39" s="243"/>
-      <c r="AQ39" s="243"/>
-      <c r="AR39" s="243"/>
-      <c r="AS39" s="243"/>
-      <c r="AT39" s="243"/>
-      <c r="AU39" s="243"/>
-      <c r="AV39" s="243"/>
-      <c r="AW39" s="243"/>
-      <c r="AX39" s="243"/>
-      <c r="AY39" s="243"/>
-      <c r="AZ39" s="244"/>
+      <c r="E39" s="256"/>
+      <c r="F39" s="256"/>
+      <c r="G39" s="256"/>
+      <c r="H39" s="256"/>
+      <c r="I39" s="256"/>
+      <c r="J39" s="256"/>
+      <c r="K39" s="256"/>
+      <c r="L39" s="256"/>
+      <c r="M39" s="256"/>
+      <c r="N39" s="256"/>
+      <c r="O39" s="256"/>
+      <c r="P39" s="256"/>
+      <c r="Q39" s="256"/>
+      <c r="R39" s="256"/>
+      <c r="S39" s="256"/>
+      <c r="T39" s="256"/>
+      <c r="U39" s="256"/>
+      <c r="V39" s="256"/>
+      <c r="W39" s="256"/>
+      <c r="X39" s="256"/>
+      <c r="Y39" s="256"/>
+      <c r="Z39" s="256"/>
+      <c r="AA39" s="256"/>
+      <c r="AB39" s="256"/>
+      <c r="AC39" s="256"/>
+      <c r="AD39" s="256"/>
+      <c r="AE39" s="256"/>
+      <c r="AF39" s="256"/>
+      <c r="AG39" s="256"/>
+      <c r="AH39" s="256"/>
+      <c r="AI39" s="256"/>
+      <c r="AJ39" s="256"/>
+      <c r="AK39" s="256"/>
+      <c r="AL39" s="256"/>
+      <c r="AM39" s="256"/>
+      <c r="AN39" s="256"/>
+      <c r="AO39" s="256"/>
+      <c r="AP39" s="256"/>
+      <c r="AQ39" s="256"/>
+      <c r="AR39" s="256"/>
+      <c r="AS39" s="256"/>
+      <c r="AT39" s="256"/>
+      <c r="AU39" s="256"/>
+      <c r="AV39" s="256"/>
+      <c r="AW39" s="256"/>
+      <c r="AX39" s="256"/>
+      <c r="AY39" s="256"/>
+      <c r="AZ39" s="257"/>
     </row>
     <row r="40" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="248"/>
-      <c r="B40" s="249"/>
-      <c r="C40" s="249"/>
+      <c r="A40" s="247"/>
+      <c r="B40" s="248"/>
+      <c r="C40" s="248"/>
       <c r="D40" s="10"/>
-      <c r="E40" s="243"/>
-      <c r="F40" s="243"/>
-      <c r="G40" s="243"/>
-      <c r="H40" s="243"/>
-      <c r="I40" s="243"/>
-      <c r="J40" s="243"/>
-      <c r="K40" s="243"/>
-      <c r="L40" s="243"/>
-      <c r="M40" s="243"/>
-      <c r="N40" s="243"/>
-      <c r="O40" s="243"/>
-      <c r="P40" s="243"/>
-      <c r="Q40" s="243"/>
-      <c r="R40" s="243"/>
-      <c r="S40" s="243"/>
-      <c r="T40" s="243"/>
-      <c r="U40" s="243"/>
-      <c r="V40" s="243"/>
-      <c r="W40" s="243"/>
-      <c r="X40" s="243"/>
-      <c r="Y40" s="243"/>
-      <c r="Z40" s="243"/>
-      <c r="AA40" s="243"/>
-      <c r="AB40" s="243"/>
-      <c r="AC40" s="243"/>
-      <c r="AD40" s="243"/>
-      <c r="AE40" s="243"/>
-      <c r="AF40" s="243"/>
-      <c r="AG40" s="243"/>
-      <c r="AH40" s="243"/>
-      <c r="AI40" s="243"/>
-      <c r="AJ40" s="243"/>
-      <c r="AK40" s="243"/>
-      <c r="AL40" s="243"/>
-      <c r="AM40" s="243"/>
-      <c r="AN40" s="243"/>
-      <c r="AO40" s="243"/>
-      <c r="AP40" s="243"/>
-      <c r="AQ40" s="243"/>
-      <c r="AR40" s="243"/>
-      <c r="AS40" s="243"/>
-      <c r="AT40" s="243"/>
-      <c r="AU40" s="243"/>
-      <c r="AV40" s="243"/>
-      <c r="AW40" s="243"/>
-      <c r="AX40" s="243"/>
-      <c r="AY40" s="243"/>
-      <c r="AZ40" s="244"/>
+      <c r="E40" s="256"/>
+      <c r="F40" s="256"/>
+      <c r="G40" s="256"/>
+      <c r="H40" s="256"/>
+      <c r="I40" s="256"/>
+      <c r="J40" s="256"/>
+      <c r="K40" s="256"/>
+      <c r="L40" s="256"/>
+      <c r="M40" s="256"/>
+      <c r="N40" s="256"/>
+      <c r="O40" s="256"/>
+      <c r="P40" s="256"/>
+      <c r="Q40" s="256"/>
+      <c r="R40" s="256"/>
+      <c r="S40" s="256"/>
+      <c r="T40" s="256"/>
+      <c r="U40" s="256"/>
+      <c r="V40" s="256"/>
+      <c r="W40" s="256"/>
+      <c r="X40" s="256"/>
+      <c r="Y40" s="256"/>
+      <c r="Z40" s="256"/>
+      <c r="AA40" s="256"/>
+      <c r="AB40" s="256"/>
+      <c r="AC40" s="256"/>
+      <c r="AD40" s="256"/>
+      <c r="AE40" s="256"/>
+      <c r="AF40" s="256"/>
+      <c r="AG40" s="256"/>
+      <c r="AH40" s="256"/>
+      <c r="AI40" s="256"/>
+      <c r="AJ40" s="256"/>
+      <c r="AK40" s="256"/>
+      <c r="AL40" s="256"/>
+      <c r="AM40" s="256"/>
+      <c r="AN40" s="256"/>
+      <c r="AO40" s="256"/>
+      <c r="AP40" s="256"/>
+      <c r="AQ40" s="256"/>
+      <c r="AR40" s="256"/>
+      <c r="AS40" s="256"/>
+      <c r="AT40" s="256"/>
+      <c r="AU40" s="256"/>
+      <c r="AV40" s="256"/>
+      <c r="AW40" s="256"/>
+      <c r="AX40" s="256"/>
+      <c r="AY40" s="256"/>
+      <c r="AZ40" s="257"/>
     </row>
     <row r="41" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="248"/>
-      <c r="B41" s="249"/>
-      <c r="C41" s="249"/>
+      <c r="A41" s="247"/>
+      <c r="B41" s="248"/>
+      <c r="C41" s="248"/>
       <c r="D41" s="10"/>
-      <c r="E41" s="243"/>
-      <c r="F41" s="243"/>
-      <c r="G41" s="243"/>
-      <c r="H41" s="243"/>
-      <c r="I41" s="243"/>
-      <c r="J41" s="243"/>
-      <c r="K41" s="243"/>
-      <c r="L41" s="243"/>
-      <c r="M41" s="243"/>
-      <c r="N41" s="243"/>
-      <c r="O41" s="243"/>
-      <c r="P41" s="243"/>
-      <c r="Q41" s="243"/>
-      <c r="R41" s="243"/>
-      <c r="S41" s="243"/>
-      <c r="T41" s="243"/>
-      <c r="U41" s="243"/>
-      <c r="V41" s="243"/>
-      <c r="W41" s="243"/>
-      <c r="X41" s="243"/>
-      <c r="Y41" s="243"/>
-      <c r="Z41" s="243"/>
-      <c r="AA41" s="243"/>
-      <c r="AB41" s="243"/>
-      <c r="AC41" s="243"/>
-      <c r="AD41" s="243"/>
-      <c r="AE41" s="243"/>
-      <c r="AF41" s="243"/>
-      <c r="AG41" s="243"/>
-      <c r="AH41" s="243"/>
-      <c r="AI41" s="243"/>
-      <c r="AJ41" s="243"/>
-      <c r="AK41" s="243"/>
-      <c r="AL41" s="243"/>
-      <c r="AM41" s="243"/>
-      <c r="AN41" s="243"/>
-      <c r="AO41" s="243"/>
-      <c r="AP41" s="243"/>
-      <c r="AQ41" s="243"/>
-      <c r="AR41" s="243"/>
-      <c r="AS41" s="243"/>
-      <c r="AT41" s="243"/>
-      <c r="AU41" s="243"/>
-      <c r="AV41" s="243"/>
-      <c r="AW41" s="243"/>
-      <c r="AX41" s="243"/>
-      <c r="AY41" s="243"/>
-      <c r="AZ41" s="244"/>
+      <c r="E41" s="256"/>
+      <c r="F41" s="256"/>
+      <c r="G41" s="256"/>
+      <c r="H41" s="256"/>
+      <c r="I41" s="256"/>
+      <c r="J41" s="256"/>
+      <c r="K41" s="256"/>
+      <c r="L41" s="256"/>
+      <c r="M41" s="256"/>
+      <c r="N41" s="256"/>
+      <c r="O41" s="256"/>
+      <c r="P41" s="256"/>
+      <c r="Q41" s="256"/>
+      <c r="R41" s="256"/>
+      <c r="S41" s="256"/>
+      <c r="T41" s="256"/>
+      <c r="U41" s="256"/>
+      <c r="V41" s="256"/>
+      <c r="W41" s="256"/>
+      <c r="X41" s="256"/>
+      <c r="Y41" s="256"/>
+      <c r="Z41" s="256"/>
+      <c r="AA41" s="256"/>
+      <c r="AB41" s="256"/>
+      <c r="AC41" s="256"/>
+      <c r="AD41" s="256"/>
+      <c r="AE41" s="256"/>
+      <c r="AF41" s="256"/>
+      <c r="AG41" s="256"/>
+      <c r="AH41" s="256"/>
+      <c r="AI41" s="256"/>
+      <c r="AJ41" s="256"/>
+      <c r="AK41" s="256"/>
+      <c r="AL41" s="256"/>
+      <c r="AM41" s="256"/>
+      <c r="AN41" s="256"/>
+      <c r="AO41" s="256"/>
+      <c r="AP41" s="256"/>
+      <c r="AQ41" s="256"/>
+      <c r="AR41" s="256"/>
+      <c r="AS41" s="256"/>
+      <c r="AT41" s="256"/>
+      <c r="AU41" s="256"/>
+      <c r="AV41" s="256"/>
+      <c r="AW41" s="256"/>
+      <c r="AX41" s="256"/>
+      <c r="AY41" s="256"/>
+      <c r="AZ41" s="257"/>
     </row>
     <row r="42" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="248"/>
-      <c r="B42" s="249"/>
-      <c r="C42" s="249"/>
+      <c r="A42" s="247"/>
+      <c r="B42" s="248"/>
+      <c r="C42" s="248"/>
       <c r="D42" s="10"/>
-      <c r="E42" s="243"/>
-      <c r="F42" s="243"/>
-      <c r="G42" s="243"/>
-      <c r="H42" s="243"/>
-      <c r="I42" s="243"/>
-      <c r="J42" s="243"/>
-      <c r="K42" s="243"/>
-      <c r="L42" s="243"/>
-      <c r="M42" s="243"/>
-      <c r="N42" s="243"/>
-      <c r="O42" s="243"/>
-      <c r="P42" s="243"/>
-      <c r="Q42" s="243"/>
-      <c r="R42" s="243"/>
-      <c r="S42" s="243"/>
-      <c r="T42" s="243"/>
-      <c r="U42" s="243"/>
-      <c r="V42" s="243"/>
-      <c r="W42" s="243"/>
-      <c r="X42" s="243"/>
-      <c r="Y42" s="243"/>
-      <c r="Z42" s="243"/>
-      <c r="AA42" s="243"/>
-      <c r="AB42" s="243"/>
-      <c r="AC42" s="243"/>
-      <c r="AD42" s="243"/>
-      <c r="AE42" s="243"/>
-      <c r="AF42" s="243"/>
-      <c r="AG42" s="243"/>
-      <c r="AH42" s="243"/>
-      <c r="AI42" s="243"/>
-      <c r="AJ42" s="243"/>
-      <c r="AK42" s="243"/>
-      <c r="AL42" s="243"/>
-      <c r="AM42" s="243"/>
-      <c r="AN42" s="243"/>
-      <c r="AO42" s="243"/>
-      <c r="AP42" s="243"/>
-      <c r="AQ42" s="243"/>
-      <c r="AR42" s="243"/>
-      <c r="AS42" s="243"/>
-      <c r="AT42" s="243"/>
-      <c r="AU42" s="243"/>
-      <c r="AV42" s="243"/>
-      <c r="AW42" s="243"/>
-      <c r="AX42" s="243"/>
-      <c r="AY42" s="243"/>
-      <c r="AZ42" s="244"/>
+      <c r="E42" s="256"/>
+      <c r="F42" s="256"/>
+      <c r="G42" s="256"/>
+      <c r="H42" s="256"/>
+      <c r="I42" s="256"/>
+      <c r="J42" s="256"/>
+      <c r="K42" s="256"/>
+      <c r="L42" s="256"/>
+      <c r="M42" s="256"/>
+      <c r="N42" s="256"/>
+      <c r="O42" s="256"/>
+      <c r="P42" s="256"/>
+      <c r="Q42" s="256"/>
+      <c r="R42" s="256"/>
+      <c r="S42" s="256"/>
+      <c r="T42" s="256"/>
+      <c r="U42" s="256"/>
+      <c r="V42" s="256"/>
+      <c r="W42" s="256"/>
+      <c r="X42" s="256"/>
+      <c r="Y42" s="256"/>
+      <c r="Z42" s="256"/>
+      <c r="AA42" s="256"/>
+      <c r="AB42" s="256"/>
+      <c r="AC42" s="256"/>
+      <c r="AD42" s="256"/>
+      <c r="AE42" s="256"/>
+      <c r="AF42" s="256"/>
+      <c r="AG42" s="256"/>
+      <c r="AH42" s="256"/>
+      <c r="AI42" s="256"/>
+      <c r="AJ42" s="256"/>
+      <c r="AK42" s="256"/>
+      <c r="AL42" s="256"/>
+      <c r="AM42" s="256"/>
+      <c r="AN42" s="256"/>
+      <c r="AO42" s="256"/>
+      <c r="AP42" s="256"/>
+      <c r="AQ42" s="256"/>
+      <c r="AR42" s="256"/>
+      <c r="AS42" s="256"/>
+      <c r="AT42" s="256"/>
+      <c r="AU42" s="256"/>
+      <c r="AV42" s="256"/>
+      <c r="AW42" s="256"/>
+      <c r="AX42" s="256"/>
+      <c r="AY42" s="256"/>
+      <c r="AZ42" s="257"/>
     </row>
     <row r="43" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="62"/>
@@ -12160,181 +12164,226 @@
       <c r="AZ44"/>
     </row>
     <row r="45" spans="1:53" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="147"/>
-      <c r="B45" s="147"/>
-      <c r="C45" s="147"/>
-      <c r="D45" s="147"/>
-      <c r="E45" s="147"/>
-      <c r="F45" s="147"/>
-      <c r="G45" s="147"/>
-      <c r="H45" s="147"/>
-      <c r="I45" s="147"/>
-      <c r="J45" s="147"/>
-      <c r="K45" s="147"/>
-      <c r="L45" s="147"/>
-      <c r="M45" s="147"/>
-      <c r="N45" s="147"/>
-      <c r="O45" s="147"/>
-      <c r="P45" s="147"/>
+      <c r="A45" s="117"/>
+      <c r="B45" s="117"/>
+      <c r="C45" s="117"/>
+      <c r="D45" s="117"/>
+      <c r="E45" s="117"/>
+      <c r="F45" s="117"/>
+      <c r="G45" s="117"/>
+      <c r="H45" s="117"/>
+      <c r="I45" s="117"/>
+      <c r="J45" s="117"/>
+      <c r="K45" s="117"/>
+      <c r="L45" s="117"/>
+      <c r="M45" s="117"/>
+      <c r="N45" s="117"/>
+      <c r="O45" s="117"/>
+      <c r="P45" s="117"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
-      <c r="S45" s="147"/>
-      <c r="T45" s="147"/>
-      <c r="U45" s="147"/>
-      <c r="V45" s="147"/>
-      <c r="W45" s="147"/>
-      <c r="X45" s="147"/>
-      <c r="Y45" s="147"/>
-      <c r="Z45" s="147"/>
-      <c r="AA45" s="147"/>
-      <c r="AB45" s="147"/>
-      <c r="AC45" s="147"/>
-      <c r="AD45" s="147"/>
-      <c r="AE45" s="147"/>
-      <c r="AF45" s="147"/>
-      <c r="AG45" s="147"/>
-      <c r="AH45" s="147"/>
+      <c r="S45" s="117"/>
+      <c r="T45" s="117"/>
+      <c r="U45" s="117"/>
+      <c r="V45" s="117"/>
+      <c r="W45" s="117"/>
+      <c r="X45" s="117"/>
+      <c r="Y45" s="117"/>
+      <c r="Z45" s="117"/>
+      <c r="AA45" s="117"/>
+      <c r="AB45" s="117"/>
+      <c r="AC45" s="117"/>
+      <c r="AD45" s="117"/>
+      <c r="AE45" s="117"/>
+      <c r="AF45" s="117"/>
+      <c r="AG45" s="117"/>
+      <c r="AH45" s="117"/>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
-      <c r="AK45" s="147"/>
-      <c r="AL45" s="147"/>
-      <c r="AM45" s="147"/>
-      <c r="AN45" s="147"/>
-      <c r="AO45" s="147"/>
-      <c r="AP45" s="147"/>
-      <c r="AQ45" s="147"/>
-      <c r="AR45" s="147"/>
-      <c r="AS45" s="147"/>
-      <c r="AT45" s="147"/>
-      <c r="AU45" s="147"/>
-      <c r="AV45" s="147"/>
-      <c r="AW45" s="147"/>
-      <c r="AX45" s="147"/>
-      <c r="AY45" s="147"/>
-      <c r="AZ45" s="147"/>
+      <c r="AK45" s="117"/>
+      <c r="AL45" s="117"/>
+      <c r="AM45" s="117"/>
+      <c r="AN45" s="117"/>
+      <c r="AO45" s="117"/>
+      <c r="AP45" s="117"/>
+      <c r="AQ45" s="117"/>
+      <c r="AR45" s="117"/>
+      <c r="AS45" s="117"/>
+      <c r="AT45" s="117"/>
+      <c r="AU45" s="117"/>
+      <c r="AV45" s="117"/>
+      <c r="AW45" s="117"/>
+      <c r="AX45" s="117"/>
+      <c r="AY45" s="117"/>
+      <c r="AZ45" s="117"/>
     </row>
     <row r="46" spans="1:53" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="211" t="s">
+      <c r="A46" s="118" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="211"/>
-      <c r="C46" s="211"/>
-      <c r="D46" s="211"/>
-      <c r="E46" s="211"/>
-      <c r="F46" s="211"/>
-      <c r="G46" s="211"/>
-      <c r="H46" s="211"/>
-      <c r="I46" s="211"/>
-      <c r="J46" s="211"/>
-      <c r="K46" s="211"/>
-      <c r="L46" s="211"/>
-      <c r="M46" s="211"/>
-      <c r="N46" s="211"/>
-      <c r="O46" s="211"/>
-      <c r="P46" s="211"/>
+      <c r="B46" s="118"/>
+      <c r="C46" s="118"/>
+      <c r="D46" s="118"/>
+      <c r="E46" s="118"/>
+      <c r="F46" s="118"/>
+      <c r="G46" s="118"/>
+      <c r="H46" s="118"/>
+      <c r="I46" s="118"/>
+      <c r="J46" s="118"/>
+      <c r="K46" s="118"/>
+      <c r="L46" s="118"/>
+      <c r="M46" s="118"/>
+      <c r="N46" s="118"/>
+      <c r="O46" s="118"/>
+      <c r="P46" s="118"/>
       <c r="Q46" s="54"/>
       <c r="R46" s="54"/>
-      <c r="S46" s="122" t="s">
+      <c r="S46" s="195" t="s">
         <v>78</v>
       </c>
-      <c r="T46" s="122"/>
-      <c r="U46" s="122"/>
-      <c r="V46" s="122"/>
-      <c r="W46" s="122"/>
-      <c r="X46" s="122"/>
-      <c r="Y46" s="122"/>
-      <c r="Z46" s="122"/>
-      <c r="AA46" s="122"/>
-      <c r="AB46" s="122"/>
-      <c r="AC46" s="122"/>
-      <c r="AD46" s="122"/>
-      <c r="AE46" s="122"/>
-      <c r="AF46" s="122"/>
-      <c r="AG46" s="122"/>
-      <c r="AH46" s="122"/>
+      <c r="T46" s="195"/>
+      <c r="U46" s="195"/>
+      <c r="V46" s="195"/>
+      <c r="W46" s="195"/>
+      <c r="X46" s="195"/>
+      <c r="Y46" s="195"/>
+      <c r="Z46" s="195"/>
+      <c r="AA46" s="195"/>
+      <c r="AB46" s="195"/>
+      <c r="AC46" s="195"/>
+      <c r="AD46" s="195"/>
+      <c r="AE46" s="195"/>
+      <c r="AF46" s="195"/>
+      <c r="AG46" s="195"/>
+      <c r="AH46" s="195"/>
       <c r="AI46" s="54"/>
       <c r="AJ46" s="54"/>
-      <c r="AK46" s="211" t="s">
+      <c r="AK46" s="118" t="s">
         <v>79</v>
       </c>
-      <c r="AL46" s="211"/>
-      <c r="AM46" s="211"/>
-      <c r="AN46" s="211"/>
-      <c r="AO46" s="211"/>
-      <c r="AP46" s="211"/>
-      <c r="AQ46" s="211"/>
-      <c r="AR46" s="211"/>
-      <c r="AS46" s="211"/>
-      <c r="AT46" s="211"/>
-      <c r="AU46" s="211"/>
-      <c r="AV46" s="211"/>
-      <c r="AW46" s="211"/>
-      <c r="AX46" s="211"/>
-      <c r="AY46" s="211"/>
-      <c r="AZ46" s="211"/>
+      <c r="AL46" s="118"/>
+      <c r="AM46" s="118"/>
+      <c r="AN46" s="118"/>
+      <c r="AO46" s="118"/>
+      <c r="AP46" s="118"/>
+      <c r="AQ46" s="118"/>
+      <c r="AR46" s="118"/>
+      <c r="AS46" s="118"/>
+      <c r="AT46" s="118"/>
+      <c r="AU46" s="118"/>
+      <c r="AV46" s="118"/>
+      <c r="AW46" s="118"/>
+      <c r="AX46" s="118"/>
+      <c r="AY46" s="118"/>
+      <c r="AZ46" s="118"/>
     </row>
     <row r="47" spans="1:53" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="245"/>
-      <c r="B47" s="245"/>
-      <c r="C47" s="245"/>
-      <c r="D47" s="245"/>
-      <c r="E47" s="245"/>
-      <c r="F47" s="245"/>
-      <c r="G47" s="245"/>
-      <c r="H47" s="245"/>
-      <c r="I47" s="245"/>
-      <c r="J47" s="245"/>
-      <c r="K47" s="245"/>
-      <c r="L47" s="245"/>
-      <c r="M47" s="245"/>
-      <c r="N47" s="245"/>
-      <c r="O47" s="245"/>
-      <c r="P47" s="245"/>
-      <c r="S47" s="245"/>
-      <c r="T47" s="245"/>
-      <c r="U47" s="245"/>
-      <c r="V47" s="246"/>
-      <c r="W47" s="247"/>
-      <c r="X47" s="247"/>
-      <c r="Y47" s="247"/>
-      <c r="Z47" s="247"/>
-      <c r="AA47" s="247"/>
-      <c r="AB47" s="247"/>
-      <c r="AC47" s="247"/>
-      <c r="AD47" s="247"/>
-      <c r="AE47" s="247"/>
-      <c r="AF47" s="247"/>
-      <c r="AG47" s="247"/>
-      <c r="AH47" s="247"/>
-      <c r="AK47" s="212" t="s">
+      <c r="A47" s="258"/>
+      <c r="B47" s="258"/>
+      <c r="C47" s="258"/>
+      <c r="D47" s="258"/>
+      <c r="E47" s="258"/>
+      <c r="F47" s="258"/>
+      <c r="G47" s="258"/>
+      <c r="H47" s="258"/>
+      <c r="I47" s="258"/>
+      <c r="J47" s="258"/>
+      <c r="K47" s="258"/>
+      <c r="L47" s="258"/>
+      <c r="M47" s="258"/>
+      <c r="N47" s="258"/>
+      <c r="O47" s="258"/>
+      <c r="P47" s="258"/>
+      <c r="S47" s="258"/>
+      <c r="T47" s="258"/>
+      <c r="U47" s="258"/>
+      <c r="V47" s="259"/>
+      <c r="W47" s="260"/>
+      <c r="X47" s="260"/>
+      <c r="Y47" s="260"/>
+      <c r="Z47" s="260"/>
+      <c r="AA47" s="260"/>
+      <c r="AB47" s="260"/>
+      <c r="AC47" s="260"/>
+      <c r="AD47" s="260"/>
+      <c r="AE47" s="260"/>
+      <c r="AF47" s="260"/>
+      <c r="AG47" s="260"/>
+      <c r="AH47" s="260"/>
+      <c r="AK47" s="119" t="s">
         <v>792</v>
       </c>
-      <c r="AL47" s="212"/>
-      <c r="AM47" s="212"/>
-      <c r="AN47" s="212"/>
-      <c r="AO47" s="212"/>
-      <c r="AP47" s="212"/>
-      <c r="AQ47" s="212"/>
-      <c r="AR47" s="212"/>
-      <c r="AS47" s="212"/>
-      <c r="AT47" s="212"/>
-      <c r="AU47" s="212"/>
-      <c r="AV47" s="212"/>
-      <c r="AW47" s="212"/>
-      <c r="AX47" s="212"/>
-      <c r="AY47" s="212"/>
-      <c r="AZ47" s="212"/>
+      <c r="AL47" s="119"/>
+      <c r="AM47" s="119"/>
+      <c r="AN47" s="119"/>
+      <c r="AO47" s="119"/>
+      <c r="AP47" s="119"/>
+      <c r="AQ47" s="119"/>
+      <c r="AR47" s="119"/>
+      <c r="AS47" s="119"/>
+      <c r="AT47" s="119"/>
+      <c r="AU47" s="119"/>
+      <c r="AV47" s="119"/>
+      <c r="AW47" s="119"/>
+      <c r="AX47" s="119"/>
+      <c r="AY47" s="119"/>
+      <c r="AZ47" s="119"/>
     </row>
     <row r="48" spans="1:53" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E30:AZ30"/>
+    <mergeCell ref="E31:AZ31"/>
+    <mergeCell ref="E32:AZ32"/>
+    <mergeCell ref="E26:AZ26"/>
+    <mergeCell ref="E27:AZ27"/>
+    <mergeCell ref="E28:AZ28"/>
+    <mergeCell ref="E29:AZ29"/>
+    <mergeCell ref="A46:P46"/>
+    <mergeCell ref="S46:AH46"/>
+    <mergeCell ref="AK46:AZ46"/>
+    <mergeCell ref="A47:P47"/>
+    <mergeCell ref="AK47:AZ47"/>
+    <mergeCell ref="S47:U47"/>
+    <mergeCell ref="V47:AH47"/>
+    <mergeCell ref="E42:AZ42"/>
+    <mergeCell ref="E39:AZ39"/>
+    <mergeCell ref="E40:AZ40"/>
+    <mergeCell ref="E41:AZ41"/>
+    <mergeCell ref="E38:AZ38"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="E9:AZ9"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="E33:AZ33"/>
+    <mergeCell ref="E34:AZ34"/>
+    <mergeCell ref="E37:AZ37"/>
+    <mergeCell ref="E35:AZ35"/>
+    <mergeCell ref="E36:AZ36"/>
+    <mergeCell ref="A4:AZ4"/>
+    <mergeCell ref="K2:AP2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="E6:AZ6"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="AS1:AZ3"/>
+    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A45:P45"/>
     <mergeCell ref="S45:AH45"/>
@@ -12351,56 +12400,11 @@
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A4:AZ4"/>
-    <mergeCell ref="K2:AP2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="E6:AZ6"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="AS1:AZ3"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="E9:AZ9"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="E33:AZ33"/>
-    <mergeCell ref="E34:AZ34"/>
-    <mergeCell ref="E37:AZ37"/>
-    <mergeCell ref="E35:AZ35"/>
-    <mergeCell ref="E36:AZ36"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="E42:AZ42"/>
-    <mergeCell ref="E39:AZ39"/>
-    <mergeCell ref="E40:AZ40"/>
-    <mergeCell ref="E41:AZ41"/>
-    <mergeCell ref="E38:AZ38"/>
-    <mergeCell ref="A46:P46"/>
-    <mergeCell ref="S46:AH46"/>
-    <mergeCell ref="AK46:AZ46"/>
-    <mergeCell ref="A47:P47"/>
-    <mergeCell ref="AK47:AZ47"/>
-    <mergeCell ref="S47:U47"/>
-    <mergeCell ref="V47:AH47"/>
-    <mergeCell ref="E30:AZ30"/>
-    <mergeCell ref="E31:AZ31"/>
-    <mergeCell ref="E32:AZ32"/>
-    <mergeCell ref="E26:AZ26"/>
-    <mergeCell ref="E27:AZ27"/>
-    <mergeCell ref="E28:AZ28"/>
-    <mergeCell ref="E29:AZ29"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -12434,126 +12438,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="14" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="264" t="e" vm="1">
+      <c r="A1" s="266" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
-      <c r="N1" s="265"/>
-      <c r="O1" s="266"/>
+      <c r="B1" s="267"/>
+      <c r="C1" s="267"/>
+      <c r="D1" s="267"/>
+      <c r="E1" s="267"/>
+      <c r="F1" s="267"/>
+      <c r="G1" s="267"/>
+      <c r="H1" s="267"/>
+      <c r="I1" s="267"/>
+      <c r="J1" s="267"/>
+      <c r="K1" s="267"/>
+      <c r="L1" s="267"/>
+      <c r="M1" s="267"/>
+      <c r="N1" s="267"/>
+      <c r="O1" s="268"/>
     </row>
     <row r="2" spans="1:15" s="14" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="267"/>
-      <c r="B2" s="268"/>
-      <c r="C2" s="268"/>
-      <c r="D2" s="268"/>
-      <c r="E2" s="268"/>
-      <c r="F2" s="268"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="268"/>
-      <c r="I2" s="268"/>
-      <c r="J2" s="268"/>
-      <c r="K2" s="268"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="268"/>
-      <c r="N2" s="268"/>
-      <c r="O2" s="269"/>
+      <c r="A2" s="269"/>
+      <c r="B2" s="270"/>
+      <c r="C2" s="270"/>
+      <c r="D2" s="270"/>
+      <c r="E2" s="270"/>
+      <c r="F2" s="270"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="270"/>
+      <c r="I2" s="270"/>
+      <c r="J2" s="270"/>
+      <c r="K2" s="270"/>
+      <c r="L2" s="270"/>
+      <c r="M2" s="270"/>
+      <c r="N2" s="270"/>
+      <c r="O2" s="271"/>
     </row>
     <row r="3" spans="1:15" s="14" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="270"/>
-      <c r="B3" s="271"/>
-      <c r="C3" s="271"/>
-      <c r="D3" s="271"/>
-      <c r="E3" s="271"/>
-      <c r="F3" s="271"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="271"/>
-      <c r="I3" s="271"/>
-      <c r="J3" s="271"/>
-      <c r="K3" s="271"/>
-      <c r="L3" s="271"/>
-      <c r="M3" s="271"/>
-      <c r="N3" s="271"/>
-      <c r="O3" s="272"/>
+      <c r="A3" s="272"/>
+      <c r="B3" s="273"/>
+      <c r="C3" s="273"/>
+      <c r="D3" s="273"/>
+      <c r="E3" s="273"/>
+      <c r="F3" s="273"/>
+      <c r="G3" s="273"/>
+      <c r="H3" s="273"/>
+      <c r="I3" s="273"/>
+      <c r="J3" s="273"/>
+      <c r="K3" s="273"/>
+      <c r="L3" s="273"/>
+      <c r="M3" s="273"/>
+      <c r="N3" s="273"/>
+      <c r="O3" s="274"/>
     </row>
     <row r="4" spans="1:15" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="261" t="s">
+      <c r="A4" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="262"/>
-      <c r="C4" s="262"/>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
-      <c r="M4" s="262"/>
-      <c r="N4" s="262"/>
-      <c r="O4" s="263"/>
+      <c r="B4" s="264"/>
+      <c r="C4" s="264"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
+      <c r="M4" s="264"/>
+      <c r="N4" s="264"/>
+      <c r="O4" s="265"/>
     </row>
     <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="273" t="s">
+      <c r="A5" s="275" t="s">
         <v>106</v>
       </c>
-      <c r="B5" s="259" t="s">
+      <c r="B5" s="261" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="259" t="s">
+      <c r="C5" s="261" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="259" t="s">
+      <c r="D5" s="261" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="259" t="s">
+      <c r="E5" s="261" t="s">
         <v>110</v>
       </c>
-      <c r="F5" s="259" t="s">
+      <c r="F5" s="261" t="s">
         <v>111</v>
       </c>
-      <c r="G5" s="259" t="s">
+      <c r="G5" s="261" t="s">
         <v>112</v>
       </c>
-      <c r="H5" s="259" t="s">
+      <c r="H5" s="261" t="s">
         <v>113</v>
       </c>
-      <c r="I5" s="259" t="s">
+      <c r="I5" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="J5" s="275" t="s">
+      <c r="J5" s="277" t="s">
         <v>115</v>
       </c>
-      <c r="K5" s="276"/>
-      <c r="L5" s="277"/>
-      <c r="M5" s="275" t="s">
+      <c r="K5" s="278"/>
+      <c r="L5" s="279"/>
+      <c r="M5" s="277" t="s">
         <v>116</v>
       </c>
-      <c r="N5" s="276"/>
-      <c r="O5" s="278"/>
+      <c r="N5" s="278"/>
+      <c r="O5" s="280"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="274"/>
-      <c r="B6" s="260"/>
-      <c r="C6" s="260"/>
-      <c r="D6" s="260"/>
-      <c r="E6" s="260"/>
-      <c r="F6" s="260"/>
-      <c r="G6" s="260"/>
-      <c r="H6" s="260"/>
-      <c r="I6" s="260"/>
+      <c r="A6" s="276"/>
+      <c r="B6" s="262"/>
+      <c r="C6" s="262"/>
+      <c r="D6" s="262"/>
+      <c r="E6" s="262"/>
+      <c r="F6" s="262"/>
+      <c r="G6" s="262"/>
+      <c r="H6" s="262"/>
+      <c r="I6" s="262"/>
       <c r="J6" s="84" t="s">
         <v>117</v>
       </c>
@@ -18261,110 +18265,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="14" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="264" t="e" vm="1">
+      <c r="A1" s="266" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="266"/>
+      <c r="B1" s="267"/>
+      <c r="C1" s="267"/>
+      <c r="D1" s="267"/>
+      <c r="E1" s="267"/>
+      <c r="F1" s="267"/>
+      <c r="G1" s="267"/>
+      <c r="H1" s="267"/>
+      <c r="I1" s="267"/>
+      <c r="J1" s="267"/>
+      <c r="K1" s="267"/>
+      <c r="L1" s="267"/>
+      <c r="M1" s="268"/>
     </row>
     <row r="2" spans="1:13" s="14" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="267"/>
-      <c r="B2" s="268"/>
-      <c r="C2" s="268"/>
-      <c r="D2" s="268"/>
-      <c r="E2" s="268"/>
-      <c r="F2" s="268"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="268"/>
-      <c r="I2" s="268"/>
-      <c r="J2" s="268"/>
-      <c r="K2" s="268"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="269"/>
+      <c r="A2" s="269"/>
+      <c r="B2" s="270"/>
+      <c r="C2" s="270"/>
+      <c r="D2" s="270"/>
+      <c r="E2" s="270"/>
+      <c r="F2" s="270"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="270"/>
+      <c r="I2" s="270"/>
+      <c r="J2" s="270"/>
+      <c r="K2" s="270"/>
+      <c r="L2" s="270"/>
+      <c r="M2" s="271"/>
     </row>
     <row r="3" spans="1:13" s="14" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="270"/>
-      <c r="B3" s="271"/>
-      <c r="C3" s="271"/>
-      <c r="D3" s="271"/>
-      <c r="E3" s="271"/>
-      <c r="F3" s="271"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="271"/>
-      <c r="I3" s="271"/>
-      <c r="J3" s="271"/>
-      <c r="K3" s="271"/>
-      <c r="L3" s="271"/>
-      <c r="M3" s="272"/>
+      <c r="A3" s="272"/>
+      <c r="B3" s="273"/>
+      <c r="C3" s="273"/>
+      <c r="D3" s="273"/>
+      <c r="E3" s="273"/>
+      <c r="F3" s="273"/>
+      <c r="G3" s="273"/>
+      <c r="H3" s="273"/>
+      <c r="I3" s="273"/>
+      <c r="J3" s="273"/>
+      <c r="K3" s="273"/>
+      <c r="L3" s="273"/>
+      <c r="M3" s="274"/>
     </row>
     <row r="4" spans="1:13" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="261" t="s">
+      <c r="A4" s="263" t="s">
         <v>660</v>
       </c>
-      <c r="B4" s="262"/>
-      <c r="C4" s="262"/>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
-      <c r="M4" s="263"/>
+      <c r="B4" s="264"/>
+      <c r="C4" s="264"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
+      <c r="M4" s="265"/>
     </row>
     <row r="5" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="285" t="s">
+      <c r="A5" s="287" t="s">
         <v>661</v>
       </c>
-      <c r="B5" s="279" t="s">
+      <c r="B5" s="281" t="s">
         <v>662</v>
       </c>
-      <c r="C5" s="279" t="s">
+      <c r="C5" s="281" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="279" t="s">
+      <c r="D5" s="281" t="s">
         <v>108</v>
       </c>
-      <c r="E5" s="279" t="s">
+      <c r="E5" s="281" t="s">
         <v>109</v>
       </c>
-      <c r="F5" s="279" t="s">
+      <c r="F5" s="281" t="s">
         <v>110</v>
       </c>
-      <c r="G5" s="279" t="s">
+      <c r="G5" s="281" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="281" t="s">
+      <c r="H5" s="283" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="282"/>
-      <c r="J5" s="283"/>
-      <c r="K5" s="281" t="s">
+      <c r="I5" s="284"/>
+      <c r="J5" s="285"/>
+      <c r="K5" s="283" t="s">
         <v>116</v>
       </c>
-      <c r="L5" s="282"/>
-      <c r="M5" s="284"/>
+      <c r="L5" s="284"/>
+      <c r="M5" s="286"/>
     </row>
     <row r="6" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="286"/>
-      <c r="B6" s="280"/>
-      <c r="C6" s="280"/>
-      <c r="D6" s="280"/>
-      <c r="E6" s="280"/>
-      <c r="F6" s="280"/>
-      <c r="G6" s="280"/>
+      <c r="A6" s="288"/>
+      <c r="B6" s="282"/>
+      <c r="C6" s="282"/>
+      <c r="D6" s="282"/>
+      <c r="E6" s="282"/>
+      <c r="F6" s="282"/>
+      <c r="G6" s="282"/>
       <c r="H6" s="50" t="s">
         <v>117</v>
       </c>
@@ -19451,6 +19455,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c24bca33-91ee-4c94-9d6c-305b441d02fd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e46781df-dd49-4a0f-be02-040bfbf345c5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2EBC4C97F3EED4F8F99B50CD61D9AF7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0ffa3ef56536b291ffb1e746207cdfaf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e46781df-dd49-4a0f-be02-040bfbf345c5" xmlns:ns3="c24bca33-91ee-4c94-9d6c-305b441d02fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="82d71f54c8a292e50b13588301f7fd2c" ns2:_="" ns3:_="">
     <xsd:import namespace="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
@@ -19679,27 +19703,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c24bca33-91ee-4c94-9d6c-305b441d02fd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e46781df-dd49-4a0f-be02-040bfbf345c5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA908177-54FE-4386-8E64-F855D4FAA630}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F87E2A-9E0E-44C0-A603-7E661F8ABEB3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c24bca33-91ee-4c94-9d6c-305b441d02fd"/>
+    <ds:schemaRef ds:uri="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDAB891A-AABF-4B04-8872-1A9CED3578DB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19716,23 +19739,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F87E2A-9E0E-44C0-A603-7E661F8ABEB3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c24bca33-91ee-4c94-9d6c-305b441d02fd"/>
-    <ds:schemaRef ds:uri="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA908177-54FE-4386-8E64-F855D4FAA630}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/RSC 08.0000.25 - Relatório de Serviço de Campo - Padrão - Rev.38.xlsx
+++ b/RSC 08.0000.25 - Relatório de Serviço de Campo - Padrão - Rev.38.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ktsabr-my.sharepoint.com/personal/gustavo_arruda_ktsa_com_br/Documents/PROJETOS/Engenharia/RSC - Relatório de Serviço de Campo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{F948FEA9-3545-4234-B576-12B0A63E47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63DB7B7C-6AA0-4CC0-89C3-D60F6F85F75F}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="13_ncr:1_{F948FEA9-3545-4234-B576-12B0A63E47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1631F2B-D7C2-4F68-93A8-65A236BA8195}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2688,7 +2688,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="48">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -3269,6 +3269,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3280,7 +3295,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="289">
+  <cellXfs count="290">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3498,31 +3513,466 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3531,18 +3981,6 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3567,482 +4005,59 @@
     <xf numFmtId="4" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="4" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4109,6 +4124,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4743,10 +4761,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -5173,14 +5187,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="137"/>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="139"/>
+      <c r="A1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="172"/>
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
       <c r="K1" s="21"/>
@@ -5217,87 +5231,87 @@
       <c r="AP1" s="22"/>
       <c r="AQ1" s="22"/>
       <c r="AR1" s="22"/>
-      <c r="AS1" s="146" t="s">
+      <c r="AS1" s="179" t="s">
         <v>0</v>
       </c>
-      <c r="AT1" s="147"/>
-      <c r="AU1" s="147"/>
-      <c r="AV1" s="147"/>
-      <c r="AW1" s="147"/>
-      <c r="AX1" s="147"/>
-      <c r="AY1" s="147"/>
-      <c r="AZ1" s="148"/>
+      <c r="AT1" s="180"/>
+      <c r="AU1" s="180"/>
+      <c r="AV1" s="180"/>
+      <c r="AW1" s="180"/>
+      <c r="AX1" s="180"/>
+      <c r="AY1" s="180"/>
+      <c r="AZ1" s="181"/>
       <c r="BD1" s="23"/>
       <c r="BF1" s="27"/>
       <c r="BG1" s="27"/>
     </row>
     <row r="2" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="140"/>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="142"/>
-      <c r="K2" s="156" t="s">
+      <c r="A2" s="173"/>
+      <c r="B2" s="174"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="175"/>
+      <c r="K2" s="189" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="157"/>
-      <c r="R2" s="157"/>
-      <c r="S2" s="157"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="157"/>
-      <c r="W2" s="157"/>
-      <c r="X2" s="157"/>
-      <c r="Y2" s="157"/>
-      <c r="Z2" s="157"/>
-      <c r="AA2" s="157"/>
-      <c r="AB2" s="157"/>
-      <c r="AC2" s="157"/>
-      <c r="AD2" s="157"/>
-      <c r="AE2" s="157"/>
-      <c r="AF2" s="157"/>
-      <c r="AG2" s="157"/>
-      <c r="AH2" s="157"/>
-      <c r="AI2" s="157"/>
-      <c r="AJ2" s="157"/>
-      <c r="AK2" s="157"/>
-      <c r="AL2" s="157"/>
-      <c r="AM2" s="157"/>
-      <c r="AN2" s="157"/>
-      <c r="AO2" s="157"/>
-      <c r="AP2" s="157"/>
+      <c r="L2" s="190"/>
+      <c r="M2" s="190"/>
+      <c r="N2" s="190"/>
+      <c r="O2" s="190"/>
+      <c r="P2" s="190"/>
+      <c r="Q2" s="190"/>
+      <c r="R2" s="190"/>
+      <c r="S2" s="190"/>
+      <c r="T2" s="190"/>
+      <c r="U2" s="190"/>
+      <c r="V2" s="190"/>
+      <c r="W2" s="190"/>
+      <c r="X2" s="190"/>
+      <c r="Y2" s="190"/>
+      <c r="Z2" s="190"/>
+      <c r="AA2" s="190"/>
+      <c r="AB2" s="190"/>
+      <c r="AC2" s="190"/>
+      <c r="AD2" s="190"/>
+      <c r="AE2" s="190"/>
+      <c r="AF2" s="190"/>
+      <c r="AG2" s="190"/>
+      <c r="AH2" s="190"/>
+      <c r="AI2" s="190"/>
+      <c r="AJ2" s="190"/>
+      <c r="AK2" s="190"/>
+      <c r="AL2" s="190"/>
+      <c r="AM2" s="190"/>
+      <c r="AN2" s="190"/>
+      <c r="AO2" s="190"/>
+      <c r="AP2" s="190"/>
       <c r="AQ2" s="17"/>
       <c r="AR2" s="17"/>
-      <c r="AS2" s="149"/>
-      <c r="AT2" s="150"/>
-      <c r="AU2" s="150"/>
-      <c r="AV2" s="150"/>
-      <c r="AW2" s="150"/>
-      <c r="AX2" s="150"/>
-      <c r="AY2" s="150"/>
-      <c r="AZ2" s="151"/>
+      <c r="AS2" s="182"/>
+      <c r="AT2" s="183"/>
+      <c r="AU2" s="183"/>
+      <c r="AV2" s="183"/>
+      <c r="AW2" s="183"/>
+      <c r="AX2" s="183"/>
+      <c r="AY2" s="183"/>
+      <c r="AZ2" s="184"/>
       <c r="BA2" s="7"/>
       <c r="BF2" s="25"/>
       <c r="BG2" s="25"/>
       <c r="BH2" s="25"/>
     </row>
     <row r="3" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="143"/>
-      <c r="B3" s="144"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="144"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="145"/>
+      <c r="A3" s="176"/>
+      <c r="B3" s="177"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="177"/>
+      <c r="H3" s="178"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -5334,392 +5348,392 @@
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
       <c r="AR3" s="4"/>
-      <c r="AS3" s="152"/>
-      <c r="AT3" s="153"/>
-      <c r="AU3" s="153"/>
-      <c r="AV3" s="153"/>
-      <c r="AW3" s="153"/>
-      <c r="AX3" s="153"/>
-      <c r="AY3" s="153"/>
-      <c r="AZ3" s="154"/>
+      <c r="AS3" s="185"/>
+      <c r="AT3" s="186"/>
+      <c r="AU3" s="186"/>
+      <c r="AV3" s="186"/>
+      <c r="AW3" s="186"/>
+      <c r="AX3" s="186"/>
+      <c r="AY3" s="186"/>
+      <c r="AZ3" s="187"/>
     </row>
     <row r="4" spans="1:60" s="3" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="191" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="101"/>
-      <c r="L4" s="101"/>
-      <c r="M4" s="101"/>
-      <c r="N4" s="101"/>
-      <c r="O4" s="101"/>
-      <c r="P4" s="101"/>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="101"/>
-      <c r="S4" s="101"/>
-      <c r="T4" s="101"/>
-      <c r="U4" s="101"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="101"/>
-      <c r="X4" s="101"/>
-      <c r="Y4" s="101"/>
-      <c r="Z4" s="101"/>
-      <c r="AA4" s="101"/>
-      <c r="AB4" s="101"/>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="101"/>
-      <c r="AE4" s="101"/>
-      <c r="AF4" s="101"/>
-      <c r="AG4" s="101"/>
-      <c r="AH4" s="101"/>
-      <c r="AI4" s="101"/>
-      <c r="AJ4" s="101"/>
-      <c r="AK4" s="101"/>
-      <c r="AL4" s="101"/>
-      <c r="AM4" s="101"/>
-      <c r="AN4" s="101"/>
-      <c r="AO4" s="101"/>
-      <c r="AP4" s="101"/>
-      <c r="AQ4" s="101"/>
-      <c r="AR4" s="101"/>
-      <c r="AS4" s="101"/>
-      <c r="AT4" s="101"/>
-      <c r="AU4" s="101"/>
-      <c r="AV4" s="101"/>
-      <c r="AW4" s="101"/>
-      <c r="AX4" s="101"/>
-      <c r="AY4" s="101"/>
-      <c r="AZ4" s="102"/>
+      <c r="B4" s="192"/>
+      <c r="C4" s="192"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="192"/>
+      <c r="K4" s="192"/>
+      <c r="L4" s="192"/>
+      <c r="M4" s="192"/>
+      <c r="N4" s="192"/>
+      <c r="O4" s="192"/>
+      <c r="P4" s="192"/>
+      <c r="Q4" s="192"/>
+      <c r="R4" s="192"/>
+      <c r="S4" s="192"/>
+      <c r="T4" s="192"/>
+      <c r="U4" s="192"/>
+      <c r="V4" s="192"/>
+      <c r="W4" s="192"/>
+      <c r="X4" s="192"/>
+      <c r="Y4" s="192"/>
+      <c r="Z4" s="192"/>
+      <c r="AA4" s="192"/>
+      <c r="AB4" s="192"/>
+      <c r="AC4" s="192"/>
+      <c r="AD4" s="192"/>
+      <c r="AE4" s="192"/>
+      <c r="AF4" s="192"/>
+      <c r="AG4" s="192"/>
+      <c r="AH4" s="192"/>
+      <c r="AI4" s="192"/>
+      <c r="AJ4" s="192"/>
+      <c r="AK4" s="192"/>
+      <c r="AL4" s="192"/>
+      <c r="AM4" s="192"/>
+      <c r="AN4" s="192"/>
+      <c r="AO4" s="192"/>
+      <c r="AP4" s="192"/>
+      <c r="AQ4" s="192"/>
+      <c r="AR4" s="192"/>
+      <c r="AS4" s="192"/>
+      <c r="AT4" s="192"/>
+      <c r="AU4" s="192"/>
+      <c r="AV4" s="192"/>
+      <c r="AW4" s="192"/>
+      <c r="AX4" s="192"/>
+      <c r="AY4" s="192"/>
+      <c r="AZ4" s="193"/>
       <c r="BA4" s="9"/>
       <c r="BB4" s="9"/>
       <c r="BC4" s="9"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="161" t="s">
+      <c r="A5" s="197" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="162"/>
-      <c r="C5" s="162"/>
-      <c r="D5" s="162"/>
-      <c r="E5" s="162"/>
-      <c r="F5" s="162"/>
-      <c r="G5" s="171"/>
-      <c r="H5" s="171"/>
-      <c r="I5" s="171"/>
-      <c r="J5" s="171"/>
-      <c r="K5" s="171"/>
-      <c r="L5" s="171"/>
-      <c r="M5" s="171"/>
-      <c r="N5" s="171"/>
-      <c r="O5" s="171"/>
-      <c r="P5" s="171"/>
-      <c r="Q5" s="171"/>
-      <c r="R5" s="171"/>
-      <c r="S5" s="171"/>
-      <c r="T5" s="171"/>
-      <c r="U5" s="171"/>
-      <c r="V5" s="171"/>
-      <c r="W5" s="171"/>
-      <c r="X5" s="171"/>
-      <c r="Y5" s="171"/>
-      <c r="Z5" s="171"/>
-      <c r="AA5" s="171"/>
-      <c r="AB5" s="171"/>
+      <c r="B5" s="198"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="198"/>
+      <c r="E5" s="198"/>
+      <c r="F5" s="198"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="203"/>
+      <c r="I5" s="203"/>
+      <c r="J5" s="203"/>
+      <c r="K5" s="203"/>
+      <c r="L5" s="203"/>
+      <c r="M5" s="203"/>
+      <c r="N5" s="203"/>
+      <c r="O5" s="203"/>
+      <c r="P5" s="203"/>
+      <c r="Q5" s="203"/>
+      <c r="R5" s="203"/>
+      <c r="S5" s="203"/>
+      <c r="T5" s="203"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="203"/>
+      <c r="W5" s="203"/>
+      <c r="X5" s="203"/>
+      <c r="Y5" s="203"/>
+      <c r="Z5" s="203"/>
+      <c r="AA5" s="203"/>
+      <c r="AB5" s="203"/>
       <c r="AC5" s="55"/>
       <c r="AD5" s="58"/>
-      <c r="AE5" s="170" t="s">
+      <c r="AE5" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="AF5" s="170"/>
-      <c r="AG5" s="170"/>
-      <c r="AH5" s="170"/>
-      <c r="AI5" s="170"/>
-      <c r="AJ5" s="170"/>
-      <c r="AK5" s="170"/>
-      <c r="AL5" s="181"/>
-      <c r="AM5" s="181"/>
-      <c r="AN5" s="181"/>
-      <c r="AO5" s="181"/>
-      <c r="AP5" s="181"/>
-      <c r="AQ5" s="181"/>
-      <c r="AR5" s="181"/>
-      <c r="AS5" s="181"/>
-      <c r="AT5" s="181"/>
-      <c r="AU5" s="181"/>
-      <c r="AV5" s="181"/>
-      <c r="AW5" s="181"/>
-      <c r="AX5" s="181"/>
-      <c r="AY5" s="181"/>
-      <c r="AZ5" s="182"/>
+      <c r="AF5" s="106"/>
+      <c r="AG5" s="106"/>
+      <c r="AH5" s="106"/>
+      <c r="AI5" s="106"/>
+      <c r="AJ5" s="106"/>
+      <c r="AK5" s="106"/>
+      <c r="AL5" s="210"/>
+      <c r="AM5" s="210"/>
+      <c r="AN5" s="210"/>
+      <c r="AO5" s="210"/>
+      <c r="AP5" s="210"/>
+      <c r="AQ5" s="210"/>
+      <c r="AR5" s="210"/>
+      <c r="AS5" s="210"/>
+      <c r="AT5" s="210"/>
+      <c r="AU5" s="210"/>
+      <c r="AV5" s="210"/>
+      <c r="AW5" s="210"/>
+      <c r="AX5" s="210"/>
+      <c r="AY5" s="210"/>
+      <c r="AZ5" s="211"/>
       <c r="BA5"/>
       <c r="BB5" s="9"/>
       <c r="BC5" s="9"/>
       <c r="BD5" s="9"/>
     </row>
     <row r="6" spans="1:60" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="161" t="s">
+      <c r="A6" s="197" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="162"/>
-      <c r="C6" s="162"/>
-      <c r="D6" s="162"/>
-      <c r="E6" s="162"/>
-      <c r="F6" s="162"/>
-      <c r="G6" s="136" t="str">
+      <c r="B6" s="198"/>
+      <c r="C6" s="198"/>
+      <c r="D6" s="198"/>
+      <c r="E6" s="198"/>
+      <c r="F6" s="198"/>
+      <c r="G6" s="91" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,4,0))</f>
         <v/>
       </c>
-      <c r="H6" s="136"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="136"/>
-      <c r="K6" s="136"/>
-      <c r="L6" s="136"/>
-      <c r="M6" s="136"/>
-      <c r="N6" s="136"/>
-      <c r="O6" s="136"/>
-      <c r="P6" s="136"/>
-      <c r="Q6" s="136"/>
-      <c r="R6" s="136"/>
-      <c r="S6" s="136"/>
-      <c r="T6" s="136"/>
-      <c r="U6" s="136"/>
-      <c r="V6" s="136"/>
-      <c r="W6" s="136"/>
-      <c r="X6" s="136"/>
-      <c r="Y6" s="136"/>
-      <c r="Z6" s="136"/>
-      <c r="AA6" s="136"/>
-      <c r="AB6" s="136"/>
-      <c r="AC6" s="136"/>
-      <c r="AD6" s="136"/>
-      <c r="AE6" s="136"/>
-      <c r="AF6" s="136"/>
-      <c r="AG6" s="136"/>
-      <c r="AH6" s="136"/>
-      <c r="AI6" s="136"/>
-      <c r="AJ6" s="136"/>
-      <c r="AK6" s="136"/>
-      <c r="AL6" s="136"/>
-      <c r="AM6" s="136"/>
-      <c r="AN6" s="136"/>
-      <c r="AO6" s="136"/>
-      <c r="AP6" s="136"/>
-      <c r="AQ6" s="136"/>
-      <c r="AR6" s="136"/>
-      <c r="AS6" s="136"/>
-      <c r="AT6" s="136"/>
-      <c r="AU6" s="136"/>
-      <c r="AV6" s="136"/>
-      <c r="AW6" s="136"/>
-      <c r="AX6" s="136"/>
-      <c r="AY6" s="136"/>
-      <c r="AZ6" s="155"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="91"/>
+      <c r="K6" s="91"/>
+      <c r="L6" s="91"/>
+      <c r="M6" s="91"/>
+      <c r="N6" s="91"/>
+      <c r="O6" s="91"/>
+      <c r="P6" s="91"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
+      <c r="V6" s="91"/>
+      <c r="W6" s="91"/>
+      <c r="X6" s="91"/>
+      <c r="Y6" s="91"/>
+      <c r="Z6" s="91"/>
+      <c r="AA6" s="91"/>
+      <c r="AB6" s="91"/>
+      <c r="AC6" s="91"/>
+      <c r="AD6" s="91"/>
+      <c r="AE6" s="91"/>
+      <c r="AF6" s="91"/>
+      <c r="AG6" s="91"/>
+      <c r="AH6" s="91"/>
+      <c r="AI6" s="91"/>
+      <c r="AJ6" s="91"/>
+      <c r="AK6" s="91"/>
+      <c r="AL6" s="91"/>
+      <c r="AM6" s="91"/>
+      <c r="AN6" s="91"/>
+      <c r="AO6" s="91"/>
+      <c r="AP6" s="91"/>
+      <c r="AQ6" s="91"/>
+      <c r="AR6" s="91"/>
+      <c r="AS6" s="91"/>
+      <c r="AT6" s="91"/>
+      <c r="AU6" s="91"/>
+      <c r="AV6" s="91"/>
+      <c r="AW6" s="91"/>
+      <c r="AX6" s="91"/>
+      <c r="AY6" s="91"/>
+      <c r="AZ6" s="188"/>
     </row>
     <row r="7" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="161" t="s">
+      <c r="A7" s="197" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="162"/>
-      <c r="C7" s="162"/>
-      <c r="D7" s="162"/>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="136" t="str">
+      <c r="B7" s="198"/>
+      <c r="C7" s="198"/>
+      <c r="D7" s="198"/>
+      <c r="E7" s="198"/>
+      <c r="F7" s="198"/>
+      <c r="G7" s="91" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,5,0))</f>
         <v/>
       </c>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="136"/>
-      <c r="L7" s="136"/>
-      <c r="M7" s="136"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="136"/>
-      <c r="P7" s="136"/>
-      <c r="Q7" s="136"/>
-      <c r="R7" s="136"/>
-      <c r="S7" s="136"/>
-      <c r="T7" s="136"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="91"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="91"/>
+      <c r="Q7" s="91"/>
+      <c r="R7" s="91"/>
+      <c r="S7" s="91"/>
+      <c r="T7" s="91"/>
       <c r="U7" s="57"/>
-      <c r="V7" s="176" t="s">
+      <c r="V7" s="163" t="s">
         <v>8</v>
       </c>
-      <c r="W7" s="176"/>
-      <c r="X7" s="176"/>
-      <c r="Y7" s="176"/>
-      <c r="Z7" s="136" t="str">
+      <c r="W7" s="163"/>
+      <c r="X7" s="163"/>
+      <c r="Y7" s="163"/>
+      <c r="Z7" s="91" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,2,0))</f>
         <v/>
       </c>
-      <c r="AA7" s="136"/>
-      <c r="AB7" s="136"/>
-      <c r="AC7" s="136"/>
-      <c r="AD7" s="136"/>
-      <c r="AE7" s="136"/>
-      <c r="AF7" s="136"/>
-      <c r="AG7" s="136"/>
-      <c r="AH7" s="136"/>
-      <c r="AI7" s="136"/>
-      <c r="AJ7" s="136"/>
-      <c r="AK7" s="136"/>
-      <c r="AL7" s="136"/>
-      <c r="AM7" s="136"/>
-      <c r="AN7" s="136"/>
-      <c r="AO7" s="136"/>
-      <c r="AP7" s="136"/>
+      <c r="AA7" s="91"/>
+      <c r="AB7" s="91"/>
+      <c r="AC7" s="91"/>
+      <c r="AD7" s="91"/>
+      <c r="AE7" s="91"/>
+      <c r="AF7" s="91"/>
+      <c r="AG7" s="91"/>
+      <c r="AH7" s="91"/>
+      <c r="AI7" s="91"/>
+      <c r="AJ7" s="91"/>
+      <c r="AK7" s="91"/>
+      <c r="AL7" s="91"/>
+      <c r="AM7" s="91"/>
+      <c r="AN7" s="91"/>
+      <c r="AO7" s="91"/>
+      <c r="AP7" s="91"/>
       <c r="AQ7" s="57"/>
-      <c r="AR7" s="176" t="s">
+      <c r="AR7" s="163" t="s">
         <v>9</v>
       </c>
-      <c r="AS7" s="176"/>
-      <c r="AT7" s="176"/>
-      <c r="AU7" s="176"/>
-      <c r="AV7" s="187" t="str">
+      <c r="AS7" s="163"/>
+      <c r="AT7" s="163"/>
+      <c r="AU7" s="163"/>
+      <c r="AV7" s="104" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,3,0))</f>
         <v/>
       </c>
-      <c r="AW7" s="187"/>
-      <c r="AX7" s="187"/>
-      <c r="AY7" s="187"/>
-      <c r="AZ7" s="188"/>
+      <c r="AW7" s="104"/>
+      <c r="AX7" s="104"/>
+      <c r="AY7" s="104"/>
+      <c r="AZ7" s="105"/>
       <c r="BA7"/>
     </row>
     <row r="8" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="172" t="s">
+      <c r="A8" s="204" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="173"/>
-      <c r="C8" s="173"/>
-      <c r="D8" s="173"/>
-      <c r="E8" s="173"/>
-      <c r="F8" s="173"/>
-      <c r="G8" s="174" t="str">
+      <c r="B8" s="205"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="205"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="205"/>
+      <c r="G8" s="206" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,6,0))</f>
         <v/>
       </c>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
-      <c r="J8" s="175"/>
-      <c r="K8" s="175"/>
-      <c r="L8" s="175"/>
-      <c r="M8" s="175"/>
-      <c r="N8" s="175"/>
-      <c r="O8" s="175"/>
-      <c r="P8" s="175"/>
-      <c r="Q8" s="175"/>
-      <c r="R8" s="175"/>
-      <c r="S8" s="175"/>
-      <c r="T8" s="175"/>
-      <c r="U8" s="175"/>
-      <c r="V8" s="175"/>
-      <c r="W8" s="175"/>
-      <c r="X8" s="175"/>
-      <c r="Y8" s="175"/>
-      <c r="Z8" s="175"/>
-      <c r="AA8" s="175"/>
-      <c r="AB8" s="175"/>
-      <c r="AC8" s="175"/>
+      <c r="H8" s="207"/>
+      <c r="I8" s="207"/>
+      <c r="J8" s="207"/>
+      <c r="K8" s="207"/>
+      <c r="L8" s="207"/>
+      <c r="M8" s="207"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="207"/>
+      <c r="P8" s="207"/>
+      <c r="Q8" s="207"/>
+      <c r="R8" s="207"/>
+      <c r="S8" s="207"/>
+      <c r="T8" s="207"/>
+      <c r="U8" s="207"/>
+      <c r="V8" s="207"/>
+      <c r="W8" s="207"/>
+      <c r="X8" s="207"/>
+      <c r="Y8" s="207"/>
+      <c r="Z8" s="207"/>
+      <c r="AA8" s="207"/>
+      <c r="AB8" s="207"/>
+      <c r="AC8" s="207"/>
       <c r="AD8" s="59"/>
-      <c r="AE8" s="186" t="s">
+      <c r="AE8" s="164" t="s">
         <v>13</v>
       </c>
-      <c r="AF8" s="186"/>
-      <c r="AG8" s="186"/>
-      <c r="AH8" s="186"/>
-      <c r="AI8" s="186"/>
-      <c r="AJ8" s="186"/>
-      <c r="AK8" s="186"/>
-      <c r="AL8" s="179" t="str">
+      <c r="AF8" s="164"/>
+      <c r="AG8" s="164"/>
+      <c r="AH8" s="164"/>
+      <c r="AI8" s="164"/>
+      <c r="AJ8" s="164"/>
+      <c r="AK8" s="164"/>
+      <c r="AL8" s="93" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,7,0))</f>
         <v/>
       </c>
-      <c r="AM8" s="179"/>
-      <c r="AN8" s="179"/>
-      <c r="AO8" s="179"/>
-      <c r="AP8" s="179"/>
-      <c r="AQ8" s="179"/>
-      <c r="AR8" s="179"/>
-      <c r="AS8" s="179"/>
-      <c r="AT8" s="179"/>
-      <c r="AU8" s="179"/>
-      <c r="AV8" s="179"/>
-      <c r="AW8" s="179"/>
-      <c r="AX8" s="179"/>
-      <c r="AY8" s="179"/>
-      <c r="AZ8" s="180"/>
+      <c r="AM8" s="93"/>
+      <c r="AN8" s="93"/>
+      <c r="AO8" s="93"/>
+      <c r="AP8" s="93"/>
+      <c r="AQ8" s="93"/>
+      <c r="AR8" s="93"/>
+      <c r="AS8" s="93"/>
+      <c r="AT8" s="93"/>
+      <c r="AU8" s="93"/>
+      <c r="AV8" s="93"/>
+      <c r="AW8" s="93"/>
+      <c r="AX8" s="93"/>
+      <c r="AY8" s="93"/>
+      <c r="AZ8" s="94"/>
     </row>
     <row r="9" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="172" t="s">
+      <c r="A9" s="204" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="173"/>
-      <c r="C9" s="173"/>
-      <c r="D9" s="173"/>
-      <c r="E9" s="173"/>
-      <c r="F9" s="173"/>
-      <c r="G9" s="177" t="str">
+      <c r="B9" s="205"/>
+      <c r="C9" s="205"/>
+      <c r="D9" s="205"/>
+      <c r="E9" s="205"/>
+      <c r="F9" s="205"/>
+      <c r="G9" s="208" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,8,0))</f>
         <v/>
       </c>
-      <c r="H9" s="178"/>
-      <c r="I9" s="178"/>
-      <c r="J9" s="178"/>
-      <c r="K9" s="178"/>
-      <c r="L9" s="178"/>
-      <c r="M9" s="178"/>
-      <c r="N9" s="178"/>
-      <c r="O9" s="178"/>
-      <c r="P9" s="178"/>
-      <c r="Q9" s="178"/>
-      <c r="R9" s="178"/>
-      <c r="S9" s="178"/>
-      <c r="T9" s="178"/>
-      <c r="U9" s="178"/>
-      <c r="V9" s="178"/>
-      <c r="W9" s="178"/>
-      <c r="X9" s="178"/>
-      <c r="Y9" s="178"/>
-      <c r="Z9" s="178"/>
-      <c r="AA9" s="178"/>
-      <c r="AB9" s="178"/>
-      <c r="AC9" s="178"/>
+      <c r="H9" s="209"/>
+      <c r="I9" s="209"/>
+      <c r="J9" s="209"/>
+      <c r="K9" s="209"/>
+      <c r="L9" s="209"/>
+      <c r="M9" s="209"/>
+      <c r="N9" s="209"/>
+      <c r="O9" s="209"/>
+      <c r="P9" s="209"/>
+      <c r="Q9" s="209"/>
+      <c r="R9" s="209"/>
+      <c r="S9" s="209"/>
+      <c r="T9" s="209"/>
+      <c r="U9" s="209"/>
+      <c r="V9" s="209"/>
+      <c r="W9" s="209"/>
+      <c r="X9" s="209"/>
+      <c r="Y9" s="209"/>
+      <c r="Z9" s="209"/>
+      <c r="AA9" s="209"/>
+      <c r="AB9" s="209"/>
+      <c r="AC9" s="209"/>
       <c r="AD9" s="59"/>
-      <c r="AE9" s="170" t="s">
+      <c r="AE9" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="AF9" s="170"/>
-      <c r="AG9" s="170"/>
-      <c r="AH9" s="170"/>
-      <c r="AI9" s="170"/>
-      <c r="AJ9" s="170"/>
-      <c r="AK9" s="170"/>
-      <c r="AL9" s="158" t="str">
+      <c r="AF9" s="106"/>
+      <c r="AG9" s="106"/>
+      <c r="AH9" s="106"/>
+      <c r="AI9" s="106"/>
+      <c r="AJ9" s="106"/>
+      <c r="AK9" s="106"/>
+      <c r="AL9" s="194" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,9,0))</f>
         <v/>
       </c>
-      <c r="AM9" s="159"/>
-      <c r="AN9" s="159"/>
-      <c r="AO9" s="159"/>
-      <c r="AP9" s="159"/>
-      <c r="AQ9" s="159"/>
-      <c r="AR9" s="159"/>
-      <c r="AS9" s="159"/>
-      <c r="AT9" s="159"/>
-      <c r="AU9" s="159"/>
-      <c r="AV9" s="159"/>
-      <c r="AW9" s="159"/>
-      <c r="AX9" s="159"/>
-      <c r="AY9" s="159"/>
-      <c r="AZ9" s="160"/>
+      <c r="AM9" s="195"/>
+      <c r="AN9" s="195"/>
+      <c r="AO9" s="195"/>
+      <c r="AP9" s="195"/>
+      <c r="AQ9" s="195"/>
+      <c r="AR9" s="195"/>
+      <c r="AS9" s="195"/>
+      <c r="AT9" s="195"/>
+      <c r="AU9" s="195"/>
+      <c r="AV9" s="195"/>
+      <c r="AW9" s="195"/>
+      <c r="AX9" s="195"/>
+      <c r="AY9" s="195"/>
+      <c r="AZ9" s="196"/>
     </row>
     <row r="10" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
@@ -5781,48 +5795,48 @@
       <c r="H12" s="59"/>
       <c r="I12" s="59"/>
       <c r="J12" s="59"/>
-      <c r="K12" s="230"/>
-      <c r="L12" s="179"/>
-      <c r="M12" s="179"/>
-      <c r="N12" s="179"/>
-      <c r="O12" s="179"/>
-      <c r="P12" s="179"/>
-      <c r="Q12" s="179"/>
-      <c r="R12" s="179"/>
-      <c r="S12" s="179"/>
-      <c r="T12" s="179"/>
-      <c r="U12" s="179"/>
-      <c r="V12" s="179"/>
-      <c r="W12" s="179"/>
-      <c r="X12" s="179"/>
-      <c r="Y12" s="179"/>
-      <c r="Z12" s="179"/>
-      <c r="AA12" s="179"/>
-      <c r="AB12" s="179"/>
-      <c r="AC12" s="179"/>
-      <c r="AD12" s="179"/>
-      <c r="AE12" s="179"/>
-      <c r="AF12" s="179"/>
-      <c r="AG12" s="179"/>
-      <c r="AH12" s="179"/>
-      <c r="AI12" s="179"/>
-      <c r="AJ12" s="179"/>
-      <c r="AK12" s="179"/>
-      <c r="AL12" s="179"/>
-      <c r="AM12" s="179"/>
-      <c r="AN12" s="179"/>
-      <c r="AO12" s="179"/>
-      <c r="AP12" s="179"/>
-      <c r="AQ12" s="179"/>
-      <c r="AR12" s="179"/>
-      <c r="AS12" s="179"/>
-      <c r="AT12" s="179"/>
-      <c r="AU12" s="179"/>
-      <c r="AV12" s="179"/>
-      <c r="AW12" s="179"/>
-      <c r="AX12" s="179"/>
-      <c r="AY12" s="179"/>
-      <c r="AZ12" s="180"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="93"/>
+      <c r="N12" s="93"/>
+      <c r="O12" s="93"/>
+      <c r="P12" s="93"/>
+      <c r="Q12" s="93"/>
+      <c r="R12" s="93"/>
+      <c r="S12" s="93"/>
+      <c r="T12" s="93"/>
+      <c r="U12" s="93"/>
+      <c r="V12" s="93"/>
+      <c r="W12" s="93"/>
+      <c r="X12" s="93"/>
+      <c r="Y12" s="93"/>
+      <c r="Z12" s="93"/>
+      <c r="AA12" s="93"/>
+      <c r="AB12" s="93"/>
+      <c r="AC12" s="93"/>
+      <c r="AD12" s="93"/>
+      <c r="AE12" s="93"/>
+      <c r="AF12" s="93"/>
+      <c r="AG12" s="93"/>
+      <c r="AH12" s="93"/>
+      <c r="AI12" s="93"/>
+      <c r="AJ12" s="93"/>
+      <c r="AK12" s="93"/>
+      <c r="AL12" s="93"/>
+      <c r="AM12" s="93"/>
+      <c r="AN12" s="93"/>
+      <c r="AO12" s="93"/>
+      <c r="AP12" s="93"/>
+      <c r="AQ12" s="93"/>
+      <c r="AR12" s="93"/>
+      <c r="AS12" s="93"/>
+      <c r="AT12" s="93"/>
+      <c r="AU12" s="93"/>
+      <c r="AV12" s="93"/>
+      <c r="AW12" s="93"/>
+      <c r="AX12" s="93"/>
+      <c r="AY12" s="93"/>
+      <c r="AZ12" s="94"/>
     </row>
     <row r="13" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56" t="s">
@@ -5837,398 +5851,398 @@
       <c r="H13" s="59"/>
       <c r="I13" s="59"/>
       <c r="J13" s="59"/>
-      <c r="K13" s="187"/>
-      <c r="L13" s="187"/>
-      <c r="M13" s="187"/>
-      <c r="N13" s="187"/>
-      <c r="O13" s="187"/>
-      <c r="P13" s="187"/>
-      <c r="Q13" s="187"/>
-      <c r="R13" s="187"/>
-      <c r="S13" s="187"/>
-      <c r="T13" s="187"/>
-      <c r="U13" s="187"/>
-      <c r="V13" s="187"/>
-      <c r="W13" s="187"/>
-      <c r="X13" s="187"/>
-      <c r="Y13" s="187"/>
-      <c r="Z13" s="187"/>
-      <c r="AA13" s="187"/>
-      <c r="AB13" s="187"/>
-      <c r="AC13" s="187"/>
-      <c r="AD13" s="187"/>
-      <c r="AE13" s="187"/>
-      <c r="AF13" s="187"/>
-      <c r="AG13" s="187"/>
-      <c r="AH13" s="187"/>
-      <c r="AI13" s="187"/>
-      <c r="AJ13" s="187"/>
-      <c r="AK13" s="187"/>
-      <c r="AL13" s="187"/>
-      <c r="AM13" s="187"/>
-      <c r="AN13" s="187"/>
-      <c r="AO13" s="187"/>
-      <c r="AP13" s="187"/>
-      <c r="AQ13" s="187"/>
-      <c r="AR13" s="187"/>
-      <c r="AS13" s="187"/>
-      <c r="AT13" s="187"/>
-      <c r="AU13" s="187"/>
-      <c r="AV13" s="187"/>
-      <c r="AW13" s="187"/>
-      <c r="AX13" s="187"/>
-      <c r="AY13" s="187"/>
-      <c r="AZ13" s="188"/>
+      <c r="K13" s="104"/>
+      <c r="L13" s="104"/>
+      <c r="M13" s="104"/>
+      <c r="N13" s="104"/>
+      <c r="O13" s="104"/>
+      <c r="P13" s="104"/>
+      <c r="Q13" s="104"/>
+      <c r="R13" s="104"/>
+      <c r="S13" s="104"/>
+      <c r="T13" s="104"/>
+      <c r="U13" s="104"/>
+      <c r="V13" s="104"/>
+      <c r="W13" s="104"/>
+      <c r="X13" s="104"/>
+      <c r="Y13" s="104"/>
+      <c r="Z13" s="104"/>
+      <c r="AA13" s="104"/>
+      <c r="AB13" s="104"/>
+      <c r="AC13" s="104"/>
+      <c r="AD13" s="104"/>
+      <c r="AE13" s="104"/>
+      <c r="AF13" s="104"/>
+      <c r="AG13" s="104"/>
+      <c r="AH13" s="104"/>
+      <c r="AI13" s="104"/>
+      <c r="AJ13" s="104"/>
+      <c r="AK13" s="104"/>
+      <c r="AL13" s="104"/>
+      <c r="AM13" s="104"/>
+      <c r="AN13" s="104"/>
+      <c r="AO13" s="104"/>
+      <c r="AP13" s="104"/>
+      <c r="AQ13" s="104"/>
+      <c r="AR13" s="104"/>
+      <c r="AS13" s="104"/>
+      <c r="AT13" s="104"/>
+      <c r="AU13" s="104"/>
+      <c r="AV13" s="104"/>
+      <c r="AW13" s="104"/>
+      <c r="AX13" s="104"/>
+      <c r="AY13" s="104"/>
+      <c r="AZ13" s="105"/>
     </row>
     <row r="14" spans="1:60" s="10" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="233"/>
-      <c r="B14" s="234"/>
-      <c r="C14" s="234"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="234"/>
-      <c r="F14" s="234"/>
-      <c r="G14" s="234"/>
-      <c r="H14" s="234"/>
-      <c r="I14" s="234"/>
-      <c r="J14" s="234"/>
-      <c r="K14" s="234"/>
-      <c r="L14" s="234"/>
-      <c r="M14" s="234"/>
-      <c r="N14" s="234"/>
-      <c r="O14" s="234"/>
-      <c r="P14" s="234"/>
-      <c r="Q14" s="234"/>
-      <c r="R14" s="234"/>
-      <c r="S14" s="234"/>
-      <c r="T14" s="234"/>
-      <c r="U14" s="234"/>
-      <c r="V14" s="234"/>
-      <c r="W14" s="234"/>
-      <c r="X14" s="234"/>
-      <c r="Y14" s="234"/>
-      <c r="Z14" s="234"/>
-      <c r="AA14" s="234"/>
-      <c r="AB14" s="234"/>
-      <c r="AC14" s="234"/>
-      <c r="AD14" s="234"/>
-      <c r="AE14" s="234"/>
-      <c r="AF14" s="234"/>
-      <c r="AG14" s="234"/>
-      <c r="AH14" s="234"/>
-      <c r="AI14" s="234"/>
-      <c r="AJ14" s="234"/>
-      <c r="AK14" s="234"/>
-      <c r="AL14" s="234"/>
-      <c r="AM14" s="234"/>
-      <c r="AN14" s="234"/>
-      <c r="AO14" s="234"/>
-      <c r="AP14" s="234"/>
-      <c r="AQ14" s="234"/>
-      <c r="AR14" s="234"/>
-      <c r="AS14" s="234"/>
-      <c r="AT14" s="234"/>
-      <c r="AU14" s="234"/>
-      <c r="AV14" s="234"/>
-      <c r="AW14" s="234"/>
-      <c r="AX14" s="234"/>
-      <c r="AY14" s="234"/>
-      <c r="AZ14" s="235"/>
+      <c r="A14" s="107"/>
+      <c r="B14" s="108"/>
+      <c r="C14" s="108"/>
+      <c r="D14" s="108"/>
+      <c r="E14" s="108"/>
+      <c r="F14" s="108"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="108"/>
+      <c r="I14" s="108"/>
+      <c r="J14" s="108"/>
+      <c r="K14" s="108"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="108"/>
+      <c r="N14" s="108"/>
+      <c r="O14" s="108"/>
+      <c r="P14" s="108"/>
+      <c r="Q14" s="108"/>
+      <c r="R14" s="108"/>
+      <c r="S14" s="108"/>
+      <c r="T14" s="108"/>
+      <c r="U14" s="108"/>
+      <c r="V14" s="108"/>
+      <c r="W14" s="108"/>
+      <c r="X14" s="108"/>
+      <c r="Y14" s="108"/>
+      <c r="Z14" s="108"/>
+      <c r="AA14" s="108"/>
+      <c r="AB14" s="108"/>
+      <c r="AC14" s="108"/>
+      <c r="AD14" s="108"/>
+      <c r="AE14" s="108"/>
+      <c r="AF14" s="108"/>
+      <c r="AG14" s="108"/>
+      <c r="AH14" s="108"/>
+      <c r="AI14" s="108"/>
+      <c r="AJ14" s="108"/>
+      <c r="AK14" s="108"/>
+      <c r="AL14" s="108"/>
+      <c r="AM14" s="108"/>
+      <c r="AN14" s="108"/>
+      <c r="AO14" s="108"/>
+      <c r="AP14" s="108"/>
+      <c r="AQ14" s="108"/>
+      <c r="AR14" s="108"/>
+      <c r="AS14" s="108"/>
+      <c r="AT14" s="108"/>
+      <c r="AU14" s="108"/>
+      <c r="AV14" s="108"/>
+      <c r="AW14" s="108"/>
+      <c r="AX14" s="108"/>
+      <c r="AY14" s="108"/>
+      <c r="AZ14" s="109"/>
       <c r="BC14" s="24"/>
     </row>
     <row r="15" spans="1:60" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="99"/>
-      <c r="B15" s="99"/>
-      <c r="C15" s="99"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="99"/>
-      <c r="G15" s="99"/>
-      <c r="H15" s="99"/>
-      <c r="I15" s="99"/>
-      <c r="J15" s="99"/>
-      <c r="K15" s="99"/>
-      <c r="L15" s="99"/>
-      <c r="M15" s="99"/>
-      <c r="N15" s="99"/>
-      <c r="O15" s="99"/>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="99"/>
-      <c r="R15" s="99"/>
-      <c r="S15" s="99"/>
-      <c r="T15" s="99"/>
-      <c r="U15" s="99"/>
-      <c r="V15" s="99"/>
-      <c r="W15" s="99"/>
-      <c r="X15" s="99"/>
-      <c r="Y15" s="99"/>
-      <c r="Z15" s="99"/>
-      <c r="AA15" s="99"/>
-      <c r="AB15" s="99"/>
-      <c r="AC15" s="99"/>
-      <c r="AD15" s="99"/>
-      <c r="AE15" s="99"/>
-      <c r="AF15" s="99"/>
-      <c r="AG15" s="99"/>
-      <c r="AH15" s="99"/>
-      <c r="AI15" s="99"/>
-      <c r="AJ15" s="99"/>
-      <c r="AK15" s="99"/>
-      <c r="AL15" s="99"/>
-      <c r="AM15" s="99"/>
-      <c r="AN15" s="99"/>
-      <c r="AO15" s="99"/>
-      <c r="AP15" s="99"/>
-      <c r="AQ15" s="99"/>
-      <c r="AR15" s="99"/>
-      <c r="AS15" s="99"/>
-      <c r="AT15" s="99"/>
-      <c r="AU15" s="99"/>
-      <c r="AV15" s="99"/>
-      <c r="AW15" s="99"/>
-      <c r="AX15" s="99"/>
-      <c r="AY15" s="99"/>
-      <c r="AZ15" s="99"/>
+      <c r="A15" s="148"/>
+      <c r="B15" s="148"/>
+      <c r="C15" s="148"/>
+      <c r="D15" s="148"/>
+      <c r="E15" s="148"/>
+      <c r="F15" s="148"/>
+      <c r="G15" s="148"/>
+      <c r="H15" s="148"/>
+      <c r="I15" s="148"/>
+      <c r="J15" s="148"/>
+      <c r="K15" s="148"/>
+      <c r="L15" s="148"/>
+      <c r="M15" s="148"/>
+      <c r="N15" s="148"/>
+      <c r="O15" s="148"/>
+      <c r="P15" s="148"/>
+      <c r="Q15" s="148"/>
+      <c r="R15" s="148"/>
+      <c r="S15" s="148"/>
+      <c r="T15" s="148"/>
+      <c r="U15" s="148"/>
+      <c r="V15" s="148"/>
+      <c r="W15" s="148"/>
+      <c r="X15" s="148"/>
+      <c r="Y15" s="148"/>
+      <c r="Z15" s="148"/>
+      <c r="AA15" s="148"/>
+      <c r="AB15" s="148"/>
+      <c r="AC15" s="148"/>
+      <c r="AD15" s="148"/>
+      <c r="AE15" s="148"/>
+      <c r="AF15" s="148"/>
+      <c r="AG15" s="148"/>
+      <c r="AH15" s="148"/>
+      <c r="AI15" s="148"/>
+      <c r="AJ15" s="148"/>
+      <c r="AK15" s="148"/>
+      <c r="AL15" s="148"/>
+      <c r="AM15" s="148"/>
+      <c r="AN15" s="148"/>
+      <c r="AO15" s="148"/>
+      <c r="AP15" s="148"/>
+      <c r="AQ15" s="148"/>
+      <c r="AR15" s="148"/>
+      <c r="AS15" s="148"/>
+      <c r="AT15" s="148"/>
+      <c r="AU15" s="148"/>
+      <c r="AV15" s="148"/>
+      <c r="AW15" s="148"/>
+      <c r="AX15" s="148"/>
+      <c r="AY15" s="148"/>
+      <c r="AZ15" s="148"/>
     </row>
     <row r="16" spans="1:60" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="236" t="s">
+      <c r="A16" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="237"/>
-      <c r="C16" s="237"/>
-      <c r="D16" s="237"/>
-      <c r="E16" s="237"/>
-      <c r="F16" s="237"/>
-      <c r="G16" s="237"/>
-      <c r="H16" s="237"/>
-      <c r="I16" s="237"/>
-      <c r="J16" s="237"/>
-      <c r="K16" s="237"/>
-      <c r="L16" s="237"/>
-      <c r="M16" s="237"/>
-      <c r="N16" s="237"/>
-      <c r="O16" s="237"/>
-      <c r="P16" s="237"/>
-      <c r="Q16" s="237"/>
-      <c r="R16" s="237"/>
-      <c r="S16" s="237"/>
-      <c r="T16" s="237"/>
-      <c r="U16" s="237"/>
-      <c r="V16" s="237"/>
-      <c r="W16" s="237"/>
-      <c r="X16" s="237"/>
-      <c r="Y16" s="237"/>
-      <c r="Z16" s="237"/>
-      <c r="AA16" s="237"/>
-      <c r="AB16" s="237"/>
-      <c r="AC16" s="237"/>
-      <c r="AD16" s="237"/>
-      <c r="AE16" s="237"/>
-      <c r="AF16" s="237"/>
-      <c r="AG16" s="237"/>
-      <c r="AH16" s="237"/>
-      <c r="AI16" s="237"/>
-      <c r="AJ16" s="237"/>
-      <c r="AK16" s="237"/>
-      <c r="AL16" s="237"/>
-      <c r="AM16" s="237"/>
-      <c r="AN16" s="237"/>
-      <c r="AO16" s="237"/>
-      <c r="AP16" s="237"/>
-      <c r="AQ16" s="237"/>
-      <c r="AR16" s="237"/>
-      <c r="AS16" s="237"/>
-      <c r="AT16" s="237"/>
-      <c r="AU16" s="237"/>
-      <c r="AV16" s="237"/>
-      <c r="AW16" s="237"/>
-      <c r="AX16" s="237"/>
-      <c r="AY16" s="237"/>
-      <c r="AZ16" s="238"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="111"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="111"/>
+      <c r="S16" s="111"/>
+      <c r="T16" s="111"/>
+      <c r="U16" s="111"/>
+      <c r="V16" s="111"/>
+      <c r="W16" s="111"/>
+      <c r="X16" s="111"/>
+      <c r="Y16" s="111"/>
+      <c r="Z16" s="111"/>
+      <c r="AA16" s="111"/>
+      <c r="AB16" s="111"/>
+      <c r="AC16" s="111"/>
+      <c r="AD16" s="111"/>
+      <c r="AE16" s="111"/>
+      <c r="AF16" s="111"/>
+      <c r="AG16" s="111"/>
+      <c r="AH16" s="111"/>
+      <c r="AI16" s="111"/>
+      <c r="AJ16" s="111"/>
+      <c r="AK16" s="111"/>
+      <c r="AL16" s="111"/>
+      <c r="AM16" s="111"/>
+      <c r="AN16" s="111"/>
+      <c r="AO16" s="111"/>
+      <c r="AP16" s="111"/>
+      <c r="AQ16" s="111"/>
+      <c r="AR16" s="111"/>
+      <c r="AS16" s="111"/>
+      <c r="AT16" s="111"/>
+      <c r="AU16" s="111"/>
+      <c r="AV16" s="111"/>
+      <c r="AW16" s="111"/>
+      <c r="AX16" s="111"/>
+      <c r="AY16" s="111"/>
+      <c r="AZ16" s="112"/>
     </row>
     <row r="17" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="168" t="s">
+      <c r="A17" s="201" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="169"/>
-      <c r="C17" s="169"/>
-      <c r="D17" s="169"/>
-      <c r="E17" s="169"/>
-      <c r="F17" s="169"/>
-      <c r="G17" s="169"/>
-      <c r="H17" s="169"/>
-      <c r="I17" s="169"/>
-      <c r="J17" s="169"/>
-      <c r="K17" s="169"/>
-      <c r="L17" s="169"/>
-      <c r="M17" s="166" t="s">
+      <c r="B17" s="202"/>
+      <c r="C17" s="202"/>
+      <c r="D17" s="202"/>
+      <c r="E17" s="202"/>
+      <c r="F17" s="202"/>
+      <c r="G17" s="202"/>
+      <c r="H17" s="202"/>
+      <c r="I17" s="202"/>
+      <c r="J17" s="202"/>
+      <c r="K17" s="202"/>
+      <c r="L17" s="202"/>
+      <c r="M17" s="199" t="s">
         <v>32</v>
       </c>
-      <c r="N17" s="167"/>
-      <c r="O17" s="167"/>
-      <c r="P17" s="167"/>
-      <c r="Q17" s="167"/>
-      <c r="R17" s="163" t="s">
+      <c r="N17" s="200"/>
+      <c r="O17" s="200"/>
+      <c r="P17" s="200"/>
+      <c r="Q17" s="200"/>
+      <c r="R17" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="S17" s="164"/>
-      <c r="T17" s="164"/>
-      <c r="U17" s="164"/>
-      <c r="V17" s="165"/>
-      <c r="W17" s="163" t="s">
+      <c r="S17" s="117"/>
+      <c r="T17" s="117"/>
+      <c r="U17" s="117"/>
+      <c r="V17" s="118"/>
+      <c r="W17" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="X17" s="164"/>
-      <c r="Y17" s="164"/>
-      <c r="Z17" s="164"/>
-      <c r="AA17" s="165"/>
-      <c r="AB17" s="163" t="s">
+      <c r="X17" s="117"/>
+      <c r="Y17" s="117"/>
+      <c r="Z17" s="117"/>
+      <c r="AA17" s="118"/>
+      <c r="AB17" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="AC17" s="164"/>
-      <c r="AD17" s="164"/>
-      <c r="AE17" s="164"/>
-      <c r="AF17" s="165"/>
-      <c r="AG17" s="163" t="s">
+      <c r="AC17" s="117"/>
+      <c r="AD17" s="117"/>
+      <c r="AE17" s="117"/>
+      <c r="AF17" s="118"/>
+      <c r="AG17" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="AH17" s="164"/>
-      <c r="AI17" s="164"/>
-      <c r="AJ17" s="164"/>
-      <c r="AK17" s="165"/>
-      <c r="AL17" s="163" t="s">
+      <c r="AH17" s="117"/>
+      <c r="AI17" s="117"/>
+      <c r="AJ17" s="117"/>
+      <c r="AK17" s="118"/>
+      <c r="AL17" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="AM17" s="164"/>
-      <c r="AN17" s="164"/>
-      <c r="AO17" s="164"/>
-      <c r="AP17" s="165"/>
-      <c r="AQ17" s="163" t="s">
+      <c r="AM17" s="117"/>
+      <c r="AN17" s="117"/>
+      <c r="AO17" s="117"/>
+      <c r="AP17" s="118"/>
+      <c r="AQ17" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="AR17" s="164"/>
-      <c r="AS17" s="164"/>
-      <c r="AT17" s="164"/>
-      <c r="AU17" s="165"/>
-      <c r="AV17" s="239" t="s">
+      <c r="AR17" s="117"/>
+      <c r="AS17" s="117"/>
+      <c r="AT17" s="117"/>
+      <c r="AU17" s="118"/>
+      <c r="AV17" s="113" t="s">
         <v>32</v>
       </c>
-      <c r="AW17" s="240"/>
-      <c r="AX17" s="240"/>
-      <c r="AY17" s="240"/>
-      <c r="AZ17" s="241"/>
+      <c r="AW17" s="114"/>
+      <c r="AX17" s="114"/>
+      <c r="AY17" s="114"/>
+      <c r="AZ17" s="115"/>
     </row>
     <row r="18" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="92" t="s">
+      <c r="A18" s="230" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="93"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="93"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="93"/>
-      <c r="J18" s="93"/>
-      <c r="K18" s="93"/>
-      <c r="L18" s="94"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="90"/>
-      <c r="O18" s="90"/>
-      <c r="P18" s="90"/>
-      <c r="Q18" s="90"/>
-      <c r="R18" s="89"/>
-      <c r="S18" s="90"/>
-      <c r="T18" s="90"/>
-      <c r="U18" s="90"/>
-      <c r="V18" s="90"/>
-      <c r="W18" s="89"/>
-      <c r="X18" s="90"/>
-      <c r="Y18" s="90"/>
-      <c r="Z18" s="90"/>
-      <c r="AA18" s="90"/>
-      <c r="AB18" s="89"/>
-      <c r="AC18" s="90"/>
-      <c r="AD18" s="90"/>
-      <c r="AE18" s="90"/>
-      <c r="AF18" s="90"/>
-      <c r="AG18" s="89"/>
-      <c r="AH18" s="90"/>
-      <c r="AI18" s="90"/>
-      <c r="AJ18" s="90"/>
-      <c r="AK18" s="90"/>
-      <c r="AL18" s="89"/>
-      <c r="AM18" s="90"/>
-      <c r="AN18" s="90"/>
-      <c r="AO18" s="90"/>
-      <c r="AP18" s="90"/>
-      <c r="AQ18" s="89"/>
-      <c r="AR18" s="90"/>
-      <c r="AS18" s="90"/>
-      <c r="AT18" s="90"/>
-      <c r="AU18" s="90"/>
-      <c r="AV18" s="242"/>
-      <c r="AW18" s="243"/>
-      <c r="AX18" s="243"/>
-      <c r="AY18" s="243"/>
-      <c r="AZ18" s="244"/>
+      <c r="B18" s="231"/>
+      <c r="C18" s="231"/>
+      <c r="D18" s="231"/>
+      <c r="E18" s="231"/>
+      <c r="F18" s="231"/>
+      <c r="G18" s="231"/>
+      <c r="H18" s="231"/>
+      <c r="I18" s="231"/>
+      <c r="J18" s="231"/>
+      <c r="K18" s="231"/>
+      <c r="L18" s="232"/>
+      <c r="M18" s="229"/>
+      <c r="N18" s="123"/>
+      <c r="O18" s="123"/>
+      <c r="P18" s="123"/>
+      <c r="Q18" s="123"/>
+      <c r="R18" s="122"/>
+      <c r="S18" s="123"/>
+      <c r="T18" s="123"/>
+      <c r="U18" s="123"/>
+      <c r="V18" s="123"/>
+      <c r="W18" s="122"/>
+      <c r="X18" s="123"/>
+      <c r="Y18" s="123"/>
+      <c r="Z18" s="123"/>
+      <c r="AA18" s="123"/>
+      <c r="AB18" s="122"/>
+      <c r="AC18" s="123"/>
+      <c r="AD18" s="123"/>
+      <c r="AE18" s="123"/>
+      <c r="AF18" s="123"/>
+      <c r="AG18" s="122"/>
+      <c r="AH18" s="123"/>
+      <c r="AI18" s="123"/>
+      <c r="AJ18" s="123"/>
+      <c r="AK18" s="123"/>
+      <c r="AL18" s="122"/>
+      <c r="AM18" s="123"/>
+      <c r="AN18" s="123"/>
+      <c r="AO18" s="123"/>
+      <c r="AP18" s="123"/>
+      <c r="AQ18" s="122"/>
+      <c r="AR18" s="123"/>
+      <c r="AS18" s="123"/>
+      <c r="AT18" s="123"/>
+      <c r="AU18" s="123"/>
+      <c r="AV18" s="119"/>
+      <c r="AW18" s="120"/>
+      <c r="AX18" s="120"/>
+      <c r="AY18" s="120"/>
+      <c r="AZ18" s="121"/>
       <c r="BD18" s="26"/>
     </row>
     <row r="19" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="129" t="s">
+      <c r="A19" s="220" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="130"/>
-      <c r="C19" s="130"/>
-      <c r="D19" s="130"/>
-      <c r="E19" s="130"/>
-      <c r="F19" s="130"/>
-      <c r="G19" s="130"/>
-      <c r="H19" s="130"/>
-      <c r="I19" s="130"/>
-      <c r="J19" s="130"/>
-      <c r="K19" s="130"/>
-      <c r="L19" s="131"/>
-      <c r="M19" s="121"/>
-      <c r="N19" s="96"/>
-      <c r="O19" s="96"/>
-      <c r="P19" s="96"/>
-      <c r="Q19" s="96"/>
-      <c r="R19" s="96"/>
-      <c r="S19" s="96"/>
-      <c r="T19" s="96"/>
-      <c r="U19" s="96"/>
-      <c r="V19" s="96"/>
-      <c r="W19" s="96"/>
-      <c r="X19" s="96"/>
-      <c r="Y19" s="96"/>
-      <c r="Z19" s="96"/>
-      <c r="AA19" s="96"/>
-      <c r="AB19" s="95"/>
-      <c r="AC19" s="96"/>
-      <c r="AD19" s="96"/>
-      <c r="AE19" s="96"/>
-      <c r="AF19" s="96"/>
-      <c r="AG19" s="95"/>
-      <c r="AH19" s="96"/>
-      <c r="AI19" s="96"/>
-      <c r="AJ19" s="96"/>
-      <c r="AK19" s="96"/>
-      <c r="AL19" s="95"/>
-      <c r="AM19" s="96"/>
-      <c r="AN19" s="96"/>
-      <c r="AO19" s="96"/>
-      <c r="AP19" s="96"/>
-      <c r="AQ19" s="95"/>
-      <c r="AR19" s="96"/>
-      <c r="AS19" s="96"/>
-      <c r="AT19" s="96"/>
-      <c r="AU19" s="96"/>
-      <c r="AV19" s="95"/>
-      <c r="AW19" s="96"/>
-      <c r="AX19" s="96"/>
-      <c r="AY19" s="96"/>
-      <c r="AZ19" s="97"/>
+      <c r="B19" s="221"/>
+      <c r="C19" s="221"/>
+      <c r="D19" s="221"/>
+      <c r="E19" s="221"/>
+      <c r="F19" s="221"/>
+      <c r="G19" s="221"/>
+      <c r="H19" s="221"/>
+      <c r="I19" s="221"/>
+      <c r="J19" s="221"/>
+      <c r="K19" s="221"/>
+      <c r="L19" s="222"/>
+      <c r="M19" s="215"/>
+      <c r="N19" s="165"/>
+      <c r="O19" s="165"/>
+      <c r="P19" s="165"/>
+      <c r="Q19" s="165"/>
+      <c r="R19" s="165"/>
+      <c r="S19" s="165"/>
+      <c r="T19" s="165"/>
+      <c r="U19" s="165"/>
+      <c r="V19" s="165"/>
+      <c r="W19" s="165"/>
+      <c r="X19" s="165"/>
+      <c r="Y19" s="165"/>
+      <c r="Z19" s="165"/>
+      <c r="AA19" s="165"/>
+      <c r="AB19" s="212"/>
+      <c r="AC19" s="165"/>
+      <c r="AD19" s="165"/>
+      <c r="AE19" s="165"/>
+      <c r="AF19" s="165"/>
+      <c r="AG19" s="212"/>
+      <c r="AH19" s="165"/>
+      <c r="AI19" s="165"/>
+      <c r="AJ19" s="165"/>
+      <c r="AK19" s="165"/>
+      <c r="AL19" s="212"/>
+      <c r="AM19" s="165"/>
+      <c r="AN19" s="165"/>
+      <c r="AO19" s="165"/>
+      <c r="AP19" s="165"/>
+      <c r="AQ19" s="212"/>
+      <c r="AR19" s="165"/>
+      <c r="AS19" s="165"/>
+      <c r="AT19" s="165"/>
+      <c r="AU19" s="165"/>
+      <c r="AV19" s="212"/>
+      <c r="AW19" s="165"/>
+      <c r="AX19" s="165"/>
+      <c r="AY19" s="165"/>
+      <c r="AZ19" s="233"/>
       <c r="BC19" s="29"/>
       <c r="BD19" s="49"/>
       <c r="BE19" s="30"/>
@@ -6239,60 +6253,60 @@
       <c r="BJ19" s="49"/>
     </row>
     <row r="20" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="132" t="s">
+      <c r="A20" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="133"/>
-      <c r="C20" s="133"/>
-      <c r="D20" s="133"/>
-      <c r="E20" s="133"/>
-      <c r="F20" s="133"/>
-      <c r="G20" s="133"/>
-      <c r="H20" s="133"/>
-      <c r="I20" s="133"/>
-      <c r="J20" s="133"/>
-      <c r="K20" s="133"/>
-      <c r="L20" s="134"/>
-      <c r="M20" s="122"/>
-      <c r="N20" s="123"/>
-      <c r="O20" s="123"/>
-      <c r="P20" s="123"/>
-      <c r="Q20" s="123"/>
-      <c r="R20" s="123"/>
-      <c r="S20" s="123"/>
-      <c r="T20" s="123"/>
-      <c r="U20" s="123"/>
-      <c r="V20" s="123"/>
-      <c r="W20" s="123"/>
-      <c r="X20" s="123"/>
-      <c r="Y20" s="123"/>
-      <c r="Z20" s="123"/>
-      <c r="AA20" s="123"/>
-      <c r="AB20" s="123"/>
-      <c r="AC20" s="123"/>
-      <c r="AD20" s="123"/>
-      <c r="AE20" s="123"/>
-      <c r="AF20" s="123"/>
-      <c r="AG20" s="123"/>
-      <c r="AH20" s="123"/>
-      <c r="AI20" s="123"/>
-      <c r="AJ20" s="123"/>
-      <c r="AK20" s="123"/>
-      <c r="AL20" s="123"/>
-      <c r="AM20" s="123"/>
-      <c r="AN20" s="123"/>
-      <c r="AO20" s="123"/>
-      <c r="AP20" s="123"/>
-      <c r="AQ20" s="123"/>
-      <c r="AR20" s="123"/>
-      <c r="AS20" s="123"/>
-      <c r="AT20" s="123"/>
-      <c r="AU20" s="123"/>
-      <c r="AV20" s="123"/>
-      <c r="AW20" s="123"/>
-      <c r="AX20" s="123"/>
-      <c r="AY20" s="123"/>
-      <c r="AZ20" s="192"/>
+      <c r="B20" s="224"/>
+      <c r="C20" s="224"/>
+      <c r="D20" s="224"/>
+      <c r="E20" s="224"/>
+      <c r="F20" s="224"/>
+      <c r="G20" s="224"/>
+      <c r="H20" s="224"/>
+      <c r="I20" s="224"/>
+      <c r="J20" s="224"/>
+      <c r="K20" s="224"/>
+      <c r="L20" s="225"/>
+      <c r="M20" s="216"/>
+      <c r="N20" s="166"/>
+      <c r="O20" s="166"/>
+      <c r="P20" s="166"/>
+      <c r="Q20" s="166"/>
+      <c r="R20" s="166"/>
+      <c r="S20" s="166"/>
+      <c r="T20" s="166"/>
+      <c r="U20" s="166"/>
+      <c r="V20" s="166"/>
+      <c r="W20" s="166"/>
+      <c r="X20" s="166"/>
+      <c r="Y20" s="166"/>
+      <c r="Z20" s="166"/>
+      <c r="AA20" s="166"/>
+      <c r="AB20" s="166"/>
+      <c r="AC20" s="166"/>
+      <c r="AD20" s="166"/>
+      <c r="AE20" s="166"/>
+      <c r="AF20" s="166"/>
+      <c r="AG20" s="166"/>
+      <c r="AH20" s="166"/>
+      <c r="AI20" s="166"/>
+      <c r="AJ20" s="166"/>
+      <c r="AK20" s="166"/>
+      <c r="AL20" s="166"/>
+      <c r="AM20" s="166"/>
+      <c r="AN20" s="166"/>
+      <c r="AO20" s="166"/>
+      <c r="AP20" s="166"/>
+      <c r="AQ20" s="166"/>
+      <c r="AR20" s="166"/>
+      <c r="AS20" s="166"/>
+      <c r="AT20" s="166"/>
+      <c r="AU20" s="166"/>
+      <c r="AV20" s="166"/>
+      <c r="AW20" s="166"/>
+      <c r="AX20" s="166"/>
+      <c r="AY20" s="166"/>
+      <c r="AZ20" s="168"/>
       <c r="BC20" s="29"/>
       <c r="BD20" s="31"/>
       <c r="BE20" s="31"/>
@@ -6303,63 +6317,63 @@
       <c r="BJ20" s="31"/>
     </row>
     <row r="21" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="132" t="s">
+      <c r="A21" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="133"/>
-      <c r="C21" s="133"/>
-      <c r="D21" s="133"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="133"/>
-      <c r="I21" s="133"/>
-      <c r="J21" s="133"/>
-      <c r="K21" s="133"/>
-      <c r="L21" s="134"/>
-      <c r="M21" s="124"/>
-      <c r="N21" s="115"/>
-      <c r="O21" s="115"/>
-      <c r="P21" s="115"/>
-      <c r="Q21" s="115"/>
-      <c r="R21" s="115"/>
-      <c r="S21" s="115"/>
-      <c r="T21" s="115"/>
-      <c r="U21" s="115"/>
-      <c r="V21" s="115"/>
-      <c r="W21" s="115"/>
-      <c r="X21" s="115"/>
-      <c r="Y21" s="115"/>
-      <c r="Z21" s="115"/>
-      <c r="AA21" s="115"/>
-      <c r="AB21" s="115"/>
-      <c r="AC21" s="115"/>
-      <c r="AD21" s="115"/>
-      <c r="AE21" s="115"/>
-      <c r="AF21" s="115"/>
-      <c r="AG21" s="115"/>
-      <c r="AH21" s="115"/>
-      <c r="AI21" s="115"/>
-      <c r="AJ21" s="115"/>
-      <c r="AK21" s="115"/>
-      <c r="AL21" s="115"/>
-      <c r="AM21" s="115"/>
-      <c r="AN21" s="115"/>
-      <c r="AO21" s="115"/>
-      <c r="AP21" s="115"/>
-      <c r="AQ21" s="115"/>
-      <c r="AR21" s="115"/>
-      <c r="AS21" s="115"/>
-      <c r="AT21" s="115"/>
-      <c r="AU21" s="115"/>
-      <c r="AV21" s="115"/>
-      <c r="AW21" s="115"/>
-      <c r="AX21" s="115"/>
-      <c r="AY21" s="115"/>
-      <c r="AZ21" s="116"/>
+      <c r="B21" s="224"/>
+      <c r="C21" s="224"/>
+      <c r="D21" s="224"/>
+      <c r="E21" s="224"/>
+      <c r="F21" s="224"/>
+      <c r="G21" s="224"/>
+      <c r="H21" s="224"/>
+      <c r="I21" s="224"/>
+      <c r="J21" s="224"/>
+      <c r="K21" s="224"/>
+      <c r="L21" s="225"/>
+      <c r="M21" s="217"/>
+      <c r="N21" s="167"/>
+      <c r="O21" s="167"/>
+      <c r="P21" s="167"/>
+      <c r="Q21" s="167"/>
+      <c r="R21" s="167"/>
+      <c r="S21" s="167"/>
+      <c r="T21" s="167"/>
+      <c r="U21" s="167"/>
+      <c r="V21" s="167"/>
+      <c r="W21" s="167"/>
+      <c r="X21" s="167"/>
+      <c r="Y21" s="167"/>
+      <c r="Z21" s="167"/>
+      <c r="AA21" s="167"/>
+      <c r="AB21" s="167"/>
+      <c r="AC21" s="167"/>
+      <c r="AD21" s="167"/>
+      <c r="AE21" s="167"/>
+      <c r="AF21" s="167"/>
+      <c r="AG21" s="167"/>
+      <c r="AH21" s="167"/>
+      <c r="AI21" s="167"/>
+      <c r="AJ21" s="167"/>
+      <c r="AK21" s="167"/>
+      <c r="AL21" s="167"/>
+      <c r="AM21" s="167"/>
+      <c r="AN21" s="167"/>
+      <c r="AO21" s="167"/>
+      <c r="AP21" s="167"/>
+      <c r="AQ21" s="167"/>
+      <c r="AR21" s="167"/>
+      <c r="AS21" s="167"/>
+      <c r="AT21" s="167"/>
+      <c r="AU21" s="167"/>
+      <c r="AV21" s="167"/>
+      <c r="AW21" s="167"/>
+      <c r="AX21" s="167"/>
+      <c r="AY21" s="167"/>
+      <c r="AZ21" s="169"/>
       <c r="BC21" s="29"/>
-      <c r="BD21" s="229"/>
-      <c r="BE21" s="229"/>
+      <c r="BD21" s="90"/>
+      <c r="BE21" s="90"/>
       <c r="BF21" s="29"/>
       <c r="BG21" s="29"/>
       <c r="BH21" s="29"/>
@@ -6367,84 +6381,84 @@
       <c r="BJ21" s="29"/>
     </row>
     <row r="22" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="132" t="s">
+      <c r="A22" s="223" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="133"/>
-      <c r="C22" s="133"/>
-      <c r="D22" s="133"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="133"/>
-      <c r="H22" s="133"/>
-      <c r="I22" s="133"/>
-      <c r="J22" s="133"/>
-      <c r="K22" s="133"/>
-      <c r="L22" s="134"/>
-      <c r="M22" s="124" t="str">
+      <c r="B22" s="224"/>
+      <c r="C22" s="224"/>
+      <c r="D22" s="224"/>
+      <c r="E22" s="224"/>
+      <c r="F22" s="224"/>
+      <c r="G22" s="224"/>
+      <c r="H22" s="224"/>
+      <c r="I22" s="224"/>
+      <c r="J22" s="224"/>
+      <c r="K22" s="224"/>
+      <c r="L22" s="225"/>
+      <c r="M22" s="217" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="N22" s="115"/>
-      <c r="O22" s="115"/>
-      <c r="P22" s="115"/>
-      <c r="Q22" s="115"/>
-      <c r="R22" s="115" t="str">
+      <c r="N22" s="167"/>
+      <c r="O22" s="167"/>
+      <c r="P22" s="167"/>
+      <c r="Q22" s="167"/>
+      <c r="R22" s="167" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="S22" s="115"/>
-      <c r="T22" s="115"/>
-      <c r="U22" s="115"/>
-      <c r="V22" s="115"/>
-      <c r="W22" s="115" t="str">
+      <c r="S22" s="167"/>
+      <c r="T22" s="167"/>
+      <c r="U22" s="167"/>
+      <c r="V22" s="167"/>
+      <c r="W22" s="167" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="X22" s="115"/>
-      <c r="Y22" s="115"/>
-      <c r="Z22" s="115"/>
-      <c r="AA22" s="115"/>
-      <c r="AB22" s="115" t="str">
+      <c r="X22" s="167"/>
+      <c r="Y22" s="167"/>
+      <c r="Z22" s="167"/>
+      <c r="AA22" s="167"/>
+      <c r="AB22" s="167" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AC22" s="115"/>
-      <c r="AD22" s="115"/>
-      <c r="AE22" s="115"/>
-      <c r="AF22" s="115"/>
-      <c r="AG22" s="115" t="str">
+      <c r="AC22" s="167"/>
+      <c r="AD22" s="167"/>
+      <c r="AE22" s="167"/>
+      <c r="AF22" s="167"/>
+      <c r="AG22" s="167" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AH22" s="115"/>
-      <c r="AI22" s="115"/>
-      <c r="AJ22" s="115"/>
-      <c r="AK22" s="115"/>
-      <c r="AL22" s="115" t="str">
+      <c r="AH22" s="167"/>
+      <c r="AI22" s="167"/>
+      <c r="AJ22" s="167"/>
+      <c r="AK22" s="167"/>
+      <c r="AL22" s="167" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AM22" s="115"/>
-      <c r="AN22" s="115"/>
-      <c r="AO22" s="115"/>
-      <c r="AP22" s="115"/>
-      <c r="AQ22" s="115" t="str">
+      <c r="AM22" s="167"/>
+      <c r="AN22" s="167"/>
+      <c r="AO22" s="167"/>
+      <c r="AP22" s="167"/>
+      <c r="AQ22" s="167" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AR22" s="115"/>
-      <c r="AS22" s="115"/>
-      <c r="AT22" s="115"/>
-      <c r="AU22" s="115"/>
-      <c r="AV22" s="115" t="str">
+      <c r="AR22" s="167"/>
+      <c r="AS22" s="167"/>
+      <c r="AT22" s="167"/>
+      <c r="AU22" s="167"/>
+      <c r="AV22" s="167" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AW22" s="115"/>
-      <c r="AX22" s="115"/>
-      <c r="AY22" s="115"/>
-      <c r="AZ22" s="116"/>
+      <c r="AW22" s="167"/>
+      <c r="AX22" s="167"/>
+      <c r="AY22" s="167"/>
+      <c r="AZ22" s="169"/>
       <c r="BC22" s="29"/>
       <c r="BD22" s="31"/>
       <c r="BE22" s="31"/>
@@ -6455,87 +6469,87 @@
       <c r="BJ22" s="29"/>
     </row>
     <row r="23" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="132" t="s">
+      <c r="A23" s="223" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="133"/>
-      <c r="C23" s="133"/>
-      <c r="D23" s="133"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="133"/>
-      <c r="I23" s="133"/>
-      <c r="J23" s="133"/>
-      <c r="K23" s="133"/>
-      <c r="L23" s="134"/>
-      <c r="M23" s="124" t="str">
+      <c r="B23" s="224"/>
+      <c r="C23" s="224"/>
+      <c r="D23" s="224"/>
+      <c r="E23" s="224"/>
+      <c r="F23" s="224"/>
+      <c r="G23" s="224"/>
+      <c r="H23" s="224"/>
+      <c r="I23" s="224"/>
+      <c r="J23" s="224"/>
+      <c r="K23" s="224"/>
+      <c r="L23" s="225"/>
+      <c r="M23" s="217" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="N23" s="115"/>
-      <c r="O23" s="115"/>
-      <c r="P23" s="115"/>
-      <c r="Q23" s="115"/>
-      <c r="R23" s="115" t="str">
+      <c r="N23" s="167"/>
+      <c r="O23" s="167"/>
+      <c r="P23" s="167"/>
+      <c r="Q23" s="167"/>
+      <c r="R23" s="167" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="S23" s="115"/>
-      <c r="T23" s="115"/>
-      <c r="U23" s="115"/>
-      <c r="V23" s="115"/>
-      <c r="W23" s="115" t="str">
+      <c r="S23" s="167"/>
+      <c r="T23" s="167"/>
+      <c r="U23" s="167"/>
+      <c r="V23" s="167"/>
+      <c r="W23" s="167" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="X23" s="115"/>
-      <c r="Y23" s="115"/>
-      <c r="Z23" s="115"/>
-      <c r="AA23" s="115"/>
-      <c r="AB23" s="115" t="str">
+      <c r="X23" s="167"/>
+      <c r="Y23" s="167"/>
+      <c r="Z23" s="167"/>
+      <c r="AA23" s="167"/>
+      <c r="AB23" s="167" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AC23" s="115"/>
-      <c r="AD23" s="115"/>
-      <c r="AE23" s="115"/>
-      <c r="AF23" s="115"/>
-      <c r="AG23" s="115" t="str">
+      <c r="AC23" s="167"/>
+      <c r="AD23" s="167"/>
+      <c r="AE23" s="167"/>
+      <c r="AF23" s="167"/>
+      <c r="AG23" s="167" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AH23" s="115"/>
-      <c r="AI23" s="115"/>
-      <c r="AJ23" s="115"/>
-      <c r="AK23" s="115"/>
-      <c r="AL23" s="115" t="str">
+      <c r="AH23" s="167"/>
+      <c r="AI23" s="167"/>
+      <c r="AJ23" s="167"/>
+      <c r="AK23" s="167"/>
+      <c r="AL23" s="167" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AM23" s="115"/>
-      <c r="AN23" s="115"/>
-      <c r="AO23" s="115"/>
-      <c r="AP23" s="115"/>
-      <c r="AQ23" s="115" t="str">
+      <c r="AM23" s="167"/>
+      <c r="AN23" s="167"/>
+      <c r="AO23" s="167"/>
+      <c r="AP23" s="167"/>
+      <c r="AQ23" s="167" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AR23" s="115"/>
-      <c r="AS23" s="115"/>
-      <c r="AT23" s="115"/>
-      <c r="AU23" s="115"/>
-      <c r="AV23" s="115" t="str">
+      <c r="AR23" s="167"/>
+      <c r="AS23" s="167"/>
+      <c r="AT23" s="167"/>
+      <c r="AU23" s="167"/>
+      <c r="AV23" s="167" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AW23" s="115"/>
-      <c r="AX23" s="115"/>
-      <c r="AY23" s="115"/>
-      <c r="AZ23" s="116"/>
+      <c r="AW23" s="167"/>
+      <c r="AX23" s="167"/>
+      <c r="AY23" s="167"/>
+      <c r="AZ23" s="169"/>
       <c r="BC23" s="32"/>
-      <c r="BD23" s="229"/>
-      <c r="BE23" s="229"/>
+      <c r="BD23" s="90"/>
+      <c r="BE23" s="90"/>
       <c r="BF23" s="32"/>
       <c r="BG23" s="32"/>
       <c r="BH23" s="32"/>
@@ -6543,84 +6557,84 @@
       <c r="BJ23" s="32"/>
     </row>
     <row r="24" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="132" t="s">
+      <c r="A24" s="223" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="133"/>
-      <c r="C24" s="133"/>
-      <c r="D24" s="133"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="133"/>
-      <c r="I24" s="133"/>
-      <c r="J24" s="133"/>
-      <c r="K24" s="133"/>
-      <c r="L24" s="134"/>
-      <c r="M24" s="125" t="str">
+      <c r="B24" s="224"/>
+      <c r="C24" s="224"/>
+      <c r="D24" s="224"/>
+      <c r="E24" s="224"/>
+      <c r="F24" s="224"/>
+      <c r="G24" s="224"/>
+      <c r="H24" s="224"/>
+      <c r="I24" s="224"/>
+      <c r="J24" s="224"/>
+      <c r="K24" s="224"/>
+      <c r="L24" s="225"/>
+      <c r="M24" s="218" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="N24" s="126"/>
-      <c r="O24" s="126"/>
-      <c r="P24" s="126"/>
-      <c r="Q24" s="126"/>
-      <c r="R24" s="126" t="str">
+      <c r="N24" s="160"/>
+      <c r="O24" s="160"/>
+      <c r="P24" s="160"/>
+      <c r="Q24" s="160"/>
+      <c r="R24" s="160" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="S24" s="126"/>
-      <c r="T24" s="126"/>
-      <c r="U24" s="126"/>
-      <c r="V24" s="126"/>
-      <c r="W24" s="126" t="str">
+      <c r="S24" s="160"/>
+      <c r="T24" s="160"/>
+      <c r="U24" s="160"/>
+      <c r="V24" s="160"/>
+      <c r="W24" s="160" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="X24" s="126"/>
-      <c r="Y24" s="126"/>
-      <c r="Z24" s="126"/>
-      <c r="AA24" s="126"/>
-      <c r="AB24" s="126" t="str">
+      <c r="X24" s="160"/>
+      <c r="Y24" s="160"/>
+      <c r="Z24" s="160"/>
+      <c r="AA24" s="160"/>
+      <c r="AB24" s="160" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AC24" s="126"/>
-      <c r="AD24" s="126"/>
-      <c r="AE24" s="126"/>
-      <c r="AF24" s="126"/>
-      <c r="AG24" s="126" t="str">
+      <c r="AC24" s="160"/>
+      <c r="AD24" s="160"/>
+      <c r="AE24" s="160"/>
+      <c r="AF24" s="160"/>
+      <c r="AG24" s="160" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AH24" s="126"/>
-      <c r="AI24" s="126"/>
-      <c r="AJ24" s="126"/>
-      <c r="AK24" s="126"/>
-      <c r="AL24" s="126" t="str">
+      <c r="AH24" s="160"/>
+      <c r="AI24" s="160"/>
+      <c r="AJ24" s="160"/>
+      <c r="AK24" s="160"/>
+      <c r="AL24" s="160" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AM24" s="126"/>
-      <c r="AN24" s="126"/>
-      <c r="AO24" s="126"/>
-      <c r="AP24" s="126"/>
-      <c r="AQ24" s="126" t="str">
+      <c r="AM24" s="160"/>
+      <c r="AN24" s="160"/>
+      <c r="AO24" s="160"/>
+      <c r="AP24" s="160"/>
+      <c r="AQ24" s="160" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AR24" s="126"/>
-      <c r="AS24" s="126"/>
-      <c r="AT24" s="126"/>
-      <c r="AU24" s="126"/>
-      <c r="AV24" s="126" t="str">
+      <c r="AR24" s="160"/>
+      <c r="AS24" s="160"/>
+      <c r="AT24" s="160"/>
+      <c r="AU24" s="160"/>
+      <c r="AV24" s="160" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AW24" s="126"/>
-      <c r="AX24" s="126"/>
-      <c r="AY24" s="126"/>
-      <c r="AZ24" s="193"/>
+      <c r="AW24" s="160"/>
+      <c r="AX24" s="160"/>
+      <c r="AY24" s="160"/>
+      <c r="AZ24" s="161"/>
       <c r="BC24" s="29"/>
       <c r="BD24" s="31"/>
       <c r="BE24" s="31"/>
@@ -6631,87 +6645,87 @@
       <c r="BJ24" s="29"/>
     </row>
     <row r="25" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="111" t="s">
+      <c r="A25" s="226" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="112"/>
-      <c r="C25" s="112"/>
-      <c r="D25" s="112"/>
-      <c r="E25" s="112"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="112"/>
-      <c r="H25" s="112"/>
-      <c r="I25" s="112"/>
-      <c r="J25" s="112"/>
-      <c r="K25" s="112"/>
-      <c r="L25" s="135"/>
-      <c r="M25" s="127" t="str">
+      <c r="B25" s="227"/>
+      <c r="C25" s="227"/>
+      <c r="D25" s="227"/>
+      <c r="E25" s="227"/>
+      <c r="F25" s="227"/>
+      <c r="G25" s="227"/>
+      <c r="H25" s="227"/>
+      <c r="I25" s="227"/>
+      <c r="J25" s="227"/>
+      <c r="K25" s="227"/>
+      <c r="L25" s="228"/>
+      <c r="M25" s="219" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="N25" s="128"/>
-      <c r="O25" s="128"/>
-      <c r="P25" s="128"/>
-      <c r="Q25" s="128"/>
-      <c r="R25" s="128" t="str">
+      <c r="N25" s="159"/>
+      <c r="O25" s="159"/>
+      <c r="P25" s="159"/>
+      <c r="Q25" s="159"/>
+      <c r="R25" s="159" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="S25" s="128"/>
-      <c r="T25" s="128"/>
-      <c r="U25" s="128"/>
-      <c r="V25" s="128"/>
-      <c r="W25" s="128" t="str">
+      <c r="S25" s="159"/>
+      <c r="T25" s="159"/>
+      <c r="U25" s="159"/>
+      <c r="V25" s="159"/>
+      <c r="W25" s="159" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="X25" s="128"/>
-      <c r="Y25" s="128"/>
-      <c r="Z25" s="128"/>
-      <c r="AA25" s="128"/>
-      <c r="AB25" s="128" t="str">
+      <c r="X25" s="159"/>
+      <c r="Y25" s="159"/>
+      <c r="Z25" s="159"/>
+      <c r="AA25" s="159"/>
+      <c r="AB25" s="159" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AC25" s="128"/>
-      <c r="AD25" s="128"/>
-      <c r="AE25" s="128"/>
-      <c r="AF25" s="128"/>
-      <c r="AG25" s="128" t="str">
+      <c r="AC25" s="159"/>
+      <c r="AD25" s="159"/>
+      <c r="AE25" s="159"/>
+      <c r="AF25" s="159"/>
+      <c r="AG25" s="159" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AH25" s="128"/>
-      <c r="AI25" s="128"/>
-      <c r="AJ25" s="128"/>
-      <c r="AK25" s="128"/>
-      <c r="AL25" s="128" t="str">
+      <c r="AH25" s="159"/>
+      <c r="AI25" s="159"/>
+      <c r="AJ25" s="159"/>
+      <c r="AK25" s="159"/>
+      <c r="AL25" s="159" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AM25" s="128"/>
-      <c r="AN25" s="128"/>
-      <c r="AO25" s="128"/>
-      <c r="AP25" s="128"/>
-      <c r="AQ25" s="128" t="str">
+      <c r="AM25" s="159"/>
+      <c r="AN25" s="159"/>
+      <c r="AO25" s="159"/>
+      <c r="AP25" s="159"/>
+      <c r="AQ25" s="159" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AR25" s="128"/>
-      <c r="AS25" s="128"/>
-      <c r="AT25" s="128"/>
-      <c r="AU25" s="128"/>
-      <c r="AV25" s="128" t="str">
+      <c r="AR25" s="159"/>
+      <c r="AS25" s="159"/>
+      <c r="AT25" s="159"/>
+      <c r="AU25" s="159"/>
+      <c r="AV25" s="159" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AW25" s="128"/>
-      <c r="AX25" s="128"/>
-      <c r="AY25" s="128"/>
-      <c r="AZ25" s="194"/>
+      <c r="AW25" s="159"/>
+      <c r="AX25" s="159"/>
+      <c r="AY25" s="159"/>
+      <c r="AZ25" s="162"/>
       <c r="BC25" s="29"/>
-      <c r="BD25" s="229"/>
-      <c r="BE25" s="229"/>
+      <c r="BD25" s="90"/>
+      <c r="BE25" s="90"/>
       <c r="BF25" s="29"/>
       <c r="BG25" s="29"/>
       <c r="BH25" s="29"/>
@@ -6719,1150 +6733,1150 @@
       <c r="BJ25" s="29"/>
     </row>
     <row r="26" spans="1:62" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="99"/>
-      <c r="B26" s="99"/>
-      <c r="C26" s="99"/>
-      <c r="D26" s="99"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="99"/>
-      <c r="G26" s="99"/>
-      <c r="H26" s="99"/>
-      <c r="I26" s="99"/>
-      <c r="J26" s="99"/>
-      <c r="K26" s="99"/>
-      <c r="L26" s="99"/>
-      <c r="M26" s="99"/>
-      <c r="N26" s="99"/>
-      <c r="O26" s="99"/>
-      <c r="P26" s="99"/>
-      <c r="Q26" s="99"/>
-      <c r="R26" s="99"/>
-      <c r="S26" s="99"/>
-      <c r="T26" s="99"/>
-      <c r="U26" s="99"/>
-      <c r="V26" s="99"/>
-      <c r="W26" s="99"/>
-      <c r="X26" s="99"/>
-      <c r="Y26" s="99"/>
-      <c r="Z26" s="99"/>
-      <c r="AA26" s="99"/>
-      <c r="AB26" s="99"/>
-      <c r="AC26" s="99"/>
-      <c r="AD26" s="99"/>
-      <c r="AE26" s="99"/>
-      <c r="AF26" s="99"/>
-      <c r="AG26" s="99"/>
-      <c r="AH26" s="99"/>
-      <c r="AI26" s="99"/>
-      <c r="AJ26" s="99"/>
-      <c r="AK26" s="99"/>
-      <c r="AL26" s="99"/>
-      <c r="AM26" s="99"/>
-      <c r="AN26" s="99"/>
-      <c r="AO26" s="99"/>
-      <c r="AP26" s="99"/>
-      <c r="AQ26" s="99"/>
-      <c r="AR26" s="99"/>
-      <c r="AS26" s="99"/>
-      <c r="AT26" s="99"/>
-      <c r="AU26" s="99"/>
-      <c r="AV26" s="99"/>
-      <c r="AW26" s="99"/>
-      <c r="AX26" s="99"/>
-      <c r="AY26" s="99"/>
-      <c r="AZ26" s="99"/>
+      <c r="A26" s="148"/>
+      <c r="B26" s="148"/>
+      <c r="C26" s="148"/>
+      <c r="D26" s="148"/>
+      <c r="E26" s="148"/>
+      <c r="F26" s="148"/>
+      <c r="G26" s="148"/>
+      <c r="H26" s="148"/>
+      <c r="I26" s="148"/>
+      <c r="J26" s="148"/>
+      <c r="K26" s="148"/>
+      <c r="L26" s="148"/>
+      <c r="M26" s="148"/>
+      <c r="N26" s="148"/>
+      <c r="O26" s="148"/>
+      <c r="P26" s="148"/>
+      <c r="Q26" s="148"/>
+      <c r="R26" s="148"/>
+      <c r="S26" s="148"/>
+      <c r="T26" s="148"/>
+      <c r="U26" s="148"/>
+      <c r="V26" s="148"/>
+      <c r="W26" s="148"/>
+      <c r="X26" s="148"/>
+      <c r="Y26" s="148"/>
+      <c r="Z26" s="148"/>
+      <c r="AA26" s="148"/>
+      <c r="AB26" s="148"/>
+      <c r="AC26" s="148"/>
+      <c r="AD26" s="148"/>
+      <c r="AE26" s="148"/>
+      <c r="AF26" s="148"/>
+      <c r="AG26" s="148"/>
+      <c r="AH26" s="148"/>
+      <c r="AI26" s="148"/>
+      <c r="AJ26" s="148"/>
+      <c r="AK26" s="148"/>
+      <c r="AL26" s="148"/>
+      <c r="AM26" s="148"/>
+      <c r="AN26" s="148"/>
+      <c r="AO26" s="148"/>
+      <c r="AP26" s="148"/>
+      <c r="AQ26" s="148"/>
+      <c r="AR26" s="148"/>
+      <c r="AS26" s="148"/>
+      <c r="AT26" s="148"/>
+      <c r="AU26" s="148"/>
+      <c r="AV26" s="148"/>
+      <c r="AW26" s="148"/>
+      <c r="AX26" s="148"/>
+      <c r="AY26" s="148"/>
+      <c r="AZ26" s="148"/>
     </row>
     <row r="27" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="100" t="s">
+      <c r="A27" s="191" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="101"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="101"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="101"/>
-      <c r="H27" s="101"/>
-      <c r="I27" s="101"/>
-      <c r="J27" s="101"/>
-      <c r="K27" s="101"/>
-      <c r="L27" s="101"/>
-      <c r="M27" s="101"/>
-      <c r="N27" s="101"/>
-      <c r="O27" s="101"/>
-      <c r="P27" s="101"/>
-      <c r="Q27" s="101"/>
-      <c r="R27" s="101"/>
-      <c r="S27" s="101"/>
-      <c r="T27" s="101"/>
-      <c r="U27" s="101"/>
-      <c r="V27" s="101"/>
-      <c r="W27" s="101"/>
-      <c r="X27" s="101"/>
-      <c r="Y27" s="101"/>
-      <c r="Z27" s="101"/>
-      <c r="AA27" s="101"/>
-      <c r="AB27" s="101"/>
-      <c r="AC27" s="101"/>
-      <c r="AD27" s="101"/>
-      <c r="AE27" s="101"/>
-      <c r="AF27" s="101"/>
-      <c r="AG27" s="101"/>
-      <c r="AH27" s="101"/>
-      <c r="AI27" s="101"/>
-      <c r="AJ27" s="101"/>
-      <c r="AK27" s="101"/>
-      <c r="AL27" s="101"/>
-      <c r="AM27" s="101"/>
-      <c r="AN27" s="101"/>
-      <c r="AO27" s="101"/>
-      <c r="AP27" s="101"/>
-      <c r="AQ27" s="101"/>
-      <c r="AR27" s="101"/>
-      <c r="AS27" s="101"/>
-      <c r="AT27" s="101"/>
-      <c r="AU27" s="101"/>
-      <c r="AV27" s="101"/>
-      <c r="AW27" s="101"/>
-      <c r="AX27" s="101"/>
-      <c r="AY27" s="101"/>
-      <c r="AZ27" s="102"/>
+      <c r="B27" s="192"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="192"/>
+      <c r="F27" s="192"/>
+      <c r="G27" s="192"/>
+      <c r="H27" s="192"/>
+      <c r="I27" s="192"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="192"/>
+      <c r="L27" s="192"/>
+      <c r="M27" s="192"/>
+      <c r="N27" s="192"/>
+      <c r="O27" s="192"/>
+      <c r="P27" s="192"/>
+      <c r="Q27" s="192"/>
+      <c r="R27" s="192"/>
+      <c r="S27" s="192"/>
+      <c r="T27" s="192"/>
+      <c r="U27" s="192"/>
+      <c r="V27" s="192"/>
+      <c r="W27" s="192"/>
+      <c r="X27" s="192"/>
+      <c r="Y27" s="192"/>
+      <c r="Z27" s="192"/>
+      <c r="AA27" s="192"/>
+      <c r="AB27" s="192"/>
+      <c r="AC27" s="192"/>
+      <c r="AD27" s="192"/>
+      <c r="AE27" s="192"/>
+      <c r="AF27" s="192"/>
+      <c r="AG27" s="192"/>
+      <c r="AH27" s="192"/>
+      <c r="AI27" s="192"/>
+      <c r="AJ27" s="192"/>
+      <c r="AK27" s="192"/>
+      <c r="AL27" s="192"/>
+      <c r="AM27" s="192"/>
+      <c r="AN27" s="192"/>
+      <c r="AO27" s="192"/>
+      <c r="AP27" s="192"/>
+      <c r="AQ27" s="192"/>
+      <c r="AR27" s="192"/>
+      <c r="AS27" s="192"/>
+      <c r="AT27" s="192"/>
+      <c r="AU27" s="192"/>
+      <c r="AV27" s="192"/>
+      <c r="AW27" s="192"/>
+      <c r="AX27" s="192"/>
+      <c r="AY27" s="192"/>
+      <c r="AZ27" s="193"/>
     </row>
     <row r="28" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="103" t="s">
+      <c r="A28" s="235" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="104"/>
-      <c r="C28" s="104"/>
-      <c r="D28" s="104"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="104"/>
-      <c r="I28" s="104"/>
-      <c r="J28" s="104"/>
-      <c r="K28" s="104"/>
-      <c r="L28" s="104"/>
-      <c r="M28" s="104"/>
-      <c r="N28" s="104"/>
-      <c r="O28" s="104"/>
-      <c r="P28" s="104"/>
-      <c r="Q28" s="104"/>
-      <c r="R28" s="104"/>
-      <c r="S28" s="104"/>
-      <c r="T28" s="105" t="s">
+      <c r="B28" s="236"/>
+      <c r="C28" s="236"/>
+      <c r="D28" s="236"/>
+      <c r="E28" s="236"/>
+      <c r="F28" s="236"/>
+      <c r="G28" s="236"/>
+      <c r="H28" s="236"/>
+      <c r="I28" s="236"/>
+      <c r="J28" s="236"/>
+      <c r="K28" s="236"/>
+      <c r="L28" s="236"/>
+      <c r="M28" s="236"/>
+      <c r="N28" s="236"/>
+      <c r="O28" s="236"/>
+      <c r="P28" s="236"/>
+      <c r="Q28" s="236"/>
+      <c r="R28" s="236"/>
+      <c r="S28" s="236"/>
+      <c r="T28" s="237" t="s">
         <v>49</v>
       </c>
-      <c r="U28" s="105"/>
-      <c r="V28" s="105"/>
-      <c r="W28" s="105"/>
-      <c r="X28" s="105"/>
-      <c r="Y28" s="105"/>
-      <c r="Z28" s="105"/>
-      <c r="AA28" s="104" t="s">
+      <c r="U28" s="237"/>
+      <c r="V28" s="237"/>
+      <c r="W28" s="237"/>
+      <c r="X28" s="237"/>
+      <c r="Y28" s="237"/>
+      <c r="Z28" s="237"/>
+      <c r="AA28" s="236" t="s">
         <v>48</v>
       </c>
-      <c r="AB28" s="104"/>
-      <c r="AC28" s="104"/>
-      <c r="AD28" s="104"/>
-      <c r="AE28" s="104"/>
-      <c r="AF28" s="104"/>
-      <c r="AG28" s="104"/>
-      <c r="AH28" s="104"/>
-      <c r="AI28" s="104"/>
-      <c r="AJ28" s="104"/>
-      <c r="AK28" s="104"/>
-      <c r="AL28" s="104"/>
-      <c r="AM28" s="104"/>
-      <c r="AN28" s="104"/>
-      <c r="AO28" s="104"/>
-      <c r="AP28" s="104"/>
-      <c r="AQ28" s="104"/>
-      <c r="AR28" s="104"/>
-      <c r="AS28" s="104"/>
-      <c r="AT28" s="105" t="s">
+      <c r="AB28" s="236"/>
+      <c r="AC28" s="236"/>
+      <c r="AD28" s="236"/>
+      <c r="AE28" s="236"/>
+      <c r="AF28" s="236"/>
+      <c r="AG28" s="236"/>
+      <c r="AH28" s="236"/>
+      <c r="AI28" s="236"/>
+      <c r="AJ28" s="236"/>
+      <c r="AK28" s="236"/>
+      <c r="AL28" s="236"/>
+      <c r="AM28" s="236"/>
+      <c r="AN28" s="236"/>
+      <c r="AO28" s="236"/>
+      <c r="AP28" s="236"/>
+      <c r="AQ28" s="236"/>
+      <c r="AR28" s="236"/>
+      <c r="AS28" s="236"/>
+      <c r="AT28" s="237" t="s">
         <v>49</v>
       </c>
-      <c r="AU28" s="105"/>
-      <c r="AV28" s="105"/>
-      <c r="AW28" s="105"/>
-      <c r="AX28" s="105"/>
-      <c r="AY28" s="105"/>
-      <c r="AZ28" s="106"/>
+      <c r="AU28" s="237"/>
+      <c r="AV28" s="237"/>
+      <c r="AW28" s="237"/>
+      <c r="AX28" s="237"/>
+      <c r="AY28" s="237"/>
+      <c r="AZ28" s="238"/>
     </row>
     <row r="29" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="107" t="s">
+      <c r="A29" s="239" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="108"/>
-      <c r="C29" s="108"/>
-      <c r="D29" s="108"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="108"/>
-      <c r="G29" s="108"/>
-      <c r="H29" s="108"/>
-      <c r="I29" s="108"/>
-      <c r="J29" s="108"/>
-      <c r="K29" s="108"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="108"/>
-      <c r="N29" s="108"/>
-      <c r="O29" s="108"/>
-      <c r="P29" s="108"/>
-      <c r="Q29" s="108"/>
-      <c r="R29" s="108"/>
-      <c r="S29" s="108"/>
-      <c r="T29" s="109"/>
-      <c r="U29" s="109"/>
-      <c r="V29" s="109"/>
-      <c r="W29" s="109"/>
-      <c r="X29" s="109"/>
-      <c r="Y29" s="109"/>
-      <c r="Z29" s="109"/>
-      <c r="AA29" s="108" t="s">
+      <c r="B29" s="240"/>
+      <c r="C29" s="240"/>
+      <c r="D29" s="240"/>
+      <c r="E29" s="240"/>
+      <c r="F29" s="240"/>
+      <c r="G29" s="240"/>
+      <c r="H29" s="240"/>
+      <c r="I29" s="240"/>
+      <c r="J29" s="240"/>
+      <c r="K29" s="240"/>
+      <c r="L29" s="240"/>
+      <c r="M29" s="240"/>
+      <c r="N29" s="240"/>
+      <c r="O29" s="240"/>
+      <c r="P29" s="240"/>
+      <c r="Q29" s="240"/>
+      <c r="R29" s="240"/>
+      <c r="S29" s="240"/>
+      <c r="T29" s="241"/>
+      <c r="U29" s="241"/>
+      <c r="V29" s="241"/>
+      <c r="W29" s="241"/>
+      <c r="X29" s="241"/>
+      <c r="Y29" s="241"/>
+      <c r="Z29" s="241"/>
+      <c r="AA29" s="240" t="s">
         <v>51</v>
       </c>
-      <c r="AB29" s="108"/>
-      <c r="AC29" s="108"/>
-      <c r="AD29" s="108"/>
-      <c r="AE29" s="108"/>
-      <c r="AF29" s="108"/>
-      <c r="AG29" s="108"/>
-      <c r="AH29" s="108"/>
-      <c r="AI29" s="108"/>
-      <c r="AJ29" s="108"/>
-      <c r="AK29" s="108"/>
-      <c r="AL29" s="108"/>
-      <c r="AM29" s="108"/>
-      <c r="AN29" s="108"/>
-      <c r="AO29" s="108"/>
-      <c r="AP29" s="108"/>
-      <c r="AQ29" s="108"/>
-      <c r="AR29" s="108"/>
-      <c r="AS29" s="108"/>
-      <c r="AT29" s="109"/>
-      <c r="AU29" s="109"/>
-      <c r="AV29" s="109"/>
-      <c r="AW29" s="109"/>
-      <c r="AX29" s="109"/>
-      <c r="AY29" s="109"/>
-      <c r="AZ29" s="110"/>
+      <c r="AB29" s="240"/>
+      <c r="AC29" s="240"/>
+      <c r="AD29" s="240"/>
+      <c r="AE29" s="240"/>
+      <c r="AF29" s="240"/>
+      <c r="AG29" s="240"/>
+      <c r="AH29" s="240"/>
+      <c r="AI29" s="240"/>
+      <c r="AJ29" s="240"/>
+      <c r="AK29" s="240"/>
+      <c r="AL29" s="240"/>
+      <c r="AM29" s="240"/>
+      <c r="AN29" s="240"/>
+      <c r="AO29" s="240"/>
+      <c r="AP29" s="240"/>
+      <c r="AQ29" s="240"/>
+      <c r="AR29" s="240"/>
+      <c r="AS29" s="240"/>
+      <c r="AT29" s="241"/>
+      <c r="AU29" s="241"/>
+      <c r="AV29" s="241"/>
+      <c r="AW29" s="241"/>
+      <c r="AX29" s="241"/>
+      <c r="AY29" s="241"/>
+      <c r="AZ29" s="289"/>
     </row>
     <row r="30" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="107" t="s">
+      <c r="A30" s="239" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="108"/>
-      <c r="C30" s="108"/>
-      <c r="D30" s="108"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="108"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="108"/>
-      <c r="I30" s="108"/>
-      <c r="J30" s="108"/>
-      <c r="K30" s="108"/>
-      <c r="L30" s="108"/>
-      <c r="M30" s="108"/>
-      <c r="N30" s="108"/>
-      <c r="O30" s="108"/>
-      <c r="P30" s="108"/>
-      <c r="Q30" s="108"/>
-      <c r="R30" s="108"/>
-      <c r="S30" s="108"/>
-      <c r="T30" s="109"/>
-      <c r="U30" s="109"/>
-      <c r="V30" s="109"/>
-      <c r="W30" s="109"/>
-      <c r="X30" s="109"/>
-      <c r="Y30" s="109"/>
-      <c r="Z30" s="109"/>
-      <c r="AA30" s="108" t="s">
+      <c r="B30" s="240"/>
+      <c r="C30" s="240"/>
+      <c r="D30" s="240"/>
+      <c r="E30" s="240"/>
+      <c r="F30" s="240"/>
+      <c r="G30" s="240"/>
+      <c r="H30" s="240"/>
+      <c r="I30" s="240"/>
+      <c r="J30" s="240"/>
+      <c r="K30" s="240"/>
+      <c r="L30" s="240"/>
+      <c r="M30" s="240"/>
+      <c r="N30" s="240"/>
+      <c r="O30" s="240"/>
+      <c r="P30" s="240"/>
+      <c r="Q30" s="240"/>
+      <c r="R30" s="240"/>
+      <c r="S30" s="240"/>
+      <c r="T30" s="241"/>
+      <c r="U30" s="241"/>
+      <c r="V30" s="241"/>
+      <c r="W30" s="241"/>
+      <c r="X30" s="241"/>
+      <c r="Y30" s="241"/>
+      <c r="Z30" s="241"/>
+      <c r="AA30" s="240" t="s">
         <v>53</v>
       </c>
-      <c r="AB30" s="108"/>
-      <c r="AC30" s="108"/>
-      <c r="AD30" s="108"/>
-      <c r="AE30" s="108"/>
-      <c r="AF30" s="108"/>
-      <c r="AG30" s="108"/>
-      <c r="AH30" s="108"/>
-      <c r="AI30" s="108"/>
-      <c r="AJ30" s="108"/>
-      <c r="AK30" s="108"/>
-      <c r="AL30" s="108"/>
-      <c r="AM30" s="108"/>
-      <c r="AN30" s="108"/>
-      <c r="AO30" s="108"/>
-      <c r="AP30" s="108"/>
-      <c r="AQ30" s="108"/>
-      <c r="AR30" s="108"/>
-      <c r="AS30" s="108"/>
-      <c r="AT30" s="109"/>
-      <c r="AU30" s="109"/>
-      <c r="AV30" s="109"/>
-      <c r="AW30" s="109"/>
-      <c r="AX30" s="109"/>
-      <c r="AY30" s="109"/>
-      <c r="AZ30" s="110"/>
+      <c r="AB30" s="240"/>
+      <c r="AC30" s="240"/>
+      <c r="AD30" s="240"/>
+      <c r="AE30" s="240"/>
+      <c r="AF30" s="240"/>
+      <c r="AG30" s="240"/>
+      <c r="AH30" s="240"/>
+      <c r="AI30" s="240"/>
+      <c r="AJ30" s="240"/>
+      <c r="AK30" s="240"/>
+      <c r="AL30" s="240"/>
+      <c r="AM30" s="240"/>
+      <c r="AN30" s="240"/>
+      <c r="AO30" s="240"/>
+      <c r="AP30" s="240"/>
+      <c r="AQ30" s="240"/>
+      <c r="AR30" s="240"/>
+      <c r="AS30" s="240"/>
+      <c r="AT30" s="241"/>
+      <c r="AU30" s="241"/>
+      <c r="AV30" s="241"/>
+      <c r="AW30" s="241"/>
+      <c r="AX30" s="241"/>
+      <c r="AY30" s="241"/>
+      <c r="AZ30" s="242"/>
     </row>
     <row r="31" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="111" t="s">
+      <c r="A31" s="226" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="112"/>
-      <c r="C31" s="112"/>
-      <c r="D31" s="112"/>
-      <c r="E31" s="112"/>
-      <c r="F31" s="112"/>
-      <c r="G31" s="112"/>
-      <c r="H31" s="112"/>
-      <c r="I31" s="112"/>
-      <c r="J31" s="112"/>
-      <c r="K31" s="112"/>
-      <c r="L31" s="112"/>
-      <c r="M31" s="112"/>
-      <c r="N31" s="112"/>
-      <c r="O31" s="112"/>
-      <c r="P31" s="112"/>
-      <c r="Q31" s="112"/>
-      <c r="R31" s="112"/>
-      <c r="S31" s="112"/>
-      <c r="T31" s="113"/>
-      <c r="U31" s="113"/>
-      <c r="V31" s="113"/>
-      <c r="W31" s="113"/>
-      <c r="X31" s="113"/>
-      <c r="Y31" s="113"/>
-      <c r="Z31" s="113"/>
-      <c r="AA31" s="112" t="s">
+      <c r="B31" s="227"/>
+      <c r="C31" s="227"/>
+      <c r="D31" s="227"/>
+      <c r="E31" s="227"/>
+      <c r="F31" s="227"/>
+      <c r="G31" s="227"/>
+      <c r="H31" s="227"/>
+      <c r="I31" s="227"/>
+      <c r="J31" s="227"/>
+      <c r="K31" s="227"/>
+      <c r="L31" s="227"/>
+      <c r="M31" s="227"/>
+      <c r="N31" s="227"/>
+      <c r="O31" s="227"/>
+      <c r="P31" s="227"/>
+      <c r="Q31" s="227"/>
+      <c r="R31" s="227"/>
+      <c r="S31" s="227"/>
+      <c r="T31" s="243"/>
+      <c r="U31" s="243"/>
+      <c r="V31" s="243"/>
+      <c r="W31" s="243"/>
+      <c r="X31" s="243"/>
+      <c r="Y31" s="243"/>
+      <c r="Z31" s="243"/>
+      <c r="AA31" s="227" t="s">
         <v>54</v>
       </c>
-      <c r="AB31" s="112"/>
-      <c r="AC31" s="112"/>
-      <c r="AD31" s="112"/>
-      <c r="AE31" s="112"/>
-      <c r="AF31" s="112"/>
-      <c r="AG31" s="112"/>
-      <c r="AH31" s="112"/>
-      <c r="AI31" s="112"/>
-      <c r="AJ31" s="112"/>
-      <c r="AK31" s="112"/>
-      <c r="AL31" s="112"/>
-      <c r="AM31" s="112"/>
-      <c r="AN31" s="112"/>
-      <c r="AO31" s="112"/>
-      <c r="AP31" s="112"/>
-      <c r="AQ31" s="112"/>
-      <c r="AR31" s="112"/>
-      <c r="AS31" s="112"/>
-      <c r="AT31" s="113"/>
-      <c r="AU31" s="113"/>
-      <c r="AV31" s="113"/>
-      <c r="AW31" s="113"/>
-      <c r="AX31" s="113"/>
-      <c r="AY31" s="113"/>
-      <c r="AZ31" s="114"/>
+      <c r="AB31" s="227"/>
+      <c r="AC31" s="227"/>
+      <c r="AD31" s="227"/>
+      <c r="AE31" s="227"/>
+      <c r="AF31" s="227"/>
+      <c r="AG31" s="227"/>
+      <c r="AH31" s="227"/>
+      <c r="AI31" s="227"/>
+      <c r="AJ31" s="227"/>
+      <c r="AK31" s="227"/>
+      <c r="AL31" s="227"/>
+      <c r="AM31" s="227"/>
+      <c r="AN31" s="227"/>
+      <c r="AO31" s="227"/>
+      <c r="AP31" s="227"/>
+      <c r="AQ31" s="227"/>
+      <c r="AR31" s="227"/>
+      <c r="AS31" s="227"/>
+      <c r="AT31" s="243"/>
+      <c r="AU31" s="243"/>
+      <c r="AV31" s="243"/>
+      <c r="AW31" s="243"/>
+      <c r="AX31" s="243"/>
+      <c r="AY31" s="243"/>
+      <c r="AZ31" s="244"/>
     </row>
     <row r="32" spans="1:62" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="98"/>
-      <c r="B32" s="98"/>
-      <c r="C32" s="98"/>
-      <c r="D32" s="98"/>
-      <c r="E32" s="98"/>
-      <c r="F32" s="98"/>
-      <c r="G32" s="98"/>
-      <c r="H32" s="98"/>
-      <c r="I32" s="98"/>
-      <c r="J32" s="98"/>
-      <c r="K32" s="98"/>
-      <c r="L32" s="98"/>
-      <c r="M32" s="98"/>
-      <c r="N32" s="98"/>
-      <c r="O32" s="98"/>
-      <c r="P32" s="98"/>
-      <c r="Q32" s="98"/>
-      <c r="R32" s="98"/>
-      <c r="S32" s="98"/>
-      <c r="T32" s="98"/>
-      <c r="U32" s="98"/>
-      <c r="V32" s="98"/>
-      <c r="W32" s="98"/>
-      <c r="X32" s="98"/>
-      <c r="Y32" s="98"/>
-      <c r="Z32" s="98"/>
-      <c r="AA32" s="98"/>
-      <c r="AB32" s="98"/>
-      <c r="AC32" s="98"/>
-      <c r="AD32" s="98"/>
-      <c r="AE32" s="98"/>
-      <c r="AF32" s="98"/>
-      <c r="AG32" s="98"/>
-      <c r="AH32" s="98"/>
-      <c r="AI32" s="98"/>
-      <c r="AJ32" s="98"/>
-      <c r="AK32" s="98"/>
-      <c r="AL32" s="98"/>
-      <c r="AM32" s="98"/>
-      <c r="AN32" s="98"/>
-      <c r="AO32" s="98"/>
-      <c r="AP32" s="98"/>
-      <c r="AQ32" s="98"/>
-      <c r="AR32" s="98"/>
-      <c r="AS32" s="98"/>
-      <c r="AT32" s="98"/>
-      <c r="AU32" s="98"/>
-      <c r="AV32" s="98"/>
-      <c r="AW32" s="98"/>
-      <c r="AX32" s="98"/>
-      <c r="AY32" s="98"/>
-      <c r="AZ32" s="98"/>
+      <c r="A32" s="234"/>
+      <c r="B32" s="234"/>
+      <c r="C32" s="234"/>
+      <c r="D32" s="234"/>
+      <c r="E32" s="234"/>
+      <c r="F32" s="234"/>
+      <c r="G32" s="234"/>
+      <c r="H32" s="234"/>
+      <c r="I32" s="234"/>
+      <c r="J32" s="234"/>
+      <c r="K32" s="234"/>
+      <c r="L32" s="234"/>
+      <c r="M32" s="234"/>
+      <c r="N32" s="234"/>
+      <c r="O32" s="234"/>
+      <c r="P32" s="234"/>
+      <c r="Q32" s="234"/>
+      <c r="R32" s="234"/>
+      <c r="S32" s="234"/>
+      <c r="T32" s="234"/>
+      <c r="U32" s="234"/>
+      <c r="V32" s="234"/>
+      <c r="W32" s="234"/>
+      <c r="X32" s="234"/>
+      <c r="Y32" s="234"/>
+      <c r="Z32" s="234"/>
+      <c r="AA32" s="234"/>
+      <c r="AB32" s="234"/>
+      <c r="AC32" s="234"/>
+      <c r="AD32" s="234"/>
+      <c r="AE32" s="234"/>
+      <c r="AF32" s="234"/>
+      <c r="AG32" s="234"/>
+      <c r="AH32" s="234"/>
+      <c r="AI32" s="234"/>
+      <c r="AJ32" s="234"/>
+      <c r="AK32" s="234"/>
+      <c r="AL32" s="234"/>
+      <c r="AM32" s="234"/>
+      <c r="AN32" s="234"/>
+      <c r="AO32" s="234"/>
+      <c r="AP32" s="234"/>
+      <c r="AQ32" s="234"/>
+      <c r="AR32" s="234"/>
+      <c r="AS32" s="234"/>
+      <c r="AT32" s="234"/>
+      <c r="AU32" s="234"/>
+      <c r="AV32" s="234"/>
+      <c r="AW32" s="234"/>
+      <c r="AX32" s="234"/>
+      <c r="AY32" s="234"/>
+      <c r="AZ32" s="234"/>
     </row>
     <row r="33" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="205" t="s">
+      <c r="A33" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="206"/>
-      <c r="C33" s="206"/>
-      <c r="D33" s="206"/>
-      <c r="E33" s="206"/>
-      <c r="F33" s="206"/>
-      <c r="G33" s="206"/>
-      <c r="H33" s="206"/>
-      <c r="I33" s="206"/>
-      <c r="J33" s="206"/>
-      <c r="K33" s="206"/>
-      <c r="L33" s="206"/>
-      <c r="M33" s="206"/>
-      <c r="N33" s="206"/>
-      <c r="O33" s="206"/>
-      <c r="P33" s="206"/>
-      <c r="Q33" s="206"/>
-      <c r="R33" s="207"/>
-      <c r="S33" s="196" t="s">
+      <c r="B33" s="134"/>
+      <c r="C33" s="134"/>
+      <c r="D33" s="134"/>
+      <c r="E33" s="134"/>
+      <c r="F33" s="134"/>
+      <c r="G33" s="134"/>
+      <c r="H33" s="134"/>
+      <c r="I33" s="134"/>
+      <c r="J33" s="134"/>
+      <c r="K33" s="134"/>
+      <c r="L33" s="134"/>
+      <c r="M33" s="134"/>
+      <c r="N33" s="134"/>
+      <c r="O33" s="134"/>
+      <c r="P33" s="134"/>
+      <c r="Q33" s="134"/>
+      <c r="R33" s="135"/>
+      <c r="S33" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="T33" s="197"/>
-      <c r="U33" s="197"/>
-      <c r="V33" s="197"/>
-      <c r="W33" s="197"/>
-      <c r="X33" s="197"/>
-      <c r="Y33" s="197"/>
-      <c r="Z33" s="197"/>
-      <c r="AA33" s="197"/>
-      <c r="AB33" s="197"/>
-      <c r="AC33" s="197"/>
-      <c r="AD33" s="197"/>
-      <c r="AE33" s="197"/>
-      <c r="AF33" s="197"/>
-      <c r="AG33" s="198"/>
-      <c r="AH33" s="196" t="s">
+      <c r="T33" s="99"/>
+      <c r="U33" s="99"/>
+      <c r="V33" s="99"/>
+      <c r="W33" s="99"/>
+      <c r="X33" s="99"/>
+      <c r="Y33" s="99"/>
+      <c r="Z33" s="99"/>
+      <c r="AA33" s="99"/>
+      <c r="AB33" s="99"/>
+      <c r="AC33" s="99"/>
+      <c r="AD33" s="99"/>
+      <c r="AE33" s="99"/>
+      <c r="AF33" s="99"/>
+      <c r="AG33" s="125"/>
+      <c r="AH33" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="AI33" s="197"/>
-      <c r="AJ33" s="197"/>
-      <c r="AK33" s="197"/>
-      <c r="AL33" s="197"/>
-      <c r="AM33" s="197"/>
-      <c r="AN33" s="197"/>
-      <c r="AO33" s="197"/>
-      <c r="AP33" s="197"/>
-      <c r="AQ33" s="197"/>
-      <c r="AR33" s="197"/>
-      <c r="AS33" s="197"/>
-      <c r="AT33" s="197"/>
-      <c r="AU33" s="197"/>
-      <c r="AV33" s="197"/>
-      <c r="AW33" s="197"/>
-      <c r="AX33" s="197"/>
-      <c r="AY33" s="197"/>
-      <c r="AZ33" s="231"/>
+      <c r="AI33" s="99"/>
+      <c r="AJ33" s="99"/>
+      <c r="AK33" s="99"/>
+      <c r="AL33" s="99"/>
+      <c r="AM33" s="99"/>
+      <c r="AN33" s="99"/>
+      <c r="AO33" s="99"/>
+      <c r="AP33" s="99"/>
+      <c r="AQ33" s="99"/>
+      <c r="AR33" s="99"/>
+      <c r="AS33" s="99"/>
+      <c r="AT33" s="99"/>
+      <c r="AU33" s="99"/>
+      <c r="AV33" s="99"/>
+      <c r="AW33" s="99"/>
+      <c r="AX33" s="99"/>
+      <c r="AY33" s="99"/>
+      <c r="AZ33" s="100"/>
     </row>
     <row r="34" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="208"/>
-      <c r="B34" s="209"/>
-      <c r="C34" s="209"/>
-      <c r="D34" s="209"/>
-      <c r="E34" s="209"/>
-      <c r="F34" s="209"/>
-      <c r="G34" s="209"/>
-      <c r="H34" s="209"/>
-      <c r="I34" s="209"/>
-      <c r="J34" s="209"/>
-      <c r="K34" s="209"/>
-      <c r="L34" s="209"/>
-      <c r="M34" s="209"/>
-      <c r="N34" s="209"/>
-      <c r="O34" s="209"/>
-      <c r="P34" s="209"/>
-      <c r="Q34" s="209"/>
-      <c r="R34" s="210"/>
-      <c r="S34" s="199"/>
-      <c r="T34" s="200"/>
-      <c r="U34" s="200"/>
-      <c r="V34" s="200"/>
-      <c r="W34" s="200"/>
-      <c r="X34" s="200"/>
-      <c r="Y34" s="200"/>
-      <c r="Z34" s="200"/>
-      <c r="AA34" s="200"/>
-      <c r="AB34" s="200"/>
-      <c r="AC34" s="200"/>
-      <c r="AD34" s="200"/>
-      <c r="AE34" s="200"/>
-      <c r="AF34" s="200"/>
-      <c r="AG34" s="201"/>
-      <c r="AH34" s="199"/>
-      <c r="AI34" s="200"/>
-      <c r="AJ34" s="200"/>
-      <c r="AK34" s="200"/>
-      <c r="AL34" s="200"/>
-      <c r="AM34" s="200"/>
-      <c r="AN34" s="200"/>
-      <c r="AO34" s="200"/>
-      <c r="AP34" s="200"/>
-      <c r="AQ34" s="200"/>
-      <c r="AR34" s="200"/>
-      <c r="AS34" s="200"/>
-      <c r="AT34" s="200"/>
-      <c r="AU34" s="200"/>
-      <c r="AV34" s="200"/>
-      <c r="AW34" s="200"/>
-      <c r="AX34" s="200"/>
-      <c r="AY34" s="200"/>
-      <c r="AZ34" s="232"/>
+      <c r="A34" s="136"/>
+      <c r="B34" s="137"/>
+      <c r="C34" s="137"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="137"/>
+      <c r="F34" s="137"/>
+      <c r="G34" s="137"/>
+      <c r="H34" s="137"/>
+      <c r="I34" s="137"/>
+      <c r="J34" s="137"/>
+      <c r="K34" s="137"/>
+      <c r="L34" s="137"/>
+      <c r="M34" s="137"/>
+      <c r="N34" s="137"/>
+      <c r="O34" s="137"/>
+      <c r="P34" s="137"/>
+      <c r="Q34" s="137"/>
+      <c r="R34" s="138"/>
+      <c r="S34" s="101"/>
+      <c r="T34" s="102"/>
+      <c r="U34" s="102"/>
+      <c r="V34" s="102"/>
+      <c r="W34" s="102"/>
+      <c r="X34" s="102"/>
+      <c r="Y34" s="102"/>
+      <c r="Z34" s="102"/>
+      <c r="AA34" s="102"/>
+      <c r="AB34" s="102"/>
+      <c r="AC34" s="102"/>
+      <c r="AD34" s="102"/>
+      <c r="AE34" s="102"/>
+      <c r="AF34" s="102"/>
+      <c r="AG34" s="126"/>
+      <c r="AH34" s="101"/>
+      <c r="AI34" s="102"/>
+      <c r="AJ34" s="102"/>
+      <c r="AK34" s="102"/>
+      <c r="AL34" s="102"/>
+      <c r="AM34" s="102"/>
+      <c r="AN34" s="102"/>
+      <c r="AO34" s="102"/>
+      <c r="AP34" s="102"/>
+      <c r="AQ34" s="102"/>
+      <c r="AR34" s="102"/>
+      <c r="AS34" s="102"/>
+      <c r="AT34" s="102"/>
+      <c r="AU34" s="102"/>
+      <c r="AV34" s="102"/>
+      <c r="AW34" s="102"/>
+      <c r="AX34" s="102"/>
+      <c r="AY34" s="102"/>
+      <c r="AZ34" s="103"/>
     </row>
     <row r="35" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="183" t="s">
+      <c r="A35" s="127" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="184"/>
-      <c r="C35" s="184"/>
-      <c r="D35" s="184"/>
-      <c r="E35" s="184"/>
-      <c r="F35" s="184"/>
-      <c r="G35" s="184"/>
-      <c r="H35" s="184"/>
-      <c r="I35" s="184"/>
-      <c r="J35" s="184"/>
-      <c r="K35" s="184"/>
-      <c r="L35" s="184"/>
-      <c r="M35" s="184"/>
-      <c r="N35" s="184"/>
-      <c r="O35" s="184"/>
-      <c r="P35" s="184"/>
-      <c r="Q35" s="184"/>
-      <c r="R35" s="185"/>
-      <c r="S35" s="189" t="s">
+      <c r="B35" s="128"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="128"/>
+      <c r="E35" s="128"/>
+      <c r="F35" s="128"/>
+      <c r="G35" s="128"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="128"/>
+      <c r="J35" s="128"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="128"/>
+      <c r="M35" s="128"/>
+      <c r="N35" s="128"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="128"/>
+      <c r="Q35" s="128"/>
+      <c r="R35" s="129"/>
+      <c r="S35" s="130" t="s">
         <v>59</v>
       </c>
-      <c r="T35" s="190"/>
-      <c r="U35" s="190"/>
-      <c r="V35" s="190"/>
-      <c r="W35" s="190"/>
-      <c r="X35" s="190"/>
-      <c r="Y35" s="190"/>
-      <c r="Z35" s="190"/>
-      <c r="AA35" s="190"/>
-      <c r="AB35" s="190"/>
-      <c r="AC35" s="190"/>
-      <c r="AD35" s="190"/>
-      <c r="AE35" s="190"/>
-      <c r="AF35" s="190"/>
-      <c r="AG35" s="191"/>
-      <c r="AH35" s="202" t="s">
+      <c r="T35" s="131"/>
+      <c r="U35" s="131"/>
+      <c r="V35" s="131"/>
+      <c r="W35" s="131"/>
+      <c r="X35" s="131"/>
+      <c r="Y35" s="131"/>
+      <c r="Z35" s="131"/>
+      <c r="AA35" s="131"/>
+      <c r="AB35" s="131"/>
+      <c r="AC35" s="131"/>
+      <c r="AD35" s="131"/>
+      <c r="AE35" s="131"/>
+      <c r="AF35" s="131"/>
+      <c r="AG35" s="132"/>
+      <c r="AH35" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="AI35" s="203"/>
-      <c r="AJ35" s="203"/>
-      <c r="AK35" s="203"/>
-      <c r="AL35" s="203"/>
-      <c r="AM35" s="203"/>
-      <c r="AN35" s="203"/>
-      <c r="AO35" s="203"/>
-      <c r="AP35" s="203"/>
-      <c r="AQ35" s="203"/>
-      <c r="AR35" s="203"/>
-      <c r="AS35" s="203"/>
-      <c r="AT35" s="203"/>
-      <c r="AU35" s="203"/>
-      <c r="AV35" s="203"/>
-      <c r="AW35" s="203"/>
-      <c r="AX35" s="203"/>
-      <c r="AY35" s="203"/>
-      <c r="AZ35" s="204"/>
+      <c r="AI35" s="96"/>
+      <c r="AJ35" s="96"/>
+      <c r="AK35" s="96"/>
+      <c r="AL35" s="96"/>
+      <c r="AM35" s="96"/>
+      <c r="AN35" s="96"/>
+      <c r="AO35" s="96"/>
+      <c r="AP35" s="96"/>
+      <c r="AQ35" s="96"/>
+      <c r="AR35" s="96"/>
+      <c r="AS35" s="96"/>
+      <c r="AT35" s="96"/>
+      <c r="AU35" s="96"/>
+      <c r="AV35" s="96"/>
+      <c r="AW35" s="96"/>
+      <c r="AX35" s="96"/>
+      <c r="AY35" s="96"/>
+      <c r="AZ35" s="97"/>
     </row>
     <row r="36" spans="1:52" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="183" t="s">
+      <c r="A36" s="127" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="184"/>
-      <c r="C36" s="184"/>
-      <c r="D36" s="184"/>
-      <c r="E36" s="184"/>
-      <c r="F36" s="184"/>
-      <c r="G36" s="184"/>
-      <c r="H36" s="184"/>
-      <c r="I36" s="184"/>
-      <c r="J36" s="184"/>
-      <c r="K36" s="184"/>
-      <c r="L36" s="184"/>
-      <c r="M36" s="184"/>
-      <c r="N36" s="184"/>
-      <c r="O36" s="184"/>
-      <c r="P36" s="184"/>
-      <c r="Q36" s="184"/>
-      <c r="R36" s="185"/>
-      <c r="S36" s="189" t="s">
+      <c r="B36" s="128"/>
+      <c r="C36" s="128"/>
+      <c r="D36" s="128"/>
+      <c r="E36" s="128"/>
+      <c r="F36" s="128"/>
+      <c r="G36" s="128"/>
+      <c r="H36" s="128"/>
+      <c r="I36" s="128"/>
+      <c r="J36" s="128"/>
+      <c r="K36" s="128"/>
+      <c r="L36" s="128"/>
+      <c r="M36" s="128"/>
+      <c r="N36" s="128"/>
+      <c r="O36" s="128"/>
+      <c r="P36" s="128"/>
+      <c r="Q36" s="128"/>
+      <c r="R36" s="129"/>
+      <c r="S36" s="130" t="s">
         <v>62</v>
       </c>
-      <c r="T36" s="190"/>
-      <c r="U36" s="190"/>
-      <c r="V36" s="190"/>
-      <c r="W36" s="190"/>
-      <c r="X36" s="190"/>
-      <c r="Y36" s="190"/>
-      <c r="Z36" s="190"/>
-      <c r="AA36" s="190"/>
-      <c r="AB36" s="190"/>
-      <c r="AC36" s="190"/>
-      <c r="AD36" s="190"/>
-      <c r="AE36" s="190"/>
-      <c r="AF36" s="190"/>
-      <c r="AG36" s="191"/>
-      <c r="AH36" s="202" t="s">
+      <c r="T36" s="131"/>
+      <c r="U36" s="131"/>
+      <c r="V36" s="131"/>
+      <c r="W36" s="131"/>
+      <c r="X36" s="131"/>
+      <c r="Y36" s="131"/>
+      <c r="Z36" s="131"/>
+      <c r="AA36" s="131"/>
+      <c r="AB36" s="131"/>
+      <c r="AC36" s="131"/>
+      <c r="AD36" s="131"/>
+      <c r="AE36" s="131"/>
+      <c r="AF36" s="131"/>
+      <c r="AG36" s="132"/>
+      <c r="AH36" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="AI36" s="203"/>
-      <c r="AJ36" s="203"/>
-      <c r="AK36" s="203"/>
-      <c r="AL36" s="203"/>
-      <c r="AM36" s="203"/>
-      <c r="AN36" s="203"/>
-      <c r="AO36" s="203"/>
-      <c r="AP36" s="203"/>
-      <c r="AQ36" s="203"/>
-      <c r="AR36" s="203"/>
-      <c r="AS36" s="203"/>
-      <c r="AT36" s="203"/>
-      <c r="AU36" s="203"/>
-      <c r="AV36" s="203"/>
-      <c r="AW36" s="203"/>
-      <c r="AX36" s="203"/>
-      <c r="AY36" s="203"/>
-      <c r="AZ36" s="204"/>
+      <c r="AI36" s="96"/>
+      <c r="AJ36" s="96"/>
+      <c r="AK36" s="96"/>
+      <c r="AL36" s="96"/>
+      <c r="AM36" s="96"/>
+      <c r="AN36" s="96"/>
+      <c r="AO36" s="96"/>
+      <c r="AP36" s="96"/>
+      <c r="AQ36" s="96"/>
+      <c r="AR36" s="96"/>
+      <c r="AS36" s="96"/>
+      <c r="AT36" s="96"/>
+      <c r="AU36" s="96"/>
+      <c r="AV36" s="96"/>
+      <c r="AW36" s="96"/>
+      <c r="AX36" s="96"/>
+      <c r="AY36" s="96"/>
+      <c r="AZ36" s="97"/>
     </row>
     <row r="37" spans="1:52" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="183" t="s">
+      <c r="A37" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="184"/>
-      <c r="C37" s="184"/>
-      <c r="D37" s="184"/>
-      <c r="E37" s="184"/>
-      <c r="F37" s="184"/>
-      <c r="G37" s="184"/>
-      <c r="H37" s="184"/>
-      <c r="I37" s="184"/>
-      <c r="J37" s="184"/>
-      <c r="K37" s="184"/>
-      <c r="L37" s="184"/>
-      <c r="M37" s="184"/>
-      <c r="N37" s="184"/>
-      <c r="O37" s="184"/>
-      <c r="P37" s="184"/>
-      <c r="Q37" s="184"/>
-      <c r="R37" s="185"/>
-      <c r="S37" s="189" t="s">
+      <c r="B37" s="128"/>
+      <c r="C37" s="128"/>
+      <c r="D37" s="128"/>
+      <c r="E37" s="128"/>
+      <c r="F37" s="128"/>
+      <c r="G37" s="128"/>
+      <c r="H37" s="128"/>
+      <c r="I37" s="128"/>
+      <c r="J37" s="128"/>
+      <c r="K37" s="128"/>
+      <c r="L37" s="128"/>
+      <c r="M37" s="128"/>
+      <c r="N37" s="128"/>
+      <c r="O37" s="128"/>
+      <c r="P37" s="128"/>
+      <c r="Q37" s="128"/>
+      <c r="R37" s="129"/>
+      <c r="S37" s="130" t="s">
         <v>65</v>
       </c>
-      <c r="T37" s="190"/>
-      <c r="U37" s="190"/>
-      <c r="V37" s="190"/>
-      <c r="W37" s="190"/>
-      <c r="X37" s="190"/>
-      <c r="Y37" s="190"/>
-      <c r="Z37" s="190"/>
-      <c r="AA37" s="190"/>
-      <c r="AB37" s="190"/>
-      <c r="AC37" s="190"/>
-      <c r="AD37" s="190"/>
-      <c r="AE37" s="190"/>
-      <c r="AF37" s="190"/>
-      <c r="AG37" s="191"/>
-      <c r="AH37" s="202" t="s">
+      <c r="T37" s="131"/>
+      <c r="U37" s="131"/>
+      <c r="V37" s="131"/>
+      <c r="W37" s="131"/>
+      <c r="X37" s="131"/>
+      <c r="Y37" s="131"/>
+      <c r="Z37" s="131"/>
+      <c r="AA37" s="131"/>
+      <c r="AB37" s="131"/>
+      <c r="AC37" s="131"/>
+      <c r="AD37" s="131"/>
+      <c r="AE37" s="131"/>
+      <c r="AF37" s="131"/>
+      <c r="AG37" s="132"/>
+      <c r="AH37" s="95" t="s">
         <v>66</v>
       </c>
-      <c r="AI37" s="203"/>
-      <c r="AJ37" s="203"/>
-      <c r="AK37" s="203"/>
-      <c r="AL37" s="203"/>
-      <c r="AM37" s="203"/>
-      <c r="AN37" s="203"/>
-      <c r="AO37" s="203"/>
-      <c r="AP37" s="203"/>
-      <c r="AQ37" s="203"/>
-      <c r="AR37" s="203"/>
-      <c r="AS37" s="203"/>
-      <c r="AT37" s="203"/>
-      <c r="AU37" s="203"/>
-      <c r="AV37" s="203"/>
-      <c r="AW37" s="203"/>
-      <c r="AX37" s="203"/>
-      <c r="AY37" s="203"/>
-      <c r="AZ37" s="204"/>
+      <c r="AI37" s="96"/>
+      <c r="AJ37" s="96"/>
+      <c r="AK37" s="96"/>
+      <c r="AL37" s="96"/>
+      <c r="AM37" s="96"/>
+      <c r="AN37" s="96"/>
+      <c r="AO37" s="96"/>
+      <c r="AP37" s="96"/>
+      <c r="AQ37" s="96"/>
+      <c r="AR37" s="96"/>
+      <c r="AS37" s="96"/>
+      <c r="AT37" s="96"/>
+      <c r="AU37" s="96"/>
+      <c r="AV37" s="96"/>
+      <c r="AW37" s="96"/>
+      <c r="AX37" s="96"/>
+      <c r="AY37" s="96"/>
+      <c r="AZ37" s="97"/>
     </row>
     <row r="38" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="183" t="s">
+      <c r="A38" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="184"/>
-      <c r="C38" s="184"/>
-      <c r="D38" s="184"/>
-      <c r="E38" s="184"/>
-      <c r="F38" s="184"/>
-      <c r="G38" s="184"/>
-      <c r="H38" s="184"/>
-      <c r="I38" s="184"/>
-      <c r="J38" s="184"/>
-      <c r="K38" s="184"/>
-      <c r="L38" s="184"/>
-      <c r="M38" s="184"/>
-      <c r="N38" s="184"/>
-      <c r="O38" s="184"/>
-      <c r="P38" s="184"/>
-      <c r="Q38" s="184"/>
-      <c r="R38" s="185"/>
-      <c r="S38" s="189" t="s">
+      <c r="B38" s="128"/>
+      <c r="C38" s="128"/>
+      <c r="D38" s="128"/>
+      <c r="E38" s="128"/>
+      <c r="F38" s="128"/>
+      <c r="G38" s="128"/>
+      <c r="H38" s="128"/>
+      <c r="I38" s="128"/>
+      <c r="J38" s="128"/>
+      <c r="K38" s="128"/>
+      <c r="L38" s="128"/>
+      <c r="M38" s="128"/>
+      <c r="N38" s="128"/>
+      <c r="O38" s="128"/>
+      <c r="P38" s="128"/>
+      <c r="Q38" s="128"/>
+      <c r="R38" s="129"/>
+      <c r="S38" s="130" t="s">
         <v>68</v>
       </c>
-      <c r="T38" s="190"/>
-      <c r="U38" s="190"/>
-      <c r="V38" s="190"/>
-      <c r="W38" s="190"/>
-      <c r="X38" s="190"/>
-      <c r="Y38" s="190"/>
-      <c r="Z38" s="190"/>
-      <c r="AA38" s="190"/>
-      <c r="AB38" s="190"/>
-      <c r="AC38" s="190"/>
-      <c r="AD38" s="190"/>
-      <c r="AE38" s="190"/>
-      <c r="AF38" s="190"/>
-      <c r="AG38" s="191"/>
-      <c r="AH38" s="202" t="s">
+      <c r="T38" s="131"/>
+      <c r="U38" s="131"/>
+      <c r="V38" s="131"/>
+      <c r="W38" s="131"/>
+      <c r="X38" s="131"/>
+      <c r="Y38" s="131"/>
+      <c r="Z38" s="131"/>
+      <c r="AA38" s="131"/>
+      <c r="AB38" s="131"/>
+      <c r="AC38" s="131"/>
+      <c r="AD38" s="131"/>
+      <c r="AE38" s="131"/>
+      <c r="AF38" s="131"/>
+      <c r="AG38" s="132"/>
+      <c r="AH38" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="AI38" s="203"/>
-      <c r="AJ38" s="203"/>
-      <c r="AK38" s="203"/>
-      <c r="AL38" s="203"/>
-      <c r="AM38" s="203"/>
-      <c r="AN38" s="203"/>
-      <c r="AO38" s="203"/>
-      <c r="AP38" s="203"/>
-      <c r="AQ38" s="203"/>
-      <c r="AR38" s="203"/>
-      <c r="AS38" s="203"/>
-      <c r="AT38" s="203"/>
-      <c r="AU38" s="203"/>
-      <c r="AV38" s="203"/>
-      <c r="AW38" s="203"/>
-      <c r="AX38" s="203"/>
-      <c r="AY38" s="203"/>
-      <c r="AZ38" s="204"/>
+      <c r="AI38" s="96"/>
+      <c r="AJ38" s="96"/>
+      <c r="AK38" s="96"/>
+      <c r="AL38" s="96"/>
+      <c r="AM38" s="96"/>
+      <c r="AN38" s="96"/>
+      <c r="AO38" s="96"/>
+      <c r="AP38" s="96"/>
+      <c r="AQ38" s="96"/>
+      <c r="AR38" s="96"/>
+      <c r="AS38" s="96"/>
+      <c r="AT38" s="96"/>
+      <c r="AU38" s="96"/>
+      <c r="AV38" s="96"/>
+      <c r="AW38" s="96"/>
+      <c r="AX38" s="96"/>
+      <c r="AY38" s="96"/>
+      <c r="AZ38" s="97"/>
     </row>
     <row r="39" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="183" t="s">
+      <c r="A39" s="127" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="184"/>
-      <c r="C39" s="184"/>
-      <c r="D39" s="184"/>
-      <c r="E39" s="184"/>
-      <c r="F39" s="184"/>
-      <c r="G39" s="184"/>
-      <c r="H39" s="184"/>
-      <c r="I39" s="184"/>
-      <c r="J39" s="184"/>
-      <c r="K39" s="184"/>
-      <c r="L39" s="184"/>
-      <c r="M39" s="184"/>
-      <c r="N39" s="184"/>
-      <c r="O39" s="184"/>
-      <c r="P39" s="184"/>
-      <c r="Q39" s="184"/>
-      <c r="R39" s="185"/>
-      <c r="S39" s="189" t="s">
+      <c r="B39" s="128"/>
+      <c r="C39" s="128"/>
+      <c r="D39" s="128"/>
+      <c r="E39" s="128"/>
+      <c r="F39" s="128"/>
+      <c r="G39" s="128"/>
+      <c r="H39" s="128"/>
+      <c r="I39" s="128"/>
+      <c r="J39" s="128"/>
+      <c r="K39" s="128"/>
+      <c r="L39" s="128"/>
+      <c r="M39" s="128"/>
+      <c r="N39" s="128"/>
+      <c r="O39" s="128"/>
+      <c r="P39" s="128"/>
+      <c r="Q39" s="128"/>
+      <c r="R39" s="129"/>
+      <c r="S39" s="130" t="s">
         <v>71</v>
       </c>
-      <c r="T39" s="190"/>
-      <c r="U39" s="190"/>
-      <c r="V39" s="190"/>
-      <c r="W39" s="190"/>
-      <c r="X39" s="190"/>
-      <c r="Y39" s="190"/>
-      <c r="Z39" s="190"/>
-      <c r="AA39" s="190"/>
-      <c r="AB39" s="190"/>
-      <c r="AC39" s="190"/>
-      <c r="AD39" s="190"/>
-      <c r="AE39" s="190"/>
-      <c r="AF39" s="190"/>
-      <c r="AG39" s="191"/>
-      <c r="AH39" s="220"/>
-      <c r="AI39" s="221"/>
-      <c r="AJ39" s="221"/>
-      <c r="AK39" s="221"/>
-      <c r="AL39" s="221"/>
-      <c r="AM39" s="221"/>
-      <c r="AN39" s="221"/>
-      <c r="AO39" s="221"/>
-      <c r="AP39" s="221"/>
-      <c r="AQ39" s="221"/>
-      <c r="AR39" s="221"/>
-      <c r="AS39" s="221"/>
-      <c r="AT39" s="221"/>
-      <c r="AU39" s="221"/>
-      <c r="AV39" s="221"/>
-      <c r="AW39" s="221"/>
-      <c r="AX39" s="221"/>
-      <c r="AY39" s="221"/>
-      <c r="AZ39" s="222"/>
+      <c r="T39" s="131"/>
+      <c r="U39" s="131"/>
+      <c r="V39" s="131"/>
+      <c r="W39" s="131"/>
+      <c r="X39" s="131"/>
+      <c r="Y39" s="131"/>
+      <c r="Z39" s="131"/>
+      <c r="AA39" s="131"/>
+      <c r="AB39" s="131"/>
+      <c r="AC39" s="131"/>
+      <c r="AD39" s="131"/>
+      <c r="AE39" s="131"/>
+      <c r="AF39" s="131"/>
+      <c r="AG39" s="132"/>
+      <c r="AH39" s="150"/>
+      <c r="AI39" s="151"/>
+      <c r="AJ39" s="151"/>
+      <c r="AK39" s="151"/>
+      <c r="AL39" s="151"/>
+      <c r="AM39" s="151"/>
+      <c r="AN39" s="151"/>
+      <c r="AO39" s="151"/>
+      <c r="AP39" s="151"/>
+      <c r="AQ39" s="151"/>
+      <c r="AR39" s="151"/>
+      <c r="AS39" s="151"/>
+      <c r="AT39" s="151"/>
+      <c r="AU39" s="151"/>
+      <c r="AV39" s="151"/>
+      <c r="AW39" s="151"/>
+      <c r="AX39" s="151"/>
+      <c r="AY39" s="151"/>
+      <c r="AZ39" s="152"/>
     </row>
     <row r="40" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="183" t="s">
+      <c r="A40" s="127" t="s">
         <v>72</v>
       </c>
-      <c r="B40" s="184"/>
-      <c r="C40" s="184"/>
-      <c r="D40" s="184"/>
-      <c r="E40" s="184"/>
-      <c r="F40" s="184"/>
-      <c r="G40" s="184"/>
-      <c r="H40" s="184"/>
-      <c r="I40" s="184"/>
-      <c r="J40" s="184"/>
-      <c r="K40" s="184"/>
-      <c r="L40" s="184"/>
-      <c r="M40" s="184"/>
-      <c r="N40" s="184"/>
-      <c r="O40" s="184"/>
-      <c r="P40" s="184"/>
-      <c r="Q40" s="184"/>
-      <c r="R40" s="185"/>
-      <c r="S40" s="189" t="s">
+      <c r="B40" s="128"/>
+      <c r="C40" s="128"/>
+      <c r="D40" s="128"/>
+      <c r="E40" s="128"/>
+      <c r="F40" s="128"/>
+      <c r="G40" s="128"/>
+      <c r="H40" s="128"/>
+      <c r="I40" s="128"/>
+      <c r="J40" s="128"/>
+      <c r="K40" s="128"/>
+      <c r="L40" s="128"/>
+      <c r="M40" s="128"/>
+      <c r="N40" s="128"/>
+      <c r="O40" s="128"/>
+      <c r="P40" s="128"/>
+      <c r="Q40" s="128"/>
+      <c r="R40" s="129"/>
+      <c r="S40" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="T40" s="190"/>
-      <c r="U40" s="190"/>
-      <c r="V40" s="190"/>
-      <c r="W40" s="190"/>
-      <c r="X40" s="190"/>
-      <c r="Y40" s="190"/>
-      <c r="Z40" s="190"/>
-      <c r="AA40" s="190"/>
-      <c r="AB40" s="190"/>
-      <c r="AC40" s="190"/>
-      <c r="AD40" s="190"/>
-      <c r="AE40" s="190"/>
-      <c r="AF40" s="190"/>
-      <c r="AG40" s="191"/>
-      <c r="AH40" s="220"/>
-      <c r="AI40" s="221"/>
-      <c r="AJ40" s="221"/>
-      <c r="AK40" s="221"/>
-      <c r="AL40" s="221"/>
-      <c r="AM40" s="221"/>
-      <c r="AN40" s="221"/>
-      <c r="AO40" s="221"/>
-      <c r="AP40" s="221"/>
-      <c r="AQ40" s="221"/>
-      <c r="AR40" s="221"/>
-      <c r="AS40" s="221"/>
-      <c r="AT40" s="221"/>
-      <c r="AU40" s="221"/>
-      <c r="AV40" s="221"/>
-      <c r="AW40" s="221"/>
-      <c r="AX40" s="221"/>
-      <c r="AY40" s="221"/>
-      <c r="AZ40" s="222"/>
+      <c r="T40" s="131"/>
+      <c r="U40" s="131"/>
+      <c r="V40" s="131"/>
+      <c r="W40" s="131"/>
+      <c r="X40" s="131"/>
+      <c r="Y40" s="131"/>
+      <c r="Z40" s="131"/>
+      <c r="AA40" s="131"/>
+      <c r="AB40" s="131"/>
+      <c r="AC40" s="131"/>
+      <c r="AD40" s="131"/>
+      <c r="AE40" s="131"/>
+      <c r="AF40" s="131"/>
+      <c r="AG40" s="132"/>
+      <c r="AH40" s="150"/>
+      <c r="AI40" s="151"/>
+      <c r="AJ40" s="151"/>
+      <c r="AK40" s="151"/>
+      <c r="AL40" s="151"/>
+      <c r="AM40" s="151"/>
+      <c r="AN40" s="151"/>
+      <c r="AO40" s="151"/>
+      <c r="AP40" s="151"/>
+      <c r="AQ40" s="151"/>
+      <c r="AR40" s="151"/>
+      <c r="AS40" s="151"/>
+      <c r="AT40" s="151"/>
+      <c r="AU40" s="151"/>
+      <c r="AV40" s="151"/>
+      <c r="AW40" s="151"/>
+      <c r="AX40" s="151"/>
+      <c r="AY40" s="151"/>
+      <c r="AZ40" s="152"/>
     </row>
     <row r="41" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="183"/>
-      <c r="B41" s="184"/>
-      <c r="C41" s="184"/>
-      <c r="D41" s="184"/>
-      <c r="E41" s="184"/>
-      <c r="F41" s="184"/>
-      <c r="G41" s="184"/>
-      <c r="H41" s="184"/>
-      <c r="I41" s="184"/>
-      <c r="J41" s="184"/>
-      <c r="K41" s="184"/>
-      <c r="L41" s="184"/>
-      <c r="M41" s="184"/>
-      <c r="N41" s="184"/>
-      <c r="O41" s="184"/>
-      <c r="P41" s="184"/>
-      <c r="Q41" s="184"/>
-      <c r="R41" s="185"/>
-      <c r="S41" s="189" t="s">
+      <c r="A41" s="127"/>
+      <c r="B41" s="128"/>
+      <c r="C41" s="128"/>
+      <c r="D41" s="128"/>
+      <c r="E41" s="128"/>
+      <c r="F41" s="128"/>
+      <c r="G41" s="128"/>
+      <c r="H41" s="128"/>
+      <c r="I41" s="128"/>
+      <c r="J41" s="128"/>
+      <c r="K41" s="128"/>
+      <c r="L41" s="128"/>
+      <c r="M41" s="128"/>
+      <c r="N41" s="128"/>
+      <c r="O41" s="128"/>
+      <c r="P41" s="128"/>
+      <c r="Q41" s="128"/>
+      <c r="R41" s="129"/>
+      <c r="S41" s="130" t="s">
         <v>74</v>
       </c>
-      <c r="T41" s="190"/>
-      <c r="U41" s="190"/>
-      <c r="V41" s="190"/>
-      <c r="W41" s="190"/>
-      <c r="X41" s="190"/>
-      <c r="Y41" s="190"/>
-      <c r="Z41" s="190"/>
-      <c r="AA41" s="190"/>
-      <c r="AB41" s="190"/>
-      <c r="AC41" s="190"/>
-      <c r="AD41" s="190"/>
-      <c r="AE41" s="190"/>
-      <c r="AF41" s="190"/>
-      <c r="AG41" s="191"/>
-      <c r="AH41" s="220"/>
-      <c r="AI41" s="221"/>
-      <c r="AJ41" s="221"/>
-      <c r="AK41" s="221"/>
-      <c r="AL41" s="221"/>
-      <c r="AM41" s="221"/>
-      <c r="AN41" s="221"/>
-      <c r="AO41" s="221"/>
-      <c r="AP41" s="221"/>
-      <c r="AQ41" s="221"/>
-      <c r="AR41" s="221"/>
-      <c r="AS41" s="221"/>
-      <c r="AT41" s="221"/>
-      <c r="AU41" s="221"/>
-      <c r="AV41" s="221"/>
-      <c r="AW41" s="221"/>
-      <c r="AX41" s="221"/>
-      <c r="AY41" s="221"/>
-      <c r="AZ41" s="222"/>
+      <c r="T41" s="131"/>
+      <c r="U41" s="131"/>
+      <c r="V41" s="131"/>
+      <c r="W41" s="131"/>
+      <c r="X41" s="131"/>
+      <c r="Y41" s="131"/>
+      <c r="Z41" s="131"/>
+      <c r="AA41" s="131"/>
+      <c r="AB41" s="131"/>
+      <c r="AC41" s="131"/>
+      <c r="AD41" s="131"/>
+      <c r="AE41" s="131"/>
+      <c r="AF41" s="131"/>
+      <c r="AG41" s="132"/>
+      <c r="AH41" s="150"/>
+      <c r="AI41" s="151"/>
+      <c r="AJ41" s="151"/>
+      <c r="AK41" s="151"/>
+      <c r="AL41" s="151"/>
+      <c r="AM41" s="151"/>
+      <c r="AN41" s="151"/>
+      <c r="AO41" s="151"/>
+      <c r="AP41" s="151"/>
+      <c r="AQ41" s="151"/>
+      <c r="AR41" s="151"/>
+      <c r="AS41" s="151"/>
+      <c r="AT41" s="151"/>
+      <c r="AU41" s="151"/>
+      <c r="AV41" s="151"/>
+      <c r="AW41" s="151"/>
+      <c r="AX41" s="151"/>
+      <c r="AY41" s="151"/>
+      <c r="AZ41" s="152"/>
     </row>
     <row r="42" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="223"/>
-      <c r="B42" s="224"/>
-      <c r="C42" s="224"/>
-      <c r="D42" s="224"/>
-      <c r="E42" s="224"/>
-      <c r="F42" s="224"/>
-      <c r="G42" s="224"/>
-      <c r="H42" s="224"/>
-      <c r="I42" s="224"/>
-      <c r="J42" s="224"/>
-      <c r="K42" s="224"/>
-      <c r="L42" s="224"/>
-      <c r="M42" s="224"/>
-      <c r="N42" s="224"/>
-      <c r="O42" s="224"/>
-      <c r="P42" s="224"/>
-      <c r="Q42" s="224"/>
-      <c r="R42" s="225"/>
-      <c r="S42" s="211" t="s">
+      <c r="A42" s="153"/>
+      <c r="B42" s="154"/>
+      <c r="C42" s="154"/>
+      <c r="D42" s="154"/>
+      <c r="E42" s="154"/>
+      <c r="F42" s="154"/>
+      <c r="G42" s="154"/>
+      <c r="H42" s="154"/>
+      <c r="I42" s="154"/>
+      <c r="J42" s="154"/>
+      <c r="K42" s="154"/>
+      <c r="L42" s="154"/>
+      <c r="M42" s="154"/>
+      <c r="N42" s="154"/>
+      <c r="O42" s="154"/>
+      <c r="P42" s="154"/>
+      <c r="Q42" s="154"/>
+      <c r="R42" s="155"/>
+      <c r="S42" s="139" t="s">
         <v>75</v>
       </c>
-      <c r="T42" s="212"/>
-      <c r="U42" s="212"/>
-      <c r="V42" s="212"/>
-      <c r="W42" s="212"/>
-      <c r="X42" s="212"/>
-      <c r="Y42" s="212"/>
-      <c r="Z42" s="212"/>
-      <c r="AA42" s="212"/>
-      <c r="AB42" s="212"/>
-      <c r="AC42" s="212"/>
-      <c r="AD42" s="212"/>
-      <c r="AE42" s="212"/>
-      <c r="AF42" s="212"/>
-      <c r="AG42" s="213"/>
-      <c r="AH42" s="226"/>
-      <c r="AI42" s="227"/>
-      <c r="AJ42" s="227"/>
-      <c r="AK42" s="227"/>
-      <c r="AL42" s="227"/>
-      <c r="AM42" s="227"/>
-      <c r="AN42" s="227"/>
-      <c r="AO42" s="227"/>
-      <c r="AP42" s="227"/>
-      <c r="AQ42" s="227"/>
-      <c r="AR42" s="227"/>
-      <c r="AS42" s="227"/>
-      <c r="AT42" s="227"/>
-      <c r="AU42" s="227"/>
-      <c r="AV42" s="227"/>
-      <c r="AW42" s="227"/>
-      <c r="AX42" s="227"/>
-      <c r="AY42" s="227"/>
-      <c r="AZ42" s="228"/>
+      <c r="T42" s="140"/>
+      <c r="U42" s="140"/>
+      <c r="V42" s="140"/>
+      <c r="W42" s="140"/>
+      <c r="X42" s="140"/>
+      <c r="Y42" s="140"/>
+      <c r="Z42" s="140"/>
+      <c r="AA42" s="140"/>
+      <c r="AB42" s="140"/>
+      <c r="AC42" s="140"/>
+      <c r="AD42" s="140"/>
+      <c r="AE42" s="140"/>
+      <c r="AF42" s="140"/>
+      <c r="AG42" s="141"/>
+      <c r="AH42" s="156"/>
+      <c r="AI42" s="157"/>
+      <c r="AJ42" s="157"/>
+      <c r="AK42" s="157"/>
+      <c r="AL42" s="157"/>
+      <c r="AM42" s="157"/>
+      <c r="AN42" s="157"/>
+      <c r="AO42" s="157"/>
+      <c r="AP42" s="157"/>
+      <c r="AQ42" s="157"/>
+      <c r="AR42" s="157"/>
+      <c r="AS42" s="157"/>
+      <c r="AT42" s="157"/>
+      <c r="AU42" s="157"/>
+      <c r="AV42" s="157"/>
+      <c r="AW42" s="157"/>
+      <c r="AX42" s="157"/>
+      <c r="AY42" s="157"/>
+      <c r="AZ42" s="158"/>
     </row>
     <row r="43" spans="1:52" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="99"/>
-      <c r="B43" s="99"/>
-      <c r="C43" s="99"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="99"/>
-      <c r="N43" s="99"/>
-      <c r="O43" s="99"/>
-      <c r="P43" s="99"/>
-      <c r="Q43" s="99"/>
-      <c r="R43" s="99"/>
-      <c r="S43" s="99"/>
-      <c r="T43" s="99"/>
-      <c r="U43" s="99"/>
-      <c r="V43" s="99"/>
-      <c r="W43" s="99"/>
-      <c r="X43" s="99"/>
-      <c r="Y43" s="99"/>
-      <c r="Z43" s="99"/>
-      <c r="AA43" s="99"/>
-      <c r="AB43" s="99"/>
-      <c r="AC43" s="99"/>
-      <c r="AD43" s="99"/>
-      <c r="AE43" s="99"/>
-      <c r="AF43" s="99"/>
-      <c r="AG43" s="99"/>
-      <c r="AH43" s="99"/>
-      <c r="AI43" s="99"/>
-      <c r="AJ43" s="99"/>
-      <c r="AK43" s="99"/>
-      <c r="AL43" s="99"/>
-      <c r="AM43" s="99"/>
-      <c r="AN43" s="99"/>
-      <c r="AO43" s="99"/>
-      <c r="AP43" s="99"/>
-      <c r="AQ43" s="99"/>
-      <c r="AR43" s="99"/>
-      <c r="AS43" s="99"/>
-      <c r="AT43" s="99"/>
-      <c r="AU43" s="99"/>
-      <c r="AV43" s="99"/>
-      <c r="AW43" s="99"/>
-      <c r="AX43" s="99"/>
-      <c r="AY43" s="99"/>
-      <c r="AZ43" s="99"/>
+      <c r="A43" s="148"/>
+      <c r="B43" s="148"/>
+      <c r="C43" s="148"/>
+      <c r="D43" s="148"/>
+      <c r="E43" s="148"/>
+      <c r="F43" s="148"/>
+      <c r="G43" s="148"/>
+      <c r="H43" s="148"/>
+      <c r="I43" s="148"/>
+      <c r="J43" s="148"/>
+      <c r="K43" s="148"/>
+      <c r="L43" s="148"/>
+      <c r="M43" s="148"/>
+      <c r="N43" s="148"/>
+      <c r="O43" s="148"/>
+      <c r="P43" s="148"/>
+      <c r="Q43" s="148"/>
+      <c r="R43" s="148"/>
+      <c r="S43" s="148"/>
+      <c r="T43" s="148"/>
+      <c r="U43" s="148"/>
+      <c r="V43" s="148"/>
+      <c r="W43" s="148"/>
+      <c r="X43" s="148"/>
+      <c r="Y43" s="148"/>
+      <c r="Z43" s="148"/>
+      <c r="AA43" s="148"/>
+      <c r="AB43" s="148"/>
+      <c r="AC43" s="148"/>
+      <c r="AD43" s="148"/>
+      <c r="AE43" s="148"/>
+      <c r="AF43" s="148"/>
+      <c r="AG43" s="148"/>
+      <c r="AH43" s="148"/>
+      <c r="AI43" s="148"/>
+      <c r="AJ43" s="148"/>
+      <c r="AK43" s="148"/>
+      <c r="AL43" s="148"/>
+      <c r="AM43" s="148"/>
+      <c r="AN43" s="148"/>
+      <c r="AO43" s="148"/>
+      <c r="AP43" s="148"/>
+      <c r="AQ43" s="148"/>
+      <c r="AR43" s="148"/>
+      <c r="AS43" s="148"/>
+      <c r="AT43" s="148"/>
+      <c r="AU43" s="148"/>
+      <c r="AV43" s="148"/>
+      <c r="AW43" s="148"/>
+      <c r="AX43" s="148"/>
+      <c r="AY43" s="148"/>
+      <c r="AZ43" s="148"/>
     </row>
     <row r="44" spans="1:52" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="214" t="s">
+      <c r="A44" s="142" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="215"/>
-      <c r="C44" s="215"/>
-      <c r="D44" s="215"/>
-      <c r="E44" s="215"/>
-      <c r="F44" s="215"/>
-      <c r="G44" s="215"/>
-      <c r="H44" s="215"/>
-      <c r="I44" s="215"/>
-      <c r="J44" s="215"/>
-      <c r="K44" s="215"/>
-      <c r="L44" s="215"/>
-      <c r="M44" s="215"/>
-      <c r="N44" s="215"/>
-      <c r="O44" s="215"/>
-      <c r="P44" s="215"/>
-      <c r="Q44" s="215"/>
-      <c r="R44" s="215"/>
-      <c r="S44" s="215"/>
-      <c r="T44" s="215"/>
-      <c r="U44" s="215"/>
-      <c r="V44" s="215"/>
-      <c r="W44" s="215"/>
-      <c r="X44" s="215"/>
-      <c r="Y44" s="215"/>
-      <c r="Z44" s="215"/>
-      <c r="AA44" s="215"/>
-      <c r="AB44" s="215"/>
-      <c r="AC44" s="215"/>
-      <c r="AD44" s="215"/>
-      <c r="AE44" s="215"/>
-      <c r="AF44" s="215"/>
-      <c r="AG44" s="215"/>
-      <c r="AH44" s="215"/>
-      <c r="AI44" s="215"/>
-      <c r="AJ44" s="215"/>
-      <c r="AK44" s="215"/>
-      <c r="AL44" s="215"/>
-      <c r="AM44" s="215"/>
-      <c r="AN44" s="215"/>
-      <c r="AO44" s="215"/>
-      <c r="AP44" s="215"/>
-      <c r="AQ44" s="215"/>
-      <c r="AR44" s="215"/>
-      <c r="AS44" s="215"/>
-      <c r="AT44" s="215"/>
-      <c r="AU44" s="215"/>
-      <c r="AV44" s="215"/>
-      <c r="AW44" s="215"/>
-      <c r="AX44" s="215"/>
-      <c r="AY44" s="215"/>
-      <c r="AZ44" s="216"/>
+      <c r="B44" s="143"/>
+      <c r="C44" s="143"/>
+      <c r="D44" s="143"/>
+      <c r="E44" s="143"/>
+      <c r="F44" s="143"/>
+      <c r="G44" s="143"/>
+      <c r="H44" s="143"/>
+      <c r="I44" s="143"/>
+      <c r="J44" s="143"/>
+      <c r="K44" s="143"/>
+      <c r="L44" s="143"/>
+      <c r="M44" s="143"/>
+      <c r="N44" s="143"/>
+      <c r="O44" s="143"/>
+      <c r="P44" s="143"/>
+      <c r="Q44" s="143"/>
+      <c r="R44" s="143"/>
+      <c r="S44" s="143"/>
+      <c r="T44" s="143"/>
+      <c r="U44" s="143"/>
+      <c r="V44" s="143"/>
+      <c r="W44" s="143"/>
+      <c r="X44" s="143"/>
+      <c r="Y44" s="143"/>
+      <c r="Z44" s="143"/>
+      <c r="AA44" s="143"/>
+      <c r="AB44" s="143"/>
+      <c r="AC44" s="143"/>
+      <c r="AD44" s="143"/>
+      <c r="AE44" s="143"/>
+      <c r="AF44" s="143"/>
+      <c r="AG44" s="143"/>
+      <c r="AH44" s="143"/>
+      <c r="AI44" s="143"/>
+      <c r="AJ44" s="143"/>
+      <c r="AK44" s="143"/>
+      <c r="AL44" s="143"/>
+      <c r="AM44" s="143"/>
+      <c r="AN44" s="143"/>
+      <c r="AO44" s="143"/>
+      <c r="AP44" s="143"/>
+      <c r="AQ44" s="143"/>
+      <c r="AR44" s="143"/>
+      <c r="AS44" s="143"/>
+      <c r="AT44" s="143"/>
+      <c r="AU44" s="143"/>
+      <c r="AV44" s="143"/>
+      <c r="AW44" s="143"/>
+      <c r="AX44" s="143"/>
+      <c r="AY44" s="143"/>
+      <c r="AZ44" s="144"/>
     </row>
     <row r="45" spans="1:52" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="217"/>
-      <c r="B45" s="218"/>
-      <c r="C45" s="218"/>
-      <c r="D45" s="218"/>
-      <c r="E45" s="218"/>
-      <c r="F45" s="218"/>
-      <c r="G45" s="218"/>
-      <c r="H45" s="218"/>
-      <c r="I45" s="218"/>
-      <c r="J45" s="218"/>
-      <c r="K45" s="218"/>
-      <c r="L45" s="218"/>
-      <c r="M45" s="218"/>
-      <c r="N45" s="218"/>
-      <c r="O45" s="218"/>
-      <c r="P45" s="218"/>
-      <c r="Q45" s="218"/>
-      <c r="R45" s="218"/>
-      <c r="S45" s="218"/>
-      <c r="T45" s="218"/>
-      <c r="U45" s="218"/>
-      <c r="V45" s="218"/>
-      <c r="W45" s="218"/>
-      <c r="X45" s="218"/>
-      <c r="Y45" s="218"/>
-      <c r="Z45" s="218"/>
-      <c r="AA45" s="218"/>
-      <c r="AB45" s="218"/>
-      <c r="AC45" s="218"/>
-      <c r="AD45" s="218"/>
-      <c r="AE45" s="218"/>
-      <c r="AF45" s="218"/>
-      <c r="AG45" s="218"/>
-      <c r="AH45" s="218"/>
-      <c r="AI45" s="218"/>
-      <c r="AJ45" s="218"/>
-      <c r="AK45" s="218"/>
-      <c r="AL45" s="218"/>
-      <c r="AM45" s="218"/>
-      <c r="AN45" s="218"/>
-      <c r="AO45" s="218"/>
-      <c r="AP45" s="218"/>
-      <c r="AQ45" s="218"/>
-      <c r="AR45" s="218"/>
-      <c r="AS45" s="218"/>
-      <c r="AT45" s="218"/>
-      <c r="AU45" s="218"/>
-      <c r="AV45" s="218"/>
-      <c r="AW45" s="218"/>
-      <c r="AX45" s="218"/>
-      <c r="AY45" s="218"/>
-      <c r="AZ45" s="219"/>
+      <c r="A45" s="145"/>
+      <c r="B45" s="146"/>
+      <c r="C45" s="146"/>
+      <c r="D45" s="146"/>
+      <c r="E45" s="146"/>
+      <c r="F45" s="146"/>
+      <c r="G45" s="146"/>
+      <c r="H45" s="146"/>
+      <c r="I45" s="146"/>
+      <c r="J45" s="146"/>
+      <c r="K45" s="146"/>
+      <c r="L45" s="146"/>
+      <c r="M45" s="146"/>
+      <c r="N45" s="146"/>
+      <c r="O45" s="146"/>
+      <c r="P45" s="146"/>
+      <c r="Q45" s="146"/>
+      <c r="R45" s="146"/>
+      <c r="S45" s="146"/>
+      <c r="T45" s="146"/>
+      <c r="U45" s="146"/>
+      <c r="V45" s="146"/>
+      <c r="W45" s="146"/>
+      <c r="X45" s="146"/>
+      <c r="Y45" s="146"/>
+      <c r="Z45" s="146"/>
+      <c r="AA45" s="146"/>
+      <c r="AB45" s="146"/>
+      <c r="AC45" s="146"/>
+      <c r="AD45" s="146"/>
+      <c r="AE45" s="146"/>
+      <c r="AF45" s="146"/>
+      <c r="AG45" s="146"/>
+      <c r="AH45" s="146"/>
+      <c r="AI45" s="146"/>
+      <c r="AJ45" s="146"/>
+      <c r="AK45" s="146"/>
+      <c r="AL45" s="146"/>
+      <c r="AM45" s="146"/>
+      <c r="AN45" s="146"/>
+      <c r="AO45" s="146"/>
+      <c r="AP45" s="146"/>
+      <c r="AQ45" s="146"/>
+      <c r="AR45" s="146"/>
+      <c r="AS45" s="146"/>
+      <c r="AT45" s="146"/>
+      <c r="AU45" s="146"/>
+      <c r="AV45" s="146"/>
+      <c r="AW45" s="146"/>
+      <c r="AX45" s="146"/>
+      <c r="AY45" s="146"/>
+      <c r="AZ45" s="147"/>
     </row>
     <row r="46" spans="1:52" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
@@ -7919,174 +7933,174 @@
       <c r="AZ46"/>
     </row>
     <row r="47" spans="1:52" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="117"/>
-      <c r="B47" s="117"/>
-      <c r="C47" s="117"/>
-      <c r="D47" s="117"/>
-      <c r="E47" s="117"/>
-      <c r="F47" s="117"/>
-      <c r="G47" s="117"/>
-      <c r="H47" s="117"/>
-      <c r="I47" s="117"/>
-      <c r="J47" s="117"/>
-      <c r="K47" s="117"/>
-      <c r="L47" s="117"/>
-      <c r="M47" s="117"/>
-      <c r="N47" s="117"/>
-      <c r="O47" s="117"/>
-      <c r="P47" s="117"/>
+      <c r="A47" s="149"/>
+      <c r="B47" s="149"/>
+      <c r="C47" s="149"/>
+      <c r="D47" s="149"/>
+      <c r="E47" s="149"/>
+      <c r="F47" s="149"/>
+      <c r="G47" s="149"/>
+      <c r="H47" s="149"/>
+      <c r="I47" s="149"/>
+      <c r="J47" s="149"/>
+      <c r="K47" s="149"/>
+      <c r="L47" s="149"/>
+      <c r="M47" s="149"/>
+      <c r="N47" s="149"/>
+      <c r="O47" s="149"/>
+      <c r="P47" s="149"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
-      <c r="S47" s="117"/>
-      <c r="T47" s="117"/>
-      <c r="U47" s="117"/>
-      <c r="V47" s="117"/>
-      <c r="W47" s="117"/>
-      <c r="X47" s="117"/>
-      <c r="Y47" s="117"/>
-      <c r="Z47" s="117"/>
-      <c r="AA47" s="117"/>
-      <c r="AB47" s="117"/>
-      <c r="AC47" s="117"/>
-      <c r="AD47" s="117"/>
-      <c r="AE47" s="117"/>
-      <c r="AF47" s="117"/>
-      <c r="AG47" s="117"/>
-      <c r="AH47" s="117"/>
+      <c r="S47" s="149"/>
+      <c r="T47" s="149"/>
+      <c r="U47" s="149"/>
+      <c r="V47" s="149"/>
+      <c r="W47" s="149"/>
+      <c r="X47" s="149"/>
+      <c r="Y47" s="149"/>
+      <c r="Z47" s="149"/>
+      <c r="AA47" s="149"/>
+      <c r="AB47" s="149"/>
+      <c r="AC47" s="149"/>
+      <c r="AD47" s="149"/>
+      <c r="AE47" s="149"/>
+      <c r="AF47" s="149"/>
+      <c r="AG47" s="149"/>
+      <c r="AH47" s="149"/>
       <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
-      <c r="AK47" s="117"/>
-      <c r="AL47" s="117"/>
-      <c r="AM47" s="117"/>
-      <c r="AN47" s="117"/>
-      <c r="AO47" s="117"/>
-      <c r="AP47" s="117"/>
-      <c r="AQ47" s="117"/>
-      <c r="AR47" s="117"/>
-      <c r="AS47" s="117"/>
-      <c r="AT47" s="117"/>
-      <c r="AU47" s="117"/>
-      <c r="AV47" s="117"/>
-      <c r="AW47" s="117"/>
-      <c r="AX47" s="117"/>
-      <c r="AY47" s="117"/>
-      <c r="AZ47" s="117"/>
+      <c r="AK47" s="149"/>
+      <c r="AL47" s="149"/>
+      <c r="AM47" s="149"/>
+      <c r="AN47" s="149"/>
+      <c r="AO47" s="149"/>
+      <c r="AP47" s="149"/>
+      <c r="AQ47" s="149"/>
+      <c r="AR47" s="149"/>
+      <c r="AS47" s="149"/>
+      <c r="AT47" s="149"/>
+      <c r="AU47" s="149"/>
+      <c r="AV47" s="149"/>
+      <c r="AW47" s="149"/>
+      <c r="AX47" s="149"/>
+      <c r="AY47" s="149"/>
+      <c r="AZ47" s="149"/>
     </row>
     <row r="48" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="118" t="s">
+      <c r="A48" s="213" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="118"/>
-      <c r="C48" s="118"/>
-      <c r="D48" s="118"/>
-      <c r="E48" s="118"/>
-      <c r="F48" s="118"/>
-      <c r="G48" s="118"/>
-      <c r="H48" s="118"/>
-      <c r="I48" s="118"/>
-      <c r="J48" s="118"/>
-      <c r="K48" s="118"/>
-      <c r="L48" s="118"/>
-      <c r="M48" s="118"/>
-      <c r="N48" s="118"/>
-      <c r="O48" s="118"/>
-      <c r="P48" s="118"/>
+      <c r="B48" s="213"/>
+      <c r="C48" s="213"/>
+      <c r="D48" s="213"/>
+      <c r="E48" s="213"/>
+      <c r="F48" s="213"/>
+      <c r="G48" s="213"/>
+      <c r="H48" s="213"/>
+      <c r="I48" s="213"/>
+      <c r="J48" s="213"/>
+      <c r="K48" s="213"/>
+      <c r="L48" s="213"/>
+      <c r="M48" s="213"/>
+      <c r="N48" s="213"/>
+      <c r="O48" s="213"/>
+      <c r="P48" s="213"/>
       <c r="Q48" s="54"/>
       <c r="R48" s="54"/>
-      <c r="S48" s="195" t="s">
+      <c r="S48" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="T48" s="195"/>
-      <c r="U48" s="195"/>
-      <c r="V48" s="195"/>
-      <c r="W48" s="195"/>
-      <c r="X48" s="195"/>
-      <c r="Y48" s="195"/>
-      <c r="Z48" s="195"/>
-      <c r="AA48" s="195"/>
-      <c r="AB48" s="195"/>
-      <c r="AC48" s="195"/>
-      <c r="AD48" s="195"/>
-      <c r="AE48" s="195"/>
-      <c r="AF48" s="195"/>
-      <c r="AG48" s="195"/>
-      <c r="AH48" s="195"/>
+      <c r="T48" s="124"/>
+      <c r="U48" s="124"/>
+      <c r="V48" s="124"/>
+      <c r="W48" s="124"/>
+      <c r="X48" s="124"/>
+      <c r="Y48" s="124"/>
+      <c r="Z48" s="124"/>
+      <c r="AA48" s="124"/>
+      <c r="AB48" s="124"/>
+      <c r="AC48" s="124"/>
+      <c r="AD48" s="124"/>
+      <c r="AE48" s="124"/>
+      <c r="AF48" s="124"/>
+      <c r="AG48" s="124"/>
+      <c r="AH48" s="124"/>
       <c r="AI48" s="54"/>
       <c r="AJ48" s="54"/>
-      <c r="AK48" s="118" t="s">
+      <c r="AK48" s="213" t="s">
         <v>79</v>
       </c>
-      <c r="AL48" s="118"/>
-      <c r="AM48" s="118"/>
-      <c r="AN48" s="118"/>
-      <c r="AO48" s="118"/>
-      <c r="AP48" s="118"/>
-      <c r="AQ48" s="118"/>
-      <c r="AR48" s="118"/>
-      <c r="AS48" s="118"/>
-      <c r="AT48" s="118"/>
-      <c r="AU48" s="118"/>
-      <c r="AV48" s="118"/>
-      <c r="AW48" s="118"/>
-      <c r="AX48" s="118"/>
-      <c r="AY48" s="118"/>
-      <c r="AZ48" s="118"/>
+      <c r="AL48" s="213"/>
+      <c r="AM48" s="213"/>
+      <c r="AN48" s="213"/>
+      <c r="AO48" s="213"/>
+      <c r="AP48" s="213"/>
+      <c r="AQ48" s="213"/>
+      <c r="AR48" s="213"/>
+      <c r="AS48" s="213"/>
+      <c r="AT48" s="213"/>
+      <c r="AU48" s="213"/>
+      <c r="AV48" s="213"/>
+      <c r="AW48" s="213"/>
+      <c r="AX48" s="213"/>
+      <c r="AY48" s="213"/>
+      <c r="AZ48" s="213"/>
     </row>
     <row r="49" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="120" t="s">
+      <c r="A49" s="89" t="s">
         <v>80</v>
       </c>
-      <c r="B49" s="120"/>
-      <c r="C49" s="120"/>
-      <c r="D49" s="120"/>
-      <c r="E49" s="120"/>
-      <c r="F49" s="120"/>
-      <c r="G49" s="120"/>
-      <c r="H49" s="120"/>
-      <c r="I49" s="120"/>
-      <c r="J49" s="120"/>
-      <c r="K49" s="120"/>
-      <c r="L49" s="120"/>
-      <c r="M49" s="120"/>
-      <c r="N49" s="120"/>
-      <c r="O49" s="120"/>
-      <c r="P49" s="120"/>
-      <c r="S49" s="120" t="s">
+      <c r="B49" s="89"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="89"/>
+      <c r="E49" s="89"/>
+      <c r="F49" s="89"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="89"/>
+      <c r="I49" s="89"/>
+      <c r="J49" s="89"/>
+      <c r="K49" s="89"/>
+      <c r="L49" s="89"/>
+      <c r="M49" s="89"/>
+      <c r="N49" s="89"/>
+      <c r="O49" s="89"/>
+      <c r="P49" s="89"/>
+      <c r="S49" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="T49" s="120"/>
-      <c r="U49" s="120"/>
-      <c r="V49" s="120"/>
-      <c r="W49" s="120"/>
-      <c r="X49" s="120"/>
-      <c r="Y49" s="120"/>
-      <c r="Z49" s="120"/>
-      <c r="AA49" s="120"/>
-      <c r="AB49" s="120"/>
-      <c r="AC49" s="120"/>
-      <c r="AD49" s="120"/>
-      <c r="AE49" s="120"/>
-      <c r="AF49" s="120"/>
-      <c r="AG49" s="120"/>
-      <c r="AH49" s="120"/>
-      <c r="AK49" s="119" t="s">
+      <c r="T49" s="89"/>
+      <c r="U49" s="89"/>
+      <c r="V49" s="89"/>
+      <c r="W49" s="89"/>
+      <c r="X49" s="89"/>
+      <c r="Y49" s="89"/>
+      <c r="Z49" s="89"/>
+      <c r="AA49" s="89"/>
+      <c r="AB49" s="89"/>
+      <c r="AC49" s="89"/>
+      <c r="AD49" s="89"/>
+      <c r="AE49" s="89"/>
+      <c r="AF49" s="89"/>
+      <c r="AG49" s="89"/>
+      <c r="AH49" s="89"/>
+      <c r="AK49" s="214" t="s">
         <v>792</v>
       </c>
-      <c r="AL49" s="119"/>
-      <c r="AM49" s="119"/>
-      <c r="AN49" s="119"/>
-      <c r="AO49" s="119"/>
-      <c r="AP49" s="119"/>
-      <c r="AQ49" s="119"/>
-      <c r="AR49" s="119"/>
-      <c r="AS49" s="119"/>
-      <c r="AT49" s="119"/>
-      <c r="AU49" s="119"/>
-      <c r="AV49" s="119"/>
-      <c r="AW49" s="119"/>
-      <c r="AX49" s="119"/>
-      <c r="AY49" s="119"/>
-      <c r="AZ49" s="119"/>
+      <c r="AL49" s="214"/>
+      <c r="AM49" s="214"/>
+      <c r="AN49" s="214"/>
+      <c r="AO49" s="214"/>
+      <c r="AP49" s="214"/>
+      <c r="AQ49" s="214"/>
+      <c r="AR49" s="214"/>
+      <c r="AS49" s="214"/>
+      <c r="AT49" s="214"/>
+      <c r="AU49" s="214"/>
+      <c r="AV49" s="214"/>
+      <c r="AW49" s="214"/>
+      <c r="AX49" s="214"/>
+      <c r="AY49" s="214"/>
+      <c r="AZ49" s="214"/>
     </row>
     <row r="50" spans="1:52" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
@@ -9556,6 +9570,153 @@
   </sortState>
   <dataConsolidate function="count"/>
   <mergeCells count="171">
+    <mergeCell ref="R18:V18"/>
+    <mergeCell ref="M18:Q18"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="AV19:AZ19"/>
+    <mergeCell ref="A32:AZ32"/>
+    <mergeCell ref="A26:AZ26"/>
+    <mergeCell ref="A27:AZ27"/>
+    <mergeCell ref="A28:S28"/>
+    <mergeCell ref="T28:Z28"/>
+    <mergeCell ref="AA28:AS28"/>
+    <mergeCell ref="AT28:AZ28"/>
+    <mergeCell ref="A29:S29"/>
+    <mergeCell ref="T29:Z29"/>
+    <mergeCell ref="AA29:AS29"/>
+    <mergeCell ref="AT29:AZ29"/>
+    <mergeCell ref="A30:S30"/>
+    <mergeCell ref="T30:Z30"/>
+    <mergeCell ref="AA30:AS30"/>
+    <mergeCell ref="AT30:AZ30"/>
+    <mergeCell ref="A31:S31"/>
+    <mergeCell ref="T31:Z31"/>
+    <mergeCell ref="AA31:AS31"/>
+    <mergeCell ref="AT31:AZ31"/>
+    <mergeCell ref="AV22:AZ22"/>
+    <mergeCell ref="A47:P47"/>
+    <mergeCell ref="AK47:AZ47"/>
+    <mergeCell ref="AK48:AZ48"/>
+    <mergeCell ref="A48:P48"/>
+    <mergeCell ref="AK49:AZ49"/>
+    <mergeCell ref="A49:P49"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="M23:Q23"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="AB19:AF19"/>
+    <mergeCell ref="AB20:AF20"/>
+    <mergeCell ref="W19:AA19"/>
+    <mergeCell ref="AB22:AF22"/>
+    <mergeCell ref="AB23:AF23"/>
+    <mergeCell ref="AB24:AF24"/>
+    <mergeCell ref="Z7:AP7"/>
+    <mergeCell ref="AV23:AZ23"/>
+    <mergeCell ref="AQ19:AU19"/>
+    <mergeCell ref="AQ20:AU20"/>
+    <mergeCell ref="AQ21:AU21"/>
+    <mergeCell ref="AQ22:AU22"/>
+    <mergeCell ref="AQ23:AU23"/>
+    <mergeCell ref="W20:AA20"/>
+    <mergeCell ref="W21:AA21"/>
+    <mergeCell ref="W22:AA22"/>
+    <mergeCell ref="W23:AA23"/>
+    <mergeCell ref="AL19:AP19"/>
+    <mergeCell ref="AL20:AP20"/>
+    <mergeCell ref="AL21:AP21"/>
+    <mergeCell ref="AL22:AP22"/>
+    <mergeCell ref="AL23:AP23"/>
+    <mergeCell ref="AG19:AK19"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="AS1:AZ3"/>
+    <mergeCell ref="G6:AZ6"/>
+    <mergeCell ref="K2:AP2"/>
+    <mergeCell ref="A4:AZ4"/>
+    <mergeCell ref="AL9:AZ9"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="R17:V17"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="AE5:AK5"/>
+    <mergeCell ref="G5:AB5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="G8:AC8"/>
+    <mergeCell ref="V7:Y7"/>
+    <mergeCell ref="G9:AC9"/>
+    <mergeCell ref="AL8:AZ8"/>
+    <mergeCell ref="AL5:AZ5"/>
+    <mergeCell ref="A38:R38"/>
+    <mergeCell ref="AR7:AU7"/>
+    <mergeCell ref="AE8:AK8"/>
+    <mergeCell ref="AV7:AZ7"/>
+    <mergeCell ref="S40:AG40"/>
+    <mergeCell ref="A39:R39"/>
+    <mergeCell ref="R19:V19"/>
+    <mergeCell ref="R20:V20"/>
+    <mergeCell ref="R21:V21"/>
+    <mergeCell ref="R22:V22"/>
+    <mergeCell ref="R23:V23"/>
+    <mergeCell ref="R24:V24"/>
+    <mergeCell ref="AG20:AK20"/>
+    <mergeCell ref="AG21:AK21"/>
+    <mergeCell ref="AG22:AK22"/>
+    <mergeCell ref="AG23:AK23"/>
+    <mergeCell ref="AG18:AK18"/>
+    <mergeCell ref="AB18:AF18"/>
+    <mergeCell ref="AB21:AF21"/>
+    <mergeCell ref="W18:AA18"/>
+    <mergeCell ref="A15:AZ15"/>
+    <mergeCell ref="AG24:AK24"/>
+    <mergeCell ref="AV20:AZ20"/>
+    <mergeCell ref="AV21:AZ21"/>
+    <mergeCell ref="R25:V25"/>
+    <mergeCell ref="AV24:AZ24"/>
+    <mergeCell ref="AV25:AZ25"/>
+    <mergeCell ref="AQ24:AU24"/>
+    <mergeCell ref="AQ25:AU25"/>
+    <mergeCell ref="W24:AA24"/>
+    <mergeCell ref="W25:AA25"/>
+    <mergeCell ref="AL24:AP24"/>
+    <mergeCell ref="AL25:AP25"/>
+    <mergeCell ref="AB25:AF25"/>
+    <mergeCell ref="AG25:AK25"/>
+    <mergeCell ref="S48:AH48"/>
+    <mergeCell ref="S33:AG34"/>
+    <mergeCell ref="AH36:AZ36"/>
+    <mergeCell ref="A36:R36"/>
+    <mergeCell ref="A37:R37"/>
+    <mergeCell ref="A35:R35"/>
+    <mergeCell ref="S35:AG35"/>
+    <mergeCell ref="A33:R34"/>
+    <mergeCell ref="S42:AG42"/>
+    <mergeCell ref="S41:AG41"/>
+    <mergeCell ref="A44:AZ45"/>
+    <mergeCell ref="A43:AZ43"/>
+    <mergeCell ref="S47:AH47"/>
+    <mergeCell ref="AH39:AZ39"/>
+    <mergeCell ref="S36:AG36"/>
+    <mergeCell ref="A40:R40"/>
+    <mergeCell ref="A42:R42"/>
+    <mergeCell ref="S39:AG39"/>
+    <mergeCell ref="S38:AG38"/>
+    <mergeCell ref="S37:AG37"/>
+    <mergeCell ref="AH42:AZ42"/>
+    <mergeCell ref="AH41:AZ41"/>
+    <mergeCell ref="AH40:AZ40"/>
+    <mergeCell ref="A41:R41"/>
     <mergeCell ref="S49:U49"/>
     <mergeCell ref="V49:AH49"/>
     <mergeCell ref="BD21:BE21"/>
@@ -9580,153 +9741,6 @@
     <mergeCell ref="AV18:AZ18"/>
     <mergeCell ref="AQ18:AU18"/>
     <mergeCell ref="AL18:AP18"/>
-    <mergeCell ref="S48:AH48"/>
-    <mergeCell ref="S33:AG34"/>
-    <mergeCell ref="AH36:AZ36"/>
-    <mergeCell ref="A36:R36"/>
-    <mergeCell ref="A37:R37"/>
-    <mergeCell ref="A35:R35"/>
-    <mergeCell ref="S35:AG35"/>
-    <mergeCell ref="A33:R34"/>
-    <mergeCell ref="S42:AG42"/>
-    <mergeCell ref="S41:AG41"/>
-    <mergeCell ref="A44:AZ45"/>
-    <mergeCell ref="A43:AZ43"/>
-    <mergeCell ref="S47:AH47"/>
-    <mergeCell ref="AH39:AZ39"/>
-    <mergeCell ref="S36:AG36"/>
-    <mergeCell ref="A40:R40"/>
-    <mergeCell ref="A42:R42"/>
-    <mergeCell ref="S39:AG39"/>
-    <mergeCell ref="S38:AG38"/>
-    <mergeCell ref="S37:AG37"/>
-    <mergeCell ref="AH42:AZ42"/>
-    <mergeCell ref="AH41:AZ41"/>
-    <mergeCell ref="AH40:AZ40"/>
-    <mergeCell ref="A41:R41"/>
-    <mergeCell ref="R25:V25"/>
-    <mergeCell ref="AV24:AZ24"/>
-    <mergeCell ref="AV25:AZ25"/>
-    <mergeCell ref="AQ24:AU24"/>
-    <mergeCell ref="AQ25:AU25"/>
-    <mergeCell ref="W24:AA24"/>
-    <mergeCell ref="W25:AA25"/>
-    <mergeCell ref="AL24:AP24"/>
-    <mergeCell ref="AL25:AP25"/>
-    <mergeCell ref="AB25:AF25"/>
-    <mergeCell ref="AG25:AK25"/>
-    <mergeCell ref="A38:R38"/>
-    <mergeCell ref="AR7:AU7"/>
-    <mergeCell ref="AE8:AK8"/>
-    <mergeCell ref="AV7:AZ7"/>
-    <mergeCell ref="S40:AG40"/>
-    <mergeCell ref="A39:R39"/>
-    <mergeCell ref="R19:V19"/>
-    <mergeCell ref="R20:V20"/>
-    <mergeCell ref="R21:V21"/>
-    <mergeCell ref="R22:V22"/>
-    <mergeCell ref="R23:V23"/>
-    <mergeCell ref="R24:V24"/>
-    <mergeCell ref="AG20:AK20"/>
-    <mergeCell ref="AG21:AK21"/>
-    <mergeCell ref="AG22:AK22"/>
-    <mergeCell ref="AG23:AK23"/>
-    <mergeCell ref="AG18:AK18"/>
-    <mergeCell ref="AB18:AF18"/>
-    <mergeCell ref="AB21:AF21"/>
-    <mergeCell ref="W18:AA18"/>
-    <mergeCell ref="A15:AZ15"/>
-    <mergeCell ref="AG24:AK24"/>
-    <mergeCell ref="AV20:AZ20"/>
-    <mergeCell ref="AV21:AZ21"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="AS1:AZ3"/>
-    <mergeCell ref="G6:AZ6"/>
-    <mergeCell ref="K2:AP2"/>
-    <mergeCell ref="A4:AZ4"/>
-    <mergeCell ref="AL9:AZ9"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="R17:V17"/>
-    <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="AE5:AK5"/>
-    <mergeCell ref="G5:AB5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="G8:AC8"/>
-    <mergeCell ref="V7:Y7"/>
-    <mergeCell ref="G9:AC9"/>
-    <mergeCell ref="AL8:AZ8"/>
-    <mergeCell ref="AL5:AZ5"/>
-    <mergeCell ref="AB23:AF23"/>
-    <mergeCell ref="AB24:AF24"/>
-    <mergeCell ref="Z7:AP7"/>
-    <mergeCell ref="AV23:AZ23"/>
-    <mergeCell ref="AQ19:AU19"/>
-    <mergeCell ref="AQ20:AU20"/>
-    <mergeCell ref="AQ21:AU21"/>
-    <mergeCell ref="AQ22:AU22"/>
-    <mergeCell ref="AQ23:AU23"/>
-    <mergeCell ref="W20:AA20"/>
-    <mergeCell ref="W21:AA21"/>
-    <mergeCell ref="W22:AA22"/>
-    <mergeCell ref="W23:AA23"/>
-    <mergeCell ref="AL19:AP19"/>
-    <mergeCell ref="AL20:AP20"/>
-    <mergeCell ref="AL21:AP21"/>
-    <mergeCell ref="AL22:AP22"/>
-    <mergeCell ref="AL23:AP23"/>
-    <mergeCell ref="AG19:AK19"/>
-    <mergeCell ref="A47:P47"/>
-    <mergeCell ref="AK47:AZ47"/>
-    <mergeCell ref="AK48:AZ48"/>
-    <mergeCell ref="A48:P48"/>
-    <mergeCell ref="AK49:AZ49"/>
-    <mergeCell ref="A49:P49"/>
-    <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="M21:Q21"/>
-    <mergeCell ref="M22:Q22"/>
-    <mergeCell ref="M23:Q23"/>
-    <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="M25:Q25"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A21:L21"/>
-    <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="AB19:AF19"/>
-    <mergeCell ref="AB20:AF20"/>
-    <mergeCell ref="W19:AA19"/>
-    <mergeCell ref="AB22:AF22"/>
-    <mergeCell ref="R18:V18"/>
-    <mergeCell ref="M18:Q18"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="AV19:AZ19"/>
-    <mergeCell ref="A32:AZ32"/>
-    <mergeCell ref="A26:AZ26"/>
-    <mergeCell ref="A27:AZ27"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="T28:Z28"/>
-    <mergeCell ref="AA28:AS28"/>
-    <mergeCell ref="AT28:AZ28"/>
-    <mergeCell ref="A29:S29"/>
-    <mergeCell ref="T29:Z29"/>
-    <mergeCell ref="AA29:AS29"/>
-    <mergeCell ref="AT29:AZ29"/>
-    <mergeCell ref="A30:S30"/>
-    <mergeCell ref="T30:Z30"/>
-    <mergeCell ref="AA30:AS30"/>
-    <mergeCell ref="AT30:AZ30"/>
-    <mergeCell ref="A31:S31"/>
-    <mergeCell ref="T31:Z31"/>
-    <mergeCell ref="AA31:AS31"/>
-    <mergeCell ref="AT31:AZ31"/>
-    <mergeCell ref="AV22:AZ22"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations count="1">
@@ -9766,14 +9780,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="137"/>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="139"/>
+      <c r="A1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="172"/>
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
       <c r="K1" s="21"/>
@@ -9810,87 +9824,87 @@
       <c r="AP1" s="22"/>
       <c r="AQ1" s="22"/>
       <c r="AR1" s="22"/>
-      <c r="AS1" s="146" t="s">
+      <c r="AS1" s="179" t="s">
         <v>0</v>
       </c>
-      <c r="AT1" s="147"/>
-      <c r="AU1" s="147"/>
-      <c r="AV1" s="147"/>
-      <c r="AW1" s="147"/>
-      <c r="AX1" s="147"/>
-      <c r="AY1" s="147"/>
-      <c r="AZ1" s="148"/>
+      <c r="AT1" s="180"/>
+      <c r="AU1" s="180"/>
+      <c r="AV1" s="180"/>
+      <c r="AW1" s="180"/>
+      <c r="AX1" s="180"/>
+      <c r="AY1" s="180"/>
+      <c r="AZ1" s="181"/>
       <c r="BD1" s="23"/>
       <c r="BF1" s="27"/>
       <c r="BG1" s="27"/>
     </row>
     <row r="2" spans="1:60" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="140"/>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="142"/>
-      <c r="K2" s="156" t="s">
+      <c r="A2" s="173"/>
+      <c r="B2" s="174"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="175"/>
+      <c r="K2" s="189" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="249"/>
-      <c r="M2" s="249"/>
-      <c r="N2" s="249"/>
-      <c r="O2" s="249"/>
-      <c r="P2" s="249"/>
-      <c r="Q2" s="249"/>
-      <c r="R2" s="249"/>
-      <c r="S2" s="249"/>
-      <c r="T2" s="249"/>
-      <c r="U2" s="249"/>
-      <c r="V2" s="249"/>
-      <c r="W2" s="249"/>
-      <c r="X2" s="249"/>
-      <c r="Y2" s="249"/>
-      <c r="Z2" s="249"/>
-      <c r="AA2" s="249"/>
-      <c r="AB2" s="249"/>
-      <c r="AC2" s="249"/>
-      <c r="AD2" s="249"/>
-      <c r="AE2" s="249"/>
-      <c r="AF2" s="249"/>
-      <c r="AG2" s="249"/>
-      <c r="AH2" s="249"/>
-      <c r="AI2" s="249"/>
-      <c r="AJ2" s="249"/>
-      <c r="AK2" s="249"/>
-      <c r="AL2" s="249"/>
-      <c r="AM2" s="249"/>
-      <c r="AN2" s="249"/>
-      <c r="AO2" s="249"/>
-      <c r="AP2" s="249"/>
+      <c r="L2" s="254"/>
+      <c r="M2" s="254"/>
+      <c r="N2" s="254"/>
+      <c r="O2" s="254"/>
+      <c r="P2" s="254"/>
+      <c r="Q2" s="254"/>
+      <c r="R2" s="254"/>
+      <c r="S2" s="254"/>
+      <c r="T2" s="254"/>
+      <c r="U2" s="254"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="254"/>
+      <c r="X2" s="254"/>
+      <c r="Y2" s="254"/>
+      <c r="Z2" s="254"/>
+      <c r="AA2" s="254"/>
+      <c r="AB2" s="254"/>
+      <c r="AC2" s="254"/>
+      <c r="AD2" s="254"/>
+      <c r="AE2" s="254"/>
+      <c r="AF2" s="254"/>
+      <c r="AG2" s="254"/>
+      <c r="AH2" s="254"/>
+      <c r="AI2" s="254"/>
+      <c r="AJ2" s="254"/>
+      <c r="AK2" s="254"/>
+      <c r="AL2" s="254"/>
+      <c r="AM2" s="254"/>
+      <c r="AN2" s="254"/>
+      <c r="AO2" s="254"/>
+      <c r="AP2" s="254"/>
       <c r="AQ2" s="17"/>
       <c r="AR2" s="17"/>
-      <c r="AS2" s="149"/>
-      <c r="AT2" s="150"/>
-      <c r="AU2" s="150"/>
-      <c r="AV2" s="150"/>
-      <c r="AW2" s="150"/>
-      <c r="AX2" s="150"/>
-      <c r="AY2" s="150"/>
-      <c r="AZ2" s="151"/>
+      <c r="AS2" s="182"/>
+      <c r="AT2" s="183"/>
+      <c r="AU2" s="183"/>
+      <c r="AV2" s="183"/>
+      <c r="AW2" s="183"/>
+      <c r="AX2" s="183"/>
+      <c r="AY2" s="183"/>
+      <c r="AZ2" s="184"/>
       <c r="BA2" s="7"/>
       <c r="BF2" s="25"/>
       <c r="BG2" s="25"/>
       <c r="BH2" s="25"/>
     </row>
     <row r="3" spans="1:60" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="143"/>
-      <c r="B3" s="144"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="144"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="145"/>
+      <c r="A3" s="176"/>
+      <c r="B3" s="177"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="177"/>
+      <c r="H3" s="178"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -9927,80 +9941,80 @@
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
       <c r="AR3" s="4"/>
-      <c r="AS3" s="152"/>
-      <c r="AT3" s="153"/>
-      <c r="AU3" s="153"/>
-      <c r="AV3" s="153"/>
-      <c r="AW3" s="153"/>
-      <c r="AX3" s="153"/>
-      <c r="AY3" s="153"/>
-      <c r="AZ3" s="154"/>
+      <c r="AS3" s="185"/>
+      <c r="AT3" s="186"/>
+      <c r="AU3" s="186"/>
+      <c r="AV3" s="186"/>
+      <c r="AW3" s="186"/>
+      <c r="AX3" s="186"/>
+      <c r="AY3" s="186"/>
+      <c r="AZ3" s="187"/>
     </row>
     <row r="4" spans="1:60" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="191" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="101"/>
-      <c r="L4" s="101"/>
-      <c r="M4" s="101"/>
-      <c r="N4" s="101"/>
-      <c r="O4" s="101"/>
-      <c r="P4" s="101"/>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="101"/>
-      <c r="S4" s="101"/>
-      <c r="T4" s="101"/>
-      <c r="U4" s="101"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="101"/>
-      <c r="X4" s="101"/>
-      <c r="Y4" s="101"/>
-      <c r="Z4" s="101"/>
-      <c r="AA4" s="101"/>
-      <c r="AB4" s="101"/>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="101"/>
-      <c r="AE4" s="101"/>
-      <c r="AF4" s="101"/>
-      <c r="AG4" s="101"/>
-      <c r="AH4" s="101"/>
-      <c r="AI4" s="101"/>
-      <c r="AJ4" s="101"/>
-      <c r="AK4" s="101"/>
-      <c r="AL4" s="101"/>
-      <c r="AM4" s="101"/>
-      <c r="AN4" s="101"/>
-      <c r="AO4" s="101"/>
-      <c r="AP4" s="101"/>
-      <c r="AQ4" s="101"/>
-      <c r="AR4" s="101"/>
-      <c r="AS4" s="101"/>
-      <c r="AT4" s="101"/>
-      <c r="AU4" s="101"/>
-      <c r="AV4" s="101"/>
-      <c r="AW4" s="101"/>
-      <c r="AX4" s="101"/>
-      <c r="AY4" s="101"/>
-      <c r="AZ4" s="102"/>
+      <c r="B4" s="192"/>
+      <c r="C4" s="192"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="192"/>
+      <c r="K4" s="192"/>
+      <c r="L4" s="192"/>
+      <c r="M4" s="192"/>
+      <c r="N4" s="192"/>
+      <c r="O4" s="192"/>
+      <c r="P4" s="192"/>
+      <c r="Q4" s="192"/>
+      <c r="R4" s="192"/>
+      <c r="S4" s="192"/>
+      <c r="T4" s="192"/>
+      <c r="U4" s="192"/>
+      <c r="V4" s="192"/>
+      <c r="W4" s="192"/>
+      <c r="X4" s="192"/>
+      <c r="Y4" s="192"/>
+      <c r="Z4" s="192"/>
+      <c r="AA4" s="192"/>
+      <c r="AB4" s="192"/>
+      <c r="AC4" s="192"/>
+      <c r="AD4" s="192"/>
+      <c r="AE4" s="192"/>
+      <c r="AF4" s="192"/>
+      <c r="AG4" s="192"/>
+      <c r="AH4" s="192"/>
+      <c r="AI4" s="192"/>
+      <c r="AJ4" s="192"/>
+      <c r="AK4" s="192"/>
+      <c r="AL4" s="192"/>
+      <c r="AM4" s="192"/>
+      <c r="AN4" s="192"/>
+      <c r="AO4" s="192"/>
+      <c r="AP4" s="192"/>
+      <c r="AQ4" s="192"/>
+      <c r="AR4" s="192"/>
+      <c r="AS4" s="192"/>
+      <c r="AT4" s="192"/>
+      <c r="AU4" s="192"/>
+      <c r="AV4" s="192"/>
+      <c r="AW4" s="192"/>
+      <c r="AX4" s="192"/>
+      <c r="AY4" s="192"/>
+      <c r="AZ4" s="193"/>
       <c r="BA4" s="9"/>
       <c r="BB4" s="9"/>
       <c r="BC4" s="9"/>
     </row>
     <row r="5" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="250" t="s">
+      <c r="A5" s="255" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="251"/>
-      <c r="C5" s="251"/>
+      <c r="B5" s="256"/>
+      <c r="C5" s="256"/>
       <c r="D5" s="11"/>
       <c r="E5" s="6" t="s">
         <v>105</v>
@@ -10057,63 +10071,63 @@
       <c r="BC5" s="9"/>
     </row>
     <row r="6" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="247"/>
-      <c r="B6" s="248"/>
-      <c r="C6" s="248"/>
+      <c r="A6" s="250"/>
+      <c r="B6" s="251"/>
+      <c r="C6" s="251"/>
       <c r="D6" s="10"/>
-      <c r="E6" s="252"/>
-      <c r="F6" s="252"/>
-      <c r="G6" s="252"/>
-      <c r="H6" s="252"/>
-      <c r="I6" s="252"/>
-      <c r="J6" s="252"/>
-      <c r="K6" s="252"/>
-      <c r="L6" s="252"/>
-      <c r="M6" s="252"/>
-      <c r="N6" s="252"/>
-      <c r="O6" s="252"/>
-      <c r="P6" s="252"/>
-      <c r="Q6" s="252"/>
-      <c r="R6" s="252"/>
-      <c r="S6" s="252"/>
-      <c r="T6" s="252"/>
-      <c r="U6" s="252"/>
-      <c r="V6" s="252"/>
-      <c r="W6" s="252"/>
-      <c r="X6" s="252"/>
-      <c r="Y6" s="252"/>
-      <c r="Z6" s="252"/>
-      <c r="AA6" s="252"/>
-      <c r="AB6" s="252"/>
-      <c r="AC6" s="252"/>
-      <c r="AD6" s="252"/>
-      <c r="AE6" s="252"/>
-      <c r="AF6" s="252"/>
-      <c r="AG6" s="252"/>
-      <c r="AH6" s="252"/>
-      <c r="AI6" s="252"/>
-      <c r="AJ6" s="252"/>
-      <c r="AK6" s="252"/>
-      <c r="AL6" s="252"/>
-      <c r="AM6" s="252"/>
-      <c r="AN6" s="252"/>
-      <c r="AO6" s="252"/>
-      <c r="AP6" s="252"/>
-      <c r="AQ6" s="252"/>
-      <c r="AR6" s="252"/>
-      <c r="AS6" s="252"/>
-      <c r="AT6" s="252"/>
-      <c r="AU6" s="252"/>
-      <c r="AV6" s="252"/>
-      <c r="AW6" s="252"/>
-      <c r="AX6" s="252"/>
-      <c r="AY6" s="252"/>
-      <c r="AZ6" s="253"/>
+      <c r="E6" s="257"/>
+      <c r="F6" s="257"/>
+      <c r="G6" s="257"/>
+      <c r="H6" s="257"/>
+      <c r="I6" s="257"/>
+      <c r="J6" s="257"/>
+      <c r="K6" s="257"/>
+      <c r="L6" s="257"/>
+      <c r="M6" s="257"/>
+      <c r="N6" s="257"/>
+      <c r="O6" s="257"/>
+      <c r="P6" s="257"/>
+      <c r="Q6" s="257"/>
+      <c r="R6" s="257"/>
+      <c r="S6" s="257"/>
+      <c r="T6" s="257"/>
+      <c r="U6" s="257"/>
+      <c r="V6" s="257"/>
+      <c r="W6" s="257"/>
+      <c r="X6" s="257"/>
+      <c r="Y6" s="257"/>
+      <c r="Z6" s="257"/>
+      <c r="AA6" s="257"/>
+      <c r="AB6" s="257"/>
+      <c r="AC6" s="257"/>
+      <c r="AD6" s="257"/>
+      <c r="AE6" s="257"/>
+      <c r="AF6" s="257"/>
+      <c r="AG6" s="257"/>
+      <c r="AH6" s="257"/>
+      <c r="AI6" s="257"/>
+      <c r="AJ6" s="257"/>
+      <c r="AK6" s="257"/>
+      <c r="AL6" s="257"/>
+      <c r="AM6" s="257"/>
+      <c r="AN6" s="257"/>
+      <c r="AO6" s="257"/>
+      <c r="AP6" s="257"/>
+      <c r="AQ6" s="257"/>
+      <c r="AR6" s="257"/>
+      <c r="AS6" s="257"/>
+      <c r="AT6" s="257"/>
+      <c r="AU6" s="257"/>
+      <c r="AV6" s="257"/>
+      <c r="AW6" s="257"/>
+      <c r="AX6" s="257"/>
+      <c r="AY6" s="257"/>
+      <c r="AZ6" s="258"/>
     </row>
     <row r="7" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="247"/>
-      <c r="B7" s="248"/>
-      <c r="C7" s="248"/>
+      <c r="A7" s="250"/>
+      <c r="B7" s="251"/>
+      <c r="C7" s="251"/>
       <c r="D7" s="10"/>
       <c r="E7" s="86"/>
       <c r="F7" s="87"/>
@@ -10165,9 +10179,9 @@
       <c r="AZ7" s="88"/>
     </row>
     <row r="8" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="245"/>
-      <c r="B8" s="246"/>
-      <c r="C8" s="246"/>
+      <c r="A8" s="259"/>
+      <c r="B8" s="260"/>
+      <c r="C8" s="260"/>
       <c r="D8" s="10"/>
       <c r="E8" s="87"/>
       <c r="F8" s="87"/>
@@ -10219,63 +10233,63 @@
       <c r="AZ8" s="88"/>
     </row>
     <row r="9" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="245"/>
-      <c r="B9" s="246"/>
-      <c r="C9" s="246"/>
+      <c r="A9" s="259"/>
+      <c r="B9" s="260"/>
+      <c r="C9" s="260"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="254"/>
-      <c r="F9" s="254"/>
-      <c r="G9" s="254"/>
-      <c r="H9" s="254"/>
-      <c r="I9" s="254"/>
-      <c r="J9" s="254"/>
-      <c r="K9" s="254"/>
-      <c r="L9" s="254"/>
-      <c r="M9" s="254"/>
-      <c r="N9" s="254"/>
-      <c r="O9" s="254"/>
-      <c r="P9" s="254"/>
-      <c r="Q9" s="254"/>
-      <c r="R9" s="254"/>
-      <c r="S9" s="254"/>
-      <c r="T9" s="254"/>
-      <c r="U9" s="254"/>
-      <c r="V9" s="254"/>
-      <c r="W9" s="254"/>
-      <c r="X9" s="254"/>
-      <c r="Y9" s="254"/>
-      <c r="Z9" s="254"/>
-      <c r="AA9" s="254"/>
-      <c r="AB9" s="254"/>
-      <c r="AC9" s="254"/>
-      <c r="AD9" s="254"/>
-      <c r="AE9" s="254"/>
-      <c r="AF9" s="254"/>
-      <c r="AG9" s="254"/>
-      <c r="AH9" s="254"/>
-      <c r="AI9" s="254"/>
-      <c r="AJ9" s="254"/>
-      <c r="AK9" s="254"/>
-      <c r="AL9" s="254"/>
-      <c r="AM9" s="254"/>
-      <c r="AN9" s="254"/>
-      <c r="AO9" s="254"/>
-      <c r="AP9" s="254"/>
-      <c r="AQ9" s="254"/>
-      <c r="AR9" s="254"/>
-      <c r="AS9" s="254"/>
-      <c r="AT9" s="254"/>
-      <c r="AU9" s="254"/>
-      <c r="AV9" s="254"/>
-      <c r="AW9" s="254"/>
-      <c r="AX9" s="254"/>
-      <c r="AY9" s="254"/>
-      <c r="AZ9" s="255"/>
+      <c r="E9" s="252"/>
+      <c r="F9" s="252"/>
+      <c r="G9" s="252"/>
+      <c r="H9" s="252"/>
+      <c r="I9" s="252"/>
+      <c r="J9" s="252"/>
+      <c r="K9" s="252"/>
+      <c r="L9" s="252"/>
+      <c r="M9" s="252"/>
+      <c r="N9" s="252"/>
+      <c r="O9" s="252"/>
+      <c r="P9" s="252"/>
+      <c r="Q9" s="252"/>
+      <c r="R9" s="252"/>
+      <c r="S9" s="252"/>
+      <c r="T9" s="252"/>
+      <c r="U9" s="252"/>
+      <c r="V9" s="252"/>
+      <c r="W9" s="252"/>
+      <c r="X9" s="252"/>
+      <c r="Y9" s="252"/>
+      <c r="Z9" s="252"/>
+      <c r="AA9" s="252"/>
+      <c r="AB9" s="252"/>
+      <c r="AC9" s="252"/>
+      <c r="AD9" s="252"/>
+      <c r="AE9" s="252"/>
+      <c r="AF9" s="252"/>
+      <c r="AG9" s="252"/>
+      <c r="AH9" s="252"/>
+      <c r="AI9" s="252"/>
+      <c r="AJ9" s="252"/>
+      <c r="AK9" s="252"/>
+      <c r="AL9" s="252"/>
+      <c r="AM9" s="252"/>
+      <c r="AN9" s="252"/>
+      <c r="AO9" s="252"/>
+      <c r="AP9" s="252"/>
+      <c r="AQ9" s="252"/>
+      <c r="AR9" s="252"/>
+      <c r="AS9" s="252"/>
+      <c r="AT9" s="252"/>
+      <c r="AU9" s="252"/>
+      <c r="AV9" s="252"/>
+      <c r="AW9" s="252"/>
+      <c r="AX9" s="252"/>
+      <c r="AY9" s="252"/>
+      <c r="AZ9" s="253"/>
     </row>
     <row r="10" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="245"/>
-      <c r="B10" s="246"/>
-      <c r="C10" s="246"/>
+      <c r="A10" s="259"/>
+      <c r="B10" s="260"/>
+      <c r="C10" s="260"/>
       <c r="D10" s="10"/>
       <c r="E10" s="86"/>
       <c r="F10" s="87"/>
@@ -10327,9 +10341,9 @@
       <c r="AZ10" s="88"/>
     </row>
     <row r="11" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="247"/>
-      <c r="B11" s="248"/>
-      <c r="C11" s="248"/>
+      <c r="A11" s="250"/>
+      <c r="B11" s="251"/>
+      <c r="C11" s="251"/>
       <c r="D11" s="10"/>
       <c r="E11" s="87"/>
       <c r="F11" s="87"/>
@@ -10381,9 +10395,9 @@
       <c r="AZ11" s="88"/>
     </row>
     <row r="12" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="247"/>
-      <c r="B12" s="248"/>
-      <c r="C12" s="248"/>
+      <c r="A12" s="250"/>
+      <c r="B12" s="251"/>
+      <c r="C12" s="251"/>
       <c r="D12" s="10"/>
       <c r="E12" s="87"/>
       <c r="F12" s="87"/>
@@ -10435,9 +10449,9 @@
       <c r="AZ12" s="88"/>
     </row>
     <row r="13" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="247"/>
-      <c r="B13" s="248"/>
-      <c r="C13" s="248"/>
+      <c r="A13" s="250"/>
+      <c r="B13" s="251"/>
+      <c r="C13" s="251"/>
       <c r="D13" s="10"/>
       <c r="E13" s="87"/>
       <c r="F13" s="87"/>
@@ -10489,9 +10503,9 @@
       <c r="AZ13" s="88"/>
     </row>
     <row r="14" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="247"/>
-      <c r="B14" s="248"/>
-      <c r="C14" s="248"/>
+      <c r="A14" s="250"/>
+      <c r="B14" s="251"/>
+      <c r="C14" s="251"/>
       <c r="D14" s="10"/>
       <c r="E14" s="87"/>
       <c r="F14" s="87"/>
@@ -10543,9 +10557,9 @@
       <c r="AZ14" s="88"/>
     </row>
     <row r="15" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="247"/>
-      <c r="B15" s="248"/>
-      <c r="C15" s="248"/>
+      <c r="A15" s="250"/>
+      <c r="B15" s="251"/>
+      <c r="C15" s="251"/>
       <c r="D15" s="10"/>
       <c r="E15" s="86"/>
       <c r="F15" s="87"/>
@@ -10597,9 +10611,9 @@
       <c r="AZ15" s="88"/>
     </row>
     <row r="16" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="247"/>
-      <c r="B16" s="248"/>
-      <c r="C16" s="248"/>
+      <c r="A16" s="250"/>
+      <c r="B16" s="251"/>
+      <c r="C16" s="251"/>
       <c r="D16" s="10"/>
       <c r="E16" s="86"/>
       <c r="F16" s="87"/>
@@ -10651,9 +10665,9 @@
       <c r="AZ16" s="88"/>
     </row>
     <row r="17" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="247"/>
-      <c r="B17" s="248"/>
-      <c r="C17" s="248"/>
+      <c r="A17" s="250"/>
+      <c r="B17" s="251"/>
+      <c r="C17" s="251"/>
       <c r="D17" s="10"/>
       <c r="E17" s="86"/>
       <c r="F17" s="87"/>
@@ -10705,9 +10719,9 @@
       <c r="AZ17" s="88"/>
     </row>
     <row r="18" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="247"/>
-      <c r="B18" s="248"/>
-      <c r="C18" s="248"/>
+      <c r="A18" s="250"/>
+      <c r="B18" s="251"/>
+      <c r="C18" s="251"/>
       <c r="D18" s="10"/>
       <c r="E18" s="86"/>
       <c r="F18" s="87"/>
@@ -10759,9 +10773,9 @@
       <c r="AZ18" s="88"/>
     </row>
     <row r="19" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="247"/>
-      <c r="B19" s="248"/>
-      <c r="C19" s="248"/>
+      <c r="A19" s="250"/>
+      <c r="B19" s="251"/>
+      <c r="C19" s="251"/>
       <c r="D19" s="10"/>
       <c r="E19" s="86"/>
       <c r="F19" s="87"/>
@@ -10813,9 +10827,9 @@
       <c r="AZ19" s="88"/>
     </row>
     <row r="20" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="247"/>
-      <c r="B20" s="248"/>
-      <c r="C20" s="248"/>
+      <c r="A20" s="250"/>
+      <c r="B20" s="251"/>
+      <c r="C20" s="251"/>
       <c r="D20" s="10"/>
       <c r="E20" s="86"/>
       <c r="F20" s="87"/>
@@ -10867,9 +10881,9 @@
       <c r="AZ20" s="88"/>
     </row>
     <row r="21" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="247"/>
-      <c r="B21" s="248"/>
-      <c r="C21" s="248"/>
+      <c r="A21" s="250"/>
+      <c r="B21" s="251"/>
+      <c r="C21" s="251"/>
       <c r="D21" s="10"/>
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
@@ -10921,9 +10935,9 @@
       <c r="AZ21" s="88"/>
     </row>
     <row r="22" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="247"/>
-      <c r="B22" s="248"/>
-      <c r="C22" s="248"/>
+      <c r="A22" s="250"/>
+      <c r="B22" s="251"/>
+      <c r="C22" s="251"/>
       <c r="D22" s="10"/>
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
@@ -10975,9 +10989,9 @@
       <c r="AZ22" s="88"/>
     </row>
     <row r="23" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="247"/>
-      <c r="B23" s="248"/>
-      <c r="C23" s="248"/>
+      <c r="A23" s="250"/>
+      <c r="B23" s="251"/>
+      <c r="C23" s="251"/>
       <c r="D23" s="10"/>
       <c r="E23" s="86"/>
       <c r="F23" s="87"/>
@@ -11029,9 +11043,9 @@
       <c r="AZ23" s="88"/>
     </row>
     <row r="24" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="247"/>
-      <c r="B24" s="248"/>
-      <c r="C24" s="248"/>
+      <c r="A24" s="250"/>
+      <c r="B24" s="251"/>
+      <c r="C24" s="251"/>
       <c r="D24" s="10"/>
       <c r="E24" s="87"/>
       <c r="F24" s="87"/>
@@ -11083,9 +11097,9 @@
       <c r="AZ24" s="88"/>
     </row>
     <row r="25" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="247"/>
-      <c r="B25" s="248"/>
-      <c r="C25" s="248"/>
+      <c r="A25" s="250"/>
+      <c r="B25" s="251"/>
+      <c r="C25" s="251"/>
       <c r="D25" s="10"/>
       <c r="E25" s="86"/>
       <c r="F25" s="87"/>
@@ -11137,922 +11151,922 @@
       <c r="AZ25" s="88"/>
     </row>
     <row r="26" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="247"/>
-      <c r="B26" s="248"/>
-      <c r="C26" s="248"/>
+      <c r="A26" s="250"/>
+      <c r="B26" s="251"/>
+      <c r="C26" s="251"/>
       <c r="D26" s="10"/>
-      <c r="E26" s="256"/>
-      <c r="F26" s="256"/>
-      <c r="G26" s="256"/>
-      <c r="H26" s="256"/>
-      <c r="I26" s="256"/>
-      <c r="J26" s="256"/>
-      <c r="K26" s="256"/>
-      <c r="L26" s="256"/>
-      <c r="M26" s="256"/>
-      <c r="N26" s="256"/>
-      <c r="O26" s="256"/>
-      <c r="P26" s="256"/>
-      <c r="Q26" s="256"/>
-      <c r="R26" s="256"/>
-      <c r="S26" s="256"/>
-      <c r="T26" s="256"/>
-      <c r="U26" s="256"/>
-      <c r="V26" s="256"/>
-      <c r="W26" s="256"/>
-      <c r="X26" s="256"/>
-      <c r="Y26" s="256"/>
-      <c r="Z26" s="256"/>
-      <c r="AA26" s="256"/>
-      <c r="AB26" s="256"/>
-      <c r="AC26" s="256"/>
-      <c r="AD26" s="256"/>
-      <c r="AE26" s="256"/>
-      <c r="AF26" s="256"/>
-      <c r="AG26" s="256"/>
-      <c r="AH26" s="256"/>
-      <c r="AI26" s="256"/>
-      <c r="AJ26" s="256"/>
-      <c r="AK26" s="256"/>
-      <c r="AL26" s="256"/>
-      <c r="AM26" s="256"/>
-      <c r="AN26" s="256"/>
-      <c r="AO26" s="256"/>
-      <c r="AP26" s="256"/>
-      <c r="AQ26" s="256"/>
-      <c r="AR26" s="256"/>
-      <c r="AS26" s="256"/>
-      <c r="AT26" s="256"/>
-      <c r="AU26" s="256"/>
-      <c r="AV26" s="256"/>
-      <c r="AW26" s="256"/>
-      <c r="AX26" s="256"/>
-      <c r="AY26" s="256"/>
-      <c r="AZ26" s="257"/>
+      <c r="E26" s="245"/>
+      <c r="F26" s="245"/>
+      <c r="G26" s="245"/>
+      <c r="H26" s="245"/>
+      <c r="I26" s="245"/>
+      <c r="J26" s="245"/>
+      <c r="K26" s="245"/>
+      <c r="L26" s="245"/>
+      <c r="M26" s="245"/>
+      <c r="N26" s="245"/>
+      <c r="O26" s="245"/>
+      <c r="P26" s="245"/>
+      <c r="Q26" s="245"/>
+      <c r="R26" s="245"/>
+      <c r="S26" s="245"/>
+      <c r="T26" s="245"/>
+      <c r="U26" s="245"/>
+      <c r="V26" s="245"/>
+      <c r="W26" s="245"/>
+      <c r="X26" s="245"/>
+      <c r="Y26" s="245"/>
+      <c r="Z26" s="245"/>
+      <c r="AA26" s="245"/>
+      <c r="AB26" s="245"/>
+      <c r="AC26" s="245"/>
+      <c r="AD26" s="245"/>
+      <c r="AE26" s="245"/>
+      <c r="AF26" s="245"/>
+      <c r="AG26" s="245"/>
+      <c r="AH26" s="245"/>
+      <c r="AI26" s="245"/>
+      <c r="AJ26" s="245"/>
+      <c r="AK26" s="245"/>
+      <c r="AL26" s="245"/>
+      <c r="AM26" s="245"/>
+      <c r="AN26" s="245"/>
+      <c r="AO26" s="245"/>
+      <c r="AP26" s="245"/>
+      <c r="AQ26" s="245"/>
+      <c r="AR26" s="245"/>
+      <c r="AS26" s="245"/>
+      <c r="AT26" s="245"/>
+      <c r="AU26" s="245"/>
+      <c r="AV26" s="245"/>
+      <c r="AW26" s="245"/>
+      <c r="AX26" s="245"/>
+      <c r="AY26" s="245"/>
+      <c r="AZ26" s="246"/>
     </row>
     <row r="27" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="247"/>
-      <c r="B27" s="248"/>
-      <c r="C27" s="248"/>
+      <c r="A27" s="250"/>
+      <c r="B27" s="251"/>
+      <c r="C27" s="251"/>
       <c r="D27" s="10"/>
-      <c r="E27" s="256"/>
-      <c r="F27" s="256"/>
-      <c r="G27" s="256"/>
-      <c r="H27" s="256"/>
-      <c r="I27" s="256"/>
-      <c r="J27" s="256"/>
-      <c r="K27" s="256"/>
-      <c r="L27" s="256"/>
-      <c r="M27" s="256"/>
-      <c r="N27" s="256"/>
-      <c r="O27" s="256"/>
-      <c r="P27" s="256"/>
-      <c r="Q27" s="256"/>
-      <c r="R27" s="256"/>
-      <c r="S27" s="256"/>
-      <c r="T27" s="256"/>
-      <c r="U27" s="256"/>
-      <c r="V27" s="256"/>
-      <c r="W27" s="256"/>
-      <c r="X27" s="256"/>
-      <c r="Y27" s="256"/>
-      <c r="Z27" s="256"/>
-      <c r="AA27" s="256"/>
-      <c r="AB27" s="256"/>
-      <c r="AC27" s="256"/>
-      <c r="AD27" s="256"/>
-      <c r="AE27" s="256"/>
-      <c r="AF27" s="256"/>
-      <c r="AG27" s="256"/>
-      <c r="AH27" s="256"/>
-      <c r="AI27" s="256"/>
-      <c r="AJ27" s="256"/>
-      <c r="AK27" s="256"/>
-      <c r="AL27" s="256"/>
-      <c r="AM27" s="256"/>
-      <c r="AN27" s="256"/>
-      <c r="AO27" s="256"/>
-      <c r="AP27" s="256"/>
-      <c r="AQ27" s="256"/>
-      <c r="AR27" s="256"/>
-      <c r="AS27" s="256"/>
-      <c r="AT27" s="256"/>
-      <c r="AU27" s="256"/>
-      <c r="AV27" s="256"/>
-      <c r="AW27" s="256"/>
-      <c r="AX27" s="256"/>
-      <c r="AY27" s="256"/>
-      <c r="AZ27" s="257"/>
+      <c r="E27" s="245"/>
+      <c r="F27" s="245"/>
+      <c r="G27" s="245"/>
+      <c r="H27" s="245"/>
+      <c r="I27" s="245"/>
+      <c r="J27" s="245"/>
+      <c r="K27" s="245"/>
+      <c r="L27" s="245"/>
+      <c r="M27" s="245"/>
+      <c r="N27" s="245"/>
+      <c r="O27" s="245"/>
+      <c r="P27" s="245"/>
+      <c r="Q27" s="245"/>
+      <c r="R27" s="245"/>
+      <c r="S27" s="245"/>
+      <c r="T27" s="245"/>
+      <c r="U27" s="245"/>
+      <c r="V27" s="245"/>
+      <c r="W27" s="245"/>
+      <c r="X27" s="245"/>
+      <c r="Y27" s="245"/>
+      <c r="Z27" s="245"/>
+      <c r="AA27" s="245"/>
+      <c r="AB27" s="245"/>
+      <c r="AC27" s="245"/>
+      <c r="AD27" s="245"/>
+      <c r="AE27" s="245"/>
+      <c r="AF27" s="245"/>
+      <c r="AG27" s="245"/>
+      <c r="AH27" s="245"/>
+      <c r="AI27" s="245"/>
+      <c r="AJ27" s="245"/>
+      <c r="AK27" s="245"/>
+      <c r="AL27" s="245"/>
+      <c r="AM27" s="245"/>
+      <c r="AN27" s="245"/>
+      <c r="AO27" s="245"/>
+      <c r="AP27" s="245"/>
+      <c r="AQ27" s="245"/>
+      <c r="AR27" s="245"/>
+      <c r="AS27" s="245"/>
+      <c r="AT27" s="245"/>
+      <c r="AU27" s="245"/>
+      <c r="AV27" s="245"/>
+      <c r="AW27" s="245"/>
+      <c r="AX27" s="245"/>
+      <c r="AY27" s="245"/>
+      <c r="AZ27" s="246"/>
     </row>
     <row r="28" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="247"/>
-      <c r="B28" s="248"/>
-      <c r="C28" s="248"/>
+      <c r="A28" s="250"/>
+      <c r="B28" s="251"/>
+      <c r="C28" s="251"/>
       <c r="D28" s="10"/>
-      <c r="E28" s="256"/>
-      <c r="F28" s="256"/>
-      <c r="G28" s="256"/>
-      <c r="H28" s="256"/>
-      <c r="I28" s="256"/>
-      <c r="J28" s="256"/>
-      <c r="K28" s="256"/>
-      <c r="L28" s="256"/>
-      <c r="M28" s="256"/>
-      <c r="N28" s="256"/>
-      <c r="O28" s="256"/>
-      <c r="P28" s="256"/>
-      <c r="Q28" s="256"/>
-      <c r="R28" s="256"/>
-      <c r="S28" s="256"/>
-      <c r="T28" s="256"/>
-      <c r="U28" s="256"/>
-      <c r="V28" s="256"/>
-      <c r="W28" s="256"/>
-      <c r="X28" s="256"/>
-      <c r="Y28" s="256"/>
-      <c r="Z28" s="256"/>
-      <c r="AA28" s="256"/>
-      <c r="AB28" s="256"/>
-      <c r="AC28" s="256"/>
-      <c r="AD28" s="256"/>
-      <c r="AE28" s="256"/>
-      <c r="AF28" s="256"/>
-      <c r="AG28" s="256"/>
-      <c r="AH28" s="256"/>
-      <c r="AI28" s="256"/>
-      <c r="AJ28" s="256"/>
-      <c r="AK28" s="256"/>
-      <c r="AL28" s="256"/>
-      <c r="AM28" s="256"/>
-      <c r="AN28" s="256"/>
-      <c r="AO28" s="256"/>
-      <c r="AP28" s="256"/>
-      <c r="AQ28" s="256"/>
-      <c r="AR28" s="256"/>
-      <c r="AS28" s="256"/>
-      <c r="AT28" s="256"/>
-      <c r="AU28" s="256"/>
-      <c r="AV28" s="256"/>
-      <c r="AW28" s="256"/>
-      <c r="AX28" s="256"/>
-      <c r="AY28" s="256"/>
-      <c r="AZ28" s="257"/>
+      <c r="E28" s="245"/>
+      <c r="F28" s="245"/>
+      <c r="G28" s="245"/>
+      <c r="H28" s="245"/>
+      <c r="I28" s="245"/>
+      <c r="J28" s="245"/>
+      <c r="K28" s="245"/>
+      <c r="L28" s="245"/>
+      <c r="M28" s="245"/>
+      <c r="N28" s="245"/>
+      <c r="O28" s="245"/>
+      <c r="P28" s="245"/>
+      <c r="Q28" s="245"/>
+      <c r="R28" s="245"/>
+      <c r="S28" s="245"/>
+      <c r="T28" s="245"/>
+      <c r="U28" s="245"/>
+      <c r="V28" s="245"/>
+      <c r="W28" s="245"/>
+      <c r="X28" s="245"/>
+      <c r="Y28" s="245"/>
+      <c r="Z28" s="245"/>
+      <c r="AA28" s="245"/>
+      <c r="AB28" s="245"/>
+      <c r="AC28" s="245"/>
+      <c r="AD28" s="245"/>
+      <c r="AE28" s="245"/>
+      <c r="AF28" s="245"/>
+      <c r="AG28" s="245"/>
+      <c r="AH28" s="245"/>
+      <c r="AI28" s="245"/>
+      <c r="AJ28" s="245"/>
+      <c r="AK28" s="245"/>
+      <c r="AL28" s="245"/>
+      <c r="AM28" s="245"/>
+      <c r="AN28" s="245"/>
+      <c r="AO28" s="245"/>
+      <c r="AP28" s="245"/>
+      <c r="AQ28" s="245"/>
+      <c r="AR28" s="245"/>
+      <c r="AS28" s="245"/>
+      <c r="AT28" s="245"/>
+      <c r="AU28" s="245"/>
+      <c r="AV28" s="245"/>
+      <c r="AW28" s="245"/>
+      <c r="AX28" s="245"/>
+      <c r="AY28" s="245"/>
+      <c r="AZ28" s="246"/>
     </row>
     <row r="29" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="247"/>
-      <c r="B29" s="248"/>
-      <c r="C29" s="248"/>
+      <c r="A29" s="250"/>
+      <c r="B29" s="251"/>
+      <c r="C29" s="251"/>
       <c r="D29" s="10"/>
-      <c r="E29" s="256"/>
-      <c r="F29" s="256"/>
-      <c r="G29" s="256"/>
-      <c r="H29" s="256"/>
-      <c r="I29" s="256"/>
-      <c r="J29" s="256"/>
-      <c r="K29" s="256"/>
-      <c r="L29" s="256"/>
-      <c r="M29" s="256"/>
-      <c r="N29" s="256"/>
-      <c r="O29" s="256"/>
-      <c r="P29" s="256"/>
-      <c r="Q29" s="256"/>
-      <c r="R29" s="256"/>
-      <c r="S29" s="256"/>
-      <c r="T29" s="256"/>
-      <c r="U29" s="256"/>
-      <c r="V29" s="256"/>
-      <c r="W29" s="256"/>
-      <c r="X29" s="256"/>
-      <c r="Y29" s="256"/>
-      <c r="Z29" s="256"/>
-      <c r="AA29" s="256"/>
-      <c r="AB29" s="256"/>
-      <c r="AC29" s="256"/>
-      <c r="AD29" s="256"/>
-      <c r="AE29" s="256"/>
-      <c r="AF29" s="256"/>
-      <c r="AG29" s="256"/>
-      <c r="AH29" s="256"/>
-      <c r="AI29" s="256"/>
-      <c r="AJ29" s="256"/>
-      <c r="AK29" s="256"/>
-      <c r="AL29" s="256"/>
-      <c r="AM29" s="256"/>
-      <c r="AN29" s="256"/>
-      <c r="AO29" s="256"/>
-      <c r="AP29" s="256"/>
-      <c r="AQ29" s="256"/>
-      <c r="AR29" s="256"/>
-      <c r="AS29" s="256"/>
-      <c r="AT29" s="256"/>
-      <c r="AU29" s="256"/>
-      <c r="AV29" s="256"/>
-      <c r="AW29" s="256"/>
-      <c r="AX29" s="256"/>
-      <c r="AY29" s="256"/>
-      <c r="AZ29" s="257"/>
+      <c r="E29" s="245"/>
+      <c r="F29" s="245"/>
+      <c r="G29" s="245"/>
+      <c r="H29" s="245"/>
+      <c r="I29" s="245"/>
+      <c r="J29" s="245"/>
+      <c r="K29" s="245"/>
+      <c r="L29" s="245"/>
+      <c r="M29" s="245"/>
+      <c r="N29" s="245"/>
+      <c r="O29" s="245"/>
+      <c r="P29" s="245"/>
+      <c r="Q29" s="245"/>
+      <c r="R29" s="245"/>
+      <c r="S29" s="245"/>
+      <c r="T29" s="245"/>
+      <c r="U29" s="245"/>
+      <c r="V29" s="245"/>
+      <c r="W29" s="245"/>
+      <c r="X29" s="245"/>
+      <c r="Y29" s="245"/>
+      <c r="Z29" s="245"/>
+      <c r="AA29" s="245"/>
+      <c r="AB29" s="245"/>
+      <c r="AC29" s="245"/>
+      <c r="AD29" s="245"/>
+      <c r="AE29" s="245"/>
+      <c r="AF29" s="245"/>
+      <c r="AG29" s="245"/>
+      <c r="AH29" s="245"/>
+      <c r="AI29" s="245"/>
+      <c r="AJ29" s="245"/>
+      <c r="AK29" s="245"/>
+      <c r="AL29" s="245"/>
+      <c r="AM29" s="245"/>
+      <c r="AN29" s="245"/>
+      <c r="AO29" s="245"/>
+      <c r="AP29" s="245"/>
+      <c r="AQ29" s="245"/>
+      <c r="AR29" s="245"/>
+      <c r="AS29" s="245"/>
+      <c r="AT29" s="245"/>
+      <c r="AU29" s="245"/>
+      <c r="AV29" s="245"/>
+      <c r="AW29" s="245"/>
+      <c r="AX29" s="245"/>
+      <c r="AY29" s="245"/>
+      <c r="AZ29" s="246"/>
     </row>
     <row r="30" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="247"/>
-      <c r="B30" s="248"/>
-      <c r="C30" s="248"/>
+      <c r="A30" s="250"/>
+      <c r="B30" s="251"/>
+      <c r="C30" s="251"/>
       <c r="D30" s="10"/>
-      <c r="E30" s="256"/>
-      <c r="F30" s="256"/>
-      <c r="G30" s="256"/>
-      <c r="H30" s="256"/>
-      <c r="I30" s="256"/>
-      <c r="J30" s="256"/>
-      <c r="K30" s="256"/>
-      <c r="L30" s="256"/>
-      <c r="M30" s="256"/>
-      <c r="N30" s="256"/>
-      <c r="O30" s="256"/>
-      <c r="P30" s="256"/>
-      <c r="Q30" s="256"/>
-      <c r="R30" s="256"/>
-      <c r="S30" s="256"/>
-      <c r="T30" s="256"/>
-      <c r="U30" s="256"/>
-      <c r="V30" s="256"/>
-      <c r="W30" s="256"/>
-      <c r="X30" s="256"/>
-      <c r="Y30" s="256"/>
-      <c r="Z30" s="256"/>
-      <c r="AA30" s="256"/>
-      <c r="AB30" s="256"/>
-      <c r="AC30" s="256"/>
-      <c r="AD30" s="256"/>
-      <c r="AE30" s="256"/>
-      <c r="AF30" s="256"/>
-      <c r="AG30" s="256"/>
-      <c r="AH30" s="256"/>
-      <c r="AI30" s="256"/>
-      <c r="AJ30" s="256"/>
-      <c r="AK30" s="256"/>
-      <c r="AL30" s="256"/>
-      <c r="AM30" s="256"/>
-      <c r="AN30" s="256"/>
-      <c r="AO30" s="256"/>
-      <c r="AP30" s="256"/>
-      <c r="AQ30" s="256"/>
-      <c r="AR30" s="256"/>
-      <c r="AS30" s="256"/>
-      <c r="AT30" s="256"/>
-      <c r="AU30" s="256"/>
-      <c r="AV30" s="256"/>
-      <c r="AW30" s="256"/>
-      <c r="AX30" s="256"/>
-      <c r="AY30" s="256"/>
-      <c r="AZ30" s="257"/>
+      <c r="E30" s="245"/>
+      <c r="F30" s="245"/>
+      <c r="G30" s="245"/>
+      <c r="H30" s="245"/>
+      <c r="I30" s="245"/>
+      <c r="J30" s="245"/>
+      <c r="K30" s="245"/>
+      <c r="L30" s="245"/>
+      <c r="M30" s="245"/>
+      <c r="N30" s="245"/>
+      <c r="O30" s="245"/>
+      <c r="P30" s="245"/>
+      <c r="Q30" s="245"/>
+      <c r="R30" s="245"/>
+      <c r="S30" s="245"/>
+      <c r="T30" s="245"/>
+      <c r="U30" s="245"/>
+      <c r="V30" s="245"/>
+      <c r="W30" s="245"/>
+      <c r="X30" s="245"/>
+      <c r="Y30" s="245"/>
+      <c r="Z30" s="245"/>
+      <c r="AA30" s="245"/>
+      <c r="AB30" s="245"/>
+      <c r="AC30" s="245"/>
+      <c r="AD30" s="245"/>
+      <c r="AE30" s="245"/>
+      <c r="AF30" s="245"/>
+      <c r="AG30" s="245"/>
+      <c r="AH30" s="245"/>
+      <c r="AI30" s="245"/>
+      <c r="AJ30" s="245"/>
+      <c r="AK30" s="245"/>
+      <c r="AL30" s="245"/>
+      <c r="AM30" s="245"/>
+      <c r="AN30" s="245"/>
+      <c r="AO30" s="245"/>
+      <c r="AP30" s="245"/>
+      <c r="AQ30" s="245"/>
+      <c r="AR30" s="245"/>
+      <c r="AS30" s="245"/>
+      <c r="AT30" s="245"/>
+      <c r="AU30" s="245"/>
+      <c r="AV30" s="245"/>
+      <c r="AW30" s="245"/>
+      <c r="AX30" s="245"/>
+      <c r="AY30" s="245"/>
+      <c r="AZ30" s="246"/>
     </row>
     <row r="31" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="247"/>
-      <c r="B31" s="248"/>
-      <c r="C31" s="248"/>
+      <c r="A31" s="250"/>
+      <c r="B31" s="251"/>
+      <c r="C31" s="251"/>
       <c r="D31" s="10"/>
-      <c r="E31" s="256"/>
-      <c r="F31" s="256"/>
-      <c r="G31" s="256"/>
-      <c r="H31" s="256"/>
-      <c r="I31" s="256"/>
-      <c r="J31" s="256"/>
-      <c r="K31" s="256"/>
-      <c r="L31" s="256"/>
-      <c r="M31" s="256"/>
-      <c r="N31" s="256"/>
-      <c r="O31" s="256"/>
-      <c r="P31" s="256"/>
-      <c r="Q31" s="256"/>
-      <c r="R31" s="256"/>
-      <c r="S31" s="256"/>
-      <c r="T31" s="256"/>
-      <c r="U31" s="256"/>
-      <c r="V31" s="256"/>
-      <c r="W31" s="256"/>
-      <c r="X31" s="256"/>
-      <c r="Y31" s="256"/>
-      <c r="Z31" s="256"/>
-      <c r="AA31" s="256"/>
-      <c r="AB31" s="256"/>
-      <c r="AC31" s="256"/>
-      <c r="AD31" s="256"/>
-      <c r="AE31" s="256"/>
-      <c r="AF31" s="256"/>
-      <c r="AG31" s="256"/>
-      <c r="AH31" s="256"/>
-      <c r="AI31" s="256"/>
-      <c r="AJ31" s="256"/>
-      <c r="AK31" s="256"/>
-      <c r="AL31" s="256"/>
-      <c r="AM31" s="256"/>
-      <c r="AN31" s="256"/>
-      <c r="AO31" s="256"/>
-      <c r="AP31" s="256"/>
-      <c r="AQ31" s="256"/>
-      <c r="AR31" s="256"/>
-      <c r="AS31" s="256"/>
-      <c r="AT31" s="256"/>
-      <c r="AU31" s="256"/>
-      <c r="AV31" s="256"/>
-      <c r="AW31" s="256"/>
-      <c r="AX31" s="256"/>
-      <c r="AY31" s="256"/>
-      <c r="AZ31" s="257"/>
+      <c r="E31" s="245"/>
+      <c r="F31" s="245"/>
+      <c r="G31" s="245"/>
+      <c r="H31" s="245"/>
+      <c r="I31" s="245"/>
+      <c r="J31" s="245"/>
+      <c r="K31" s="245"/>
+      <c r="L31" s="245"/>
+      <c r="M31" s="245"/>
+      <c r="N31" s="245"/>
+      <c r="O31" s="245"/>
+      <c r="P31" s="245"/>
+      <c r="Q31" s="245"/>
+      <c r="R31" s="245"/>
+      <c r="S31" s="245"/>
+      <c r="T31" s="245"/>
+      <c r="U31" s="245"/>
+      <c r="V31" s="245"/>
+      <c r="W31" s="245"/>
+      <c r="X31" s="245"/>
+      <c r="Y31" s="245"/>
+      <c r="Z31" s="245"/>
+      <c r="AA31" s="245"/>
+      <c r="AB31" s="245"/>
+      <c r="AC31" s="245"/>
+      <c r="AD31" s="245"/>
+      <c r="AE31" s="245"/>
+      <c r="AF31" s="245"/>
+      <c r="AG31" s="245"/>
+      <c r="AH31" s="245"/>
+      <c r="AI31" s="245"/>
+      <c r="AJ31" s="245"/>
+      <c r="AK31" s="245"/>
+      <c r="AL31" s="245"/>
+      <c r="AM31" s="245"/>
+      <c r="AN31" s="245"/>
+      <c r="AO31" s="245"/>
+      <c r="AP31" s="245"/>
+      <c r="AQ31" s="245"/>
+      <c r="AR31" s="245"/>
+      <c r="AS31" s="245"/>
+      <c r="AT31" s="245"/>
+      <c r="AU31" s="245"/>
+      <c r="AV31" s="245"/>
+      <c r="AW31" s="245"/>
+      <c r="AX31" s="245"/>
+      <c r="AY31" s="245"/>
+      <c r="AZ31" s="246"/>
     </row>
     <row r="32" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="247"/>
-      <c r="B32" s="248"/>
-      <c r="C32" s="248"/>
+      <c r="A32" s="250"/>
+      <c r="B32" s="251"/>
+      <c r="C32" s="251"/>
       <c r="D32" s="10"/>
-      <c r="E32" s="256"/>
-      <c r="F32" s="256"/>
-      <c r="G32" s="256"/>
-      <c r="H32" s="256"/>
-      <c r="I32" s="256"/>
-      <c r="J32" s="256"/>
-      <c r="K32" s="256"/>
-      <c r="L32" s="256"/>
-      <c r="M32" s="256"/>
-      <c r="N32" s="256"/>
-      <c r="O32" s="256"/>
-      <c r="P32" s="256"/>
-      <c r="Q32" s="256"/>
-      <c r="R32" s="256"/>
-      <c r="S32" s="256"/>
-      <c r="T32" s="256"/>
-      <c r="U32" s="256"/>
-      <c r="V32" s="256"/>
-      <c r="W32" s="256"/>
-      <c r="X32" s="256"/>
-      <c r="Y32" s="256"/>
-      <c r="Z32" s="256"/>
-      <c r="AA32" s="256"/>
-      <c r="AB32" s="256"/>
-      <c r="AC32" s="256"/>
-      <c r="AD32" s="256"/>
-      <c r="AE32" s="256"/>
-      <c r="AF32" s="256"/>
-      <c r="AG32" s="256"/>
-      <c r="AH32" s="256"/>
-      <c r="AI32" s="256"/>
-      <c r="AJ32" s="256"/>
-      <c r="AK32" s="256"/>
-      <c r="AL32" s="256"/>
-      <c r="AM32" s="256"/>
-      <c r="AN32" s="256"/>
-      <c r="AO32" s="256"/>
-      <c r="AP32" s="256"/>
-      <c r="AQ32" s="256"/>
-      <c r="AR32" s="256"/>
-      <c r="AS32" s="256"/>
-      <c r="AT32" s="256"/>
-      <c r="AU32" s="256"/>
-      <c r="AV32" s="256"/>
-      <c r="AW32" s="256"/>
-      <c r="AX32" s="256"/>
-      <c r="AY32" s="256"/>
-      <c r="AZ32" s="257"/>
+      <c r="E32" s="245"/>
+      <c r="F32" s="245"/>
+      <c r="G32" s="245"/>
+      <c r="H32" s="245"/>
+      <c r="I32" s="245"/>
+      <c r="J32" s="245"/>
+      <c r="K32" s="245"/>
+      <c r="L32" s="245"/>
+      <c r="M32" s="245"/>
+      <c r="N32" s="245"/>
+      <c r="O32" s="245"/>
+      <c r="P32" s="245"/>
+      <c r="Q32" s="245"/>
+      <c r="R32" s="245"/>
+      <c r="S32" s="245"/>
+      <c r="T32" s="245"/>
+      <c r="U32" s="245"/>
+      <c r="V32" s="245"/>
+      <c r="W32" s="245"/>
+      <c r="X32" s="245"/>
+      <c r="Y32" s="245"/>
+      <c r="Z32" s="245"/>
+      <c r="AA32" s="245"/>
+      <c r="AB32" s="245"/>
+      <c r="AC32" s="245"/>
+      <c r="AD32" s="245"/>
+      <c r="AE32" s="245"/>
+      <c r="AF32" s="245"/>
+      <c r="AG32" s="245"/>
+      <c r="AH32" s="245"/>
+      <c r="AI32" s="245"/>
+      <c r="AJ32" s="245"/>
+      <c r="AK32" s="245"/>
+      <c r="AL32" s="245"/>
+      <c r="AM32" s="245"/>
+      <c r="AN32" s="245"/>
+      <c r="AO32" s="245"/>
+      <c r="AP32" s="245"/>
+      <c r="AQ32" s="245"/>
+      <c r="AR32" s="245"/>
+      <c r="AS32" s="245"/>
+      <c r="AT32" s="245"/>
+      <c r="AU32" s="245"/>
+      <c r="AV32" s="245"/>
+      <c r="AW32" s="245"/>
+      <c r="AX32" s="245"/>
+      <c r="AY32" s="245"/>
+      <c r="AZ32" s="246"/>
     </row>
     <row r="33" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="247"/>
-      <c r="B33" s="248"/>
-      <c r="C33" s="248"/>
+      <c r="A33" s="250"/>
+      <c r="B33" s="251"/>
+      <c r="C33" s="251"/>
       <c r="D33" s="10"/>
-      <c r="E33" s="256"/>
-      <c r="F33" s="256"/>
-      <c r="G33" s="256"/>
-      <c r="H33" s="256"/>
-      <c r="I33" s="256"/>
-      <c r="J33" s="256"/>
-      <c r="K33" s="256"/>
-      <c r="L33" s="256"/>
-      <c r="M33" s="256"/>
-      <c r="N33" s="256"/>
-      <c r="O33" s="256"/>
-      <c r="P33" s="256"/>
-      <c r="Q33" s="256"/>
-      <c r="R33" s="256"/>
-      <c r="S33" s="256"/>
-      <c r="T33" s="256"/>
-      <c r="U33" s="256"/>
-      <c r="V33" s="256"/>
-      <c r="W33" s="256"/>
-      <c r="X33" s="256"/>
-      <c r="Y33" s="256"/>
-      <c r="Z33" s="256"/>
-      <c r="AA33" s="256"/>
-      <c r="AB33" s="256"/>
-      <c r="AC33" s="256"/>
-      <c r="AD33" s="256"/>
-      <c r="AE33" s="256"/>
-      <c r="AF33" s="256"/>
-      <c r="AG33" s="256"/>
-      <c r="AH33" s="256"/>
-      <c r="AI33" s="256"/>
-      <c r="AJ33" s="256"/>
-      <c r="AK33" s="256"/>
-      <c r="AL33" s="256"/>
-      <c r="AM33" s="256"/>
-      <c r="AN33" s="256"/>
-      <c r="AO33" s="256"/>
-      <c r="AP33" s="256"/>
-      <c r="AQ33" s="256"/>
-      <c r="AR33" s="256"/>
-      <c r="AS33" s="256"/>
-      <c r="AT33" s="256"/>
-      <c r="AU33" s="256"/>
-      <c r="AV33" s="256"/>
-      <c r="AW33" s="256"/>
-      <c r="AX33" s="256"/>
-      <c r="AY33" s="256"/>
-      <c r="AZ33" s="257"/>
+      <c r="E33" s="245"/>
+      <c r="F33" s="245"/>
+      <c r="G33" s="245"/>
+      <c r="H33" s="245"/>
+      <c r="I33" s="245"/>
+      <c r="J33" s="245"/>
+      <c r="K33" s="245"/>
+      <c r="L33" s="245"/>
+      <c r="M33" s="245"/>
+      <c r="N33" s="245"/>
+      <c r="O33" s="245"/>
+      <c r="P33" s="245"/>
+      <c r="Q33" s="245"/>
+      <c r="R33" s="245"/>
+      <c r="S33" s="245"/>
+      <c r="T33" s="245"/>
+      <c r="U33" s="245"/>
+      <c r="V33" s="245"/>
+      <c r="W33" s="245"/>
+      <c r="X33" s="245"/>
+      <c r="Y33" s="245"/>
+      <c r="Z33" s="245"/>
+      <c r="AA33" s="245"/>
+      <c r="AB33" s="245"/>
+      <c r="AC33" s="245"/>
+      <c r="AD33" s="245"/>
+      <c r="AE33" s="245"/>
+      <c r="AF33" s="245"/>
+      <c r="AG33" s="245"/>
+      <c r="AH33" s="245"/>
+      <c r="AI33" s="245"/>
+      <c r="AJ33" s="245"/>
+      <c r="AK33" s="245"/>
+      <c r="AL33" s="245"/>
+      <c r="AM33" s="245"/>
+      <c r="AN33" s="245"/>
+      <c r="AO33" s="245"/>
+      <c r="AP33" s="245"/>
+      <c r="AQ33" s="245"/>
+      <c r="AR33" s="245"/>
+      <c r="AS33" s="245"/>
+      <c r="AT33" s="245"/>
+      <c r="AU33" s="245"/>
+      <c r="AV33" s="245"/>
+      <c r="AW33" s="245"/>
+      <c r="AX33" s="245"/>
+      <c r="AY33" s="245"/>
+      <c r="AZ33" s="246"/>
     </row>
     <row r="34" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="247"/>
-      <c r="B34" s="248"/>
-      <c r="C34" s="248"/>
+      <c r="A34" s="250"/>
+      <c r="B34" s="251"/>
+      <c r="C34" s="251"/>
       <c r="D34" s="10"/>
-      <c r="E34" s="256"/>
-      <c r="F34" s="256"/>
-      <c r="G34" s="256"/>
-      <c r="H34" s="256"/>
-      <c r="I34" s="256"/>
-      <c r="J34" s="256"/>
-      <c r="K34" s="256"/>
-      <c r="L34" s="256"/>
-      <c r="M34" s="256"/>
-      <c r="N34" s="256"/>
-      <c r="O34" s="256"/>
-      <c r="P34" s="256"/>
-      <c r="Q34" s="256"/>
-      <c r="R34" s="256"/>
-      <c r="S34" s="256"/>
-      <c r="T34" s="256"/>
-      <c r="U34" s="256"/>
-      <c r="V34" s="256"/>
-      <c r="W34" s="256"/>
-      <c r="X34" s="256"/>
-      <c r="Y34" s="256"/>
-      <c r="Z34" s="256"/>
-      <c r="AA34" s="256"/>
-      <c r="AB34" s="256"/>
-      <c r="AC34" s="256"/>
-      <c r="AD34" s="256"/>
-      <c r="AE34" s="256"/>
-      <c r="AF34" s="256"/>
-      <c r="AG34" s="256"/>
-      <c r="AH34" s="256"/>
-      <c r="AI34" s="256"/>
-      <c r="AJ34" s="256"/>
-      <c r="AK34" s="256"/>
-      <c r="AL34" s="256"/>
-      <c r="AM34" s="256"/>
-      <c r="AN34" s="256"/>
-      <c r="AO34" s="256"/>
-      <c r="AP34" s="256"/>
-      <c r="AQ34" s="256"/>
-      <c r="AR34" s="256"/>
-      <c r="AS34" s="256"/>
-      <c r="AT34" s="256"/>
-      <c r="AU34" s="256"/>
-      <c r="AV34" s="256"/>
-      <c r="AW34" s="256"/>
-      <c r="AX34" s="256"/>
-      <c r="AY34" s="256"/>
-      <c r="AZ34" s="257"/>
+      <c r="E34" s="245"/>
+      <c r="F34" s="245"/>
+      <c r="G34" s="245"/>
+      <c r="H34" s="245"/>
+      <c r="I34" s="245"/>
+      <c r="J34" s="245"/>
+      <c r="K34" s="245"/>
+      <c r="L34" s="245"/>
+      <c r="M34" s="245"/>
+      <c r="N34" s="245"/>
+      <c r="O34" s="245"/>
+      <c r="P34" s="245"/>
+      <c r="Q34" s="245"/>
+      <c r="R34" s="245"/>
+      <c r="S34" s="245"/>
+      <c r="T34" s="245"/>
+      <c r="U34" s="245"/>
+      <c r="V34" s="245"/>
+      <c r="W34" s="245"/>
+      <c r="X34" s="245"/>
+      <c r="Y34" s="245"/>
+      <c r="Z34" s="245"/>
+      <c r="AA34" s="245"/>
+      <c r="AB34" s="245"/>
+      <c r="AC34" s="245"/>
+      <c r="AD34" s="245"/>
+      <c r="AE34" s="245"/>
+      <c r="AF34" s="245"/>
+      <c r="AG34" s="245"/>
+      <c r="AH34" s="245"/>
+      <c r="AI34" s="245"/>
+      <c r="AJ34" s="245"/>
+      <c r="AK34" s="245"/>
+      <c r="AL34" s="245"/>
+      <c r="AM34" s="245"/>
+      <c r="AN34" s="245"/>
+      <c r="AO34" s="245"/>
+      <c r="AP34" s="245"/>
+      <c r="AQ34" s="245"/>
+      <c r="AR34" s="245"/>
+      <c r="AS34" s="245"/>
+      <c r="AT34" s="245"/>
+      <c r="AU34" s="245"/>
+      <c r="AV34" s="245"/>
+      <c r="AW34" s="245"/>
+      <c r="AX34" s="245"/>
+      <c r="AY34" s="245"/>
+      <c r="AZ34" s="246"/>
     </row>
     <row r="35" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="247"/>
-      <c r="B35" s="248"/>
-      <c r="C35" s="248"/>
+      <c r="A35" s="250"/>
+      <c r="B35" s="251"/>
+      <c r="C35" s="251"/>
       <c r="D35" s="10"/>
-      <c r="E35" s="256"/>
-      <c r="F35" s="256"/>
-      <c r="G35" s="256"/>
-      <c r="H35" s="256"/>
-      <c r="I35" s="256"/>
-      <c r="J35" s="256"/>
-      <c r="K35" s="256"/>
-      <c r="L35" s="256"/>
-      <c r="M35" s="256"/>
-      <c r="N35" s="256"/>
-      <c r="O35" s="256"/>
-      <c r="P35" s="256"/>
-      <c r="Q35" s="256"/>
-      <c r="R35" s="256"/>
-      <c r="S35" s="256"/>
-      <c r="T35" s="256"/>
-      <c r="U35" s="256"/>
-      <c r="V35" s="256"/>
-      <c r="W35" s="256"/>
-      <c r="X35" s="256"/>
-      <c r="Y35" s="256"/>
-      <c r="Z35" s="256"/>
-      <c r="AA35" s="256"/>
-      <c r="AB35" s="256"/>
-      <c r="AC35" s="256"/>
-      <c r="AD35" s="256"/>
-      <c r="AE35" s="256"/>
-      <c r="AF35" s="256"/>
-      <c r="AG35" s="256"/>
-      <c r="AH35" s="256"/>
-      <c r="AI35" s="256"/>
-      <c r="AJ35" s="256"/>
-      <c r="AK35" s="256"/>
-      <c r="AL35" s="256"/>
-      <c r="AM35" s="256"/>
-      <c r="AN35" s="256"/>
-      <c r="AO35" s="256"/>
-      <c r="AP35" s="256"/>
-      <c r="AQ35" s="256"/>
-      <c r="AR35" s="256"/>
-      <c r="AS35" s="256"/>
-      <c r="AT35" s="256"/>
-      <c r="AU35" s="256"/>
-      <c r="AV35" s="256"/>
-      <c r="AW35" s="256"/>
-      <c r="AX35" s="256"/>
-      <c r="AY35" s="256"/>
-      <c r="AZ35" s="257"/>
+      <c r="E35" s="245"/>
+      <c r="F35" s="245"/>
+      <c r="G35" s="245"/>
+      <c r="H35" s="245"/>
+      <c r="I35" s="245"/>
+      <c r="J35" s="245"/>
+      <c r="K35" s="245"/>
+      <c r="L35" s="245"/>
+      <c r="M35" s="245"/>
+      <c r="N35" s="245"/>
+      <c r="O35" s="245"/>
+      <c r="P35" s="245"/>
+      <c r="Q35" s="245"/>
+      <c r="R35" s="245"/>
+      <c r="S35" s="245"/>
+      <c r="T35" s="245"/>
+      <c r="U35" s="245"/>
+      <c r="V35" s="245"/>
+      <c r="W35" s="245"/>
+      <c r="X35" s="245"/>
+      <c r="Y35" s="245"/>
+      <c r="Z35" s="245"/>
+      <c r="AA35" s="245"/>
+      <c r="AB35" s="245"/>
+      <c r="AC35" s="245"/>
+      <c r="AD35" s="245"/>
+      <c r="AE35" s="245"/>
+      <c r="AF35" s="245"/>
+      <c r="AG35" s="245"/>
+      <c r="AH35" s="245"/>
+      <c r="AI35" s="245"/>
+      <c r="AJ35" s="245"/>
+      <c r="AK35" s="245"/>
+      <c r="AL35" s="245"/>
+      <c r="AM35" s="245"/>
+      <c r="AN35" s="245"/>
+      <c r="AO35" s="245"/>
+      <c r="AP35" s="245"/>
+      <c r="AQ35" s="245"/>
+      <c r="AR35" s="245"/>
+      <c r="AS35" s="245"/>
+      <c r="AT35" s="245"/>
+      <c r="AU35" s="245"/>
+      <c r="AV35" s="245"/>
+      <c r="AW35" s="245"/>
+      <c r="AX35" s="245"/>
+      <c r="AY35" s="245"/>
+      <c r="AZ35" s="246"/>
     </row>
     <row r="36" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="247"/>
-      <c r="B36" s="248"/>
-      <c r="C36" s="248"/>
+      <c r="A36" s="250"/>
+      <c r="B36" s="251"/>
+      <c r="C36" s="251"/>
       <c r="D36" s="10"/>
-      <c r="E36" s="256"/>
-      <c r="F36" s="256"/>
-      <c r="G36" s="256"/>
-      <c r="H36" s="256"/>
-      <c r="I36" s="256"/>
-      <c r="J36" s="256"/>
-      <c r="K36" s="256"/>
-      <c r="L36" s="256"/>
-      <c r="M36" s="256"/>
-      <c r="N36" s="256"/>
-      <c r="O36" s="256"/>
-      <c r="P36" s="256"/>
-      <c r="Q36" s="256"/>
-      <c r="R36" s="256"/>
-      <c r="S36" s="256"/>
-      <c r="T36" s="256"/>
-      <c r="U36" s="256"/>
-      <c r="V36" s="256"/>
-      <c r="W36" s="256"/>
-      <c r="X36" s="256"/>
-      <c r="Y36" s="256"/>
-      <c r="Z36" s="256"/>
-      <c r="AA36" s="256"/>
-      <c r="AB36" s="256"/>
-      <c r="AC36" s="256"/>
-      <c r="AD36" s="256"/>
-      <c r="AE36" s="256"/>
-      <c r="AF36" s="256"/>
-      <c r="AG36" s="256"/>
-      <c r="AH36" s="256"/>
-      <c r="AI36" s="256"/>
-      <c r="AJ36" s="256"/>
-      <c r="AK36" s="256"/>
-      <c r="AL36" s="256"/>
-      <c r="AM36" s="256"/>
-      <c r="AN36" s="256"/>
-      <c r="AO36" s="256"/>
-      <c r="AP36" s="256"/>
-      <c r="AQ36" s="256"/>
-      <c r="AR36" s="256"/>
-      <c r="AS36" s="256"/>
-      <c r="AT36" s="256"/>
-      <c r="AU36" s="256"/>
-      <c r="AV36" s="256"/>
-      <c r="AW36" s="256"/>
-      <c r="AX36" s="256"/>
-      <c r="AY36" s="256"/>
-      <c r="AZ36" s="257"/>
+      <c r="E36" s="245"/>
+      <c r="F36" s="245"/>
+      <c r="G36" s="245"/>
+      <c r="H36" s="245"/>
+      <c r="I36" s="245"/>
+      <c r="J36" s="245"/>
+      <c r="K36" s="245"/>
+      <c r="L36" s="245"/>
+      <c r="M36" s="245"/>
+      <c r="N36" s="245"/>
+      <c r="O36" s="245"/>
+      <c r="P36" s="245"/>
+      <c r="Q36" s="245"/>
+      <c r="R36" s="245"/>
+      <c r="S36" s="245"/>
+      <c r="T36" s="245"/>
+      <c r="U36" s="245"/>
+      <c r="V36" s="245"/>
+      <c r="W36" s="245"/>
+      <c r="X36" s="245"/>
+      <c r="Y36" s="245"/>
+      <c r="Z36" s="245"/>
+      <c r="AA36" s="245"/>
+      <c r="AB36" s="245"/>
+      <c r="AC36" s="245"/>
+      <c r="AD36" s="245"/>
+      <c r="AE36" s="245"/>
+      <c r="AF36" s="245"/>
+      <c r="AG36" s="245"/>
+      <c r="AH36" s="245"/>
+      <c r="AI36" s="245"/>
+      <c r="AJ36" s="245"/>
+      <c r="AK36" s="245"/>
+      <c r="AL36" s="245"/>
+      <c r="AM36" s="245"/>
+      <c r="AN36" s="245"/>
+      <c r="AO36" s="245"/>
+      <c r="AP36" s="245"/>
+      <c r="AQ36" s="245"/>
+      <c r="AR36" s="245"/>
+      <c r="AS36" s="245"/>
+      <c r="AT36" s="245"/>
+      <c r="AU36" s="245"/>
+      <c r="AV36" s="245"/>
+      <c r="AW36" s="245"/>
+      <c r="AX36" s="245"/>
+      <c r="AY36" s="245"/>
+      <c r="AZ36" s="246"/>
     </row>
     <row r="37" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="247"/>
-      <c r="B37" s="248"/>
-      <c r="C37" s="248"/>
+      <c r="A37" s="250"/>
+      <c r="B37" s="251"/>
+      <c r="C37" s="251"/>
       <c r="D37" s="10"/>
-      <c r="E37" s="256"/>
-      <c r="F37" s="256"/>
-      <c r="G37" s="256"/>
-      <c r="H37" s="256"/>
-      <c r="I37" s="256"/>
-      <c r="J37" s="256"/>
-      <c r="K37" s="256"/>
-      <c r="L37" s="256"/>
-      <c r="M37" s="256"/>
-      <c r="N37" s="256"/>
-      <c r="O37" s="256"/>
-      <c r="P37" s="256"/>
-      <c r="Q37" s="256"/>
-      <c r="R37" s="256"/>
-      <c r="S37" s="256"/>
-      <c r="T37" s="256"/>
-      <c r="U37" s="256"/>
-      <c r="V37" s="256"/>
-      <c r="W37" s="256"/>
-      <c r="X37" s="256"/>
-      <c r="Y37" s="256"/>
-      <c r="Z37" s="256"/>
-      <c r="AA37" s="256"/>
-      <c r="AB37" s="256"/>
-      <c r="AC37" s="256"/>
-      <c r="AD37" s="256"/>
-      <c r="AE37" s="256"/>
-      <c r="AF37" s="256"/>
-      <c r="AG37" s="256"/>
-      <c r="AH37" s="256"/>
-      <c r="AI37" s="256"/>
-      <c r="AJ37" s="256"/>
-      <c r="AK37" s="256"/>
-      <c r="AL37" s="256"/>
-      <c r="AM37" s="256"/>
-      <c r="AN37" s="256"/>
-      <c r="AO37" s="256"/>
-      <c r="AP37" s="256"/>
-      <c r="AQ37" s="256"/>
-      <c r="AR37" s="256"/>
-      <c r="AS37" s="256"/>
-      <c r="AT37" s="256"/>
-      <c r="AU37" s="256"/>
-      <c r="AV37" s="256"/>
-      <c r="AW37" s="256"/>
-      <c r="AX37" s="256"/>
-      <c r="AY37" s="256"/>
-      <c r="AZ37" s="257"/>
+      <c r="E37" s="245"/>
+      <c r="F37" s="245"/>
+      <c r="G37" s="245"/>
+      <c r="H37" s="245"/>
+      <c r="I37" s="245"/>
+      <c r="J37" s="245"/>
+      <c r="K37" s="245"/>
+      <c r="L37" s="245"/>
+      <c r="M37" s="245"/>
+      <c r="N37" s="245"/>
+      <c r="O37" s="245"/>
+      <c r="P37" s="245"/>
+      <c r="Q37" s="245"/>
+      <c r="R37" s="245"/>
+      <c r="S37" s="245"/>
+      <c r="T37" s="245"/>
+      <c r="U37" s="245"/>
+      <c r="V37" s="245"/>
+      <c r="W37" s="245"/>
+      <c r="X37" s="245"/>
+      <c r="Y37" s="245"/>
+      <c r="Z37" s="245"/>
+      <c r="AA37" s="245"/>
+      <c r="AB37" s="245"/>
+      <c r="AC37" s="245"/>
+      <c r="AD37" s="245"/>
+      <c r="AE37" s="245"/>
+      <c r="AF37" s="245"/>
+      <c r="AG37" s="245"/>
+      <c r="AH37" s="245"/>
+      <c r="AI37" s="245"/>
+      <c r="AJ37" s="245"/>
+      <c r="AK37" s="245"/>
+      <c r="AL37" s="245"/>
+      <c r="AM37" s="245"/>
+      <c r="AN37" s="245"/>
+      <c r="AO37" s="245"/>
+      <c r="AP37" s="245"/>
+      <c r="AQ37" s="245"/>
+      <c r="AR37" s="245"/>
+      <c r="AS37" s="245"/>
+      <c r="AT37" s="245"/>
+      <c r="AU37" s="245"/>
+      <c r="AV37" s="245"/>
+      <c r="AW37" s="245"/>
+      <c r="AX37" s="245"/>
+      <c r="AY37" s="245"/>
+      <c r="AZ37" s="246"/>
     </row>
     <row r="38" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="247"/>
-      <c r="B38" s="248"/>
-      <c r="C38" s="248"/>
+      <c r="A38" s="250"/>
+      <c r="B38" s="251"/>
+      <c r="C38" s="251"/>
       <c r="D38" s="10"/>
-      <c r="E38" s="256"/>
-      <c r="F38" s="256"/>
-      <c r="G38" s="256"/>
-      <c r="H38" s="256"/>
-      <c r="I38" s="256"/>
-      <c r="J38" s="256"/>
-      <c r="K38" s="256"/>
-      <c r="L38" s="256"/>
-      <c r="M38" s="256"/>
-      <c r="N38" s="256"/>
-      <c r="O38" s="256"/>
-      <c r="P38" s="256"/>
-      <c r="Q38" s="256"/>
-      <c r="R38" s="256"/>
-      <c r="S38" s="256"/>
-      <c r="T38" s="256"/>
-      <c r="U38" s="256"/>
-      <c r="V38" s="256"/>
-      <c r="W38" s="256"/>
-      <c r="X38" s="256"/>
-      <c r="Y38" s="256"/>
-      <c r="Z38" s="256"/>
-      <c r="AA38" s="256"/>
-      <c r="AB38" s="256"/>
-      <c r="AC38" s="256"/>
-      <c r="AD38" s="256"/>
-      <c r="AE38" s="256"/>
-      <c r="AF38" s="256"/>
-      <c r="AG38" s="256"/>
-      <c r="AH38" s="256"/>
-      <c r="AI38" s="256"/>
-      <c r="AJ38" s="256"/>
-      <c r="AK38" s="256"/>
-      <c r="AL38" s="256"/>
-      <c r="AM38" s="256"/>
-      <c r="AN38" s="256"/>
-      <c r="AO38" s="256"/>
-      <c r="AP38" s="256"/>
-      <c r="AQ38" s="256"/>
-      <c r="AR38" s="256"/>
-      <c r="AS38" s="256"/>
-      <c r="AT38" s="256"/>
-      <c r="AU38" s="256"/>
-      <c r="AV38" s="256"/>
-      <c r="AW38" s="256"/>
-      <c r="AX38" s="256"/>
-      <c r="AY38" s="256"/>
-      <c r="AZ38" s="257"/>
+      <c r="E38" s="245"/>
+      <c r="F38" s="245"/>
+      <c r="G38" s="245"/>
+      <c r="H38" s="245"/>
+      <c r="I38" s="245"/>
+      <c r="J38" s="245"/>
+      <c r="K38" s="245"/>
+      <c r="L38" s="245"/>
+      <c r="M38" s="245"/>
+      <c r="N38" s="245"/>
+      <c r="O38" s="245"/>
+      <c r="P38" s="245"/>
+      <c r="Q38" s="245"/>
+      <c r="R38" s="245"/>
+      <c r="S38" s="245"/>
+      <c r="T38" s="245"/>
+      <c r="U38" s="245"/>
+      <c r="V38" s="245"/>
+      <c r="W38" s="245"/>
+      <c r="X38" s="245"/>
+      <c r="Y38" s="245"/>
+      <c r="Z38" s="245"/>
+      <c r="AA38" s="245"/>
+      <c r="AB38" s="245"/>
+      <c r="AC38" s="245"/>
+      <c r="AD38" s="245"/>
+      <c r="AE38" s="245"/>
+      <c r="AF38" s="245"/>
+      <c r="AG38" s="245"/>
+      <c r="AH38" s="245"/>
+      <c r="AI38" s="245"/>
+      <c r="AJ38" s="245"/>
+      <c r="AK38" s="245"/>
+      <c r="AL38" s="245"/>
+      <c r="AM38" s="245"/>
+      <c r="AN38" s="245"/>
+      <c r="AO38" s="245"/>
+      <c r="AP38" s="245"/>
+      <c r="AQ38" s="245"/>
+      <c r="AR38" s="245"/>
+      <c r="AS38" s="245"/>
+      <c r="AT38" s="245"/>
+      <c r="AU38" s="245"/>
+      <c r="AV38" s="245"/>
+      <c r="AW38" s="245"/>
+      <c r="AX38" s="245"/>
+      <c r="AY38" s="245"/>
+      <c r="AZ38" s="246"/>
     </row>
     <row r="39" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="247"/>
-      <c r="B39" s="248"/>
-      <c r="C39" s="248"/>
+      <c r="A39" s="250"/>
+      <c r="B39" s="251"/>
+      <c r="C39" s="251"/>
       <c r="D39" s="10"/>
-      <c r="E39" s="256"/>
-      <c r="F39" s="256"/>
-      <c r="G39" s="256"/>
-      <c r="H39" s="256"/>
-      <c r="I39" s="256"/>
-      <c r="J39" s="256"/>
-      <c r="K39" s="256"/>
-      <c r="L39" s="256"/>
-      <c r="M39" s="256"/>
-      <c r="N39" s="256"/>
-      <c r="O39" s="256"/>
-      <c r="P39" s="256"/>
-      <c r="Q39" s="256"/>
-      <c r="R39" s="256"/>
-      <c r="S39" s="256"/>
-      <c r="T39" s="256"/>
-      <c r="U39" s="256"/>
-      <c r="V39" s="256"/>
-      <c r="W39" s="256"/>
-      <c r="X39" s="256"/>
-      <c r="Y39" s="256"/>
-      <c r="Z39" s="256"/>
-      <c r="AA39" s="256"/>
-      <c r="AB39" s="256"/>
-      <c r="AC39" s="256"/>
-      <c r="AD39" s="256"/>
-      <c r="AE39" s="256"/>
-      <c r="AF39" s="256"/>
-      <c r="AG39" s="256"/>
-      <c r="AH39" s="256"/>
-      <c r="AI39" s="256"/>
-      <c r="AJ39" s="256"/>
-      <c r="AK39" s="256"/>
-      <c r="AL39" s="256"/>
-      <c r="AM39" s="256"/>
-      <c r="AN39" s="256"/>
-      <c r="AO39" s="256"/>
-      <c r="AP39" s="256"/>
-      <c r="AQ39" s="256"/>
-      <c r="AR39" s="256"/>
-      <c r="AS39" s="256"/>
-      <c r="AT39" s="256"/>
-      <c r="AU39" s="256"/>
-      <c r="AV39" s="256"/>
-      <c r="AW39" s="256"/>
-      <c r="AX39" s="256"/>
-      <c r="AY39" s="256"/>
-      <c r="AZ39" s="257"/>
+      <c r="E39" s="245"/>
+      <c r="F39" s="245"/>
+      <c r="G39" s="245"/>
+      <c r="H39" s="245"/>
+      <c r="I39" s="245"/>
+      <c r="J39" s="245"/>
+      <c r="K39" s="245"/>
+      <c r="L39" s="245"/>
+      <c r="M39" s="245"/>
+      <c r="N39" s="245"/>
+      <c r="O39" s="245"/>
+      <c r="P39" s="245"/>
+      <c r="Q39" s="245"/>
+      <c r="R39" s="245"/>
+      <c r="S39" s="245"/>
+      <c r="T39" s="245"/>
+      <c r="U39" s="245"/>
+      <c r="V39" s="245"/>
+      <c r="W39" s="245"/>
+      <c r="X39" s="245"/>
+      <c r="Y39" s="245"/>
+      <c r="Z39" s="245"/>
+      <c r="AA39" s="245"/>
+      <c r="AB39" s="245"/>
+      <c r="AC39" s="245"/>
+      <c r="AD39" s="245"/>
+      <c r="AE39" s="245"/>
+      <c r="AF39" s="245"/>
+      <c r="AG39" s="245"/>
+      <c r="AH39" s="245"/>
+      <c r="AI39" s="245"/>
+      <c r="AJ39" s="245"/>
+      <c r="AK39" s="245"/>
+      <c r="AL39" s="245"/>
+      <c r="AM39" s="245"/>
+      <c r="AN39" s="245"/>
+      <c r="AO39" s="245"/>
+      <c r="AP39" s="245"/>
+      <c r="AQ39" s="245"/>
+      <c r="AR39" s="245"/>
+      <c r="AS39" s="245"/>
+      <c r="AT39" s="245"/>
+      <c r="AU39" s="245"/>
+      <c r="AV39" s="245"/>
+      <c r="AW39" s="245"/>
+      <c r="AX39" s="245"/>
+      <c r="AY39" s="245"/>
+      <c r="AZ39" s="246"/>
     </row>
     <row r="40" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="247"/>
-      <c r="B40" s="248"/>
-      <c r="C40" s="248"/>
+      <c r="A40" s="250"/>
+      <c r="B40" s="251"/>
+      <c r="C40" s="251"/>
       <c r="D40" s="10"/>
-      <c r="E40" s="256"/>
-      <c r="F40" s="256"/>
-      <c r="G40" s="256"/>
-      <c r="H40" s="256"/>
-      <c r="I40" s="256"/>
-      <c r="J40" s="256"/>
-      <c r="K40" s="256"/>
-      <c r="L40" s="256"/>
-      <c r="M40" s="256"/>
-      <c r="N40" s="256"/>
-      <c r="O40" s="256"/>
-      <c r="P40" s="256"/>
-      <c r="Q40" s="256"/>
-      <c r="R40" s="256"/>
-      <c r="S40" s="256"/>
-      <c r="T40" s="256"/>
-      <c r="U40" s="256"/>
-      <c r="V40" s="256"/>
-      <c r="W40" s="256"/>
-      <c r="X40" s="256"/>
-      <c r="Y40" s="256"/>
-      <c r="Z40" s="256"/>
-      <c r="AA40" s="256"/>
-      <c r="AB40" s="256"/>
-      <c r="AC40" s="256"/>
-      <c r="AD40" s="256"/>
-      <c r="AE40" s="256"/>
-      <c r="AF40" s="256"/>
-      <c r="AG40" s="256"/>
-      <c r="AH40" s="256"/>
-      <c r="AI40" s="256"/>
-      <c r="AJ40" s="256"/>
-      <c r="AK40" s="256"/>
-      <c r="AL40" s="256"/>
-      <c r="AM40" s="256"/>
-      <c r="AN40" s="256"/>
-      <c r="AO40" s="256"/>
-      <c r="AP40" s="256"/>
-      <c r="AQ40" s="256"/>
-      <c r="AR40" s="256"/>
-      <c r="AS40" s="256"/>
-      <c r="AT40" s="256"/>
-      <c r="AU40" s="256"/>
-      <c r="AV40" s="256"/>
-      <c r="AW40" s="256"/>
-      <c r="AX40" s="256"/>
-      <c r="AY40" s="256"/>
-      <c r="AZ40" s="257"/>
+      <c r="E40" s="245"/>
+      <c r="F40" s="245"/>
+      <c r="G40" s="245"/>
+      <c r="H40" s="245"/>
+      <c r="I40" s="245"/>
+      <c r="J40" s="245"/>
+      <c r="K40" s="245"/>
+      <c r="L40" s="245"/>
+      <c r="M40" s="245"/>
+      <c r="N40" s="245"/>
+      <c r="O40" s="245"/>
+      <c r="P40" s="245"/>
+      <c r="Q40" s="245"/>
+      <c r="R40" s="245"/>
+      <c r="S40" s="245"/>
+      <c r="T40" s="245"/>
+      <c r="U40" s="245"/>
+      <c r="V40" s="245"/>
+      <c r="W40" s="245"/>
+      <c r="X40" s="245"/>
+      <c r="Y40" s="245"/>
+      <c r="Z40" s="245"/>
+      <c r="AA40" s="245"/>
+      <c r="AB40" s="245"/>
+      <c r="AC40" s="245"/>
+      <c r="AD40" s="245"/>
+      <c r="AE40" s="245"/>
+      <c r="AF40" s="245"/>
+      <c r="AG40" s="245"/>
+      <c r="AH40" s="245"/>
+      <c r="AI40" s="245"/>
+      <c r="AJ40" s="245"/>
+      <c r="AK40" s="245"/>
+      <c r="AL40" s="245"/>
+      <c r="AM40" s="245"/>
+      <c r="AN40" s="245"/>
+      <c r="AO40" s="245"/>
+      <c r="AP40" s="245"/>
+      <c r="AQ40" s="245"/>
+      <c r="AR40" s="245"/>
+      <c r="AS40" s="245"/>
+      <c r="AT40" s="245"/>
+      <c r="AU40" s="245"/>
+      <c r="AV40" s="245"/>
+      <c r="AW40" s="245"/>
+      <c r="AX40" s="245"/>
+      <c r="AY40" s="245"/>
+      <c r="AZ40" s="246"/>
     </row>
     <row r="41" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="247"/>
-      <c r="B41" s="248"/>
-      <c r="C41" s="248"/>
+      <c r="A41" s="250"/>
+      <c r="B41" s="251"/>
+      <c r="C41" s="251"/>
       <c r="D41" s="10"/>
-      <c r="E41" s="256"/>
-      <c r="F41" s="256"/>
-      <c r="G41" s="256"/>
-      <c r="H41" s="256"/>
-      <c r="I41" s="256"/>
-      <c r="J41" s="256"/>
-      <c r="K41" s="256"/>
-      <c r="L41" s="256"/>
-      <c r="M41" s="256"/>
-      <c r="N41" s="256"/>
-      <c r="O41" s="256"/>
-      <c r="P41" s="256"/>
-      <c r="Q41" s="256"/>
-      <c r="R41" s="256"/>
-      <c r="S41" s="256"/>
-      <c r="T41" s="256"/>
-      <c r="U41" s="256"/>
-      <c r="V41" s="256"/>
-      <c r="W41" s="256"/>
-      <c r="X41" s="256"/>
-      <c r="Y41" s="256"/>
-      <c r="Z41" s="256"/>
-      <c r="AA41" s="256"/>
-      <c r="AB41" s="256"/>
-      <c r="AC41" s="256"/>
-      <c r="AD41" s="256"/>
-      <c r="AE41" s="256"/>
-      <c r="AF41" s="256"/>
-      <c r="AG41" s="256"/>
-      <c r="AH41" s="256"/>
-      <c r="AI41" s="256"/>
-      <c r="AJ41" s="256"/>
-      <c r="AK41" s="256"/>
-      <c r="AL41" s="256"/>
-      <c r="AM41" s="256"/>
-      <c r="AN41" s="256"/>
-      <c r="AO41" s="256"/>
-      <c r="AP41" s="256"/>
-      <c r="AQ41" s="256"/>
-      <c r="AR41" s="256"/>
-      <c r="AS41" s="256"/>
-      <c r="AT41" s="256"/>
-      <c r="AU41" s="256"/>
-      <c r="AV41" s="256"/>
-      <c r="AW41" s="256"/>
-      <c r="AX41" s="256"/>
-      <c r="AY41" s="256"/>
-      <c r="AZ41" s="257"/>
+      <c r="E41" s="245"/>
+      <c r="F41" s="245"/>
+      <c r="G41" s="245"/>
+      <c r="H41" s="245"/>
+      <c r="I41" s="245"/>
+      <c r="J41" s="245"/>
+      <c r="K41" s="245"/>
+      <c r="L41" s="245"/>
+      <c r="M41" s="245"/>
+      <c r="N41" s="245"/>
+      <c r="O41" s="245"/>
+      <c r="P41" s="245"/>
+      <c r="Q41" s="245"/>
+      <c r="R41" s="245"/>
+      <c r="S41" s="245"/>
+      <c r="T41" s="245"/>
+      <c r="U41" s="245"/>
+      <c r="V41" s="245"/>
+      <c r="W41" s="245"/>
+      <c r="X41" s="245"/>
+      <c r="Y41" s="245"/>
+      <c r="Z41" s="245"/>
+      <c r="AA41" s="245"/>
+      <c r="AB41" s="245"/>
+      <c r="AC41" s="245"/>
+      <c r="AD41" s="245"/>
+      <c r="AE41" s="245"/>
+      <c r="AF41" s="245"/>
+      <c r="AG41" s="245"/>
+      <c r="AH41" s="245"/>
+      <c r="AI41" s="245"/>
+      <c r="AJ41" s="245"/>
+      <c r="AK41" s="245"/>
+      <c r="AL41" s="245"/>
+      <c r="AM41" s="245"/>
+      <c r="AN41" s="245"/>
+      <c r="AO41" s="245"/>
+      <c r="AP41" s="245"/>
+      <c r="AQ41" s="245"/>
+      <c r="AR41" s="245"/>
+      <c r="AS41" s="245"/>
+      <c r="AT41" s="245"/>
+      <c r="AU41" s="245"/>
+      <c r="AV41" s="245"/>
+      <c r="AW41" s="245"/>
+      <c r="AX41" s="245"/>
+      <c r="AY41" s="245"/>
+      <c r="AZ41" s="246"/>
     </row>
     <row r="42" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="247"/>
-      <c r="B42" s="248"/>
-      <c r="C42" s="248"/>
+      <c r="A42" s="250"/>
+      <c r="B42" s="251"/>
+      <c r="C42" s="251"/>
       <c r="D42" s="10"/>
-      <c r="E42" s="256"/>
-      <c r="F42" s="256"/>
-      <c r="G42" s="256"/>
-      <c r="H42" s="256"/>
-      <c r="I42" s="256"/>
-      <c r="J42" s="256"/>
-      <c r="K42" s="256"/>
-      <c r="L42" s="256"/>
-      <c r="M42" s="256"/>
-      <c r="N42" s="256"/>
-      <c r="O42" s="256"/>
-      <c r="P42" s="256"/>
-      <c r="Q42" s="256"/>
-      <c r="R42" s="256"/>
-      <c r="S42" s="256"/>
-      <c r="T42" s="256"/>
-      <c r="U42" s="256"/>
-      <c r="V42" s="256"/>
-      <c r="W42" s="256"/>
-      <c r="X42" s="256"/>
-      <c r="Y42" s="256"/>
-      <c r="Z42" s="256"/>
-      <c r="AA42" s="256"/>
-      <c r="AB42" s="256"/>
-      <c r="AC42" s="256"/>
-      <c r="AD42" s="256"/>
-      <c r="AE42" s="256"/>
-      <c r="AF42" s="256"/>
-      <c r="AG42" s="256"/>
-      <c r="AH42" s="256"/>
-      <c r="AI42" s="256"/>
-      <c r="AJ42" s="256"/>
-      <c r="AK42" s="256"/>
-      <c r="AL42" s="256"/>
-      <c r="AM42" s="256"/>
-      <c r="AN42" s="256"/>
-      <c r="AO42" s="256"/>
-      <c r="AP42" s="256"/>
-      <c r="AQ42" s="256"/>
-      <c r="AR42" s="256"/>
-      <c r="AS42" s="256"/>
-      <c r="AT42" s="256"/>
-      <c r="AU42" s="256"/>
-      <c r="AV42" s="256"/>
-      <c r="AW42" s="256"/>
-      <c r="AX42" s="256"/>
-      <c r="AY42" s="256"/>
-      <c r="AZ42" s="257"/>
+      <c r="E42" s="245"/>
+      <c r="F42" s="245"/>
+      <c r="G42" s="245"/>
+      <c r="H42" s="245"/>
+      <c r="I42" s="245"/>
+      <c r="J42" s="245"/>
+      <c r="K42" s="245"/>
+      <c r="L42" s="245"/>
+      <c r="M42" s="245"/>
+      <c r="N42" s="245"/>
+      <c r="O42" s="245"/>
+      <c r="P42" s="245"/>
+      <c r="Q42" s="245"/>
+      <c r="R42" s="245"/>
+      <c r="S42" s="245"/>
+      <c r="T42" s="245"/>
+      <c r="U42" s="245"/>
+      <c r="V42" s="245"/>
+      <c r="W42" s="245"/>
+      <c r="X42" s="245"/>
+      <c r="Y42" s="245"/>
+      <c r="Z42" s="245"/>
+      <c r="AA42" s="245"/>
+      <c r="AB42" s="245"/>
+      <c r="AC42" s="245"/>
+      <c r="AD42" s="245"/>
+      <c r="AE42" s="245"/>
+      <c r="AF42" s="245"/>
+      <c r="AG42" s="245"/>
+      <c r="AH42" s="245"/>
+      <c r="AI42" s="245"/>
+      <c r="AJ42" s="245"/>
+      <c r="AK42" s="245"/>
+      <c r="AL42" s="245"/>
+      <c r="AM42" s="245"/>
+      <c r="AN42" s="245"/>
+      <c r="AO42" s="245"/>
+      <c r="AP42" s="245"/>
+      <c r="AQ42" s="245"/>
+      <c r="AR42" s="245"/>
+      <c r="AS42" s="245"/>
+      <c r="AT42" s="245"/>
+      <c r="AU42" s="245"/>
+      <c r="AV42" s="245"/>
+      <c r="AW42" s="245"/>
+      <c r="AX42" s="245"/>
+      <c r="AY42" s="245"/>
+      <c r="AZ42" s="246"/>
     </row>
     <row r="43" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="62"/>
@@ -12164,203 +12178,204 @@
       <c r="AZ44"/>
     </row>
     <row r="45" spans="1:53" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="117"/>
-      <c r="B45" s="117"/>
-      <c r="C45" s="117"/>
-      <c r="D45" s="117"/>
-      <c r="E45" s="117"/>
-      <c r="F45" s="117"/>
-      <c r="G45" s="117"/>
-      <c r="H45" s="117"/>
-      <c r="I45" s="117"/>
-      <c r="J45" s="117"/>
-      <c r="K45" s="117"/>
-      <c r="L45" s="117"/>
-      <c r="M45" s="117"/>
-      <c r="N45" s="117"/>
-      <c r="O45" s="117"/>
-      <c r="P45" s="117"/>
+      <c r="A45" s="149"/>
+      <c r="B45" s="149"/>
+      <c r="C45" s="149"/>
+      <c r="D45" s="149"/>
+      <c r="E45" s="149"/>
+      <c r="F45" s="149"/>
+      <c r="G45" s="149"/>
+      <c r="H45" s="149"/>
+      <c r="I45" s="149"/>
+      <c r="J45" s="149"/>
+      <c r="K45" s="149"/>
+      <c r="L45" s="149"/>
+      <c r="M45" s="149"/>
+      <c r="N45" s="149"/>
+      <c r="O45" s="149"/>
+      <c r="P45" s="149"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
-      <c r="S45" s="117"/>
-      <c r="T45" s="117"/>
-      <c r="U45" s="117"/>
-      <c r="V45" s="117"/>
-      <c r="W45" s="117"/>
-      <c r="X45" s="117"/>
-      <c r="Y45" s="117"/>
-      <c r="Z45" s="117"/>
-      <c r="AA45" s="117"/>
-      <c r="AB45" s="117"/>
-      <c r="AC45" s="117"/>
-      <c r="AD45" s="117"/>
-      <c r="AE45" s="117"/>
-      <c r="AF45" s="117"/>
-      <c r="AG45" s="117"/>
-      <c r="AH45" s="117"/>
+      <c r="S45" s="149"/>
+      <c r="T45" s="149"/>
+      <c r="U45" s="149"/>
+      <c r="V45" s="149"/>
+      <c r="W45" s="149"/>
+      <c r="X45" s="149"/>
+      <c r="Y45" s="149"/>
+      <c r="Z45" s="149"/>
+      <c r="AA45" s="149"/>
+      <c r="AB45" s="149"/>
+      <c r="AC45" s="149"/>
+      <c r="AD45" s="149"/>
+      <c r="AE45" s="149"/>
+      <c r="AF45" s="149"/>
+      <c r="AG45" s="149"/>
+      <c r="AH45" s="149"/>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
-      <c r="AK45" s="117"/>
-      <c r="AL45" s="117"/>
-      <c r="AM45" s="117"/>
-      <c r="AN45" s="117"/>
-      <c r="AO45" s="117"/>
-      <c r="AP45" s="117"/>
-      <c r="AQ45" s="117"/>
-      <c r="AR45" s="117"/>
-      <c r="AS45" s="117"/>
-      <c r="AT45" s="117"/>
-      <c r="AU45" s="117"/>
-      <c r="AV45" s="117"/>
-      <c r="AW45" s="117"/>
-      <c r="AX45" s="117"/>
-      <c r="AY45" s="117"/>
-      <c r="AZ45" s="117"/>
+      <c r="AK45" s="149"/>
+      <c r="AL45" s="149"/>
+      <c r="AM45" s="149"/>
+      <c r="AN45" s="149"/>
+      <c r="AO45" s="149"/>
+      <c r="AP45" s="149"/>
+      <c r="AQ45" s="149"/>
+      <c r="AR45" s="149"/>
+      <c r="AS45" s="149"/>
+      <c r="AT45" s="149"/>
+      <c r="AU45" s="149"/>
+      <c r="AV45" s="149"/>
+      <c r="AW45" s="149"/>
+      <c r="AX45" s="149"/>
+      <c r="AY45" s="149"/>
+      <c r="AZ45" s="149"/>
     </row>
     <row r="46" spans="1:53" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="118" t="s">
+      <c r="A46" s="213" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="118"/>
-      <c r="C46" s="118"/>
-      <c r="D46" s="118"/>
-      <c r="E46" s="118"/>
-      <c r="F46" s="118"/>
-      <c r="G46" s="118"/>
-      <c r="H46" s="118"/>
-      <c r="I46" s="118"/>
-      <c r="J46" s="118"/>
-      <c r="K46" s="118"/>
-      <c r="L46" s="118"/>
-      <c r="M46" s="118"/>
-      <c r="N46" s="118"/>
-      <c r="O46" s="118"/>
-      <c r="P46" s="118"/>
+      <c r="B46" s="213"/>
+      <c r="C46" s="213"/>
+      <c r="D46" s="213"/>
+      <c r="E46" s="213"/>
+      <c r="F46" s="213"/>
+      <c r="G46" s="213"/>
+      <c r="H46" s="213"/>
+      <c r="I46" s="213"/>
+      <c r="J46" s="213"/>
+      <c r="K46" s="213"/>
+      <c r="L46" s="213"/>
+      <c r="M46" s="213"/>
+      <c r="N46" s="213"/>
+      <c r="O46" s="213"/>
+      <c r="P46" s="213"/>
       <c r="Q46" s="54"/>
       <c r="R46" s="54"/>
-      <c r="S46" s="195" t="s">
+      <c r="S46" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="T46" s="195"/>
-      <c r="U46" s="195"/>
-      <c r="V46" s="195"/>
-      <c r="W46" s="195"/>
-      <c r="X46" s="195"/>
-      <c r="Y46" s="195"/>
-      <c r="Z46" s="195"/>
-      <c r="AA46" s="195"/>
-      <c r="AB46" s="195"/>
-      <c r="AC46" s="195"/>
-      <c r="AD46" s="195"/>
-      <c r="AE46" s="195"/>
-      <c r="AF46" s="195"/>
-      <c r="AG46" s="195"/>
-      <c r="AH46" s="195"/>
+      <c r="T46" s="124"/>
+      <c r="U46" s="124"/>
+      <c r="V46" s="124"/>
+      <c r="W46" s="124"/>
+      <c r="X46" s="124"/>
+      <c r="Y46" s="124"/>
+      <c r="Z46" s="124"/>
+      <c r="AA46" s="124"/>
+      <c r="AB46" s="124"/>
+      <c r="AC46" s="124"/>
+      <c r="AD46" s="124"/>
+      <c r="AE46" s="124"/>
+      <c r="AF46" s="124"/>
+      <c r="AG46" s="124"/>
+      <c r="AH46" s="124"/>
       <c r="AI46" s="54"/>
       <c r="AJ46" s="54"/>
-      <c r="AK46" s="118" t="s">
+      <c r="AK46" s="213" t="s">
         <v>79</v>
       </c>
-      <c r="AL46" s="118"/>
-      <c r="AM46" s="118"/>
-      <c r="AN46" s="118"/>
-      <c r="AO46" s="118"/>
-      <c r="AP46" s="118"/>
-      <c r="AQ46" s="118"/>
-      <c r="AR46" s="118"/>
-      <c r="AS46" s="118"/>
-      <c r="AT46" s="118"/>
-      <c r="AU46" s="118"/>
-      <c r="AV46" s="118"/>
-      <c r="AW46" s="118"/>
-      <c r="AX46" s="118"/>
-      <c r="AY46" s="118"/>
-      <c r="AZ46" s="118"/>
+      <c r="AL46" s="213"/>
+      <c r="AM46" s="213"/>
+      <c r="AN46" s="213"/>
+      <c r="AO46" s="213"/>
+      <c r="AP46" s="213"/>
+      <c r="AQ46" s="213"/>
+      <c r="AR46" s="213"/>
+      <c r="AS46" s="213"/>
+      <c r="AT46" s="213"/>
+      <c r="AU46" s="213"/>
+      <c r="AV46" s="213"/>
+      <c r="AW46" s="213"/>
+      <c r="AX46" s="213"/>
+      <c r="AY46" s="213"/>
+      <c r="AZ46" s="213"/>
     </row>
     <row r="47" spans="1:53" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="258"/>
-      <c r="B47" s="258"/>
-      <c r="C47" s="258"/>
-      <c r="D47" s="258"/>
-      <c r="E47" s="258"/>
-      <c r="F47" s="258"/>
-      <c r="G47" s="258"/>
-      <c r="H47" s="258"/>
-      <c r="I47" s="258"/>
-      <c r="J47" s="258"/>
-      <c r="K47" s="258"/>
-      <c r="L47" s="258"/>
-      <c r="M47" s="258"/>
-      <c r="N47" s="258"/>
-      <c r="O47" s="258"/>
-      <c r="P47" s="258"/>
-      <c r="S47" s="258"/>
-      <c r="T47" s="258"/>
-      <c r="U47" s="258"/>
-      <c r="V47" s="259"/>
-      <c r="W47" s="260"/>
-      <c r="X47" s="260"/>
-      <c r="Y47" s="260"/>
-      <c r="Z47" s="260"/>
-      <c r="AA47" s="260"/>
-      <c r="AB47" s="260"/>
-      <c r="AC47" s="260"/>
-      <c r="AD47" s="260"/>
-      <c r="AE47" s="260"/>
-      <c r="AF47" s="260"/>
-      <c r="AG47" s="260"/>
-      <c r="AH47" s="260"/>
-      <c r="AK47" s="119" t="s">
+      <c r="A47" s="247"/>
+      <c r="B47" s="247"/>
+      <c r="C47" s="247"/>
+      <c r="D47" s="247"/>
+      <c r="E47" s="247"/>
+      <c r="F47" s="247"/>
+      <c r="G47" s="247"/>
+      <c r="H47" s="247"/>
+      <c r="I47" s="247"/>
+      <c r="J47" s="247"/>
+      <c r="K47" s="247"/>
+      <c r="L47" s="247"/>
+      <c r="M47" s="247"/>
+      <c r="N47" s="247"/>
+      <c r="O47" s="247"/>
+      <c r="P47" s="247"/>
+      <c r="S47" s="247"/>
+      <c r="T47" s="247"/>
+      <c r="U47" s="247"/>
+      <c r="V47" s="248"/>
+      <c r="W47" s="249"/>
+      <c r="X47" s="249"/>
+      <c r="Y47" s="249"/>
+      <c r="Z47" s="249"/>
+      <c r="AA47" s="249"/>
+      <c r="AB47" s="249"/>
+      <c r="AC47" s="249"/>
+      <c r="AD47" s="249"/>
+      <c r="AE47" s="249"/>
+      <c r="AF47" s="249"/>
+      <c r="AG47" s="249"/>
+      <c r="AH47" s="249"/>
+      <c r="AK47" s="214" t="s">
         <v>792</v>
       </c>
-      <c r="AL47" s="119"/>
-      <c r="AM47" s="119"/>
-      <c r="AN47" s="119"/>
-      <c r="AO47" s="119"/>
-      <c r="AP47" s="119"/>
-      <c r="AQ47" s="119"/>
-      <c r="AR47" s="119"/>
-      <c r="AS47" s="119"/>
-      <c r="AT47" s="119"/>
-      <c r="AU47" s="119"/>
-      <c r="AV47" s="119"/>
-      <c r="AW47" s="119"/>
-      <c r="AX47" s="119"/>
-      <c r="AY47" s="119"/>
-      <c r="AZ47" s="119"/>
+      <c r="AL47" s="214"/>
+      <c r="AM47" s="214"/>
+      <c r="AN47" s="214"/>
+      <c r="AO47" s="214"/>
+      <c r="AP47" s="214"/>
+      <c r="AQ47" s="214"/>
+      <c r="AR47" s="214"/>
+      <c r="AS47" s="214"/>
+      <c r="AT47" s="214"/>
+      <c r="AU47" s="214"/>
+      <c r="AV47" s="214"/>
+      <c r="AW47" s="214"/>
+      <c r="AX47" s="214"/>
+      <c r="AY47" s="214"/>
+      <c r="AZ47" s="214"/>
     </row>
     <row r="48" spans="1:53" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="E30:AZ30"/>
-    <mergeCell ref="E31:AZ31"/>
-    <mergeCell ref="E32:AZ32"/>
-    <mergeCell ref="E26:AZ26"/>
-    <mergeCell ref="E27:AZ27"/>
-    <mergeCell ref="E28:AZ28"/>
-    <mergeCell ref="E29:AZ29"/>
-    <mergeCell ref="A46:P46"/>
-    <mergeCell ref="S46:AH46"/>
-    <mergeCell ref="AK46:AZ46"/>
-    <mergeCell ref="A47:P47"/>
-    <mergeCell ref="AK47:AZ47"/>
-    <mergeCell ref="S47:U47"/>
-    <mergeCell ref="V47:AH47"/>
-    <mergeCell ref="E42:AZ42"/>
-    <mergeCell ref="E39:AZ39"/>
-    <mergeCell ref="E40:AZ40"/>
-    <mergeCell ref="E41:AZ41"/>
-    <mergeCell ref="E38:AZ38"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A45:P45"/>
+    <mergeCell ref="S45:AH45"/>
+    <mergeCell ref="AK45:AZ45"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A4:AZ4"/>
+    <mergeCell ref="K2:AP2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="E6:AZ6"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="AS1:AZ3"/>
+    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="E9:AZ9"/>
     <mergeCell ref="A31:C31"/>
@@ -12377,34 +12392,33 @@
     <mergeCell ref="E37:AZ37"/>
     <mergeCell ref="E35:AZ35"/>
     <mergeCell ref="E36:AZ36"/>
-    <mergeCell ref="A4:AZ4"/>
-    <mergeCell ref="K2:AP2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="E6:AZ6"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="AS1:AZ3"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A45:P45"/>
-    <mergeCell ref="S45:AH45"/>
-    <mergeCell ref="AK45:AZ45"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="E42:AZ42"/>
+    <mergeCell ref="E39:AZ39"/>
+    <mergeCell ref="E40:AZ40"/>
+    <mergeCell ref="E41:AZ41"/>
+    <mergeCell ref="E38:AZ38"/>
+    <mergeCell ref="A46:P46"/>
+    <mergeCell ref="S46:AH46"/>
+    <mergeCell ref="AK46:AZ46"/>
+    <mergeCell ref="A47:P47"/>
+    <mergeCell ref="AK47:AZ47"/>
+    <mergeCell ref="S47:U47"/>
+    <mergeCell ref="V47:AH47"/>
+    <mergeCell ref="E30:AZ30"/>
+    <mergeCell ref="E31:AZ31"/>
+    <mergeCell ref="E32:AZ32"/>
+    <mergeCell ref="E26:AZ26"/>
+    <mergeCell ref="E27:AZ27"/>
+    <mergeCell ref="E28:AZ28"/>
+    <mergeCell ref="E29:AZ29"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -19455,26 +19469,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c24bca33-91ee-4c94-9d6c-305b441d02fd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e46781df-dd49-4a0f-be02-040bfbf345c5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2EBC4C97F3EED4F8F99B50CD61D9AF7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0ffa3ef56536b291ffb1e746207cdfaf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e46781df-dd49-4a0f-be02-040bfbf345c5" xmlns:ns3="c24bca33-91ee-4c94-9d6c-305b441d02fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="82d71f54c8a292e50b13588301f7fd2c" ns2:_="" ns3:_="">
     <xsd:import namespace="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
@@ -19703,10 +19697,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c24bca33-91ee-4c94-9d6c-305b441d02fd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e46781df-dd49-4a0f-be02-040bfbf345c5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA908177-54FE-4386-8E64-F855D4FAA630}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDAB891A-AABF-4B04-8872-1A9CED3578DB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
+    <ds:schemaRef ds:uri="c24bca33-91ee-4c94-9d6c-305b441d02fd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19723,20 +19748,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDAB891A-AABF-4B04-8872-1A9CED3578DB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA908177-54FE-4386-8E64-F855D4FAA630}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
-    <ds:schemaRef ds:uri="c24bca33-91ee-4c94-9d6c-305b441d02fd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/RSC 08.0000.25 - Relatório de Serviço de Campo - Padrão - Rev.38.xlsx
+++ b/RSC 08.0000.25 - Relatório de Serviço de Campo - Padrão - Rev.38.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ktsabr-my.sharepoint.com/personal/gustavo_arruda_ktsa_com_br/Documents/PROJETOS/Engenharia/RSC - Relatório de Serviço de Campo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="13_ncr:1_{F948FEA9-3545-4234-B576-12B0A63E47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1631F2B-D7C2-4F68-93A8-65A236BA8195}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{F948FEA9-3545-4234-B576-12B0A63E47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D7388F5-1249-416D-94F2-1602273A5A7B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2688,7 +2688,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="49">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -3269,21 +3269,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3295,7 +3280,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="290">
+  <cellXfs count="289">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3513,67 +3498,468 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3601,15 +3987,6 @@
     <xf numFmtId="164" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3619,397 +3996,38 @@
     <xf numFmtId="166" fontId="18" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4025,39 +4043,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4124,9 +4109,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4761,6 +4743,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -5187,14 +5173,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="170"/>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="172"/>
+      <c r="A1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="139"/>
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
       <c r="K1" s="21"/>
@@ -5231,87 +5217,87 @@
       <c r="AP1" s="22"/>
       <c r="AQ1" s="22"/>
       <c r="AR1" s="22"/>
-      <c r="AS1" s="179" t="s">
+      <c r="AS1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="AT1" s="180"/>
-      <c r="AU1" s="180"/>
-      <c r="AV1" s="180"/>
-      <c r="AW1" s="180"/>
-      <c r="AX1" s="180"/>
-      <c r="AY1" s="180"/>
-      <c r="AZ1" s="181"/>
+      <c r="AT1" s="147"/>
+      <c r="AU1" s="147"/>
+      <c r="AV1" s="147"/>
+      <c r="AW1" s="147"/>
+      <c r="AX1" s="147"/>
+      <c r="AY1" s="147"/>
+      <c r="AZ1" s="148"/>
       <c r="BD1" s="23"/>
       <c r="BF1" s="27"/>
       <c r="BG1" s="27"/>
     </row>
     <row r="2" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="173"/>
-      <c r="B2" s="174"/>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174"/>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
-      <c r="H2" s="175"/>
-      <c r="K2" s="189" t="s">
+      <c r="A2" s="140"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="142"/>
+      <c r="K2" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="190"/>
-      <c r="M2" s="190"/>
-      <c r="N2" s="190"/>
-      <c r="O2" s="190"/>
-      <c r="P2" s="190"/>
-      <c r="Q2" s="190"/>
-      <c r="R2" s="190"/>
-      <c r="S2" s="190"/>
-      <c r="T2" s="190"/>
-      <c r="U2" s="190"/>
-      <c r="V2" s="190"/>
-      <c r="W2" s="190"/>
-      <c r="X2" s="190"/>
-      <c r="Y2" s="190"/>
-      <c r="Z2" s="190"/>
-      <c r="AA2" s="190"/>
-      <c r="AB2" s="190"/>
-      <c r="AC2" s="190"/>
-      <c r="AD2" s="190"/>
-      <c r="AE2" s="190"/>
-      <c r="AF2" s="190"/>
-      <c r="AG2" s="190"/>
-      <c r="AH2" s="190"/>
-      <c r="AI2" s="190"/>
-      <c r="AJ2" s="190"/>
-      <c r="AK2" s="190"/>
-      <c r="AL2" s="190"/>
-      <c r="AM2" s="190"/>
-      <c r="AN2" s="190"/>
-      <c r="AO2" s="190"/>
-      <c r="AP2" s="190"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="157"/>
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="157"/>
+      <c r="U2" s="157"/>
+      <c r="V2" s="157"/>
+      <c r="W2" s="157"/>
+      <c r="X2" s="157"/>
+      <c r="Y2" s="157"/>
+      <c r="Z2" s="157"/>
+      <c r="AA2" s="157"/>
+      <c r="AB2" s="157"/>
+      <c r="AC2" s="157"/>
+      <c r="AD2" s="157"/>
+      <c r="AE2" s="157"/>
+      <c r="AF2" s="157"/>
+      <c r="AG2" s="157"/>
+      <c r="AH2" s="157"/>
+      <c r="AI2" s="157"/>
+      <c r="AJ2" s="157"/>
+      <c r="AK2" s="157"/>
+      <c r="AL2" s="157"/>
+      <c r="AM2" s="157"/>
+      <c r="AN2" s="157"/>
+      <c r="AO2" s="157"/>
+      <c r="AP2" s="157"/>
       <c r="AQ2" s="17"/>
       <c r="AR2" s="17"/>
-      <c r="AS2" s="182"/>
-      <c r="AT2" s="183"/>
-      <c r="AU2" s="183"/>
-      <c r="AV2" s="183"/>
-      <c r="AW2" s="183"/>
-      <c r="AX2" s="183"/>
-      <c r="AY2" s="183"/>
-      <c r="AZ2" s="184"/>
+      <c r="AS2" s="149"/>
+      <c r="AT2" s="150"/>
+      <c r="AU2" s="150"/>
+      <c r="AV2" s="150"/>
+      <c r="AW2" s="150"/>
+      <c r="AX2" s="150"/>
+      <c r="AY2" s="150"/>
+      <c r="AZ2" s="151"/>
       <c r="BA2" s="7"/>
       <c r="BF2" s="25"/>
       <c r="BG2" s="25"/>
       <c r="BH2" s="25"/>
     </row>
     <row r="3" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="176"/>
-      <c r="B3" s="177"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="177"/>
-      <c r="H3" s="178"/>
+      <c r="A3" s="143"/>
+      <c r="B3" s="144"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="145"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -5348,392 +5334,392 @@
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
       <c r="AR3" s="4"/>
-      <c r="AS3" s="185"/>
-      <c r="AT3" s="186"/>
-      <c r="AU3" s="186"/>
-      <c r="AV3" s="186"/>
-      <c r="AW3" s="186"/>
-      <c r="AX3" s="186"/>
-      <c r="AY3" s="186"/>
-      <c r="AZ3" s="187"/>
+      <c r="AS3" s="152"/>
+      <c r="AT3" s="153"/>
+      <c r="AU3" s="153"/>
+      <c r="AV3" s="153"/>
+      <c r="AW3" s="153"/>
+      <c r="AX3" s="153"/>
+      <c r="AY3" s="153"/>
+      <c r="AZ3" s="154"/>
     </row>
     <row r="4" spans="1:60" s="3" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="191" t="s">
+      <c r="A4" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="192"/>
-      <c r="C4" s="192"/>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="192"/>
-      <c r="L4" s="192"/>
-      <c r="M4" s="192"/>
-      <c r="N4" s="192"/>
-      <c r="O4" s="192"/>
-      <c r="P4" s="192"/>
-      <c r="Q4" s="192"/>
-      <c r="R4" s="192"/>
-      <c r="S4" s="192"/>
-      <c r="T4" s="192"/>
-      <c r="U4" s="192"/>
-      <c r="V4" s="192"/>
-      <c r="W4" s="192"/>
-      <c r="X4" s="192"/>
-      <c r="Y4" s="192"/>
-      <c r="Z4" s="192"/>
-      <c r="AA4" s="192"/>
-      <c r="AB4" s="192"/>
-      <c r="AC4" s="192"/>
-      <c r="AD4" s="192"/>
-      <c r="AE4" s="192"/>
-      <c r="AF4" s="192"/>
-      <c r="AG4" s="192"/>
-      <c r="AH4" s="192"/>
-      <c r="AI4" s="192"/>
-      <c r="AJ4" s="192"/>
-      <c r="AK4" s="192"/>
-      <c r="AL4" s="192"/>
-      <c r="AM4" s="192"/>
-      <c r="AN4" s="192"/>
-      <c r="AO4" s="192"/>
-      <c r="AP4" s="192"/>
-      <c r="AQ4" s="192"/>
-      <c r="AR4" s="192"/>
-      <c r="AS4" s="192"/>
-      <c r="AT4" s="192"/>
-      <c r="AU4" s="192"/>
-      <c r="AV4" s="192"/>
-      <c r="AW4" s="192"/>
-      <c r="AX4" s="192"/>
-      <c r="AY4" s="192"/>
-      <c r="AZ4" s="193"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="101"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="101"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="101"/>
+      <c r="S4" s="101"/>
+      <c r="T4" s="101"/>
+      <c r="U4" s="101"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="101"/>
+      <c r="X4" s="101"/>
+      <c r="Y4" s="101"/>
+      <c r="Z4" s="101"/>
+      <c r="AA4" s="101"/>
+      <c r="AB4" s="101"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="101"/>
+      <c r="AE4" s="101"/>
+      <c r="AF4" s="101"/>
+      <c r="AG4" s="101"/>
+      <c r="AH4" s="101"/>
+      <c r="AI4" s="101"/>
+      <c r="AJ4" s="101"/>
+      <c r="AK4" s="101"/>
+      <c r="AL4" s="101"/>
+      <c r="AM4" s="101"/>
+      <c r="AN4" s="101"/>
+      <c r="AO4" s="101"/>
+      <c r="AP4" s="101"/>
+      <c r="AQ4" s="101"/>
+      <c r="AR4" s="101"/>
+      <c r="AS4" s="101"/>
+      <c r="AT4" s="101"/>
+      <c r="AU4" s="101"/>
+      <c r="AV4" s="101"/>
+      <c r="AW4" s="101"/>
+      <c r="AX4" s="101"/>
+      <c r="AY4" s="101"/>
+      <c r="AZ4" s="102"/>
       <c r="BA4" s="9"/>
       <c r="BB4" s="9"/>
       <c r="BC4" s="9"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="197" t="s">
+      <c r="A5" s="161" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="198"/>
-      <c r="C5" s="198"/>
-      <c r="D5" s="198"/>
-      <c r="E5" s="198"/>
-      <c r="F5" s="198"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="203"/>
-      <c r="I5" s="203"/>
-      <c r="J5" s="203"/>
-      <c r="K5" s="203"/>
-      <c r="L5" s="203"/>
-      <c r="M5" s="203"/>
-      <c r="N5" s="203"/>
-      <c r="O5" s="203"/>
-      <c r="P5" s="203"/>
-      <c r="Q5" s="203"/>
-      <c r="R5" s="203"/>
-      <c r="S5" s="203"/>
-      <c r="T5" s="203"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="203"/>
-      <c r="W5" s="203"/>
-      <c r="X5" s="203"/>
-      <c r="Y5" s="203"/>
-      <c r="Z5" s="203"/>
-      <c r="AA5" s="203"/>
-      <c r="AB5" s="203"/>
+      <c r="B5" s="162"/>
+      <c r="C5" s="162"/>
+      <c r="D5" s="162"/>
+      <c r="E5" s="162"/>
+      <c r="F5" s="162"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="171"/>
+      <c r="J5" s="171"/>
+      <c r="K5" s="171"/>
+      <c r="L5" s="171"/>
+      <c r="M5" s="171"/>
+      <c r="N5" s="171"/>
+      <c r="O5" s="171"/>
+      <c r="P5" s="171"/>
+      <c r="Q5" s="171"/>
+      <c r="R5" s="171"/>
+      <c r="S5" s="171"/>
+      <c r="T5" s="171"/>
+      <c r="U5" s="171"/>
+      <c r="V5" s="171"/>
+      <c r="W5" s="171"/>
+      <c r="X5" s="171"/>
+      <c r="Y5" s="171"/>
+      <c r="Z5" s="171"/>
+      <c r="AA5" s="171"/>
+      <c r="AB5" s="171"/>
       <c r="AC5" s="55"/>
       <c r="AD5" s="58"/>
-      <c r="AE5" s="106" t="s">
+      <c r="AE5" s="170" t="s">
         <v>5</v>
       </c>
-      <c r="AF5" s="106"/>
-      <c r="AG5" s="106"/>
-      <c r="AH5" s="106"/>
-      <c r="AI5" s="106"/>
-      <c r="AJ5" s="106"/>
-      <c r="AK5" s="106"/>
-      <c r="AL5" s="210"/>
-      <c r="AM5" s="210"/>
-      <c r="AN5" s="210"/>
-      <c r="AO5" s="210"/>
-      <c r="AP5" s="210"/>
-      <c r="AQ5" s="210"/>
-      <c r="AR5" s="210"/>
-      <c r="AS5" s="210"/>
-      <c r="AT5" s="210"/>
-      <c r="AU5" s="210"/>
-      <c r="AV5" s="210"/>
-      <c r="AW5" s="210"/>
-      <c r="AX5" s="210"/>
-      <c r="AY5" s="210"/>
-      <c r="AZ5" s="211"/>
+      <c r="AF5" s="170"/>
+      <c r="AG5" s="170"/>
+      <c r="AH5" s="170"/>
+      <c r="AI5" s="170"/>
+      <c r="AJ5" s="170"/>
+      <c r="AK5" s="170"/>
+      <c r="AL5" s="181"/>
+      <c r="AM5" s="181"/>
+      <c r="AN5" s="181"/>
+      <c r="AO5" s="181"/>
+      <c r="AP5" s="181"/>
+      <c r="AQ5" s="181"/>
+      <c r="AR5" s="181"/>
+      <c r="AS5" s="181"/>
+      <c r="AT5" s="181"/>
+      <c r="AU5" s="181"/>
+      <c r="AV5" s="181"/>
+      <c r="AW5" s="181"/>
+      <c r="AX5" s="181"/>
+      <c r="AY5" s="181"/>
+      <c r="AZ5" s="182"/>
       <c r="BA5"/>
       <c r="BB5" s="9"/>
       <c r="BC5" s="9"/>
       <c r="BD5" s="9"/>
     </row>
     <row r="6" spans="1:60" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="197" t="s">
+      <c r="A6" s="161" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
-      <c r="D6" s="198"/>
-      <c r="E6" s="198"/>
-      <c r="F6" s="198"/>
-      <c r="G6" s="91" t="str">
+      <c r="B6" s="162"/>
+      <c r="C6" s="162"/>
+      <c r="D6" s="162"/>
+      <c r="E6" s="162"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="136" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,4,0))</f>
         <v/>
       </c>
-      <c r="H6" s="91"/>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
-      <c r="K6" s="91"/>
-      <c r="L6" s="91"/>
-      <c r="M6" s="91"/>
-      <c r="N6" s="91"/>
-      <c r="O6" s="91"/>
-      <c r="P6" s="91"/>
-      <c r="Q6" s="91"/>
-      <c r="R6" s="91"/>
-      <c r="S6" s="91"/>
-      <c r="T6" s="91"/>
-      <c r="U6" s="91"/>
-      <c r="V6" s="91"/>
-      <c r="W6" s="91"/>
-      <c r="X6" s="91"/>
-      <c r="Y6" s="91"/>
-      <c r="Z6" s="91"/>
-      <c r="AA6" s="91"/>
-      <c r="AB6" s="91"/>
-      <c r="AC6" s="91"/>
-      <c r="AD6" s="91"/>
-      <c r="AE6" s="91"/>
-      <c r="AF6" s="91"/>
-      <c r="AG6" s="91"/>
-      <c r="AH6" s="91"/>
-      <c r="AI6" s="91"/>
-      <c r="AJ6" s="91"/>
-      <c r="AK6" s="91"/>
-      <c r="AL6" s="91"/>
-      <c r="AM6" s="91"/>
-      <c r="AN6" s="91"/>
-      <c r="AO6" s="91"/>
-      <c r="AP6" s="91"/>
-      <c r="AQ6" s="91"/>
-      <c r="AR6" s="91"/>
-      <c r="AS6" s="91"/>
-      <c r="AT6" s="91"/>
-      <c r="AU6" s="91"/>
-      <c r="AV6" s="91"/>
-      <c r="AW6" s="91"/>
-      <c r="AX6" s="91"/>
-      <c r="AY6" s="91"/>
-      <c r="AZ6" s="188"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
+      <c r="N6" s="136"/>
+      <c r="O6" s="136"/>
+      <c r="P6" s="136"/>
+      <c r="Q6" s="136"/>
+      <c r="R6" s="136"/>
+      <c r="S6" s="136"/>
+      <c r="T6" s="136"/>
+      <c r="U6" s="136"/>
+      <c r="V6" s="136"/>
+      <c r="W6" s="136"/>
+      <c r="X6" s="136"/>
+      <c r="Y6" s="136"/>
+      <c r="Z6" s="136"/>
+      <c r="AA6" s="136"/>
+      <c r="AB6" s="136"/>
+      <c r="AC6" s="136"/>
+      <c r="AD6" s="136"/>
+      <c r="AE6" s="136"/>
+      <c r="AF6" s="136"/>
+      <c r="AG6" s="136"/>
+      <c r="AH6" s="136"/>
+      <c r="AI6" s="136"/>
+      <c r="AJ6" s="136"/>
+      <c r="AK6" s="136"/>
+      <c r="AL6" s="136"/>
+      <c r="AM6" s="136"/>
+      <c r="AN6" s="136"/>
+      <c r="AO6" s="136"/>
+      <c r="AP6" s="136"/>
+      <c r="AQ6" s="136"/>
+      <c r="AR6" s="136"/>
+      <c r="AS6" s="136"/>
+      <c r="AT6" s="136"/>
+      <c r="AU6" s="136"/>
+      <c r="AV6" s="136"/>
+      <c r="AW6" s="136"/>
+      <c r="AX6" s="136"/>
+      <c r="AY6" s="136"/>
+      <c r="AZ6" s="155"/>
     </row>
     <row r="7" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
-      <c r="D7" s="198"/>
-      <c r="E7" s="198"/>
-      <c r="F7" s="198"/>
-      <c r="G7" s="91" t="str">
+      <c r="B7" s="162"/>
+      <c r="C7" s="162"/>
+      <c r="D7" s="162"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="136" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,5,0))</f>
         <v/>
       </c>
-      <c r="H7" s="91"/>
-      <c r="I7" s="91"/>
-      <c r="J7" s="91"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="91"/>
-      <c r="N7" s="91"/>
-      <c r="O7" s="91"/>
-      <c r="P7" s="91"/>
-      <c r="Q7" s="91"/>
-      <c r="R7" s="91"/>
-      <c r="S7" s="91"/>
-      <c r="T7" s="91"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="136"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="136"/>
+      <c r="P7" s="136"/>
+      <c r="Q7" s="136"/>
+      <c r="R7" s="136"/>
+      <c r="S7" s="136"/>
+      <c r="T7" s="136"/>
       <c r="U7" s="57"/>
-      <c r="V7" s="163" t="s">
+      <c r="V7" s="176" t="s">
         <v>8</v>
       </c>
-      <c r="W7" s="163"/>
-      <c r="X7" s="163"/>
-      <c r="Y7" s="163"/>
-      <c r="Z7" s="91" t="str">
+      <c r="W7" s="176"/>
+      <c r="X7" s="176"/>
+      <c r="Y7" s="176"/>
+      <c r="Z7" s="136" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,2,0))</f>
         <v/>
       </c>
-      <c r="AA7" s="91"/>
-      <c r="AB7" s="91"/>
-      <c r="AC7" s="91"/>
-      <c r="AD7" s="91"/>
-      <c r="AE7" s="91"/>
-      <c r="AF7" s="91"/>
-      <c r="AG7" s="91"/>
-      <c r="AH7" s="91"/>
-      <c r="AI7" s="91"/>
-      <c r="AJ7" s="91"/>
-      <c r="AK7" s="91"/>
-      <c r="AL7" s="91"/>
-      <c r="AM7" s="91"/>
-      <c r="AN7" s="91"/>
-      <c r="AO7" s="91"/>
-      <c r="AP7" s="91"/>
+      <c r="AA7" s="136"/>
+      <c r="AB7" s="136"/>
+      <c r="AC7" s="136"/>
+      <c r="AD7" s="136"/>
+      <c r="AE7" s="136"/>
+      <c r="AF7" s="136"/>
+      <c r="AG7" s="136"/>
+      <c r="AH7" s="136"/>
+      <c r="AI7" s="136"/>
+      <c r="AJ7" s="136"/>
+      <c r="AK7" s="136"/>
+      <c r="AL7" s="136"/>
+      <c r="AM7" s="136"/>
+      <c r="AN7" s="136"/>
+      <c r="AO7" s="136"/>
+      <c r="AP7" s="136"/>
       <c r="AQ7" s="57"/>
-      <c r="AR7" s="163" t="s">
+      <c r="AR7" s="176" t="s">
         <v>9</v>
       </c>
-      <c r="AS7" s="163"/>
-      <c r="AT7" s="163"/>
-      <c r="AU7" s="163"/>
-      <c r="AV7" s="104" t="str">
+      <c r="AS7" s="176"/>
+      <c r="AT7" s="176"/>
+      <c r="AU7" s="176"/>
+      <c r="AV7" s="187" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,3,0))</f>
         <v/>
       </c>
-      <c r="AW7" s="104"/>
-      <c r="AX7" s="104"/>
-      <c r="AY7" s="104"/>
-      <c r="AZ7" s="105"/>
+      <c r="AW7" s="187"/>
+      <c r="AX7" s="187"/>
+      <c r="AY7" s="187"/>
+      <c r="AZ7" s="188"/>
       <c r="BA7"/>
     </row>
     <row r="8" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="204" t="s">
+      <c r="A8" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="205"/>
-      <c r="C8" s="205"/>
-      <c r="D8" s="205"/>
-      <c r="E8" s="205"/>
-      <c r="F8" s="205"/>
-      <c r="G8" s="206" t="str">
+      <c r="B8" s="173"/>
+      <c r="C8" s="173"/>
+      <c r="D8" s="173"/>
+      <c r="E8" s="173"/>
+      <c r="F8" s="173"/>
+      <c r="G8" s="174" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,6,0))</f>
         <v/>
       </c>
-      <c r="H8" s="207"/>
-      <c r="I8" s="207"/>
-      <c r="J8" s="207"/>
-      <c r="K8" s="207"/>
-      <c r="L8" s="207"/>
-      <c r="M8" s="207"/>
-      <c r="N8" s="207"/>
-      <c r="O8" s="207"/>
-      <c r="P8" s="207"/>
-      <c r="Q8" s="207"/>
-      <c r="R8" s="207"/>
-      <c r="S8" s="207"/>
-      <c r="T8" s="207"/>
-      <c r="U8" s="207"/>
-      <c r="V8" s="207"/>
-      <c r="W8" s="207"/>
-      <c r="X8" s="207"/>
-      <c r="Y8" s="207"/>
-      <c r="Z8" s="207"/>
-      <c r="AA8" s="207"/>
-      <c r="AB8" s="207"/>
-      <c r="AC8" s="207"/>
+      <c r="H8" s="175"/>
+      <c r="I8" s="175"/>
+      <c r="J8" s="175"/>
+      <c r="K8" s="175"/>
+      <c r="L8" s="175"/>
+      <c r="M8" s="175"/>
+      <c r="N8" s="175"/>
+      <c r="O8" s="175"/>
+      <c r="P8" s="175"/>
+      <c r="Q8" s="175"/>
+      <c r="R8" s="175"/>
+      <c r="S8" s="175"/>
+      <c r="T8" s="175"/>
+      <c r="U8" s="175"/>
+      <c r="V8" s="175"/>
+      <c r="W8" s="175"/>
+      <c r="X8" s="175"/>
+      <c r="Y8" s="175"/>
+      <c r="Z8" s="175"/>
+      <c r="AA8" s="175"/>
+      <c r="AB8" s="175"/>
+      <c r="AC8" s="175"/>
       <c r="AD8" s="59"/>
-      <c r="AE8" s="164" t="s">
+      <c r="AE8" s="186" t="s">
         <v>13</v>
       </c>
-      <c r="AF8" s="164"/>
-      <c r="AG8" s="164"/>
-      <c r="AH8" s="164"/>
-      <c r="AI8" s="164"/>
-      <c r="AJ8" s="164"/>
-      <c r="AK8" s="164"/>
-      <c r="AL8" s="93" t="str">
+      <c r="AF8" s="186"/>
+      <c r="AG8" s="186"/>
+      <c r="AH8" s="186"/>
+      <c r="AI8" s="186"/>
+      <c r="AJ8" s="186"/>
+      <c r="AK8" s="186"/>
+      <c r="AL8" s="179" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,7,0))</f>
         <v/>
       </c>
-      <c r="AM8" s="93"/>
-      <c r="AN8" s="93"/>
-      <c r="AO8" s="93"/>
-      <c r="AP8" s="93"/>
-      <c r="AQ8" s="93"/>
-      <c r="AR8" s="93"/>
-      <c r="AS8" s="93"/>
-      <c r="AT8" s="93"/>
-      <c r="AU8" s="93"/>
-      <c r="AV8" s="93"/>
-      <c r="AW8" s="93"/>
-      <c r="AX8" s="93"/>
-      <c r="AY8" s="93"/>
-      <c r="AZ8" s="94"/>
+      <c r="AM8" s="179"/>
+      <c r="AN8" s="179"/>
+      <c r="AO8" s="179"/>
+      <c r="AP8" s="179"/>
+      <c r="AQ8" s="179"/>
+      <c r="AR8" s="179"/>
+      <c r="AS8" s="179"/>
+      <c r="AT8" s="179"/>
+      <c r="AU8" s="179"/>
+      <c r="AV8" s="179"/>
+      <c r="AW8" s="179"/>
+      <c r="AX8" s="179"/>
+      <c r="AY8" s="179"/>
+      <c r="AZ8" s="180"/>
     </row>
     <row r="9" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="204" t="s">
+      <c r="A9" s="172" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="205"/>
-      <c r="C9" s="205"/>
-      <c r="D9" s="205"/>
-      <c r="E9" s="205"/>
-      <c r="F9" s="205"/>
-      <c r="G9" s="208" t="str">
+      <c r="B9" s="173"/>
+      <c r="C9" s="173"/>
+      <c r="D9" s="173"/>
+      <c r="E9" s="173"/>
+      <c r="F9" s="173"/>
+      <c r="G9" s="177" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,8,0))</f>
         <v/>
       </c>
-      <c r="H9" s="209"/>
-      <c r="I9" s="209"/>
-      <c r="J9" s="209"/>
-      <c r="K9" s="209"/>
-      <c r="L9" s="209"/>
-      <c r="M9" s="209"/>
-      <c r="N9" s="209"/>
-      <c r="O9" s="209"/>
-      <c r="P9" s="209"/>
-      <c r="Q9" s="209"/>
-      <c r="R9" s="209"/>
-      <c r="S9" s="209"/>
-      <c r="T9" s="209"/>
-      <c r="U9" s="209"/>
-      <c r="V9" s="209"/>
-      <c r="W9" s="209"/>
-      <c r="X9" s="209"/>
-      <c r="Y9" s="209"/>
-      <c r="Z9" s="209"/>
-      <c r="AA9" s="209"/>
-      <c r="AB9" s="209"/>
-      <c r="AC9" s="209"/>
+      <c r="H9" s="178"/>
+      <c r="I9" s="178"/>
+      <c r="J9" s="178"/>
+      <c r="K9" s="178"/>
+      <c r="L9" s="178"/>
+      <c r="M9" s="178"/>
+      <c r="N9" s="178"/>
+      <c r="O9" s="178"/>
+      <c r="P9" s="178"/>
+      <c r="Q9" s="178"/>
+      <c r="R9" s="178"/>
+      <c r="S9" s="178"/>
+      <c r="T9" s="178"/>
+      <c r="U9" s="178"/>
+      <c r="V9" s="178"/>
+      <c r="W9" s="178"/>
+      <c r="X9" s="178"/>
+      <c r="Y9" s="178"/>
+      <c r="Z9" s="178"/>
+      <c r="AA9" s="178"/>
+      <c r="AB9" s="178"/>
+      <c r="AC9" s="178"/>
       <c r="AD9" s="59"/>
-      <c r="AE9" s="106" t="s">
+      <c r="AE9" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="AF9" s="106"/>
-      <c r="AG9" s="106"/>
-      <c r="AH9" s="106"/>
-      <c r="AI9" s="106"/>
-      <c r="AJ9" s="106"/>
-      <c r="AK9" s="106"/>
-      <c r="AL9" s="194" t="str">
+      <c r="AF9" s="170"/>
+      <c r="AG9" s="170"/>
+      <c r="AH9" s="170"/>
+      <c r="AI9" s="170"/>
+      <c r="AJ9" s="170"/>
+      <c r="AK9" s="170"/>
+      <c r="AL9" s="158" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,9,0))</f>
         <v/>
       </c>
-      <c r="AM9" s="195"/>
-      <c r="AN9" s="195"/>
-      <c r="AO9" s="195"/>
-      <c r="AP9" s="195"/>
-      <c r="AQ9" s="195"/>
-      <c r="AR9" s="195"/>
-      <c r="AS9" s="195"/>
-      <c r="AT9" s="195"/>
-      <c r="AU9" s="195"/>
-      <c r="AV9" s="195"/>
-      <c r="AW9" s="195"/>
-      <c r="AX9" s="195"/>
-      <c r="AY9" s="195"/>
-      <c r="AZ9" s="196"/>
+      <c r="AM9" s="159"/>
+      <c r="AN9" s="159"/>
+      <c r="AO9" s="159"/>
+      <c r="AP9" s="159"/>
+      <c r="AQ9" s="159"/>
+      <c r="AR9" s="159"/>
+      <c r="AS9" s="159"/>
+      <c r="AT9" s="159"/>
+      <c r="AU9" s="159"/>
+      <c r="AV9" s="159"/>
+      <c r="AW9" s="159"/>
+      <c r="AX9" s="159"/>
+      <c r="AY9" s="159"/>
+      <c r="AZ9" s="160"/>
     </row>
     <row r="10" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
@@ -5795,48 +5781,48 @@
       <c r="H12" s="59"/>
       <c r="I12" s="59"/>
       <c r="J12" s="59"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="93"/>
-      <c r="N12" s="93"/>
-      <c r="O12" s="93"/>
-      <c r="P12" s="93"/>
-      <c r="Q12" s="93"/>
-      <c r="R12" s="93"/>
-      <c r="S12" s="93"/>
-      <c r="T12" s="93"/>
-      <c r="U12" s="93"/>
-      <c r="V12" s="93"/>
-      <c r="W12" s="93"/>
-      <c r="X12" s="93"/>
-      <c r="Y12" s="93"/>
-      <c r="Z12" s="93"/>
-      <c r="AA12" s="93"/>
-      <c r="AB12" s="93"/>
-      <c r="AC12" s="93"/>
-      <c r="AD12" s="93"/>
-      <c r="AE12" s="93"/>
-      <c r="AF12" s="93"/>
-      <c r="AG12" s="93"/>
-      <c r="AH12" s="93"/>
-      <c r="AI12" s="93"/>
-      <c r="AJ12" s="93"/>
-      <c r="AK12" s="93"/>
-      <c r="AL12" s="93"/>
-      <c r="AM12" s="93"/>
-      <c r="AN12" s="93"/>
-      <c r="AO12" s="93"/>
-      <c r="AP12" s="93"/>
-      <c r="AQ12" s="93"/>
-      <c r="AR12" s="93"/>
-      <c r="AS12" s="93"/>
-      <c r="AT12" s="93"/>
-      <c r="AU12" s="93"/>
-      <c r="AV12" s="93"/>
-      <c r="AW12" s="93"/>
-      <c r="AX12" s="93"/>
-      <c r="AY12" s="93"/>
-      <c r="AZ12" s="94"/>
+      <c r="K12" s="230"/>
+      <c r="L12" s="179"/>
+      <c r="M12" s="179"/>
+      <c r="N12" s="179"/>
+      <c r="O12" s="179"/>
+      <c r="P12" s="179"/>
+      <c r="Q12" s="179"/>
+      <c r="R12" s="179"/>
+      <c r="S12" s="179"/>
+      <c r="T12" s="179"/>
+      <c r="U12" s="179"/>
+      <c r="V12" s="179"/>
+      <c r="W12" s="179"/>
+      <c r="X12" s="179"/>
+      <c r="Y12" s="179"/>
+      <c r="Z12" s="179"/>
+      <c r="AA12" s="179"/>
+      <c r="AB12" s="179"/>
+      <c r="AC12" s="179"/>
+      <c r="AD12" s="179"/>
+      <c r="AE12" s="179"/>
+      <c r="AF12" s="179"/>
+      <c r="AG12" s="179"/>
+      <c r="AH12" s="179"/>
+      <c r="AI12" s="179"/>
+      <c r="AJ12" s="179"/>
+      <c r="AK12" s="179"/>
+      <c r="AL12" s="179"/>
+      <c r="AM12" s="179"/>
+      <c r="AN12" s="179"/>
+      <c r="AO12" s="179"/>
+      <c r="AP12" s="179"/>
+      <c r="AQ12" s="179"/>
+      <c r="AR12" s="179"/>
+      <c r="AS12" s="179"/>
+      <c r="AT12" s="179"/>
+      <c r="AU12" s="179"/>
+      <c r="AV12" s="179"/>
+      <c r="AW12" s="179"/>
+      <c r="AX12" s="179"/>
+      <c r="AY12" s="179"/>
+      <c r="AZ12" s="180"/>
     </row>
     <row r="13" spans="1:60" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56" t="s">
@@ -5851,398 +5837,398 @@
       <c r="H13" s="59"/>
       <c r="I13" s="59"/>
       <c r="J13" s="59"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="104"/>
-      <c r="O13" s="104"/>
-      <c r="P13" s="104"/>
-      <c r="Q13" s="104"/>
-      <c r="R13" s="104"/>
-      <c r="S13" s="104"/>
-      <c r="T13" s="104"/>
-      <c r="U13" s="104"/>
-      <c r="V13" s="104"/>
-      <c r="W13" s="104"/>
-      <c r="X13" s="104"/>
-      <c r="Y13" s="104"/>
-      <c r="Z13" s="104"/>
-      <c r="AA13" s="104"/>
-      <c r="AB13" s="104"/>
-      <c r="AC13" s="104"/>
-      <c r="AD13" s="104"/>
-      <c r="AE13" s="104"/>
-      <c r="AF13" s="104"/>
-      <c r="AG13" s="104"/>
-      <c r="AH13" s="104"/>
-      <c r="AI13" s="104"/>
-      <c r="AJ13" s="104"/>
-      <c r="AK13" s="104"/>
-      <c r="AL13" s="104"/>
-      <c r="AM13" s="104"/>
-      <c r="AN13" s="104"/>
-      <c r="AO13" s="104"/>
-      <c r="AP13" s="104"/>
-      <c r="AQ13" s="104"/>
-      <c r="AR13" s="104"/>
-      <c r="AS13" s="104"/>
-      <c r="AT13" s="104"/>
-      <c r="AU13" s="104"/>
-      <c r="AV13" s="104"/>
-      <c r="AW13" s="104"/>
-      <c r="AX13" s="104"/>
-      <c r="AY13" s="104"/>
-      <c r="AZ13" s="105"/>
+      <c r="K13" s="187"/>
+      <c r="L13" s="187"/>
+      <c r="M13" s="187"/>
+      <c r="N13" s="187"/>
+      <c r="O13" s="187"/>
+      <c r="P13" s="187"/>
+      <c r="Q13" s="187"/>
+      <c r="R13" s="187"/>
+      <c r="S13" s="187"/>
+      <c r="T13" s="187"/>
+      <c r="U13" s="187"/>
+      <c r="V13" s="187"/>
+      <c r="W13" s="187"/>
+      <c r="X13" s="187"/>
+      <c r="Y13" s="187"/>
+      <c r="Z13" s="187"/>
+      <c r="AA13" s="187"/>
+      <c r="AB13" s="187"/>
+      <c r="AC13" s="187"/>
+      <c r="AD13" s="187"/>
+      <c r="AE13" s="187"/>
+      <c r="AF13" s="187"/>
+      <c r="AG13" s="187"/>
+      <c r="AH13" s="187"/>
+      <c r="AI13" s="187"/>
+      <c r="AJ13" s="187"/>
+      <c r="AK13" s="187"/>
+      <c r="AL13" s="187"/>
+      <c r="AM13" s="187"/>
+      <c r="AN13" s="187"/>
+      <c r="AO13" s="187"/>
+      <c r="AP13" s="187"/>
+      <c r="AQ13" s="187"/>
+      <c r="AR13" s="187"/>
+      <c r="AS13" s="187"/>
+      <c r="AT13" s="187"/>
+      <c r="AU13" s="187"/>
+      <c r="AV13" s="187"/>
+      <c r="AW13" s="187"/>
+      <c r="AX13" s="187"/>
+      <c r="AY13" s="187"/>
+      <c r="AZ13" s="188"/>
     </row>
     <row r="14" spans="1:60" s="10" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="107"/>
-      <c r="B14" s="108"/>
-      <c r="C14" s="108"/>
-      <c r="D14" s="108"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="108"/>
-      <c r="I14" s="108"/>
-      <c r="J14" s="108"/>
-      <c r="K14" s="108"/>
-      <c r="L14" s="108"/>
-      <c r="M14" s="108"/>
-      <c r="N14" s="108"/>
-      <c r="O14" s="108"/>
-      <c r="P14" s="108"/>
-      <c r="Q14" s="108"/>
-      <c r="R14" s="108"/>
-      <c r="S14" s="108"/>
-      <c r="T14" s="108"/>
-      <c r="U14" s="108"/>
-      <c r="V14" s="108"/>
-      <c r="W14" s="108"/>
-      <c r="X14" s="108"/>
-      <c r="Y14" s="108"/>
-      <c r="Z14" s="108"/>
-      <c r="AA14" s="108"/>
-      <c r="AB14" s="108"/>
-      <c r="AC14" s="108"/>
-      <c r="AD14" s="108"/>
-      <c r="AE14" s="108"/>
-      <c r="AF14" s="108"/>
-      <c r="AG14" s="108"/>
-      <c r="AH14" s="108"/>
-      <c r="AI14" s="108"/>
-      <c r="AJ14" s="108"/>
-      <c r="AK14" s="108"/>
-      <c r="AL14" s="108"/>
-      <c r="AM14" s="108"/>
-      <c r="AN14" s="108"/>
-      <c r="AO14" s="108"/>
-      <c r="AP14" s="108"/>
-      <c r="AQ14" s="108"/>
-      <c r="AR14" s="108"/>
-      <c r="AS14" s="108"/>
-      <c r="AT14" s="108"/>
-      <c r="AU14" s="108"/>
-      <c r="AV14" s="108"/>
-      <c r="AW14" s="108"/>
-      <c r="AX14" s="108"/>
-      <c r="AY14" s="108"/>
-      <c r="AZ14" s="109"/>
+      <c r="A14" s="233"/>
+      <c r="B14" s="234"/>
+      <c r="C14" s="234"/>
+      <c r="D14" s="234"/>
+      <c r="E14" s="234"/>
+      <c r="F14" s="234"/>
+      <c r="G14" s="234"/>
+      <c r="H14" s="234"/>
+      <c r="I14" s="234"/>
+      <c r="J14" s="234"/>
+      <c r="K14" s="234"/>
+      <c r="L14" s="234"/>
+      <c r="M14" s="234"/>
+      <c r="N14" s="234"/>
+      <c r="O14" s="234"/>
+      <c r="P14" s="234"/>
+      <c r="Q14" s="234"/>
+      <c r="R14" s="234"/>
+      <c r="S14" s="234"/>
+      <c r="T14" s="234"/>
+      <c r="U14" s="234"/>
+      <c r="V14" s="234"/>
+      <c r="W14" s="234"/>
+      <c r="X14" s="234"/>
+      <c r="Y14" s="234"/>
+      <c r="Z14" s="234"/>
+      <c r="AA14" s="234"/>
+      <c r="AB14" s="234"/>
+      <c r="AC14" s="234"/>
+      <c r="AD14" s="234"/>
+      <c r="AE14" s="234"/>
+      <c r="AF14" s="234"/>
+      <c r="AG14" s="234"/>
+      <c r="AH14" s="234"/>
+      <c r="AI14" s="234"/>
+      <c r="AJ14" s="234"/>
+      <c r="AK14" s="234"/>
+      <c r="AL14" s="234"/>
+      <c r="AM14" s="234"/>
+      <c r="AN14" s="234"/>
+      <c r="AO14" s="234"/>
+      <c r="AP14" s="234"/>
+      <c r="AQ14" s="234"/>
+      <c r="AR14" s="234"/>
+      <c r="AS14" s="234"/>
+      <c r="AT14" s="234"/>
+      <c r="AU14" s="234"/>
+      <c r="AV14" s="234"/>
+      <c r="AW14" s="234"/>
+      <c r="AX14" s="234"/>
+      <c r="AY14" s="234"/>
+      <c r="AZ14" s="235"/>
       <c r="BC14" s="24"/>
     </row>
     <row r="15" spans="1:60" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="148"/>
-      <c r="B15" s="148"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="148"/>
-      <c r="E15" s="148"/>
-      <c r="F15" s="148"/>
-      <c r="G15" s="148"/>
-      <c r="H15" s="148"/>
-      <c r="I15" s="148"/>
-      <c r="J15" s="148"/>
-      <c r="K15" s="148"/>
-      <c r="L15" s="148"/>
-      <c r="M15" s="148"/>
-      <c r="N15" s="148"/>
-      <c r="O15" s="148"/>
-      <c r="P15" s="148"/>
-      <c r="Q15" s="148"/>
-      <c r="R15" s="148"/>
-      <c r="S15" s="148"/>
-      <c r="T15" s="148"/>
-      <c r="U15" s="148"/>
-      <c r="V15" s="148"/>
-      <c r="W15" s="148"/>
-      <c r="X15" s="148"/>
-      <c r="Y15" s="148"/>
-      <c r="Z15" s="148"/>
-      <c r="AA15" s="148"/>
-      <c r="AB15" s="148"/>
-      <c r="AC15" s="148"/>
-      <c r="AD15" s="148"/>
-      <c r="AE15" s="148"/>
-      <c r="AF15" s="148"/>
-      <c r="AG15" s="148"/>
-      <c r="AH15" s="148"/>
-      <c r="AI15" s="148"/>
-      <c r="AJ15" s="148"/>
-      <c r="AK15" s="148"/>
-      <c r="AL15" s="148"/>
-      <c r="AM15" s="148"/>
-      <c r="AN15" s="148"/>
-      <c r="AO15" s="148"/>
-      <c r="AP15" s="148"/>
-      <c r="AQ15" s="148"/>
-      <c r="AR15" s="148"/>
-      <c r="AS15" s="148"/>
-      <c r="AT15" s="148"/>
-      <c r="AU15" s="148"/>
-      <c r="AV15" s="148"/>
-      <c r="AW15" s="148"/>
-      <c r="AX15" s="148"/>
-      <c r="AY15" s="148"/>
-      <c r="AZ15" s="148"/>
+      <c r="A15" s="99"/>
+      <c r="B15" s="99"/>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="99"/>
+      <c r="L15" s="99"/>
+      <c r="M15" s="99"/>
+      <c r="N15" s="99"/>
+      <c r="O15" s="99"/>
+      <c r="P15" s="99"/>
+      <c r="Q15" s="99"/>
+      <c r="R15" s="99"/>
+      <c r="S15" s="99"/>
+      <c r="T15" s="99"/>
+      <c r="U15" s="99"/>
+      <c r="V15" s="99"/>
+      <c r="W15" s="99"/>
+      <c r="X15" s="99"/>
+      <c r="Y15" s="99"/>
+      <c r="Z15" s="99"/>
+      <c r="AA15" s="99"/>
+      <c r="AB15" s="99"/>
+      <c r="AC15" s="99"/>
+      <c r="AD15" s="99"/>
+      <c r="AE15" s="99"/>
+      <c r="AF15" s="99"/>
+      <c r="AG15" s="99"/>
+      <c r="AH15" s="99"/>
+      <c r="AI15" s="99"/>
+      <c r="AJ15" s="99"/>
+      <c r="AK15" s="99"/>
+      <c r="AL15" s="99"/>
+      <c r="AM15" s="99"/>
+      <c r="AN15" s="99"/>
+      <c r="AO15" s="99"/>
+      <c r="AP15" s="99"/>
+      <c r="AQ15" s="99"/>
+      <c r="AR15" s="99"/>
+      <c r="AS15" s="99"/>
+      <c r="AT15" s="99"/>
+      <c r="AU15" s="99"/>
+      <c r="AV15" s="99"/>
+      <c r="AW15" s="99"/>
+      <c r="AX15" s="99"/>
+      <c r="AY15" s="99"/>
+      <c r="AZ15" s="99"/>
     </row>
     <row r="16" spans="1:60" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="110" t="s">
+      <c r="A16" s="236" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="111"/>
-      <c r="P16" s="111"/>
-      <c r="Q16" s="111"/>
-      <c r="R16" s="111"/>
-      <c r="S16" s="111"/>
-      <c r="T16" s="111"/>
-      <c r="U16" s="111"/>
-      <c r="V16" s="111"/>
-      <c r="W16" s="111"/>
-      <c r="X16" s="111"/>
-      <c r="Y16" s="111"/>
-      <c r="Z16" s="111"/>
-      <c r="AA16" s="111"/>
-      <c r="AB16" s="111"/>
-      <c r="AC16" s="111"/>
-      <c r="AD16" s="111"/>
-      <c r="AE16" s="111"/>
-      <c r="AF16" s="111"/>
-      <c r="AG16" s="111"/>
-      <c r="AH16" s="111"/>
-      <c r="AI16" s="111"/>
-      <c r="AJ16" s="111"/>
-      <c r="AK16" s="111"/>
-      <c r="AL16" s="111"/>
-      <c r="AM16" s="111"/>
-      <c r="AN16" s="111"/>
-      <c r="AO16" s="111"/>
-      <c r="AP16" s="111"/>
-      <c r="AQ16" s="111"/>
-      <c r="AR16" s="111"/>
-      <c r="AS16" s="111"/>
-      <c r="AT16" s="111"/>
-      <c r="AU16" s="111"/>
-      <c r="AV16" s="111"/>
-      <c r="AW16" s="111"/>
-      <c r="AX16" s="111"/>
-      <c r="AY16" s="111"/>
-      <c r="AZ16" s="112"/>
+      <c r="B16" s="237"/>
+      <c r="C16" s="237"/>
+      <c r="D16" s="237"/>
+      <c r="E16" s="237"/>
+      <c r="F16" s="237"/>
+      <c r="G16" s="237"/>
+      <c r="H16" s="237"/>
+      <c r="I16" s="237"/>
+      <c r="J16" s="237"/>
+      <c r="K16" s="237"/>
+      <c r="L16" s="237"/>
+      <c r="M16" s="237"/>
+      <c r="N16" s="237"/>
+      <c r="O16" s="237"/>
+      <c r="P16" s="237"/>
+      <c r="Q16" s="237"/>
+      <c r="R16" s="237"/>
+      <c r="S16" s="237"/>
+      <c r="T16" s="237"/>
+      <c r="U16" s="237"/>
+      <c r="V16" s="237"/>
+      <c r="W16" s="237"/>
+      <c r="X16" s="237"/>
+      <c r="Y16" s="237"/>
+      <c r="Z16" s="237"/>
+      <c r="AA16" s="237"/>
+      <c r="AB16" s="237"/>
+      <c r="AC16" s="237"/>
+      <c r="AD16" s="237"/>
+      <c r="AE16" s="237"/>
+      <c r="AF16" s="237"/>
+      <c r="AG16" s="237"/>
+      <c r="AH16" s="237"/>
+      <c r="AI16" s="237"/>
+      <c r="AJ16" s="237"/>
+      <c r="AK16" s="237"/>
+      <c r="AL16" s="237"/>
+      <c r="AM16" s="237"/>
+      <c r="AN16" s="237"/>
+      <c r="AO16" s="237"/>
+      <c r="AP16" s="237"/>
+      <c r="AQ16" s="237"/>
+      <c r="AR16" s="237"/>
+      <c r="AS16" s="237"/>
+      <c r="AT16" s="237"/>
+      <c r="AU16" s="237"/>
+      <c r="AV16" s="237"/>
+      <c r="AW16" s="237"/>
+      <c r="AX16" s="237"/>
+      <c r="AY16" s="237"/>
+      <c r="AZ16" s="238"/>
     </row>
     <row r="17" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="201" t="s">
+      <c r="A17" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="202"/>
-      <c r="C17" s="202"/>
-      <c r="D17" s="202"/>
-      <c r="E17" s="202"/>
-      <c r="F17" s="202"/>
-      <c r="G17" s="202"/>
-      <c r="H17" s="202"/>
-      <c r="I17" s="202"/>
-      <c r="J17" s="202"/>
-      <c r="K17" s="202"/>
-      <c r="L17" s="202"/>
-      <c r="M17" s="199" t="s">
+      <c r="B17" s="169"/>
+      <c r="C17" s="169"/>
+      <c r="D17" s="169"/>
+      <c r="E17" s="169"/>
+      <c r="F17" s="169"/>
+      <c r="G17" s="169"/>
+      <c r="H17" s="169"/>
+      <c r="I17" s="169"/>
+      <c r="J17" s="169"/>
+      <c r="K17" s="169"/>
+      <c r="L17" s="169"/>
+      <c r="M17" s="166" t="s">
         <v>32</v>
       </c>
-      <c r="N17" s="200"/>
-      <c r="O17" s="200"/>
-      <c r="P17" s="200"/>
-      <c r="Q17" s="200"/>
-      <c r="R17" s="116" t="s">
+      <c r="N17" s="167"/>
+      <c r="O17" s="167"/>
+      <c r="P17" s="167"/>
+      <c r="Q17" s="167"/>
+      <c r="R17" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="118"/>
-      <c r="W17" s="116" t="s">
+      <c r="S17" s="164"/>
+      <c r="T17" s="164"/>
+      <c r="U17" s="164"/>
+      <c r="V17" s="165"/>
+      <c r="W17" s="163" t="s">
         <v>34</v>
       </c>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="118"/>
-      <c r="AB17" s="116" t="s">
+      <c r="X17" s="164"/>
+      <c r="Y17" s="164"/>
+      <c r="Z17" s="164"/>
+      <c r="AA17" s="165"/>
+      <c r="AB17" s="163" t="s">
         <v>35</v>
       </c>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="118"/>
-      <c r="AG17" s="116" t="s">
+      <c r="AC17" s="164"/>
+      <c r="AD17" s="164"/>
+      <c r="AE17" s="164"/>
+      <c r="AF17" s="165"/>
+      <c r="AG17" s="163" t="s">
         <v>36</v>
       </c>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="117"/>
-      <c r="AJ17" s="117"/>
-      <c r="AK17" s="118"/>
-      <c r="AL17" s="116" t="s">
+      <c r="AH17" s="164"/>
+      <c r="AI17" s="164"/>
+      <c r="AJ17" s="164"/>
+      <c r="AK17" s="165"/>
+      <c r="AL17" s="163" t="s">
         <v>37</v>
       </c>
-      <c r="AM17" s="117"/>
-      <c r="AN17" s="117"/>
-      <c r="AO17" s="117"/>
-      <c r="AP17" s="118"/>
-      <c r="AQ17" s="116" t="s">
+      <c r="AM17" s="164"/>
+      <c r="AN17" s="164"/>
+      <c r="AO17" s="164"/>
+      <c r="AP17" s="165"/>
+      <c r="AQ17" s="163" t="s">
         <v>38</v>
       </c>
-      <c r="AR17" s="117"/>
-      <c r="AS17" s="117"/>
-      <c r="AT17" s="117"/>
-      <c r="AU17" s="118"/>
-      <c r="AV17" s="113" t="s">
+      <c r="AR17" s="164"/>
+      <c r="AS17" s="164"/>
+      <c r="AT17" s="164"/>
+      <c r="AU17" s="165"/>
+      <c r="AV17" s="239" t="s">
         <v>32</v>
       </c>
-      <c r="AW17" s="114"/>
-      <c r="AX17" s="114"/>
-      <c r="AY17" s="114"/>
-      <c r="AZ17" s="115"/>
+      <c r="AW17" s="240"/>
+      <c r="AX17" s="240"/>
+      <c r="AY17" s="240"/>
+      <c r="AZ17" s="241"/>
     </row>
     <row r="18" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="230" t="s">
+      <c r="A18" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="231"/>
-      <c r="C18" s="231"/>
-      <c r="D18" s="231"/>
-      <c r="E18" s="231"/>
-      <c r="F18" s="231"/>
-      <c r="G18" s="231"/>
-      <c r="H18" s="231"/>
-      <c r="I18" s="231"/>
-      <c r="J18" s="231"/>
-      <c r="K18" s="231"/>
-      <c r="L18" s="232"/>
-      <c r="M18" s="229"/>
-      <c r="N18" s="123"/>
-      <c r="O18" s="123"/>
-      <c r="P18" s="123"/>
-      <c r="Q18" s="123"/>
-      <c r="R18" s="122"/>
-      <c r="S18" s="123"/>
-      <c r="T18" s="123"/>
-      <c r="U18" s="123"/>
-      <c r="V18" s="123"/>
-      <c r="W18" s="122"/>
-      <c r="X18" s="123"/>
-      <c r="Y18" s="123"/>
-      <c r="Z18" s="123"/>
-      <c r="AA18" s="123"/>
-      <c r="AB18" s="122"/>
-      <c r="AC18" s="123"/>
-      <c r="AD18" s="123"/>
-      <c r="AE18" s="123"/>
-      <c r="AF18" s="123"/>
-      <c r="AG18" s="122"/>
-      <c r="AH18" s="123"/>
-      <c r="AI18" s="123"/>
-      <c r="AJ18" s="123"/>
-      <c r="AK18" s="123"/>
-      <c r="AL18" s="122"/>
-      <c r="AM18" s="123"/>
-      <c r="AN18" s="123"/>
-      <c r="AO18" s="123"/>
-      <c r="AP18" s="123"/>
-      <c r="AQ18" s="122"/>
-      <c r="AR18" s="123"/>
-      <c r="AS18" s="123"/>
-      <c r="AT18" s="123"/>
-      <c r="AU18" s="123"/>
-      <c r="AV18" s="119"/>
-      <c r="AW18" s="120"/>
-      <c r="AX18" s="120"/>
-      <c r="AY18" s="120"/>
-      <c r="AZ18" s="121"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="93"/>
+      <c r="K18" s="93"/>
+      <c r="L18" s="94"/>
+      <c r="M18" s="91"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="89"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="89"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="89"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="89"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="90"/>
+      <c r="AK18" s="90"/>
+      <c r="AL18" s="89"/>
+      <c r="AM18" s="90"/>
+      <c r="AN18" s="90"/>
+      <c r="AO18" s="90"/>
+      <c r="AP18" s="90"/>
+      <c r="AQ18" s="89"/>
+      <c r="AR18" s="90"/>
+      <c r="AS18" s="90"/>
+      <c r="AT18" s="90"/>
+      <c r="AU18" s="90"/>
+      <c r="AV18" s="242"/>
+      <c r="AW18" s="243"/>
+      <c r="AX18" s="243"/>
+      <c r="AY18" s="243"/>
+      <c r="AZ18" s="244"/>
       <c r="BD18" s="26"/>
     </row>
     <row r="19" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="220" t="s">
+      <c r="A19" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="221"/>
-      <c r="C19" s="221"/>
-      <c r="D19" s="221"/>
-      <c r="E19" s="221"/>
-      <c r="F19" s="221"/>
-      <c r="G19" s="221"/>
-      <c r="H19" s="221"/>
-      <c r="I19" s="221"/>
-      <c r="J19" s="221"/>
-      <c r="K19" s="221"/>
-      <c r="L19" s="222"/>
-      <c r="M19" s="215"/>
-      <c r="N19" s="165"/>
-      <c r="O19" s="165"/>
-      <c r="P19" s="165"/>
-      <c r="Q19" s="165"/>
-      <c r="R19" s="165"/>
-      <c r="S19" s="165"/>
-      <c r="T19" s="165"/>
-      <c r="U19" s="165"/>
-      <c r="V19" s="165"/>
-      <c r="W19" s="165"/>
-      <c r="X19" s="165"/>
-      <c r="Y19" s="165"/>
-      <c r="Z19" s="165"/>
-      <c r="AA19" s="165"/>
-      <c r="AB19" s="212"/>
-      <c r="AC19" s="165"/>
-      <c r="AD19" s="165"/>
-      <c r="AE19" s="165"/>
-      <c r="AF19" s="165"/>
-      <c r="AG19" s="212"/>
-      <c r="AH19" s="165"/>
-      <c r="AI19" s="165"/>
-      <c r="AJ19" s="165"/>
-      <c r="AK19" s="165"/>
-      <c r="AL19" s="212"/>
-      <c r="AM19" s="165"/>
-      <c r="AN19" s="165"/>
-      <c r="AO19" s="165"/>
-      <c r="AP19" s="165"/>
-      <c r="AQ19" s="212"/>
-      <c r="AR19" s="165"/>
-      <c r="AS19" s="165"/>
-      <c r="AT19" s="165"/>
-      <c r="AU19" s="165"/>
-      <c r="AV19" s="212"/>
-      <c r="AW19" s="165"/>
-      <c r="AX19" s="165"/>
-      <c r="AY19" s="165"/>
-      <c r="AZ19" s="233"/>
+      <c r="B19" s="130"/>
+      <c r="C19" s="130"/>
+      <c r="D19" s="130"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="130"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="130"/>
+      <c r="J19" s="130"/>
+      <c r="K19" s="130"/>
+      <c r="L19" s="131"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="96"/>
+      <c r="O19" s="96"/>
+      <c r="P19" s="96"/>
+      <c r="Q19" s="96"/>
+      <c r="R19" s="96"/>
+      <c r="S19" s="96"/>
+      <c r="T19" s="96"/>
+      <c r="U19" s="96"/>
+      <c r="V19" s="96"/>
+      <c r="W19" s="96"/>
+      <c r="X19" s="96"/>
+      <c r="Y19" s="96"/>
+      <c r="Z19" s="96"/>
+      <c r="AA19" s="96"/>
+      <c r="AB19" s="95"/>
+      <c r="AC19" s="96"/>
+      <c r="AD19" s="96"/>
+      <c r="AE19" s="96"/>
+      <c r="AF19" s="96"/>
+      <c r="AG19" s="95"/>
+      <c r="AH19" s="96"/>
+      <c r="AI19" s="96"/>
+      <c r="AJ19" s="96"/>
+      <c r="AK19" s="96"/>
+      <c r="AL19" s="95"/>
+      <c r="AM19" s="96"/>
+      <c r="AN19" s="96"/>
+      <c r="AO19" s="96"/>
+      <c r="AP19" s="96"/>
+      <c r="AQ19" s="95"/>
+      <c r="AR19" s="96"/>
+      <c r="AS19" s="96"/>
+      <c r="AT19" s="96"/>
+      <c r="AU19" s="96"/>
+      <c r="AV19" s="95"/>
+      <c r="AW19" s="96"/>
+      <c r="AX19" s="96"/>
+      <c r="AY19" s="96"/>
+      <c r="AZ19" s="97"/>
       <c r="BC19" s="29"/>
       <c r="BD19" s="49"/>
       <c r="BE19" s="30"/>
@@ -6253,60 +6239,60 @@
       <c r="BJ19" s="49"/>
     </row>
     <row r="20" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="223" t="s">
+      <c r="A20" s="132" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="224"/>
-      <c r="C20" s="224"/>
-      <c r="D20" s="224"/>
-      <c r="E20" s="224"/>
-      <c r="F20" s="224"/>
-      <c r="G20" s="224"/>
-      <c r="H20" s="224"/>
-      <c r="I20" s="224"/>
-      <c r="J20" s="224"/>
-      <c r="K20" s="224"/>
-      <c r="L20" s="225"/>
-      <c r="M20" s="216"/>
-      <c r="N20" s="166"/>
-      <c r="O20" s="166"/>
-      <c r="P20" s="166"/>
-      <c r="Q20" s="166"/>
-      <c r="R20" s="166"/>
-      <c r="S20" s="166"/>
-      <c r="T20" s="166"/>
-      <c r="U20" s="166"/>
-      <c r="V20" s="166"/>
-      <c r="W20" s="166"/>
-      <c r="X20" s="166"/>
-      <c r="Y20" s="166"/>
-      <c r="Z20" s="166"/>
-      <c r="AA20" s="166"/>
-      <c r="AB20" s="166"/>
-      <c r="AC20" s="166"/>
-      <c r="AD20" s="166"/>
-      <c r="AE20" s="166"/>
-      <c r="AF20" s="166"/>
-      <c r="AG20" s="166"/>
-      <c r="AH20" s="166"/>
-      <c r="AI20" s="166"/>
-      <c r="AJ20" s="166"/>
-      <c r="AK20" s="166"/>
-      <c r="AL20" s="166"/>
-      <c r="AM20" s="166"/>
-      <c r="AN20" s="166"/>
-      <c r="AO20" s="166"/>
-      <c r="AP20" s="166"/>
-      <c r="AQ20" s="166"/>
-      <c r="AR20" s="166"/>
-      <c r="AS20" s="166"/>
-      <c r="AT20" s="166"/>
-      <c r="AU20" s="166"/>
-      <c r="AV20" s="166"/>
-      <c r="AW20" s="166"/>
-      <c r="AX20" s="166"/>
-      <c r="AY20" s="166"/>
-      <c r="AZ20" s="168"/>
+      <c r="B20" s="133"/>
+      <c r="C20" s="133"/>
+      <c r="D20" s="133"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="133"/>
+      <c r="G20" s="133"/>
+      <c r="H20" s="133"/>
+      <c r="I20" s="133"/>
+      <c r="J20" s="133"/>
+      <c r="K20" s="133"/>
+      <c r="L20" s="134"/>
+      <c r="M20" s="122"/>
+      <c r="N20" s="123"/>
+      <c r="O20" s="123"/>
+      <c r="P20" s="123"/>
+      <c r="Q20" s="123"/>
+      <c r="R20" s="123"/>
+      <c r="S20" s="123"/>
+      <c r="T20" s="123"/>
+      <c r="U20" s="123"/>
+      <c r="V20" s="123"/>
+      <c r="W20" s="123"/>
+      <c r="X20" s="123"/>
+      <c r="Y20" s="123"/>
+      <c r="Z20" s="123"/>
+      <c r="AA20" s="123"/>
+      <c r="AB20" s="123"/>
+      <c r="AC20" s="123"/>
+      <c r="AD20" s="123"/>
+      <c r="AE20" s="123"/>
+      <c r="AF20" s="123"/>
+      <c r="AG20" s="123"/>
+      <c r="AH20" s="123"/>
+      <c r="AI20" s="123"/>
+      <c r="AJ20" s="123"/>
+      <c r="AK20" s="123"/>
+      <c r="AL20" s="123"/>
+      <c r="AM20" s="123"/>
+      <c r="AN20" s="123"/>
+      <c r="AO20" s="123"/>
+      <c r="AP20" s="123"/>
+      <c r="AQ20" s="123"/>
+      <c r="AR20" s="123"/>
+      <c r="AS20" s="123"/>
+      <c r="AT20" s="123"/>
+      <c r="AU20" s="123"/>
+      <c r="AV20" s="123"/>
+      <c r="AW20" s="123"/>
+      <c r="AX20" s="123"/>
+      <c r="AY20" s="123"/>
+      <c r="AZ20" s="192"/>
       <c r="BC20" s="29"/>
       <c r="BD20" s="31"/>
       <c r="BE20" s="31"/>
@@ -6317,63 +6303,63 @@
       <c r="BJ20" s="31"/>
     </row>
     <row r="21" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="223" t="s">
+      <c r="A21" s="132" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="224"/>
-      <c r="C21" s="224"/>
-      <c r="D21" s="224"/>
-      <c r="E21" s="224"/>
-      <c r="F21" s="224"/>
-      <c r="G21" s="224"/>
-      <c r="H21" s="224"/>
-      <c r="I21" s="224"/>
-      <c r="J21" s="224"/>
-      <c r="K21" s="224"/>
-      <c r="L21" s="225"/>
-      <c r="M21" s="217"/>
-      <c r="N21" s="167"/>
-      <c r="O21" s="167"/>
-      <c r="P21" s="167"/>
-      <c r="Q21" s="167"/>
-      <c r="R21" s="167"/>
-      <c r="S21" s="167"/>
-      <c r="T21" s="167"/>
-      <c r="U21" s="167"/>
-      <c r="V21" s="167"/>
-      <c r="W21" s="167"/>
-      <c r="X21" s="167"/>
-      <c r="Y21" s="167"/>
-      <c r="Z21" s="167"/>
-      <c r="AA21" s="167"/>
-      <c r="AB21" s="167"/>
-      <c r="AC21" s="167"/>
-      <c r="AD21" s="167"/>
-      <c r="AE21" s="167"/>
-      <c r="AF21" s="167"/>
-      <c r="AG21" s="167"/>
-      <c r="AH21" s="167"/>
-      <c r="AI21" s="167"/>
-      <c r="AJ21" s="167"/>
-      <c r="AK21" s="167"/>
-      <c r="AL21" s="167"/>
-      <c r="AM21" s="167"/>
-      <c r="AN21" s="167"/>
-      <c r="AO21" s="167"/>
-      <c r="AP21" s="167"/>
-      <c r="AQ21" s="167"/>
-      <c r="AR21" s="167"/>
-      <c r="AS21" s="167"/>
-      <c r="AT21" s="167"/>
-      <c r="AU21" s="167"/>
-      <c r="AV21" s="167"/>
-      <c r="AW21" s="167"/>
-      <c r="AX21" s="167"/>
-      <c r="AY21" s="167"/>
-      <c r="AZ21" s="169"/>
+      <c r="B21" s="133"/>
+      <c r="C21" s="133"/>
+      <c r="D21" s="133"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="133"/>
+      <c r="I21" s="133"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="134"/>
+      <c r="M21" s="124"/>
+      <c r="N21" s="115"/>
+      <c r="O21" s="115"/>
+      <c r="P21" s="115"/>
+      <c r="Q21" s="115"/>
+      <c r="R21" s="115"/>
+      <c r="S21" s="115"/>
+      <c r="T21" s="115"/>
+      <c r="U21" s="115"/>
+      <c r="V21" s="115"/>
+      <c r="W21" s="115"/>
+      <c r="X21" s="115"/>
+      <c r="Y21" s="115"/>
+      <c r="Z21" s="115"/>
+      <c r="AA21" s="115"/>
+      <c r="AB21" s="115"/>
+      <c r="AC21" s="115"/>
+      <c r="AD21" s="115"/>
+      <c r="AE21" s="115"/>
+      <c r="AF21" s="115"/>
+      <c r="AG21" s="115"/>
+      <c r="AH21" s="115"/>
+      <c r="AI21" s="115"/>
+      <c r="AJ21" s="115"/>
+      <c r="AK21" s="115"/>
+      <c r="AL21" s="115"/>
+      <c r="AM21" s="115"/>
+      <c r="AN21" s="115"/>
+      <c r="AO21" s="115"/>
+      <c r="AP21" s="115"/>
+      <c r="AQ21" s="115"/>
+      <c r="AR21" s="115"/>
+      <c r="AS21" s="115"/>
+      <c r="AT21" s="115"/>
+      <c r="AU21" s="115"/>
+      <c r="AV21" s="115"/>
+      <c r="AW21" s="115"/>
+      <c r="AX21" s="115"/>
+      <c r="AY21" s="115"/>
+      <c r="AZ21" s="116"/>
       <c r="BC21" s="29"/>
-      <c r="BD21" s="90"/>
-      <c r="BE21" s="90"/>
+      <c r="BD21" s="229"/>
+      <c r="BE21" s="229"/>
       <c r="BF21" s="29"/>
       <c r="BG21" s="29"/>
       <c r="BH21" s="29"/>
@@ -6381,84 +6367,84 @@
       <c r="BJ21" s="29"/>
     </row>
     <row r="22" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="223" t="s">
+      <c r="A22" s="132" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="224"/>
-      <c r="C22" s="224"/>
-      <c r="D22" s="224"/>
-      <c r="E22" s="224"/>
-      <c r="F22" s="224"/>
-      <c r="G22" s="224"/>
-      <c r="H22" s="224"/>
-      <c r="I22" s="224"/>
-      <c r="J22" s="224"/>
-      <c r="K22" s="224"/>
-      <c r="L22" s="225"/>
-      <c r="M22" s="217" t="str">
+      <c r="B22" s="133"/>
+      <c r="C22" s="133"/>
+      <c r="D22" s="133"/>
+      <c r="E22" s="133"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="133"/>
+      <c r="I22" s="133"/>
+      <c r="J22" s="133"/>
+      <c r="K22" s="133"/>
+      <c r="L22" s="134"/>
+      <c r="M22" s="124" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="N22" s="167"/>
-      <c r="O22" s="167"/>
-      <c r="P22" s="167"/>
-      <c r="Q22" s="167"/>
-      <c r="R22" s="167" t="str">
+      <c r="N22" s="115"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="115"/>
+      <c r="Q22" s="115"/>
+      <c r="R22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="S22" s="167"/>
-      <c r="T22" s="167"/>
-      <c r="U22" s="167"/>
-      <c r="V22" s="167"/>
-      <c r="W22" s="167" t="str">
+      <c r="S22" s="115"/>
+      <c r="T22" s="115"/>
+      <c r="U22" s="115"/>
+      <c r="V22" s="115"/>
+      <c r="W22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="X22" s="167"/>
-      <c r="Y22" s="167"/>
-      <c r="Z22" s="167"/>
-      <c r="AA22" s="167"/>
-      <c r="AB22" s="167" t="str">
+      <c r="X22" s="115"/>
+      <c r="Y22" s="115"/>
+      <c r="Z22" s="115"/>
+      <c r="AA22" s="115"/>
+      <c r="AB22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AC22" s="167"/>
-      <c r="AD22" s="167"/>
-      <c r="AE22" s="167"/>
-      <c r="AF22" s="167"/>
-      <c r="AG22" s="167" t="str">
+      <c r="AC22" s="115"/>
+      <c r="AD22" s="115"/>
+      <c r="AE22" s="115"/>
+      <c r="AF22" s="115"/>
+      <c r="AG22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AH22" s="167"/>
-      <c r="AI22" s="167"/>
-      <c r="AJ22" s="167"/>
-      <c r="AK22" s="167"/>
-      <c r="AL22" s="167" t="str">
+      <c r="AH22" s="115"/>
+      <c r="AI22" s="115"/>
+      <c r="AJ22" s="115"/>
+      <c r="AK22" s="115"/>
+      <c r="AL22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AM22" s="167"/>
-      <c r="AN22" s="167"/>
-      <c r="AO22" s="167"/>
-      <c r="AP22" s="167"/>
-      <c r="AQ22" s="167" t="str">
+      <c r="AM22" s="115"/>
+      <c r="AN22" s="115"/>
+      <c r="AO22" s="115"/>
+      <c r="AP22" s="115"/>
+      <c r="AQ22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AR22" s="167"/>
-      <c r="AS22" s="167"/>
-      <c r="AT22" s="167"/>
-      <c r="AU22" s="167"/>
-      <c r="AV22" s="167" t="str">
+      <c r="AR22" s="115"/>
+      <c r="AS22" s="115"/>
+      <c r="AT22" s="115"/>
+      <c r="AU22" s="115"/>
+      <c r="AV22" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,13,0))</f>
         <v/>
       </c>
-      <c r="AW22" s="167"/>
-      <c r="AX22" s="167"/>
-      <c r="AY22" s="167"/>
-      <c r="AZ22" s="169"/>
+      <c r="AW22" s="115"/>
+      <c r="AX22" s="115"/>
+      <c r="AY22" s="115"/>
+      <c r="AZ22" s="116"/>
       <c r="BC22" s="29"/>
       <c r="BD22" s="31"/>
       <c r="BE22" s="31"/>
@@ -6469,87 +6455,87 @@
       <c r="BJ22" s="29"/>
     </row>
     <row r="23" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="223" t="s">
+      <c r="A23" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="224"/>
-      <c r="C23" s="224"/>
-      <c r="D23" s="224"/>
-      <c r="E23" s="224"/>
-      <c r="F23" s="224"/>
-      <c r="G23" s="224"/>
-      <c r="H23" s="224"/>
-      <c r="I23" s="224"/>
-      <c r="J23" s="224"/>
-      <c r="K23" s="224"/>
-      <c r="L23" s="225"/>
-      <c r="M23" s="217" t="str">
+      <c r="B23" s="133"/>
+      <c r="C23" s="133"/>
+      <c r="D23" s="133"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="133"/>
+      <c r="I23" s="133"/>
+      <c r="J23" s="133"/>
+      <c r="K23" s="133"/>
+      <c r="L23" s="134"/>
+      <c r="M23" s="124" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="N23" s="167"/>
-      <c r="O23" s="167"/>
-      <c r="P23" s="167"/>
-      <c r="Q23" s="167"/>
-      <c r="R23" s="167" t="str">
+      <c r="N23" s="115"/>
+      <c r="O23" s="115"/>
+      <c r="P23" s="115"/>
+      <c r="Q23" s="115"/>
+      <c r="R23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="S23" s="167"/>
-      <c r="T23" s="167"/>
-      <c r="U23" s="167"/>
-      <c r="V23" s="167"/>
-      <c r="W23" s="167" t="str">
+      <c r="S23" s="115"/>
+      <c r="T23" s="115"/>
+      <c r="U23" s="115"/>
+      <c r="V23" s="115"/>
+      <c r="W23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="X23" s="167"/>
-      <c r="Y23" s="167"/>
-      <c r="Z23" s="167"/>
-      <c r="AA23" s="167"/>
-      <c r="AB23" s="167" t="str">
+      <c r="X23" s="115"/>
+      <c r="Y23" s="115"/>
+      <c r="Z23" s="115"/>
+      <c r="AA23" s="115"/>
+      <c r="AB23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AC23" s="167"/>
-      <c r="AD23" s="167"/>
-      <c r="AE23" s="167"/>
-      <c r="AF23" s="167"/>
-      <c r="AG23" s="167" t="str">
+      <c r="AC23" s="115"/>
+      <c r="AD23" s="115"/>
+      <c r="AE23" s="115"/>
+      <c r="AF23" s="115"/>
+      <c r="AG23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AH23" s="167"/>
-      <c r="AI23" s="167"/>
-      <c r="AJ23" s="167"/>
-      <c r="AK23" s="167"/>
-      <c r="AL23" s="167" t="str">
+      <c r="AH23" s="115"/>
+      <c r="AI23" s="115"/>
+      <c r="AJ23" s="115"/>
+      <c r="AK23" s="115"/>
+      <c r="AL23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AM23" s="167"/>
-      <c r="AN23" s="167"/>
-      <c r="AO23" s="167"/>
-      <c r="AP23" s="167"/>
-      <c r="AQ23" s="167" t="str">
+      <c r="AM23" s="115"/>
+      <c r="AN23" s="115"/>
+      <c r="AO23" s="115"/>
+      <c r="AP23" s="115"/>
+      <c r="AQ23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AR23" s="167"/>
-      <c r="AS23" s="167"/>
-      <c r="AT23" s="167"/>
-      <c r="AU23" s="167"/>
-      <c r="AV23" s="167" t="str">
+      <c r="AR23" s="115"/>
+      <c r="AS23" s="115"/>
+      <c r="AT23" s="115"/>
+      <c r="AU23" s="115"/>
+      <c r="AV23" s="115" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,14,0))</f>
         <v/>
       </c>
-      <c r="AW23" s="167"/>
-      <c r="AX23" s="167"/>
-      <c r="AY23" s="167"/>
-      <c r="AZ23" s="169"/>
+      <c r="AW23" s="115"/>
+      <c r="AX23" s="115"/>
+      <c r="AY23" s="115"/>
+      <c r="AZ23" s="116"/>
       <c r="BC23" s="32"/>
-      <c r="BD23" s="90"/>
-      <c r="BE23" s="90"/>
+      <c r="BD23" s="229"/>
+      <c r="BE23" s="229"/>
       <c r="BF23" s="32"/>
       <c r="BG23" s="32"/>
       <c r="BH23" s="32"/>
@@ -6557,84 +6543,84 @@
       <c r="BJ23" s="32"/>
     </row>
     <row r="24" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="223" t="s">
+      <c r="A24" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="224"/>
-      <c r="C24" s="224"/>
-      <c r="D24" s="224"/>
-      <c r="E24" s="224"/>
-      <c r="F24" s="224"/>
-      <c r="G24" s="224"/>
-      <c r="H24" s="224"/>
-      <c r="I24" s="224"/>
-      <c r="J24" s="224"/>
-      <c r="K24" s="224"/>
-      <c r="L24" s="225"/>
-      <c r="M24" s="218" t="str">
+      <c r="B24" s="133"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="133"/>
+      <c r="I24" s="133"/>
+      <c r="J24" s="133"/>
+      <c r="K24" s="133"/>
+      <c r="L24" s="134"/>
+      <c r="M24" s="125" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="N24" s="160"/>
-      <c r="O24" s="160"/>
-      <c r="P24" s="160"/>
-      <c r="Q24" s="160"/>
-      <c r="R24" s="160" t="str">
+      <c r="N24" s="126"/>
+      <c r="O24" s="126"/>
+      <c r="P24" s="126"/>
+      <c r="Q24" s="126"/>
+      <c r="R24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="S24" s="160"/>
-      <c r="T24" s="160"/>
-      <c r="U24" s="160"/>
-      <c r="V24" s="160"/>
-      <c r="W24" s="160" t="str">
+      <c r="S24" s="126"/>
+      <c r="T24" s="126"/>
+      <c r="U24" s="126"/>
+      <c r="V24" s="126"/>
+      <c r="W24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="X24" s="160"/>
-      <c r="Y24" s="160"/>
-      <c r="Z24" s="160"/>
-      <c r="AA24" s="160"/>
-      <c r="AB24" s="160" t="str">
+      <c r="X24" s="126"/>
+      <c r="Y24" s="126"/>
+      <c r="Z24" s="126"/>
+      <c r="AA24" s="126"/>
+      <c r="AB24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AC24" s="160"/>
-      <c r="AD24" s="160"/>
-      <c r="AE24" s="160"/>
-      <c r="AF24" s="160"/>
-      <c r="AG24" s="160" t="str">
+      <c r="AC24" s="126"/>
+      <c r="AD24" s="126"/>
+      <c r="AE24" s="126"/>
+      <c r="AF24" s="126"/>
+      <c r="AG24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AH24" s="160"/>
-      <c r="AI24" s="160"/>
-      <c r="AJ24" s="160"/>
-      <c r="AK24" s="160"/>
-      <c r="AL24" s="160" t="str">
+      <c r="AH24" s="126"/>
+      <c r="AI24" s="126"/>
+      <c r="AJ24" s="126"/>
+      <c r="AK24" s="126"/>
+      <c r="AL24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AM24" s="160"/>
-      <c r="AN24" s="160"/>
-      <c r="AO24" s="160"/>
-      <c r="AP24" s="160"/>
-      <c r="AQ24" s="160" t="str">
+      <c r="AM24" s="126"/>
+      <c r="AN24" s="126"/>
+      <c r="AO24" s="126"/>
+      <c r="AP24" s="126"/>
+      <c r="AQ24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AR24" s="160"/>
-      <c r="AS24" s="160"/>
-      <c r="AT24" s="160"/>
-      <c r="AU24" s="160"/>
-      <c r="AV24" s="160" t="str">
+      <c r="AR24" s="126"/>
+      <c r="AS24" s="126"/>
+      <c r="AT24" s="126"/>
+      <c r="AU24" s="126"/>
+      <c r="AV24" s="126" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,10,0))</f>
         <v/>
       </c>
-      <c r="AW24" s="160"/>
-      <c r="AX24" s="160"/>
-      <c r="AY24" s="160"/>
-      <c r="AZ24" s="161"/>
+      <c r="AW24" s="126"/>
+      <c r="AX24" s="126"/>
+      <c r="AY24" s="126"/>
+      <c r="AZ24" s="193"/>
       <c r="BC24" s="29"/>
       <c r="BD24" s="31"/>
       <c r="BE24" s="31"/>
@@ -6645,87 +6631,87 @@
       <c r="BJ24" s="29"/>
     </row>
     <row r="25" spans="1:62" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="226" t="s">
+      <c r="A25" s="111" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="227"/>
-      <c r="C25" s="227"/>
-      <c r="D25" s="227"/>
-      <c r="E25" s="227"/>
-      <c r="F25" s="227"/>
-      <c r="G25" s="227"/>
-      <c r="H25" s="227"/>
-      <c r="I25" s="227"/>
-      <c r="J25" s="227"/>
-      <c r="K25" s="227"/>
-      <c r="L25" s="228"/>
-      <c r="M25" s="219" t="str">
+      <c r="B25" s="112"/>
+      <c r="C25" s="112"/>
+      <c r="D25" s="112"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="112"/>
+      <c r="H25" s="112"/>
+      <c r="I25" s="112"/>
+      <c r="J25" s="112"/>
+      <c r="K25" s="112"/>
+      <c r="L25" s="135"/>
+      <c r="M25" s="127" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="N25" s="159"/>
-      <c r="O25" s="159"/>
-      <c r="P25" s="159"/>
-      <c r="Q25" s="159"/>
-      <c r="R25" s="159" t="str">
+      <c r="N25" s="128"/>
+      <c r="O25" s="128"/>
+      <c r="P25" s="128"/>
+      <c r="Q25" s="128"/>
+      <c r="R25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="S25" s="159"/>
-      <c r="T25" s="159"/>
-      <c r="U25" s="159"/>
-      <c r="V25" s="159"/>
-      <c r="W25" s="159" t="str">
+      <c r="S25" s="128"/>
+      <c r="T25" s="128"/>
+      <c r="U25" s="128"/>
+      <c r="V25" s="128"/>
+      <c r="W25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="X25" s="159"/>
-      <c r="Y25" s="159"/>
-      <c r="Z25" s="159"/>
-      <c r="AA25" s="159"/>
-      <c r="AB25" s="159" t="str">
+      <c r="X25" s="128"/>
+      <c r="Y25" s="128"/>
+      <c r="Z25" s="128"/>
+      <c r="AA25" s="128"/>
+      <c r="AB25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AC25" s="159"/>
-      <c r="AD25" s="159"/>
-      <c r="AE25" s="159"/>
-      <c r="AF25" s="159"/>
-      <c r="AG25" s="159" t="str">
+      <c r="AC25" s="128"/>
+      <c r="AD25" s="128"/>
+      <c r="AE25" s="128"/>
+      <c r="AF25" s="128"/>
+      <c r="AG25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AH25" s="159"/>
-      <c r="AI25" s="159"/>
-      <c r="AJ25" s="159"/>
-      <c r="AK25" s="159"/>
-      <c r="AL25" s="159" t="str">
+      <c r="AH25" s="128"/>
+      <c r="AI25" s="128"/>
+      <c r="AJ25" s="128"/>
+      <c r="AK25" s="128"/>
+      <c r="AL25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AM25" s="159"/>
-      <c r="AN25" s="159"/>
-      <c r="AO25" s="159"/>
-      <c r="AP25" s="159"/>
-      <c r="AQ25" s="159" t="str">
+      <c r="AM25" s="128"/>
+      <c r="AN25" s="128"/>
+      <c r="AO25" s="128"/>
+      <c r="AP25" s="128"/>
+      <c r="AQ25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AR25" s="159"/>
-      <c r="AS25" s="159"/>
-      <c r="AT25" s="159"/>
-      <c r="AU25" s="159"/>
-      <c r="AV25" s="159" t="str">
+      <c r="AR25" s="128"/>
+      <c r="AS25" s="128"/>
+      <c r="AT25" s="128"/>
+      <c r="AU25" s="128"/>
+      <c r="AV25" s="128" t="str">
         <f>IF(G5="","",VLOOKUP(G5,'KM e Tempo Percurso'!A7:O201,11,0))</f>
         <v/>
       </c>
-      <c r="AW25" s="159"/>
-      <c r="AX25" s="159"/>
-      <c r="AY25" s="159"/>
-      <c r="AZ25" s="162"/>
+      <c r="AW25" s="128"/>
+      <c r="AX25" s="128"/>
+      <c r="AY25" s="128"/>
+      <c r="AZ25" s="194"/>
       <c r="BC25" s="29"/>
-      <c r="BD25" s="90"/>
-      <c r="BE25" s="90"/>
+      <c r="BD25" s="229"/>
+      <c r="BE25" s="229"/>
       <c r="BF25" s="29"/>
       <c r="BG25" s="29"/>
       <c r="BH25" s="29"/>
@@ -6733,1150 +6719,1150 @@
       <c r="BJ25" s="29"/>
     </row>
     <row r="26" spans="1:62" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="148"/>
-      <c r="B26" s="148"/>
-      <c r="C26" s="148"/>
-      <c r="D26" s="148"/>
-      <c r="E26" s="148"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="148"/>
-      <c r="H26" s="148"/>
-      <c r="I26" s="148"/>
-      <c r="J26" s="148"/>
-      <c r="K26" s="148"/>
-      <c r="L26" s="148"/>
-      <c r="M26" s="148"/>
-      <c r="N26" s="148"/>
-      <c r="O26" s="148"/>
-      <c r="P26" s="148"/>
-      <c r="Q26" s="148"/>
-      <c r="R26" s="148"/>
-      <c r="S26" s="148"/>
-      <c r="T26" s="148"/>
-      <c r="U26" s="148"/>
-      <c r="V26" s="148"/>
-      <c r="W26" s="148"/>
-      <c r="X26" s="148"/>
-      <c r="Y26" s="148"/>
-      <c r="Z26" s="148"/>
-      <c r="AA26" s="148"/>
-      <c r="AB26" s="148"/>
-      <c r="AC26" s="148"/>
-      <c r="AD26" s="148"/>
-      <c r="AE26" s="148"/>
-      <c r="AF26" s="148"/>
-      <c r="AG26" s="148"/>
-      <c r="AH26" s="148"/>
-      <c r="AI26" s="148"/>
-      <c r="AJ26" s="148"/>
-      <c r="AK26" s="148"/>
-      <c r="AL26" s="148"/>
-      <c r="AM26" s="148"/>
-      <c r="AN26" s="148"/>
-      <c r="AO26" s="148"/>
-      <c r="AP26" s="148"/>
-      <c r="AQ26" s="148"/>
-      <c r="AR26" s="148"/>
-      <c r="AS26" s="148"/>
-      <c r="AT26" s="148"/>
-      <c r="AU26" s="148"/>
-      <c r="AV26" s="148"/>
-      <c r="AW26" s="148"/>
-      <c r="AX26" s="148"/>
-      <c r="AY26" s="148"/>
-      <c r="AZ26" s="148"/>
+      <c r="A26" s="99"/>
+      <c r="B26" s="99"/>
+      <c r="C26" s="99"/>
+      <c r="D26" s="99"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="99"/>
+      <c r="H26" s="99"/>
+      <c r="I26" s="99"/>
+      <c r="J26" s="99"/>
+      <c r="K26" s="99"/>
+      <c r="L26" s="99"/>
+      <c r="M26" s="99"/>
+      <c r="N26" s="99"/>
+      <c r="O26" s="99"/>
+      <c r="P26" s="99"/>
+      <c r="Q26" s="99"/>
+      <c r="R26" s="99"/>
+      <c r="S26" s="99"/>
+      <c r="T26" s="99"/>
+      <c r="U26" s="99"/>
+      <c r="V26" s="99"/>
+      <c r="W26" s="99"/>
+      <c r="X26" s="99"/>
+      <c r="Y26" s="99"/>
+      <c r="Z26" s="99"/>
+      <c r="AA26" s="99"/>
+      <c r="AB26" s="99"/>
+      <c r="AC26" s="99"/>
+      <c r="AD26" s="99"/>
+      <c r="AE26" s="99"/>
+      <c r="AF26" s="99"/>
+      <c r="AG26" s="99"/>
+      <c r="AH26" s="99"/>
+      <c r="AI26" s="99"/>
+      <c r="AJ26" s="99"/>
+      <c r="AK26" s="99"/>
+      <c r="AL26" s="99"/>
+      <c r="AM26" s="99"/>
+      <c r="AN26" s="99"/>
+      <c r="AO26" s="99"/>
+      <c r="AP26" s="99"/>
+      <c r="AQ26" s="99"/>
+      <c r="AR26" s="99"/>
+      <c r="AS26" s="99"/>
+      <c r="AT26" s="99"/>
+      <c r="AU26" s="99"/>
+      <c r="AV26" s="99"/>
+      <c r="AW26" s="99"/>
+      <c r="AX26" s="99"/>
+      <c r="AY26" s="99"/>
+      <c r="AZ26" s="99"/>
     </row>
     <row r="27" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="191" t="s">
+      <c r="A27" s="100" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="192"/>
-      <c r="C27" s="192"/>
-      <c r="D27" s="192"/>
-      <c r="E27" s="192"/>
-      <c r="F27" s="192"/>
-      <c r="G27" s="192"/>
-      <c r="H27" s="192"/>
-      <c r="I27" s="192"/>
-      <c r="J27" s="192"/>
-      <c r="K27" s="192"/>
-      <c r="L27" s="192"/>
-      <c r="M27" s="192"/>
-      <c r="N27" s="192"/>
-      <c r="O27" s="192"/>
-      <c r="P27" s="192"/>
-      <c r="Q27" s="192"/>
-      <c r="R27" s="192"/>
-      <c r="S27" s="192"/>
-      <c r="T27" s="192"/>
-      <c r="U27" s="192"/>
-      <c r="V27" s="192"/>
-      <c r="W27" s="192"/>
-      <c r="X27" s="192"/>
-      <c r="Y27" s="192"/>
-      <c r="Z27" s="192"/>
-      <c r="AA27" s="192"/>
-      <c r="AB27" s="192"/>
-      <c r="AC27" s="192"/>
-      <c r="AD27" s="192"/>
-      <c r="AE27" s="192"/>
-      <c r="AF27" s="192"/>
-      <c r="AG27" s="192"/>
-      <c r="AH27" s="192"/>
-      <c r="AI27" s="192"/>
-      <c r="AJ27" s="192"/>
-      <c r="AK27" s="192"/>
-      <c r="AL27" s="192"/>
-      <c r="AM27" s="192"/>
-      <c r="AN27" s="192"/>
-      <c r="AO27" s="192"/>
-      <c r="AP27" s="192"/>
-      <c r="AQ27" s="192"/>
-      <c r="AR27" s="192"/>
-      <c r="AS27" s="192"/>
-      <c r="AT27" s="192"/>
-      <c r="AU27" s="192"/>
-      <c r="AV27" s="192"/>
-      <c r="AW27" s="192"/>
-      <c r="AX27" s="192"/>
-      <c r="AY27" s="192"/>
-      <c r="AZ27" s="193"/>
-    </row>
-    <row r="28" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="235" t="s">
+      <c r="B27" s="101"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="101"/>
+      <c r="F27" s="101"/>
+      <c r="G27" s="101"/>
+      <c r="H27" s="101"/>
+      <c r="I27" s="101"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="101"/>
+      <c r="L27" s="101"/>
+      <c r="M27" s="101"/>
+      <c r="N27" s="101"/>
+      <c r="O27" s="101"/>
+      <c r="P27" s="101"/>
+      <c r="Q27" s="101"/>
+      <c r="R27" s="101"/>
+      <c r="S27" s="101"/>
+      <c r="T27" s="101"/>
+      <c r="U27" s="101"/>
+      <c r="V27" s="101"/>
+      <c r="W27" s="101"/>
+      <c r="X27" s="101"/>
+      <c r="Y27" s="101"/>
+      <c r="Z27" s="101"/>
+      <c r="AA27" s="101"/>
+      <c r="AB27" s="101"/>
+      <c r="AC27" s="101"/>
+      <c r="AD27" s="101"/>
+      <c r="AE27" s="101"/>
+      <c r="AF27" s="101"/>
+      <c r="AG27" s="101"/>
+      <c r="AH27" s="101"/>
+      <c r="AI27" s="101"/>
+      <c r="AJ27" s="101"/>
+      <c r="AK27" s="101"/>
+      <c r="AL27" s="101"/>
+      <c r="AM27" s="101"/>
+      <c r="AN27" s="101"/>
+      <c r="AO27" s="101"/>
+      <c r="AP27" s="101"/>
+      <c r="AQ27" s="101"/>
+      <c r="AR27" s="101"/>
+      <c r="AS27" s="101"/>
+      <c r="AT27" s="101"/>
+      <c r="AU27" s="101"/>
+      <c r="AV27" s="101"/>
+      <c r="AW27" s="101"/>
+      <c r="AX27" s="101"/>
+      <c r="AY27" s="101"/>
+      <c r="AZ27" s="102"/>
+    </row>
+    <row r="28" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="236"/>
-      <c r="C28" s="236"/>
-      <c r="D28" s="236"/>
-      <c r="E28" s="236"/>
-      <c r="F28" s="236"/>
-      <c r="G28" s="236"/>
-      <c r="H28" s="236"/>
-      <c r="I28" s="236"/>
-      <c r="J28" s="236"/>
-      <c r="K28" s="236"/>
-      <c r="L28" s="236"/>
-      <c r="M28" s="236"/>
-      <c r="N28" s="236"/>
-      <c r="O28" s="236"/>
-      <c r="P28" s="236"/>
-      <c r="Q28" s="236"/>
-      <c r="R28" s="236"/>
-      <c r="S28" s="236"/>
-      <c r="T28" s="237" t="s">
+      <c r="B28" s="104"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="104"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="104"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="104"/>
+      <c r="N28" s="104"/>
+      <c r="O28" s="104"/>
+      <c r="P28" s="104"/>
+      <c r="Q28" s="104"/>
+      <c r="R28" s="104"/>
+      <c r="S28" s="104"/>
+      <c r="T28" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="U28" s="237"/>
-      <c r="V28" s="237"/>
-      <c r="W28" s="237"/>
-      <c r="X28" s="237"/>
-      <c r="Y28" s="237"/>
-      <c r="Z28" s="237"/>
-      <c r="AA28" s="236" t="s">
+      <c r="U28" s="105"/>
+      <c r="V28" s="105"/>
+      <c r="W28" s="105"/>
+      <c r="X28" s="105"/>
+      <c r="Y28" s="105"/>
+      <c r="Z28" s="105"/>
+      <c r="AA28" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="AB28" s="236"/>
-      <c r="AC28" s="236"/>
-      <c r="AD28" s="236"/>
-      <c r="AE28" s="236"/>
-      <c r="AF28" s="236"/>
-      <c r="AG28" s="236"/>
-      <c r="AH28" s="236"/>
-      <c r="AI28" s="236"/>
-      <c r="AJ28" s="236"/>
-      <c r="AK28" s="236"/>
-      <c r="AL28" s="236"/>
-      <c r="AM28" s="236"/>
-      <c r="AN28" s="236"/>
-      <c r="AO28" s="236"/>
-      <c r="AP28" s="236"/>
-      <c r="AQ28" s="236"/>
-      <c r="AR28" s="236"/>
-      <c r="AS28" s="236"/>
-      <c r="AT28" s="237" t="s">
+      <c r="AB28" s="104"/>
+      <c r="AC28" s="104"/>
+      <c r="AD28" s="104"/>
+      <c r="AE28" s="104"/>
+      <c r="AF28" s="104"/>
+      <c r="AG28" s="104"/>
+      <c r="AH28" s="104"/>
+      <c r="AI28" s="104"/>
+      <c r="AJ28" s="104"/>
+      <c r="AK28" s="104"/>
+      <c r="AL28" s="104"/>
+      <c r="AM28" s="104"/>
+      <c r="AN28" s="104"/>
+      <c r="AO28" s="104"/>
+      <c r="AP28" s="104"/>
+      <c r="AQ28" s="104"/>
+      <c r="AR28" s="104"/>
+      <c r="AS28" s="104"/>
+      <c r="AT28" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="AU28" s="237"/>
-      <c r="AV28" s="237"/>
-      <c r="AW28" s="237"/>
-      <c r="AX28" s="237"/>
-      <c r="AY28" s="237"/>
-      <c r="AZ28" s="238"/>
-    </row>
-    <row r="29" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="239" t="s">
+      <c r="AU28" s="105"/>
+      <c r="AV28" s="105"/>
+      <c r="AW28" s="105"/>
+      <c r="AX28" s="105"/>
+      <c r="AY28" s="105"/>
+      <c r="AZ28" s="106"/>
+    </row>
+    <row r="29" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="107" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="240"/>
-      <c r="C29" s="240"/>
-      <c r="D29" s="240"/>
-      <c r="E29" s="240"/>
-      <c r="F29" s="240"/>
-      <c r="G29" s="240"/>
-      <c r="H29" s="240"/>
-      <c r="I29" s="240"/>
-      <c r="J29" s="240"/>
-      <c r="K29" s="240"/>
-      <c r="L29" s="240"/>
-      <c r="M29" s="240"/>
-      <c r="N29" s="240"/>
-      <c r="O29" s="240"/>
-      <c r="P29" s="240"/>
-      <c r="Q29" s="240"/>
-      <c r="R29" s="240"/>
-      <c r="S29" s="240"/>
-      <c r="T29" s="241"/>
-      <c r="U29" s="241"/>
-      <c r="V29" s="241"/>
-      <c r="W29" s="241"/>
-      <c r="X29" s="241"/>
-      <c r="Y29" s="241"/>
-      <c r="Z29" s="241"/>
-      <c r="AA29" s="240" t="s">
+      <c r="B29" s="108"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="108"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="108"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="108"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="108"/>
+      <c r="K29" s="108"/>
+      <c r="L29" s="108"/>
+      <c r="M29" s="108"/>
+      <c r="N29" s="108"/>
+      <c r="O29" s="108"/>
+      <c r="P29" s="108"/>
+      <c r="Q29" s="108"/>
+      <c r="R29" s="108"/>
+      <c r="S29" s="108"/>
+      <c r="T29" s="109"/>
+      <c r="U29" s="109"/>
+      <c r="V29" s="109"/>
+      <c r="W29" s="109"/>
+      <c r="X29" s="109"/>
+      <c r="Y29" s="109"/>
+      <c r="Z29" s="109"/>
+      <c r="AA29" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="AB29" s="240"/>
-      <c r="AC29" s="240"/>
-      <c r="AD29" s="240"/>
-      <c r="AE29" s="240"/>
-      <c r="AF29" s="240"/>
-      <c r="AG29" s="240"/>
-      <c r="AH29" s="240"/>
-      <c r="AI29" s="240"/>
-      <c r="AJ29" s="240"/>
-      <c r="AK29" s="240"/>
-      <c r="AL29" s="240"/>
-      <c r="AM29" s="240"/>
-      <c r="AN29" s="240"/>
-      <c r="AO29" s="240"/>
-      <c r="AP29" s="240"/>
-      <c r="AQ29" s="240"/>
-      <c r="AR29" s="240"/>
-      <c r="AS29" s="240"/>
-      <c r="AT29" s="241"/>
-      <c r="AU29" s="241"/>
-      <c r="AV29" s="241"/>
-      <c r="AW29" s="241"/>
-      <c r="AX29" s="241"/>
-      <c r="AY29" s="241"/>
-      <c r="AZ29" s="289"/>
+      <c r="AB29" s="108"/>
+      <c r="AC29" s="108"/>
+      <c r="AD29" s="108"/>
+      <c r="AE29" s="108"/>
+      <c r="AF29" s="108"/>
+      <c r="AG29" s="108"/>
+      <c r="AH29" s="108"/>
+      <c r="AI29" s="108"/>
+      <c r="AJ29" s="108"/>
+      <c r="AK29" s="108"/>
+      <c r="AL29" s="108"/>
+      <c r="AM29" s="108"/>
+      <c r="AN29" s="108"/>
+      <c r="AO29" s="108"/>
+      <c r="AP29" s="108"/>
+      <c r="AQ29" s="108"/>
+      <c r="AR29" s="108"/>
+      <c r="AS29" s="108"/>
+      <c r="AT29" s="181"/>
+      <c r="AU29" s="181"/>
+      <c r="AV29" s="181"/>
+      <c r="AW29" s="181"/>
+      <c r="AX29" s="181"/>
+      <c r="AY29" s="181"/>
+      <c r="AZ29" s="181"/>
     </row>
     <row r="30" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="239" t="s">
+      <c r="A30" s="107" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="240"/>
-      <c r="C30" s="240"/>
-      <c r="D30" s="240"/>
-      <c r="E30" s="240"/>
-      <c r="F30" s="240"/>
-      <c r="G30" s="240"/>
-      <c r="H30" s="240"/>
-      <c r="I30" s="240"/>
-      <c r="J30" s="240"/>
-      <c r="K30" s="240"/>
-      <c r="L30" s="240"/>
-      <c r="M30" s="240"/>
-      <c r="N30" s="240"/>
-      <c r="O30" s="240"/>
-      <c r="P30" s="240"/>
-      <c r="Q30" s="240"/>
-      <c r="R30" s="240"/>
-      <c r="S30" s="240"/>
-      <c r="T30" s="241"/>
-      <c r="U30" s="241"/>
-      <c r="V30" s="241"/>
-      <c r="W30" s="241"/>
-      <c r="X30" s="241"/>
-      <c r="Y30" s="241"/>
-      <c r="Z30" s="241"/>
-      <c r="AA30" s="240" t="s">
+      <c r="B30" s="108"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="108"/>
+      <c r="I30" s="108"/>
+      <c r="J30" s="108"/>
+      <c r="K30" s="108"/>
+      <c r="L30" s="108"/>
+      <c r="M30" s="108"/>
+      <c r="N30" s="108"/>
+      <c r="O30" s="108"/>
+      <c r="P30" s="108"/>
+      <c r="Q30" s="108"/>
+      <c r="R30" s="108"/>
+      <c r="S30" s="108"/>
+      <c r="T30" s="109"/>
+      <c r="U30" s="109"/>
+      <c r="V30" s="109"/>
+      <c r="W30" s="109"/>
+      <c r="X30" s="109"/>
+      <c r="Y30" s="109"/>
+      <c r="Z30" s="109"/>
+      <c r="AA30" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="AB30" s="240"/>
-      <c r="AC30" s="240"/>
-      <c r="AD30" s="240"/>
-      <c r="AE30" s="240"/>
-      <c r="AF30" s="240"/>
-      <c r="AG30" s="240"/>
-      <c r="AH30" s="240"/>
-      <c r="AI30" s="240"/>
-      <c r="AJ30" s="240"/>
-      <c r="AK30" s="240"/>
-      <c r="AL30" s="240"/>
-      <c r="AM30" s="240"/>
-      <c r="AN30" s="240"/>
-      <c r="AO30" s="240"/>
-      <c r="AP30" s="240"/>
-      <c r="AQ30" s="240"/>
-      <c r="AR30" s="240"/>
-      <c r="AS30" s="240"/>
-      <c r="AT30" s="241"/>
-      <c r="AU30" s="241"/>
-      <c r="AV30" s="241"/>
-      <c r="AW30" s="241"/>
-      <c r="AX30" s="241"/>
-      <c r="AY30" s="241"/>
-      <c r="AZ30" s="242"/>
+      <c r="AB30" s="108"/>
+      <c r="AC30" s="108"/>
+      <c r="AD30" s="108"/>
+      <c r="AE30" s="108"/>
+      <c r="AF30" s="108"/>
+      <c r="AG30" s="108"/>
+      <c r="AH30" s="108"/>
+      <c r="AI30" s="108"/>
+      <c r="AJ30" s="108"/>
+      <c r="AK30" s="108"/>
+      <c r="AL30" s="108"/>
+      <c r="AM30" s="108"/>
+      <c r="AN30" s="108"/>
+      <c r="AO30" s="108"/>
+      <c r="AP30" s="108"/>
+      <c r="AQ30" s="108"/>
+      <c r="AR30" s="108"/>
+      <c r="AS30" s="108"/>
+      <c r="AT30" s="109"/>
+      <c r="AU30" s="109"/>
+      <c r="AV30" s="109"/>
+      <c r="AW30" s="109"/>
+      <c r="AX30" s="109"/>
+      <c r="AY30" s="109"/>
+      <c r="AZ30" s="110"/>
     </row>
     <row r="31" spans="1:62" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="226" t="s">
+      <c r="A31" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="227"/>
-      <c r="C31" s="227"/>
-      <c r="D31" s="227"/>
-      <c r="E31" s="227"/>
-      <c r="F31" s="227"/>
-      <c r="G31" s="227"/>
-      <c r="H31" s="227"/>
-      <c r="I31" s="227"/>
-      <c r="J31" s="227"/>
-      <c r="K31" s="227"/>
-      <c r="L31" s="227"/>
-      <c r="M31" s="227"/>
-      <c r="N31" s="227"/>
-      <c r="O31" s="227"/>
-      <c r="P31" s="227"/>
-      <c r="Q31" s="227"/>
-      <c r="R31" s="227"/>
-      <c r="S31" s="227"/>
-      <c r="T31" s="243"/>
-      <c r="U31" s="243"/>
-      <c r="V31" s="243"/>
-      <c r="W31" s="243"/>
-      <c r="X31" s="243"/>
-      <c r="Y31" s="243"/>
-      <c r="Z31" s="243"/>
-      <c r="AA31" s="227" t="s">
+      <c r="B31" s="112"/>
+      <c r="C31" s="112"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="112"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="112"/>
+      <c r="J31" s="112"/>
+      <c r="K31" s="112"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="112"/>
+      <c r="R31" s="112"/>
+      <c r="S31" s="112"/>
+      <c r="T31" s="113"/>
+      <c r="U31" s="113"/>
+      <c r="V31" s="113"/>
+      <c r="W31" s="113"/>
+      <c r="X31" s="113"/>
+      <c r="Y31" s="113"/>
+      <c r="Z31" s="113"/>
+      <c r="AA31" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="AB31" s="227"/>
-      <c r="AC31" s="227"/>
-      <c r="AD31" s="227"/>
-      <c r="AE31" s="227"/>
-      <c r="AF31" s="227"/>
-      <c r="AG31" s="227"/>
-      <c r="AH31" s="227"/>
-      <c r="AI31" s="227"/>
-      <c r="AJ31" s="227"/>
-      <c r="AK31" s="227"/>
-      <c r="AL31" s="227"/>
-      <c r="AM31" s="227"/>
-      <c r="AN31" s="227"/>
-      <c r="AO31" s="227"/>
-      <c r="AP31" s="227"/>
-      <c r="AQ31" s="227"/>
-      <c r="AR31" s="227"/>
-      <c r="AS31" s="227"/>
-      <c r="AT31" s="243"/>
-      <c r="AU31" s="243"/>
-      <c r="AV31" s="243"/>
-      <c r="AW31" s="243"/>
-      <c r="AX31" s="243"/>
-      <c r="AY31" s="243"/>
-      <c r="AZ31" s="244"/>
+      <c r="AB31" s="112"/>
+      <c r="AC31" s="112"/>
+      <c r="AD31" s="112"/>
+      <c r="AE31" s="112"/>
+      <c r="AF31" s="112"/>
+      <c r="AG31" s="112"/>
+      <c r="AH31" s="112"/>
+      <c r="AI31" s="112"/>
+      <c r="AJ31" s="112"/>
+      <c r="AK31" s="112"/>
+      <c r="AL31" s="112"/>
+      <c r="AM31" s="112"/>
+      <c r="AN31" s="112"/>
+      <c r="AO31" s="112"/>
+      <c r="AP31" s="112"/>
+      <c r="AQ31" s="112"/>
+      <c r="AR31" s="112"/>
+      <c r="AS31" s="112"/>
+      <c r="AT31" s="113"/>
+      <c r="AU31" s="113"/>
+      <c r="AV31" s="113"/>
+      <c r="AW31" s="113"/>
+      <c r="AX31" s="113"/>
+      <c r="AY31" s="113"/>
+      <c r="AZ31" s="114"/>
     </row>
     <row r="32" spans="1:62" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="234"/>
-      <c r="B32" s="234"/>
-      <c r="C32" s="234"/>
-      <c r="D32" s="234"/>
-      <c r="E32" s="234"/>
-      <c r="F32" s="234"/>
-      <c r="G32" s="234"/>
-      <c r="H32" s="234"/>
-      <c r="I32" s="234"/>
-      <c r="J32" s="234"/>
-      <c r="K32" s="234"/>
-      <c r="L32" s="234"/>
-      <c r="M32" s="234"/>
-      <c r="N32" s="234"/>
-      <c r="O32" s="234"/>
-      <c r="P32" s="234"/>
-      <c r="Q32" s="234"/>
-      <c r="R32" s="234"/>
-      <c r="S32" s="234"/>
-      <c r="T32" s="234"/>
-      <c r="U32" s="234"/>
-      <c r="V32" s="234"/>
-      <c r="W32" s="234"/>
-      <c r="X32" s="234"/>
-      <c r="Y32" s="234"/>
-      <c r="Z32" s="234"/>
-      <c r="AA32" s="234"/>
-      <c r="AB32" s="234"/>
-      <c r="AC32" s="234"/>
-      <c r="AD32" s="234"/>
-      <c r="AE32" s="234"/>
-      <c r="AF32" s="234"/>
-      <c r="AG32" s="234"/>
-      <c r="AH32" s="234"/>
-      <c r="AI32" s="234"/>
-      <c r="AJ32" s="234"/>
-      <c r="AK32" s="234"/>
-      <c r="AL32" s="234"/>
-      <c r="AM32" s="234"/>
-      <c r="AN32" s="234"/>
-      <c r="AO32" s="234"/>
-      <c r="AP32" s="234"/>
-      <c r="AQ32" s="234"/>
-      <c r="AR32" s="234"/>
-      <c r="AS32" s="234"/>
-      <c r="AT32" s="234"/>
-      <c r="AU32" s="234"/>
-      <c r="AV32" s="234"/>
-      <c r="AW32" s="234"/>
-      <c r="AX32" s="234"/>
-      <c r="AY32" s="234"/>
-      <c r="AZ32" s="234"/>
+      <c r="A32" s="98"/>
+      <c r="B32" s="98"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="98"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="98"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="98"/>
+      <c r="N32" s="98"/>
+      <c r="O32" s="98"/>
+      <c r="P32" s="98"/>
+      <c r="Q32" s="98"/>
+      <c r="R32" s="98"/>
+      <c r="S32" s="98"/>
+      <c r="T32" s="98"/>
+      <c r="U32" s="98"/>
+      <c r="V32" s="98"/>
+      <c r="W32" s="98"/>
+      <c r="X32" s="98"/>
+      <c r="Y32" s="98"/>
+      <c r="Z32" s="98"/>
+      <c r="AA32" s="98"/>
+      <c r="AB32" s="98"/>
+      <c r="AC32" s="98"/>
+      <c r="AD32" s="98"/>
+      <c r="AE32" s="98"/>
+      <c r="AF32" s="98"/>
+      <c r="AG32" s="98"/>
+      <c r="AH32" s="98"/>
+      <c r="AI32" s="98"/>
+      <c r="AJ32" s="98"/>
+      <c r="AK32" s="98"/>
+      <c r="AL32" s="98"/>
+      <c r="AM32" s="98"/>
+      <c r="AN32" s="98"/>
+      <c r="AO32" s="98"/>
+      <c r="AP32" s="98"/>
+      <c r="AQ32" s="98"/>
+      <c r="AR32" s="98"/>
+      <c r="AS32" s="98"/>
+      <c r="AT32" s="98"/>
+      <c r="AU32" s="98"/>
+      <c r="AV32" s="98"/>
+      <c r="AW32" s="98"/>
+      <c r="AX32" s="98"/>
+      <c r="AY32" s="98"/>
+      <c r="AZ32" s="98"/>
     </row>
     <row r="33" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="133" t="s">
+      <c r="A33" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="134"/>
-      <c r="C33" s="134"/>
-      <c r="D33" s="134"/>
-      <c r="E33" s="134"/>
-      <c r="F33" s="134"/>
-      <c r="G33" s="134"/>
-      <c r="H33" s="134"/>
-      <c r="I33" s="134"/>
-      <c r="J33" s="134"/>
-      <c r="K33" s="134"/>
-      <c r="L33" s="134"/>
-      <c r="M33" s="134"/>
-      <c r="N33" s="134"/>
-      <c r="O33" s="134"/>
-      <c r="P33" s="134"/>
-      <c r="Q33" s="134"/>
-      <c r="R33" s="135"/>
-      <c r="S33" s="98" t="s">
+      <c r="B33" s="206"/>
+      <c r="C33" s="206"/>
+      <c r="D33" s="206"/>
+      <c r="E33" s="206"/>
+      <c r="F33" s="206"/>
+      <c r="G33" s="206"/>
+      <c r="H33" s="206"/>
+      <c r="I33" s="206"/>
+      <c r="J33" s="206"/>
+      <c r="K33" s="206"/>
+      <c r="L33" s="206"/>
+      <c r="M33" s="206"/>
+      <c r="N33" s="206"/>
+      <c r="O33" s="206"/>
+      <c r="P33" s="206"/>
+      <c r="Q33" s="206"/>
+      <c r="R33" s="207"/>
+      <c r="S33" s="196" t="s">
         <v>56</v>
       </c>
-      <c r="T33" s="99"/>
-      <c r="U33" s="99"/>
-      <c r="V33" s="99"/>
-      <c r="W33" s="99"/>
-      <c r="X33" s="99"/>
-      <c r="Y33" s="99"/>
-      <c r="Z33" s="99"/>
-      <c r="AA33" s="99"/>
-      <c r="AB33" s="99"/>
-      <c r="AC33" s="99"/>
-      <c r="AD33" s="99"/>
-      <c r="AE33" s="99"/>
-      <c r="AF33" s="99"/>
-      <c r="AG33" s="125"/>
-      <c r="AH33" s="98" t="s">
+      <c r="T33" s="197"/>
+      <c r="U33" s="197"/>
+      <c r="V33" s="197"/>
+      <c r="W33" s="197"/>
+      <c r="X33" s="197"/>
+      <c r="Y33" s="197"/>
+      <c r="Z33" s="197"/>
+      <c r="AA33" s="197"/>
+      <c r="AB33" s="197"/>
+      <c r="AC33" s="197"/>
+      <c r="AD33" s="197"/>
+      <c r="AE33" s="197"/>
+      <c r="AF33" s="197"/>
+      <c r="AG33" s="198"/>
+      <c r="AH33" s="196" t="s">
         <v>57</v>
       </c>
-      <c r="AI33" s="99"/>
-      <c r="AJ33" s="99"/>
-      <c r="AK33" s="99"/>
-      <c r="AL33" s="99"/>
-      <c r="AM33" s="99"/>
-      <c r="AN33" s="99"/>
-      <c r="AO33" s="99"/>
-      <c r="AP33" s="99"/>
-      <c r="AQ33" s="99"/>
-      <c r="AR33" s="99"/>
-      <c r="AS33" s="99"/>
-      <c r="AT33" s="99"/>
-      <c r="AU33" s="99"/>
-      <c r="AV33" s="99"/>
-      <c r="AW33" s="99"/>
-      <c r="AX33" s="99"/>
-      <c r="AY33" s="99"/>
-      <c r="AZ33" s="100"/>
+      <c r="AI33" s="197"/>
+      <c r="AJ33" s="197"/>
+      <c r="AK33" s="197"/>
+      <c r="AL33" s="197"/>
+      <c r="AM33" s="197"/>
+      <c r="AN33" s="197"/>
+      <c r="AO33" s="197"/>
+      <c r="AP33" s="197"/>
+      <c r="AQ33" s="197"/>
+      <c r="AR33" s="197"/>
+      <c r="AS33" s="197"/>
+      <c r="AT33" s="197"/>
+      <c r="AU33" s="197"/>
+      <c r="AV33" s="197"/>
+      <c r="AW33" s="197"/>
+      <c r="AX33" s="197"/>
+      <c r="AY33" s="197"/>
+      <c r="AZ33" s="231"/>
     </row>
     <row r="34" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="136"/>
-      <c r="B34" s="137"/>
-      <c r="C34" s="137"/>
-      <c r="D34" s="137"/>
-      <c r="E34" s="137"/>
-      <c r="F34" s="137"/>
-      <c r="G34" s="137"/>
-      <c r="H34" s="137"/>
-      <c r="I34" s="137"/>
-      <c r="J34" s="137"/>
-      <c r="K34" s="137"/>
-      <c r="L34" s="137"/>
-      <c r="M34" s="137"/>
-      <c r="N34" s="137"/>
-      <c r="O34" s="137"/>
-      <c r="P34" s="137"/>
-      <c r="Q34" s="137"/>
-      <c r="R34" s="138"/>
-      <c r="S34" s="101"/>
-      <c r="T34" s="102"/>
-      <c r="U34" s="102"/>
-      <c r="V34" s="102"/>
-      <c r="W34" s="102"/>
-      <c r="X34" s="102"/>
-      <c r="Y34" s="102"/>
-      <c r="Z34" s="102"/>
-      <c r="AA34" s="102"/>
-      <c r="AB34" s="102"/>
-      <c r="AC34" s="102"/>
-      <c r="AD34" s="102"/>
-      <c r="AE34" s="102"/>
-      <c r="AF34" s="102"/>
-      <c r="AG34" s="126"/>
-      <c r="AH34" s="101"/>
-      <c r="AI34" s="102"/>
-      <c r="AJ34" s="102"/>
-      <c r="AK34" s="102"/>
-      <c r="AL34" s="102"/>
-      <c r="AM34" s="102"/>
-      <c r="AN34" s="102"/>
-      <c r="AO34" s="102"/>
-      <c r="AP34" s="102"/>
-      <c r="AQ34" s="102"/>
-      <c r="AR34" s="102"/>
-      <c r="AS34" s="102"/>
-      <c r="AT34" s="102"/>
-      <c r="AU34" s="102"/>
-      <c r="AV34" s="102"/>
-      <c r="AW34" s="102"/>
-      <c r="AX34" s="102"/>
-      <c r="AY34" s="102"/>
-      <c r="AZ34" s="103"/>
+      <c r="A34" s="208"/>
+      <c r="B34" s="209"/>
+      <c r="C34" s="209"/>
+      <c r="D34" s="209"/>
+      <c r="E34" s="209"/>
+      <c r="F34" s="209"/>
+      <c r="G34" s="209"/>
+      <c r="H34" s="209"/>
+      <c r="I34" s="209"/>
+      <c r="J34" s="209"/>
+      <c r="K34" s="209"/>
+      <c r="L34" s="209"/>
+      <c r="M34" s="209"/>
+      <c r="N34" s="209"/>
+      <c r="O34" s="209"/>
+      <c r="P34" s="209"/>
+      <c r="Q34" s="209"/>
+      <c r="R34" s="210"/>
+      <c r="S34" s="199"/>
+      <c r="T34" s="200"/>
+      <c r="U34" s="200"/>
+      <c r="V34" s="200"/>
+      <c r="W34" s="200"/>
+      <c r="X34" s="200"/>
+      <c r="Y34" s="200"/>
+      <c r="Z34" s="200"/>
+      <c r="AA34" s="200"/>
+      <c r="AB34" s="200"/>
+      <c r="AC34" s="200"/>
+      <c r="AD34" s="200"/>
+      <c r="AE34" s="200"/>
+      <c r="AF34" s="200"/>
+      <c r="AG34" s="201"/>
+      <c r="AH34" s="199"/>
+      <c r="AI34" s="200"/>
+      <c r="AJ34" s="200"/>
+      <c r="AK34" s="200"/>
+      <c r="AL34" s="200"/>
+      <c r="AM34" s="200"/>
+      <c r="AN34" s="200"/>
+      <c r="AO34" s="200"/>
+      <c r="AP34" s="200"/>
+      <c r="AQ34" s="200"/>
+      <c r="AR34" s="200"/>
+      <c r="AS34" s="200"/>
+      <c r="AT34" s="200"/>
+      <c r="AU34" s="200"/>
+      <c r="AV34" s="200"/>
+      <c r="AW34" s="200"/>
+      <c r="AX34" s="200"/>
+      <c r="AY34" s="200"/>
+      <c r="AZ34" s="232"/>
     </row>
     <row r="35" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="127" t="s">
+      <c r="A35" s="183" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="128"/>
-      <c r="C35" s="128"/>
-      <c r="D35" s="128"/>
-      <c r="E35" s="128"/>
-      <c r="F35" s="128"/>
-      <c r="G35" s="128"/>
-      <c r="H35" s="128"/>
-      <c r="I35" s="128"/>
-      <c r="J35" s="128"/>
-      <c r="K35" s="128"/>
-      <c r="L35" s="128"/>
-      <c r="M35" s="128"/>
-      <c r="N35" s="128"/>
-      <c r="O35" s="128"/>
-      <c r="P35" s="128"/>
-      <c r="Q35" s="128"/>
-      <c r="R35" s="129"/>
-      <c r="S35" s="130" t="s">
+      <c r="B35" s="184"/>
+      <c r="C35" s="184"/>
+      <c r="D35" s="184"/>
+      <c r="E35" s="184"/>
+      <c r="F35" s="184"/>
+      <c r="G35" s="184"/>
+      <c r="H35" s="184"/>
+      <c r="I35" s="184"/>
+      <c r="J35" s="184"/>
+      <c r="K35" s="184"/>
+      <c r="L35" s="184"/>
+      <c r="M35" s="184"/>
+      <c r="N35" s="184"/>
+      <c r="O35" s="184"/>
+      <c r="P35" s="184"/>
+      <c r="Q35" s="184"/>
+      <c r="R35" s="185"/>
+      <c r="S35" s="189" t="s">
         <v>59</v>
       </c>
-      <c r="T35" s="131"/>
-      <c r="U35" s="131"/>
-      <c r="V35" s="131"/>
-      <c r="W35" s="131"/>
-      <c r="X35" s="131"/>
-      <c r="Y35" s="131"/>
-      <c r="Z35" s="131"/>
-      <c r="AA35" s="131"/>
-      <c r="AB35" s="131"/>
-      <c r="AC35" s="131"/>
-      <c r="AD35" s="131"/>
-      <c r="AE35" s="131"/>
-      <c r="AF35" s="131"/>
-      <c r="AG35" s="132"/>
-      <c r="AH35" s="95" t="s">
+      <c r="T35" s="190"/>
+      <c r="U35" s="190"/>
+      <c r="V35" s="190"/>
+      <c r="W35" s="190"/>
+      <c r="X35" s="190"/>
+      <c r="Y35" s="190"/>
+      <c r="Z35" s="190"/>
+      <c r="AA35" s="190"/>
+      <c r="AB35" s="190"/>
+      <c r="AC35" s="190"/>
+      <c r="AD35" s="190"/>
+      <c r="AE35" s="190"/>
+      <c r="AF35" s="190"/>
+      <c r="AG35" s="191"/>
+      <c r="AH35" s="202" t="s">
         <v>60</v>
       </c>
-      <c r="AI35" s="96"/>
-      <c r="AJ35" s="96"/>
-      <c r="AK35" s="96"/>
-      <c r="AL35" s="96"/>
-      <c r="AM35" s="96"/>
-      <c r="AN35" s="96"/>
-      <c r="AO35" s="96"/>
-      <c r="AP35" s="96"/>
-      <c r="AQ35" s="96"/>
-      <c r="AR35" s="96"/>
-      <c r="AS35" s="96"/>
-      <c r="AT35" s="96"/>
-      <c r="AU35" s="96"/>
-      <c r="AV35" s="96"/>
-      <c r="AW35" s="96"/>
-      <c r="AX35" s="96"/>
-      <c r="AY35" s="96"/>
-      <c r="AZ35" s="97"/>
+      <c r="AI35" s="203"/>
+      <c r="AJ35" s="203"/>
+      <c r="AK35" s="203"/>
+      <c r="AL35" s="203"/>
+      <c r="AM35" s="203"/>
+      <c r="AN35" s="203"/>
+      <c r="AO35" s="203"/>
+      <c r="AP35" s="203"/>
+      <c r="AQ35" s="203"/>
+      <c r="AR35" s="203"/>
+      <c r="AS35" s="203"/>
+      <c r="AT35" s="203"/>
+      <c r="AU35" s="203"/>
+      <c r="AV35" s="203"/>
+      <c r="AW35" s="203"/>
+      <c r="AX35" s="203"/>
+      <c r="AY35" s="203"/>
+      <c r="AZ35" s="204"/>
     </row>
     <row r="36" spans="1:52" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="127" t="s">
+      <c r="A36" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="128"/>
-      <c r="C36" s="128"/>
-      <c r="D36" s="128"/>
-      <c r="E36" s="128"/>
-      <c r="F36" s="128"/>
-      <c r="G36" s="128"/>
-      <c r="H36" s="128"/>
-      <c r="I36" s="128"/>
-      <c r="J36" s="128"/>
-      <c r="K36" s="128"/>
-      <c r="L36" s="128"/>
-      <c r="M36" s="128"/>
-      <c r="N36" s="128"/>
-      <c r="O36" s="128"/>
-      <c r="P36" s="128"/>
-      <c r="Q36" s="128"/>
-      <c r="R36" s="129"/>
-      <c r="S36" s="130" t="s">
+      <c r="B36" s="184"/>
+      <c r="C36" s="184"/>
+      <c r="D36" s="184"/>
+      <c r="E36" s="184"/>
+      <c r="F36" s="184"/>
+      <c r="G36" s="184"/>
+      <c r="H36" s="184"/>
+      <c r="I36" s="184"/>
+      <c r="J36" s="184"/>
+      <c r="K36" s="184"/>
+      <c r="L36" s="184"/>
+      <c r="M36" s="184"/>
+      <c r="N36" s="184"/>
+      <c r="O36" s="184"/>
+      <c r="P36" s="184"/>
+      <c r="Q36" s="184"/>
+      <c r="R36" s="185"/>
+      <c r="S36" s="189" t="s">
         <v>62</v>
       </c>
-      <c r="T36" s="131"/>
-      <c r="U36" s="131"/>
-      <c r="V36" s="131"/>
-      <c r="W36" s="131"/>
-      <c r="X36" s="131"/>
-      <c r="Y36" s="131"/>
-      <c r="Z36" s="131"/>
-      <c r="AA36" s="131"/>
-      <c r="AB36" s="131"/>
-      <c r="AC36" s="131"/>
-      <c r="AD36" s="131"/>
-      <c r="AE36" s="131"/>
-      <c r="AF36" s="131"/>
-      <c r="AG36" s="132"/>
-      <c r="AH36" s="95" t="s">
+      <c r="T36" s="190"/>
+      <c r="U36" s="190"/>
+      <c r="V36" s="190"/>
+      <c r="W36" s="190"/>
+      <c r="X36" s="190"/>
+      <c r="Y36" s="190"/>
+      <c r="Z36" s="190"/>
+      <c r="AA36" s="190"/>
+      <c r="AB36" s="190"/>
+      <c r="AC36" s="190"/>
+      <c r="AD36" s="190"/>
+      <c r="AE36" s="190"/>
+      <c r="AF36" s="190"/>
+      <c r="AG36" s="191"/>
+      <c r="AH36" s="202" t="s">
         <v>63</v>
       </c>
-      <c r="AI36" s="96"/>
-      <c r="AJ36" s="96"/>
-      <c r="AK36" s="96"/>
-      <c r="AL36" s="96"/>
-      <c r="AM36" s="96"/>
-      <c r="AN36" s="96"/>
-      <c r="AO36" s="96"/>
-      <c r="AP36" s="96"/>
-      <c r="AQ36" s="96"/>
-      <c r="AR36" s="96"/>
-      <c r="AS36" s="96"/>
-      <c r="AT36" s="96"/>
-      <c r="AU36" s="96"/>
-      <c r="AV36" s="96"/>
-      <c r="AW36" s="96"/>
-      <c r="AX36" s="96"/>
-      <c r="AY36" s="96"/>
-      <c r="AZ36" s="97"/>
+      <c r="AI36" s="203"/>
+      <c r="AJ36" s="203"/>
+      <c r="AK36" s="203"/>
+      <c r="AL36" s="203"/>
+      <c r="AM36" s="203"/>
+      <c r="AN36" s="203"/>
+      <c r="AO36" s="203"/>
+      <c r="AP36" s="203"/>
+      <c r="AQ36" s="203"/>
+      <c r="AR36" s="203"/>
+      <c r="AS36" s="203"/>
+      <c r="AT36" s="203"/>
+      <c r="AU36" s="203"/>
+      <c r="AV36" s="203"/>
+      <c r="AW36" s="203"/>
+      <c r="AX36" s="203"/>
+      <c r="AY36" s="203"/>
+      <c r="AZ36" s="204"/>
     </row>
     <row r="37" spans="1:52" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="127" t="s">
+      <c r="A37" s="183" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="128"/>
-      <c r="C37" s="128"/>
-      <c r="D37" s="128"/>
-      <c r="E37" s="128"/>
-      <c r="F37" s="128"/>
-      <c r="G37" s="128"/>
-      <c r="H37" s="128"/>
-      <c r="I37" s="128"/>
-      <c r="J37" s="128"/>
-      <c r="K37" s="128"/>
-      <c r="L37" s="128"/>
-      <c r="M37" s="128"/>
-      <c r="N37" s="128"/>
-      <c r="O37" s="128"/>
-      <c r="P37" s="128"/>
-      <c r="Q37" s="128"/>
-      <c r="R37" s="129"/>
-      <c r="S37" s="130" t="s">
+      <c r="B37" s="184"/>
+      <c r="C37" s="184"/>
+      <c r="D37" s="184"/>
+      <c r="E37" s="184"/>
+      <c r="F37" s="184"/>
+      <c r="G37" s="184"/>
+      <c r="H37" s="184"/>
+      <c r="I37" s="184"/>
+      <c r="J37" s="184"/>
+      <c r="K37" s="184"/>
+      <c r="L37" s="184"/>
+      <c r="M37" s="184"/>
+      <c r="N37" s="184"/>
+      <c r="O37" s="184"/>
+      <c r="P37" s="184"/>
+      <c r="Q37" s="184"/>
+      <c r="R37" s="185"/>
+      <c r="S37" s="189" t="s">
         <v>65</v>
       </c>
-      <c r="T37" s="131"/>
-      <c r="U37" s="131"/>
-      <c r="V37" s="131"/>
-      <c r="W37" s="131"/>
-      <c r="X37" s="131"/>
-      <c r="Y37" s="131"/>
-      <c r="Z37" s="131"/>
-      <c r="AA37" s="131"/>
-      <c r="AB37" s="131"/>
-      <c r="AC37" s="131"/>
-      <c r="AD37" s="131"/>
-      <c r="AE37" s="131"/>
-      <c r="AF37" s="131"/>
-      <c r="AG37" s="132"/>
-      <c r="AH37" s="95" t="s">
+      <c r="T37" s="190"/>
+      <c r="U37" s="190"/>
+      <c r="V37" s="190"/>
+      <c r="W37" s="190"/>
+      <c r="X37" s="190"/>
+      <c r="Y37" s="190"/>
+      <c r="Z37" s="190"/>
+      <c r="AA37" s="190"/>
+      <c r="AB37" s="190"/>
+      <c r="AC37" s="190"/>
+      <c r="AD37" s="190"/>
+      <c r="AE37" s="190"/>
+      <c r="AF37" s="190"/>
+      <c r="AG37" s="191"/>
+      <c r="AH37" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="AI37" s="96"/>
-      <c r="AJ37" s="96"/>
-      <c r="AK37" s="96"/>
-      <c r="AL37" s="96"/>
-      <c r="AM37" s="96"/>
-      <c r="AN37" s="96"/>
-      <c r="AO37" s="96"/>
-      <c r="AP37" s="96"/>
-      <c r="AQ37" s="96"/>
-      <c r="AR37" s="96"/>
-      <c r="AS37" s="96"/>
-      <c r="AT37" s="96"/>
-      <c r="AU37" s="96"/>
-      <c r="AV37" s="96"/>
-      <c r="AW37" s="96"/>
-      <c r="AX37" s="96"/>
-      <c r="AY37" s="96"/>
-      <c r="AZ37" s="97"/>
+      <c r="AI37" s="203"/>
+      <c r="AJ37" s="203"/>
+      <c r="AK37" s="203"/>
+      <c r="AL37" s="203"/>
+      <c r="AM37" s="203"/>
+      <c r="AN37" s="203"/>
+      <c r="AO37" s="203"/>
+      <c r="AP37" s="203"/>
+      <c r="AQ37" s="203"/>
+      <c r="AR37" s="203"/>
+      <c r="AS37" s="203"/>
+      <c r="AT37" s="203"/>
+      <c r="AU37" s="203"/>
+      <c r="AV37" s="203"/>
+      <c r="AW37" s="203"/>
+      <c r="AX37" s="203"/>
+      <c r="AY37" s="203"/>
+      <c r="AZ37" s="204"/>
     </row>
     <row r="38" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="127" t="s">
+      <c r="A38" s="183" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="128"/>
-      <c r="C38" s="128"/>
-      <c r="D38" s="128"/>
-      <c r="E38" s="128"/>
-      <c r="F38" s="128"/>
-      <c r="G38" s="128"/>
-      <c r="H38" s="128"/>
-      <c r="I38" s="128"/>
-      <c r="J38" s="128"/>
-      <c r="K38" s="128"/>
-      <c r="L38" s="128"/>
-      <c r="M38" s="128"/>
-      <c r="N38" s="128"/>
-      <c r="O38" s="128"/>
-      <c r="P38" s="128"/>
-      <c r="Q38" s="128"/>
-      <c r="R38" s="129"/>
-      <c r="S38" s="130" t="s">
+      <c r="B38" s="184"/>
+      <c r="C38" s="184"/>
+      <c r="D38" s="184"/>
+      <c r="E38" s="184"/>
+      <c r="F38" s="184"/>
+      <c r="G38" s="184"/>
+      <c r="H38" s="184"/>
+      <c r="I38" s="184"/>
+      <c r="J38" s="184"/>
+      <c r="K38" s="184"/>
+      <c r="L38" s="184"/>
+      <c r="M38" s="184"/>
+      <c r="N38" s="184"/>
+      <c r="O38" s="184"/>
+      <c r="P38" s="184"/>
+      <c r="Q38" s="184"/>
+      <c r="R38" s="185"/>
+      <c r="S38" s="189" t="s">
         <v>68</v>
       </c>
-      <c r="T38" s="131"/>
-      <c r="U38" s="131"/>
-      <c r="V38" s="131"/>
-      <c r="W38" s="131"/>
-      <c r="X38" s="131"/>
-      <c r="Y38" s="131"/>
-      <c r="Z38" s="131"/>
-      <c r="AA38" s="131"/>
-      <c r="AB38" s="131"/>
-      <c r="AC38" s="131"/>
-      <c r="AD38" s="131"/>
-      <c r="AE38" s="131"/>
-      <c r="AF38" s="131"/>
-      <c r="AG38" s="132"/>
-      <c r="AH38" s="95" t="s">
+      <c r="T38" s="190"/>
+      <c r="U38" s="190"/>
+      <c r="V38" s="190"/>
+      <c r="W38" s="190"/>
+      <c r="X38" s="190"/>
+      <c r="Y38" s="190"/>
+      <c r="Z38" s="190"/>
+      <c r="AA38" s="190"/>
+      <c r="AB38" s="190"/>
+      <c r="AC38" s="190"/>
+      <c r="AD38" s="190"/>
+      <c r="AE38" s="190"/>
+      <c r="AF38" s="190"/>
+      <c r="AG38" s="191"/>
+      <c r="AH38" s="202" t="s">
         <v>69</v>
       </c>
-      <c r="AI38" s="96"/>
-      <c r="AJ38" s="96"/>
-      <c r="AK38" s="96"/>
-      <c r="AL38" s="96"/>
-      <c r="AM38" s="96"/>
-      <c r="AN38" s="96"/>
-      <c r="AO38" s="96"/>
-      <c r="AP38" s="96"/>
-      <c r="AQ38" s="96"/>
-      <c r="AR38" s="96"/>
-      <c r="AS38" s="96"/>
-      <c r="AT38" s="96"/>
-      <c r="AU38" s="96"/>
-      <c r="AV38" s="96"/>
-      <c r="AW38" s="96"/>
-      <c r="AX38" s="96"/>
-      <c r="AY38" s="96"/>
-      <c r="AZ38" s="97"/>
+      <c r="AI38" s="203"/>
+      <c r="AJ38" s="203"/>
+      <c r="AK38" s="203"/>
+      <c r="AL38" s="203"/>
+      <c r="AM38" s="203"/>
+      <c r="AN38" s="203"/>
+      <c r="AO38" s="203"/>
+      <c r="AP38" s="203"/>
+      <c r="AQ38" s="203"/>
+      <c r="AR38" s="203"/>
+      <c r="AS38" s="203"/>
+      <c r="AT38" s="203"/>
+      <c r="AU38" s="203"/>
+      <c r="AV38" s="203"/>
+      <c r="AW38" s="203"/>
+      <c r="AX38" s="203"/>
+      <c r="AY38" s="203"/>
+      <c r="AZ38" s="204"/>
     </row>
     <row r="39" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="127" t="s">
+      <c r="A39" s="183" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="128"/>
-      <c r="C39" s="128"/>
-      <c r="D39" s="128"/>
-      <c r="E39" s="128"/>
-      <c r="F39" s="128"/>
-      <c r="G39" s="128"/>
-      <c r="H39" s="128"/>
-      <c r="I39" s="128"/>
-      <c r="J39" s="128"/>
-      <c r="K39" s="128"/>
-      <c r="L39" s="128"/>
-      <c r="M39" s="128"/>
-      <c r="N39" s="128"/>
-      <c r="O39" s="128"/>
-      <c r="P39" s="128"/>
-      <c r="Q39" s="128"/>
-      <c r="R39" s="129"/>
-      <c r="S39" s="130" t="s">
+      <c r="B39" s="184"/>
+      <c r="C39" s="184"/>
+      <c r="D39" s="184"/>
+      <c r="E39" s="184"/>
+      <c r="F39" s="184"/>
+      <c r="G39" s="184"/>
+      <c r="H39" s="184"/>
+      <c r="I39" s="184"/>
+      <c r="J39" s="184"/>
+      <c r="K39" s="184"/>
+      <c r="L39" s="184"/>
+      <c r="M39" s="184"/>
+      <c r="N39" s="184"/>
+      <c r="O39" s="184"/>
+      <c r="P39" s="184"/>
+      <c r="Q39" s="184"/>
+      <c r="R39" s="185"/>
+      <c r="S39" s="189" t="s">
         <v>71</v>
       </c>
-      <c r="T39" s="131"/>
-      <c r="U39" s="131"/>
-      <c r="V39" s="131"/>
-      <c r="W39" s="131"/>
-      <c r="X39" s="131"/>
-      <c r="Y39" s="131"/>
-      <c r="Z39" s="131"/>
-      <c r="AA39" s="131"/>
-      <c r="AB39" s="131"/>
-      <c r="AC39" s="131"/>
-      <c r="AD39" s="131"/>
-      <c r="AE39" s="131"/>
-      <c r="AF39" s="131"/>
-      <c r="AG39" s="132"/>
-      <c r="AH39" s="150"/>
-      <c r="AI39" s="151"/>
-      <c r="AJ39" s="151"/>
-      <c r="AK39" s="151"/>
-      <c r="AL39" s="151"/>
-      <c r="AM39" s="151"/>
-      <c r="AN39" s="151"/>
-      <c r="AO39" s="151"/>
-      <c r="AP39" s="151"/>
-      <c r="AQ39" s="151"/>
-      <c r="AR39" s="151"/>
-      <c r="AS39" s="151"/>
-      <c r="AT39" s="151"/>
-      <c r="AU39" s="151"/>
-      <c r="AV39" s="151"/>
-      <c r="AW39" s="151"/>
-      <c r="AX39" s="151"/>
-      <c r="AY39" s="151"/>
-      <c r="AZ39" s="152"/>
+      <c r="T39" s="190"/>
+      <c r="U39" s="190"/>
+      <c r="V39" s="190"/>
+      <c r="W39" s="190"/>
+      <c r="X39" s="190"/>
+      <c r="Y39" s="190"/>
+      <c r="Z39" s="190"/>
+      <c r="AA39" s="190"/>
+      <c r="AB39" s="190"/>
+      <c r="AC39" s="190"/>
+      <c r="AD39" s="190"/>
+      <c r="AE39" s="190"/>
+      <c r="AF39" s="190"/>
+      <c r="AG39" s="191"/>
+      <c r="AH39" s="220"/>
+      <c r="AI39" s="221"/>
+      <c r="AJ39" s="221"/>
+      <c r="AK39" s="221"/>
+      <c r="AL39" s="221"/>
+      <c r="AM39" s="221"/>
+      <c r="AN39" s="221"/>
+      <c r="AO39" s="221"/>
+      <c r="AP39" s="221"/>
+      <c r="AQ39" s="221"/>
+      <c r="AR39" s="221"/>
+      <c r="AS39" s="221"/>
+      <c r="AT39" s="221"/>
+      <c r="AU39" s="221"/>
+      <c r="AV39" s="221"/>
+      <c r="AW39" s="221"/>
+      <c r="AX39" s="221"/>
+      <c r="AY39" s="221"/>
+      <c r="AZ39" s="222"/>
     </row>
     <row r="40" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="127" t="s">
+      <c r="A40" s="183" t="s">
         <v>72</v>
       </c>
-      <c r="B40" s="128"/>
-      <c r="C40" s="128"/>
-      <c r="D40" s="128"/>
-      <c r="E40" s="128"/>
-      <c r="F40" s="128"/>
-      <c r="G40" s="128"/>
-      <c r="H40" s="128"/>
-      <c r="I40" s="128"/>
-      <c r="J40" s="128"/>
-      <c r="K40" s="128"/>
-      <c r="L40" s="128"/>
-      <c r="M40" s="128"/>
-      <c r="N40" s="128"/>
-      <c r="O40" s="128"/>
-      <c r="P40" s="128"/>
-      <c r="Q40" s="128"/>
-      <c r="R40" s="129"/>
-      <c r="S40" s="130" t="s">
+      <c r="B40" s="184"/>
+      <c r="C40" s="184"/>
+      <c r="D40" s="184"/>
+      <c r="E40" s="184"/>
+      <c r="F40" s="184"/>
+      <c r="G40" s="184"/>
+      <c r="H40" s="184"/>
+      <c r="I40" s="184"/>
+      <c r="J40" s="184"/>
+      <c r="K40" s="184"/>
+      <c r="L40" s="184"/>
+      <c r="M40" s="184"/>
+      <c r="N40" s="184"/>
+      <c r="O40" s="184"/>
+      <c r="P40" s="184"/>
+      <c r="Q40" s="184"/>
+      <c r="R40" s="185"/>
+      <c r="S40" s="189" t="s">
         <v>73</v>
       </c>
-      <c r="T40" s="131"/>
-      <c r="U40" s="131"/>
-      <c r="V40" s="131"/>
-      <c r="W40" s="131"/>
-      <c r="X40" s="131"/>
-      <c r="Y40" s="131"/>
-      <c r="Z40" s="131"/>
-      <c r="AA40" s="131"/>
-      <c r="AB40" s="131"/>
-      <c r="AC40" s="131"/>
-      <c r="AD40" s="131"/>
-      <c r="AE40" s="131"/>
-      <c r="AF40" s="131"/>
-      <c r="AG40" s="132"/>
-      <c r="AH40" s="150"/>
-      <c r="AI40" s="151"/>
-      <c r="AJ40" s="151"/>
-      <c r="AK40" s="151"/>
-      <c r="AL40" s="151"/>
-      <c r="AM40" s="151"/>
-      <c r="AN40" s="151"/>
-      <c r="AO40" s="151"/>
-      <c r="AP40" s="151"/>
-      <c r="AQ40" s="151"/>
-      <c r="AR40" s="151"/>
-      <c r="AS40" s="151"/>
-      <c r="AT40" s="151"/>
-      <c r="AU40" s="151"/>
-      <c r="AV40" s="151"/>
-      <c r="AW40" s="151"/>
-      <c r="AX40" s="151"/>
-      <c r="AY40" s="151"/>
-      <c r="AZ40" s="152"/>
+      <c r="T40" s="190"/>
+      <c r="U40" s="190"/>
+      <c r="V40" s="190"/>
+      <c r="W40" s="190"/>
+      <c r="X40" s="190"/>
+      <c r="Y40" s="190"/>
+      <c r="Z40" s="190"/>
+      <c r="AA40" s="190"/>
+      <c r="AB40" s="190"/>
+      <c r="AC40" s="190"/>
+      <c r="AD40" s="190"/>
+      <c r="AE40" s="190"/>
+      <c r="AF40" s="190"/>
+      <c r="AG40" s="191"/>
+      <c r="AH40" s="220"/>
+      <c r="AI40" s="221"/>
+      <c r="AJ40" s="221"/>
+      <c r="AK40" s="221"/>
+      <c r="AL40" s="221"/>
+      <c r="AM40" s="221"/>
+      <c r="AN40" s="221"/>
+      <c r="AO40" s="221"/>
+      <c r="AP40" s="221"/>
+      <c r="AQ40" s="221"/>
+      <c r="AR40" s="221"/>
+      <c r="AS40" s="221"/>
+      <c r="AT40" s="221"/>
+      <c r="AU40" s="221"/>
+      <c r="AV40" s="221"/>
+      <c r="AW40" s="221"/>
+      <c r="AX40" s="221"/>
+      <c r="AY40" s="221"/>
+      <c r="AZ40" s="222"/>
     </row>
     <row r="41" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="127"/>
-      <c r="B41" s="128"/>
-      <c r="C41" s="128"/>
-      <c r="D41" s="128"/>
-      <c r="E41" s="128"/>
-      <c r="F41" s="128"/>
-      <c r="G41" s="128"/>
-      <c r="H41" s="128"/>
-      <c r="I41" s="128"/>
-      <c r="J41" s="128"/>
-      <c r="K41" s="128"/>
-      <c r="L41" s="128"/>
-      <c r="M41" s="128"/>
-      <c r="N41" s="128"/>
-      <c r="O41" s="128"/>
-      <c r="P41" s="128"/>
-      <c r="Q41" s="128"/>
-      <c r="R41" s="129"/>
-      <c r="S41" s="130" t="s">
+      <c r="A41" s="183"/>
+      <c r="B41" s="184"/>
+      <c r="C41" s="184"/>
+      <c r="D41" s="184"/>
+      <c r="E41" s="184"/>
+      <c r="F41" s="184"/>
+      <c r="G41" s="184"/>
+      <c r="H41" s="184"/>
+      <c r="I41" s="184"/>
+      <c r="J41" s="184"/>
+      <c r="K41" s="184"/>
+      <c r="L41" s="184"/>
+      <c r="M41" s="184"/>
+      <c r="N41" s="184"/>
+      <c r="O41" s="184"/>
+      <c r="P41" s="184"/>
+      <c r="Q41" s="184"/>
+      <c r="R41" s="185"/>
+      <c r="S41" s="189" t="s">
         <v>74</v>
       </c>
-      <c r="T41" s="131"/>
-      <c r="U41" s="131"/>
-      <c r="V41" s="131"/>
-      <c r="W41" s="131"/>
-      <c r="X41" s="131"/>
-      <c r="Y41" s="131"/>
-      <c r="Z41" s="131"/>
-      <c r="AA41" s="131"/>
-      <c r="AB41" s="131"/>
-      <c r="AC41" s="131"/>
-      <c r="AD41" s="131"/>
-      <c r="AE41" s="131"/>
-      <c r="AF41" s="131"/>
-      <c r="AG41" s="132"/>
-      <c r="AH41" s="150"/>
-      <c r="AI41" s="151"/>
-      <c r="AJ41" s="151"/>
-      <c r="AK41" s="151"/>
-      <c r="AL41" s="151"/>
-      <c r="AM41" s="151"/>
-      <c r="AN41" s="151"/>
-      <c r="AO41" s="151"/>
-      <c r="AP41" s="151"/>
-      <c r="AQ41" s="151"/>
-      <c r="AR41" s="151"/>
-      <c r="AS41" s="151"/>
-      <c r="AT41" s="151"/>
-      <c r="AU41" s="151"/>
-      <c r="AV41" s="151"/>
-      <c r="AW41" s="151"/>
-      <c r="AX41" s="151"/>
-      <c r="AY41" s="151"/>
-      <c r="AZ41" s="152"/>
+      <c r="T41" s="190"/>
+      <c r="U41" s="190"/>
+      <c r="V41" s="190"/>
+      <c r="W41" s="190"/>
+      <c r="X41" s="190"/>
+      <c r="Y41" s="190"/>
+      <c r="Z41" s="190"/>
+      <c r="AA41" s="190"/>
+      <c r="AB41" s="190"/>
+      <c r="AC41" s="190"/>
+      <c r="AD41" s="190"/>
+      <c r="AE41" s="190"/>
+      <c r="AF41" s="190"/>
+      <c r="AG41" s="191"/>
+      <c r="AH41" s="220"/>
+      <c r="AI41" s="221"/>
+      <c r="AJ41" s="221"/>
+      <c r="AK41" s="221"/>
+      <c r="AL41" s="221"/>
+      <c r="AM41" s="221"/>
+      <c r="AN41" s="221"/>
+      <c r="AO41" s="221"/>
+      <c r="AP41" s="221"/>
+      <c r="AQ41" s="221"/>
+      <c r="AR41" s="221"/>
+      <c r="AS41" s="221"/>
+      <c r="AT41" s="221"/>
+      <c r="AU41" s="221"/>
+      <c r="AV41" s="221"/>
+      <c r="AW41" s="221"/>
+      <c r="AX41" s="221"/>
+      <c r="AY41" s="221"/>
+      <c r="AZ41" s="222"/>
     </row>
     <row r="42" spans="1:52" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="153"/>
-      <c r="B42" s="154"/>
-      <c r="C42" s="154"/>
-      <c r="D42" s="154"/>
-      <c r="E42" s="154"/>
-      <c r="F42" s="154"/>
-      <c r="G42" s="154"/>
-      <c r="H42" s="154"/>
-      <c r="I42" s="154"/>
-      <c r="J42" s="154"/>
-      <c r="K42" s="154"/>
-      <c r="L42" s="154"/>
-      <c r="M42" s="154"/>
-      <c r="N42" s="154"/>
-      <c r="O42" s="154"/>
-      <c r="P42" s="154"/>
-      <c r="Q42" s="154"/>
-      <c r="R42" s="155"/>
-      <c r="S42" s="139" t="s">
+      <c r="A42" s="223"/>
+      <c r="B42" s="224"/>
+      <c r="C42" s="224"/>
+      <c r="D42" s="224"/>
+      <c r="E42" s="224"/>
+      <c r="F42" s="224"/>
+      <c r="G42" s="224"/>
+      <c r="H42" s="224"/>
+      <c r="I42" s="224"/>
+      <c r="J42" s="224"/>
+      <c r="K42" s="224"/>
+      <c r="L42" s="224"/>
+      <c r="M42" s="224"/>
+      <c r="N42" s="224"/>
+      <c r="O42" s="224"/>
+      <c r="P42" s="224"/>
+      <c r="Q42" s="224"/>
+      <c r="R42" s="225"/>
+      <c r="S42" s="211" t="s">
         <v>75</v>
       </c>
-      <c r="T42" s="140"/>
-      <c r="U42" s="140"/>
-      <c r="V42" s="140"/>
-      <c r="W42" s="140"/>
-      <c r="X42" s="140"/>
-      <c r="Y42" s="140"/>
-      <c r="Z42" s="140"/>
-      <c r="AA42" s="140"/>
-      <c r="AB42" s="140"/>
-      <c r="AC42" s="140"/>
-      <c r="AD42" s="140"/>
-      <c r="AE42" s="140"/>
-      <c r="AF42" s="140"/>
-      <c r="AG42" s="141"/>
-      <c r="AH42" s="156"/>
-      <c r="AI42" s="157"/>
-      <c r="AJ42" s="157"/>
-      <c r="AK42" s="157"/>
-      <c r="AL42" s="157"/>
-      <c r="AM42" s="157"/>
-      <c r="AN42" s="157"/>
-      <c r="AO42" s="157"/>
-      <c r="AP42" s="157"/>
-      <c r="AQ42" s="157"/>
-      <c r="AR42" s="157"/>
-      <c r="AS42" s="157"/>
-      <c r="AT42" s="157"/>
-      <c r="AU42" s="157"/>
-      <c r="AV42" s="157"/>
-      <c r="AW42" s="157"/>
-      <c r="AX42" s="157"/>
-      <c r="AY42" s="157"/>
-      <c r="AZ42" s="158"/>
+      <c r="T42" s="212"/>
+      <c r="U42" s="212"/>
+      <c r="V42" s="212"/>
+      <c r="W42" s="212"/>
+      <c r="X42" s="212"/>
+      <c r="Y42" s="212"/>
+      <c r="Z42" s="212"/>
+      <c r="AA42" s="212"/>
+      <c r="AB42" s="212"/>
+      <c r="AC42" s="212"/>
+      <c r="AD42" s="212"/>
+      <c r="AE42" s="212"/>
+      <c r="AF42" s="212"/>
+      <c r="AG42" s="213"/>
+      <c r="AH42" s="226"/>
+      <c r="AI42" s="227"/>
+      <c r="AJ42" s="227"/>
+      <c r="AK42" s="227"/>
+      <c r="AL42" s="227"/>
+      <c r="AM42" s="227"/>
+      <c r="AN42" s="227"/>
+      <c r="AO42" s="227"/>
+      <c r="AP42" s="227"/>
+      <c r="AQ42" s="227"/>
+      <c r="AR42" s="227"/>
+      <c r="AS42" s="227"/>
+      <c r="AT42" s="227"/>
+      <c r="AU42" s="227"/>
+      <c r="AV42" s="227"/>
+      <c r="AW42" s="227"/>
+      <c r="AX42" s="227"/>
+      <c r="AY42" s="227"/>
+      <c r="AZ42" s="228"/>
     </row>
     <row r="43" spans="1:52" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="148"/>
-      <c r="B43" s="148"/>
-      <c r="C43" s="148"/>
-      <c r="D43" s="148"/>
-      <c r="E43" s="148"/>
-      <c r="F43" s="148"/>
-      <c r="G43" s="148"/>
-      <c r="H43" s="148"/>
-      <c r="I43" s="148"/>
-      <c r="J43" s="148"/>
-      <c r="K43" s="148"/>
-      <c r="L43" s="148"/>
-      <c r="M43" s="148"/>
-      <c r="N43" s="148"/>
-      <c r="O43" s="148"/>
-      <c r="P43" s="148"/>
-      <c r="Q43" s="148"/>
-      <c r="R43" s="148"/>
-      <c r="S43" s="148"/>
-      <c r="T43" s="148"/>
-      <c r="U43" s="148"/>
-      <c r="V43" s="148"/>
-      <c r="W43" s="148"/>
-      <c r="X43" s="148"/>
-      <c r="Y43" s="148"/>
-      <c r="Z43" s="148"/>
-      <c r="AA43" s="148"/>
-      <c r="AB43" s="148"/>
-      <c r="AC43" s="148"/>
-      <c r="AD43" s="148"/>
-      <c r="AE43" s="148"/>
-      <c r="AF43" s="148"/>
-      <c r="AG43" s="148"/>
-      <c r="AH43" s="148"/>
-      <c r="AI43" s="148"/>
-      <c r="AJ43" s="148"/>
-      <c r="AK43" s="148"/>
-      <c r="AL43" s="148"/>
-      <c r="AM43" s="148"/>
-      <c r="AN43" s="148"/>
-      <c r="AO43" s="148"/>
-      <c r="AP43" s="148"/>
-      <c r="AQ43" s="148"/>
-      <c r="AR43" s="148"/>
-      <c r="AS43" s="148"/>
-      <c r="AT43" s="148"/>
-      <c r="AU43" s="148"/>
-      <c r="AV43" s="148"/>
-      <c r="AW43" s="148"/>
-      <c r="AX43" s="148"/>
-      <c r="AY43" s="148"/>
-      <c r="AZ43" s="148"/>
+      <c r="A43" s="99"/>
+      <c r="B43" s="99"/>
+      <c r="C43" s="99"/>
+      <c r="D43" s="99"/>
+      <c r="E43" s="99"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="99"/>
+      <c r="J43" s="99"/>
+      <c r="K43" s="99"/>
+      <c r="L43" s="99"/>
+      <c r="M43" s="99"/>
+      <c r="N43" s="99"/>
+      <c r="O43" s="99"/>
+      <c r="P43" s="99"/>
+      <c r="Q43" s="99"/>
+      <c r="R43" s="99"/>
+      <c r="S43" s="99"/>
+      <c r="T43" s="99"/>
+      <c r="U43" s="99"/>
+      <c r="V43" s="99"/>
+      <c r="W43" s="99"/>
+      <c r="X43" s="99"/>
+      <c r="Y43" s="99"/>
+      <c r="Z43" s="99"/>
+      <c r="AA43" s="99"/>
+      <c r="AB43" s="99"/>
+      <c r="AC43" s="99"/>
+      <c r="AD43" s="99"/>
+      <c r="AE43" s="99"/>
+      <c r="AF43" s="99"/>
+      <c r="AG43" s="99"/>
+      <c r="AH43" s="99"/>
+      <c r="AI43" s="99"/>
+      <c r="AJ43" s="99"/>
+      <c r="AK43" s="99"/>
+      <c r="AL43" s="99"/>
+      <c r="AM43" s="99"/>
+      <c r="AN43" s="99"/>
+      <c r="AO43" s="99"/>
+      <c r="AP43" s="99"/>
+      <c r="AQ43" s="99"/>
+      <c r="AR43" s="99"/>
+      <c r="AS43" s="99"/>
+      <c r="AT43" s="99"/>
+      <c r="AU43" s="99"/>
+      <c r="AV43" s="99"/>
+      <c r="AW43" s="99"/>
+      <c r="AX43" s="99"/>
+      <c r="AY43" s="99"/>
+      <c r="AZ43" s="99"/>
     </row>
     <row r="44" spans="1:52" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="142" t="s">
+      <c r="A44" s="214" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="143"/>
-      <c r="C44" s="143"/>
-      <c r="D44" s="143"/>
-      <c r="E44" s="143"/>
-      <c r="F44" s="143"/>
-      <c r="G44" s="143"/>
-      <c r="H44" s="143"/>
-      <c r="I44" s="143"/>
-      <c r="J44" s="143"/>
-      <c r="K44" s="143"/>
-      <c r="L44" s="143"/>
-      <c r="M44" s="143"/>
-      <c r="N44" s="143"/>
-      <c r="O44" s="143"/>
-      <c r="P44" s="143"/>
-      <c r="Q44" s="143"/>
-      <c r="R44" s="143"/>
-      <c r="S44" s="143"/>
-      <c r="T44" s="143"/>
-      <c r="U44" s="143"/>
-      <c r="V44" s="143"/>
-      <c r="W44" s="143"/>
-      <c r="X44" s="143"/>
-      <c r="Y44" s="143"/>
-      <c r="Z44" s="143"/>
-      <c r="AA44" s="143"/>
-      <c r="AB44" s="143"/>
-      <c r="AC44" s="143"/>
-      <c r="AD44" s="143"/>
-      <c r="AE44" s="143"/>
-      <c r="AF44" s="143"/>
-      <c r="AG44" s="143"/>
-      <c r="AH44" s="143"/>
-      <c r="AI44" s="143"/>
-      <c r="AJ44" s="143"/>
-      <c r="AK44" s="143"/>
-      <c r="AL44" s="143"/>
-      <c r="AM44" s="143"/>
-      <c r="AN44" s="143"/>
-      <c r="AO44" s="143"/>
-      <c r="AP44" s="143"/>
-      <c r="AQ44" s="143"/>
-      <c r="AR44" s="143"/>
-      <c r="AS44" s="143"/>
-      <c r="AT44" s="143"/>
-      <c r="AU44" s="143"/>
-      <c r="AV44" s="143"/>
-      <c r="AW44" s="143"/>
-      <c r="AX44" s="143"/>
-      <c r="AY44" s="143"/>
-      <c r="AZ44" s="144"/>
+      <c r="B44" s="215"/>
+      <c r="C44" s="215"/>
+      <c r="D44" s="215"/>
+      <c r="E44" s="215"/>
+      <c r="F44" s="215"/>
+      <c r="G44" s="215"/>
+      <c r="H44" s="215"/>
+      <c r="I44" s="215"/>
+      <c r="J44" s="215"/>
+      <c r="K44" s="215"/>
+      <c r="L44" s="215"/>
+      <c r="M44" s="215"/>
+      <c r="N44" s="215"/>
+      <c r="O44" s="215"/>
+      <c r="P44" s="215"/>
+      <c r="Q44" s="215"/>
+      <c r="R44" s="215"/>
+      <c r="S44" s="215"/>
+      <c r="T44" s="215"/>
+      <c r="U44" s="215"/>
+      <c r="V44" s="215"/>
+      <c r="W44" s="215"/>
+      <c r="X44" s="215"/>
+      <c r="Y44" s="215"/>
+      <c r="Z44" s="215"/>
+      <c r="AA44" s="215"/>
+      <c r="AB44" s="215"/>
+      <c r="AC44" s="215"/>
+      <c r="AD44" s="215"/>
+      <c r="AE44" s="215"/>
+      <c r="AF44" s="215"/>
+      <c r="AG44" s="215"/>
+      <c r="AH44" s="215"/>
+      <c r="AI44" s="215"/>
+      <c r="AJ44" s="215"/>
+      <c r="AK44" s="215"/>
+      <c r="AL44" s="215"/>
+      <c r="AM44" s="215"/>
+      <c r="AN44" s="215"/>
+      <c r="AO44" s="215"/>
+      <c r="AP44" s="215"/>
+      <c r="AQ44" s="215"/>
+      <c r="AR44" s="215"/>
+      <c r="AS44" s="215"/>
+      <c r="AT44" s="215"/>
+      <c r="AU44" s="215"/>
+      <c r="AV44" s="215"/>
+      <c r="AW44" s="215"/>
+      <c r="AX44" s="215"/>
+      <c r="AY44" s="215"/>
+      <c r="AZ44" s="216"/>
     </row>
     <row r="45" spans="1:52" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="145"/>
-      <c r="B45" s="146"/>
-      <c r="C45" s="146"/>
-      <c r="D45" s="146"/>
-      <c r="E45" s="146"/>
-      <c r="F45" s="146"/>
-      <c r="G45" s="146"/>
-      <c r="H45" s="146"/>
-      <c r="I45" s="146"/>
-      <c r="J45" s="146"/>
-      <c r="K45" s="146"/>
-      <c r="L45" s="146"/>
-      <c r="M45" s="146"/>
-      <c r="N45" s="146"/>
-      <c r="O45" s="146"/>
-      <c r="P45" s="146"/>
-      <c r="Q45" s="146"/>
-      <c r="R45" s="146"/>
-      <c r="S45" s="146"/>
-      <c r="T45" s="146"/>
-      <c r="U45" s="146"/>
-      <c r="V45" s="146"/>
-      <c r="W45" s="146"/>
-      <c r="X45" s="146"/>
-      <c r="Y45" s="146"/>
-      <c r="Z45" s="146"/>
-      <c r="AA45" s="146"/>
-      <c r="AB45" s="146"/>
-      <c r="AC45" s="146"/>
-      <c r="AD45" s="146"/>
-      <c r="AE45" s="146"/>
-      <c r="AF45" s="146"/>
-      <c r="AG45" s="146"/>
-      <c r="AH45" s="146"/>
-      <c r="AI45" s="146"/>
-      <c r="AJ45" s="146"/>
-      <c r="AK45" s="146"/>
-      <c r="AL45" s="146"/>
-      <c r="AM45" s="146"/>
-      <c r="AN45" s="146"/>
-      <c r="AO45" s="146"/>
-      <c r="AP45" s="146"/>
-      <c r="AQ45" s="146"/>
-      <c r="AR45" s="146"/>
-      <c r="AS45" s="146"/>
-      <c r="AT45" s="146"/>
-      <c r="AU45" s="146"/>
-      <c r="AV45" s="146"/>
-      <c r="AW45" s="146"/>
-      <c r="AX45" s="146"/>
-      <c r="AY45" s="146"/>
-      <c r="AZ45" s="147"/>
+      <c r="A45" s="217"/>
+      <c r="B45" s="218"/>
+      <c r="C45" s="218"/>
+      <c r="D45" s="218"/>
+      <c r="E45" s="218"/>
+      <c r="F45" s="218"/>
+      <c r="G45" s="218"/>
+      <c r="H45" s="218"/>
+      <c r="I45" s="218"/>
+      <c r="J45" s="218"/>
+      <c r="K45" s="218"/>
+      <c r="L45" s="218"/>
+      <c r="M45" s="218"/>
+      <c r="N45" s="218"/>
+      <c r="O45" s="218"/>
+      <c r="P45" s="218"/>
+      <c r="Q45" s="218"/>
+      <c r="R45" s="218"/>
+      <c r="S45" s="218"/>
+      <c r="T45" s="218"/>
+      <c r="U45" s="218"/>
+      <c r="V45" s="218"/>
+      <c r="W45" s="218"/>
+      <c r="X45" s="218"/>
+      <c r="Y45" s="218"/>
+      <c r="Z45" s="218"/>
+      <c r="AA45" s="218"/>
+      <c r="AB45" s="218"/>
+      <c r="AC45" s="218"/>
+      <c r="AD45" s="218"/>
+      <c r="AE45" s="218"/>
+      <c r="AF45" s="218"/>
+      <c r="AG45" s="218"/>
+      <c r="AH45" s="218"/>
+      <c r="AI45" s="218"/>
+      <c r="AJ45" s="218"/>
+      <c r="AK45" s="218"/>
+      <c r="AL45" s="218"/>
+      <c r="AM45" s="218"/>
+      <c r="AN45" s="218"/>
+      <c r="AO45" s="218"/>
+      <c r="AP45" s="218"/>
+      <c r="AQ45" s="218"/>
+      <c r="AR45" s="218"/>
+      <c r="AS45" s="218"/>
+      <c r="AT45" s="218"/>
+      <c r="AU45" s="218"/>
+      <c r="AV45" s="218"/>
+      <c r="AW45" s="218"/>
+      <c r="AX45" s="218"/>
+      <c r="AY45" s="218"/>
+      <c r="AZ45" s="219"/>
     </row>
     <row r="46" spans="1:52" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
@@ -7933,174 +7919,174 @@
       <c r="AZ46"/>
     </row>
     <row r="47" spans="1:52" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="149"/>
-      <c r="B47" s="149"/>
-      <c r="C47" s="149"/>
-      <c r="D47" s="149"/>
-      <c r="E47" s="149"/>
-      <c r="F47" s="149"/>
-      <c r="G47" s="149"/>
-      <c r="H47" s="149"/>
-      <c r="I47" s="149"/>
-      <c r="J47" s="149"/>
-      <c r="K47" s="149"/>
-      <c r="L47" s="149"/>
-      <c r="M47" s="149"/>
-      <c r="N47" s="149"/>
-      <c r="O47" s="149"/>
-      <c r="P47" s="149"/>
+      <c r="A47" s="117"/>
+      <c r="B47" s="117"/>
+      <c r="C47" s="117"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="117"/>
+      <c r="H47" s="117"/>
+      <c r="I47" s="117"/>
+      <c r="J47" s="117"/>
+      <c r="K47" s="117"/>
+      <c r="L47" s="117"/>
+      <c r="M47" s="117"/>
+      <c r="N47" s="117"/>
+      <c r="O47" s="117"/>
+      <c r="P47" s="117"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
-      <c r="S47" s="149"/>
-      <c r="T47" s="149"/>
-      <c r="U47" s="149"/>
-      <c r="V47" s="149"/>
-      <c r="W47" s="149"/>
-      <c r="X47" s="149"/>
-      <c r="Y47" s="149"/>
-      <c r="Z47" s="149"/>
-      <c r="AA47" s="149"/>
-      <c r="AB47" s="149"/>
-      <c r="AC47" s="149"/>
-      <c r="AD47" s="149"/>
-      <c r="AE47" s="149"/>
-      <c r="AF47" s="149"/>
-      <c r="AG47" s="149"/>
-      <c r="AH47" s="149"/>
+      <c r="S47" s="117"/>
+      <c r="T47" s="117"/>
+      <c r="U47" s="117"/>
+      <c r="V47" s="117"/>
+      <c r="W47" s="117"/>
+      <c r="X47" s="117"/>
+      <c r="Y47" s="117"/>
+      <c r="Z47" s="117"/>
+      <c r="AA47" s="117"/>
+      <c r="AB47" s="117"/>
+      <c r="AC47" s="117"/>
+      <c r="AD47" s="117"/>
+      <c r="AE47" s="117"/>
+      <c r="AF47" s="117"/>
+      <c r="AG47" s="117"/>
+      <c r="AH47" s="117"/>
       <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
-      <c r="AK47" s="149"/>
-      <c r="AL47" s="149"/>
-      <c r="AM47" s="149"/>
-      <c r="AN47" s="149"/>
-      <c r="AO47" s="149"/>
-      <c r="AP47" s="149"/>
-      <c r="AQ47" s="149"/>
-      <c r="AR47" s="149"/>
-      <c r="AS47" s="149"/>
-      <c r="AT47" s="149"/>
-      <c r="AU47" s="149"/>
-      <c r="AV47" s="149"/>
-      <c r="AW47" s="149"/>
-      <c r="AX47" s="149"/>
-      <c r="AY47" s="149"/>
-      <c r="AZ47" s="149"/>
+      <c r="AK47" s="117"/>
+      <c r="AL47" s="117"/>
+      <c r="AM47" s="117"/>
+      <c r="AN47" s="117"/>
+      <c r="AO47" s="117"/>
+      <c r="AP47" s="117"/>
+      <c r="AQ47" s="117"/>
+      <c r="AR47" s="117"/>
+      <c r="AS47" s="117"/>
+      <c r="AT47" s="117"/>
+      <c r="AU47" s="117"/>
+      <c r="AV47" s="117"/>
+      <c r="AW47" s="117"/>
+      <c r="AX47" s="117"/>
+      <c r="AY47" s="117"/>
+      <c r="AZ47" s="117"/>
     </row>
     <row r="48" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="213" t="s">
+      <c r="A48" s="118" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="213"/>
-      <c r="C48" s="213"/>
-      <c r="D48" s="213"/>
-      <c r="E48" s="213"/>
-      <c r="F48" s="213"/>
-      <c r="G48" s="213"/>
-      <c r="H48" s="213"/>
-      <c r="I48" s="213"/>
-      <c r="J48" s="213"/>
-      <c r="K48" s="213"/>
-      <c r="L48" s="213"/>
-      <c r="M48" s="213"/>
-      <c r="N48" s="213"/>
-      <c r="O48" s="213"/>
-      <c r="P48" s="213"/>
+      <c r="B48" s="118"/>
+      <c r="C48" s="118"/>
+      <c r="D48" s="118"/>
+      <c r="E48" s="118"/>
+      <c r="F48" s="118"/>
+      <c r="G48" s="118"/>
+      <c r="H48" s="118"/>
+      <c r="I48" s="118"/>
+      <c r="J48" s="118"/>
+      <c r="K48" s="118"/>
+      <c r="L48" s="118"/>
+      <c r="M48" s="118"/>
+      <c r="N48" s="118"/>
+      <c r="O48" s="118"/>
+      <c r="P48" s="118"/>
       <c r="Q48" s="54"/>
       <c r="R48" s="54"/>
-      <c r="S48" s="124" t="s">
+      <c r="S48" s="195" t="s">
         <v>78</v>
       </c>
-      <c r="T48" s="124"/>
-      <c r="U48" s="124"/>
-      <c r="V48" s="124"/>
-      <c r="W48" s="124"/>
-      <c r="X48" s="124"/>
-      <c r="Y48" s="124"/>
-      <c r="Z48" s="124"/>
-      <c r="AA48" s="124"/>
-      <c r="AB48" s="124"/>
-      <c r="AC48" s="124"/>
-      <c r="AD48" s="124"/>
-      <c r="AE48" s="124"/>
-      <c r="AF48" s="124"/>
-      <c r="AG48" s="124"/>
-      <c r="AH48" s="124"/>
+      <c r="T48" s="195"/>
+      <c r="U48" s="195"/>
+      <c r="V48" s="195"/>
+      <c r="W48" s="195"/>
+      <c r="X48" s="195"/>
+      <c r="Y48" s="195"/>
+      <c r="Z48" s="195"/>
+      <c r="AA48" s="195"/>
+      <c r="AB48" s="195"/>
+      <c r="AC48" s="195"/>
+      <c r="AD48" s="195"/>
+      <c r="AE48" s="195"/>
+      <c r="AF48" s="195"/>
+      <c r="AG48" s="195"/>
+      <c r="AH48" s="195"/>
       <c r="AI48" s="54"/>
       <c r="AJ48" s="54"/>
-      <c r="AK48" s="213" t="s">
+      <c r="AK48" s="118" t="s">
         <v>79</v>
       </c>
-      <c r="AL48" s="213"/>
-      <c r="AM48" s="213"/>
-      <c r="AN48" s="213"/>
-      <c r="AO48" s="213"/>
-      <c r="AP48" s="213"/>
-      <c r="AQ48" s="213"/>
-      <c r="AR48" s="213"/>
-      <c r="AS48" s="213"/>
-      <c r="AT48" s="213"/>
-      <c r="AU48" s="213"/>
-      <c r="AV48" s="213"/>
-      <c r="AW48" s="213"/>
-      <c r="AX48" s="213"/>
-      <c r="AY48" s="213"/>
-      <c r="AZ48" s="213"/>
+      <c r="AL48" s="118"/>
+      <c r="AM48" s="118"/>
+      <c r="AN48" s="118"/>
+      <c r="AO48" s="118"/>
+      <c r="AP48" s="118"/>
+      <c r="AQ48" s="118"/>
+      <c r="AR48" s="118"/>
+      <c r="AS48" s="118"/>
+      <c r="AT48" s="118"/>
+      <c r="AU48" s="118"/>
+      <c r="AV48" s="118"/>
+      <c r="AW48" s="118"/>
+      <c r="AX48" s="118"/>
+      <c r="AY48" s="118"/>
+      <c r="AZ48" s="118"/>
     </row>
     <row r="49" spans="1:52" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="89" t="s">
+      <c r="A49" s="120" t="s">
         <v>80</v>
       </c>
-      <c r="B49" s="89"/>
-      <c r="C49" s="89"/>
-      <c r="D49" s="89"/>
-      <c r="E49" s="89"/>
-      <c r="F49" s="89"/>
-      <c r="G49" s="89"/>
-      <c r="H49" s="89"/>
-      <c r="I49" s="89"/>
-      <c r="J49" s="89"/>
-      <c r="K49" s="89"/>
-      <c r="L49" s="89"/>
-      <c r="M49" s="89"/>
-      <c r="N49" s="89"/>
-      <c r="O49" s="89"/>
-      <c r="P49" s="89"/>
-      <c r="S49" s="89" t="s">
+      <c r="B49" s="120"/>
+      <c r="C49" s="120"/>
+      <c r="D49" s="120"/>
+      <c r="E49" s="120"/>
+      <c r="F49" s="120"/>
+      <c r="G49" s="120"/>
+      <c r="H49" s="120"/>
+      <c r="I49" s="120"/>
+      <c r="J49" s="120"/>
+      <c r="K49" s="120"/>
+      <c r="L49" s="120"/>
+      <c r="M49" s="120"/>
+      <c r="N49" s="120"/>
+      <c r="O49" s="120"/>
+      <c r="P49" s="120"/>
+      <c r="S49" s="120" t="s">
         <v>81</v>
       </c>
-      <c r="T49" s="89"/>
-      <c r="U49" s="89"/>
-      <c r="V49" s="89"/>
-      <c r="W49" s="89"/>
-      <c r="X49" s="89"/>
-      <c r="Y49" s="89"/>
-      <c r="Z49" s="89"/>
-      <c r="AA49" s="89"/>
-      <c r="AB49" s="89"/>
-      <c r="AC49" s="89"/>
-      <c r="AD49" s="89"/>
-      <c r="AE49" s="89"/>
-      <c r="AF49" s="89"/>
-      <c r="AG49" s="89"/>
-      <c r="AH49" s="89"/>
-      <c r="AK49" s="214" t="s">
+      <c r="T49" s="120"/>
+      <c r="U49" s="120"/>
+      <c r="V49" s="120"/>
+      <c r="W49" s="120"/>
+      <c r="X49" s="120"/>
+      <c r="Y49" s="120"/>
+      <c r="Z49" s="120"/>
+      <c r="AA49" s="120"/>
+      <c r="AB49" s="120"/>
+      <c r="AC49" s="120"/>
+      <c r="AD49" s="120"/>
+      <c r="AE49" s="120"/>
+      <c r="AF49" s="120"/>
+      <c r="AG49" s="120"/>
+      <c r="AH49" s="120"/>
+      <c r="AK49" s="119" t="s">
         <v>792</v>
       </c>
-      <c r="AL49" s="214"/>
-      <c r="AM49" s="214"/>
-      <c r="AN49" s="214"/>
-      <c r="AO49" s="214"/>
-      <c r="AP49" s="214"/>
-      <c r="AQ49" s="214"/>
-      <c r="AR49" s="214"/>
-      <c r="AS49" s="214"/>
-      <c r="AT49" s="214"/>
-      <c r="AU49" s="214"/>
-      <c r="AV49" s="214"/>
-      <c r="AW49" s="214"/>
-      <c r="AX49" s="214"/>
-      <c r="AY49" s="214"/>
-      <c r="AZ49" s="214"/>
+      <c r="AL49" s="119"/>
+      <c r="AM49" s="119"/>
+      <c r="AN49" s="119"/>
+      <c r="AO49" s="119"/>
+      <c r="AP49" s="119"/>
+      <c r="AQ49" s="119"/>
+      <c r="AR49" s="119"/>
+      <c r="AS49" s="119"/>
+      <c r="AT49" s="119"/>
+      <c r="AU49" s="119"/>
+      <c r="AV49" s="119"/>
+      <c r="AW49" s="119"/>
+      <c r="AX49" s="119"/>
+      <c r="AY49" s="119"/>
+      <c r="AZ49" s="119"/>
     </row>
     <row r="50" spans="1:52" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
@@ -9570,6 +9556,153 @@
   </sortState>
   <dataConsolidate function="count"/>
   <mergeCells count="171">
+    <mergeCell ref="S49:U49"/>
+    <mergeCell ref="V49:AH49"/>
+    <mergeCell ref="BD21:BE21"/>
+    <mergeCell ref="BD23:BE23"/>
+    <mergeCell ref="BD25:BE25"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="K12:AZ12"/>
+    <mergeCell ref="AH37:AZ37"/>
+    <mergeCell ref="AH38:AZ38"/>
+    <mergeCell ref="AH33:AZ34"/>
+    <mergeCell ref="AH35:AZ35"/>
+    <mergeCell ref="K13:AZ13"/>
+    <mergeCell ref="AE9:AK9"/>
+    <mergeCell ref="A14:AZ14"/>
+    <mergeCell ref="A16:AZ16"/>
+    <mergeCell ref="AV17:AZ17"/>
+    <mergeCell ref="AQ17:AU17"/>
+    <mergeCell ref="AL17:AP17"/>
+    <mergeCell ref="AG17:AK17"/>
+    <mergeCell ref="AB17:AF17"/>
+    <mergeCell ref="W17:AA17"/>
+    <mergeCell ref="AV18:AZ18"/>
+    <mergeCell ref="AQ18:AU18"/>
+    <mergeCell ref="AL18:AP18"/>
+    <mergeCell ref="S48:AH48"/>
+    <mergeCell ref="S33:AG34"/>
+    <mergeCell ref="AH36:AZ36"/>
+    <mergeCell ref="A36:R36"/>
+    <mergeCell ref="A37:R37"/>
+    <mergeCell ref="A35:R35"/>
+    <mergeCell ref="S35:AG35"/>
+    <mergeCell ref="A33:R34"/>
+    <mergeCell ref="S42:AG42"/>
+    <mergeCell ref="S41:AG41"/>
+    <mergeCell ref="A44:AZ45"/>
+    <mergeCell ref="A43:AZ43"/>
+    <mergeCell ref="S47:AH47"/>
+    <mergeCell ref="AH39:AZ39"/>
+    <mergeCell ref="S36:AG36"/>
+    <mergeCell ref="A40:R40"/>
+    <mergeCell ref="A42:R42"/>
+    <mergeCell ref="S39:AG39"/>
+    <mergeCell ref="S38:AG38"/>
+    <mergeCell ref="S37:AG37"/>
+    <mergeCell ref="AH42:AZ42"/>
+    <mergeCell ref="AH41:AZ41"/>
+    <mergeCell ref="AH40:AZ40"/>
+    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="R25:V25"/>
+    <mergeCell ref="AV24:AZ24"/>
+    <mergeCell ref="AV25:AZ25"/>
+    <mergeCell ref="AQ24:AU24"/>
+    <mergeCell ref="AQ25:AU25"/>
+    <mergeCell ref="W24:AA24"/>
+    <mergeCell ref="W25:AA25"/>
+    <mergeCell ref="AL24:AP24"/>
+    <mergeCell ref="AL25:AP25"/>
+    <mergeCell ref="AB25:AF25"/>
+    <mergeCell ref="AG25:AK25"/>
+    <mergeCell ref="A38:R38"/>
+    <mergeCell ref="AR7:AU7"/>
+    <mergeCell ref="AE8:AK8"/>
+    <mergeCell ref="AV7:AZ7"/>
+    <mergeCell ref="S40:AG40"/>
+    <mergeCell ref="A39:R39"/>
+    <mergeCell ref="R19:V19"/>
+    <mergeCell ref="R20:V20"/>
+    <mergeCell ref="R21:V21"/>
+    <mergeCell ref="R22:V22"/>
+    <mergeCell ref="R23:V23"/>
+    <mergeCell ref="R24:V24"/>
+    <mergeCell ref="AG20:AK20"/>
+    <mergeCell ref="AG21:AK21"/>
+    <mergeCell ref="AG22:AK22"/>
+    <mergeCell ref="AG23:AK23"/>
+    <mergeCell ref="AG18:AK18"/>
+    <mergeCell ref="AB18:AF18"/>
+    <mergeCell ref="AB21:AF21"/>
+    <mergeCell ref="W18:AA18"/>
+    <mergeCell ref="A15:AZ15"/>
+    <mergeCell ref="AG24:AK24"/>
+    <mergeCell ref="AV20:AZ20"/>
+    <mergeCell ref="AV21:AZ21"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="AS1:AZ3"/>
+    <mergeCell ref="G6:AZ6"/>
+    <mergeCell ref="K2:AP2"/>
+    <mergeCell ref="A4:AZ4"/>
+    <mergeCell ref="AL9:AZ9"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="R17:V17"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="AE5:AK5"/>
+    <mergeCell ref="G5:AB5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="G8:AC8"/>
+    <mergeCell ref="V7:Y7"/>
+    <mergeCell ref="G9:AC9"/>
+    <mergeCell ref="AL8:AZ8"/>
+    <mergeCell ref="AL5:AZ5"/>
+    <mergeCell ref="AB23:AF23"/>
+    <mergeCell ref="AB24:AF24"/>
+    <mergeCell ref="Z7:AP7"/>
+    <mergeCell ref="AV23:AZ23"/>
+    <mergeCell ref="AQ19:AU19"/>
+    <mergeCell ref="AQ20:AU20"/>
+    <mergeCell ref="AQ21:AU21"/>
+    <mergeCell ref="AQ22:AU22"/>
+    <mergeCell ref="AQ23:AU23"/>
+    <mergeCell ref="W20:AA20"/>
+    <mergeCell ref="W21:AA21"/>
+    <mergeCell ref="W22:AA22"/>
+    <mergeCell ref="W23:AA23"/>
+    <mergeCell ref="AL19:AP19"/>
+    <mergeCell ref="AL20:AP20"/>
+    <mergeCell ref="AL21:AP21"/>
+    <mergeCell ref="AL22:AP22"/>
+    <mergeCell ref="AL23:AP23"/>
+    <mergeCell ref="AG19:AK19"/>
+    <mergeCell ref="A47:P47"/>
+    <mergeCell ref="AK47:AZ47"/>
+    <mergeCell ref="AK48:AZ48"/>
+    <mergeCell ref="A48:P48"/>
+    <mergeCell ref="AK49:AZ49"/>
+    <mergeCell ref="A49:P49"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="M23:Q23"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="AB19:AF19"/>
+    <mergeCell ref="AB20:AF20"/>
+    <mergeCell ref="W19:AA19"/>
+    <mergeCell ref="AB22:AF22"/>
     <mergeCell ref="R18:V18"/>
     <mergeCell ref="M18:Q18"/>
     <mergeCell ref="A18:L18"/>
@@ -9594,153 +9727,6 @@
     <mergeCell ref="AA31:AS31"/>
     <mergeCell ref="AT31:AZ31"/>
     <mergeCell ref="AV22:AZ22"/>
-    <mergeCell ref="A47:P47"/>
-    <mergeCell ref="AK47:AZ47"/>
-    <mergeCell ref="AK48:AZ48"/>
-    <mergeCell ref="A48:P48"/>
-    <mergeCell ref="AK49:AZ49"/>
-    <mergeCell ref="A49:P49"/>
-    <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="M21:Q21"/>
-    <mergeCell ref="M22:Q22"/>
-    <mergeCell ref="M23:Q23"/>
-    <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="M25:Q25"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A21:L21"/>
-    <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="AB19:AF19"/>
-    <mergeCell ref="AB20:AF20"/>
-    <mergeCell ref="W19:AA19"/>
-    <mergeCell ref="AB22:AF22"/>
-    <mergeCell ref="AB23:AF23"/>
-    <mergeCell ref="AB24:AF24"/>
-    <mergeCell ref="Z7:AP7"/>
-    <mergeCell ref="AV23:AZ23"/>
-    <mergeCell ref="AQ19:AU19"/>
-    <mergeCell ref="AQ20:AU20"/>
-    <mergeCell ref="AQ21:AU21"/>
-    <mergeCell ref="AQ22:AU22"/>
-    <mergeCell ref="AQ23:AU23"/>
-    <mergeCell ref="W20:AA20"/>
-    <mergeCell ref="W21:AA21"/>
-    <mergeCell ref="W22:AA22"/>
-    <mergeCell ref="W23:AA23"/>
-    <mergeCell ref="AL19:AP19"/>
-    <mergeCell ref="AL20:AP20"/>
-    <mergeCell ref="AL21:AP21"/>
-    <mergeCell ref="AL22:AP22"/>
-    <mergeCell ref="AL23:AP23"/>
-    <mergeCell ref="AG19:AK19"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="AS1:AZ3"/>
-    <mergeCell ref="G6:AZ6"/>
-    <mergeCell ref="K2:AP2"/>
-    <mergeCell ref="A4:AZ4"/>
-    <mergeCell ref="AL9:AZ9"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="R17:V17"/>
-    <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="AE5:AK5"/>
-    <mergeCell ref="G5:AB5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="G8:AC8"/>
-    <mergeCell ref="V7:Y7"/>
-    <mergeCell ref="G9:AC9"/>
-    <mergeCell ref="AL8:AZ8"/>
-    <mergeCell ref="AL5:AZ5"/>
-    <mergeCell ref="A38:R38"/>
-    <mergeCell ref="AR7:AU7"/>
-    <mergeCell ref="AE8:AK8"/>
-    <mergeCell ref="AV7:AZ7"/>
-    <mergeCell ref="S40:AG40"/>
-    <mergeCell ref="A39:R39"/>
-    <mergeCell ref="R19:V19"/>
-    <mergeCell ref="R20:V20"/>
-    <mergeCell ref="R21:V21"/>
-    <mergeCell ref="R22:V22"/>
-    <mergeCell ref="R23:V23"/>
-    <mergeCell ref="R24:V24"/>
-    <mergeCell ref="AG20:AK20"/>
-    <mergeCell ref="AG21:AK21"/>
-    <mergeCell ref="AG22:AK22"/>
-    <mergeCell ref="AG23:AK23"/>
-    <mergeCell ref="AG18:AK18"/>
-    <mergeCell ref="AB18:AF18"/>
-    <mergeCell ref="AB21:AF21"/>
-    <mergeCell ref="W18:AA18"/>
-    <mergeCell ref="A15:AZ15"/>
-    <mergeCell ref="AG24:AK24"/>
-    <mergeCell ref="AV20:AZ20"/>
-    <mergeCell ref="AV21:AZ21"/>
-    <mergeCell ref="R25:V25"/>
-    <mergeCell ref="AV24:AZ24"/>
-    <mergeCell ref="AV25:AZ25"/>
-    <mergeCell ref="AQ24:AU24"/>
-    <mergeCell ref="AQ25:AU25"/>
-    <mergeCell ref="W24:AA24"/>
-    <mergeCell ref="W25:AA25"/>
-    <mergeCell ref="AL24:AP24"/>
-    <mergeCell ref="AL25:AP25"/>
-    <mergeCell ref="AB25:AF25"/>
-    <mergeCell ref="AG25:AK25"/>
-    <mergeCell ref="S48:AH48"/>
-    <mergeCell ref="S33:AG34"/>
-    <mergeCell ref="AH36:AZ36"/>
-    <mergeCell ref="A36:R36"/>
-    <mergeCell ref="A37:R37"/>
-    <mergeCell ref="A35:R35"/>
-    <mergeCell ref="S35:AG35"/>
-    <mergeCell ref="A33:R34"/>
-    <mergeCell ref="S42:AG42"/>
-    <mergeCell ref="S41:AG41"/>
-    <mergeCell ref="A44:AZ45"/>
-    <mergeCell ref="A43:AZ43"/>
-    <mergeCell ref="S47:AH47"/>
-    <mergeCell ref="AH39:AZ39"/>
-    <mergeCell ref="S36:AG36"/>
-    <mergeCell ref="A40:R40"/>
-    <mergeCell ref="A42:R42"/>
-    <mergeCell ref="S39:AG39"/>
-    <mergeCell ref="S38:AG38"/>
-    <mergeCell ref="S37:AG37"/>
-    <mergeCell ref="AH42:AZ42"/>
-    <mergeCell ref="AH41:AZ41"/>
-    <mergeCell ref="AH40:AZ40"/>
-    <mergeCell ref="A41:R41"/>
-    <mergeCell ref="S49:U49"/>
-    <mergeCell ref="V49:AH49"/>
-    <mergeCell ref="BD21:BE21"/>
-    <mergeCell ref="BD23:BE23"/>
-    <mergeCell ref="BD25:BE25"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="K12:AZ12"/>
-    <mergeCell ref="AH37:AZ37"/>
-    <mergeCell ref="AH38:AZ38"/>
-    <mergeCell ref="AH33:AZ34"/>
-    <mergeCell ref="AH35:AZ35"/>
-    <mergeCell ref="K13:AZ13"/>
-    <mergeCell ref="AE9:AK9"/>
-    <mergeCell ref="A14:AZ14"/>
-    <mergeCell ref="A16:AZ16"/>
-    <mergeCell ref="AV17:AZ17"/>
-    <mergeCell ref="AQ17:AU17"/>
-    <mergeCell ref="AL17:AP17"/>
-    <mergeCell ref="AG17:AK17"/>
-    <mergeCell ref="AB17:AF17"/>
-    <mergeCell ref="W17:AA17"/>
-    <mergeCell ref="AV18:AZ18"/>
-    <mergeCell ref="AQ18:AU18"/>
-    <mergeCell ref="AL18:AP18"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations count="1">
@@ -9780,14 +9766,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="170"/>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="172"/>
+      <c r="A1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="139"/>
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
       <c r="K1" s="21"/>
@@ -9824,87 +9810,87 @@
       <c r="AP1" s="22"/>
       <c r="AQ1" s="22"/>
       <c r="AR1" s="22"/>
-      <c r="AS1" s="179" t="s">
+      <c r="AS1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="AT1" s="180"/>
-      <c r="AU1" s="180"/>
-      <c r="AV1" s="180"/>
-      <c r="AW1" s="180"/>
-      <c r="AX1" s="180"/>
-      <c r="AY1" s="180"/>
-      <c r="AZ1" s="181"/>
+      <c r="AT1" s="147"/>
+      <c r="AU1" s="147"/>
+      <c r="AV1" s="147"/>
+      <c r="AW1" s="147"/>
+      <c r="AX1" s="147"/>
+      <c r="AY1" s="147"/>
+      <c r="AZ1" s="148"/>
       <c r="BD1" s="23"/>
       <c r="BF1" s="27"/>
       <c r="BG1" s="27"/>
     </row>
     <row r="2" spans="1:60" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="173"/>
-      <c r="B2" s="174"/>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174"/>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
-      <c r="H2" s="175"/>
-      <c r="K2" s="189" t="s">
+      <c r="A2" s="140"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="142"/>
+      <c r="K2" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="254"/>
-      <c r="M2" s="254"/>
-      <c r="N2" s="254"/>
-      <c r="O2" s="254"/>
-      <c r="P2" s="254"/>
-      <c r="Q2" s="254"/>
-      <c r="R2" s="254"/>
-      <c r="S2" s="254"/>
-      <c r="T2" s="254"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="254"/>
-      <c r="W2" s="254"/>
-      <c r="X2" s="254"/>
-      <c r="Y2" s="254"/>
-      <c r="Z2" s="254"/>
-      <c r="AA2" s="254"/>
-      <c r="AB2" s="254"/>
-      <c r="AC2" s="254"/>
-      <c r="AD2" s="254"/>
-      <c r="AE2" s="254"/>
-      <c r="AF2" s="254"/>
-      <c r="AG2" s="254"/>
-      <c r="AH2" s="254"/>
-      <c r="AI2" s="254"/>
-      <c r="AJ2" s="254"/>
-      <c r="AK2" s="254"/>
-      <c r="AL2" s="254"/>
-      <c r="AM2" s="254"/>
-      <c r="AN2" s="254"/>
-      <c r="AO2" s="254"/>
-      <c r="AP2" s="254"/>
+      <c r="L2" s="249"/>
+      <c r="M2" s="249"/>
+      <c r="N2" s="249"/>
+      <c r="O2" s="249"/>
+      <c r="P2" s="249"/>
+      <c r="Q2" s="249"/>
+      <c r="R2" s="249"/>
+      <c r="S2" s="249"/>
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
+      <c r="AA2" s="249"/>
+      <c r="AB2" s="249"/>
+      <c r="AC2" s="249"/>
+      <c r="AD2" s="249"/>
+      <c r="AE2" s="249"/>
+      <c r="AF2" s="249"/>
+      <c r="AG2" s="249"/>
+      <c r="AH2" s="249"/>
+      <c r="AI2" s="249"/>
+      <c r="AJ2" s="249"/>
+      <c r="AK2" s="249"/>
+      <c r="AL2" s="249"/>
+      <c r="AM2" s="249"/>
+      <c r="AN2" s="249"/>
+      <c r="AO2" s="249"/>
+      <c r="AP2" s="249"/>
       <c r="AQ2" s="17"/>
       <c r="AR2" s="17"/>
-      <c r="AS2" s="182"/>
-      <c r="AT2" s="183"/>
-      <c r="AU2" s="183"/>
-      <c r="AV2" s="183"/>
-      <c r="AW2" s="183"/>
-      <c r="AX2" s="183"/>
-      <c r="AY2" s="183"/>
-      <c r="AZ2" s="184"/>
+      <c r="AS2" s="149"/>
+      <c r="AT2" s="150"/>
+      <c r="AU2" s="150"/>
+      <c r="AV2" s="150"/>
+      <c r="AW2" s="150"/>
+      <c r="AX2" s="150"/>
+      <c r="AY2" s="150"/>
+      <c r="AZ2" s="151"/>
       <c r="BA2" s="7"/>
       <c r="BF2" s="25"/>
       <c r="BG2" s="25"/>
       <c r="BH2" s="25"/>
     </row>
     <row r="3" spans="1:60" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="176"/>
-      <c r="B3" s="177"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="177"/>
-      <c r="H3" s="178"/>
+      <c r="A3" s="143"/>
+      <c r="B3" s="144"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="145"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -9941,80 +9927,80 @@
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
       <c r="AR3" s="4"/>
-      <c r="AS3" s="185"/>
-      <c r="AT3" s="186"/>
-      <c r="AU3" s="186"/>
-      <c r="AV3" s="186"/>
-      <c r="AW3" s="186"/>
-      <c r="AX3" s="186"/>
-      <c r="AY3" s="186"/>
-      <c r="AZ3" s="187"/>
+      <c r="AS3" s="152"/>
+      <c r="AT3" s="153"/>
+      <c r="AU3" s="153"/>
+      <c r="AV3" s="153"/>
+      <c r="AW3" s="153"/>
+      <c r="AX3" s="153"/>
+      <c r="AY3" s="153"/>
+      <c r="AZ3" s="154"/>
     </row>
     <row r="4" spans="1:60" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="191" t="s">
+      <c r="A4" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="192"/>
-      <c r="C4" s="192"/>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="192"/>
-      <c r="L4" s="192"/>
-      <c r="M4" s="192"/>
-      <c r="N4" s="192"/>
-      <c r="O4" s="192"/>
-      <c r="P4" s="192"/>
-      <c r="Q4" s="192"/>
-      <c r="R4" s="192"/>
-      <c r="S4" s="192"/>
-      <c r="T4" s="192"/>
-      <c r="U4" s="192"/>
-      <c r="V4" s="192"/>
-      <c r="W4" s="192"/>
-      <c r="X4" s="192"/>
-      <c r="Y4" s="192"/>
-      <c r="Z4" s="192"/>
-      <c r="AA4" s="192"/>
-      <c r="AB4" s="192"/>
-      <c r="AC4" s="192"/>
-      <c r="AD4" s="192"/>
-      <c r="AE4" s="192"/>
-      <c r="AF4" s="192"/>
-      <c r="AG4" s="192"/>
-      <c r="AH4" s="192"/>
-      <c r="AI4" s="192"/>
-      <c r="AJ4" s="192"/>
-      <c r="AK4" s="192"/>
-      <c r="AL4" s="192"/>
-      <c r="AM4" s="192"/>
-      <c r="AN4" s="192"/>
-      <c r="AO4" s="192"/>
-      <c r="AP4" s="192"/>
-      <c r="AQ4" s="192"/>
-      <c r="AR4" s="192"/>
-      <c r="AS4" s="192"/>
-      <c r="AT4" s="192"/>
-      <c r="AU4" s="192"/>
-      <c r="AV4" s="192"/>
-      <c r="AW4" s="192"/>
-      <c r="AX4" s="192"/>
-      <c r="AY4" s="192"/>
-      <c r="AZ4" s="193"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="101"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="101"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="101"/>
+      <c r="S4" s="101"/>
+      <c r="T4" s="101"/>
+      <c r="U4" s="101"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="101"/>
+      <c r="X4" s="101"/>
+      <c r="Y4" s="101"/>
+      <c r="Z4" s="101"/>
+      <c r="AA4" s="101"/>
+      <c r="AB4" s="101"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="101"/>
+      <c r="AE4" s="101"/>
+      <c r="AF4" s="101"/>
+      <c r="AG4" s="101"/>
+      <c r="AH4" s="101"/>
+      <c r="AI4" s="101"/>
+      <c r="AJ4" s="101"/>
+      <c r="AK4" s="101"/>
+      <c r="AL4" s="101"/>
+      <c r="AM4" s="101"/>
+      <c r="AN4" s="101"/>
+      <c r="AO4" s="101"/>
+      <c r="AP4" s="101"/>
+      <c r="AQ4" s="101"/>
+      <c r="AR4" s="101"/>
+      <c r="AS4" s="101"/>
+      <c r="AT4" s="101"/>
+      <c r="AU4" s="101"/>
+      <c r="AV4" s="101"/>
+      <c r="AW4" s="101"/>
+      <c r="AX4" s="101"/>
+      <c r="AY4" s="101"/>
+      <c r="AZ4" s="102"/>
       <c r="BA4" s="9"/>
       <c r="BB4" s="9"/>
       <c r="BC4" s="9"/>
     </row>
     <row r="5" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="255" t="s">
+      <c r="A5" s="250" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="256"/>
-      <c r="C5" s="256"/>
+      <c r="B5" s="251"/>
+      <c r="C5" s="251"/>
       <c r="D5" s="11"/>
       <c r="E5" s="6" t="s">
         <v>105</v>
@@ -10071,63 +10057,63 @@
       <c r="BC5" s="9"/>
     </row>
     <row r="6" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="250"/>
-      <c r="B6" s="251"/>
-      <c r="C6" s="251"/>
+      <c r="A6" s="247"/>
+      <c r="B6" s="248"/>
+      <c r="C6" s="248"/>
       <c r="D6" s="10"/>
-      <c r="E6" s="257"/>
-      <c r="F6" s="257"/>
-      <c r="G6" s="257"/>
-      <c r="H6" s="257"/>
-      <c r="I6" s="257"/>
-      <c r="J6" s="257"/>
-      <c r="K6" s="257"/>
-      <c r="L6" s="257"/>
-      <c r="M6" s="257"/>
-      <c r="N6" s="257"/>
-      <c r="O6" s="257"/>
-      <c r="P6" s="257"/>
-      <c r="Q6" s="257"/>
-      <c r="R6" s="257"/>
-      <c r="S6" s="257"/>
-      <c r="T6" s="257"/>
-      <c r="U6" s="257"/>
-      <c r="V6" s="257"/>
-      <c r="W6" s="257"/>
-      <c r="X6" s="257"/>
-      <c r="Y6" s="257"/>
-      <c r="Z6" s="257"/>
-      <c r="AA6" s="257"/>
-      <c r="AB6" s="257"/>
-      <c r="AC6" s="257"/>
-      <c r="AD6" s="257"/>
-      <c r="AE6" s="257"/>
-      <c r="AF6" s="257"/>
-      <c r="AG6" s="257"/>
-      <c r="AH6" s="257"/>
-      <c r="AI6" s="257"/>
-      <c r="AJ6" s="257"/>
-      <c r="AK6" s="257"/>
-      <c r="AL6" s="257"/>
-      <c r="AM6" s="257"/>
-      <c r="AN6" s="257"/>
-      <c r="AO6" s="257"/>
-      <c r="AP6" s="257"/>
-      <c r="AQ6" s="257"/>
-      <c r="AR6" s="257"/>
-      <c r="AS6" s="257"/>
-      <c r="AT6" s="257"/>
-      <c r="AU6" s="257"/>
-      <c r="AV6" s="257"/>
-      <c r="AW6" s="257"/>
-      <c r="AX6" s="257"/>
-      <c r="AY6" s="257"/>
-      <c r="AZ6" s="258"/>
+      <c r="E6" s="252"/>
+      <c r="F6" s="252"/>
+      <c r="G6" s="252"/>
+      <c r="H6" s="252"/>
+      <c r="I6" s="252"/>
+      <c r="J6" s="252"/>
+      <c r="K6" s="252"/>
+      <c r="L6" s="252"/>
+      <c r="M6" s="252"/>
+      <c r="N6" s="252"/>
+      <c r="O6" s="252"/>
+      <c r="P6" s="252"/>
+      <c r="Q6" s="252"/>
+      <c r="R6" s="252"/>
+      <c r="S6" s="252"/>
+      <c r="T6" s="252"/>
+      <c r="U6" s="252"/>
+      <c r="V6" s="252"/>
+      <c r="W6" s="252"/>
+      <c r="X6" s="252"/>
+      <c r="Y6" s="252"/>
+      <c r="Z6" s="252"/>
+      <c r="AA6" s="252"/>
+      <c r="AB6" s="252"/>
+      <c r="AC6" s="252"/>
+      <c r="AD6" s="252"/>
+      <c r="AE6" s="252"/>
+      <c r="AF6" s="252"/>
+      <c r="AG6" s="252"/>
+      <c r="AH6" s="252"/>
+      <c r="AI6" s="252"/>
+      <c r="AJ6" s="252"/>
+      <c r="AK6" s="252"/>
+      <c r="AL6" s="252"/>
+      <c r="AM6" s="252"/>
+      <c r="AN6" s="252"/>
+      <c r="AO6" s="252"/>
+      <c r="AP6" s="252"/>
+      <c r="AQ6" s="252"/>
+      <c r="AR6" s="252"/>
+      <c r="AS6" s="252"/>
+      <c r="AT6" s="252"/>
+      <c r="AU6" s="252"/>
+      <c r="AV6" s="252"/>
+      <c r="AW6" s="252"/>
+      <c r="AX6" s="252"/>
+      <c r="AY6" s="252"/>
+      <c r="AZ6" s="253"/>
     </row>
     <row r="7" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="250"/>
-      <c r="B7" s="251"/>
-      <c r="C7" s="251"/>
+      <c r="A7" s="247"/>
+      <c r="B7" s="248"/>
+      <c r="C7" s="248"/>
       <c r="D7" s="10"/>
       <c r="E7" s="86"/>
       <c r="F7" s="87"/>
@@ -10179,9 +10165,9 @@
       <c r="AZ7" s="88"/>
     </row>
     <row r="8" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="259"/>
-      <c r="B8" s="260"/>
-      <c r="C8" s="260"/>
+      <c r="A8" s="245"/>
+      <c r="B8" s="246"/>
+      <c r="C8" s="246"/>
       <c r="D8" s="10"/>
       <c r="E8" s="87"/>
       <c r="F8" s="87"/>
@@ -10233,63 +10219,63 @@
       <c r="AZ8" s="88"/>
     </row>
     <row r="9" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="259"/>
-      <c r="B9" s="260"/>
-      <c r="C9" s="260"/>
+      <c r="A9" s="245"/>
+      <c r="B9" s="246"/>
+      <c r="C9" s="246"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="252"/>
-      <c r="F9" s="252"/>
-      <c r="G9" s="252"/>
-      <c r="H9" s="252"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="252"/>
-      <c r="K9" s="252"/>
-      <c r="L9" s="252"/>
-      <c r="M9" s="252"/>
-      <c r="N9" s="252"/>
-      <c r="O9" s="252"/>
-      <c r="P9" s="252"/>
-      <c r="Q9" s="252"/>
-      <c r="R9" s="252"/>
-      <c r="S9" s="252"/>
-      <c r="T9" s="252"/>
-      <c r="U9" s="252"/>
-      <c r="V9" s="252"/>
-      <c r="W9" s="252"/>
-      <c r="X9" s="252"/>
-      <c r="Y9" s="252"/>
-      <c r="Z9" s="252"/>
-      <c r="AA9" s="252"/>
-      <c r="AB9" s="252"/>
-      <c r="AC9" s="252"/>
-      <c r="AD9" s="252"/>
-      <c r="AE9" s="252"/>
-      <c r="AF9" s="252"/>
-      <c r="AG9" s="252"/>
-      <c r="AH9" s="252"/>
-      <c r="AI9" s="252"/>
-      <c r="AJ9" s="252"/>
-      <c r="AK9" s="252"/>
-      <c r="AL9" s="252"/>
-      <c r="AM9" s="252"/>
-      <c r="AN9" s="252"/>
-      <c r="AO9" s="252"/>
-      <c r="AP9" s="252"/>
-      <c r="AQ9" s="252"/>
-      <c r="AR9" s="252"/>
-      <c r="AS9" s="252"/>
-      <c r="AT9" s="252"/>
-      <c r="AU9" s="252"/>
-      <c r="AV9" s="252"/>
-      <c r="AW9" s="252"/>
-      <c r="AX9" s="252"/>
-      <c r="AY9" s="252"/>
-      <c r="AZ9" s="253"/>
+      <c r="E9" s="254"/>
+      <c r="F9" s="254"/>
+      <c r="G9" s="254"/>
+      <c r="H9" s="254"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="254"/>
+      <c r="K9" s="254"/>
+      <c r="L9" s="254"/>
+      <c r="M9" s="254"/>
+      <c r="N9" s="254"/>
+      <c r="O9" s="254"/>
+      <c r="P9" s="254"/>
+      <c r="Q9" s="254"/>
+      <c r="R9" s="254"/>
+      <c r="S9" s="254"/>
+      <c r="T9" s="254"/>
+      <c r="U9" s="254"/>
+      <c r="V9" s="254"/>
+      <c r="W9" s="254"/>
+      <c r="X9" s="254"/>
+      <c r="Y9" s="254"/>
+      <c r="Z9" s="254"/>
+      <c r="AA9" s="254"/>
+      <c r="AB9" s="254"/>
+      <c r="AC9" s="254"/>
+      <c r="AD9" s="254"/>
+      <c r="AE9" s="254"/>
+      <c r="AF9" s="254"/>
+      <c r="AG9" s="254"/>
+      <c r="AH9" s="254"/>
+      <c r="AI9" s="254"/>
+      <c r="AJ9" s="254"/>
+      <c r="AK9" s="254"/>
+      <c r="AL9" s="254"/>
+      <c r="AM9" s="254"/>
+      <c r="AN9" s="254"/>
+      <c r="AO9" s="254"/>
+      <c r="AP9" s="254"/>
+      <c r="AQ9" s="254"/>
+      <c r="AR9" s="254"/>
+      <c r="AS9" s="254"/>
+      <c r="AT9" s="254"/>
+      <c r="AU9" s="254"/>
+      <c r="AV9" s="254"/>
+      <c r="AW9" s="254"/>
+      <c r="AX9" s="254"/>
+      <c r="AY9" s="254"/>
+      <c r="AZ9" s="255"/>
     </row>
     <row r="10" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="259"/>
-      <c r="B10" s="260"/>
-      <c r="C10" s="260"/>
+      <c r="A10" s="245"/>
+      <c r="B10" s="246"/>
+      <c r="C10" s="246"/>
       <c r="D10" s="10"/>
       <c r="E10" s="86"/>
       <c r="F10" s="87"/>
@@ -10341,9 +10327,9 @@
       <c r="AZ10" s="88"/>
     </row>
     <row r="11" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="250"/>
-      <c r="B11" s="251"/>
-      <c r="C11" s="251"/>
+      <c r="A11" s="247"/>
+      <c r="B11" s="248"/>
+      <c r="C11" s="248"/>
       <c r="D11" s="10"/>
       <c r="E11" s="87"/>
       <c r="F11" s="87"/>
@@ -10395,9 +10381,9 @@
       <c r="AZ11" s="88"/>
     </row>
     <row r="12" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="250"/>
-      <c r="B12" s="251"/>
-      <c r="C12" s="251"/>
+      <c r="A12" s="247"/>
+      <c r="B12" s="248"/>
+      <c r="C12" s="248"/>
       <c r="D12" s="10"/>
       <c r="E12" s="87"/>
       <c r="F12" s="87"/>
@@ -10449,9 +10435,9 @@
       <c r="AZ12" s="88"/>
     </row>
     <row r="13" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="250"/>
-      <c r="B13" s="251"/>
-      <c r="C13" s="251"/>
+      <c r="A13" s="247"/>
+      <c r="B13" s="248"/>
+      <c r="C13" s="248"/>
       <c r="D13" s="10"/>
       <c r="E13" s="87"/>
       <c r="F13" s="87"/>
@@ -10503,9 +10489,9 @@
       <c r="AZ13" s="88"/>
     </row>
     <row r="14" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="250"/>
-      <c r="B14" s="251"/>
-      <c r="C14" s="251"/>
+      <c r="A14" s="247"/>
+      <c r="B14" s="248"/>
+      <c r="C14" s="248"/>
       <c r="D14" s="10"/>
       <c r="E14" s="87"/>
       <c r="F14" s="87"/>
@@ -10557,9 +10543,9 @@
       <c r="AZ14" s="88"/>
     </row>
     <row r="15" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="250"/>
-      <c r="B15" s="251"/>
-      <c r="C15" s="251"/>
+      <c r="A15" s="247"/>
+      <c r="B15" s="248"/>
+      <c r="C15" s="248"/>
       <c r="D15" s="10"/>
       <c r="E15" s="86"/>
       <c r="F15" s="87"/>
@@ -10611,9 +10597,9 @@
       <c r="AZ15" s="88"/>
     </row>
     <row r="16" spans="1:60" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="250"/>
-      <c r="B16" s="251"/>
-      <c r="C16" s="251"/>
+      <c r="A16" s="247"/>
+      <c r="B16" s="248"/>
+      <c r="C16" s="248"/>
       <c r="D16" s="10"/>
       <c r="E16" s="86"/>
       <c r="F16" s="87"/>
@@ -10665,9 +10651,9 @@
       <c r="AZ16" s="88"/>
     </row>
     <row r="17" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="250"/>
-      <c r="B17" s="251"/>
-      <c r="C17" s="251"/>
+      <c r="A17" s="247"/>
+      <c r="B17" s="248"/>
+      <c r="C17" s="248"/>
       <c r="D17" s="10"/>
       <c r="E17" s="86"/>
       <c r="F17" s="87"/>
@@ -10719,9 +10705,9 @@
       <c r="AZ17" s="88"/>
     </row>
     <row r="18" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="250"/>
-      <c r="B18" s="251"/>
-      <c r="C18" s="251"/>
+      <c r="A18" s="247"/>
+      <c r="B18" s="248"/>
+      <c r="C18" s="248"/>
       <c r="D18" s="10"/>
       <c r="E18" s="86"/>
       <c r="F18" s="87"/>
@@ -10773,9 +10759,9 @@
       <c r="AZ18" s="88"/>
     </row>
     <row r="19" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="250"/>
-      <c r="B19" s="251"/>
-      <c r="C19" s="251"/>
+      <c r="A19" s="247"/>
+      <c r="B19" s="248"/>
+      <c r="C19" s="248"/>
       <c r="D19" s="10"/>
       <c r="E19" s="86"/>
       <c r="F19" s="87"/>
@@ -10827,9 +10813,9 @@
       <c r="AZ19" s="88"/>
     </row>
     <row r="20" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="250"/>
-      <c r="B20" s="251"/>
-      <c r="C20" s="251"/>
+      <c r="A20" s="247"/>
+      <c r="B20" s="248"/>
+      <c r="C20" s="248"/>
       <c r="D20" s="10"/>
       <c r="E20" s="86"/>
       <c r="F20" s="87"/>
@@ -10881,9 +10867,9 @@
       <c r="AZ20" s="88"/>
     </row>
     <row r="21" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="250"/>
-      <c r="B21" s="251"/>
-      <c r="C21" s="251"/>
+      <c r="A21" s="247"/>
+      <c r="B21" s="248"/>
+      <c r="C21" s="248"/>
       <c r="D21" s="10"/>
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
@@ -10935,9 +10921,9 @@
       <c r="AZ21" s="88"/>
     </row>
     <row r="22" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="250"/>
-      <c r="B22" s="251"/>
-      <c r="C22" s="251"/>
+      <c r="A22" s="247"/>
+      <c r="B22" s="248"/>
+      <c r="C22" s="248"/>
       <c r="D22" s="10"/>
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
@@ -10989,9 +10975,9 @@
       <c r="AZ22" s="88"/>
     </row>
     <row r="23" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="250"/>
-      <c r="B23" s="251"/>
-      <c r="C23" s="251"/>
+      <c r="A23" s="247"/>
+      <c r="B23" s="248"/>
+      <c r="C23" s="248"/>
       <c r="D23" s="10"/>
       <c r="E23" s="86"/>
       <c r="F23" s="87"/>
@@ -11043,9 +11029,9 @@
       <c r="AZ23" s="88"/>
     </row>
     <row r="24" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="250"/>
-      <c r="B24" s="251"/>
-      <c r="C24" s="251"/>
+      <c r="A24" s="247"/>
+      <c r="B24" s="248"/>
+      <c r="C24" s="248"/>
       <c r="D24" s="10"/>
       <c r="E24" s="87"/>
       <c r="F24" s="87"/>
@@ -11097,9 +11083,9 @@
       <c r="AZ24" s="88"/>
     </row>
     <row r="25" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="250"/>
-      <c r="B25" s="251"/>
-      <c r="C25" s="251"/>
+      <c r="A25" s="247"/>
+      <c r="B25" s="248"/>
+      <c r="C25" s="248"/>
       <c r="D25" s="10"/>
       <c r="E25" s="86"/>
       <c r="F25" s="87"/>
@@ -11151,922 +11137,922 @@
       <c r="AZ25" s="88"/>
     </row>
     <row r="26" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="250"/>
-      <c r="B26" s="251"/>
-      <c r="C26" s="251"/>
+      <c r="A26" s="247"/>
+      <c r="B26" s="248"/>
+      <c r="C26" s="248"/>
       <c r="D26" s="10"/>
-      <c r="E26" s="245"/>
-      <c r="F26" s="245"/>
-      <c r="G26" s="245"/>
-      <c r="H26" s="245"/>
-      <c r="I26" s="245"/>
-      <c r="J26" s="245"/>
-      <c r="K26" s="245"/>
-      <c r="L26" s="245"/>
-      <c r="M26" s="245"/>
-      <c r="N26" s="245"/>
-      <c r="O26" s="245"/>
-      <c r="P26" s="245"/>
-      <c r="Q26" s="245"/>
-      <c r="R26" s="245"/>
-      <c r="S26" s="245"/>
-      <c r="T26" s="245"/>
-      <c r="U26" s="245"/>
-      <c r="V26" s="245"/>
-      <c r="W26" s="245"/>
-      <c r="X26" s="245"/>
-      <c r="Y26" s="245"/>
-      <c r="Z26" s="245"/>
-      <c r="AA26" s="245"/>
-      <c r="AB26" s="245"/>
-      <c r="AC26" s="245"/>
-      <c r="AD26" s="245"/>
-      <c r="AE26" s="245"/>
-      <c r="AF26" s="245"/>
-      <c r="AG26" s="245"/>
-      <c r="AH26" s="245"/>
-      <c r="AI26" s="245"/>
-      <c r="AJ26" s="245"/>
-      <c r="AK26" s="245"/>
-      <c r="AL26" s="245"/>
-      <c r="AM26" s="245"/>
-      <c r="AN26" s="245"/>
-      <c r="AO26" s="245"/>
-      <c r="AP26" s="245"/>
-      <c r="AQ26" s="245"/>
-      <c r="AR26" s="245"/>
-      <c r="AS26" s="245"/>
-      <c r="AT26" s="245"/>
-      <c r="AU26" s="245"/>
-      <c r="AV26" s="245"/>
-      <c r="AW26" s="245"/>
-      <c r="AX26" s="245"/>
-      <c r="AY26" s="245"/>
-      <c r="AZ26" s="246"/>
+      <c r="E26" s="256"/>
+      <c r="F26" s="256"/>
+      <c r="G26" s="256"/>
+      <c r="H26" s="256"/>
+      <c r="I26" s="256"/>
+      <c r="J26" s="256"/>
+      <c r="K26" s="256"/>
+      <c r="L26" s="256"/>
+      <c r="M26" s="256"/>
+      <c r="N26" s="256"/>
+      <c r="O26" s="256"/>
+      <c r="P26" s="256"/>
+      <c r="Q26" s="256"/>
+      <c r="R26" s="256"/>
+      <c r="S26" s="256"/>
+      <c r="T26" s="256"/>
+      <c r="U26" s="256"/>
+      <c r="V26" s="256"/>
+      <c r="W26" s="256"/>
+      <c r="X26" s="256"/>
+      <c r="Y26" s="256"/>
+      <c r="Z26" s="256"/>
+      <c r="AA26" s="256"/>
+      <c r="AB26" s="256"/>
+      <c r="AC26" s="256"/>
+      <c r="AD26" s="256"/>
+      <c r="AE26" s="256"/>
+      <c r="AF26" s="256"/>
+      <c r="AG26" s="256"/>
+      <c r="AH26" s="256"/>
+      <c r="AI26" s="256"/>
+      <c r="AJ26" s="256"/>
+      <c r="AK26" s="256"/>
+      <c r="AL26" s="256"/>
+      <c r="AM26" s="256"/>
+      <c r="AN26" s="256"/>
+      <c r="AO26" s="256"/>
+      <c r="AP26" s="256"/>
+      <c r="AQ26" s="256"/>
+      <c r="AR26" s="256"/>
+      <c r="AS26" s="256"/>
+      <c r="AT26" s="256"/>
+      <c r="AU26" s="256"/>
+      <c r="AV26" s="256"/>
+      <c r="AW26" s="256"/>
+      <c r="AX26" s="256"/>
+      <c r="AY26" s="256"/>
+      <c r="AZ26" s="257"/>
     </row>
     <row r="27" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="250"/>
-      <c r="B27" s="251"/>
-      <c r="C27" s="251"/>
+      <c r="A27" s="247"/>
+      <c r="B27" s="248"/>
+      <c r="C27" s="248"/>
       <c r="D27" s="10"/>
-      <c r="E27" s="245"/>
-      <c r="F27" s="245"/>
-      <c r="G27" s="245"/>
-      <c r="H27" s="245"/>
-      <c r="I27" s="245"/>
-      <c r="J27" s="245"/>
-      <c r="K27" s="245"/>
-      <c r="L27" s="245"/>
-      <c r="M27" s="245"/>
-      <c r="N27" s="245"/>
-      <c r="O27" s="245"/>
-      <c r="P27" s="245"/>
-      <c r="Q27" s="245"/>
-      <c r="R27" s="245"/>
-      <c r="S27" s="245"/>
-      <c r="T27" s="245"/>
-      <c r="U27" s="245"/>
-      <c r="V27" s="245"/>
-      <c r="W27" s="245"/>
-      <c r="X27" s="245"/>
-      <c r="Y27" s="245"/>
-      <c r="Z27" s="245"/>
-      <c r="AA27" s="245"/>
-      <c r="AB27" s="245"/>
-      <c r="AC27" s="245"/>
-      <c r="AD27" s="245"/>
-      <c r="AE27" s="245"/>
-      <c r="AF27" s="245"/>
-      <c r="AG27" s="245"/>
-      <c r="AH27" s="245"/>
-      <c r="AI27" s="245"/>
-      <c r="AJ27" s="245"/>
-      <c r="AK27" s="245"/>
-      <c r="AL27" s="245"/>
-      <c r="AM27" s="245"/>
-      <c r="AN27" s="245"/>
-      <c r="AO27" s="245"/>
-      <c r="AP27" s="245"/>
-      <c r="AQ27" s="245"/>
-      <c r="AR27" s="245"/>
-      <c r="AS27" s="245"/>
-      <c r="AT27" s="245"/>
-      <c r="AU27" s="245"/>
-      <c r="AV27" s="245"/>
-      <c r="AW27" s="245"/>
-      <c r="AX27" s="245"/>
-      <c r="AY27" s="245"/>
-      <c r="AZ27" s="246"/>
+      <c r="E27" s="256"/>
+      <c r="F27" s="256"/>
+      <c r="G27" s="256"/>
+      <c r="H27" s="256"/>
+      <c r="I27" s="256"/>
+      <c r="J27" s="256"/>
+      <c r="K27" s="256"/>
+      <c r="L27" s="256"/>
+      <c r="M27" s="256"/>
+      <c r="N27" s="256"/>
+      <c r="O27" s="256"/>
+      <c r="P27" s="256"/>
+      <c r="Q27" s="256"/>
+      <c r="R27" s="256"/>
+      <c r="S27" s="256"/>
+      <c r="T27" s="256"/>
+      <c r="U27" s="256"/>
+      <c r="V27" s="256"/>
+      <c r="W27" s="256"/>
+      <c r="X27" s="256"/>
+      <c r="Y27" s="256"/>
+      <c r="Z27" s="256"/>
+      <c r="AA27" s="256"/>
+      <c r="AB27" s="256"/>
+      <c r="AC27" s="256"/>
+      <c r="AD27" s="256"/>
+      <c r="AE27" s="256"/>
+      <c r="AF27" s="256"/>
+      <c r="AG27" s="256"/>
+      <c r="AH27" s="256"/>
+      <c r="AI27" s="256"/>
+      <c r="AJ27" s="256"/>
+      <c r="AK27" s="256"/>
+      <c r="AL27" s="256"/>
+      <c r="AM27" s="256"/>
+      <c r="AN27" s="256"/>
+      <c r="AO27" s="256"/>
+      <c r="AP27" s="256"/>
+      <c r="AQ27" s="256"/>
+      <c r="AR27" s="256"/>
+      <c r="AS27" s="256"/>
+      <c r="AT27" s="256"/>
+      <c r="AU27" s="256"/>
+      <c r="AV27" s="256"/>
+      <c r="AW27" s="256"/>
+      <c r="AX27" s="256"/>
+      <c r="AY27" s="256"/>
+      <c r="AZ27" s="257"/>
     </row>
     <row r="28" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="250"/>
-      <c r="B28" s="251"/>
-      <c r="C28" s="251"/>
+      <c r="A28" s="247"/>
+      <c r="B28" s="248"/>
+      <c r="C28" s="248"/>
       <c r="D28" s="10"/>
-      <c r="E28" s="245"/>
-      <c r="F28" s="245"/>
-      <c r="G28" s="245"/>
-      <c r="H28" s="245"/>
-      <c r="I28" s="245"/>
-      <c r="J28" s="245"/>
-      <c r="K28" s="245"/>
-      <c r="L28" s="245"/>
-      <c r="M28" s="245"/>
-      <c r="N28" s="245"/>
-      <c r="O28" s="245"/>
-      <c r="P28" s="245"/>
-      <c r="Q28" s="245"/>
-      <c r="R28" s="245"/>
-      <c r="S28" s="245"/>
-      <c r="T28" s="245"/>
-      <c r="U28" s="245"/>
-      <c r="V28" s="245"/>
-      <c r="W28" s="245"/>
-      <c r="X28" s="245"/>
-      <c r="Y28" s="245"/>
-      <c r="Z28" s="245"/>
-      <c r="AA28" s="245"/>
-      <c r="AB28" s="245"/>
-      <c r="AC28" s="245"/>
-      <c r="AD28" s="245"/>
-      <c r="AE28" s="245"/>
-      <c r="AF28" s="245"/>
-      <c r="AG28" s="245"/>
-      <c r="AH28" s="245"/>
-      <c r="AI28" s="245"/>
-      <c r="AJ28" s="245"/>
-      <c r="AK28" s="245"/>
-      <c r="AL28" s="245"/>
-      <c r="AM28" s="245"/>
-      <c r="AN28" s="245"/>
-      <c r="AO28" s="245"/>
-      <c r="AP28" s="245"/>
-      <c r="AQ28" s="245"/>
-      <c r="AR28" s="245"/>
-      <c r="AS28" s="245"/>
-      <c r="AT28" s="245"/>
-      <c r="AU28" s="245"/>
-      <c r="AV28" s="245"/>
-      <c r="AW28" s="245"/>
-      <c r="AX28" s="245"/>
-      <c r="AY28" s="245"/>
-      <c r="AZ28" s="246"/>
+      <c r="E28" s="256"/>
+      <c r="F28" s="256"/>
+      <c r="G28" s="256"/>
+      <c r="H28" s="256"/>
+      <c r="I28" s="256"/>
+      <c r="J28" s="256"/>
+      <c r="K28" s="256"/>
+      <c r="L28" s="256"/>
+      <c r="M28" s="256"/>
+      <c r="N28" s="256"/>
+      <c r="O28" s="256"/>
+      <c r="P28" s="256"/>
+      <c r="Q28" s="256"/>
+      <c r="R28" s="256"/>
+      <c r="S28" s="256"/>
+      <c r="T28" s="256"/>
+      <c r="U28" s="256"/>
+      <c r="V28" s="256"/>
+      <c r="W28" s="256"/>
+      <c r="X28" s="256"/>
+      <c r="Y28" s="256"/>
+      <c r="Z28" s="256"/>
+      <c r="AA28" s="256"/>
+      <c r="AB28" s="256"/>
+      <c r="AC28" s="256"/>
+      <c r="AD28" s="256"/>
+      <c r="AE28" s="256"/>
+      <c r="AF28" s="256"/>
+      <c r="AG28" s="256"/>
+      <c r="AH28" s="256"/>
+      <c r="AI28" s="256"/>
+      <c r="AJ28" s="256"/>
+      <c r="AK28" s="256"/>
+      <c r="AL28" s="256"/>
+      <c r="AM28" s="256"/>
+      <c r="AN28" s="256"/>
+      <c r="AO28" s="256"/>
+      <c r="AP28" s="256"/>
+      <c r="AQ28" s="256"/>
+      <c r="AR28" s="256"/>
+      <c r="AS28" s="256"/>
+      <c r="AT28" s="256"/>
+      <c r="AU28" s="256"/>
+      <c r="AV28" s="256"/>
+      <c r="AW28" s="256"/>
+      <c r="AX28" s="256"/>
+      <c r="AY28" s="256"/>
+      <c r="AZ28" s="257"/>
     </row>
     <row r="29" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="250"/>
-      <c r="B29" s="251"/>
-      <c r="C29" s="251"/>
+      <c r="A29" s="247"/>
+      <c r="B29" s="248"/>
+      <c r="C29" s="248"/>
       <c r="D29" s="10"/>
-      <c r="E29" s="245"/>
-      <c r="F29" s="245"/>
-      <c r="G29" s="245"/>
-      <c r="H29" s="245"/>
-      <c r="I29" s="245"/>
-      <c r="J29" s="245"/>
-      <c r="K29" s="245"/>
-      <c r="L29" s="245"/>
-      <c r="M29" s="245"/>
-      <c r="N29" s="245"/>
-      <c r="O29" s="245"/>
-      <c r="P29" s="245"/>
-      <c r="Q29" s="245"/>
-      <c r="R29" s="245"/>
-      <c r="S29" s="245"/>
-      <c r="T29" s="245"/>
-      <c r="U29" s="245"/>
-      <c r="V29" s="245"/>
-      <c r="W29" s="245"/>
-      <c r="X29" s="245"/>
-      <c r="Y29" s="245"/>
-      <c r="Z29" s="245"/>
-      <c r="AA29" s="245"/>
-      <c r="AB29" s="245"/>
-      <c r="AC29" s="245"/>
-      <c r="AD29" s="245"/>
-      <c r="AE29" s="245"/>
-      <c r="AF29" s="245"/>
-      <c r="AG29" s="245"/>
-      <c r="AH29" s="245"/>
-      <c r="AI29" s="245"/>
-      <c r="AJ29" s="245"/>
-      <c r="AK29" s="245"/>
-      <c r="AL29" s="245"/>
-      <c r="AM29" s="245"/>
-      <c r="AN29" s="245"/>
-      <c r="AO29" s="245"/>
-      <c r="AP29" s="245"/>
-      <c r="AQ29" s="245"/>
-      <c r="AR29" s="245"/>
-      <c r="AS29" s="245"/>
-      <c r="AT29" s="245"/>
-      <c r="AU29" s="245"/>
-      <c r="AV29" s="245"/>
-      <c r="AW29" s="245"/>
-      <c r="AX29" s="245"/>
-      <c r="AY29" s="245"/>
-      <c r="AZ29" s="246"/>
+      <c r="E29" s="256"/>
+      <c r="F29" s="256"/>
+      <c r="G29" s="256"/>
+      <c r="H29" s="256"/>
+      <c r="I29" s="256"/>
+      <c r="J29" s="256"/>
+      <c r="K29" s="256"/>
+      <c r="L29" s="256"/>
+      <c r="M29" s="256"/>
+      <c r="N29" s="256"/>
+      <c r="O29" s="256"/>
+      <c r="P29" s="256"/>
+      <c r="Q29" s="256"/>
+      <c r="R29" s="256"/>
+      <c r="S29" s="256"/>
+      <c r="T29" s="256"/>
+      <c r="U29" s="256"/>
+      <c r="V29" s="256"/>
+      <c r="W29" s="256"/>
+      <c r="X29" s="256"/>
+      <c r="Y29" s="256"/>
+      <c r="Z29" s="256"/>
+      <c r="AA29" s="256"/>
+      <c r="AB29" s="256"/>
+      <c r="AC29" s="256"/>
+      <c r="AD29" s="256"/>
+      <c r="AE29" s="256"/>
+      <c r="AF29" s="256"/>
+      <c r="AG29" s="256"/>
+      <c r="AH29" s="256"/>
+      <c r="AI29" s="256"/>
+      <c r="AJ29" s="256"/>
+      <c r="AK29" s="256"/>
+      <c r="AL29" s="256"/>
+      <c r="AM29" s="256"/>
+      <c r="AN29" s="256"/>
+      <c r="AO29" s="256"/>
+      <c r="AP29" s="256"/>
+      <c r="AQ29" s="256"/>
+      <c r="AR29" s="256"/>
+      <c r="AS29" s="256"/>
+      <c r="AT29" s="256"/>
+      <c r="AU29" s="256"/>
+      <c r="AV29" s="256"/>
+      <c r="AW29" s="256"/>
+      <c r="AX29" s="256"/>
+      <c r="AY29" s="256"/>
+      <c r="AZ29" s="257"/>
     </row>
     <row r="30" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="250"/>
-      <c r="B30" s="251"/>
-      <c r="C30" s="251"/>
+      <c r="A30" s="247"/>
+      <c r="B30" s="248"/>
+      <c r="C30" s="248"/>
       <c r="D30" s="10"/>
-      <c r="E30" s="245"/>
-      <c r="F30" s="245"/>
-      <c r="G30" s="245"/>
-      <c r="H30" s="245"/>
-      <c r="I30" s="245"/>
-      <c r="J30" s="245"/>
-      <c r="K30" s="245"/>
-      <c r="L30" s="245"/>
-      <c r="M30" s="245"/>
-      <c r="N30" s="245"/>
-      <c r="O30" s="245"/>
-      <c r="P30" s="245"/>
-      <c r="Q30" s="245"/>
-      <c r="R30" s="245"/>
-      <c r="S30" s="245"/>
-      <c r="T30" s="245"/>
-      <c r="U30" s="245"/>
-      <c r="V30" s="245"/>
-      <c r="W30" s="245"/>
-      <c r="X30" s="245"/>
-      <c r="Y30" s="245"/>
-      <c r="Z30" s="245"/>
-      <c r="AA30" s="245"/>
-      <c r="AB30" s="245"/>
-      <c r="AC30" s="245"/>
-      <c r="AD30" s="245"/>
-      <c r="AE30" s="245"/>
-      <c r="AF30" s="245"/>
-      <c r="AG30" s="245"/>
-      <c r="AH30" s="245"/>
-      <c r="AI30" s="245"/>
-      <c r="AJ30" s="245"/>
-      <c r="AK30" s="245"/>
-      <c r="AL30" s="245"/>
-      <c r="AM30" s="245"/>
-      <c r="AN30" s="245"/>
-      <c r="AO30" s="245"/>
-      <c r="AP30" s="245"/>
-      <c r="AQ30" s="245"/>
-      <c r="AR30" s="245"/>
-      <c r="AS30" s="245"/>
-      <c r="AT30" s="245"/>
-      <c r="AU30" s="245"/>
-      <c r="AV30" s="245"/>
-      <c r="AW30" s="245"/>
-      <c r="AX30" s="245"/>
-      <c r="AY30" s="245"/>
-      <c r="AZ30" s="246"/>
+      <c r="E30" s="256"/>
+      <c r="F30" s="256"/>
+      <c r="G30" s="256"/>
+      <c r="H30" s="256"/>
+      <c r="I30" s="256"/>
+      <c r="J30" s="256"/>
+      <c r="K30" s="256"/>
+      <c r="L30" s="256"/>
+      <c r="M30" s="256"/>
+      <c r="N30" s="256"/>
+      <c r="O30" s="256"/>
+      <c r="P30" s="256"/>
+      <c r="Q30" s="256"/>
+      <c r="R30" s="256"/>
+      <c r="S30" s="256"/>
+      <c r="T30" s="256"/>
+      <c r="U30" s="256"/>
+      <c r="V30" s="256"/>
+      <c r="W30" s="256"/>
+      <c r="X30" s="256"/>
+      <c r="Y30" s="256"/>
+      <c r="Z30" s="256"/>
+      <c r="AA30" s="256"/>
+      <c r="AB30" s="256"/>
+      <c r="AC30" s="256"/>
+      <c r="AD30" s="256"/>
+      <c r="AE30" s="256"/>
+      <c r="AF30" s="256"/>
+      <c r="AG30" s="256"/>
+      <c r="AH30" s="256"/>
+      <c r="AI30" s="256"/>
+      <c r="AJ30" s="256"/>
+      <c r="AK30" s="256"/>
+      <c r="AL30" s="256"/>
+      <c r="AM30" s="256"/>
+      <c r="AN30" s="256"/>
+      <c r="AO30" s="256"/>
+      <c r="AP30" s="256"/>
+      <c r="AQ30" s="256"/>
+      <c r="AR30" s="256"/>
+      <c r="AS30" s="256"/>
+      <c r="AT30" s="256"/>
+      <c r="AU30" s="256"/>
+      <c r="AV30" s="256"/>
+      <c r="AW30" s="256"/>
+      <c r="AX30" s="256"/>
+      <c r="AY30" s="256"/>
+      <c r="AZ30" s="257"/>
     </row>
     <row r="31" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="250"/>
-      <c r="B31" s="251"/>
-      <c r="C31" s="251"/>
+      <c r="A31" s="247"/>
+      <c r="B31" s="248"/>
+      <c r="C31" s="248"/>
       <c r="D31" s="10"/>
-      <c r="E31" s="245"/>
-      <c r="F31" s="245"/>
-      <c r="G31" s="245"/>
-      <c r="H31" s="245"/>
-      <c r="I31" s="245"/>
-      <c r="J31" s="245"/>
-      <c r="K31" s="245"/>
-      <c r="L31" s="245"/>
-      <c r="M31" s="245"/>
-      <c r="N31" s="245"/>
-      <c r="O31" s="245"/>
-      <c r="P31" s="245"/>
-      <c r="Q31" s="245"/>
-      <c r="R31" s="245"/>
-      <c r="S31" s="245"/>
-      <c r="T31" s="245"/>
-      <c r="U31" s="245"/>
-      <c r="V31" s="245"/>
-      <c r="W31" s="245"/>
-      <c r="X31" s="245"/>
-      <c r="Y31" s="245"/>
-      <c r="Z31" s="245"/>
-      <c r="AA31" s="245"/>
-      <c r="AB31" s="245"/>
-      <c r="AC31" s="245"/>
-      <c r="AD31" s="245"/>
-      <c r="AE31" s="245"/>
-      <c r="AF31" s="245"/>
-      <c r="AG31" s="245"/>
-      <c r="AH31" s="245"/>
-      <c r="AI31" s="245"/>
-      <c r="AJ31" s="245"/>
-      <c r="AK31" s="245"/>
-      <c r="AL31" s="245"/>
-      <c r="AM31" s="245"/>
-      <c r="AN31" s="245"/>
-      <c r="AO31" s="245"/>
-      <c r="AP31" s="245"/>
-      <c r="AQ31" s="245"/>
-      <c r="AR31" s="245"/>
-      <c r="AS31" s="245"/>
-      <c r="AT31" s="245"/>
-      <c r="AU31" s="245"/>
-      <c r="AV31" s="245"/>
-      <c r="AW31" s="245"/>
-      <c r="AX31" s="245"/>
-      <c r="AY31" s="245"/>
-      <c r="AZ31" s="246"/>
+      <c r="E31" s="256"/>
+      <c r="F31" s="256"/>
+      <c r="G31" s="256"/>
+      <c r="H31" s="256"/>
+      <c r="I31" s="256"/>
+      <c r="J31" s="256"/>
+      <c r="K31" s="256"/>
+      <c r="L31" s="256"/>
+      <c r="M31" s="256"/>
+      <c r="N31" s="256"/>
+      <c r="O31" s="256"/>
+      <c r="P31" s="256"/>
+      <c r="Q31" s="256"/>
+      <c r="R31" s="256"/>
+      <c r="S31" s="256"/>
+      <c r="T31" s="256"/>
+      <c r="U31" s="256"/>
+      <c r="V31" s="256"/>
+      <c r="W31" s="256"/>
+      <c r="X31" s="256"/>
+      <c r="Y31" s="256"/>
+      <c r="Z31" s="256"/>
+      <c r="AA31" s="256"/>
+      <c r="AB31" s="256"/>
+      <c r="AC31" s="256"/>
+      <c r="AD31" s="256"/>
+      <c r="AE31" s="256"/>
+      <c r="AF31" s="256"/>
+      <c r="AG31" s="256"/>
+      <c r="AH31" s="256"/>
+      <c r="AI31" s="256"/>
+      <c r="AJ31" s="256"/>
+      <c r="AK31" s="256"/>
+      <c r="AL31" s="256"/>
+      <c r="AM31" s="256"/>
+      <c r="AN31" s="256"/>
+      <c r="AO31" s="256"/>
+      <c r="AP31" s="256"/>
+      <c r="AQ31" s="256"/>
+      <c r="AR31" s="256"/>
+      <c r="AS31" s="256"/>
+      <c r="AT31" s="256"/>
+      <c r="AU31" s="256"/>
+      <c r="AV31" s="256"/>
+      <c r="AW31" s="256"/>
+      <c r="AX31" s="256"/>
+      <c r="AY31" s="256"/>
+      <c r="AZ31" s="257"/>
     </row>
     <row r="32" spans="1:52" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="250"/>
-      <c r="B32" s="251"/>
-      <c r="C32" s="251"/>
+      <c r="A32" s="247"/>
+      <c r="B32" s="248"/>
+      <c r="C32" s="248"/>
       <c r="D32" s="10"/>
-      <c r="E32" s="245"/>
-      <c r="F32" s="245"/>
-      <c r="G32" s="245"/>
-      <c r="H32" s="245"/>
-      <c r="I32" s="245"/>
-      <c r="J32" s="245"/>
-      <c r="K32" s="245"/>
-      <c r="L32" s="245"/>
-      <c r="M32" s="245"/>
-      <c r="N32" s="245"/>
-      <c r="O32" s="245"/>
-      <c r="P32" s="245"/>
-      <c r="Q32" s="245"/>
-      <c r="R32" s="245"/>
-      <c r="S32" s="245"/>
-      <c r="T32" s="245"/>
-      <c r="U32" s="245"/>
-      <c r="V32" s="245"/>
-      <c r="W32" s="245"/>
-      <c r="X32" s="245"/>
-      <c r="Y32" s="245"/>
-      <c r="Z32" s="245"/>
-      <c r="AA32" s="245"/>
-      <c r="AB32" s="245"/>
-      <c r="AC32" s="245"/>
-      <c r="AD32" s="245"/>
-      <c r="AE32" s="245"/>
-      <c r="AF32" s="245"/>
-      <c r="AG32" s="245"/>
-      <c r="AH32" s="245"/>
-      <c r="AI32" s="245"/>
-      <c r="AJ32" s="245"/>
-      <c r="AK32" s="245"/>
-      <c r="AL32" s="245"/>
-      <c r="AM32" s="245"/>
-      <c r="AN32" s="245"/>
-      <c r="AO32" s="245"/>
-      <c r="AP32" s="245"/>
-      <c r="AQ32" s="245"/>
-      <c r="AR32" s="245"/>
-      <c r="AS32" s="245"/>
-      <c r="AT32" s="245"/>
-      <c r="AU32" s="245"/>
-      <c r="AV32" s="245"/>
-      <c r="AW32" s="245"/>
-      <c r="AX32" s="245"/>
-      <c r="AY32" s="245"/>
-      <c r="AZ32" s="246"/>
+      <c r="E32" s="256"/>
+      <c r="F32" s="256"/>
+      <c r="G32" s="256"/>
+      <c r="H32" s="256"/>
+      <c r="I32" s="256"/>
+      <c r="J32" s="256"/>
+      <c r="K32" s="256"/>
+      <c r="L32" s="256"/>
+      <c r="M32" s="256"/>
+      <c r="N32" s="256"/>
+      <c r="O32" s="256"/>
+      <c r="P32" s="256"/>
+      <c r="Q32" s="256"/>
+      <c r="R32" s="256"/>
+      <c r="S32" s="256"/>
+      <c r="T32" s="256"/>
+      <c r="U32" s="256"/>
+      <c r="V32" s="256"/>
+      <c r="W32" s="256"/>
+      <c r="X32" s="256"/>
+      <c r="Y32" s="256"/>
+      <c r="Z32" s="256"/>
+      <c r="AA32" s="256"/>
+      <c r="AB32" s="256"/>
+      <c r="AC32" s="256"/>
+      <c r="AD32" s="256"/>
+      <c r="AE32" s="256"/>
+      <c r="AF32" s="256"/>
+      <c r="AG32" s="256"/>
+      <c r="AH32" s="256"/>
+      <c r="AI32" s="256"/>
+      <c r="AJ32" s="256"/>
+      <c r="AK32" s="256"/>
+      <c r="AL32" s="256"/>
+      <c r="AM32" s="256"/>
+      <c r="AN32" s="256"/>
+      <c r="AO32" s="256"/>
+      <c r="AP32" s="256"/>
+      <c r="AQ32" s="256"/>
+      <c r="AR32" s="256"/>
+      <c r="AS32" s="256"/>
+      <c r="AT32" s="256"/>
+      <c r="AU32" s="256"/>
+      <c r="AV32" s="256"/>
+      <c r="AW32" s="256"/>
+      <c r="AX32" s="256"/>
+      <c r="AY32" s="256"/>
+      <c r="AZ32" s="257"/>
     </row>
     <row r="33" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="250"/>
-      <c r="B33" s="251"/>
-      <c r="C33" s="251"/>
+      <c r="A33" s="247"/>
+      <c r="B33" s="248"/>
+      <c r="C33" s="248"/>
       <c r="D33" s="10"/>
-      <c r="E33" s="245"/>
-      <c r="F33" s="245"/>
-      <c r="G33" s="245"/>
-      <c r="H33" s="245"/>
-      <c r="I33" s="245"/>
-      <c r="J33" s="245"/>
-      <c r="K33" s="245"/>
-      <c r="L33" s="245"/>
-      <c r="M33" s="245"/>
-      <c r="N33" s="245"/>
-      <c r="O33" s="245"/>
-      <c r="P33" s="245"/>
-      <c r="Q33" s="245"/>
-      <c r="R33" s="245"/>
-      <c r="S33" s="245"/>
-      <c r="T33" s="245"/>
-      <c r="U33" s="245"/>
-      <c r="V33" s="245"/>
-      <c r="W33" s="245"/>
-      <c r="X33" s="245"/>
-      <c r="Y33" s="245"/>
-      <c r="Z33" s="245"/>
-      <c r="AA33" s="245"/>
-      <c r="AB33" s="245"/>
-      <c r="AC33" s="245"/>
-      <c r="AD33" s="245"/>
-      <c r="AE33" s="245"/>
-      <c r="AF33" s="245"/>
-      <c r="AG33" s="245"/>
-      <c r="AH33" s="245"/>
-      <c r="AI33" s="245"/>
-      <c r="AJ33" s="245"/>
-      <c r="AK33" s="245"/>
-      <c r="AL33" s="245"/>
-      <c r="AM33" s="245"/>
-      <c r="AN33" s="245"/>
-      <c r="AO33" s="245"/>
-      <c r="AP33" s="245"/>
-      <c r="AQ33" s="245"/>
-      <c r="AR33" s="245"/>
-      <c r="AS33" s="245"/>
-      <c r="AT33" s="245"/>
-      <c r="AU33" s="245"/>
-      <c r="AV33" s="245"/>
-      <c r="AW33" s="245"/>
-      <c r="AX33" s="245"/>
-      <c r="AY33" s="245"/>
-      <c r="AZ33" s="246"/>
+      <c r="E33" s="256"/>
+      <c r="F33" s="256"/>
+      <c r="G33" s="256"/>
+      <c r="H33" s="256"/>
+      <c r="I33" s="256"/>
+      <c r="J33" s="256"/>
+      <c r="K33" s="256"/>
+      <c r="L33" s="256"/>
+      <c r="M33" s="256"/>
+      <c r="N33" s="256"/>
+      <c r="O33" s="256"/>
+      <c r="P33" s="256"/>
+      <c r="Q33" s="256"/>
+      <c r="R33" s="256"/>
+      <c r="S33" s="256"/>
+      <c r="T33" s="256"/>
+      <c r="U33" s="256"/>
+      <c r="V33" s="256"/>
+      <c r="W33" s="256"/>
+      <c r="X33" s="256"/>
+      <c r="Y33" s="256"/>
+      <c r="Z33" s="256"/>
+      <c r="AA33" s="256"/>
+      <c r="AB33" s="256"/>
+      <c r="AC33" s="256"/>
+      <c r="AD33" s="256"/>
+      <c r="AE33" s="256"/>
+      <c r="AF33" s="256"/>
+      <c r="AG33" s="256"/>
+      <c r="AH33" s="256"/>
+      <c r="AI33" s="256"/>
+      <c r="AJ33" s="256"/>
+      <c r="AK33" s="256"/>
+      <c r="AL33" s="256"/>
+      <c r="AM33" s="256"/>
+      <c r="AN33" s="256"/>
+      <c r="AO33" s="256"/>
+      <c r="AP33" s="256"/>
+      <c r="AQ33" s="256"/>
+      <c r="AR33" s="256"/>
+      <c r="AS33" s="256"/>
+      <c r="AT33" s="256"/>
+      <c r="AU33" s="256"/>
+      <c r="AV33" s="256"/>
+      <c r="AW33" s="256"/>
+      <c r="AX33" s="256"/>
+      <c r="AY33" s="256"/>
+      <c r="AZ33" s="257"/>
     </row>
     <row r="34" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="250"/>
-      <c r="B34" s="251"/>
-      <c r="C34" s="251"/>
+      <c r="A34" s="247"/>
+      <c r="B34" s="248"/>
+      <c r="C34" s="248"/>
       <c r="D34" s="10"/>
-      <c r="E34" s="245"/>
-      <c r="F34" s="245"/>
-      <c r="G34" s="245"/>
-      <c r="H34" s="245"/>
-      <c r="I34" s="245"/>
-      <c r="J34" s="245"/>
-      <c r="K34" s="245"/>
-      <c r="L34" s="245"/>
-      <c r="M34" s="245"/>
-      <c r="N34" s="245"/>
-      <c r="O34" s="245"/>
-      <c r="P34" s="245"/>
-      <c r="Q34" s="245"/>
-      <c r="R34" s="245"/>
-      <c r="S34" s="245"/>
-      <c r="T34" s="245"/>
-      <c r="U34" s="245"/>
-      <c r="V34" s="245"/>
-      <c r="W34" s="245"/>
-      <c r="X34" s="245"/>
-      <c r="Y34" s="245"/>
-      <c r="Z34" s="245"/>
-      <c r="AA34" s="245"/>
-      <c r="AB34" s="245"/>
-      <c r="AC34" s="245"/>
-      <c r="AD34" s="245"/>
-      <c r="AE34" s="245"/>
-      <c r="AF34" s="245"/>
-      <c r="AG34" s="245"/>
-      <c r="AH34" s="245"/>
-      <c r="AI34" s="245"/>
-      <c r="AJ34" s="245"/>
-      <c r="AK34" s="245"/>
-      <c r="AL34" s="245"/>
-      <c r="AM34" s="245"/>
-      <c r="AN34" s="245"/>
-      <c r="AO34" s="245"/>
-      <c r="AP34" s="245"/>
-      <c r="AQ34" s="245"/>
-      <c r="AR34" s="245"/>
-      <c r="AS34" s="245"/>
-      <c r="AT34" s="245"/>
-      <c r="AU34" s="245"/>
-      <c r="AV34" s="245"/>
-      <c r="AW34" s="245"/>
-      <c r="AX34" s="245"/>
-      <c r="AY34" s="245"/>
-      <c r="AZ34" s="246"/>
+      <c r="E34" s="256"/>
+      <c r="F34" s="256"/>
+      <c r="G34" s="256"/>
+      <c r="H34" s="256"/>
+      <c r="I34" s="256"/>
+      <c r="J34" s="256"/>
+      <c r="K34" s="256"/>
+      <c r="L34" s="256"/>
+      <c r="M34" s="256"/>
+      <c r="N34" s="256"/>
+      <c r="O34" s="256"/>
+      <c r="P34" s="256"/>
+      <c r="Q34" s="256"/>
+      <c r="R34" s="256"/>
+      <c r="S34" s="256"/>
+      <c r="T34" s="256"/>
+      <c r="U34" s="256"/>
+      <c r="V34" s="256"/>
+      <c r="W34" s="256"/>
+      <c r="X34" s="256"/>
+      <c r="Y34" s="256"/>
+      <c r="Z34" s="256"/>
+      <c r="AA34" s="256"/>
+      <c r="AB34" s="256"/>
+      <c r="AC34" s="256"/>
+      <c r="AD34" s="256"/>
+      <c r="AE34" s="256"/>
+      <c r="AF34" s="256"/>
+      <c r="AG34" s="256"/>
+      <c r="AH34" s="256"/>
+      <c r="AI34" s="256"/>
+      <c r="AJ34" s="256"/>
+      <c r="AK34" s="256"/>
+      <c r="AL34" s="256"/>
+      <c r="AM34" s="256"/>
+      <c r="AN34" s="256"/>
+      <c r="AO34" s="256"/>
+      <c r="AP34" s="256"/>
+      <c r="AQ34" s="256"/>
+      <c r="AR34" s="256"/>
+      <c r="AS34" s="256"/>
+      <c r="AT34" s="256"/>
+      <c r="AU34" s="256"/>
+      <c r="AV34" s="256"/>
+      <c r="AW34" s="256"/>
+      <c r="AX34" s="256"/>
+      <c r="AY34" s="256"/>
+      <c r="AZ34" s="257"/>
     </row>
     <row r="35" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="250"/>
-      <c r="B35" s="251"/>
-      <c r="C35" s="251"/>
+      <c r="A35" s="247"/>
+      <c r="B35" s="248"/>
+      <c r="C35" s="248"/>
       <c r="D35" s="10"/>
-      <c r="E35" s="245"/>
-      <c r="F35" s="245"/>
-      <c r="G35" s="245"/>
-      <c r="H35" s="245"/>
-      <c r="I35" s="245"/>
-      <c r="J35" s="245"/>
-      <c r="K35" s="245"/>
-      <c r="L35" s="245"/>
-      <c r="M35" s="245"/>
-      <c r="N35" s="245"/>
-      <c r="O35" s="245"/>
-      <c r="P35" s="245"/>
-      <c r="Q35" s="245"/>
-      <c r="R35" s="245"/>
-      <c r="S35" s="245"/>
-      <c r="T35" s="245"/>
-      <c r="U35" s="245"/>
-      <c r="V35" s="245"/>
-      <c r="W35" s="245"/>
-      <c r="X35" s="245"/>
-      <c r="Y35" s="245"/>
-      <c r="Z35" s="245"/>
-      <c r="AA35" s="245"/>
-      <c r="AB35" s="245"/>
-      <c r="AC35" s="245"/>
-      <c r="AD35" s="245"/>
-      <c r="AE35" s="245"/>
-      <c r="AF35" s="245"/>
-      <c r="AG35" s="245"/>
-      <c r="AH35" s="245"/>
-      <c r="AI35" s="245"/>
-      <c r="AJ35" s="245"/>
-      <c r="AK35" s="245"/>
-      <c r="AL35" s="245"/>
-      <c r="AM35" s="245"/>
-      <c r="AN35" s="245"/>
-      <c r="AO35" s="245"/>
-      <c r="AP35" s="245"/>
-      <c r="AQ35" s="245"/>
-      <c r="AR35" s="245"/>
-      <c r="AS35" s="245"/>
-      <c r="AT35" s="245"/>
-      <c r="AU35" s="245"/>
-      <c r="AV35" s="245"/>
-      <c r="AW35" s="245"/>
-      <c r="AX35" s="245"/>
-      <c r="AY35" s="245"/>
-      <c r="AZ35" s="246"/>
+      <c r="E35" s="256"/>
+      <c r="F35" s="256"/>
+      <c r="G35" s="256"/>
+      <c r="H35" s="256"/>
+      <c r="I35" s="256"/>
+      <c r="J35" s="256"/>
+      <c r="K35" s="256"/>
+      <c r="L35" s="256"/>
+      <c r="M35" s="256"/>
+      <c r="N35" s="256"/>
+      <c r="O35" s="256"/>
+      <c r="P35" s="256"/>
+      <c r="Q35" s="256"/>
+      <c r="R35" s="256"/>
+      <c r="S35" s="256"/>
+      <c r="T35" s="256"/>
+      <c r="U35" s="256"/>
+      <c r="V35" s="256"/>
+      <c r="W35" s="256"/>
+      <c r="X35" s="256"/>
+      <c r="Y35" s="256"/>
+      <c r="Z35" s="256"/>
+      <c r="AA35" s="256"/>
+      <c r="AB35" s="256"/>
+      <c r="AC35" s="256"/>
+      <c r="AD35" s="256"/>
+      <c r="AE35" s="256"/>
+      <c r="AF35" s="256"/>
+      <c r="AG35" s="256"/>
+      <c r="AH35" s="256"/>
+      <c r="AI35" s="256"/>
+      <c r="AJ35" s="256"/>
+      <c r="AK35" s="256"/>
+      <c r="AL35" s="256"/>
+      <c r="AM35" s="256"/>
+      <c r="AN35" s="256"/>
+      <c r="AO35" s="256"/>
+      <c r="AP35" s="256"/>
+      <c r="AQ35" s="256"/>
+      <c r="AR35" s="256"/>
+      <c r="AS35" s="256"/>
+      <c r="AT35" s="256"/>
+      <c r="AU35" s="256"/>
+      <c r="AV35" s="256"/>
+      <c r="AW35" s="256"/>
+      <c r="AX35" s="256"/>
+      <c r="AY35" s="256"/>
+      <c r="AZ35" s="257"/>
     </row>
     <row r="36" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="250"/>
-      <c r="B36" s="251"/>
-      <c r="C36" s="251"/>
+      <c r="A36" s="247"/>
+      <c r="B36" s="248"/>
+      <c r="C36" s="248"/>
       <c r="D36" s="10"/>
-      <c r="E36" s="245"/>
-      <c r="F36" s="245"/>
-      <c r="G36" s="245"/>
-      <c r="H36" s="245"/>
-      <c r="I36" s="245"/>
-      <c r="J36" s="245"/>
-      <c r="K36" s="245"/>
-      <c r="L36" s="245"/>
-      <c r="M36" s="245"/>
-      <c r="N36" s="245"/>
-      <c r="O36" s="245"/>
-      <c r="P36" s="245"/>
-      <c r="Q36" s="245"/>
-      <c r="R36" s="245"/>
-      <c r="S36" s="245"/>
-      <c r="T36" s="245"/>
-      <c r="U36" s="245"/>
-      <c r="V36" s="245"/>
-      <c r="W36" s="245"/>
-      <c r="X36" s="245"/>
-      <c r="Y36" s="245"/>
-      <c r="Z36" s="245"/>
-      <c r="AA36" s="245"/>
-      <c r="AB36" s="245"/>
-      <c r="AC36" s="245"/>
-      <c r="AD36" s="245"/>
-      <c r="AE36" s="245"/>
-      <c r="AF36" s="245"/>
-      <c r="AG36" s="245"/>
-      <c r="AH36" s="245"/>
-      <c r="AI36" s="245"/>
-      <c r="AJ36" s="245"/>
-      <c r="AK36" s="245"/>
-      <c r="AL36" s="245"/>
-      <c r="AM36" s="245"/>
-      <c r="AN36" s="245"/>
-      <c r="AO36" s="245"/>
-      <c r="AP36" s="245"/>
-      <c r="AQ36" s="245"/>
-      <c r="AR36" s="245"/>
-      <c r="AS36" s="245"/>
-      <c r="AT36" s="245"/>
-      <c r="AU36" s="245"/>
-      <c r="AV36" s="245"/>
-      <c r="AW36" s="245"/>
-      <c r="AX36" s="245"/>
-      <c r="AY36" s="245"/>
-      <c r="AZ36" s="246"/>
+      <c r="E36" s="256"/>
+      <c r="F36" s="256"/>
+      <c r="G36" s="256"/>
+      <c r="H36" s="256"/>
+      <c r="I36" s="256"/>
+      <c r="J36" s="256"/>
+      <c r="K36" s="256"/>
+      <c r="L36" s="256"/>
+      <c r="M36" s="256"/>
+      <c r="N36" s="256"/>
+      <c r="O36" s="256"/>
+      <c r="P36" s="256"/>
+      <c r="Q36" s="256"/>
+      <c r="R36" s="256"/>
+      <c r="S36" s="256"/>
+      <c r="T36" s="256"/>
+      <c r="U36" s="256"/>
+      <c r="V36" s="256"/>
+      <c r="W36" s="256"/>
+      <c r="X36" s="256"/>
+      <c r="Y36" s="256"/>
+      <c r="Z36" s="256"/>
+      <c r="AA36" s="256"/>
+      <c r="AB36" s="256"/>
+      <c r="AC36" s="256"/>
+      <c r="AD36" s="256"/>
+      <c r="AE36" s="256"/>
+      <c r="AF36" s="256"/>
+      <c r="AG36" s="256"/>
+      <c r="AH36" s="256"/>
+      <c r="AI36" s="256"/>
+      <c r="AJ36" s="256"/>
+      <c r="AK36" s="256"/>
+      <c r="AL36" s="256"/>
+      <c r="AM36" s="256"/>
+      <c r="AN36" s="256"/>
+      <c r="AO36" s="256"/>
+      <c r="AP36" s="256"/>
+      <c r="AQ36" s="256"/>
+      <c r="AR36" s="256"/>
+      <c r="AS36" s="256"/>
+      <c r="AT36" s="256"/>
+      <c r="AU36" s="256"/>
+      <c r="AV36" s="256"/>
+      <c r="AW36" s="256"/>
+      <c r="AX36" s="256"/>
+      <c r="AY36" s="256"/>
+      <c r="AZ36" s="257"/>
     </row>
     <row r="37" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="250"/>
-      <c r="B37" s="251"/>
-      <c r="C37" s="251"/>
+      <c r="A37" s="247"/>
+      <c r="B37" s="248"/>
+      <c r="C37" s="248"/>
       <c r="D37" s="10"/>
-      <c r="E37" s="245"/>
-      <c r="F37" s="245"/>
-      <c r="G37" s="245"/>
-      <c r="H37" s="245"/>
-      <c r="I37" s="245"/>
-      <c r="J37" s="245"/>
-      <c r="K37" s="245"/>
-      <c r="L37" s="245"/>
-      <c r="M37" s="245"/>
-      <c r="N37" s="245"/>
-      <c r="O37" s="245"/>
-      <c r="P37" s="245"/>
-      <c r="Q37" s="245"/>
-      <c r="R37" s="245"/>
-      <c r="S37" s="245"/>
-      <c r="T37" s="245"/>
-      <c r="U37" s="245"/>
-      <c r="V37" s="245"/>
-      <c r="W37" s="245"/>
-      <c r="X37" s="245"/>
-      <c r="Y37" s="245"/>
-      <c r="Z37" s="245"/>
-      <c r="AA37" s="245"/>
-      <c r="AB37" s="245"/>
-      <c r="AC37" s="245"/>
-      <c r="AD37" s="245"/>
-      <c r="AE37" s="245"/>
-      <c r="AF37" s="245"/>
-      <c r="AG37" s="245"/>
-      <c r="AH37" s="245"/>
-      <c r="AI37" s="245"/>
-      <c r="AJ37" s="245"/>
-      <c r="AK37" s="245"/>
-      <c r="AL37" s="245"/>
-      <c r="AM37" s="245"/>
-      <c r="AN37" s="245"/>
-      <c r="AO37" s="245"/>
-      <c r="AP37" s="245"/>
-      <c r="AQ37" s="245"/>
-      <c r="AR37" s="245"/>
-      <c r="AS37" s="245"/>
-      <c r="AT37" s="245"/>
-      <c r="AU37" s="245"/>
-      <c r="AV37" s="245"/>
-      <c r="AW37" s="245"/>
-      <c r="AX37" s="245"/>
-      <c r="AY37" s="245"/>
-      <c r="AZ37" s="246"/>
+      <c r="E37" s="256"/>
+      <c r="F37" s="256"/>
+      <c r="G37" s="256"/>
+      <c r="H37" s="256"/>
+      <c r="I37" s="256"/>
+      <c r="J37" s="256"/>
+      <c r="K37" s="256"/>
+      <c r="L37" s="256"/>
+      <c r="M37" s="256"/>
+      <c r="N37" s="256"/>
+      <c r="O37" s="256"/>
+      <c r="P37" s="256"/>
+      <c r="Q37" s="256"/>
+      <c r="R37" s="256"/>
+      <c r="S37" s="256"/>
+      <c r="T37" s="256"/>
+      <c r="U37" s="256"/>
+      <c r="V37" s="256"/>
+      <c r="W37" s="256"/>
+      <c r="X37" s="256"/>
+      <c r="Y37" s="256"/>
+      <c r="Z37" s="256"/>
+      <c r="AA37" s="256"/>
+      <c r="AB37" s="256"/>
+      <c r="AC37" s="256"/>
+      <c r="AD37" s="256"/>
+      <c r="AE37" s="256"/>
+      <c r="AF37" s="256"/>
+      <c r="AG37" s="256"/>
+      <c r="AH37" s="256"/>
+      <c r="AI37" s="256"/>
+      <c r="AJ37" s="256"/>
+      <c r="AK37" s="256"/>
+      <c r="AL37" s="256"/>
+      <c r="AM37" s="256"/>
+      <c r="AN37" s="256"/>
+      <c r="AO37" s="256"/>
+      <c r="AP37" s="256"/>
+      <c r="AQ37" s="256"/>
+      <c r="AR37" s="256"/>
+      <c r="AS37" s="256"/>
+      <c r="AT37" s="256"/>
+      <c r="AU37" s="256"/>
+      <c r="AV37" s="256"/>
+      <c r="AW37" s="256"/>
+      <c r="AX37" s="256"/>
+      <c r="AY37" s="256"/>
+      <c r="AZ37" s="257"/>
     </row>
     <row r="38" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="250"/>
-      <c r="B38" s="251"/>
-      <c r="C38" s="251"/>
+      <c r="A38" s="247"/>
+      <c r="B38" s="248"/>
+      <c r="C38" s="248"/>
       <c r="D38" s="10"/>
-      <c r="E38" s="245"/>
-      <c r="F38" s="245"/>
-      <c r="G38" s="245"/>
-      <c r="H38" s="245"/>
-      <c r="I38" s="245"/>
-      <c r="J38" s="245"/>
-      <c r="K38" s="245"/>
-      <c r="L38" s="245"/>
-      <c r="M38" s="245"/>
-      <c r="N38" s="245"/>
-      <c r="O38" s="245"/>
-      <c r="P38" s="245"/>
-      <c r="Q38" s="245"/>
-      <c r="R38" s="245"/>
-      <c r="S38" s="245"/>
-      <c r="T38" s="245"/>
-      <c r="U38" s="245"/>
-      <c r="V38" s="245"/>
-      <c r="W38" s="245"/>
-      <c r="X38" s="245"/>
-      <c r="Y38" s="245"/>
-      <c r="Z38" s="245"/>
-      <c r="AA38" s="245"/>
-      <c r="AB38" s="245"/>
-      <c r="AC38" s="245"/>
-      <c r="AD38" s="245"/>
-      <c r="AE38" s="245"/>
-      <c r="AF38" s="245"/>
-      <c r="AG38" s="245"/>
-      <c r="AH38" s="245"/>
-      <c r="AI38" s="245"/>
-      <c r="AJ38" s="245"/>
-      <c r="AK38" s="245"/>
-      <c r="AL38" s="245"/>
-      <c r="AM38" s="245"/>
-      <c r="AN38" s="245"/>
-      <c r="AO38" s="245"/>
-      <c r="AP38" s="245"/>
-      <c r="AQ38" s="245"/>
-      <c r="AR38" s="245"/>
-      <c r="AS38" s="245"/>
-      <c r="AT38" s="245"/>
-      <c r="AU38" s="245"/>
-      <c r="AV38" s="245"/>
-      <c r="AW38" s="245"/>
-      <c r="AX38" s="245"/>
-      <c r="AY38" s="245"/>
-      <c r="AZ38" s="246"/>
+      <c r="E38" s="256"/>
+      <c r="F38" s="256"/>
+      <c r="G38" s="256"/>
+      <c r="H38" s="256"/>
+      <c r="I38" s="256"/>
+      <c r="J38" s="256"/>
+      <c r="K38" s="256"/>
+      <c r="L38" s="256"/>
+      <c r="M38" s="256"/>
+      <c r="N38" s="256"/>
+      <c r="O38" s="256"/>
+      <c r="P38" s="256"/>
+      <c r="Q38" s="256"/>
+      <c r="R38" s="256"/>
+      <c r="S38" s="256"/>
+      <c r="T38" s="256"/>
+      <c r="U38" s="256"/>
+      <c r="V38" s="256"/>
+      <c r="W38" s="256"/>
+      <c r="X38" s="256"/>
+      <c r="Y38" s="256"/>
+      <c r="Z38" s="256"/>
+      <c r="AA38" s="256"/>
+      <c r="AB38" s="256"/>
+      <c r="AC38" s="256"/>
+      <c r="AD38" s="256"/>
+      <c r="AE38" s="256"/>
+      <c r="AF38" s="256"/>
+      <c r="AG38" s="256"/>
+      <c r="AH38" s="256"/>
+      <c r="AI38" s="256"/>
+      <c r="AJ38" s="256"/>
+      <c r="AK38" s="256"/>
+      <c r="AL38" s="256"/>
+      <c r="AM38" s="256"/>
+      <c r="AN38" s="256"/>
+      <c r="AO38" s="256"/>
+      <c r="AP38" s="256"/>
+      <c r="AQ38" s="256"/>
+      <c r="AR38" s="256"/>
+      <c r="AS38" s="256"/>
+      <c r="AT38" s="256"/>
+      <c r="AU38" s="256"/>
+      <c r="AV38" s="256"/>
+      <c r="AW38" s="256"/>
+      <c r="AX38" s="256"/>
+      <c r="AY38" s="256"/>
+      <c r="AZ38" s="257"/>
     </row>
     <row r="39" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="250"/>
-      <c r="B39" s="251"/>
-      <c r="C39" s="251"/>
+      <c r="A39" s="247"/>
+      <c r="B39" s="248"/>
+      <c r="C39" s="248"/>
       <c r="D39" s="10"/>
-      <c r="E39" s="245"/>
-      <c r="F39" s="245"/>
-      <c r="G39" s="245"/>
-      <c r="H39" s="245"/>
-      <c r="I39" s="245"/>
-      <c r="J39" s="245"/>
-      <c r="K39" s="245"/>
-      <c r="L39" s="245"/>
-      <c r="M39" s="245"/>
-      <c r="N39" s="245"/>
-      <c r="O39" s="245"/>
-      <c r="P39" s="245"/>
-      <c r="Q39" s="245"/>
-      <c r="R39" s="245"/>
-      <c r="S39" s="245"/>
-      <c r="T39" s="245"/>
-      <c r="U39" s="245"/>
-      <c r="V39" s="245"/>
-      <c r="W39" s="245"/>
-      <c r="X39" s="245"/>
-      <c r="Y39" s="245"/>
-      <c r="Z39" s="245"/>
-      <c r="AA39" s="245"/>
-      <c r="AB39" s="245"/>
-      <c r="AC39" s="245"/>
-      <c r="AD39" s="245"/>
-      <c r="AE39" s="245"/>
-      <c r="AF39" s="245"/>
-      <c r="AG39" s="245"/>
-      <c r="AH39" s="245"/>
-      <c r="AI39" s="245"/>
-      <c r="AJ39" s="245"/>
-      <c r="AK39" s="245"/>
-      <c r="AL39" s="245"/>
-      <c r="AM39" s="245"/>
-      <c r="AN39" s="245"/>
-      <c r="AO39" s="245"/>
-      <c r="AP39" s="245"/>
-      <c r="AQ39" s="245"/>
-      <c r="AR39" s="245"/>
-      <c r="AS39" s="245"/>
-      <c r="AT39" s="245"/>
-      <c r="AU39" s="245"/>
-      <c r="AV39" s="245"/>
-      <c r="AW39" s="245"/>
-      <c r="AX39" s="245"/>
-      <c r="AY39" s="245"/>
-      <c r="AZ39" s="246"/>
+      <c r="E39" s="256"/>
+      <c r="F39" s="256"/>
+      <c r="G39" s="256"/>
+      <c r="H39" s="256"/>
+      <c r="I39" s="256"/>
+      <c r="J39" s="256"/>
+      <c r="K39" s="256"/>
+      <c r="L39" s="256"/>
+      <c r="M39" s="256"/>
+      <c r="N39" s="256"/>
+      <c r="O39" s="256"/>
+      <c r="P39" s="256"/>
+      <c r="Q39" s="256"/>
+      <c r="R39" s="256"/>
+      <c r="S39" s="256"/>
+      <c r="T39" s="256"/>
+      <c r="U39" s="256"/>
+      <c r="V39" s="256"/>
+      <c r="W39" s="256"/>
+      <c r="X39" s="256"/>
+      <c r="Y39" s="256"/>
+      <c r="Z39" s="256"/>
+      <c r="AA39" s="256"/>
+      <c r="AB39" s="256"/>
+      <c r="AC39" s="256"/>
+      <c r="AD39" s="256"/>
+      <c r="AE39" s="256"/>
+      <c r="AF39" s="256"/>
+      <c r="AG39" s="256"/>
+      <c r="AH39" s="256"/>
+      <c r="AI39" s="256"/>
+      <c r="AJ39" s="256"/>
+      <c r="AK39" s="256"/>
+      <c r="AL39" s="256"/>
+      <c r="AM39" s="256"/>
+      <c r="AN39" s="256"/>
+      <c r="AO39" s="256"/>
+      <c r="AP39" s="256"/>
+      <c r="AQ39" s="256"/>
+      <c r="AR39" s="256"/>
+      <c r="AS39" s="256"/>
+      <c r="AT39" s="256"/>
+      <c r="AU39" s="256"/>
+      <c r="AV39" s="256"/>
+      <c r="AW39" s="256"/>
+      <c r="AX39" s="256"/>
+      <c r="AY39" s="256"/>
+      <c r="AZ39" s="257"/>
     </row>
     <row r="40" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="250"/>
-      <c r="B40" s="251"/>
-      <c r="C40" s="251"/>
+      <c r="A40" s="247"/>
+      <c r="B40" s="248"/>
+      <c r="C40" s="248"/>
       <c r="D40" s="10"/>
-      <c r="E40" s="245"/>
-      <c r="F40" s="245"/>
-      <c r="G40" s="245"/>
-      <c r="H40" s="245"/>
-      <c r="I40" s="245"/>
-      <c r="J40" s="245"/>
-      <c r="K40" s="245"/>
-      <c r="L40" s="245"/>
-      <c r="M40" s="245"/>
-      <c r="N40" s="245"/>
-      <c r="O40" s="245"/>
-      <c r="P40" s="245"/>
-      <c r="Q40" s="245"/>
-      <c r="R40" s="245"/>
-      <c r="S40" s="245"/>
-      <c r="T40" s="245"/>
-      <c r="U40" s="245"/>
-      <c r="V40" s="245"/>
-      <c r="W40" s="245"/>
-      <c r="X40" s="245"/>
-      <c r="Y40" s="245"/>
-      <c r="Z40" s="245"/>
-      <c r="AA40" s="245"/>
-      <c r="AB40" s="245"/>
-      <c r="AC40" s="245"/>
-      <c r="AD40" s="245"/>
-      <c r="AE40" s="245"/>
-      <c r="AF40" s="245"/>
-      <c r="AG40" s="245"/>
-      <c r="AH40" s="245"/>
-      <c r="AI40" s="245"/>
-      <c r="AJ40" s="245"/>
-      <c r="AK40" s="245"/>
-      <c r="AL40" s="245"/>
-      <c r="AM40" s="245"/>
-      <c r="AN40" s="245"/>
-      <c r="AO40" s="245"/>
-      <c r="AP40" s="245"/>
-      <c r="AQ40" s="245"/>
-      <c r="AR40" s="245"/>
-      <c r="AS40" s="245"/>
-      <c r="AT40" s="245"/>
-      <c r="AU40" s="245"/>
-      <c r="AV40" s="245"/>
-      <c r="AW40" s="245"/>
-      <c r="AX40" s="245"/>
-      <c r="AY40" s="245"/>
-      <c r="AZ40" s="246"/>
+      <c r="E40" s="256"/>
+      <c r="F40" s="256"/>
+      <c r="G40" s="256"/>
+      <c r="H40" s="256"/>
+      <c r="I40" s="256"/>
+      <c r="J40" s="256"/>
+      <c r="K40" s="256"/>
+      <c r="L40" s="256"/>
+      <c r="M40" s="256"/>
+      <c r="N40" s="256"/>
+      <c r="O40" s="256"/>
+      <c r="P40" s="256"/>
+      <c r="Q40" s="256"/>
+      <c r="R40" s="256"/>
+      <c r="S40" s="256"/>
+      <c r="T40" s="256"/>
+      <c r="U40" s="256"/>
+      <c r="V40" s="256"/>
+      <c r="W40" s="256"/>
+      <c r="X40" s="256"/>
+      <c r="Y40" s="256"/>
+      <c r="Z40" s="256"/>
+      <c r="AA40" s="256"/>
+      <c r="AB40" s="256"/>
+      <c r="AC40" s="256"/>
+      <c r="AD40" s="256"/>
+      <c r="AE40" s="256"/>
+      <c r="AF40" s="256"/>
+      <c r="AG40" s="256"/>
+      <c r="AH40" s="256"/>
+      <c r="AI40" s="256"/>
+      <c r="AJ40" s="256"/>
+      <c r="AK40" s="256"/>
+      <c r="AL40" s="256"/>
+      <c r="AM40" s="256"/>
+      <c r="AN40" s="256"/>
+      <c r="AO40" s="256"/>
+      <c r="AP40" s="256"/>
+      <c r="AQ40" s="256"/>
+      <c r="AR40" s="256"/>
+      <c r="AS40" s="256"/>
+      <c r="AT40" s="256"/>
+      <c r="AU40" s="256"/>
+      <c r="AV40" s="256"/>
+      <c r="AW40" s="256"/>
+      <c r="AX40" s="256"/>
+      <c r="AY40" s="256"/>
+      <c r="AZ40" s="257"/>
     </row>
     <row r="41" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="250"/>
-      <c r="B41" s="251"/>
-      <c r="C41" s="251"/>
+      <c r="A41" s="247"/>
+      <c r="B41" s="248"/>
+      <c r="C41" s="248"/>
       <c r="D41" s="10"/>
-      <c r="E41" s="245"/>
-      <c r="F41" s="245"/>
-      <c r="G41" s="245"/>
-      <c r="H41" s="245"/>
-      <c r="I41" s="245"/>
-      <c r="J41" s="245"/>
-      <c r="K41" s="245"/>
-      <c r="L41" s="245"/>
-      <c r="M41" s="245"/>
-      <c r="N41" s="245"/>
-      <c r="O41" s="245"/>
-      <c r="P41" s="245"/>
-      <c r="Q41" s="245"/>
-      <c r="R41" s="245"/>
-      <c r="S41" s="245"/>
-      <c r="T41" s="245"/>
-      <c r="U41" s="245"/>
-      <c r="V41" s="245"/>
-      <c r="W41" s="245"/>
-      <c r="X41" s="245"/>
-      <c r="Y41" s="245"/>
-      <c r="Z41" s="245"/>
-      <c r="AA41" s="245"/>
-      <c r="AB41" s="245"/>
-      <c r="AC41" s="245"/>
-      <c r="AD41" s="245"/>
-      <c r="AE41" s="245"/>
-      <c r="AF41" s="245"/>
-      <c r="AG41" s="245"/>
-      <c r="AH41" s="245"/>
-      <c r="AI41" s="245"/>
-      <c r="AJ41" s="245"/>
-      <c r="AK41" s="245"/>
-      <c r="AL41" s="245"/>
-      <c r="AM41" s="245"/>
-      <c r="AN41" s="245"/>
-      <c r="AO41" s="245"/>
-      <c r="AP41" s="245"/>
-      <c r="AQ41" s="245"/>
-      <c r="AR41" s="245"/>
-      <c r="AS41" s="245"/>
-      <c r="AT41" s="245"/>
-      <c r="AU41" s="245"/>
-      <c r="AV41" s="245"/>
-      <c r="AW41" s="245"/>
-      <c r="AX41" s="245"/>
-      <c r="AY41" s="245"/>
-      <c r="AZ41" s="246"/>
+      <c r="E41" s="256"/>
+      <c r="F41" s="256"/>
+      <c r="G41" s="256"/>
+      <c r="H41" s="256"/>
+      <c r="I41" s="256"/>
+      <c r="J41" s="256"/>
+      <c r="K41" s="256"/>
+      <c r="L41" s="256"/>
+      <c r="M41" s="256"/>
+      <c r="N41" s="256"/>
+      <c r="O41" s="256"/>
+      <c r="P41" s="256"/>
+      <c r="Q41" s="256"/>
+      <c r="R41" s="256"/>
+      <c r="S41" s="256"/>
+      <c r="T41" s="256"/>
+      <c r="U41" s="256"/>
+      <c r="V41" s="256"/>
+      <c r="W41" s="256"/>
+      <c r="X41" s="256"/>
+      <c r="Y41" s="256"/>
+      <c r="Z41" s="256"/>
+      <c r="AA41" s="256"/>
+      <c r="AB41" s="256"/>
+      <c r="AC41" s="256"/>
+      <c r="AD41" s="256"/>
+      <c r="AE41" s="256"/>
+      <c r="AF41" s="256"/>
+      <c r="AG41" s="256"/>
+      <c r="AH41" s="256"/>
+      <c r="AI41" s="256"/>
+      <c r="AJ41" s="256"/>
+      <c r="AK41" s="256"/>
+      <c r="AL41" s="256"/>
+      <c r="AM41" s="256"/>
+      <c r="AN41" s="256"/>
+      <c r="AO41" s="256"/>
+      <c r="AP41" s="256"/>
+      <c r="AQ41" s="256"/>
+      <c r="AR41" s="256"/>
+      <c r="AS41" s="256"/>
+      <c r="AT41" s="256"/>
+      <c r="AU41" s="256"/>
+      <c r="AV41" s="256"/>
+      <c r="AW41" s="256"/>
+      <c r="AX41" s="256"/>
+      <c r="AY41" s="256"/>
+      <c r="AZ41" s="257"/>
     </row>
     <row r="42" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="250"/>
-      <c r="B42" s="251"/>
-      <c r="C42" s="251"/>
+      <c r="A42" s="247"/>
+      <c r="B42" s="248"/>
+      <c r="C42" s="248"/>
       <c r="D42" s="10"/>
-      <c r="E42" s="245"/>
-      <c r="F42" s="245"/>
-      <c r="G42" s="245"/>
-      <c r="H42" s="245"/>
-      <c r="I42" s="245"/>
-      <c r="J42" s="245"/>
-      <c r="K42" s="245"/>
-      <c r="L42" s="245"/>
-      <c r="M42" s="245"/>
-      <c r="N42" s="245"/>
-      <c r="O42" s="245"/>
-      <c r="P42" s="245"/>
-      <c r="Q42" s="245"/>
-      <c r="R42" s="245"/>
-      <c r="S42" s="245"/>
-      <c r="T42" s="245"/>
-      <c r="U42" s="245"/>
-      <c r="V42" s="245"/>
-      <c r="W42" s="245"/>
-      <c r="X42" s="245"/>
-      <c r="Y42" s="245"/>
-      <c r="Z42" s="245"/>
-      <c r="AA42" s="245"/>
-      <c r="AB42" s="245"/>
-      <c r="AC42" s="245"/>
-      <c r="AD42" s="245"/>
-      <c r="AE42" s="245"/>
-      <c r="AF42" s="245"/>
-      <c r="AG42" s="245"/>
-      <c r="AH42" s="245"/>
-      <c r="AI42" s="245"/>
-      <c r="AJ42" s="245"/>
-      <c r="AK42" s="245"/>
-      <c r="AL42" s="245"/>
-      <c r="AM42" s="245"/>
-      <c r="AN42" s="245"/>
-      <c r="AO42" s="245"/>
-      <c r="AP42" s="245"/>
-      <c r="AQ42" s="245"/>
-      <c r="AR42" s="245"/>
-      <c r="AS42" s="245"/>
-      <c r="AT42" s="245"/>
-      <c r="AU42" s="245"/>
-      <c r="AV42" s="245"/>
-      <c r="AW42" s="245"/>
-      <c r="AX42" s="245"/>
-      <c r="AY42" s="245"/>
-      <c r="AZ42" s="246"/>
+      <c r="E42" s="256"/>
+      <c r="F42" s="256"/>
+      <c r="G42" s="256"/>
+      <c r="H42" s="256"/>
+      <c r="I42" s="256"/>
+      <c r="J42" s="256"/>
+      <c r="K42" s="256"/>
+      <c r="L42" s="256"/>
+      <c r="M42" s="256"/>
+      <c r="N42" s="256"/>
+      <c r="O42" s="256"/>
+      <c r="P42" s="256"/>
+      <c r="Q42" s="256"/>
+      <c r="R42" s="256"/>
+      <c r="S42" s="256"/>
+      <c r="T42" s="256"/>
+      <c r="U42" s="256"/>
+      <c r="V42" s="256"/>
+      <c r="W42" s="256"/>
+      <c r="X42" s="256"/>
+      <c r="Y42" s="256"/>
+      <c r="Z42" s="256"/>
+      <c r="AA42" s="256"/>
+      <c r="AB42" s="256"/>
+      <c r="AC42" s="256"/>
+      <c r="AD42" s="256"/>
+      <c r="AE42" s="256"/>
+      <c r="AF42" s="256"/>
+      <c r="AG42" s="256"/>
+      <c r="AH42" s="256"/>
+      <c r="AI42" s="256"/>
+      <c r="AJ42" s="256"/>
+      <c r="AK42" s="256"/>
+      <c r="AL42" s="256"/>
+      <c r="AM42" s="256"/>
+      <c r="AN42" s="256"/>
+      <c r="AO42" s="256"/>
+      <c r="AP42" s="256"/>
+      <c r="AQ42" s="256"/>
+      <c r="AR42" s="256"/>
+      <c r="AS42" s="256"/>
+      <c r="AT42" s="256"/>
+      <c r="AU42" s="256"/>
+      <c r="AV42" s="256"/>
+      <c r="AW42" s="256"/>
+      <c r="AX42" s="256"/>
+      <c r="AY42" s="256"/>
+      <c r="AZ42" s="257"/>
     </row>
     <row r="43" spans="1:53" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="62"/>
@@ -12178,181 +12164,226 @@
       <c r="AZ44"/>
     </row>
     <row r="45" spans="1:53" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="149"/>
-      <c r="B45" s="149"/>
-      <c r="C45" s="149"/>
-      <c r="D45" s="149"/>
-      <c r="E45" s="149"/>
-      <c r="F45" s="149"/>
-      <c r="G45" s="149"/>
-      <c r="H45" s="149"/>
-      <c r="I45" s="149"/>
-      <c r="J45" s="149"/>
-      <c r="K45" s="149"/>
-      <c r="L45" s="149"/>
-      <c r="M45" s="149"/>
-      <c r="N45" s="149"/>
-      <c r="O45" s="149"/>
-      <c r="P45" s="149"/>
+      <c r="A45" s="117"/>
+      <c r="B45" s="117"/>
+      <c r="C45" s="117"/>
+      <c r="D45" s="117"/>
+      <c r="E45" s="117"/>
+      <c r="F45" s="117"/>
+      <c r="G45" s="117"/>
+      <c r="H45" s="117"/>
+      <c r="I45" s="117"/>
+      <c r="J45" s="117"/>
+      <c r="K45" s="117"/>
+      <c r="L45" s="117"/>
+      <c r="M45" s="117"/>
+      <c r="N45" s="117"/>
+      <c r="O45" s="117"/>
+      <c r="P45" s="117"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
-      <c r="S45" s="149"/>
-      <c r="T45" s="149"/>
-      <c r="U45" s="149"/>
-      <c r="V45" s="149"/>
-      <c r="W45" s="149"/>
-      <c r="X45" s="149"/>
-      <c r="Y45" s="149"/>
-      <c r="Z45" s="149"/>
-      <c r="AA45" s="149"/>
-      <c r="AB45" s="149"/>
-      <c r="AC45" s="149"/>
-      <c r="AD45" s="149"/>
-      <c r="AE45" s="149"/>
-      <c r="AF45" s="149"/>
-      <c r="AG45" s="149"/>
-      <c r="AH45" s="149"/>
+      <c r="S45" s="117"/>
+      <c r="T45" s="117"/>
+      <c r="U45" s="117"/>
+      <c r="V45" s="117"/>
+      <c r="W45" s="117"/>
+      <c r="X45" s="117"/>
+      <c r="Y45" s="117"/>
+      <c r="Z45" s="117"/>
+      <c r="AA45" s="117"/>
+      <c r="AB45" s="117"/>
+      <c r="AC45" s="117"/>
+      <c r="AD45" s="117"/>
+      <c r="AE45" s="117"/>
+      <c r="AF45" s="117"/>
+      <c r="AG45" s="117"/>
+      <c r="AH45" s="117"/>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
-      <c r="AK45" s="149"/>
-      <c r="AL45" s="149"/>
-      <c r="AM45" s="149"/>
-      <c r="AN45" s="149"/>
-      <c r="AO45" s="149"/>
-      <c r="AP45" s="149"/>
-      <c r="AQ45" s="149"/>
-      <c r="AR45" s="149"/>
-      <c r="AS45" s="149"/>
-      <c r="AT45" s="149"/>
-      <c r="AU45" s="149"/>
-      <c r="AV45" s="149"/>
-      <c r="AW45" s="149"/>
-      <c r="AX45" s="149"/>
-      <c r="AY45" s="149"/>
-      <c r="AZ45" s="149"/>
+      <c r="AK45" s="117"/>
+      <c r="AL45" s="117"/>
+      <c r="AM45" s="117"/>
+      <c r="AN45" s="117"/>
+      <c r="AO45" s="117"/>
+      <c r="AP45" s="117"/>
+      <c r="AQ45" s="117"/>
+      <c r="AR45" s="117"/>
+      <c r="AS45" s="117"/>
+      <c r="AT45" s="117"/>
+      <c r="AU45" s="117"/>
+      <c r="AV45" s="117"/>
+      <c r="AW45" s="117"/>
+      <c r="AX45" s="117"/>
+      <c r="AY45" s="117"/>
+      <c r="AZ45" s="117"/>
     </row>
     <row r="46" spans="1:53" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="213" t="s">
+      <c r="A46" s="118" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="213"/>
-      <c r="C46" s="213"/>
-      <c r="D46" s="213"/>
-      <c r="E46" s="213"/>
-      <c r="F46" s="213"/>
-      <c r="G46" s="213"/>
-      <c r="H46" s="213"/>
-      <c r="I46" s="213"/>
-      <c r="J46" s="213"/>
-      <c r="K46" s="213"/>
-      <c r="L46" s="213"/>
-      <c r="M46" s="213"/>
-      <c r="N46" s="213"/>
-      <c r="O46" s="213"/>
-      <c r="P46" s="213"/>
+      <c r="B46" s="118"/>
+      <c r="C46" s="118"/>
+      <c r="D46" s="118"/>
+      <c r="E46" s="118"/>
+      <c r="F46" s="118"/>
+      <c r="G46" s="118"/>
+      <c r="H46" s="118"/>
+      <c r="I46" s="118"/>
+      <c r="J46" s="118"/>
+      <c r="K46" s="118"/>
+      <c r="L46" s="118"/>
+      <c r="M46" s="118"/>
+      <c r="N46" s="118"/>
+      <c r="O46" s="118"/>
+      <c r="P46" s="118"/>
       <c r="Q46" s="54"/>
       <c r="R46" s="54"/>
-      <c r="S46" s="124" t="s">
+      <c r="S46" s="195" t="s">
         <v>78</v>
       </c>
-      <c r="T46" s="124"/>
-      <c r="U46" s="124"/>
-      <c r="V46" s="124"/>
-      <c r="W46" s="124"/>
-      <c r="X46" s="124"/>
-      <c r="Y46" s="124"/>
-      <c r="Z46" s="124"/>
-      <c r="AA46" s="124"/>
-      <c r="AB46" s="124"/>
-      <c r="AC46" s="124"/>
-      <c r="AD46" s="124"/>
-      <c r="AE46" s="124"/>
-      <c r="AF46" s="124"/>
-      <c r="AG46" s="124"/>
-      <c r="AH46" s="124"/>
+      <c r="T46" s="195"/>
+      <c r="U46" s="195"/>
+      <c r="V46" s="195"/>
+      <c r="W46" s="195"/>
+      <c r="X46" s="195"/>
+      <c r="Y46" s="195"/>
+      <c r="Z46" s="195"/>
+      <c r="AA46" s="195"/>
+      <c r="AB46" s="195"/>
+      <c r="AC46" s="195"/>
+      <c r="AD46" s="195"/>
+      <c r="AE46" s="195"/>
+      <c r="AF46" s="195"/>
+      <c r="AG46" s="195"/>
+      <c r="AH46" s="195"/>
       <c r="AI46" s="54"/>
       <c r="AJ46" s="54"/>
-      <c r="AK46" s="213" t="s">
+      <c r="AK46" s="118" t="s">
         <v>79</v>
       </c>
-      <c r="AL46" s="213"/>
-      <c r="AM46" s="213"/>
-      <c r="AN46" s="213"/>
-      <c r="AO46" s="213"/>
-      <c r="AP46" s="213"/>
-      <c r="AQ46" s="213"/>
-      <c r="AR46" s="213"/>
-      <c r="AS46" s="213"/>
-      <c r="AT46" s="213"/>
-      <c r="AU46" s="213"/>
-      <c r="AV46" s="213"/>
-      <c r="AW46" s="213"/>
-      <c r="AX46" s="213"/>
-      <c r="AY46" s="213"/>
-      <c r="AZ46" s="213"/>
+      <c r="AL46" s="118"/>
+      <c r="AM46" s="118"/>
+      <c r="AN46" s="118"/>
+      <c r="AO46" s="118"/>
+      <c r="AP46" s="118"/>
+      <c r="AQ46" s="118"/>
+      <c r="AR46" s="118"/>
+      <c r="AS46" s="118"/>
+      <c r="AT46" s="118"/>
+      <c r="AU46" s="118"/>
+      <c r="AV46" s="118"/>
+      <c r="AW46" s="118"/>
+      <c r="AX46" s="118"/>
+      <c r="AY46" s="118"/>
+      <c r="AZ46" s="118"/>
     </row>
     <row r="47" spans="1:53" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="247"/>
-      <c r="B47" s="247"/>
-      <c r="C47" s="247"/>
-      <c r="D47" s="247"/>
-      <c r="E47" s="247"/>
-      <c r="F47" s="247"/>
-      <c r="G47" s="247"/>
-      <c r="H47" s="247"/>
-      <c r="I47" s="247"/>
-      <c r="J47" s="247"/>
-      <c r="K47" s="247"/>
-      <c r="L47" s="247"/>
-      <c r="M47" s="247"/>
-      <c r="N47" s="247"/>
-      <c r="O47" s="247"/>
-      <c r="P47" s="247"/>
-      <c r="S47" s="247"/>
-      <c r="T47" s="247"/>
-      <c r="U47" s="247"/>
-      <c r="V47" s="248"/>
-      <c r="W47" s="249"/>
-      <c r="X47" s="249"/>
-      <c r="Y47" s="249"/>
-      <c r="Z47" s="249"/>
-      <c r="AA47" s="249"/>
-      <c r="AB47" s="249"/>
-      <c r="AC47" s="249"/>
-      <c r="AD47" s="249"/>
-      <c r="AE47" s="249"/>
-      <c r="AF47" s="249"/>
-      <c r="AG47" s="249"/>
-      <c r="AH47" s="249"/>
-      <c r="AK47" s="214" t="s">
+      <c r="A47" s="258"/>
+      <c r="B47" s="258"/>
+      <c r="C47" s="258"/>
+      <c r="D47" s="258"/>
+      <c r="E47" s="258"/>
+      <c r="F47" s="258"/>
+      <c r="G47" s="258"/>
+      <c r="H47" s="258"/>
+      <c r="I47" s="258"/>
+      <c r="J47" s="258"/>
+      <c r="K47" s="258"/>
+      <c r="L47" s="258"/>
+      <c r="M47" s="258"/>
+      <c r="N47" s="258"/>
+      <c r="O47" s="258"/>
+      <c r="P47" s="258"/>
+      <c r="S47" s="258"/>
+      <c r="T47" s="258"/>
+      <c r="U47" s="258"/>
+      <c r="V47" s="259"/>
+      <c r="W47" s="260"/>
+      <c r="X47" s="260"/>
+      <c r="Y47" s="260"/>
+      <c r="Z47" s="260"/>
+      <c r="AA47" s="260"/>
+      <c r="AB47" s="260"/>
+      <c r="AC47" s="260"/>
+      <c r="AD47" s="260"/>
+      <c r="AE47" s="260"/>
+      <c r="AF47" s="260"/>
+      <c r="AG47" s="260"/>
+      <c r="AH47" s="260"/>
+      <c r="AK47" s="119" t="s">
         <v>792</v>
       </c>
-      <c r="AL47" s="214"/>
-      <c r="AM47" s="214"/>
-      <c r="AN47" s="214"/>
-      <c r="AO47" s="214"/>
-      <c r="AP47" s="214"/>
-      <c r="AQ47" s="214"/>
-      <c r="AR47" s="214"/>
-      <c r="AS47" s="214"/>
-      <c r="AT47" s="214"/>
-      <c r="AU47" s="214"/>
-      <c r="AV47" s="214"/>
-      <c r="AW47" s="214"/>
-      <c r="AX47" s="214"/>
-      <c r="AY47" s="214"/>
-      <c r="AZ47" s="214"/>
+      <c r="AL47" s="119"/>
+      <c r="AM47" s="119"/>
+      <c r="AN47" s="119"/>
+      <c r="AO47" s="119"/>
+      <c r="AP47" s="119"/>
+      <c r="AQ47" s="119"/>
+      <c r="AR47" s="119"/>
+      <c r="AS47" s="119"/>
+      <c r="AT47" s="119"/>
+      <c r="AU47" s="119"/>
+      <c r="AV47" s="119"/>
+      <c r="AW47" s="119"/>
+      <c r="AX47" s="119"/>
+      <c r="AY47" s="119"/>
+      <c r="AZ47" s="119"/>
     </row>
     <row r="48" spans="1:53" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E30:AZ30"/>
+    <mergeCell ref="E31:AZ31"/>
+    <mergeCell ref="E32:AZ32"/>
+    <mergeCell ref="E26:AZ26"/>
+    <mergeCell ref="E27:AZ27"/>
+    <mergeCell ref="E28:AZ28"/>
+    <mergeCell ref="E29:AZ29"/>
+    <mergeCell ref="A46:P46"/>
+    <mergeCell ref="S46:AH46"/>
+    <mergeCell ref="AK46:AZ46"/>
+    <mergeCell ref="A47:P47"/>
+    <mergeCell ref="AK47:AZ47"/>
+    <mergeCell ref="S47:U47"/>
+    <mergeCell ref="V47:AH47"/>
+    <mergeCell ref="E42:AZ42"/>
+    <mergeCell ref="E39:AZ39"/>
+    <mergeCell ref="E40:AZ40"/>
+    <mergeCell ref="E41:AZ41"/>
+    <mergeCell ref="E38:AZ38"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="E9:AZ9"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="E33:AZ33"/>
+    <mergeCell ref="E34:AZ34"/>
+    <mergeCell ref="E37:AZ37"/>
+    <mergeCell ref="E35:AZ35"/>
+    <mergeCell ref="E36:AZ36"/>
+    <mergeCell ref="A4:AZ4"/>
+    <mergeCell ref="K2:AP2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="E6:AZ6"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="AS1:AZ3"/>
+    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A45:P45"/>
     <mergeCell ref="S45:AH45"/>
@@ -12369,56 +12400,11 @@
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A4:AZ4"/>
-    <mergeCell ref="K2:AP2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="E6:AZ6"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="AS1:AZ3"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="E9:AZ9"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="E33:AZ33"/>
-    <mergeCell ref="E34:AZ34"/>
-    <mergeCell ref="E37:AZ37"/>
-    <mergeCell ref="E35:AZ35"/>
-    <mergeCell ref="E36:AZ36"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="E42:AZ42"/>
-    <mergeCell ref="E39:AZ39"/>
-    <mergeCell ref="E40:AZ40"/>
-    <mergeCell ref="E41:AZ41"/>
-    <mergeCell ref="E38:AZ38"/>
-    <mergeCell ref="A46:P46"/>
-    <mergeCell ref="S46:AH46"/>
-    <mergeCell ref="AK46:AZ46"/>
-    <mergeCell ref="A47:P47"/>
-    <mergeCell ref="AK47:AZ47"/>
-    <mergeCell ref="S47:U47"/>
-    <mergeCell ref="V47:AH47"/>
-    <mergeCell ref="E30:AZ30"/>
-    <mergeCell ref="E31:AZ31"/>
-    <mergeCell ref="E32:AZ32"/>
-    <mergeCell ref="E26:AZ26"/>
-    <mergeCell ref="E27:AZ27"/>
-    <mergeCell ref="E28:AZ28"/>
-    <mergeCell ref="E29:AZ29"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -19469,6 +19455,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c24bca33-91ee-4c94-9d6c-305b441d02fd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e46781df-dd49-4a0f-be02-040bfbf345c5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2EBC4C97F3EED4F8F99B50CD61D9AF7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0ffa3ef56536b291ffb1e746207cdfaf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e46781df-dd49-4a0f-be02-040bfbf345c5" xmlns:ns3="c24bca33-91ee-4c94-9d6c-305b441d02fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="82d71f54c8a292e50b13588301f7fd2c" ns2:_="" ns3:_="">
     <xsd:import namespace="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
@@ -19697,27 +19703,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c24bca33-91ee-4c94-9d6c-305b441d02fd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e46781df-dd49-4a0f-be02-040bfbf345c5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA908177-54FE-4386-8E64-F855D4FAA630}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F87E2A-9E0E-44C0-A603-7E661F8ABEB3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c24bca33-91ee-4c94-9d6c-305b441d02fd"/>
+    <ds:schemaRef ds:uri="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDAB891A-AABF-4B04-8872-1A9CED3578DB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19734,23 +19739,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F87E2A-9E0E-44C0-A603-7E661F8ABEB3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c24bca33-91ee-4c94-9d6c-305b441d02fd"/>
-    <ds:schemaRef ds:uri="e46781df-dd49-4a0f-be02-040bfbf345c5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA908177-54FE-4386-8E64-F855D4FAA630}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>